--- a/reports/watchlist_history.xlsx
+++ b/reports/watchlist_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="71">
   <si>
     <t>Date</t>
   </si>
@@ -64,115 +64,169 @@
     <t>FII Cr</t>
   </si>
   <si>
+    <t>20260422</t>
+  </si>
+  <si>
+    <t>APARINDS</t>
+  </si>
+  <si>
+    <t>STARHEALTH</t>
+  </si>
+  <si>
+    <t>TORNTPOWER</t>
+  </si>
+  <si>
+    <t>UNIONBANK</t>
+  </si>
+  <si>
+    <t>ANURAS</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>TITAN</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
+    <t>NATCOPHARM</t>
+  </si>
+  <si>
+    <t>SONACOMS</t>
+  </si>
+  <si>
+    <t>BAJAJCON</t>
+  </si>
+  <si>
+    <t>DCBBANK</t>
+  </si>
+  <si>
+    <t>SCHAEFFLER</t>
+  </si>
+  <si>
+    <t>NAVINFLUOR</t>
+  </si>
+  <si>
+    <t>CCL</t>
+  </si>
+  <si>
+    <t>NESTLEIND</t>
+  </si>
+  <si>
+    <t>BAJAJ-AUTO</t>
+  </si>
+  <si>
+    <t>POLYCAB</t>
+  </si>
+  <si>
+    <t>ABSLAMC</t>
+  </si>
+  <si>
+    <t>PNBHOUSING</t>
+  </si>
+  <si>
+    <t>POWERGRID</t>
+  </si>
+  <si>
+    <t>MARICO</t>
+  </si>
+  <si>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>SIEMENS</t>
+  </si>
+  <si>
+    <t>ADANIPOWER</t>
+  </si>
+  <si>
+    <t>NMDC</t>
+  </si>
+  <si>
+    <t>JINDALSTEL</t>
+  </si>
+  <si>
+    <t>ICICIB22</t>
+  </si>
+  <si>
+    <t>ADANIGREEN</t>
+  </si>
+  <si>
+    <t>LUPIN</t>
+  </si>
+  <si>
+    <t>TVSMOTOR</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>GOLDBEES</t>
+  </si>
+  <si>
+    <t>BUY</t>
+  </si>
+  <si>
+    <t>WATCH</t>
+  </si>
+  <si>
+    <t>+0.0</t>
+  </si>
+  <si>
+    <t>+7.8</t>
+  </si>
+  <si>
+    <t>-0.5</t>
+  </si>
+  <si>
+    <t>-6.5</t>
+  </si>
+  <si>
+    <t>-2.9</t>
+  </si>
+  <si>
+    <t>Stage 2 — Uptrend ✓</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>VCP incomplete — price range still wide, wait for tighter base (3 contractions)</t>
+  </si>
+  <si>
+    <t>Price below 100/200 DMA — wait for MA alignment</t>
+  </si>
+  <si>
+    <t>VCP incomplete — price range still wide, wait for tighter base (3 contractions),</t>
+  </si>
+  <si>
+    <t>Score 65/100 — need macro improvement or volume surge</t>
+  </si>
+  <si>
+    <t>Price below 100/200 DMA — wait for MA alignment, RSI outside 50-70 zone</t>
+  </si>
+  <si>
     <t>20260421</t>
   </si>
   <si>
-    <t>APARINDS</t>
-  </si>
-  <si>
-    <t>STARHEALTH</t>
-  </si>
-  <si>
-    <t>TORNTPOWER</t>
-  </si>
-  <si>
-    <t>UNIONBANK</t>
-  </si>
-  <si>
-    <t>ANURAS</t>
-  </si>
-  <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>TITAN</t>
-  </si>
-  <si>
-    <t>SHRIRAMFIN</t>
-  </si>
-  <si>
-    <t>NATCOPHARM</t>
-  </si>
-  <si>
-    <t>SONACOMS</t>
-  </si>
-  <si>
-    <t>BAJAJCON</t>
-  </si>
-  <si>
-    <t>DCBBANK</t>
-  </si>
-  <si>
-    <t>SCHAEFFLER</t>
-  </si>
-  <si>
-    <t>NAVINFLUOR</t>
-  </si>
-  <si>
-    <t>CCL</t>
-  </si>
-  <si>
-    <t>NESTLEIND</t>
-  </si>
-  <si>
-    <t>BAJAJ-AUTO</t>
-  </si>
-  <si>
-    <t>POLYCAB</t>
-  </si>
-  <si>
-    <t>ABSLAMC</t>
-  </si>
-  <si>
-    <t>PNBHOUSING</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>BUY</t>
-  </si>
-  <si>
-    <t>WATCH</t>
-  </si>
-  <si>
-    <t>+0.0</t>
-  </si>
-  <si>
-    <t>-0.5</t>
-  </si>
-  <si>
-    <t>Stage 2 — Uptrend ✓</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>VCP incomplete — price range still wide, wait for tighter base (3 contractions)</t>
-  </si>
-  <si>
-    <t>Price below 100/200 DMA — wait for MA alignment</t>
-  </si>
-  <si>
-    <t>VCP incomplete — price range still wide, wait for tighter base (3 contractions),</t>
-  </si>
-  <si>
-    <t>Score 65/100 — need macro improvement or volume surge</t>
-  </si>
-  <si>
-    <t>Price below 100/200 DMA — wait for MA alignment, RSI outside 50-70 zone</t>
-  </si>
-  <si>
     <t>2026-04-21</t>
   </si>
   <si>
     <t>2026-04-20</t>
   </si>
   <si>
+    <t>2026-04-22</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
     <t>-2.3%</t>
+  </si>
+  <si>
+    <t>-2.8%</t>
   </si>
 </sst>
 </file>
@@ -504,7 +558,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P24"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -558,26 +612,26 @@
       </c>
     </row>
     <row r="2" spans="1:16">
-      <c r="A2" t="s">
-        <v>16</v>
+      <c r="A2">
+        <v>20260421</v>
       </c>
       <c r="B2" t="s">
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D2">
         <v>77.09999999999999</v>
       </c>
-      <c r="E2" t="s">
-        <v>40</v>
+      <c r="E2">
+        <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G2" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H2">
         <v>11714</v>
@@ -589,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="M2" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N2" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O2">
         <v>17.53</v>
@@ -605,26 +659,26 @@
       </c>
     </row>
     <row r="3" spans="1:16">
-      <c r="A3" t="s">
-        <v>16</v>
+      <c r="A3">
+        <v>20260421</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D3">
         <v>74</v>
       </c>
-      <c r="E3" t="s">
-        <v>40</v>
+      <c r="E3">
+        <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G3" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H3">
         <v>514.05</v>
@@ -636,13 +690,13 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="M3" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N3" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O3">
         <v>17.53</v>
@@ -652,26 +706,26 @@
       </c>
     </row>
     <row r="4" spans="1:16">
-      <c r="A4" t="s">
-        <v>16</v>
+      <c r="A4">
+        <v>20260421</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="D4">
         <v>72</v>
       </c>
-      <c r="E4" t="s">
-        <v>40</v>
+      <c r="E4">
+        <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G4" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H4">
         <v>1621.5</v>
@@ -683,13 +737,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="M4" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N4" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O4">
         <v>17.53</v>
@@ -699,26 +753,26 @@
       </c>
     </row>
     <row r="5" spans="1:16">
-      <c r="A5" t="s">
-        <v>16</v>
+      <c r="A5">
+        <v>20260421</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D5">
         <v>69.59999999999999</v>
       </c>
-      <c r="E5" t="s">
-        <v>40</v>
+      <c r="E5">
+        <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G5" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H5">
         <v>191.38</v>
@@ -727,19 +781,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J5" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="M5" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N5" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O5">
         <v>17.53</v>
@@ -749,26 +803,26 @@
       </c>
     </row>
     <row r="6" spans="1:16">
-      <c r="A6" t="s">
-        <v>16</v>
+      <c r="A6">
+        <v>20260421</v>
       </c>
       <c r="B6" t="s">
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D6">
         <v>69.09999999999999</v>
       </c>
-      <c r="E6" t="s">
-        <v>40</v>
+      <c r="E6">
+        <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G6" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H6">
         <v>1318.1</v>
@@ -777,19 +831,19 @@
         <v>0.9000000000000057</v>
       </c>
       <c r="J6" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="M6" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N6" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O6">
         <v>17.53</v>
@@ -799,26 +853,26 @@
       </c>
     </row>
     <row r="7" spans="1:16">
-      <c r="A7" t="s">
-        <v>16</v>
+      <c r="A7">
+        <v>20260421</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D7">
         <v>67.2</v>
       </c>
-      <c r="E7" t="s">
-        <v>41</v>
+      <c r="E7">
+        <v>-0.5</v>
       </c>
       <c r="F7" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G7" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H7">
         <v>1377.7</v>
@@ -827,19 +881,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J7" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="K7">
         <v>6</v>
       </c>
       <c r="L7" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="M7" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N7" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O7">
         <v>17.53</v>
@@ -849,26 +903,26 @@
       </c>
     </row>
     <row r="8" spans="1:16">
-      <c r="A8" t="s">
-        <v>16</v>
+      <c r="A8">
+        <v>20260421</v>
       </c>
       <c r="B8" t="s">
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D8">
         <v>67.2</v>
       </c>
-      <c r="E8" t="s">
-        <v>41</v>
+      <c r="E8">
+        <v>-0.5</v>
       </c>
       <c r="F8" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G8" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H8">
         <v>4479.7</v>
@@ -877,19 +931,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J8" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="K8">
         <v>6</v>
       </c>
       <c r="L8" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="M8" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N8" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O8">
         <v>17.53</v>
@@ -899,26 +953,26 @@
       </c>
     </row>
     <row r="9" spans="1:16">
-      <c r="A9" t="s">
-        <v>16</v>
+      <c r="A9">
+        <v>20260421</v>
       </c>
       <c r="B9" t="s">
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D9">
         <v>67.2</v>
       </c>
-      <c r="E9" t="s">
-        <v>41</v>
+      <c r="E9">
+        <v>-0.5</v>
       </c>
       <c r="F9" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G9" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H9">
         <v>1045.3</v>
@@ -927,19 +981,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J9" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="K9">
         <v>6</v>
       </c>
       <c r="L9" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="M9" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N9" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O9">
         <v>17.53</v>
@@ -949,26 +1003,26 @@
       </c>
     </row>
     <row r="10" spans="1:16">
-      <c r="A10" t="s">
-        <v>16</v>
+      <c r="A10">
+        <v>20260421</v>
       </c>
       <c r="B10" t="s">
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D10">
         <v>67.2</v>
       </c>
-      <c r="E10" t="s">
-        <v>40</v>
+      <c r="E10">
+        <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G10" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H10">
         <v>1055.65</v>
@@ -977,19 +1031,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J10" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="M10" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N10" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O10">
         <v>17.53</v>
@@ -999,26 +1053,26 @@
       </c>
     </row>
     <row r="11" spans="1:16">
-      <c r="A11" t="s">
-        <v>16</v>
+      <c r="A11">
+        <v>20260421</v>
       </c>
       <c r="B11" t="s">
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D11">
         <v>67.2</v>
       </c>
-      <c r="E11" t="s">
-        <v>41</v>
+      <c r="E11">
+        <v>-0.5</v>
       </c>
       <c r="F11" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G11" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H11">
         <v>1045.3</v>
@@ -1027,19 +1081,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J11" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="K11">
         <v>6</v>
       </c>
       <c r="L11" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="M11" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N11" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O11">
         <v>17.53</v>
@@ -1049,26 +1103,26 @@
       </c>
     </row>
     <row r="12" spans="1:16">
-      <c r="A12" t="s">
-        <v>16</v>
+      <c r="A12">
+        <v>20260421</v>
       </c>
       <c r="B12" t="s">
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D12">
         <v>67.2</v>
       </c>
-      <c r="E12" t="s">
-        <v>41</v>
+      <c r="E12">
+        <v>-0.5</v>
       </c>
       <c r="F12" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G12" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H12">
         <v>4479.7</v>
@@ -1077,19 +1131,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J12" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="K12">
         <v>6</v>
       </c>
       <c r="L12" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="M12" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N12" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O12">
         <v>17.53</v>
@@ -1099,26 +1153,26 @@
       </c>
     </row>
     <row r="13" spans="1:16">
-      <c r="A13" t="s">
-        <v>16</v>
+      <c r="A13">
+        <v>20260421</v>
       </c>
       <c r="B13" t="s">
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D13">
         <v>67.09999999999999</v>
       </c>
-      <c r="E13" t="s">
-        <v>40</v>
+      <c r="E13">
+        <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G13" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H13">
         <v>581.3</v>
@@ -1127,19 +1181,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J13" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="K13">
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="M13" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N13" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O13">
         <v>17.53</v>
@@ -1149,26 +1203,26 @@
       </c>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" t="s">
-        <v>16</v>
+      <c r="A14">
+        <v>20260421</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D14">
         <v>67.09999999999999</v>
       </c>
-      <c r="E14" t="s">
-        <v>40</v>
+      <c r="E14">
+        <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G14" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H14">
         <v>458.9</v>
@@ -1177,19 +1231,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J14" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="M14" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N14" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O14">
         <v>17.53</v>
@@ -1199,26 +1253,26 @@
       </c>
     </row>
     <row r="15" spans="1:16">
-      <c r="A15" t="s">
-        <v>16</v>
+      <c r="A15">
+        <v>20260421</v>
       </c>
       <c r="B15" t="s">
         <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D15">
         <v>65.59999999999999</v>
       </c>
-      <c r="E15" t="s">
-        <v>40</v>
+      <c r="E15">
+        <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G15" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H15">
         <v>196.02</v>
@@ -1227,19 +1281,19 @@
         <v>4.400000000000006</v>
       </c>
       <c r="J15" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="M15" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N15" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O15">
         <v>17.53</v>
@@ -1249,26 +1303,26 @@
       </c>
     </row>
     <row r="16" spans="1:16">
-      <c r="A16" t="s">
-        <v>16</v>
+      <c r="A16">
+        <v>20260421</v>
       </c>
       <c r="B16" t="s">
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D16">
         <v>65</v>
       </c>
-      <c r="E16" t="s">
-        <v>40</v>
+      <c r="E16">
+        <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G16" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H16">
         <v>4172.9</v>
@@ -1277,19 +1331,19 @@
         <v>5</v>
       </c>
       <c r="J16" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="K16">
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="M16" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N16" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O16">
         <v>17.53</v>
@@ -1299,26 +1353,26 @@
       </c>
     </row>
     <row r="17" spans="1:16">
-      <c r="A17" t="s">
-        <v>16</v>
+      <c r="A17">
+        <v>20260421</v>
       </c>
       <c r="B17" t="s">
         <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D17">
         <v>64.7</v>
       </c>
-      <c r="E17" t="s">
-        <v>40</v>
+      <c r="E17">
+        <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G17" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H17">
         <v>6373.5</v>
@@ -1327,19 +1381,19 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J17" t="s">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="K17">
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="M17" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N17" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O17">
         <v>17.53</v>
@@ -1349,26 +1403,26 @@
       </c>
     </row>
     <row r="18" spans="1:16">
-      <c r="A18" t="s">
-        <v>16</v>
+      <c r="A18">
+        <v>20260421</v>
       </c>
       <c r="B18" t="s">
         <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D18">
         <v>64.7</v>
       </c>
-      <c r="E18" t="s">
-        <v>40</v>
+      <c r="E18">
+        <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H18">
         <v>1113.1</v>
@@ -1377,19 +1431,19 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J18" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="M18" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N18" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O18">
         <v>17.53</v>
@@ -1399,26 +1453,26 @@
       </c>
     </row>
     <row r="19" spans="1:16">
-      <c r="A19" t="s">
-        <v>16</v>
+      <c r="A19">
+        <v>20260421</v>
       </c>
       <c r="B19" t="s">
         <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D19">
         <v>64.59999999999999</v>
       </c>
-      <c r="E19" t="s">
-        <v>40</v>
+      <c r="E19">
+        <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H19">
         <v>1379.9</v>
@@ -1427,19 +1481,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J19" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="K19">
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="M19" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N19" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O19">
         <v>17.53</v>
@@ -1449,26 +1503,26 @@
       </c>
     </row>
     <row r="20" spans="1:16">
-      <c r="A20" t="s">
-        <v>16</v>
+      <c r="A20">
+        <v>20260421</v>
       </c>
       <c r="B20" t="s">
         <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D20">
         <v>64.2</v>
       </c>
-      <c r="E20" t="s">
-        <v>41</v>
+      <c r="E20">
+        <v>-0.5</v>
       </c>
       <c r="F20" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H20">
         <v>9793</v>
@@ -1477,19 +1531,19 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J20" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="K20">
         <v>6</v>
       </c>
       <c r="L20" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="M20" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N20" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O20">
         <v>17.53</v>
@@ -1499,26 +1553,26 @@
       </c>
     </row>
     <row r="21" spans="1:16">
-      <c r="A21" t="s">
-        <v>16</v>
+      <c r="A21">
+        <v>20260421</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D21">
         <v>64.2</v>
       </c>
-      <c r="E21" t="s">
-        <v>40</v>
+      <c r="E21">
+        <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G21" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H21">
         <v>7955.5</v>
@@ -1527,19 +1581,19 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J21" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="K21">
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="M21" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N21" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O21">
         <v>17.53</v>
@@ -1549,26 +1603,26 @@
       </c>
     </row>
     <row r="22" spans="1:16">
-      <c r="A22" t="s">
-        <v>16</v>
+      <c r="A22">
+        <v>20260421</v>
       </c>
       <c r="B22" t="s">
         <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D22">
         <v>63.6</v>
       </c>
-      <c r="E22" t="s">
-        <v>40</v>
+      <c r="E22">
+        <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H22">
         <v>1037.85</v>
@@ -1577,19 +1631,19 @@
         <v>6.399999999999999</v>
       </c>
       <c r="J22" t="s">
-        <v>44</v>
+        <v>59</v>
       </c>
       <c r="K22">
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="M22" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N22" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O22">
         <v>17.53</v>
@@ -1599,26 +1653,26 @@
       </c>
     </row>
     <row r="23" spans="1:16">
-      <c r="A23" t="s">
-        <v>16</v>
+      <c r="A23">
+        <v>20260421</v>
       </c>
       <c r="B23" t="s">
         <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D23">
         <v>61.6</v>
       </c>
-      <c r="E23" t="s">
-        <v>40</v>
+      <c r="E23">
+        <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H23">
         <v>979.1</v>
@@ -1627,19 +1681,19 @@
         <v>8.399999999999999</v>
       </c>
       <c r="J23" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="K23">
         <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>49</v>
+        <v>65</v>
       </c>
       <c r="M23" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N23" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O23">
         <v>17.53</v>
@@ -1649,26 +1703,26 @@
       </c>
     </row>
     <row r="24" spans="1:16">
-      <c r="A24" t="s">
-        <v>16</v>
+      <c r="A24">
+        <v>20260421</v>
       </c>
       <c r="B24" t="s">
         <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="D24">
         <v>61.5</v>
       </c>
-      <c r="E24" t="s">
-        <v>41</v>
+      <c r="E24">
+        <v>-0.5</v>
       </c>
       <c r="F24" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="H24">
         <v>319.35</v>
@@ -1677,25 +1731,922 @@
         <v>8.5</v>
       </c>
       <c r="J24" t="s">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="K24">
         <v>6</v>
       </c>
       <c r="L24" t="s">
-        <v>50</v>
+        <v>66</v>
       </c>
       <c r="M24" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="N24" t="s">
-        <v>52</v>
+        <v>69</v>
       </c>
       <c r="O24">
         <v>17.53</v>
       </c>
       <c r="P24">
         <v>-123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
+      <c r="A25" t="s">
+        <v>16</v>
+      </c>
+      <c r="B25" t="s">
+        <v>38</v>
+      </c>
+      <c r="C25" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25">
+        <v>70</v>
+      </c>
+      <c r="E25" t="s">
+        <v>52</v>
+      </c>
+      <c r="F25" t="s">
+        <v>57</v>
+      </c>
+      <c r="G25" t="s">
+        <v>58</v>
+      </c>
+      <c r="H25">
+        <v>767.65</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>1</v>
+      </c>
+      <c r="L25" t="s">
+        <v>16</v>
+      </c>
+      <c r="M25" t="s">
+        <v>68</v>
+      </c>
+      <c r="N25" t="s">
+        <v>70</v>
+      </c>
+      <c r="O25">
+        <v>18.27</v>
+      </c>
+      <c r="P25">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
+      <c r="A26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B26" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" t="s">
+        <v>51</v>
+      </c>
+      <c r="D26">
+        <v>69</v>
+      </c>
+      <c r="E26" t="s">
+        <v>53</v>
+      </c>
+      <c r="F26" t="s">
+        <v>57</v>
+      </c>
+      <c r="G26" t="s">
+        <v>58</v>
+      </c>
+      <c r="H26">
+        <v>404.1</v>
+      </c>
+      <c r="I26">
+        <v>1</v>
+      </c>
+      <c r="J26" t="s">
+        <v>59</v>
+      </c>
+      <c r="K26">
+        <v>7</v>
+      </c>
+      <c r="L26" t="s">
+        <v>66</v>
+      </c>
+      <c r="M26" t="s">
+        <v>68</v>
+      </c>
+      <c r="N26" t="s">
+        <v>70</v>
+      </c>
+      <c r="O26">
+        <v>18.27</v>
+      </c>
+      <c r="P26">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16">
+      <c r="A27" t="s">
+        <v>16</v>
+      </c>
+      <c r="B27" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" t="s">
+        <v>51</v>
+      </c>
+      <c r="D27">
+        <v>69</v>
+      </c>
+      <c r="E27" t="s">
+        <v>52</v>
+      </c>
+      <c r="F27" t="s">
+        <v>57</v>
+      </c>
+      <c r="G27" t="s">
+        <v>58</v>
+      </c>
+      <c r="H27">
+        <v>3847</v>
+      </c>
+      <c r="I27">
+        <v>1</v>
+      </c>
+      <c r="J27" t="s">
+        <v>59</v>
+      </c>
+      <c r="K27">
+        <v>1</v>
+      </c>
+      <c r="L27" t="s">
+        <v>67</v>
+      </c>
+      <c r="M27" t="s">
+        <v>68</v>
+      </c>
+      <c r="N27" t="s">
+        <v>70</v>
+      </c>
+      <c r="O27">
+        <v>18.27</v>
+      </c>
+      <c r="P27">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16">
+      <c r="A28" t="s">
+        <v>16</v>
+      </c>
+      <c r="B28" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" t="s">
+        <v>51</v>
+      </c>
+      <c r="D28">
+        <v>67.5</v>
+      </c>
+      <c r="E28" t="s">
+        <v>52</v>
+      </c>
+      <c r="F28" t="s">
+        <v>57</v>
+      </c>
+      <c r="G28" t="s">
+        <v>58</v>
+      </c>
+      <c r="H28">
+        <v>211.75</v>
+      </c>
+      <c r="I28">
+        <v>2.5</v>
+      </c>
+      <c r="J28" t="s">
+        <v>61</v>
+      </c>
+      <c r="K28">
+        <v>1</v>
+      </c>
+      <c r="L28" t="s">
+        <v>67</v>
+      </c>
+      <c r="M28" t="s">
+        <v>68</v>
+      </c>
+      <c r="N28" t="s">
+        <v>70</v>
+      </c>
+      <c r="O28">
+        <v>18.27</v>
+      </c>
+      <c r="P28">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16">
+      <c r="A29" t="s">
+        <v>16</v>
+      </c>
+      <c r="B29" t="s">
+        <v>22</v>
+      </c>
+      <c r="C29" t="s">
+        <v>51</v>
+      </c>
+      <c r="D29">
+        <v>66.7</v>
+      </c>
+      <c r="E29" t="s">
+        <v>54</v>
+      </c>
+      <c r="F29" t="s">
+        <v>57</v>
+      </c>
+      <c r="G29" t="s">
+        <v>58</v>
+      </c>
+      <c r="H29">
+        <v>1381.5</v>
+      </c>
+      <c r="I29">
+        <v>3.299999999999997</v>
+      </c>
+      <c r="J29" t="s">
+        <v>59</v>
+      </c>
+      <c r="K29">
+        <v>7</v>
+      </c>
+      <c r="L29" t="s">
+        <v>66</v>
+      </c>
+      <c r="M29" t="s">
+        <v>68</v>
+      </c>
+      <c r="N29" t="s">
+        <v>70</v>
+      </c>
+      <c r="O29">
+        <v>18.27</v>
+      </c>
+      <c r="P29">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16">
+      <c r="A30" t="s">
+        <v>16</v>
+      </c>
+      <c r="B30" t="s">
+        <v>23</v>
+      </c>
+      <c r="C30" t="s">
+        <v>51</v>
+      </c>
+      <c r="D30">
+        <v>66.7</v>
+      </c>
+      <c r="E30" t="s">
+        <v>54</v>
+      </c>
+      <c r="F30" t="s">
+        <v>57</v>
+      </c>
+      <c r="G30" t="s">
+        <v>58</v>
+      </c>
+      <c r="H30">
+        <v>4483</v>
+      </c>
+      <c r="I30">
+        <v>3.299999999999997</v>
+      </c>
+      <c r="J30" t="s">
+        <v>59</v>
+      </c>
+      <c r="K30">
+        <v>7</v>
+      </c>
+      <c r="L30" t="s">
+        <v>66</v>
+      </c>
+      <c r="M30" t="s">
+        <v>68</v>
+      </c>
+      <c r="N30" t="s">
+        <v>70</v>
+      </c>
+      <c r="O30">
+        <v>18.27</v>
+      </c>
+      <c r="P30">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="31" spans="1:16">
+      <c r="A31" t="s">
+        <v>16</v>
+      </c>
+      <c r="B31" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" t="s">
+        <v>51</v>
+      </c>
+      <c r="D31">
+        <v>66.7</v>
+      </c>
+      <c r="E31" t="s">
+        <v>52</v>
+      </c>
+      <c r="F31" t="s">
+        <v>57</v>
+      </c>
+      <c r="G31" t="s">
+        <v>58</v>
+      </c>
+      <c r="H31">
+        <v>89.05</v>
+      </c>
+      <c r="I31">
+        <v>3.299999999999997</v>
+      </c>
+      <c r="J31" t="s">
+        <v>59</v>
+      </c>
+      <c r="K31">
+        <v>1</v>
+      </c>
+      <c r="L31" t="s">
+        <v>67</v>
+      </c>
+      <c r="M31" t="s">
+        <v>68</v>
+      </c>
+      <c r="N31" t="s">
+        <v>70</v>
+      </c>
+      <c r="O31">
+        <v>18.27</v>
+      </c>
+      <c r="P31">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="32" spans="1:16">
+      <c r="A32" t="s">
+        <v>16</v>
+      </c>
+      <c r="B32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32" t="s">
+        <v>51</v>
+      </c>
+      <c r="D32">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="E32" t="s">
+        <v>52</v>
+      </c>
+      <c r="F32" t="s">
+        <v>57</v>
+      </c>
+      <c r="G32" t="s">
+        <v>58</v>
+      </c>
+      <c r="H32">
+        <v>1291.1</v>
+      </c>
+      <c r="I32">
+        <v>3.400000000000006</v>
+      </c>
+      <c r="J32" t="s">
+        <v>59</v>
+      </c>
+      <c r="K32">
+        <v>1</v>
+      </c>
+      <c r="L32" t="s">
+        <v>67</v>
+      </c>
+      <c r="M32" t="s">
+        <v>68</v>
+      </c>
+      <c r="N32" t="s">
+        <v>70</v>
+      </c>
+      <c r="O32">
+        <v>18.27</v>
+      </c>
+      <c r="P32">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="33" spans="1:16">
+      <c r="A33" t="s">
+        <v>16</v>
+      </c>
+      <c r="B33" t="s">
+        <v>32</v>
+      </c>
+      <c r="C33" t="s">
+        <v>51</v>
+      </c>
+      <c r="D33">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="E33" t="s">
+        <v>54</v>
+      </c>
+      <c r="F33" t="s">
+        <v>57</v>
+      </c>
+      <c r="G33" t="s">
+        <v>58</v>
+      </c>
+      <c r="H33">
+        <v>1414.6</v>
+      </c>
+      <c r="I33">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="J33" t="s">
+        <v>61</v>
+      </c>
+      <c r="K33">
+        <v>2</v>
+      </c>
+      <c r="L33" t="s">
+        <v>65</v>
+      </c>
+      <c r="M33" t="s">
+        <v>68</v>
+      </c>
+      <c r="N33" t="s">
+        <v>70</v>
+      </c>
+      <c r="O33">
+        <v>18.27</v>
+      </c>
+      <c r="P33">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
+      <c r="A34" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" t="s">
+        <v>33</v>
+      </c>
+      <c r="C34" t="s">
+        <v>51</v>
+      </c>
+      <c r="D34">
+        <v>63.7</v>
+      </c>
+      <c r="E34" t="s">
+        <v>54</v>
+      </c>
+      <c r="F34" t="s">
+        <v>57</v>
+      </c>
+      <c r="G34" t="s">
+        <v>58</v>
+      </c>
+      <c r="H34">
+        <v>9760</v>
+      </c>
+      <c r="I34">
+        <v>6.299999999999997</v>
+      </c>
+      <c r="J34" t="s">
+        <v>59</v>
+      </c>
+      <c r="K34">
+        <v>7</v>
+      </c>
+      <c r="L34" t="s">
+        <v>66</v>
+      </c>
+      <c r="M34" t="s">
+        <v>68</v>
+      </c>
+      <c r="N34" t="s">
+        <v>70</v>
+      </c>
+      <c r="O34">
+        <v>18.27</v>
+      </c>
+      <c r="P34">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
+      <c r="A35" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" t="s">
+        <v>44</v>
+      </c>
+      <c r="C35" t="s">
+        <v>51</v>
+      </c>
+      <c r="D35">
+        <v>62.7</v>
+      </c>
+      <c r="E35" t="s">
+        <v>52</v>
+      </c>
+      <c r="F35" t="s">
+        <v>57</v>
+      </c>
+      <c r="G35" t="s">
+        <v>58</v>
+      </c>
+      <c r="H35">
+        <v>125.85</v>
+      </c>
+      <c r="I35">
+        <v>7.299999999999997</v>
+      </c>
+      <c r="J35" t="s">
+        <v>59</v>
+      </c>
+      <c r="K35">
+        <v>1</v>
+      </c>
+      <c r="L35" t="s">
+        <v>67</v>
+      </c>
+      <c r="M35" t="s">
+        <v>68</v>
+      </c>
+      <c r="N35" t="s">
+        <v>70</v>
+      </c>
+      <c r="O35">
+        <v>18.27</v>
+      </c>
+      <c r="P35">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
+      <c r="A36" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" t="s">
+        <v>45</v>
+      </c>
+      <c r="C36" t="s">
+        <v>51</v>
+      </c>
+      <c r="D36">
+        <v>62.1</v>
+      </c>
+      <c r="E36" t="s">
+        <v>52</v>
+      </c>
+      <c r="F36" t="s">
+        <v>57</v>
+      </c>
+      <c r="G36" t="s">
+        <v>58</v>
+      </c>
+      <c r="H36">
+        <v>1171.95</v>
+      </c>
+      <c r="I36">
+        <v>7.899999999999999</v>
+      </c>
+      <c r="J36" t="s">
+        <v>61</v>
+      </c>
+      <c r="K36">
+        <v>1</v>
+      </c>
+      <c r="L36" t="s">
+        <v>67</v>
+      </c>
+      <c r="M36" t="s">
+        <v>68</v>
+      </c>
+      <c r="N36" t="s">
+        <v>70</v>
+      </c>
+      <c r="O36">
+        <v>18.27</v>
+      </c>
+      <c r="P36">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="37" spans="1:16">
+      <c r="A37" t="s">
+        <v>16</v>
+      </c>
+      <c r="B37" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" t="s">
+        <v>51</v>
+      </c>
+      <c r="D37">
+        <v>60.7</v>
+      </c>
+      <c r="E37" t="s">
+        <v>55</v>
+      </c>
+      <c r="F37" t="s">
+        <v>57</v>
+      </c>
+      <c r="G37" t="s">
+        <v>58</v>
+      </c>
+      <c r="H37">
+        <v>1038.1</v>
+      </c>
+      <c r="I37">
+        <v>9.299999999999997</v>
+      </c>
+      <c r="J37" t="s">
+        <v>59</v>
+      </c>
+      <c r="K37">
+        <v>7</v>
+      </c>
+      <c r="L37" t="s">
+        <v>66</v>
+      </c>
+      <c r="M37" t="s">
+        <v>68</v>
+      </c>
+      <c r="N37" t="s">
+        <v>70</v>
+      </c>
+      <c r="O37">
+        <v>18.27</v>
+      </c>
+      <c r="P37">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="38" spans="1:16">
+      <c r="A38" t="s">
+        <v>16</v>
+      </c>
+      <c r="B38" t="s">
+        <v>37</v>
+      </c>
+      <c r="C38" t="s">
+        <v>51</v>
+      </c>
+      <c r="D38">
+        <v>58.6</v>
+      </c>
+      <c r="E38" t="s">
+        <v>56</v>
+      </c>
+      <c r="F38" t="s">
+        <v>57</v>
+      </c>
+      <c r="G38" t="s">
+        <v>58</v>
+      </c>
+      <c r="H38">
+        <v>319.6</v>
+      </c>
+      <c r="I38">
+        <v>11.4</v>
+      </c>
+      <c r="J38" t="s">
+        <v>63</v>
+      </c>
+      <c r="K38">
+        <v>7</v>
+      </c>
+      <c r="L38" t="s">
+        <v>66</v>
+      </c>
+      <c r="M38" t="s">
+        <v>68</v>
+      </c>
+      <c r="N38" t="s">
+        <v>70</v>
+      </c>
+      <c r="O38">
+        <v>18.27</v>
+      </c>
+      <c r="P38">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="39" spans="1:16">
+      <c r="A39" t="s">
+        <v>16</v>
+      </c>
+      <c r="B39" t="s">
+        <v>46</v>
+      </c>
+      <c r="C39" t="s">
+        <v>51</v>
+      </c>
+      <c r="D39">
+        <v>58.3</v>
+      </c>
+      <c r="E39" t="s">
+        <v>52</v>
+      </c>
+      <c r="F39" t="s">
+        <v>57</v>
+      </c>
+      <c r="G39" t="s">
+        <v>58</v>
+      </c>
+      <c r="H39">
+        <v>2314.1</v>
+      </c>
+      <c r="I39">
+        <v>11.7</v>
+      </c>
+      <c r="J39" t="s">
+        <v>61</v>
+      </c>
+      <c r="K39">
+        <v>1</v>
+      </c>
+      <c r="L39" t="s">
+        <v>67</v>
+      </c>
+      <c r="M39" t="s">
+        <v>68</v>
+      </c>
+      <c r="N39" t="s">
+        <v>70</v>
+      </c>
+      <c r="O39">
+        <v>18.27</v>
+      </c>
+      <c r="P39">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
+      <c r="A40" t="s">
+        <v>16</v>
+      </c>
+      <c r="B40" t="s">
+        <v>47</v>
+      </c>
+      <c r="C40" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40">
+        <v>58.3</v>
+      </c>
+      <c r="E40" t="s">
+        <v>52</v>
+      </c>
+      <c r="F40" t="s">
+        <v>57</v>
+      </c>
+      <c r="G40" t="s">
+        <v>58</v>
+      </c>
+      <c r="H40">
+        <v>3723.6</v>
+      </c>
+      <c r="I40">
+        <v>11.7</v>
+      </c>
+      <c r="J40" t="s">
+        <v>59</v>
+      </c>
+      <c r="K40">
+        <v>1</v>
+      </c>
+      <c r="L40" t="s">
+        <v>67</v>
+      </c>
+      <c r="M40" t="s">
+        <v>68</v>
+      </c>
+      <c r="N40" t="s">
+        <v>70</v>
+      </c>
+      <c r="O40">
+        <v>18.27</v>
+      </c>
+      <c r="P40">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
+      <c r="A41" t="s">
+        <v>16</v>
+      </c>
+      <c r="B41" t="s">
+        <v>48</v>
+      </c>
+      <c r="C41" t="s">
+        <v>51</v>
+      </c>
+      <c r="D41">
+        <v>56.7</v>
+      </c>
+      <c r="E41" t="s">
+        <v>54</v>
+      </c>
+      <c r="F41" t="s">
+        <v>57</v>
+      </c>
+      <c r="G41" t="s">
+        <v>58</v>
+      </c>
+      <c r="H41">
+        <v>4049.2</v>
+      </c>
+      <c r="I41">
+        <v>13.3</v>
+      </c>
+      <c r="J41" t="s">
+        <v>61</v>
+      </c>
+      <c r="K41">
+        <v>3</v>
+      </c>
+      <c r="L41" t="s">
+        <v>65</v>
+      </c>
+      <c r="M41" t="s">
+        <v>68</v>
+      </c>
+      <c r="N41" t="s">
+        <v>70</v>
+      </c>
+      <c r="O41">
+        <v>18.27</v>
+      </c>
+      <c r="P41">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
+      <c r="A42" t="s">
+        <v>16</v>
+      </c>
+      <c r="B42" t="s">
+        <v>49</v>
+      </c>
+      <c r="C42" t="s">
+        <v>51</v>
+      </c>
+      <c r="D42">
+        <v>55.4</v>
+      </c>
+      <c r="E42" t="s">
+        <v>52</v>
+      </c>
+      <c r="F42" t="s">
+        <v>57</v>
+      </c>
+      <c r="G42" t="s">
+        <v>58</v>
+      </c>
+      <c r="H42">
+        <v>124.98</v>
+      </c>
+      <c r="I42">
+        <v>14.6</v>
+      </c>
+      <c r="J42" t="s">
+        <v>60</v>
+      </c>
+      <c r="K42">
+        <v>1</v>
+      </c>
+      <c r="L42" t="s">
+        <v>67</v>
+      </c>
+      <c r="M42" t="s">
+        <v>68</v>
+      </c>
+      <c r="N42" t="s">
+        <v>70</v>
+      </c>
+      <c r="O42">
+        <v>18.27</v>
+      </c>
+      <c r="P42">
+        <v>272</v>
       </c>
     </row>
   </sheetData>

--- a/reports/watchlist_history.xlsx
+++ b/reports/watchlist_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="69">
   <si>
     <t>Date</t>
   </si>
@@ -172,19 +172,13 @@
     <t>WATCH</t>
   </si>
   <si>
+    <t>+2.4</t>
+  </si>
+  <si>
     <t>+0.0</t>
   </si>
   <si>
-    <t>+7.8</t>
-  </si>
-  <si>
-    <t>-0.5</t>
-  </si>
-  <si>
-    <t>-6.5</t>
-  </si>
-  <si>
-    <t>-2.9</t>
+    <t>+1.0</t>
   </si>
   <si>
     <t>Stage 2 — Uptrend ✓</t>
@@ -558,7 +552,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P42"/>
+  <dimension ref="A1:P59"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -628,10 +622,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H2">
         <v>11714</v>
@@ -643,13 +637,13 @@
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="M2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N2" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O2">
         <v>17.53</v>
@@ -675,10 +669,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G3" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H3">
         <v>514.05</v>
@@ -690,13 +684,13 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="M3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O3">
         <v>17.53</v>
@@ -722,10 +716,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G4" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H4">
         <v>1621.5</v>
@@ -737,13 +731,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="M4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O4">
         <v>17.53</v>
@@ -769,10 +763,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G5" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H5">
         <v>191.38</v>
@@ -781,19 +775,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N5" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O5">
         <v>17.53</v>
@@ -819,10 +813,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H6">
         <v>1318.1</v>
@@ -831,19 +825,19 @@
         <v>0.9000000000000057</v>
       </c>
       <c r="J6" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O6">
         <v>17.53</v>
@@ -869,10 +863,10 @@
         <v>-0.5</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H7">
         <v>1377.7</v>
@@ -881,19 +875,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J7" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K7">
         <v>6</v>
       </c>
       <c r="L7" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M7" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O7">
         <v>17.53</v>
@@ -919,10 +913,10 @@
         <v>-0.5</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G8" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H8">
         <v>4479.7</v>
@@ -931,19 +925,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K8">
         <v>6</v>
       </c>
       <c r="L8" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M8" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N8" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O8">
         <v>17.53</v>
@@ -969,10 +963,10 @@
         <v>-0.5</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H9">
         <v>1045.3</v>
@@ -981,19 +975,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J9" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K9">
         <v>6</v>
       </c>
       <c r="L9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M9" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N9" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O9">
         <v>17.53</v>
@@ -1019,10 +1013,10 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G10" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H10">
         <v>1055.65</v>
@@ -1031,19 +1025,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M10" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N10" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O10">
         <v>17.53</v>
@@ -1069,10 +1063,10 @@
         <v>-0.5</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G11" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H11">
         <v>1045.3</v>
@@ -1081,19 +1075,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K11">
         <v>6</v>
       </c>
       <c r="L11" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N11" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O11">
         <v>17.53</v>
@@ -1119,10 +1113,10 @@
         <v>-0.5</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G12" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H12">
         <v>4479.7</v>
@@ -1131,19 +1125,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J12" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K12">
         <v>6</v>
       </c>
       <c r="L12" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M12" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N12" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O12">
         <v>17.53</v>
@@ -1169,10 +1163,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H13">
         <v>581.3</v>
@@ -1181,19 +1175,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K13">
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O13">
         <v>17.53</v>
@@ -1219,10 +1213,10 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G14" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H14">
         <v>458.9</v>
@@ -1231,19 +1225,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J14" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M14" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N14" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O14">
         <v>17.53</v>
@@ -1269,10 +1263,10 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G15" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H15">
         <v>196.02</v>
@@ -1281,19 +1275,19 @@
         <v>4.400000000000006</v>
       </c>
       <c r="J15" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M15" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N15" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O15">
         <v>17.53</v>
@@ -1319,10 +1313,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G16" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H16">
         <v>4172.9</v>
@@ -1331,19 +1325,19 @@
         <v>5</v>
       </c>
       <c r="J16" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K16">
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M16" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N16" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O16">
         <v>17.53</v>
@@ -1369,10 +1363,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G17" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H17">
         <v>6373.5</v>
@@ -1381,19 +1375,19 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="K17">
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N17" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O17">
         <v>17.53</v>
@@ -1419,10 +1413,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G18" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H18">
         <v>1113.1</v>
@@ -1431,19 +1425,19 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J18" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M18" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N18" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O18">
         <v>17.53</v>
@@ -1469,10 +1463,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G19" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H19">
         <v>1379.9</v>
@@ -1481,19 +1475,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J19" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K19">
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M19" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N19" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O19">
         <v>17.53</v>
@@ -1519,10 +1513,10 @@
         <v>-0.5</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H20">
         <v>9793</v>
@@ -1531,19 +1525,19 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K20">
         <v>6</v>
       </c>
       <c r="L20" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M20" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N20" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O20">
         <v>17.53</v>
@@ -1569,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G21" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H21">
         <v>7955.5</v>
@@ -1581,19 +1575,19 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J21" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K21">
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M21" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N21" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O21">
         <v>17.53</v>
@@ -1619,10 +1613,10 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G22" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H22">
         <v>1037.85</v>
@@ -1631,19 +1625,19 @@
         <v>6.399999999999999</v>
       </c>
       <c r="J22" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K22">
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M22" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N22" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O22">
         <v>17.53</v>
@@ -1669,10 +1663,10 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G23" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H23">
         <v>979.1</v>
@@ -1681,19 +1675,19 @@
         <v>8.399999999999999</v>
       </c>
       <c r="J23" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K23">
         <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M23" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N23" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O23">
         <v>17.53</v>
@@ -1719,10 +1713,10 @@
         <v>-0.5</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G24" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H24">
         <v>319.35</v>
@@ -1731,19 +1725,19 @@
         <v>8.5</v>
       </c>
       <c r="J24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K24">
         <v>6</v>
       </c>
       <c r="L24" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M24" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="N24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="O24">
         <v>17.53</v>
@@ -1753,8 +1747,8 @@
       </c>
     </row>
     <row r="25" spans="1:16">
-      <c r="A25" t="s">
-        <v>16</v>
+      <c r="A25">
+        <v>20260422</v>
       </c>
       <c r="B25" t="s">
         <v>38</v>
@@ -1765,14 +1759,14 @@
       <c r="D25">
         <v>70</v>
       </c>
-      <c r="E25" t="s">
-        <v>52</v>
+      <c r="E25">
+        <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G25" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H25">
         <v>767.65</v>
@@ -1787,10 +1781,10 @@
         <v>16</v>
       </c>
       <c r="M25" t="s">
+        <v>66</v>
+      </c>
+      <c r="N25" t="s">
         <v>68</v>
-      </c>
-      <c r="N25" t="s">
-        <v>70</v>
       </c>
       <c r="O25">
         <v>18.27</v>
@@ -1800,8 +1794,8 @@
       </c>
     </row>
     <row r="26" spans="1:16">
-      <c r="A26" t="s">
-        <v>16</v>
+      <c r="A26">
+        <v>20260422</v>
       </c>
       <c r="B26" t="s">
         <v>39</v>
@@ -1812,14 +1806,14 @@
       <c r="D26">
         <v>69</v>
       </c>
-      <c r="E26" t="s">
-        <v>53</v>
+      <c r="E26">
+        <v>7.8</v>
       </c>
       <c r="F26" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G26" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H26">
         <v>404.1</v>
@@ -1828,19 +1822,19 @@
         <v>1</v>
       </c>
       <c r="J26" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K26">
         <v>7</v>
       </c>
       <c r="L26" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M26" t="s">
+        <v>66</v>
+      </c>
+      <c r="N26" t="s">
         <v>68</v>
-      </c>
-      <c r="N26" t="s">
-        <v>70</v>
       </c>
       <c r="O26">
         <v>18.27</v>
@@ -1850,8 +1844,8 @@
       </c>
     </row>
     <row r="27" spans="1:16">
-      <c r="A27" t="s">
-        <v>16</v>
+      <c r="A27">
+        <v>20260422</v>
       </c>
       <c r="B27" t="s">
         <v>40</v>
@@ -1862,14 +1856,14 @@
       <c r="D27">
         <v>69</v>
       </c>
-      <c r="E27" t="s">
-        <v>52</v>
+      <c r="E27">
+        <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G27" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H27">
         <v>3847</v>
@@ -1878,19 +1872,19 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K27">
         <v>1</v>
       </c>
       <c r="L27" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M27" t="s">
+        <v>66</v>
+      </c>
+      <c r="N27" t="s">
         <v>68</v>
-      </c>
-      <c r="N27" t="s">
-        <v>70</v>
       </c>
       <c r="O27">
         <v>18.27</v>
@@ -1900,8 +1894,8 @@
       </c>
     </row>
     <row r="28" spans="1:16">
-      <c r="A28" t="s">
-        <v>16</v>
+      <c r="A28">
+        <v>20260422</v>
       </c>
       <c r="B28" t="s">
         <v>41</v>
@@ -1912,14 +1906,14 @@
       <c r="D28">
         <v>67.5</v>
       </c>
-      <c r="E28" t="s">
-        <v>52</v>
+      <c r="E28">
+        <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G28" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H28">
         <v>211.75</v>
@@ -1928,19 +1922,19 @@
         <v>2.5</v>
       </c>
       <c r="J28" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K28">
         <v>1</v>
       </c>
       <c r="L28" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M28" t="s">
+        <v>66</v>
+      </c>
+      <c r="N28" t="s">
         <v>68</v>
-      </c>
-      <c r="N28" t="s">
-        <v>70</v>
       </c>
       <c r="O28">
         <v>18.27</v>
@@ -1950,8 +1944,8 @@
       </c>
     </row>
     <row r="29" spans="1:16">
-      <c r="A29" t="s">
-        <v>16</v>
+      <c r="A29">
+        <v>20260422</v>
       </c>
       <c r="B29" t="s">
         <v>22</v>
@@ -1962,14 +1956,14 @@
       <c r="D29">
         <v>66.7</v>
       </c>
-      <c r="E29" t="s">
-        <v>54</v>
+      <c r="E29">
+        <v>-0.5</v>
       </c>
       <c r="F29" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G29" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H29">
         <v>1381.5</v>
@@ -1978,19 +1972,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J29" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K29">
         <v>7</v>
       </c>
       <c r="L29" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M29" t="s">
+        <v>66</v>
+      </c>
+      <c r="N29" t="s">
         <v>68</v>
-      </c>
-      <c r="N29" t="s">
-        <v>70</v>
       </c>
       <c r="O29">
         <v>18.27</v>
@@ -2000,8 +1994,8 @@
       </c>
     </row>
     <row r="30" spans="1:16">
-      <c r="A30" t="s">
-        <v>16</v>
+      <c r="A30">
+        <v>20260422</v>
       </c>
       <c r="B30" t="s">
         <v>23</v>
@@ -2012,14 +2006,14 @@
       <c r="D30">
         <v>66.7</v>
       </c>
-      <c r="E30" t="s">
-        <v>54</v>
+      <c r="E30">
+        <v>-0.5</v>
       </c>
       <c r="F30" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G30" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H30">
         <v>4483</v>
@@ -2028,19 +2022,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J30" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K30">
         <v>7</v>
       </c>
       <c r="L30" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M30" t="s">
+        <v>66</v>
+      </c>
+      <c r="N30" t="s">
         <v>68</v>
-      </c>
-      <c r="N30" t="s">
-        <v>70</v>
       </c>
       <c r="O30">
         <v>18.27</v>
@@ -2050,8 +2044,8 @@
       </c>
     </row>
     <row r="31" spans="1:16">
-      <c r="A31" t="s">
-        <v>16</v>
+      <c r="A31">
+        <v>20260422</v>
       </c>
       <c r="B31" t="s">
         <v>42</v>
@@ -2062,14 +2056,14 @@
       <c r="D31">
         <v>66.7</v>
       </c>
-      <c r="E31" t="s">
-        <v>52</v>
+      <c r="E31">
+        <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G31" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H31">
         <v>89.05</v>
@@ -2078,19 +2072,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J31" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K31">
         <v>1</v>
       </c>
       <c r="L31" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M31" t="s">
+        <v>66</v>
+      </c>
+      <c r="N31" t="s">
         <v>68</v>
-      </c>
-      <c r="N31" t="s">
-        <v>70</v>
       </c>
       <c r="O31">
         <v>18.27</v>
@@ -2100,8 +2094,8 @@
       </c>
     </row>
     <row r="32" spans="1:16">
-      <c r="A32" t="s">
-        <v>16</v>
+      <c r="A32">
+        <v>20260422</v>
       </c>
       <c r="B32" t="s">
         <v>43</v>
@@ -2112,14 +2106,14 @@
       <c r="D32">
         <v>66.59999999999999</v>
       </c>
-      <c r="E32" t="s">
-        <v>52</v>
+      <c r="E32">
+        <v>0</v>
       </c>
       <c r="F32" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G32" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H32">
         <v>1291.1</v>
@@ -2128,19 +2122,19 @@
         <v>3.400000000000006</v>
       </c>
       <c r="J32" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K32">
         <v>1</v>
       </c>
       <c r="L32" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M32" t="s">
+        <v>66</v>
+      </c>
+      <c r="N32" t="s">
         <v>68</v>
-      </c>
-      <c r="N32" t="s">
-        <v>70</v>
       </c>
       <c r="O32">
         <v>18.27</v>
@@ -2150,8 +2144,8 @@
       </c>
     </row>
     <row r="33" spans="1:16">
-      <c r="A33" t="s">
-        <v>16</v>
+      <c r="A33">
+        <v>20260422</v>
       </c>
       <c r="B33" t="s">
         <v>32</v>
@@ -2162,14 +2156,14 @@
       <c r="D33">
         <v>64.09999999999999</v>
       </c>
-      <c r="E33" t="s">
-        <v>54</v>
+      <c r="E33">
+        <v>-0.5</v>
       </c>
       <c r="F33" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G33" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H33">
         <v>1414.6</v>
@@ -2178,19 +2172,19 @@
         <v>5.900000000000006</v>
       </c>
       <c r="J33" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K33">
         <v>2</v>
       </c>
       <c r="L33" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M33" t="s">
+        <v>66</v>
+      </c>
+      <c r="N33" t="s">
         <v>68</v>
-      </c>
-      <c r="N33" t="s">
-        <v>70</v>
       </c>
       <c r="O33">
         <v>18.27</v>
@@ -2200,8 +2194,8 @@
       </c>
     </row>
     <row r="34" spans="1:16">
-      <c r="A34" t="s">
-        <v>16</v>
+      <c r="A34">
+        <v>20260422</v>
       </c>
       <c r="B34" t="s">
         <v>33</v>
@@ -2212,14 +2206,14 @@
       <c r="D34">
         <v>63.7</v>
       </c>
-      <c r="E34" t="s">
-        <v>54</v>
+      <c r="E34">
+        <v>-0.5</v>
       </c>
       <c r="F34" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G34" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H34">
         <v>9760</v>
@@ -2228,19 +2222,19 @@
         <v>6.299999999999997</v>
       </c>
       <c r="J34" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K34">
         <v>7</v>
       </c>
       <c r="L34" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M34" t="s">
+        <v>66</v>
+      </c>
+      <c r="N34" t="s">
         <v>68</v>
-      </c>
-      <c r="N34" t="s">
-        <v>70</v>
       </c>
       <c r="O34">
         <v>18.27</v>
@@ -2250,8 +2244,8 @@
       </c>
     </row>
     <row r="35" spans="1:16">
-      <c r="A35" t="s">
-        <v>16</v>
+      <c r="A35">
+        <v>20260422</v>
       </c>
       <c r="B35" t="s">
         <v>44</v>
@@ -2262,14 +2256,14 @@
       <c r="D35">
         <v>62.7</v>
       </c>
-      <c r="E35" t="s">
-        <v>52</v>
+      <c r="E35">
+        <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G35" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H35">
         <v>125.85</v>
@@ -2278,19 +2272,19 @@
         <v>7.299999999999997</v>
       </c>
       <c r="J35" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K35">
         <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M35" t="s">
+        <v>66</v>
+      </c>
+      <c r="N35" t="s">
         <v>68</v>
-      </c>
-      <c r="N35" t="s">
-        <v>70</v>
       </c>
       <c r="O35">
         <v>18.27</v>
@@ -2300,8 +2294,8 @@
       </c>
     </row>
     <row r="36" spans="1:16">
-      <c r="A36" t="s">
-        <v>16</v>
+      <c r="A36">
+        <v>20260422</v>
       </c>
       <c r="B36" t="s">
         <v>45</v>
@@ -2312,14 +2306,14 @@
       <c r="D36">
         <v>62.1</v>
       </c>
-      <c r="E36" t="s">
-        <v>52</v>
+      <c r="E36">
+        <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G36" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H36">
         <v>1171.95</v>
@@ -2328,19 +2322,19 @@
         <v>7.899999999999999</v>
       </c>
       <c r="J36" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K36">
         <v>1</v>
       </c>
       <c r="L36" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M36" t="s">
+        <v>66</v>
+      </c>
+      <c r="N36" t="s">
         <v>68</v>
-      </c>
-      <c r="N36" t="s">
-        <v>70</v>
       </c>
       <c r="O36">
         <v>18.27</v>
@@ -2350,8 +2344,8 @@
       </c>
     </row>
     <row r="37" spans="1:16">
-      <c r="A37" t="s">
-        <v>16</v>
+      <c r="A37">
+        <v>20260422</v>
       </c>
       <c r="B37" t="s">
         <v>24</v>
@@ -2362,14 +2356,14 @@
       <c r="D37">
         <v>60.7</v>
       </c>
-      <c r="E37" t="s">
-        <v>55</v>
+      <c r="E37">
+        <v>-6.5</v>
       </c>
       <c r="F37" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G37" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H37">
         <v>1038.1</v>
@@ -2378,19 +2372,19 @@
         <v>9.299999999999997</v>
       </c>
       <c r="J37" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K37">
         <v>7</v>
       </c>
       <c r="L37" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M37" t="s">
+        <v>66</v>
+      </c>
+      <c r="N37" t="s">
         <v>68</v>
-      </c>
-      <c r="N37" t="s">
-        <v>70</v>
       </c>
       <c r="O37">
         <v>18.27</v>
@@ -2400,8 +2394,8 @@
       </c>
     </row>
     <row r="38" spans="1:16">
-      <c r="A38" t="s">
-        <v>16</v>
+      <c r="A38">
+        <v>20260422</v>
       </c>
       <c r="B38" t="s">
         <v>37</v>
@@ -2412,14 +2406,14 @@
       <c r="D38">
         <v>58.6</v>
       </c>
-      <c r="E38" t="s">
-        <v>56</v>
+      <c r="E38">
+        <v>-2.9</v>
       </c>
       <c r="F38" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G38" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H38">
         <v>319.6</v>
@@ -2428,19 +2422,19 @@
         <v>11.4</v>
       </c>
       <c r="J38" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="K38">
         <v>7</v>
       </c>
       <c r="L38" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M38" t="s">
+        <v>66</v>
+      </c>
+      <c r="N38" t="s">
         <v>68</v>
-      </c>
-      <c r="N38" t="s">
-        <v>70</v>
       </c>
       <c r="O38">
         <v>18.27</v>
@@ -2450,8 +2444,8 @@
       </c>
     </row>
     <row r="39" spans="1:16">
-      <c r="A39" t="s">
-        <v>16</v>
+      <c r="A39">
+        <v>20260422</v>
       </c>
       <c r="B39" t="s">
         <v>46</v>
@@ -2462,14 +2456,14 @@
       <c r="D39">
         <v>58.3</v>
       </c>
-      <c r="E39" t="s">
-        <v>52</v>
+      <c r="E39">
+        <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G39" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H39">
         <v>2314.1</v>
@@ -2478,19 +2472,19 @@
         <v>11.7</v>
       </c>
       <c r="J39" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K39">
         <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M39" t="s">
+        <v>66</v>
+      </c>
+      <c r="N39" t="s">
         <v>68</v>
-      </c>
-      <c r="N39" t="s">
-        <v>70</v>
       </c>
       <c r="O39">
         <v>18.27</v>
@@ -2500,8 +2494,8 @@
       </c>
     </row>
     <row r="40" spans="1:16">
-      <c r="A40" t="s">
-        <v>16</v>
+      <c r="A40">
+        <v>20260422</v>
       </c>
       <c r="B40" t="s">
         <v>47</v>
@@ -2512,14 +2506,14 @@
       <c r="D40">
         <v>58.3</v>
       </c>
-      <c r="E40" t="s">
-        <v>52</v>
+      <c r="E40">
+        <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G40" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H40">
         <v>3723.6</v>
@@ -2528,19 +2522,19 @@
         <v>11.7</v>
       </c>
       <c r="J40" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="K40">
         <v>1</v>
       </c>
       <c r="L40" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M40" t="s">
+        <v>66</v>
+      </c>
+      <c r="N40" t="s">
         <v>68</v>
-      </c>
-      <c r="N40" t="s">
-        <v>70</v>
       </c>
       <c r="O40">
         <v>18.27</v>
@@ -2550,8 +2544,8 @@
       </c>
     </row>
     <row r="41" spans="1:16">
-      <c r="A41" t="s">
-        <v>16</v>
+      <c r="A41">
+        <v>20260422</v>
       </c>
       <c r="B41" t="s">
         <v>48</v>
@@ -2562,14 +2556,14 @@
       <c r="D41">
         <v>56.7</v>
       </c>
-      <c r="E41" t="s">
-        <v>54</v>
+      <c r="E41">
+        <v>-0.5</v>
       </c>
       <c r="F41" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G41" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H41">
         <v>4049.2</v>
@@ -2578,19 +2572,19 @@
         <v>13.3</v>
       </c>
       <c r="J41" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="K41">
         <v>3</v>
       </c>
       <c r="L41" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="M41" t="s">
+        <v>66</v>
+      </c>
+      <c r="N41" t="s">
         <v>68</v>
-      </c>
-      <c r="N41" t="s">
-        <v>70</v>
       </c>
       <c r="O41">
         <v>18.27</v>
@@ -2600,8 +2594,8 @@
       </c>
     </row>
     <row r="42" spans="1:16">
-      <c r="A42" t="s">
-        <v>16</v>
+      <c r="A42">
+        <v>20260422</v>
       </c>
       <c r="B42" t="s">
         <v>49</v>
@@ -2612,14 +2606,14 @@
       <c r="D42">
         <v>55.4</v>
       </c>
-      <c r="E42" t="s">
-        <v>52</v>
+      <c r="E42">
+        <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G42" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H42">
         <v>124.98</v>
@@ -2628,25 +2622,875 @@
         <v>14.6</v>
       </c>
       <c r="J42" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="K42">
         <v>1</v>
       </c>
       <c r="L42" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M42" t="s">
+        <v>66</v>
+      </c>
+      <c r="N42" t="s">
         <v>68</v>
-      </c>
-      <c r="N42" t="s">
-        <v>70</v>
       </c>
       <c r="O42">
         <v>18.27</v>
       </c>
       <c r="P42">
         <v>272</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
+      <c r="A43" t="s">
+        <v>16</v>
+      </c>
+      <c r="B43" t="s">
+        <v>22</v>
+      </c>
+      <c r="C43" t="s">
+        <v>51</v>
+      </c>
+      <c r="D43">
+        <v>69.09999999999999</v>
+      </c>
+      <c r="E43" t="s">
+        <v>52</v>
+      </c>
+      <c r="F43" t="s">
+        <v>55</v>
+      </c>
+      <c r="G43" t="s">
+        <v>56</v>
+      </c>
+      <c r="H43">
+        <v>1388.7</v>
+      </c>
+      <c r="I43">
+        <v>0.9000000000000057</v>
+      </c>
+      <c r="J43" t="s">
+        <v>57</v>
+      </c>
+      <c r="K43">
+        <v>8</v>
+      </c>
+      <c r="L43" t="s">
+        <v>64</v>
+      </c>
+      <c r="M43" t="s">
+        <v>66</v>
+      </c>
+      <c r="N43" t="s">
+        <v>68</v>
+      </c>
+      <c r="O43">
+        <v>18.23</v>
+      </c>
+      <c r="P43">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
+      <c r="A44" t="s">
+        <v>16</v>
+      </c>
+      <c r="B44" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" t="s">
+        <v>51</v>
+      </c>
+      <c r="D44">
+        <v>69</v>
+      </c>
+      <c r="E44" t="s">
+        <v>53</v>
+      </c>
+      <c r="F44" t="s">
+        <v>55</v>
+      </c>
+      <c r="G44" t="s">
+        <v>56</v>
+      </c>
+      <c r="H44">
+        <v>404.8</v>
+      </c>
+      <c r="I44">
+        <v>1</v>
+      </c>
+      <c r="J44" t="s">
+        <v>57</v>
+      </c>
+      <c r="K44">
+        <v>8</v>
+      </c>
+      <c r="L44" t="s">
+        <v>64</v>
+      </c>
+      <c r="M44" t="s">
+        <v>66</v>
+      </c>
+      <c r="N44" t="s">
+        <v>68</v>
+      </c>
+      <c r="O44">
+        <v>18.23</v>
+      </c>
+      <c r="P44">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
+      <c r="A45" t="s">
+        <v>16</v>
+      </c>
+      <c r="B45" t="s">
+        <v>40</v>
+      </c>
+      <c r="C45" t="s">
+        <v>51</v>
+      </c>
+      <c r="D45">
+        <v>69</v>
+      </c>
+      <c r="E45" t="s">
+        <v>53</v>
+      </c>
+      <c r="F45" t="s">
+        <v>55</v>
+      </c>
+      <c r="G45" t="s">
+        <v>56</v>
+      </c>
+      <c r="H45">
+        <v>3845.7</v>
+      </c>
+      <c r="I45">
+        <v>1</v>
+      </c>
+      <c r="J45" t="s">
+        <v>57</v>
+      </c>
+      <c r="K45">
+        <v>2</v>
+      </c>
+      <c r="L45" t="s">
+        <v>65</v>
+      </c>
+      <c r="M45" t="s">
+        <v>66</v>
+      </c>
+      <c r="N45" t="s">
+        <v>68</v>
+      </c>
+      <c r="O45">
+        <v>18.23</v>
+      </c>
+      <c r="P45">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="46" spans="1:16">
+      <c r="A46" t="s">
+        <v>16</v>
+      </c>
+      <c r="B46" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46" t="s">
+        <v>51</v>
+      </c>
+      <c r="D46">
+        <v>68.5</v>
+      </c>
+      <c r="E46" t="s">
+        <v>54</v>
+      </c>
+      <c r="F46" t="s">
+        <v>55</v>
+      </c>
+      <c r="G46" t="s">
+        <v>56</v>
+      </c>
+      <c r="H46">
+        <v>213.03</v>
+      </c>
+      <c r="I46">
+        <v>1.5</v>
+      </c>
+      <c r="J46" t="s">
+        <v>59</v>
+      </c>
+      <c r="K46">
+        <v>2</v>
+      </c>
+      <c r="L46" t="s">
+        <v>65</v>
+      </c>
+      <c r="M46" t="s">
+        <v>66</v>
+      </c>
+      <c r="N46" t="s">
+        <v>68</v>
+      </c>
+      <c r="O46">
+        <v>18.23</v>
+      </c>
+      <c r="P46">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="47" spans="1:16">
+      <c r="A47" t="s">
+        <v>16</v>
+      </c>
+      <c r="B47" t="s">
+        <v>23</v>
+      </c>
+      <c r="C47" t="s">
+        <v>51</v>
+      </c>
+      <c r="D47">
+        <v>66.7</v>
+      </c>
+      <c r="E47" t="s">
+        <v>53</v>
+      </c>
+      <c r="F47" t="s">
+        <v>55</v>
+      </c>
+      <c r="G47" t="s">
+        <v>56</v>
+      </c>
+      <c r="H47">
+        <v>4477</v>
+      </c>
+      <c r="I47">
+        <v>3.299999999999997</v>
+      </c>
+      <c r="J47" t="s">
+        <v>57</v>
+      </c>
+      <c r="K47">
+        <v>8</v>
+      </c>
+      <c r="L47" t="s">
+        <v>64</v>
+      </c>
+      <c r="M47" t="s">
+        <v>66</v>
+      </c>
+      <c r="N47" t="s">
+        <v>68</v>
+      </c>
+      <c r="O47">
+        <v>18.23</v>
+      </c>
+      <c r="P47">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="48" spans="1:16">
+      <c r="A48" t="s">
+        <v>16</v>
+      </c>
+      <c r="B48" t="s">
+        <v>42</v>
+      </c>
+      <c r="C48" t="s">
+        <v>51</v>
+      </c>
+      <c r="D48">
+        <v>66.7</v>
+      </c>
+      <c r="E48" t="s">
+        <v>53</v>
+      </c>
+      <c r="F48" t="s">
+        <v>55</v>
+      </c>
+      <c r="G48" t="s">
+        <v>56</v>
+      </c>
+      <c r="H48">
+        <v>88.98999999999999</v>
+      </c>
+      <c r="I48">
+        <v>3.299999999999997</v>
+      </c>
+      <c r="J48" t="s">
+        <v>57</v>
+      </c>
+      <c r="K48">
+        <v>2</v>
+      </c>
+      <c r="L48" t="s">
+        <v>65</v>
+      </c>
+      <c r="M48" t="s">
+        <v>66</v>
+      </c>
+      <c r="N48" t="s">
+        <v>68</v>
+      </c>
+      <c r="O48">
+        <v>18.23</v>
+      </c>
+      <c r="P48">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="49" spans="1:16">
+      <c r="A49" t="s">
+        <v>16</v>
+      </c>
+      <c r="B49" t="s">
+        <v>43</v>
+      </c>
+      <c r="C49" t="s">
+        <v>51</v>
+      </c>
+      <c r="D49">
+        <v>66.59999999999999</v>
+      </c>
+      <c r="E49" t="s">
+        <v>53</v>
+      </c>
+      <c r="F49" t="s">
+        <v>55</v>
+      </c>
+      <c r="G49" t="s">
+        <v>56</v>
+      </c>
+      <c r="H49">
+        <v>1288.9</v>
+      </c>
+      <c r="I49">
+        <v>3.400000000000006</v>
+      </c>
+      <c r="J49" t="s">
+        <v>57</v>
+      </c>
+      <c r="K49">
+        <v>2</v>
+      </c>
+      <c r="L49" t="s">
+        <v>65</v>
+      </c>
+      <c r="M49" t="s">
+        <v>66</v>
+      </c>
+      <c r="N49" t="s">
+        <v>68</v>
+      </c>
+      <c r="O49">
+        <v>18.23</v>
+      </c>
+      <c r="P49">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="50" spans="1:16">
+      <c r="A50" t="s">
+        <v>16</v>
+      </c>
+      <c r="B50" t="s">
+        <v>32</v>
+      </c>
+      <c r="C50" t="s">
+        <v>51</v>
+      </c>
+      <c r="D50">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="E50" t="s">
+        <v>53</v>
+      </c>
+      <c r="F50" t="s">
+        <v>55</v>
+      </c>
+      <c r="G50" t="s">
+        <v>56</v>
+      </c>
+      <c r="H50">
+        <v>1419</v>
+      </c>
+      <c r="I50">
+        <v>5.900000000000006</v>
+      </c>
+      <c r="J50" t="s">
+        <v>59</v>
+      </c>
+      <c r="K50">
+        <v>3</v>
+      </c>
+      <c r="L50" t="s">
+        <v>63</v>
+      </c>
+      <c r="M50" t="s">
+        <v>66</v>
+      </c>
+      <c r="N50" t="s">
+        <v>68</v>
+      </c>
+      <c r="O50">
+        <v>18.23</v>
+      </c>
+      <c r="P50">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="51" spans="1:16">
+      <c r="A51" t="s">
+        <v>16</v>
+      </c>
+      <c r="B51" t="s">
+        <v>33</v>
+      </c>
+      <c r="C51" t="s">
+        <v>51</v>
+      </c>
+      <c r="D51">
+        <v>63.7</v>
+      </c>
+      <c r="E51" t="s">
+        <v>53</v>
+      </c>
+      <c r="F51" t="s">
+        <v>55</v>
+      </c>
+      <c r="G51" t="s">
+        <v>56</v>
+      </c>
+      <c r="H51">
+        <v>9758</v>
+      </c>
+      <c r="I51">
+        <v>6.299999999999997</v>
+      </c>
+      <c r="J51" t="s">
+        <v>57</v>
+      </c>
+      <c r="K51">
+        <v>8</v>
+      </c>
+      <c r="L51" t="s">
+        <v>64</v>
+      </c>
+      <c r="M51" t="s">
+        <v>66</v>
+      </c>
+      <c r="N51" t="s">
+        <v>68</v>
+      </c>
+      <c r="O51">
+        <v>18.23</v>
+      </c>
+      <c r="P51">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16">
+      <c r="A52" t="s">
+        <v>16</v>
+      </c>
+      <c r="B52" t="s">
+        <v>44</v>
+      </c>
+      <c r="C52" t="s">
+        <v>51</v>
+      </c>
+      <c r="D52">
+        <v>62.7</v>
+      </c>
+      <c r="E52" t="s">
+        <v>53</v>
+      </c>
+      <c r="F52" t="s">
+        <v>55</v>
+      </c>
+      <c r="G52" t="s">
+        <v>56</v>
+      </c>
+      <c r="H52">
+        <v>125.98</v>
+      </c>
+      <c r="I52">
+        <v>7.299999999999997</v>
+      </c>
+      <c r="J52" t="s">
+        <v>57</v>
+      </c>
+      <c r="K52">
+        <v>2</v>
+      </c>
+      <c r="L52" t="s">
+        <v>65</v>
+      </c>
+      <c r="M52" t="s">
+        <v>66</v>
+      </c>
+      <c r="N52" t="s">
+        <v>68</v>
+      </c>
+      <c r="O52">
+        <v>18.23</v>
+      </c>
+      <c r="P52">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16">
+      <c r="A53" t="s">
+        <v>16</v>
+      </c>
+      <c r="B53" t="s">
+        <v>45</v>
+      </c>
+      <c r="C53" t="s">
+        <v>51</v>
+      </c>
+      <c r="D53">
+        <v>62.1</v>
+      </c>
+      <c r="E53" t="s">
+        <v>53</v>
+      </c>
+      <c r="F53" t="s">
+        <v>55</v>
+      </c>
+      <c r="G53" t="s">
+        <v>56</v>
+      </c>
+      <c r="H53">
+        <v>1182</v>
+      </c>
+      <c r="I53">
+        <v>7.899999999999999</v>
+      </c>
+      <c r="J53" t="s">
+        <v>59</v>
+      </c>
+      <c r="K53">
+        <v>2</v>
+      </c>
+      <c r="L53" t="s">
+        <v>65</v>
+      </c>
+      <c r="M53" t="s">
+        <v>66</v>
+      </c>
+      <c r="N53" t="s">
+        <v>68</v>
+      </c>
+      <c r="O53">
+        <v>18.23</v>
+      </c>
+      <c r="P53">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16">
+      <c r="A54" t="s">
+        <v>16</v>
+      </c>
+      <c r="B54" t="s">
+        <v>24</v>
+      </c>
+      <c r="C54" t="s">
+        <v>51</v>
+      </c>
+      <c r="D54">
+        <v>60.7</v>
+      </c>
+      <c r="E54" t="s">
+        <v>53</v>
+      </c>
+      <c r="F54" t="s">
+        <v>55</v>
+      </c>
+      <c r="G54" t="s">
+        <v>56</v>
+      </c>
+      <c r="H54">
+        <v>1040</v>
+      </c>
+      <c r="I54">
+        <v>9.299999999999997</v>
+      </c>
+      <c r="J54" t="s">
+        <v>57</v>
+      </c>
+      <c r="K54">
+        <v>8</v>
+      </c>
+      <c r="L54" t="s">
+        <v>64</v>
+      </c>
+      <c r="M54" t="s">
+        <v>66</v>
+      </c>
+      <c r="N54" t="s">
+        <v>68</v>
+      </c>
+      <c r="O54">
+        <v>18.23</v>
+      </c>
+      <c r="P54">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="55" spans="1:16">
+      <c r="A55" t="s">
+        <v>16</v>
+      </c>
+      <c r="B55" t="s">
+        <v>37</v>
+      </c>
+      <c r="C55" t="s">
+        <v>51</v>
+      </c>
+      <c r="D55">
+        <v>58.6</v>
+      </c>
+      <c r="E55" t="s">
+        <v>53</v>
+      </c>
+      <c r="F55" t="s">
+        <v>55</v>
+      </c>
+      <c r="G55" t="s">
+        <v>56</v>
+      </c>
+      <c r="H55">
+        <v>320.2</v>
+      </c>
+      <c r="I55">
+        <v>11.4</v>
+      </c>
+      <c r="J55" t="s">
+        <v>61</v>
+      </c>
+      <c r="K55">
+        <v>8</v>
+      </c>
+      <c r="L55" t="s">
+        <v>64</v>
+      </c>
+      <c r="M55" t="s">
+        <v>66</v>
+      </c>
+      <c r="N55" t="s">
+        <v>68</v>
+      </c>
+      <c r="O55">
+        <v>18.23</v>
+      </c>
+      <c r="P55">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="56" spans="1:16">
+      <c r="A56" t="s">
+        <v>16</v>
+      </c>
+      <c r="B56" t="s">
+        <v>46</v>
+      </c>
+      <c r="C56" t="s">
+        <v>51</v>
+      </c>
+      <c r="D56">
+        <v>58.3</v>
+      </c>
+      <c r="E56" t="s">
+        <v>53</v>
+      </c>
+      <c r="F56" t="s">
+        <v>55</v>
+      </c>
+      <c r="G56" t="s">
+        <v>56</v>
+      </c>
+      <c r="H56">
+        <v>2314.8</v>
+      </c>
+      <c r="I56">
+        <v>11.7</v>
+      </c>
+      <c r="J56" t="s">
+        <v>59</v>
+      </c>
+      <c r="K56">
+        <v>2</v>
+      </c>
+      <c r="L56" t="s">
+        <v>65</v>
+      </c>
+      <c r="M56" t="s">
+        <v>66</v>
+      </c>
+      <c r="N56" t="s">
+        <v>68</v>
+      </c>
+      <c r="O56">
+        <v>18.23</v>
+      </c>
+      <c r="P56">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="57" spans="1:16">
+      <c r="A57" t="s">
+        <v>16</v>
+      </c>
+      <c r="B57" t="s">
+        <v>47</v>
+      </c>
+      <c r="C57" t="s">
+        <v>51</v>
+      </c>
+      <c r="D57">
+        <v>58.3</v>
+      </c>
+      <c r="E57" t="s">
+        <v>53</v>
+      </c>
+      <c r="F57" t="s">
+        <v>55</v>
+      </c>
+      <c r="G57" t="s">
+        <v>56</v>
+      </c>
+      <c r="H57">
+        <v>3716.5</v>
+      </c>
+      <c r="I57">
+        <v>11.7</v>
+      </c>
+      <c r="J57" t="s">
+        <v>57</v>
+      </c>
+      <c r="K57">
+        <v>2</v>
+      </c>
+      <c r="L57" t="s">
+        <v>65</v>
+      </c>
+      <c r="M57" t="s">
+        <v>66</v>
+      </c>
+      <c r="N57" t="s">
+        <v>68</v>
+      </c>
+      <c r="O57">
+        <v>18.23</v>
+      </c>
+      <c r="P57">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="58" spans="1:16">
+      <c r="A58" t="s">
+        <v>16</v>
+      </c>
+      <c r="B58" t="s">
+        <v>48</v>
+      </c>
+      <c r="C58" t="s">
+        <v>51</v>
+      </c>
+      <c r="D58">
+        <v>56.7</v>
+      </c>
+      <c r="E58" t="s">
+        <v>53</v>
+      </c>
+      <c r="F58" t="s">
+        <v>55</v>
+      </c>
+      <c r="G58" t="s">
+        <v>56</v>
+      </c>
+      <c r="H58">
+        <v>4043</v>
+      </c>
+      <c r="I58">
+        <v>13.3</v>
+      </c>
+      <c r="J58" t="s">
+        <v>59</v>
+      </c>
+      <c r="K58">
+        <v>4</v>
+      </c>
+      <c r="L58" t="s">
+        <v>63</v>
+      </c>
+      <c r="M58" t="s">
+        <v>66</v>
+      </c>
+      <c r="N58" t="s">
+        <v>68</v>
+      </c>
+      <c r="O58">
+        <v>18.23</v>
+      </c>
+      <c r="P58">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="59" spans="1:16">
+      <c r="A59" t="s">
+        <v>16</v>
+      </c>
+      <c r="B59" t="s">
+        <v>49</v>
+      </c>
+      <c r="C59" t="s">
+        <v>51</v>
+      </c>
+      <c r="D59">
+        <v>55.4</v>
+      </c>
+      <c r="E59" t="s">
+        <v>53</v>
+      </c>
+      <c r="F59" t="s">
+        <v>55</v>
+      </c>
+      <c r="G59" t="s">
+        <v>56</v>
+      </c>
+      <c r="H59">
+        <v>125.04</v>
+      </c>
+      <c r="I59">
+        <v>14.6</v>
+      </c>
+      <c r="J59" t="s">
+        <v>58</v>
+      </c>
+      <c r="K59">
+        <v>2</v>
+      </c>
+      <c r="L59" t="s">
+        <v>65</v>
+      </c>
+      <c r="M59" t="s">
+        <v>66</v>
+      </c>
+      <c r="N59" t="s">
+        <v>68</v>
+      </c>
+      <c r="O59">
+        <v>18.23</v>
+      </c>
+      <c r="P59">
+        <v>254</v>
       </c>
     </row>
   </sheetData>

--- a/reports/watchlist_history.xlsx
+++ b/reports/watchlist_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="72">
   <si>
     <t>Date</t>
   </si>
@@ -166,19 +166,25 @@
     <t>GOLDBEES</t>
   </si>
   <si>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
     <t>BUY</t>
   </si>
   <si>
     <t>WATCH</t>
   </si>
   <si>
-    <t>+2.4</t>
-  </si>
-  <si>
     <t>+0.0</t>
   </si>
   <si>
-    <t>+1.0</t>
+    <t>+0.5</t>
+  </si>
+  <si>
+    <t>+6.5</t>
+  </si>
+  <si>
+    <t>-3.1</t>
   </si>
   <si>
     <t>Stage 2 — Uptrend ✓</t>
@@ -221,6 +227,9 @@
   </si>
   <si>
     <t>-2.8%</t>
+  </si>
+  <si>
+    <t>-2.9%</t>
   </si>
 </sst>
 </file>
@@ -552,7 +561,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P59"/>
+  <dimension ref="A1:P77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -613,7 +622,7 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2">
         <v>77.09999999999999</v>
@@ -622,10 +631,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H2">
         <v>11714</v>
@@ -637,13 +646,13 @@
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O2">
         <v>17.53</v>
@@ -660,7 +669,7 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D3">
         <v>74</v>
@@ -669,10 +678,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H3">
         <v>514.05</v>
@@ -684,13 +693,13 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O3">
         <v>17.53</v>
@@ -707,7 +716,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D4">
         <v>72</v>
@@ -716,10 +725,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G4" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H4">
         <v>1621.5</v>
@@ -731,13 +740,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="M4" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O4">
         <v>17.53</v>
@@ -754,7 +763,7 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D5">
         <v>69.59999999999999</v>
@@ -763,10 +772,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G5" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H5">
         <v>191.38</v>
@@ -775,19 +784,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J5" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N5" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O5">
         <v>17.53</v>
@@ -804,7 +813,7 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D6">
         <v>69.09999999999999</v>
@@ -813,10 +822,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G6" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H6">
         <v>1318.1</v>
@@ -825,19 +834,19 @@
         <v>0.9000000000000057</v>
       </c>
       <c r="J6" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M6" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O6">
         <v>17.53</v>
@@ -854,7 +863,7 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D7">
         <v>67.2</v>
@@ -863,10 +872,10 @@
         <v>-0.5</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G7" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H7">
         <v>1377.7</v>
@@ -875,19 +884,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J7" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K7">
         <v>6</v>
       </c>
       <c r="L7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M7" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O7">
         <v>17.53</v>
@@ -904,7 +913,7 @@
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8">
         <v>67.2</v>
@@ -913,10 +922,10 @@
         <v>-0.5</v>
       </c>
       <c r="F8" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G8" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H8">
         <v>4479.7</v>
@@ -925,19 +934,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J8" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K8">
         <v>6</v>
       </c>
       <c r="L8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M8" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N8" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O8">
         <v>17.53</v>
@@ -954,7 +963,7 @@
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D9">
         <v>67.2</v>
@@ -963,10 +972,10 @@
         <v>-0.5</v>
       </c>
       <c r="F9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G9" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H9">
         <v>1045.3</v>
@@ -975,19 +984,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K9">
         <v>6</v>
       </c>
       <c r="L9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O9">
         <v>17.53</v>
@@ -1004,7 +1013,7 @@
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D10">
         <v>67.2</v>
@@ -1013,10 +1022,10 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H10">
         <v>1055.65</v>
@@ -1025,19 +1034,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J10" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O10">
         <v>17.53</v>
@@ -1054,7 +1063,7 @@
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D11">
         <v>67.2</v>
@@ -1063,10 +1072,10 @@
         <v>-0.5</v>
       </c>
       <c r="F11" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G11" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H11">
         <v>1045.3</v>
@@ -1075,19 +1084,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K11">
         <v>6</v>
       </c>
       <c r="L11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M11" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N11" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O11">
         <v>17.53</v>
@@ -1104,7 +1113,7 @@
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D12">
         <v>67.2</v>
@@ -1113,10 +1122,10 @@
         <v>-0.5</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H12">
         <v>4479.7</v>
@@ -1125,19 +1134,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J12" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K12">
         <v>6</v>
       </c>
       <c r="L12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N12" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O12">
         <v>17.53</v>
@@ -1154,7 +1163,7 @@
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D13">
         <v>67.09999999999999</v>
@@ -1163,10 +1172,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G13" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H13">
         <v>581.3</v>
@@ -1175,19 +1184,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J13" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K13">
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M13" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N13" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O13">
         <v>17.53</v>
@@ -1204,7 +1213,7 @@
         <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D14">
         <v>67.09999999999999</v>
@@ -1213,10 +1222,10 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H14">
         <v>458.9</v>
@@ -1225,19 +1234,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J14" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M14" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N14" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O14">
         <v>17.53</v>
@@ -1254,7 +1263,7 @@
         <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D15">
         <v>65.59999999999999</v>
@@ -1263,10 +1272,10 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G15" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H15">
         <v>196.02</v>
@@ -1275,19 +1284,19 @@
         <v>4.400000000000006</v>
       </c>
       <c r="J15" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N15" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O15">
         <v>17.53</v>
@@ -1304,7 +1313,7 @@
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D16">
         <v>65</v>
@@ -1313,10 +1322,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G16" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H16">
         <v>4172.9</v>
@@ -1325,19 +1334,19 @@
         <v>5</v>
       </c>
       <c r="J16" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K16">
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N16" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O16">
         <v>17.53</v>
@@ -1354,7 +1363,7 @@
         <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D17">
         <v>64.7</v>
@@ -1363,10 +1372,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G17" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H17">
         <v>6373.5</v>
@@ -1375,19 +1384,19 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J17" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K17">
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M17" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O17">
         <v>17.53</v>
@@ -1404,7 +1413,7 @@
         <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D18">
         <v>64.7</v>
@@ -1413,10 +1422,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H18">
         <v>1113.1</v>
@@ -1425,19 +1434,19 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J18" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M18" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N18" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O18">
         <v>17.53</v>
@@ -1454,7 +1463,7 @@
         <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D19">
         <v>64.59999999999999</v>
@@ -1463,10 +1472,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G19" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H19">
         <v>1379.9</v>
@@ -1475,19 +1484,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J19" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K19">
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N19" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O19">
         <v>17.53</v>
@@ -1504,7 +1513,7 @@
         <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D20">
         <v>64.2</v>
@@ -1513,10 +1522,10 @@
         <v>-0.5</v>
       </c>
       <c r="F20" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G20" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H20">
         <v>9793</v>
@@ -1525,19 +1534,19 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J20" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K20">
         <v>6</v>
       </c>
       <c r="L20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M20" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N20" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O20">
         <v>17.53</v>
@@ -1554,7 +1563,7 @@
         <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D21">
         <v>64.2</v>
@@ -1563,10 +1572,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G21" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H21">
         <v>7955.5</v>
@@ -1575,19 +1584,19 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J21" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K21">
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M21" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N21" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O21">
         <v>17.53</v>
@@ -1604,7 +1613,7 @@
         <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D22">
         <v>63.6</v>
@@ -1613,10 +1622,10 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G22" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H22">
         <v>1037.85</v>
@@ -1625,19 +1634,19 @@
         <v>6.399999999999999</v>
       </c>
       <c r="J22" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K22">
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M22" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N22" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O22">
         <v>17.53</v>
@@ -1654,7 +1663,7 @@
         <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D23">
         <v>61.6</v>
@@ -1663,10 +1672,10 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G23" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H23">
         <v>979.1</v>
@@ -1675,19 +1684,19 @@
         <v>8.399999999999999</v>
       </c>
       <c r="J23" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K23">
         <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M23" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N23" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O23">
         <v>17.53</v>
@@ -1704,7 +1713,7 @@
         <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D24">
         <v>61.5</v>
@@ -1713,10 +1722,10 @@
         <v>-0.5</v>
       </c>
       <c r="F24" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G24" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H24">
         <v>319.35</v>
@@ -1725,19 +1734,19 @@
         <v>8.5</v>
       </c>
       <c r="J24" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K24">
         <v>6</v>
       </c>
       <c r="L24" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M24" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N24" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="O24">
         <v>17.53</v>
@@ -1754,7 +1763,7 @@
         <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D25">
         <v>70</v>
@@ -1763,10 +1772,10 @@
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G25" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H25">
         <v>767.65</v>
@@ -1781,10 +1790,10 @@
         <v>16</v>
       </c>
       <c r="M25" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N25" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O25">
         <v>18.27</v>
@@ -1801,7 +1810,7 @@
         <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D26">
         <v>69</v>
@@ -1810,10 +1819,10 @@
         <v>7.8</v>
       </c>
       <c r="F26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G26" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H26">
         <v>404.1</v>
@@ -1822,19 +1831,19 @@
         <v>1</v>
       </c>
       <c r="J26" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K26">
         <v>7</v>
       </c>
       <c r="L26" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M26" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N26" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O26">
         <v>18.27</v>
@@ -1851,7 +1860,7 @@
         <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D27">
         <v>69</v>
@@ -1860,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G27" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H27">
         <v>3847</v>
@@ -1872,19 +1881,19 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K27">
         <v>1</v>
       </c>
       <c r="L27" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M27" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N27" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O27">
         <v>18.27</v>
@@ -1901,7 +1910,7 @@
         <v>41</v>
       </c>
       <c r="C28" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D28">
         <v>67.5</v>
@@ -1910,10 +1919,10 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G28" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H28">
         <v>211.75</v>
@@ -1922,19 +1931,19 @@
         <v>2.5</v>
       </c>
       <c r="J28" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K28">
         <v>1</v>
       </c>
       <c r="L28" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M28" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N28" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O28">
         <v>18.27</v>
@@ -1951,7 +1960,7 @@
         <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D29">
         <v>66.7</v>
@@ -1960,10 +1969,10 @@
         <v>-0.5</v>
       </c>
       <c r="F29" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G29" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H29">
         <v>1381.5</v>
@@ -1972,19 +1981,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J29" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K29">
         <v>7</v>
       </c>
       <c r="L29" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M29" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N29" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O29">
         <v>18.27</v>
@@ -2001,7 +2010,7 @@
         <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D30">
         <v>66.7</v>
@@ -2010,10 +2019,10 @@
         <v>-0.5</v>
       </c>
       <c r="F30" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G30" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H30">
         <v>4483</v>
@@ -2022,19 +2031,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J30" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K30">
         <v>7</v>
       </c>
       <c r="L30" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M30" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N30" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O30">
         <v>18.27</v>
@@ -2051,7 +2060,7 @@
         <v>42</v>
       </c>
       <c r="C31" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D31">
         <v>66.7</v>
@@ -2060,10 +2069,10 @@
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G31" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H31">
         <v>89.05</v>
@@ -2072,19 +2081,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J31" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K31">
         <v>1</v>
       </c>
       <c r="L31" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M31" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N31" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O31">
         <v>18.27</v>
@@ -2101,7 +2110,7 @@
         <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D32">
         <v>66.59999999999999</v>
@@ -2110,10 +2119,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G32" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H32">
         <v>1291.1</v>
@@ -2122,19 +2131,19 @@
         <v>3.400000000000006</v>
       </c>
       <c r="J32" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K32">
         <v>1</v>
       </c>
       <c r="L32" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M32" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N32" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O32">
         <v>18.27</v>
@@ -2151,7 +2160,7 @@
         <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D33">
         <v>64.09999999999999</v>
@@ -2160,10 +2169,10 @@
         <v>-0.5</v>
       </c>
       <c r="F33" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G33" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H33">
         <v>1414.6</v>
@@ -2172,19 +2181,19 @@
         <v>5.900000000000006</v>
       </c>
       <c r="J33" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K33">
         <v>2</v>
       </c>
       <c r="L33" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M33" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N33" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O33">
         <v>18.27</v>
@@ -2201,7 +2210,7 @@
         <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D34">
         <v>63.7</v>
@@ -2210,10 +2219,10 @@
         <v>-0.5</v>
       </c>
       <c r="F34" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G34" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H34">
         <v>9760</v>
@@ -2222,19 +2231,19 @@
         <v>6.299999999999997</v>
       </c>
       <c r="J34" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K34">
         <v>7</v>
       </c>
       <c r="L34" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M34" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N34" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O34">
         <v>18.27</v>
@@ -2251,7 +2260,7 @@
         <v>44</v>
       </c>
       <c r="C35" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D35">
         <v>62.7</v>
@@ -2260,10 +2269,10 @@
         <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G35" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H35">
         <v>125.85</v>
@@ -2272,19 +2281,19 @@
         <v>7.299999999999997</v>
       </c>
       <c r="J35" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K35">
         <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M35" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N35" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O35">
         <v>18.27</v>
@@ -2301,7 +2310,7 @@
         <v>45</v>
       </c>
       <c r="C36" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D36">
         <v>62.1</v>
@@ -2310,10 +2319,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G36" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H36">
         <v>1171.95</v>
@@ -2322,19 +2331,19 @@
         <v>7.899999999999999</v>
       </c>
       <c r="J36" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K36">
         <v>1</v>
       </c>
       <c r="L36" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M36" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N36" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O36">
         <v>18.27</v>
@@ -2351,7 +2360,7 @@
         <v>24</v>
       </c>
       <c r="C37" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D37">
         <v>60.7</v>
@@ -2360,10 +2369,10 @@
         <v>-6.5</v>
       </c>
       <c r="F37" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G37" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H37">
         <v>1038.1</v>
@@ -2372,19 +2381,19 @@
         <v>9.299999999999997</v>
       </c>
       <c r="J37" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K37">
         <v>7</v>
       </c>
       <c r="L37" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M37" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N37" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O37">
         <v>18.27</v>
@@ -2401,7 +2410,7 @@
         <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D38">
         <v>58.6</v>
@@ -2410,10 +2419,10 @@
         <v>-2.9</v>
       </c>
       <c r="F38" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G38" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H38">
         <v>319.6</v>
@@ -2422,19 +2431,19 @@
         <v>11.4</v>
       </c>
       <c r="J38" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K38">
         <v>7</v>
       </c>
       <c r="L38" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M38" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N38" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O38">
         <v>18.27</v>
@@ -2451,7 +2460,7 @@
         <v>46</v>
       </c>
       <c r="C39" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D39">
         <v>58.3</v>
@@ -2460,10 +2469,10 @@
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G39" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H39">
         <v>2314.1</v>
@@ -2472,19 +2481,19 @@
         <v>11.7</v>
       </c>
       <c r="J39" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K39">
         <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M39" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N39" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O39">
         <v>18.27</v>
@@ -2501,7 +2510,7 @@
         <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D40">
         <v>58.3</v>
@@ -2510,10 +2519,10 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G40" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H40">
         <v>3723.6</v>
@@ -2522,19 +2531,19 @@
         <v>11.7</v>
       </c>
       <c r="J40" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K40">
         <v>1</v>
       </c>
       <c r="L40" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M40" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N40" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O40">
         <v>18.27</v>
@@ -2551,7 +2560,7 @@
         <v>48</v>
       </c>
       <c r="C41" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D41">
         <v>56.7</v>
@@ -2560,10 +2569,10 @@
         <v>-0.5</v>
       </c>
       <c r="F41" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G41" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H41">
         <v>4049.2</v>
@@ -2572,19 +2581,19 @@
         <v>13.3</v>
       </c>
       <c r="J41" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K41">
         <v>3</v>
       </c>
       <c r="L41" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M41" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N41" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O41">
         <v>18.27</v>
@@ -2601,7 +2610,7 @@
         <v>49</v>
       </c>
       <c r="C42" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D42">
         <v>55.4</v>
@@ -2610,10 +2619,10 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G42" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H42">
         <v>124.98</v>
@@ -2622,19 +2631,19 @@
         <v>14.6</v>
       </c>
       <c r="J42" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K42">
         <v>1</v>
       </c>
       <c r="L42" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M42" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N42" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O42">
         <v>18.27</v>
@@ -2644,26 +2653,26 @@
       </c>
     </row>
     <row r="43" spans="1:16">
-      <c r="A43" t="s">
-        <v>16</v>
+      <c r="A43">
+        <v>20260422</v>
       </c>
       <c r="B43" t="s">
         <v>22</v>
       </c>
       <c r="C43" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D43">
         <v>69.09999999999999</v>
       </c>
-      <c r="E43" t="s">
-        <v>52</v>
+      <c r="E43">
+        <v>2.4</v>
       </c>
       <c r="F43" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G43" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H43">
         <v>1388.7</v>
@@ -2672,19 +2681,19 @@
         <v>0.9000000000000057</v>
       </c>
       <c r="J43" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K43">
         <v>8</v>
       </c>
       <c r="L43" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M43" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N43" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O43">
         <v>18.23</v>
@@ -2694,26 +2703,26 @@
       </c>
     </row>
     <row r="44" spans="1:16">
-      <c r="A44" t="s">
-        <v>16</v>
+      <c r="A44">
+        <v>20260422</v>
       </c>
       <c r="B44" t="s">
         <v>39</v>
       </c>
       <c r="C44" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D44">
         <v>69</v>
       </c>
-      <c r="E44" t="s">
-        <v>53</v>
+      <c r="E44">
+        <v>0</v>
       </c>
       <c r="F44" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G44" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H44">
         <v>404.8</v>
@@ -2722,19 +2731,19 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K44">
         <v>8</v>
       </c>
       <c r="L44" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M44" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N44" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O44">
         <v>18.23</v>
@@ -2744,26 +2753,26 @@
       </c>
     </row>
     <row r="45" spans="1:16">
-      <c r="A45" t="s">
-        <v>16</v>
+      <c r="A45">
+        <v>20260422</v>
       </c>
       <c r="B45" t="s">
         <v>40</v>
       </c>
       <c r="C45" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D45">
         <v>69</v>
       </c>
-      <c r="E45" t="s">
-        <v>53</v>
+      <c r="E45">
+        <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G45" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H45">
         <v>3845.7</v>
@@ -2772,19 +2781,19 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K45">
         <v>2</v>
       </c>
       <c r="L45" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M45" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N45" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O45">
         <v>18.23</v>
@@ -2794,26 +2803,26 @@
       </c>
     </row>
     <row r="46" spans="1:16">
-      <c r="A46" t="s">
-        <v>16</v>
+      <c r="A46">
+        <v>20260422</v>
       </c>
       <c r="B46" t="s">
         <v>41</v>
       </c>
       <c r="C46" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D46">
         <v>68.5</v>
       </c>
-      <c r="E46" t="s">
-        <v>54</v>
+      <c r="E46">
+        <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G46" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H46">
         <v>213.03</v>
@@ -2822,19 +2831,19 @@
         <v>1.5</v>
       </c>
       <c r="J46" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K46">
         <v>2</v>
       </c>
       <c r="L46" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M46" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N46" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O46">
         <v>18.23</v>
@@ -2844,26 +2853,26 @@
       </c>
     </row>
     <row r="47" spans="1:16">
-      <c r="A47" t="s">
-        <v>16</v>
+      <c r="A47">
+        <v>20260422</v>
       </c>
       <c r="B47" t="s">
         <v>23</v>
       </c>
       <c r="C47" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D47">
         <v>66.7</v>
       </c>
-      <c r="E47" t="s">
-        <v>53</v>
+      <c r="E47">
+        <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G47" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H47">
         <v>4477</v>
@@ -2872,19 +2881,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J47" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K47">
         <v>8</v>
       </c>
       <c r="L47" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M47" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N47" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O47">
         <v>18.23</v>
@@ -2894,26 +2903,26 @@
       </c>
     </row>
     <row r="48" spans="1:16">
-      <c r="A48" t="s">
-        <v>16</v>
+      <c r="A48">
+        <v>20260422</v>
       </c>
       <c r="B48" t="s">
         <v>42</v>
       </c>
       <c r="C48" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D48">
         <v>66.7</v>
       </c>
-      <c r="E48" t="s">
-        <v>53</v>
+      <c r="E48">
+        <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G48" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H48">
         <v>88.98999999999999</v>
@@ -2922,19 +2931,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J48" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K48">
         <v>2</v>
       </c>
       <c r="L48" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M48" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N48" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O48">
         <v>18.23</v>
@@ -2944,26 +2953,26 @@
       </c>
     </row>
     <row r="49" spans="1:16">
-      <c r="A49" t="s">
-        <v>16</v>
+      <c r="A49">
+        <v>20260422</v>
       </c>
       <c r="B49" t="s">
         <v>43</v>
       </c>
       <c r="C49" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D49">
         <v>66.59999999999999</v>
       </c>
-      <c r="E49" t="s">
-        <v>53</v>
+      <c r="E49">
+        <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G49" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H49">
         <v>1288.9</v>
@@ -2972,19 +2981,19 @@
         <v>3.400000000000006</v>
       </c>
       <c r="J49" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K49">
         <v>2</v>
       </c>
       <c r="L49" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M49" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N49" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O49">
         <v>18.23</v>
@@ -2994,26 +3003,26 @@
       </c>
     </row>
     <row r="50" spans="1:16">
-      <c r="A50" t="s">
-        <v>16</v>
+      <c r="A50">
+        <v>20260422</v>
       </c>
       <c r="B50" t="s">
         <v>32</v>
       </c>
       <c r="C50" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D50">
         <v>64.09999999999999</v>
       </c>
-      <c r="E50" t="s">
-        <v>53</v>
+      <c r="E50">
+        <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G50" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H50">
         <v>1419</v>
@@ -3022,19 +3031,19 @@
         <v>5.900000000000006</v>
       </c>
       <c r="J50" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K50">
         <v>3</v>
       </c>
       <c r="L50" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M50" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N50" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O50">
         <v>18.23</v>
@@ -3044,26 +3053,26 @@
       </c>
     </row>
     <row r="51" spans="1:16">
-      <c r="A51" t="s">
-        <v>16</v>
+      <c r="A51">
+        <v>20260422</v>
       </c>
       <c r="B51" t="s">
         <v>33</v>
       </c>
       <c r="C51" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D51">
         <v>63.7</v>
       </c>
-      <c r="E51" t="s">
-        <v>53</v>
+      <c r="E51">
+        <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G51" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H51">
         <v>9758</v>
@@ -3072,19 +3081,19 @@
         <v>6.299999999999997</v>
       </c>
       <c r="J51" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K51">
         <v>8</v>
       </c>
       <c r="L51" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M51" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N51" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O51">
         <v>18.23</v>
@@ -3094,26 +3103,26 @@
       </c>
     </row>
     <row r="52" spans="1:16">
-      <c r="A52" t="s">
-        <v>16</v>
+      <c r="A52">
+        <v>20260422</v>
       </c>
       <c r="B52" t="s">
         <v>44</v>
       </c>
       <c r="C52" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D52">
         <v>62.7</v>
       </c>
-      <c r="E52" t="s">
-        <v>53</v>
+      <c r="E52">
+        <v>0</v>
       </c>
       <c r="F52" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G52" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H52">
         <v>125.98</v>
@@ -3122,19 +3131,19 @@
         <v>7.299999999999997</v>
       </c>
       <c r="J52" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K52">
         <v>2</v>
       </c>
       <c r="L52" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M52" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N52" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O52">
         <v>18.23</v>
@@ -3144,26 +3153,26 @@
       </c>
     </row>
     <row r="53" spans="1:16">
-      <c r="A53" t="s">
-        <v>16</v>
+      <c r="A53">
+        <v>20260422</v>
       </c>
       <c r="B53" t="s">
         <v>45</v>
       </c>
       <c r="C53" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D53">
         <v>62.1</v>
       </c>
-      <c r="E53" t="s">
-        <v>53</v>
+      <c r="E53">
+        <v>0</v>
       </c>
       <c r="F53" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G53" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H53">
         <v>1182</v>
@@ -3172,19 +3181,19 @@
         <v>7.899999999999999</v>
       </c>
       <c r="J53" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K53">
         <v>2</v>
       </c>
       <c r="L53" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M53" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N53" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O53">
         <v>18.23</v>
@@ -3194,26 +3203,26 @@
       </c>
     </row>
     <row r="54" spans="1:16">
-      <c r="A54" t="s">
-        <v>16</v>
+      <c r="A54">
+        <v>20260422</v>
       </c>
       <c r="B54" t="s">
         <v>24</v>
       </c>
       <c r="C54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D54">
         <v>60.7</v>
       </c>
-      <c r="E54" t="s">
-        <v>53</v>
+      <c r="E54">
+        <v>0</v>
       </c>
       <c r="F54" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G54" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H54">
         <v>1040</v>
@@ -3222,19 +3231,19 @@
         <v>9.299999999999997</v>
       </c>
       <c r="J54" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K54">
         <v>8</v>
       </c>
       <c r="L54" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M54" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N54" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O54">
         <v>18.23</v>
@@ -3244,26 +3253,26 @@
       </c>
     </row>
     <row r="55" spans="1:16">
-      <c r="A55" t="s">
-        <v>16</v>
+      <c r="A55">
+        <v>20260422</v>
       </c>
       <c r="B55" t="s">
         <v>37</v>
       </c>
       <c r="C55" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D55">
         <v>58.6</v>
       </c>
-      <c r="E55" t="s">
-        <v>53</v>
+      <c r="E55">
+        <v>0</v>
       </c>
       <c r="F55" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G55" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H55">
         <v>320.2</v>
@@ -3272,19 +3281,19 @@
         <v>11.4</v>
       </c>
       <c r="J55" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K55">
         <v>8</v>
       </c>
       <c r="L55" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="M55" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N55" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O55">
         <v>18.23</v>
@@ -3294,26 +3303,26 @@
       </c>
     </row>
     <row r="56" spans="1:16">
-      <c r="A56" t="s">
-        <v>16</v>
+      <c r="A56">
+        <v>20260422</v>
       </c>
       <c r="B56" t="s">
         <v>46</v>
       </c>
       <c r="C56" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D56">
         <v>58.3</v>
       </c>
-      <c r="E56" t="s">
-        <v>53</v>
+      <c r="E56">
+        <v>0</v>
       </c>
       <c r="F56" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G56" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H56">
         <v>2314.8</v>
@@ -3322,19 +3331,19 @@
         <v>11.7</v>
       </c>
       <c r="J56" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K56">
         <v>2</v>
       </c>
       <c r="L56" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M56" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N56" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O56">
         <v>18.23</v>
@@ -3344,26 +3353,26 @@
       </c>
     </row>
     <row r="57" spans="1:16">
-      <c r="A57" t="s">
-        <v>16</v>
+      <c r="A57">
+        <v>20260422</v>
       </c>
       <c r="B57" t="s">
         <v>47</v>
       </c>
       <c r="C57" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D57">
         <v>58.3</v>
       </c>
-      <c r="E57" t="s">
-        <v>53</v>
+      <c r="E57">
+        <v>0</v>
       </c>
       <c r="F57" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G57" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H57">
         <v>3716.5</v>
@@ -3372,19 +3381,19 @@
         <v>11.7</v>
       </c>
       <c r="J57" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="K57">
         <v>2</v>
       </c>
       <c r="L57" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M57" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N57" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O57">
         <v>18.23</v>
@@ -3394,26 +3403,26 @@
       </c>
     </row>
     <row r="58" spans="1:16">
-      <c r="A58" t="s">
-        <v>16</v>
+      <c r="A58">
+        <v>20260422</v>
       </c>
       <c r="B58" t="s">
         <v>48</v>
       </c>
       <c r="C58" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D58">
         <v>56.7</v>
       </c>
-      <c r="E58" t="s">
-        <v>53</v>
+      <c r="E58">
+        <v>0</v>
       </c>
       <c r="F58" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G58" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H58">
         <v>4043</v>
@@ -3422,19 +3431,19 @@
         <v>13.3</v>
       </c>
       <c r="J58" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="K58">
         <v>4</v>
       </c>
       <c r="L58" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M58" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N58" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O58">
         <v>18.23</v>
@@ -3444,26 +3453,26 @@
       </c>
     </row>
     <row r="59" spans="1:16">
-      <c r="A59" t="s">
-        <v>16</v>
+      <c r="A59">
+        <v>20260422</v>
       </c>
       <c r="B59" t="s">
         <v>49</v>
       </c>
       <c r="C59" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D59">
         <v>55.4</v>
       </c>
-      <c r="E59" t="s">
-        <v>53</v>
+      <c r="E59">
+        <v>0</v>
       </c>
       <c r="F59" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G59" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H59">
         <v>125.04</v>
@@ -3472,25 +3481,922 @@
         <v>14.6</v>
       </c>
       <c r="J59" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K59">
         <v>2</v>
       </c>
       <c r="L59" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="M59" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N59" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="O59">
         <v>18.23</v>
       </c>
       <c r="P59">
         <v>254</v>
+      </c>
+    </row>
+    <row r="60" spans="1:16">
+      <c r="A60" t="s">
+        <v>16</v>
+      </c>
+      <c r="B60" t="s">
+        <v>40</v>
+      </c>
+      <c r="C60" t="s">
+        <v>51</v>
+      </c>
+      <c r="D60">
+        <v>71.5</v>
+      </c>
+      <c r="E60" t="s">
+        <v>53</v>
+      </c>
+      <c r="F60" t="s">
+        <v>57</v>
+      </c>
+      <c r="G60" t="s">
+        <v>58</v>
+      </c>
+      <c r="H60">
+        <v>3852.5</v>
+      </c>
+      <c r="I60">
+        <v>0</v>
+      </c>
+      <c r="K60">
+        <v>1</v>
+      </c>
+      <c r="L60" t="s">
+        <v>16</v>
+      </c>
+      <c r="M60" t="s">
+        <v>68</v>
+      </c>
+      <c r="N60" t="s">
+        <v>71</v>
+      </c>
+      <c r="O60">
+        <v>18.08</v>
+      </c>
+      <c r="P60">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="61" spans="1:16">
+      <c r="A61" t="s">
+        <v>16</v>
+      </c>
+      <c r="B61" t="s">
+        <v>22</v>
+      </c>
+      <c r="C61" t="s">
+        <v>52</v>
+      </c>
+      <c r="D61">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="E61" t="s">
+        <v>54</v>
+      </c>
+      <c r="F61" t="s">
+        <v>57</v>
+      </c>
+      <c r="G61" t="s">
+        <v>58</v>
+      </c>
+      <c r="H61">
+        <v>1388.5</v>
+      </c>
+      <c r="I61">
+        <v>0.4000000000000057</v>
+      </c>
+      <c r="J61" t="s">
+        <v>59</v>
+      </c>
+      <c r="K61">
+        <v>9</v>
+      </c>
+      <c r="L61" t="s">
+        <v>66</v>
+      </c>
+      <c r="M61" t="s">
+        <v>68</v>
+      </c>
+      <c r="N61" t="s">
+        <v>71</v>
+      </c>
+      <c r="O61">
+        <v>18.08</v>
+      </c>
+      <c r="P61">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="62" spans="1:16">
+      <c r="A62" t="s">
+        <v>16</v>
+      </c>
+      <c r="B62" t="s">
+        <v>39</v>
+      </c>
+      <c r="C62" t="s">
+        <v>52</v>
+      </c>
+      <c r="D62">
+        <v>69.5</v>
+      </c>
+      <c r="E62" t="s">
+        <v>54</v>
+      </c>
+      <c r="F62" t="s">
+        <v>57</v>
+      </c>
+      <c r="G62" t="s">
+        <v>58</v>
+      </c>
+      <c r="H62">
+        <v>406.1</v>
+      </c>
+      <c r="I62">
+        <v>0.5</v>
+      </c>
+      <c r="J62" t="s">
+        <v>59</v>
+      </c>
+      <c r="K62">
+        <v>9</v>
+      </c>
+      <c r="L62" t="s">
+        <v>66</v>
+      </c>
+      <c r="M62" t="s">
+        <v>68</v>
+      </c>
+      <c r="N62" t="s">
+        <v>71</v>
+      </c>
+      <c r="O62">
+        <v>18.08</v>
+      </c>
+      <c r="P62">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="63" spans="1:16">
+      <c r="A63" t="s">
+        <v>16</v>
+      </c>
+      <c r="B63" t="s">
+        <v>41</v>
+      </c>
+      <c r="C63" t="s">
+        <v>52</v>
+      </c>
+      <c r="D63">
+        <v>69</v>
+      </c>
+      <c r="E63" t="s">
+        <v>54</v>
+      </c>
+      <c r="F63" t="s">
+        <v>57</v>
+      </c>
+      <c r="G63" t="s">
+        <v>58</v>
+      </c>
+      <c r="H63">
+        <v>213.6</v>
+      </c>
+      <c r="I63">
+        <v>1</v>
+      </c>
+      <c r="J63" t="s">
+        <v>61</v>
+      </c>
+      <c r="K63">
+        <v>3</v>
+      </c>
+      <c r="L63" t="s">
+        <v>67</v>
+      </c>
+      <c r="M63" t="s">
+        <v>68</v>
+      </c>
+      <c r="N63" t="s">
+        <v>71</v>
+      </c>
+      <c r="O63">
+        <v>18.08</v>
+      </c>
+      <c r="P63">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="64" spans="1:16">
+      <c r="A64" t="s">
+        <v>16</v>
+      </c>
+      <c r="B64" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64" t="s">
+        <v>52</v>
+      </c>
+      <c r="D64">
+        <v>67.2</v>
+      </c>
+      <c r="E64" t="s">
+        <v>54</v>
+      </c>
+      <c r="F64" t="s">
+        <v>57</v>
+      </c>
+      <c r="G64" t="s">
+        <v>58</v>
+      </c>
+      <c r="H64">
+        <v>4478</v>
+      </c>
+      <c r="I64">
+        <v>2.799999999999997</v>
+      </c>
+      <c r="J64" t="s">
+        <v>59</v>
+      </c>
+      <c r="K64">
+        <v>9</v>
+      </c>
+      <c r="L64" t="s">
+        <v>66</v>
+      </c>
+      <c r="M64" t="s">
+        <v>68</v>
+      </c>
+      <c r="N64" t="s">
+        <v>71</v>
+      </c>
+      <c r="O64">
+        <v>18.08</v>
+      </c>
+      <c r="P64">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="65" spans="1:16">
+      <c r="A65" t="s">
+        <v>16</v>
+      </c>
+      <c r="B65" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" t="s">
+        <v>52</v>
+      </c>
+      <c r="D65">
+        <v>67.2</v>
+      </c>
+      <c r="E65" t="s">
+        <v>55</v>
+      </c>
+      <c r="F65" t="s">
+        <v>57</v>
+      </c>
+      <c r="G65" t="s">
+        <v>58</v>
+      </c>
+      <c r="H65">
+        <v>1050.05</v>
+      </c>
+      <c r="I65">
+        <v>2.799999999999997</v>
+      </c>
+      <c r="J65" t="s">
+        <v>59</v>
+      </c>
+      <c r="K65">
+        <v>9</v>
+      </c>
+      <c r="L65" t="s">
+        <v>66</v>
+      </c>
+      <c r="M65" t="s">
+        <v>68</v>
+      </c>
+      <c r="N65" t="s">
+        <v>71</v>
+      </c>
+      <c r="O65">
+        <v>18.08</v>
+      </c>
+      <c r="P65">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="66" spans="1:16">
+      <c r="A66" t="s">
+        <v>16</v>
+      </c>
+      <c r="B66" t="s">
+        <v>42</v>
+      </c>
+      <c r="C66" t="s">
+        <v>52</v>
+      </c>
+      <c r="D66">
+        <v>67.2</v>
+      </c>
+      <c r="E66" t="s">
+        <v>54</v>
+      </c>
+      <c r="F66" t="s">
+        <v>57</v>
+      </c>
+      <c r="G66" t="s">
+        <v>58</v>
+      </c>
+      <c r="H66">
+        <v>88.59</v>
+      </c>
+      <c r="I66">
+        <v>2.799999999999997</v>
+      </c>
+      <c r="J66" t="s">
+        <v>59</v>
+      </c>
+      <c r="K66">
+        <v>3</v>
+      </c>
+      <c r="L66" t="s">
+        <v>67</v>
+      </c>
+      <c r="M66" t="s">
+        <v>68</v>
+      </c>
+      <c r="N66" t="s">
+        <v>71</v>
+      </c>
+      <c r="O66">
+        <v>18.08</v>
+      </c>
+      <c r="P66">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="67" spans="1:16">
+      <c r="A67" t="s">
+        <v>16</v>
+      </c>
+      <c r="B67" t="s">
+        <v>43</v>
+      </c>
+      <c r="C67" t="s">
+        <v>52</v>
+      </c>
+      <c r="D67">
+        <v>67.09999999999999</v>
+      </c>
+      <c r="E67" t="s">
+        <v>54</v>
+      </c>
+      <c r="F67" t="s">
+        <v>57</v>
+      </c>
+      <c r="G67" t="s">
+        <v>58</v>
+      </c>
+      <c r="H67">
+        <v>1291.7</v>
+      </c>
+      <c r="I67">
+        <v>2.900000000000006</v>
+      </c>
+      <c r="J67" t="s">
+        <v>59</v>
+      </c>
+      <c r="K67">
+        <v>3</v>
+      </c>
+      <c r="L67" t="s">
+        <v>67</v>
+      </c>
+      <c r="M67" t="s">
+        <v>68</v>
+      </c>
+      <c r="N67" t="s">
+        <v>71</v>
+      </c>
+      <c r="O67">
+        <v>18.08</v>
+      </c>
+      <c r="P67">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="68" spans="1:16">
+      <c r="A68" t="s">
+        <v>16</v>
+      </c>
+      <c r="B68" t="s">
+        <v>32</v>
+      </c>
+      <c r="C68" t="s">
+        <v>52</v>
+      </c>
+      <c r="D68">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="E68" t="s">
+        <v>54</v>
+      </c>
+      <c r="F68" t="s">
+        <v>57</v>
+      </c>
+      <c r="G68" t="s">
+        <v>58</v>
+      </c>
+      <c r="H68">
+        <v>1405.3</v>
+      </c>
+      <c r="I68">
+        <v>5.400000000000006</v>
+      </c>
+      <c r="J68" t="s">
+        <v>61</v>
+      </c>
+      <c r="K68">
+        <v>4</v>
+      </c>
+      <c r="L68" t="s">
+        <v>65</v>
+      </c>
+      <c r="M68" t="s">
+        <v>68</v>
+      </c>
+      <c r="N68" t="s">
+        <v>71</v>
+      </c>
+      <c r="O68">
+        <v>18.08</v>
+      </c>
+      <c r="P68">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="69" spans="1:16">
+      <c r="A69" t="s">
+        <v>16</v>
+      </c>
+      <c r="B69" t="s">
+        <v>44</v>
+      </c>
+      <c r="C69" t="s">
+        <v>52</v>
+      </c>
+      <c r="D69">
+        <v>63.2</v>
+      </c>
+      <c r="E69" t="s">
+        <v>54</v>
+      </c>
+      <c r="F69" t="s">
+        <v>57</v>
+      </c>
+      <c r="G69" t="s">
+        <v>58</v>
+      </c>
+      <c r="H69">
+        <v>125.89</v>
+      </c>
+      <c r="I69">
+        <v>6.799999999999997</v>
+      </c>
+      <c r="J69" t="s">
+        <v>59</v>
+      </c>
+      <c r="K69">
+        <v>3</v>
+      </c>
+      <c r="L69" t="s">
+        <v>67</v>
+      </c>
+      <c r="M69" t="s">
+        <v>68</v>
+      </c>
+      <c r="N69" t="s">
+        <v>71</v>
+      </c>
+      <c r="O69">
+        <v>18.08</v>
+      </c>
+      <c r="P69">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="70" spans="1:16">
+      <c r="A70" t="s">
+        <v>16</v>
+      </c>
+      <c r="B70" t="s">
+        <v>45</v>
+      </c>
+      <c r="C70" t="s">
+        <v>52</v>
+      </c>
+      <c r="D70">
+        <v>62.6</v>
+      </c>
+      <c r="E70" t="s">
+        <v>54</v>
+      </c>
+      <c r="F70" t="s">
+        <v>57</v>
+      </c>
+      <c r="G70" t="s">
+        <v>58</v>
+      </c>
+      <c r="H70">
+        <v>1190.45</v>
+      </c>
+      <c r="I70">
+        <v>7.399999999999999</v>
+      </c>
+      <c r="J70" t="s">
+        <v>61</v>
+      </c>
+      <c r="K70">
+        <v>3</v>
+      </c>
+      <c r="L70" t="s">
+        <v>67</v>
+      </c>
+      <c r="M70" t="s">
+        <v>68</v>
+      </c>
+      <c r="N70" t="s">
+        <v>71</v>
+      </c>
+      <c r="O70">
+        <v>18.08</v>
+      </c>
+      <c r="P70">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="71" spans="1:16">
+      <c r="A71" t="s">
+        <v>16</v>
+      </c>
+      <c r="B71" t="s">
+        <v>33</v>
+      </c>
+      <c r="C71" t="s">
+        <v>52</v>
+      </c>
+      <c r="D71">
+        <v>60.6</v>
+      </c>
+      <c r="E71" t="s">
+        <v>56</v>
+      </c>
+      <c r="F71" t="s">
+        <v>57</v>
+      </c>
+      <c r="G71" t="s">
+        <v>58</v>
+      </c>
+      <c r="H71">
+        <v>9700</v>
+      </c>
+      <c r="I71">
+        <v>9.399999999999999</v>
+      </c>
+      <c r="J71" t="s">
+        <v>59</v>
+      </c>
+      <c r="K71">
+        <v>9</v>
+      </c>
+      <c r="L71" t="s">
+        <v>66</v>
+      </c>
+      <c r="M71" t="s">
+        <v>68</v>
+      </c>
+      <c r="N71" t="s">
+        <v>71</v>
+      </c>
+      <c r="O71">
+        <v>18.08</v>
+      </c>
+      <c r="P71">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="72" spans="1:16">
+      <c r="A72" t="s">
+        <v>16</v>
+      </c>
+      <c r="B72" t="s">
+        <v>37</v>
+      </c>
+      <c r="C72" t="s">
+        <v>52</v>
+      </c>
+      <c r="D72">
+        <v>59.1</v>
+      </c>
+      <c r="E72" t="s">
+        <v>54</v>
+      </c>
+      <c r="F72" t="s">
+        <v>57</v>
+      </c>
+      <c r="G72" t="s">
+        <v>58</v>
+      </c>
+      <c r="H72">
+        <v>319.85</v>
+      </c>
+      <c r="I72">
+        <v>10.9</v>
+      </c>
+      <c r="J72" t="s">
+        <v>63</v>
+      </c>
+      <c r="K72">
+        <v>9</v>
+      </c>
+      <c r="L72" t="s">
+        <v>66</v>
+      </c>
+      <c r="M72" t="s">
+        <v>68</v>
+      </c>
+      <c r="N72" t="s">
+        <v>71</v>
+      </c>
+      <c r="O72">
+        <v>18.08</v>
+      </c>
+      <c r="P72">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="73" spans="1:16">
+      <c r="A73" t="s">
+        <v>16</v>
+      </c>
+      <c r="B73" t="s">
+        <v>46</v>
+      </c>
+      <c r="C73" t="s">
+        <v>52</v>
+      </c>
+      <c r="D73">
+        <v>58.8</v>
+      </c>
+      <c r="E73" t="s">
+        <v>54</v>
+      </c>
+      <c r="F73" t="s">
+        <v>57</v>
+      </c>
+      <c r="G73" t="s">
+        <v>58</v>
+      </c>
+      <c r="H73">
+        <v>2305.6</v>
+      </c>
+      <c r="I73">
+        <v>11.2</v>
+      </c>
+      <c r="J73" t="s">
+        <v>61</v>
+      </c>
+      <c r="K73">
+        <v>3</v>
+      </c>
+      <c r="L73" t="s">
+        <v>67</v>
+      </c>
+      <c r="M73" t="s">
+        <v>68</v>
+      </c>
+      <c r="N73" t="s">
+        <v>71</v>
+      </c>
+      <c r="O73">
+        <v>18.08</v>
+      </c>
+      <c r="P73">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="74" spans="1:16">
+      <c r="A74" t="s">
+        <v>16</v>
+      </c>
+      <c r="B74" t="s">
+        <v>47</v>
+      </c>
+      <c r="C74" t="s">
+        <v>52</v>
+      </c>
+      <c r="D74">
+        <v>58.8</v>
+      </c>
+      <c r="E74" t="s">
+        <v>54</v>
+      </c>
+      <c r="F74" t="s">
+        <v>57</v>
+      </c>
+      <c r="G74" t="s">
+        <v>58</v>
+      </c>
+      <c r="H74">
+        <v>3703.3</v>
+      </c>
+      <c r="I74">
+        <v>11.2</v>
+      </c>
+      <c r="J74" t="s">
+        <v>59</v>
+      </c>
+      <c r="K74">
+        <v>3</v>
+      </c>
+      <c r="L74" t="s">
+        <v>67</v>
+      </c>
+      <c r="M74" t="s">
+        <v>68</v>
+      </c>
+      <c r="N74" t="s">
+        <v>71</v>
+      </c>
+      <c r="O74">
+        <v>18.08</v>
+      </c>
+      <c r="P74">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="75" spans="1:16">
+      <c r="A75" t="s">
+        <v>16</v>
+      </c>
+      <c r="B75" t="s">
+        <v>48</v>
+      </c>
+      <c r="C75" t="s">
+        <v>52</v>
+      </c>
+      <c r="D75">
+        <v>57.2</v>
+      </c>
+      <c r="E75" t="s">
+        <v>54</v>
+      </c>
+      <c r="F75" t="s">
+        <v>57</v>
+      </c>
+      <c r="G75" t="s">
+        <v>58</v>
+      </c>
+      <c r="H75">
+        <v>4023.5</v>
+      </c>
+      <c r="I75">
+        <v>12.8</v>
+      </c>
+      <c r="J75" t="s">
+        <v>61</v>
+      </c>
+      <c r="K75">
+        <v>5</v>
+      </c>
+      <c r="L75" t="s">
+        <v>65</v>
+      </c>
+      <c r="M75" t="s">
+        <v>68</v>
+      </c>
+      <c r="N75" t="s">
+        <v>71</v>
+      </c>
+      <c r="O75">
+        <v>18.08</v>
+      </c>
+      <c r="P75">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16">
+      <c r="A76" t="s">
+        <v>16</v>
+      </c>
+      <c r="B76" t="s">
+        <v>50</v>
+      </c>
+      <c r="C76" t="s">
+        <v>52</v>
+      </c>
+      <c r="D76">
+        <v>56.8</v>
+      </c>
+      <c r="E76" t="s">
+        <v>53</v>
+      </c>
+      <c r="F76" t="s">
+        <v>57</v>
+      </c>
+      <c r="G76" t="s">
+        <v>58</v>
+      </c>
+      <c r="H76">
+        <v>7196</v>
+      </c>
+      <c r="I76">
+        <v>13.2</v>
+      </c>
+      <c r="J76" t="s">
+        <v>60</v>
+      </c>
+      <c r="K76">
+        <v>1</v>
+      </c>
+      <c r="L76" t="s">
+        <v>67</v>
+      </c>
+      <c r="M76" t="s">
+        <v>68</v>
+      </c>
+      <c r="N76" t="s">
+        <v>71</v>
+      </c>
+      <c r="O76">
+        <v>18.08</v>
+      </c>
+      <c r="P76">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="77" spans="1:16">
+      <c r="A77" t="s">
+        <v>16</v>
+      </c>
+      <c r="B77" t="s">
+        <v>49</v>
+      </c>
+      <c r="C77" t="s">
+        <v>52</v>
+      </c>
+      <c r="D77">
+        <v>55.9</v>
+      </c>
+      <c r="E77" t="s">
+        <v>54</v>
+      </c>
+      <c r="F77" t="s">
+        <v>57</v>
+      </c>
+      <c r="G77" t="s">
+        <v>58</v>
+      </c>
+      <c r="H77">
+        <v>125</v>
+      </c>
+      <c r="I77">
+        <v>14.1</v>
+      </c>
+      <c r="J77" t="s">
+        <v>60</v>
+      </c>
+      <c r="K77">
+        <v>3</v>
+      </c>
+      <c r="L77" t="s">
+        <v>67</v>
+      </c>
+      <c r="M77" t="s">
+        <v>68</v>
+      </c>
+      <c r="N77" t="s">
+        <v>71</v>
+      </c>
+      <c r="O77">
+        <v>18.08</v>
+      </c>
+      <c r="P77">
+        <v>144</v>
       </c>
     </row>
   </sheetData>

--- a/reports/watchlist_history.xlsx
+++ b/reports/watchlist_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="655" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="79">
   <si>
     <t>Date</t>
   </si>
@@ -169,6 +169,21 @@
     <t>EICHERMOT</t>
   </si>
   <si>
+    <t>GESHIP</t>
+  </si>
+  <si>
+    <t>HAPPYFORGE</t>
+  </si>
+  <si>
+    <t>ELGIEQUIP</t>
+  </si>
+  <si>
+    <t>HINDCOPPER</t>
+  </si>
+  <si>
+    <t>ESABINDIA</t>
+  </si>
+  <si>
     <t>BUY</t>
   </si>
   <si>
@@ -178,13 +193,13 @@
     <t>+0.0</t>
   </si>
   <si>
-    <t>+0.5</t>
-  </si>
-  <si>
-    <t>+6.5</t>
-  </si>
-  <si>
-    <t>-3.1</t>
+    <t>-2.4</t>
+  </si>
+  <si>
+    <t>+1.0</t>
+  </si>
+  <si>
+    <t>-6.0</t>
   </si>
   <si>
     <t>Stage 2 — Uptrend ✓</t>
@@ -193,6 +208,9 @@
     <t>No</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>VCP incomplete — price range still wide, wait for tighter base (3 contractions)</t>
   </si>
   <si>
@@ -230,6 +248,9 @@
   </si>
   <si>
     <t>-2.9%</t>
+  </si>
+  <si>
+    <t>-3.0%</t>
   </si>
 </sst>
 </file>
@@ -561,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P77"/>
+  <dimension ref="A1:P97"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -622,7 +643,7 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D2">
         <v>77.09999999999999</v>
@@ -631,10 +652,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H2">
         <v>11714</v>
@@ -646,13 +667,13 @@
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="M2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O2">
         <v>17.53</v>
@@ -669,7 +690,7 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D3">
         <v>74</v>
@@ -678,10 +699,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G3" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H3">
         <v>514.05</v>
@@ -693,13 +714,13 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="M3" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N3" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O3">
         <v>17.53</v>
@@ -716,7 +737,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D4">
         <v>72</v>
@@ -725,10 +746,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G4" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H4">
         <v>1621.5</v>
@@ -740,13 +761,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="M4" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N4" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O4">
         <v>17.53</v>
@@ -763,7 +784,7 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D5">
         <v>69.59999999999999</v>
@@ -772,10 +793,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G5" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H5">
         <v>191.38</v>
@@ -784,19 +805,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J5" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M5" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N5" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O5">
         <v>17.53</v>
@@ -813,7 +834,7 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D6">
         <v>69.09999999999999</v>
@@ -822,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G6" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H6">
         <v>1318.1</v>
@@ -834,19 +855,19 @@
         <v>0.9000000000000057</v>
       </c>
       <c r="J6" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M6" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N6" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O6">
         <v>17.53</v>
@@ -863,7 +884,7 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D7">
         <v>67.2</v>
@@ -872,10 +893,10 @@
         <v>-0.5</v>
       </c>
       <c r="F7" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G7" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H7">
         <v>1377.7</v>
@@ -884,19 +905,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J7" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K7">
         <v>6</v>
       </c>
       <c r="L7" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M7" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N7" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O7">
         <v>17.53</v>
@@ -913,7 +934,7 @@
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D8">
         <v>67.2</v>
@@ -922,10 +943,10 @@
         <v>-0.5</v>
       </c>
       <c r="F8" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G8" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H8">
         <v>4479.7</v>
@@ -934,19 +955,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J8" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K8">
         <v>6</v>
       </c>
       <c r="L8" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M8" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N8" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O8">
         <v>17.53</v>
@@ -963,7 +984,7 @@
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D9">
         <v>67.2</v>
@@ -972,10 +993,10 @@
         <v>-0.5</v>
       </c>
       <c r="F9" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G9" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H9">
         <v>1045.3</v>
@@ -984,19 +1005,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J9" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K9">
         <v>6</v>
       </c>
       <c r="L9" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M9" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N9" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O9">
         <v>17.53</v>
@@ -1013,7 +1034,7 @@
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D10">
         <v>67.2</v>
@@ -1022,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G10" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H10">
         <v>1055.65</v>
@@ -1034,19 +1055,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J10" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M10" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N10" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O10">
         <v>17.53</v>
@@ -1063,7 +1084,7 @@
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D11">
         <v>67.2</v>
@@ -1072,10 +1093,10 @@
         <v>-0.5</v>
       </c>
       <c r="F11" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G11" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H11">
         <v>1045.3</v>
@@ -1084,19 +1105,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J11" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K11">
         <v>6</v>
       </c>
       <c r="L11" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M11" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N11" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O11">
         <v>17.53</v>
@@ -1113,7 +1134,7 @@
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D12">
         <v>67.2</v>
@@ -1122,10 +1143,10 @@
         <v>-0.5</v>
       </c>
       <c r="F12" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G12" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H12">
         <v>4479.7</v>
@@ -1134,19 +1155,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J12" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K12">
         <v>6</v>
       </c>
       <c r="L12" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M12" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N12" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O12">
         <v>17.53</v>
@@ -1163,7 +1184,7 @@
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D13">
         <v>67.09999999999999</v>
@@ -1172,10 +1193,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G13" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H13">
         <v>581.3</v>
@@ -1184,19 +1205,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J13" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K13">
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M13" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N13" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O13">
         <v>17.53</v>
@@ -1213,7 +1234,7 @@
         <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D14">
         <v>67.09999999999999</v>
@@ -1222,10 +1243,10 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G14" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H14">
         <v>458.9</v>
@@ -1234,19 +1255,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J14" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M14" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N14" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O14">
         <v>17.53</v>
@@ -1263,7 +1284,7 @@
         <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D15">
         <v>65.59999999999999</v>
@@ -1272,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G15" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H15">
         <v>196.02</v>
@@ -1284,19 +1305,19 @@
         <v>4.400000000000006</v>
       </c>
       <c r="J15" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M15" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N15" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O15">
         <v>17.53</v>
@@ -1313,7 +1334,7 @@
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D16">
         <v>65</v>
@@ -1322,10 +1343,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G16" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H16">
         <v>4172.9</v>
@@ -1334,19 +1355,19 @@
         <v>5</v>
       </c>
       <c r="J16" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K16">
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M16" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N16" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O16">
         <v>17.53</v>
@@ -1363,7 +1384,7 @@
         <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D17">
         <v>64.7</v>
@@ -1372,10 +1393,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G17" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H17">
         <v>6373.5</v>
@@ -1384,19 +1405,19 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J17" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="K17">
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M17" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N17" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O17">
         <v>17.53</v>
@@ -1413,7 +1434,7 @@
         <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D18">
         <v>64.7</v>
@@ -1422,10 +1443,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G18" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H18">
         <v>1113.1</v>
@@ -1434,19 +1455,19 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J18" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M18" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N18" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O18">
         <v>17.53</v>
@@ -1463,7 +1484,7 @@
         <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D19">
         <v>64.59999999999999</v>
@@ -1472,10 +1493,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G19" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H19">
         <v>1379.9</v>
@@ -1484,19 +1505,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J19" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K19">
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M19" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N19" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O19">
         <v>17.53</v>
@@ -1513,7 +1534,7 @@
         <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D20">
         <v>64.2</v>
@@ -1522,10 +1543,10 @@
         <v>-0.5</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G20" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H20">
         <v>9793</v>
@@ -1534,19 +1555,19 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J20" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K20">
         <v>6</v>
       </c>
       <c r="L20" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M20" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N20" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O20">
         <v>17.53</v>
@@ -1563,7 +1584,7 @@
         <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D21">
         <v>64.2</v>
@@ -1572,10 +1593,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G21" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H21">
         <v>7955.5</v>
@@ -1584,19 +1605,19 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J21" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K21">
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M21" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N21" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O21">
         <v>17.53</v>
@@ -1613,7 +1634,7 @@
         <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D22">
         <v>63.6</v>
@@ -1622,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G22" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H22">
         <v>1037.85</v>
@@ -1634,19 +1655,19 @@
         <v>6.399999999999999</v>
       </c>
       <c r="J22" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K22">
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M22" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N22" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O22">
         <v>17.53</v>
@@ -1663,7 +1684,7 @@
         <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D23">
         <v>61.6</v>
@@ -1672,10 +1693,10 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G23" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H23">
         <v>979.1</v>
@@ -1684,19 +1705,19 @@
         <v>8.399999999999999</v>
       </c>
       <c r="J23" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K23">
         <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M23" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N23" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O23">
         <v>17.53</v>
@@ -1713,7 +1734,7 @@
         <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D24">
         <v>61.5</v>
@@ -1722,10 +1743,10 @@
         <v>-0.5</v>
       </c>
       <c r="F24" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G24" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H24">
         <v>319.35</v>
@@ -1734,19 +1755,19 @@
         <v>8.5</v>
       </c>
       <c r="J24" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="K24">
         <v>6</v>
       </c>
       <c r="L24" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M24" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N24" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="O24">
         <v>17.53</v>
@@ -1763,7 +1784,7 @@
         <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D25">
         <v>70</v>
@@ -1772,10 +1793,10 @@
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G25" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H25">
         <v>767.65</v>
@@ -1790,10 +1811,10 @@
         <v>16</v>
       </c>
       <c r="M25" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N25" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O25">
         <v>18.27</v>
@@ -1810,7 +1831,7 @@
         <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D26">
         <v>69</v>
@@ -1819,10 +1840,10 @@
         <v>7.8</v>
       </c>
       <c r="F26" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G26" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H26">
         <v>404.1</v>
@@ -1831,19 +1852,19 @@
         <v>1</v>
       </c>
       <c r="J26" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K26">
         <v>7</v>
       </c>
       <c r="L26" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M26" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N26" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O26">
         <v>18.27</v>
@@ -1860,7 +1881,7 @@
         <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D27">
         <v>69</v>
@@ -1869,10 +1890,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G27" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H27">
         <v>3847</v>
@@ -1881,19 +1902,19 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K27">
         <v>1</v>
       </c>
       <c r="L27" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M27" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N27" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O27">
         <v>18.27</v>
@@ -1910,7 +1931,7 @@
         <v>41</v>
       </c>
       <c r="C28" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D28">
         <v>67.5</v>
@@ -1919,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G28" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H28">
         <v>211.75</v>
@@ -1931,19 +1952,19 @@
         <v>2.5</v>
       </c>
       <c r="J28" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K28">
         <v>1</v>
       </c>
       <c r="L28" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M28" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N28" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O28">
         <v>18.27</v>
@@ -1960,7 +1981,7 @@
         <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D29">
         <v>66.7</v>
@@ -1969,10 +1990,10 @@
         <v>-0.5</v>
       </c>
       <c r="F29" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G29" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H29">
         <v>1381.5</v>
@@ -1981,19 +2002,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J29" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K29">
         <v>7</v>
       </c>
       <c r="L29" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M29" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N29" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O29">
         <v>18.27</v>
@@ -2010,7 +2031,7 @@
         <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D30">
         <v>66.7</v>
@@ -2019,10 +2040,10 @@
         <v>-0.5</v>
       </c>
       <c r="F30" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G30" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H30">
         <v>4483</v>
@@ -2031,19 +2052,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J30" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K30">
         <v>7</v>
       </c>
       <c r="L30" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M30" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N30" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O30">
         <v>18.27</v>
@@ -2060,7 +2081,7 @@
         <v>42</v>
       </c>
       <c r="C31" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D31">
         <v>66.7</v>
@@ -2069,10 +2090,10 @@
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G31" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H31">
         <v>89.05</v>
@@ -2081,19 +2102,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J31" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K31">
         <v>1</v>
       </c>
       <c r="L31" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M31" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N31" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O31">
         <v>18.27</v>
@@ -2110,7 +2131,7 @@
         <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D32">
         <v>66.59999999999999</v>
@@ -2119,10 +2140,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G32" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H32">
         <v>1291.1</v>
@@ -2131,19 +2152,19 @@
         <v>3.400000000000006</v>
       </c>
       <c r="J32" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K32">
         <v>1</v>
       </c>
       <c r="L32" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M32" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N32" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O32">
         <v>18.27</v>
@@ -2160,7 +2181,7 @@
         <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D33">
         <v>64.09999999999999</v>
@@ -2169,10 +2190,10 @@
         <v>-0.5</v>
       </c>
       <c r="F33" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G33" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H33">
         <v>1414.6</v>
@@ -2181,19 +2202,19 @@
         <v>5.900000000000006</v>
       </c>
       <c r="J33" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K33">
         <v>2</v>
       </c>
       <c r="L33" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M33" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N33" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O33">
         <v>18.27</v>
@@ -2210,7 +2231,7 @@
         <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D34">
         <v>63.7</v>
@@ -2219,10 +2240,10 @@
         <v>-0.5</v>
       </c>
       <c r="F34" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G34" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H34">
         <v>9760</v>
@@ -2231,19 +2252,19 @@
         <v>6.299999999999997</v>
       </c>
       <c r="J34" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K34">
         <v>7</v>
       </c>
       <c r="L34" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M34" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N34" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O34">
         <v>18.27</v>
@@ -2260,7 +2281,7 @@
         <v>44</v>
       </c>
       <c r="C35" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D35">
         <v>62.7</v>
@@ -2269,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G35" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H35">
         <v>125.85</v>
@@ -2281,19 +2302,19 @@
         <v>7.299999999999997</v>
       </c>
       <c r="J35" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K35">
         <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M35" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N35" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O35">
         <v>18.27</v>
@@ -2310,7 +2331,7 @@
         <v>45</v>
       </c>
       <c r="C36" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D36">
         <v>62.1</v>
@@ -2319,10 +2340,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G36" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H36">
         <v>1171.95</v>
@@ -2331,19 +2352,19 @@
         <v>7.899999999999999</v>
       </c>
       <c r="J36" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K36">
         <v>1</v>
       </c>
       <c r="L36" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M36" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N36" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O36">
         <v>18.27</v>
@@ -2360,7 +2381,7 @@
         <v>24</v>
       </c>
       <c r="C37" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D37">
         <v>60.7</v>
@@ -2369,10 +2390,10 @@
         <v>-6.5</v>
       </c>
       <c r="F37" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G37" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H37">
         <v>1038.1</v>
@@ -2381,19 +2402,19 @@
         <v>9.299999999999997</v>
       </c>
       <c r="J37" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K37">
         <v>7</v>
       </c>
       <c r="L37" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M37" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N37" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O37">
         <v>18.27</v>
@@ -2410,7 +2431,7 @@
         <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D38">
         <v>58.6</v>
@@ -2419,10 +2440,10 @@
         <v>-2.9</v>
       </c>
       <c r="F38" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G38" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H38">
         <v>319.6</v>
@@ -2431,19 +2452,19 @@
         <v>11.4</v>
       </c>
       <c r="J38" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="K38">
         <v>7</v>
       </c>
       <c r="L38" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M38" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N38" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O38">
         <v>18.27</v>
@@ -2460,7 +2481,7 @@
         <v>46</v>
       </c>
       <c r="C39" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D39">
         <v>58.3</v>
@@ -2469,10 +2490,10 @@
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G39" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H39">
         <v>2314.1</v>
@@ -2481,19 +2502,19 @@
         <v>11.7</v>
       </c>
       <c r="J39" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K39">
         <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M39" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N39" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O39">
         <v>18.27</v>
@@ -2510,7 +2531,7 @@
         <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D40">
         <v>58.3</v>
@@ -2519,10 +2540,10 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G40" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H40">
         <v>3723.6</v>
@@ -2531,19 +2552,19 @@
         <v>11.7</v>
       </c>
       <c r="J40" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K40">
         <v>1</v>
       </c>
       <c r="L40" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M40" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N40" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O40">
         <v>18.27</v>
@@ -2560,7 +2581,7 @@
         <v>48</v>
       </c>
       <c r="C41" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D41">
         <v>56.7</v>
@@ -2569,10 +2590,10 @@
         <v>-0.5</v>
       </c>
       <c r="F41" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G41" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H41">
         <v>4049.2</v>
@@ -2581,19 +2602,19 @@
         <v>13.3</v>
       </c>
       <c r="J41" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K41">
         <v>3</v>
       </c>
       <c r="L41" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M41" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N41" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O41">
         <v>18.27</v>
@@ -2610,7 +2631,7 @@
         <v>49</v>
       </c>
       <c r="C42" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D42">
         <v>55.4</v>
@@ -2619,10 +2640,10 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G42" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H42">
         <v>124.98</v>
@@ -2631,19 +2652,19 @@
         <v>14.6</v>
       </c>
       <c r="J42" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K42">
         <v>1</v>
       </c>
       <c r="L42" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M42" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N42" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O42">
         <v>18.27</v>
@@ -2660,7 +2681,7 @@
         <v>22</v>
       </c>
       <c r="C43" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D43">
         <v>69.09999999999999</v>
@@ -2669,10 +2690,10 @@
         <v>2.4</v>
       </c>
       <c r="F43" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G43" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H43">
         <v>1388.7</v>
@@ -2681,19 +2702,19 @@
         <v>0.9000000000000057</v>
       </c>
       <c r="J43" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K43">
         <v>8</v>
       </c>
       <c r="L43" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M43" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N43" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O43">
         <v>18.23</v>
@@ -2710,7 +2731,7 @@
         <v>39</v>
       </c>
       <c r="C44" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D44">
         <v>69</v>
@@ -2719,10 +2740,10 @@
         <v>0</v>
       </c>
       <c r="F44" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G44" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H44">
         <v>404.8</v>
@@ -2731,19 +2752,19 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K44">
         <v>8</v>
       </c>
       <c r="L44" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M44" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N44" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O44">
         <v>18.23</v>
@@ -2760,7 +2781,7 @@
         <v>40</v>
       </c>
       <c r="C45" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D45">
         <v>69</v>
@@ -2769,10 +2790,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G45" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H45">
         <v>3845.7</v>
@@ -2781,19 +2802,19 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K45">
         <v>2</v>
       </c>
       <c r="L45" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M45" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N45" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O45">
         <v>18.23</v>
@@ -2810,7 +2831,7 @@
         <v>41</v>
       </c>
       <c r="C46" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D46">
         <v>68.5</v>
@@ -2819,10 +2840,10 @@
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G46" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H46">
         <v>213.03</v>
@@ -2831,19 +2852,19 @@
         <v>1.5</v>
       </c>
       <c r="J46" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K46">
         <v>2</v>
       </c>
       <c r="L46" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M46" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N46" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O46">
         <v>18.23</v>
@@ -2860,7 +2881,7 @@
         <v>23</v>
       </c>
       <c r="C47" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D47">
         <v>66.7</v>
@@ -2869,10 +2890,10 @@
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G47" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H47">
         <v>4477</v>
@@ -2881,19 +2902,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J47" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K47">
         <v>8</v>
       </c>
       <c r="L47" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M47" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N47" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O47">
         <v>18.23</v>
@@ -2910,7 +2931,7 @@
         <v>42</v>
       </c>
       <c r="C48" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D48">
         <v>66.7</v>
@@ -2919,10 +2940,10 @@
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G48" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H48">
         <v>88.98999999999999</v>
@@ -2931,19 +2952,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J48" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K48">
         <v>2</v>
       </c>
       <c r="L48" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M48" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N48" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O48">
         <v>18.23</v>
@@ -2960,7 +2981,7 @@
         <v>43</v>
       </c>
       <c r="C49" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D49">
         <v>66.59999999999999</v>
@@ -2969,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G49" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H49">
         <v>1288.9</v>
@@ -2981,19 +3002,19 @@
         <v>3.400000000000006</v>
       </c>
       <c r="J49" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K49">
         <v>2</v>
       </c>
       <c r="L49" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M49" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N49" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O49">
         <v>18.23</v>
@@ -3010,7 +3031,7 @@
         <v>32</v>
       </c>
       <c r="C50" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D50">
         <v>64.09999999999999</v>
@@ -3019,10 +3040,10 @@
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G50" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H50">
         <v>1419</v>
@@ -3031,19 +3052,19 @@
         <v>5.900000000000006</v>
       </c>
       <c r="J50" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K50">
         <v>3</v>
       </c>
       <c r="L50" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M50" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N50" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O50">
         <v>18.23</v>
@@ -3060,7 +3081,7 @@
         <v>33</v>
       </c>
       <c r="C51" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D51">
         <v>63.7</v>
@@ -3069,10 +3090,10 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G51" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H51">
         <v>9758</v>
@@ -3081,19 +3102,19 @@
         <v>6.299999999999997</v>
       </c>
       <c r="J51" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K51">
         <v>8</v>
       </c>
       <c r="L51" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M51" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N51" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O51">
         <v>18.23</v>
@@ -3110,7 +3131,7 @@
         <v>44</v>
       </c>
       <c r="C52" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D52">
         <v>62.7</v>
@@ -3119,10 +3140,10 @@
         <v>0</v>
       </c>
       <c r="F52" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G52" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H52">
         <v>125.98</v>
@@ -3131,19 +3152,19 @@
         <v>7.299999999999997</v>
       </c>
       <c r="J52" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K52">
         <v>2</v>
       </c>
       <c r="L52" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M52" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N52" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O52">
         <v>18.23</v>
@@ -3160,7 +3181,7 @@
         <v>45</v>
       </c>
       <c r="C53" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D53">
         <v>62.1</v>
@@ -3169,10 +3190,10 @@
         <v>0</v>
       </c>
       <c r="F53" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G53" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H53">
         <v>1182</v>
@@ -3181,19 +3202,19 @@
         <v>7.899999999999999</v>
       </c>
       <c r="J53" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K53">
         <v>2</v>
       </c>
       <c r="L53" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M53" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N53" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O53">
         <v>18.23</v>
@@ -3210,7 +3231,7 @@
         <v>24</v>
       </c>
       <c r="C54" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D54">
         <v>60.7</v>
@@ -3219,10 +3240,10 @@
         <v>0</v>
       </c>
       <c r="F54" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G54" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H54">
         <v>1040</v>
@@ -3231,19 +3252,19 @@
         <v>9.299999999999997</v>
       </c>
       <c r="J54" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K54">
         <v>8</v>
       </c>
       <c r="L54" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M54" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N54" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O54">
         <v>18.23</v>
@@ -3260,7 +3281,7 @@
         <v>37</v>
       </c>
       <c r="C55" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D55">
         <v>58.6</v>
@@ -3269,10 +3290,10 @@
         <v>0</v>
       </c>
       <c r="F55" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G55" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H55">
         <v>320.2</v>
@@ -3281,19 +3302,19 @@
         <v>11.4</v>
       </c>
       <c r="J55" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="K55">
         <v>8</v>
       </c>
       <c r="L55" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M55" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N55" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O55">
         <v>18.23</v>
@@ -3310,7 +3331,7 @@
         <v>46</v>
       </c>
       <c r="C56" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D56">
         <v>58.3</v>
@@ -3319,10 +3340,10 @@
         <v>0</v>
       </c>
       <c r="F56" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G56" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H56">
         <v>2314.8</v>
@@ -3331,19 +3352,19 @@
         <v>11.7</v>
       </c>
       <c r="J56" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K56">
         <v>2</v>
       </c>
       <c r="L56" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M56" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N56" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O56">
         <v>18.23</v>
@@ -3360,7 +3381,7 @@
         <v>47</v>
       </c>
       <c r="C57" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D57">
         <v>58.3</v>
@@ -3369,10 +3390,10 @@
         <v>0</v>
       </c>
       <c r="F57" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G57" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H57">
         <v>3716.5</v>
@@ -3381,19 +3402,19 @@
         <v>11.7</v>
       </c>
       <c r="J57" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K57">
         <v>2</v>
       </c>
       <c r="L57" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M57" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N57" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O57">
         <v>18.23</v>
@@ -3410,7 +3431,7 @@
         <v>48</v>
       </c>
       <c r="C58" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D58">
         <v>56.7</v>
@@ -3419,10 +3440,10 @@
         <v>0</v>
       </c>
       <c r="F58" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G58" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H58">
         <v>4043</v>
@@ -3431,19 +3452,19 @@
         <v>13.3</v>
       </c>
       <c r="J58" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K58">
         <v>4</v>
       </c>
       <c r="L58" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M58" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N58" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O58">
         <v>18.23</v>
@@ -3460,7 +3481,7 @@
         <v>49</v>
       </c>
       <c r="C59" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D59">
         <v>55.4</v>
@@ -3469,10 +3490,10 @@
         <v>0</v>
       </c>
       <c r="F59" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G59" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H59">
         <v>125.04</v>
@@ -3481,19 +3502,19 @@
         <v>14.6</v>
       </c>
       <c r="J59" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K59">
         <v>2</v>
       </c>
       <c r="L59" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M59" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N59" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="O59">
         <v>18.23</v>
@@ -3503,26 +3524,26 @@
       </c>
     </row>
     <row r="60" spans="1:16">
-      <c r="A60" t="s">
-        <v>16</v>
+      <c r="A60">
+        <v>20260422</v>
       </c>
       <c r="B60" t="s">
         <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D60">
         <v>71.5</v>
       </c>
-      <c r="E60" t="s">
-        <v>53</v>
+      <c r="E60">
+        <v>0</v>
       </c>
       <c r="F60" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G60" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H60">
         <v>3852.5</v>
@@ -3537,10 +3558,10 @@
         <v>16</v>
       </c>
       <c r="M60" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N60" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O60">
         <v>18.08</v>
@@ -3550,26 +3571,26 @@
       </c>
     </row>
     <row r="61" spans="1:16">
-      <c r="A61" t="s">
-        <v>16</v>
+      <c r="A61">
+        <v>20260422</v>
       </c>
       <c r="B61" t="s">
         <v>22</v>
       </c>
       <c r="C61" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D61">
         <v>69.59999999999999</v>
       </c>
-      <c r="E61" t="s">
-        <v>54</v>
+      <c r="E61">
+        <v>0.5</v>
       </c>
       <c r="F61" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G61" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H61">
         <v>1388.5</v>
@@ -3578,19 +3599,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J61" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K61">
         <v>9</v>
       </c>
       <c r="L61" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M61" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N61" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O61">
         <v>18.08</v>
@@ -3600,26 +3621,26 @@
       </c>
     </row>
     <row r="62" spans="1:16">
-      <c r="A62" t="s">
-        <v>16</v>
+      <c r="A62">
+        <v>20260422</v>
       </c>
       <c r="B62" t="s">
         <v>39</v>
       </c>
       <c r="C62" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D62">
         <v>69.5</v>
       </c>
-      <c r="E62" t="s">
-        <v>54</v>
+      <c r="E62">
+        <v>0.5</v>
       </c>
       <c r="F62" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G62" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H62">
         <v>406.1</v>
@@ -3628,19 +3649,19 @@
         <v>0.5</v>
       </c>
       <c r="J62" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K62">
         <v>9</v>
       </c>
       <c r="L62" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M62" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N62" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O62">
         <v>18.08</v>
@@ -3650,26 +3671,26 @@
       </c>
     </row>
     <row r="63" spans="1:16">
-      <c r="A63" t="s">
-        <v>16</v>
+      <c r="A63">
+        <v>20260422</v>
       </c>
       <c r="B63" t="s">
         <v>41</v>
       </c>
       <c r="C63" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D63">
         <v>69</v>
       </c>
-      <c r="E63" t="s">
-        <v>54</v>
+      <c r="E63">
+        <v>0.5</v>
       </c>
       <c r="F63" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G63" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H63">
         <v>213.6</v>
@@ -3678,19 +3699,19 @@
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K63">
         <v>3</v>
       </c>
       <c r="L63" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M63" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N63" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O63">
         <v>18.08</v>
@@ -3700,26 +3721,26 @@
       </c>
     </row>
     <row r="64" spans="1:16">
-      <c r="A64" t="s">
-        <v>16</v>
+      <c r="A64">
+        <v>20260422</v>
       </c>
       <c r="B64" t="s">
         <v>23</v>
       </c>
       <c r="C64" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D64">
         <v>67.2</v>
       </c>
-      <c r="E64" t="s">
-        <v>54</v>
+      <c r="E64">
+        <v>0.5</v>
       </c>
       <c r="F64" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G64" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H64">
         <v>4478</v>
@@ -3728,19 +3749,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J64" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K64">
         <v>9</v>
       </c>
       <c r="L64" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M64" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N64" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O64">
         <v>18.08</v>
@@ -3750,26 +3771,26 @@
       </c>
     </row>
     <row r="65" spans="1:16">
-      <c r="A65" t="s">
-        <v>16</v>
+      <c r="A65">
+        <v>20260422</v>
       </c>
       <c r="B65" t="s">
         <v>24</v>
       </c>
       <c r="C65" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D65">
         <v>67.2</v>
       </c>
-      <c r="E65" t="s">
-        <v>55</v>
+      <c r="E65">
+        <v>6.5</v>
       </c>
       <c r="F65" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G65" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H65">
         <v>1050.05</v>
@@ -3778,19 +3799,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J65" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K65">
         <v>9</v>
       </c>
       <c r="L65" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M65" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N65" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O65">
         <v>18.08</v>
@@ -3800,26 +3821,26 @@
       </c>
     </row>
     <row r="66" spans="1:16">
-      <c r="A66" t="s">
-        <v>16</v>
+      <c r="A66">
+        <v>20260422</v>
       </c>
       <c r="B66" t="s">
         <v>42</v>
       </c>
       <c r="C66" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D66">
         <v>67.2</v>
       </c>
-      <c r="E66" t="s">
-        <v>54</v>
+      <c r="E66">
+        <v>0.5</v>
       </c>
       <c r="F66" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G66" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H66">
         <v>88.59</v>
@@ -3828,19 +3849,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J66" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K66">
         <v>3</v>
       </c>
       <c r="L66" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M66" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N66" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O66">
         <v>18.08</v>
@@ -3850,26 +3871,26 @@
       </c>
     </row>
     <row r="67" spans="1:16">
-      <c r="A67" t="s">
-        <v>16</v>
+      <c r="A67">
+        <v>20260422</v>
       </c>
       <c r="B67" t="s">
         <v>43</v>
       </c>
       <c r="C67" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D67">
         <v>67.09999999999999</v>
       </c>
-      <c r="E67" t="s">
-        <v>54</v>
+      <c r="E67">
+        <v>0.5</v>
       </c>
       <c r="F67" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G67" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H67">
         <v>1291.7</v>
@@ -3878,19 +3899,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J67" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K67">
         <v>3</v>
       </c>
       <c r="L67" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M67" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N67" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O67">
         <v>18.08</v>
@@ -3900,26 +3921,26 @@
       </c>
     </row>
     <row r="68" spans="1:16">
-      <c r="A68" t="s">
-        <v>16</v>
+      <c r="A68">
+        <v>20260422</v>
       </c>
       <c r="B68" t="s">
         <v>32</v>
       </c>
       <c r="C68" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D68">
         <v>64.59999999999999</v>
       </c>
-      <c r="E68" t="s">
-        <v>54</v>
+      <c r="E68">
+        <v>0.5</v>
       </c>
       <c r="F68" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G68" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H68">
         <v>1405.3</v>
@@ -3928,19 +3949,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J68" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K68">
         <v>4</v>
       </c>
       <c r="L68" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M68" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N68" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O68">
         <v>18.08</v>
@@ -3950,26 +3971,26 @@
       </c>
     </row>
     <row r="69" spans="1:16">
-      <c r="A69" t="s">
-        <v>16</v>
+      <c r="A69">
+        <v>20260422</v>
       </c>
       <c r="B69" t="s">
         <v>44</v>
       </c>
       <c r="C69" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D69">
         <v>63.2</v>
       </c>
-      <c r="E69" t="s">
-        <v>54</v>
+      <c r="E69">
+        <v>0.5</v>
       </c>
       <c r="F69" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G69" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H69">
         <v>125.89</v>
@@ -3978,19 +3999,19 @@
         <v>6.799999999999997</v>
       </c>
       <c r="J69" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K69">
         <v>3</v>
       </c>
       <c r="L69" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M69" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N69" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O69">
         <v>18.08</v>
@@ -4000,26 +4021,26 @@
       </c>
     </row>
     <row r="70" spans="1:16">
-      <c r="A70" t="s">
-        <v>16</v>
+      <c r="A70">
+        <v>20260422</v>
       </c>
       <c r="B70" t="s">
         <v>45</v>
       </c>
       <c r="C70" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D70">
         <v>62.6</v>
       </c>
-      <c r="E70" t="s">
-        <v>54</v>
+      <c r="E70">
+        <v>0.5</v>
       </c>
       <c r="F70" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G70" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H70">
         <v>1190.45</v>
@@ -4028,19 +4049,19 @@
         <v>7.399999999999999</v>
       </c>
       <c r="J70" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K70">
         <v>3</v>
       </c>
       <c r="L70" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M70" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N70" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O70">
         <v>18.08</v>
@@ -4050,26 +4071,26 @@
       </c>
     </row>
     <row r="71" spans="1:16">
-      <c r="A71" t="s">
-        <v>16</v>
+      <c r="A71">
+        <v>20260422</v>
       </c>
       <c r="B71" t="s">
         <v>33</v>
       </c>
       <c r="C71" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D71">
         <v>60.6</v>
       </c>
-      <c r="E71" t="s">
-        <v>56</v>
+      <c r="E71">
+        <v>-3.1</v>
       </c>
       <c r="F71" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G71" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H71">
         <v>9700</v>
@@ -4078,19 +4099,19 @@
         <v>9.399999999999999</v>
       </c>
       <c r="J71" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K71">
         <v>9</v>
       </c>
       <c r="L71" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M71" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N71" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O71">
         <v>18.08</v>
@@ -4100,26 +4121,26 @@
       </c>
     </row>
     <row r="72" spans="1:16">
-      <c r="A72" t="s">
-        <v>16</v>
+      <c r="A72">
+        <v>20260422</v>
       </c>
       <c r="B72" t="s">
         <v>37</v>
       </c>
       <c r="C72" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D72">
         <v>59.1</v>
       </c>
-      <c r="E72" t="s">
-        <v>54</v>
+      <c r="E72">
+        <v>0.5</v>
       </c>
       <c r="F72" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G72" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H72">
         <v>319.85</v>
@@ -4128,19 +4149,19 @@
         <v>10.9</v>
       </c>
       <c r="J72" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="K72">
         <v>9</v>
       </c>
       <c r="L72" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="M72" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N72" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O72">
         <v>18.08</v>
@@ -4150,26 +4171,26 @@
       </c>
     </row>
     <row r="73" spans="1:16">
-      <c r="A73" t="s">
-        <v>16</v>
+      <c r="A73">
+        <v>20260422</v>
       </c>
       <c r="B73" t="s">
         <v>46</v>
       </c>
       <c r="C73" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D73">
         <v>58.8</v>
       </c>
-      <c r="E73" t="s">
-        <v>54</v>
+      <c r="E73">
+        <v>0.5</v>
       </c>
       <c r="F73" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G73" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H73">
         <v>2305.6</v>
@@ -4178,19 +4199,19 @@
         <v>11.2</v>
       </c>
       <c r="J73" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K73">
         <v>3</v>
       </c>
       <c r="L73" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M73" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N73" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O73">
         <v>18.08</v>
@@ -4200,26 +4221,26 @@
       </c>
     </row>
     <row r="74" spans="1:16">
-      <c r="A74" t="s">
-        <v>16</v>
+      <c r="A74">
+        <v>20260422</v>
       </c>
       <c r="B74" t="s">
         <v>47</v>
       </c>
       <c r="C74" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D74">
         <v>58.8</v>
       </c>
-      <c r="E74" t="s">
-        <v>54</v>
+      <c r="E74">
+        <v>0.5</v>
       </c>
       <c r="F74" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G74" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H74">
         <v>3703.3</v>
@@ -4228,19 +4249,19 @@
         <v>11.2</v>
       </c>
       <c r="J74" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K74">
         <v>3</v>
       </c>
       <c r="L74" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M74" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N74" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O74">
         <v>18.08</v>
@@ -4250,26 +4271,26 @@
       </c>
     </row>
     <row r="75" spans="1:16">
-      <c r="A75" t="s">
-        <v>16</v>
+      <c r="A75">
+        <v>20260422</v>
       </c>
       <c r="B75" t="s">
         <v>48</v>
       </c>
       <c r="C75" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D75">
         <v>57.2</v>
       </c>
-      <c r="E75" t="s">
-        <v>54</v>
+      <c r="E75">
+        <v>0.5</v>
       </c>
       <c r="F75" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G75" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H75">
         <v>4023.5</v>
@@ -4278,19 +4299,19 @@
         <v>12.8</v>
       </c>
       <c r="J75" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K75">
         <v>5</v>
       </c>
       <c r="L75" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="M75" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N75" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O75">
         <v>18.08</v>
@@ -4300,26 +4321,26 @@
       </c>
     </row>
     <row r="76" spans="1:16">
-      <c r="A76" t="s">
-        <v>16</v>
+      <c r="A76">
+        <v>20260422</v>
       </c>
       <c r="B76" t="s">
         <v>50</v>
       </c>
       <c r="C76" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D76">
         <v>56.8</v>
       </c>
-      <c r="E76" t="s">
-        <v>53</v>
+      <c r="E76">
+        <v>0</v>
       </c>
       <c r="F76" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G76" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H76">
         <v>7196</v>
@@ -4328,19 +4349,19 @@
         <v>13.2</v>
       </c>
       <c r="J76" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K76">
         <v>1</v>
       </c>
       <c r="L76" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M76" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N76" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O76">
         <v>18.08</v>
@@ -4350,26 +4371,26 @@
       </c>
     </row>
     <row r="77" spans="1:16">
-      <c r="A77" t="s">
-        <v>16</v>
+      <c r="A77">
+        <v>20260422</v>
       </c>
       <c r="B77" t="s">
         <v>49</v>
       </c>
       <c r="C77" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D77">
         <v>55.9</v>
       </c>
-      <c r="E77" t="s">
-        <v>54</v>
+      <c r="E77">
+        <v>0.5</v>
       </c>
       <c r="F77" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="G77" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="H77">
         <v>125</v>
@@ -4378,25 +4399,1013 @@
         <v>14.1</v>
       </c>
       <c r="J77" t="s">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="K77">
         <v>3</v>
       </c>
       <c r="L77" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="M77" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="N77" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="O77">
         <v>18.08</v>
       </c>
       <c r="P77">
         <v>144</v>
+      </c>
+    </row>
+    <row r="78" spans="1:16">
+      <c r="A78" t="s">
+        <v>16</v>
+      </c>
+      <c r="B78" t="s">
+        <v>51</v>
+      </c>
+      <c r="C78" t="s">
+        <v>56</v>
+      </c>
+      <c r="D78">
+        <v>73.7</v>
+      </c>
+      <c r="E78" t="s">
+        <v>58</v>
+      </c>
+      <c r="F78" t="s">
+        <v>62</v>
+      </c>
+      <c r="G78" t="s">
+        <v>64</v>
+      </c>
+      <c r="H78">
+        <v>1449.1</v>
+      </c>
+      <c r="I78">
+        <v>0</v>
+      </c>
+      <c r="K78">
+        <v>1</v>
+      </c>
+      <c r="L78" t="s">
+        <v>16</v>
+      </c>
+      <c r="M78" t="s">
+        <v>74</v>
+      </c>
+      <c r="N78" t="s">
+        <v>78</v>
+      </c>
+      <c r="O78">
+        <v>18.3</v>
+      </c>
+      <c r="P78">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="79" spans="1:16">
+      <c r="A79" t="s">
+        <v>16</v>
+      </c>
+      <c r="B79" t="s">
+        <v>40</v>
+      </c>
+      <c r="C79" t="s">
+        <v>56</v>
+      </c>
+      <c r="D79">
+        <v>71.5</v>
+      </c>
+      <c r="E79" t="s">
+        <v>58</v>
+      </c>
+      <c r="F79" t="s">
+        <v>62</v>
+      </c>
+      <c r="G79" t="s">
+        <v>63</v>
+      </c>
+      <c r="H79">
+        <v>3844.3</v>
+      </c>
+      <c r="I79">
+        <v>0</v>
+      </c>
+      <c r="K79">
+        <v>1</v>
+      </c>
+      <c r="L79" t="s">
+        <v>16</v>
+      </c>
+      <c r="M79" t="s">
+        <v>74</v>
+      </c>
+      <c r="N79" t="s">
+        <v>78</v>
+      </c>
+      <c r="O79">
+        <v>18.3</v>
+      </c>
+      <c r="P79">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="80" spans="1:16">
+      <c r="A80" t="s">
+        <v>16</v>
+      </c>
+      <c r="B80" t="s">
+        <v>52</v>
+      </c>
+      <c r="C80" t="s">
+        <v>56</v>
+      </c>
+      <c r="D80">
+        <v>71.09999999999999</v>
+      </c>
+      <c r="E80" t="s">
+        <v>58</v>
+      </c>
+      <c r="F80" t="s">
+        <v>62</v>
+      </c>
+      <c r="G80" t="s">
+        <v>63</v>
+      </c>
+      <c r="H80">
+        <v>1330.5</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="K80">
+        <v>1</v>
+      </c>
+      <c r="L80" t="s">
+        <v>16</v>
+      </c>
+      <c r="M80" t="s">
+        <v>74</v>
+      </c>
+      <c r="N80" t="s">
+        <v>78</v>
+      </c>
+      <c r="O80">
+        <v>18.3</v>
+      </c>
+      <c r="P80">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="81" spans="1:16">
+      <c r="A81" t="s">
+        <v>16</v>
+      </c>
+      <c r="B81" t="s">
+        <v>39</v>
+      </c>
+      <c r="C81" t="s">
+        <v>56</v>
+      </c>
+      <c r="D81">
+        <v>70.5</v>
+      </c>
+      <c r="E81" t="s">
+        <v>58</v>
+      </c>
+      <c r="F81" t="s">
+        <v>62</v>
+      </c>
+      <c r="G81" t="s">
+        <v>63</v>
+      </c>
+      <c r="H81">
+        <v>405.4</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="K81">
+        <v>1</v>
+      </c>
+      <c r="L81" t="s">
+        <v>16</v>
+      </c>
+      <c r="M81" t="s">
+        <v>74</v>
+      </c>
+      <c r="N81" t="s">
+        <v>78</v>
+      </c>
+      <c r="O81">
+        <v>18.3</v>
+      </c>
+      <c r="P81">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="82" spans="1:16">
+      <c r="A82" t="s">
+        <v>16</v>
+      </c>
+      <c r="B82" t="s">
+        <v>53</v>
+      </c>
+      <c r="C82" t="s">
+        <v>57</v>
+      </c>
+      <c r="D82">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="E82" t="s">
+        <v>58</v>
+      </c>
+      <c r="F82" t="s">
+        <v>62</v>
+      </c>
+      <c r="G82" t="s">
+        <v>63</v>
+      </c>
+      <c r="H82">
+        <v>554.7</v>
+      </c>
+      <c r="I82">
+        <v>0.4000000000000057</v>
+      </c>
+      <c r="J82" t="s">
+        <v>66</v>
+      </c>
+      <c r="K82">
+        <v>1</v>
+      </c>
+      <c r="L82" t="s">
+        <v>73</v>
+      </c>
+      <c r="M82" t="s">
+        <v>74</v>
+      </c>
+      <c r="N82" t="s">
+        <v>78</v>
+      </c>
+      <c r="O82">
+        <v>18.3</v>
+      </c>
+      <c r="P82">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="83" spans="1:16">
+      <c r="A83" t="s">
+        <v>16</v>
+      </c>
+      <c r="B83" t="s">
+        <v>41</v>
+      </c>
+      <c r="C83" t="s">
+        <v>57</v>
+      </c>
+      <c r="D83">
+        <v>69</v>
+      </c>
+      <c r="E83" t="s">
+        <v>58</v>
+      </c>
+      <c r="F83" t="s">
+        <v>62</v>
+      </c>
+      <c r="G83" t="s">
+        <v>63</v>
+      </c>
+      <c r="H83">
+        <v>215.65</v>
+      </c>
+      <c r="I83">
+        <v>1</v>
+      </c>
+      <c r="J83" t="s">
+        <v>67</v>
+      </c>
+      <c r="K83">
+        <v>4</v>
+      </c>
+      <c r="L83" t="s">
+        <v>73</v>
+      </c>
+      <c r="M83" t="s">
+        <v>74</v>
+      </c>
+      <c r="N83" t="s">
+        <v>78</v>
+      </c>
+      <c r="O83">
+        <v>18.3</v>
+      </c>
+      <c r="P83">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="84" spans="1:16">
+      <c r="A84" t="s">
+        <v>16</v>
+      </c>
+      <c r="B84" t="s">
+        <v>22</v>
+      </c>
+      <c r="C84" t="s">
+        <v>57</v>
+      </c>
+      <c r="D84">
+        <v>67.2</v>
+      </c>
+      <c r="E84" t="s">
+        <v>59</v>
+      </c>
+      <c r="F84" t="s">
+        <v>62</v>
+      </c>
+      <c r="G84" t="s">
+        <v>63</v>
+      </c>
+      <c r="H84">
+        <v>1379.6</v>
+      </c>
+      <c r="I84">
+        <v>2.799999999999997</v>
+      </c>
+      <c r="J84" t="s">
+        <v>65</v>
+      </c>
+      <c r="K84">
+        <v>10</v>
+      </c>
+      <c r="L84" t="s">
+        <v>72</v>
+      </c>
+      <c r="M84" t="s">
+        <v>74</v>
+      </c>
+      <c r="N84" t="s">
+        <v>78</v>
+      </c>
+      <c r="O84">
+        <v>18.3</v>
+      </c>
+      <c r="P84">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="85" spans="1:16">
+      <c r="A85" t="s">
+        <v>16</v>
+      </c>
+      <c r="B85" t="s">
+        <v>23</v>
+      </c>
+      <c r="C85" t="s">
+        <v>57</v>
+      </c>
+      <c r="D85">
+        <v>67.2</v>
+      </c>
+      <c r="E85" t="s">
+        <v>58</v>
+      </c>
+      <c r="F85" t="s">
+        <v>62</v>
+      </c>
+      <c r="G85" t="s">
+        <v>63</v>
+      </c>
+      <c r="H85">
+        <v>4454.6</v>
+      </c>
+      <c r="I85">
+        <v>2.799999999999997</v>
+      </c>
+      <c r="J85" t="s">
+        <v>65</v>
+      </c>
+      <c r="K85">
+        <v>10</v>
+      </c>
+      <c r="L85" t="s">
+        <v>72</v>
+      </c>
+      <c r="M85" t="s">
+        <v>74</v>
+      </c>
+      <c r="N85" t="s">
+        <v>78</v>
+      </c>
+      <c r="O85">
+        <v>18.3</v>
+      </c>
+      <c r="P85">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="86" spans="1:16">
+      <c r="A86" t="s">
+        <v>16</v>
+      </c>
+      <c r="B86" t="s">
+        <v>24</v>
+      </c>
+      <c r="C86" t="s">
+        <v>57</v>
+      </c>
+      <c r="D86">
+        <v>67.2</v>
+      </c>
+      <c r="E86" t="s">
+        <v>58</v>
+      </c>
+      <c r="F86" t="s">
+        <v>62</v>
+      </c>
+      <c r="G86" t="s">
+        <v>63</v>
+      </c>
+      <c r="H86">
+        <v>1044.55</v>
+      </c>
+      <c r="I86">
+        <v>2.799999999999997</v>
+      </c>
+      <c r="J86" t="s">
+        <v>65</v>
+      </c>
+      <c r="K86">
+        <v>10</v>
+      </c>
+      <c r="L86" t="s">
+        <v>72</v>
+      </c>
+      <c r="M86" t="s">
+        <v>74</v>
+      </c>
+      <c r="N86" t="s">
+        <v>78</v>
+      </c>
+      <c r="O86">
+        <v>18.3</v>
+      </c>
+      <c r="P86">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="87" spans="1:16">
+      <c r="A87" t="s">
+        <v>16</v>
+      </c>
+      <c r="B87" t="s">
+        <v>42</v>
+      </c>
+      <c r="C87" t="s">
+        <v>57</v>
+      </c>
+      <c r="D87">
+        <v>67.2</v>
+      </c>
+      <c r="E87" t="s">
+        <v>58</v>
+      </c>
+      <c r="F87" t="s">
+        <v>62</v>
+      </c>
+      <c r="G87" t="s">
+        <v>63</v>
+      </c>
+      <c r="H87">
+        <v>88.59</v>
+      </c>
+      <c r="I87">
+        <v>2.799999999999997</v>
+      </c>
+      <c r="J87" t="s">
+        <v>65</v>
+      </c>
+      <c r="K87">
+        <v>4</v>
+      </c>
+      <c r="L87" t="s">
+        <v>73</v>
+      </c>
+      <c r="M87" t="s">
+        <v>74</v>
+      </c>
+      <c r="N87" t="s">
+        <v>78</v>
+      </c>
+      <c r="O87">
+        <v>18.3</v>
+      </c>
+      <c r="P87">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="88" spans="1:16">
+      <c r="A88" t="s">
+        <v>16</v>
+      </c>
+      <c r="B88" t="s">
+        <v>54</v>
+      </c>
+      <c r="C88" t="s">
+        <v>57</v>
+      </c>
+      <c r="D88">
+        <v>65.2</v>
+      </c>
+      <c r="E88" t="s">
+        <v>58</v>
+      </c>
+      <c r="F88" t="s">
+        <v>62</v>
+      </c>
+      <c r="G88" t="s">
+        <v>63</v>
+      </c>
+      <c r="H88">
+        <v>556.95</v>
+      </c>
+      <c r="I88">
+        <v>4.799999999999997</v>
+      </c>
+      <c r="J88" t="s">
+        <v>68</v>
+      </c>
+      <c r="K88">
+        <v>1</v>
+      </c>
+      <c r="L88" t="s">
+        <v>73</v>
+      </c>
+      <c r="M88" t="s">
+        <v>74</v>
+      </c>
+      <c r="N88" t="s">
+        <v>78</v>
+      </c>
+      <c r="O88">
+        <v>18.3</v>
+      </c>
+      <c r="P88">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="89" spans="1:16">
+      <c r="A89" t="s">
+        <v>16</v>
+      </c>
+      <c r="B89" t="s">
+        <v>32</v>
+      </c>
+      <c r="C89" t="s">
+        <v>57</v>
+      </c>
+      <c r="D89">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="E89" t="s">
+        <v>58</v>
+      </c>
+      <c r="F89" t="s">
+        <v>62</v>
+      </c>
+      <c r="G89" t="s">
+        <v>63</v>
+      </c>
+      <c r="H89">
+        <v>1395.8</v>
+      </c>
+      <c r="I89">
+        <v>5.400000000000006</v>
+      </c>
+      <c r="J89" t="s">
+        <v>67</v>
+      </c>
+      <c r="K89">
+        <v>5</v>
+      </c>
+      <c r="L89" t="s">
+        <v>71</v>
+      </c>
+      <c r="M89" t="s">
+        <v>74</v>
+      </c>
+      <c r="N89" t="s">
+        <v>78</v>
+      </c>
+      <c r="O89">
+        <v>18.3</v>
+      </c>
+      <c r="P89">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="90" spans="1:16">
+      <c r="A90" t="s">
+        <v>16</v>
+      </c>
+      <c r="B90" t="s">
+        <v>55</v>
+      </c>
+      <c r="C90" t="s">
+        <v>57</v>
+      </c>
+      <c r="D90">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="E90" t="s">
+        <v>58</v>
+      </c>
+      <c r="F90" t="s">
+        <v>62</v>
+      </c>
+      <c r="G90" t="s">
+        <v>63</v>
+      </c>
+      <c r="H90">
+        <v>5977</v>
+      </c>
+      <c r="I90">
+        <v>5.400000000000006</v>
+      </c>
+      <c r="J90" t="s">
+        <v>67</v>
+      </c>
+      <c r="K90">
+        <v>1</v>
+      </c>
+      <c r="L90" t="s">
+        <v>73</v>
+      </c>
+      <c r="M90" t="s">
+        <v>74</v>
+      </c>
+      <c r="N90" t="s">
+        <v>78</v>
+      </c>
+      <c r="O90">
+        <v>18.3</v>
+      </c>
+      <c r="P90">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="91" spans="1:16">
+      <c r="A91" t="s">
+        <v>16</v>
+      </c>
+      <c r="B91" t="s">
+        <v>45</v>
+      </c>
+      <c r="C91" t="s">
+        <v>57</v>
+      </c>
+      <c r="D91">
+        <v>63.6</v>
+      </c>
+      <c r="E91" t="s">
+        <v>60</v>
+      </c>
+      <c r="F91" t="s">
+        <v>62</v>
+      </c>
+      <c r="G91" t="s">
+        <v>63</v>
+      </c>
+      <c r="H91">
+        <v>1198.95</v>
+      </c>
+      <c r="I91">
+        <v>6.399999999999999</v>
+      </c>
+      <c r="J91" t="s">
+        <v>67</v>
+      </c>
+      <c r="K91">
+        <v>4</v>
+      </c>
+      <c r="L91" t="s">
+        <v>73</v>
+      </c>
+      <c r="M91" t="s">
+        <v>74</v>
+      </c>
+      <c r="N91" t="s">
+        <v>78</v>
+      </c>
+      <c r="O91">
+        <v>18.3</v>
+      </c>
+      <c r="P91">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="92" spans="1:16">
+      <c r="A92" t="s">
+        <v>16</v>
+      </c>
+      <c r="B92" t="s">
+        <v>43</v>
+      </c>
+      <c r="C92" t="s">
+        <v>57</v>
+      </c>
+      <c r="D92">
+        <v>61.1</v>
+      </c>
+      <c r="E92" t="s">
+        <v>61</v>
+      </c>
+      <c r="F92" t="s">
+        <v>62</v>
+      </c>
+      <c r="G92" t="s">
+        <v>63</v>
+      </c>
+      <c r="H92">
+        <v>1278.6</v>
+      </c>
+      <c r="I92">
+        <v>8.899999999999999</v>
+      </c>
+      <c r="J92" t="s">
+        <v>65</v>
+      </c>
+      <c r="K92">
+        <v>4</v>
+      </c>
+      <c r="L92" t="s">
+        <v>73</v>
+      </c>
+      <c r="M92" t="s">
+        <v>74</v>
+      </c>
+      <c r="N92" t="s">
+        <v>78</v>
+      </c>
+      <c r="O92">
+        <v>18.3</v>
+      </c>
+      <c r="P92">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16">
+      <c r="A93" t="s">
+        <v>16</v>
+      </c>
+      <c r="B93" t="s">
+        <v>33</v>
+      </c>
+      <c r="C93" t="s">
+        <v>57</v>
+      </c>
+      <c r="D93">
+        <v>60.6</v>
+      </c>
+      <c r="E93" t="s">
+        <v>58</v>
+      </c>
+      <c r="F93" t="s">
+        <v>62</v>
+      </c>
+      <c r="G93" t="s">
+        <v>63</v>
+      </c>
+      <c r="H93">
+        <v>9602</v>
+      </c>
+      <c r="I93">
+        <v>9.399999999999999</v>
+      </c>
+      <c r="J93" t="s">
+        <v>65</v>
+      </c>
+      <c r="K93">
+        <v>10</v>
+      </c>
+      <c r="L93" t="s">
+        <v>72</v>
+      </c>
+      <c r="M93" t="s">
+        <v>74</v>
+      </c>
+      <c r="N93" t="s">
+        <v>78</v>
+      </c>
+      <c r="O93">
+        <v>18.3</v>
+      </c>
+      <c r="P93">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="94" spans="1:16">
+      <c r="A94" t="s">
+        <v>16</v>
+      </c>
+      <c r="B94" t="s">
+        <v>37</v>
+      </c>
+      <c r="C94" t="s">
+        <v>57</v>
+      </c>
+      <c r="D94">
+        <v>59.1</v>
+      </c>
+      <c r="E94" t="s">
+        <v>58</v>
+      </c>
+      <c r="F94" t="s">
+        <v>62</v>
+      </c>
+      <c r="G94" t="s">
+        <v>63</v>
+      </c>
+      <c r="H94">
+        <v>319.75</v>
+      </c>
+      <c r="I94">
+        <v>10.9</v>
+      </c>
+      <c r="J94" t="s">
+        <v>69</v>
+      </c>
+      <c r="K94">
+        <v>10</v>
+      </c>
+      <c r="L94" t="s">
+        <v>72</v>
+      </c>
+      <c r="M94" t="s">
+        <v>74</v>
+      </c>
+      <c r="N94" t="s">
+        <v>78</v>
+      </c>
+      <c r="O94">
+        <v>18.3</v>
+      </c>
+      <c r="P94">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="95" spans="1:16">
+      <c r="A95" t="s">
+        <v>16</v>
+      </c>
+      <c r="B95" t="s">
+        <v>46</v>
+      </c>
+      <c r="C95" t="s">
+        <v>57</v>
+      </c>
+      <c r="D95">
+        <v>58.8</v>
+      </c>
+      <c r="E95" t="s">
+        <v>58</v>
+      </c>
+      <c r="F95" t="s">
+        <v>62</v>
+      </c>
+      <c r="G95" t="s">
+        <v>63</v>
+      </c>
+      <c r="H95">
+        <v>2307.9</v>
+      </c>
+      <c r="I95">
+        <v>11.2</v>
+      </c>
+      <c r="J95" t="s">
+        <v>67</v>
+      </c>
+      <c r="K95">
+        <v>4</v>
+      </c>
+      <c r="L95" t="s">
+        <v>73</v>
+      </c>
+      <c r="M95" t="s">
+        <v>74</v>
+      </c>
+      <c r="N95" t="s">
+        <v>78</v>
+      </c>
+      <c r="O95">
+        <v>18.3</v>
+      </c>
+      <c r="P95">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="96" spans="1:16">
+      <c r="A96" t="s">
+        <v>16</v>
+      </c>
+      <c r="B96" t="s">
+        <v>48</v>
+      </c>
+      <c r="C96" t="s">
+        <v>57</v>
+      </c>
+      <c r="D96">
+        <v>57.2</v>
+      </c>
+      <c r="E96" t="s">
+        <v>58</v>
+      </c>
+      <c r="F96" t="s">
+        <v>62</v>
+      </c>
+      <c r="G96" t="s">
+        <v>63</v>
+      </c>
+      <c r="H96">
+        <v>4021.1</v>
+      </c>
+      <c r="I96">
+        <v>12.8</v>
+      </c>
+      <c r="J96" t="s">
+        <v>67</v>
+      </c>
+      <c r="K96">
+        <v>6</v>
+      </c>
+      <c r="L96" t="s">
+        <v>71</v>
+      </c>
+      <c r="M96" t="s">
+        <v>74</v>
+      </c>
+      <c r="N96" t="s">
+        <v>78</v>
+      </c>
+      <c r="O96">
+        <v>18.3</v>
+      </c>
+      <c r="P96">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="97" spans="1:16">
+      <c r="A97" t="s">
+        <v>16</v>
+      </c>
+      <c r="B97" t="s">
+        <v>50</v>
+      </c>
+      <c r="C97" t="s">
+        <v>57</v>
+      </c>
+      <c r="D97">
+        <v>56.8</v>
+      </c>
+      <c r="E97" t="s">
+        <v>58</v>
+      </c>
+      <c r="F97" t="s">
+        <v>62</v>
+      </c>
+      <c r="G97" t="s">
+        <v>63</v>
+      </c>
+      <c r="H97">
+        <v>7230</v>
+      </c>
+      <c r="I97">
+        <v>13.2</v>
+      </c>
+      <c r="J97" t="s">
+        <v>66</v>
+      </c>
+      <c r="K97">
+        <v>2</v>
+      </c>
+      <c r="L97" t="s">
+        <v>73</v>
+      </c>
+      <c r="M97" t="s">
+        <v>74</v>
+      </c>
+      <c r="N97" t="s">
+        <v>78</v>
+      </c>
+      <c r="O97">
+        <v>18.3</v>
+      </c>
+      <c r="P97">
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/reports/watchlist_history.xlsx
+++ b/reports/watchlist_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="79">
   <si>
     <t>Date</t>
   </si>
@@ -193,13 +193,7 @@
     <t>+0.0</t>
   </si>
   <si>
-    <t>-2.4</t>
-  </si>
-  <si>
-    <t>+1.0</t>
-  </si>
-  <si>
-    <t>-6.0</t>
+    <t>-1.2</t>
   </si>
   <si>
     <t>Stage 2 — Uptrend ✓</t>
@@ -224,6 +218,12 @@
   </si>
   <si>
     <t>Price below 100/200 DMA — wait for MA alignment, RSI outside 50-70 zone</t>
+  </si>
+  <si>
+    <t>Score 70/100 — need macro improvement or volume surge</t>
+  </si>
+  <si>
+    <t>Score 64/100 — need macro improvement or volume surge</t>
   </si>
   <si>
     <t>20260421</t>
@@ -582,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P97"/>
+  <dimension ref="A1:P116"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -652,10 +652,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H2">
         <v>11714</v>
@@ -699,10 +699,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H3">
         <v>514.05</v>
@@ -746,10 +746,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G4" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H4">
         <v>1621.5</v>
@@ -793,10 +793,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H5">
         <v>191.38</v>
@@ -805,7 +805,7 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K5">
         <v>1</v>
@@ -843,10 +843,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G6" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H6">
         <v>1318.1</v>
@@ -855,7 +855,7 @@
         <v>0.9000000000000057</v>
       </c>
       <c r="J6" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K6">
         <v>1</v>
@@ -893,10 +893,10 @@
         <v>-0.5</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H7">
         <v>1377.7</v>
@@ -905,7 +905,7 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J7" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K7">
         <v>6</v>
@@ -943,10 +943,10 @@
         <v>-0.5</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G8" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H8">
         <v>4479.7</v>
@@ -955,7 +955,7 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J8" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K8">
         <v>6</v>
@@ -993,10 +993,10 @@
         <v>-0.5</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G9" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H9">
         <v>1045.3</v>
@@ -1005,7 +1005,7 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K9">
         <v>6</v>
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G10" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H10">
         <v>1055.65</v>
@@ -1055,7 +1055,7 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J10" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K10">
         <v>1</v>
@@ -1093,10 +1093,10 @@
         <v>-0.5</v>
       </c>
       <c r="F11" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H11">
         <v>1045.3</v>
@@ -1105,7 +1105,7 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J11" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K11">
         <v>6</v>
@@ -1143,10 +1143,10 @@
         <v>-0.5</v>
       </c>
       <c r="F12" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G12" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H12">
         <v>4479.7</v>
@@ -1155,7 +1155,7 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J12" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K12">
         <v>6</v>
@@ -1193,10 +1193,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H13">
         <v>581.3</v>
@@ -1205,7 +1205,7 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -1243,10 +1243,10 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G14" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H14">
         <v>458.9</v>
@@ -1255,7 +1255,7 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J14" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K14">
         <v>1</v>
@@ -1293,10 +1293,10 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G15" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H15">
         <v>196.02</v>
@@ -1305,7 +1305,7 @@
         <v>4.400000000000006</v>
       </c>
       <c r="J15" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K15">
         <v>1</v>
@@ -1343,10 +1343,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G16" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H16">
         <v>4172.9</v>
@@ -1355,7 +1355,7 @@
         <v>5</v>
       </c>
       <c r="J16" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K16">
         <v>1</v>
@@ -1393,10 +1393,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G17" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H17">
         <v>6373.5</v>
@@ -1405,7 +1405,7 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J17" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K17">
         <v>1</v>
@@ -1443,10 +1443,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G18" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H18">
         <v>1113.1</v>
@@ -1455,7 +1455,7 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J18" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K18">
         <v>1</v>
@@ -1493,10 +1493,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G19" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H19">
         <v>1379.9</v>
@@ -1505,7 +1505,7 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J19" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K19">
         <v>1</v>
@@ -1543,10 +1543,10 @@
         <v>-0.5</v>
       </c>
       <c r="F20" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G20" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H20">
         <v>9793</v>
@@ -1555,7 +1555,7 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J20" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K20">
         <v>6</v>
@@ -1593,10 +1593,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G21" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H21">
         <v>7955.5</v>
@@ -1605,7 +1605,7 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J21" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K21">
         <v>1</v>
@@ -1643,10 +1643,10 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G22" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H22">
         <v>1037.85</v>
@@ -1655,7 +1655,7 @@
         <v>6.399999999999999</v>
       </c>
       <c r="J22" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K22">
         <v>1</v>
@@ -1693,10 +1693,10 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G23" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H23">
         <v>979.1</v>
@@ -1705,7 +1705,7 @@
         <v>8.399999999999999</v>
       </c>
       <c r="J23" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -1743,10 +1743,10 @@
         <v>-0.5</v>
       </c>
       <c r="F24" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G24" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H24">
         <v>319.35</v>
@@ -1755,7 +1755,7 @@
         <v>8.5</v>
       </c>
       <c r="J24" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K24">
         <v>6</v>
@@ -1793,10 +1793,10 @@
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G25" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H25">
         <v>767.65</v>
@@ -1840,10 +1840,10 @@
         <v>7.8</v>
       </c>
       <c r="F26" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G26" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H26">
         <v>404.1</v>
@@ -1852,7 +1852,7 @@
         <v>1</v>
       </c>
       <c r="J26" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K26">
         <v>7</v>
@@ -1890,10 +1890,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G27" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H27">
         <v>3847</v>
@@ -1902,7 +1902,7 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K27">
         <v>1</v>
@@ -1940,10 +1940,10 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G28" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H28">
         <v>211.75</v>
@@ -1952,7 +1952,7 @@
         <v>2.5</v>
       </c>
       <c r="J28" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K28">
         <v>1</v>
@@ -1990,10 +1990,10 @@
         <v>-0.5</v>
       </c>
       <c r="F29" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G29" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H29">
         <v>1381.5</v>
@@ -2002,7 +2002,7 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J29" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K29">
         <v>7</v>
@@ -2040,10 +2040,10 @@
         <v>-0.5</v>
       </c>
       <c r="F30" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G30" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H30">
         <v>4483</v>
@@ -2052,7 +2052,7 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J30" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K30">
         <v>7</v>
@@ -2090,10 +2090,10 @@
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G31" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H31">
         <v>89.05</v>
@@ -2102,7 +2102,7 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J31" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K31">
         <v>1</v>
@@ -2140,10 +2140,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G32" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H32">
         <v>1291.1</v>
@@ -2152,7 +2152,7 @@
         <v>3.400000000000006</v>
       </c>
       <c r="J32" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K32">
         <v>1</v>
@@ -2190,10 +2190,10 @@
         <v>-0.5</v>
       </c>
       <c r="F33" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G33" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H33">
         <v>1414.6</v>
@@ -2202,7 +2202,7 @@
         <v>5.900000000000006</v>
       </c>
       <c r="J33" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K33">
         <v>2</v>
@@ -2240,10 +2240,10 @@
         <v>-0.5</v>
       </c>
       <c r="F34" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G34" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H34">
         <v>9760</v>
@@ -2252,7 +2252,7 @@
         <v>6.299999999999997</v>
       </c>
       <c r="J34" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K34">
         <v>7</v>
@@ -2290,10 +2290,10 @@
         <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G35" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H35">
         <v>125.85</v>
@@ -2302,7 +2302,7 @@
         <v>7.299999999999997</v>
       </c>
       <c r="J35" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K35">
         <v>1</v>
@@ -2340,10 +2340,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G36" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H36">
         <v>1171.95</v>
@@ -2352,7 +2352,7 @@
         <v>7.899999999999999</v>
       </c>
       <c r="J36" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K36">
         <v>1</v>
@@ -2390,10 +2390,10 @@
         <v>-6.5</v>
       </c>
       <c r="F37" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G37" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H37">
         <v>1038.1</v>
@@ -2402,7 +2402,7 @@
         <v>9.299999999999997</v>
       </c>
       <c r="J37" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K37">
         <v>7</v>
@@ -2440,10 +2440,10 @@
         <v>-2.9</v>
       </c>
       <c r="F38" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G38" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H38">
         <v>319.6</v>
@@ -2452,7 +2452,7 @@
         <v>11.4</v>
       </c>
       <c r="J38" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K38">
         <v>7</v>
@@ -2490,10 +2490,10 @@
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G39" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H39">
         <v>2314.1</v>
@@ -2502,7 +2502,7 @@
         <v>11.7</v>
       </c>
       <c r="J39" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K39">
         <v>1</v>
@@ -2540,10 +2540,10 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G40" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H40">
         <v>3723.6</v>
@@ -2552,7 +2552,7 @@
         <v>11.7</v>
       </c>
       <c r="J40" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K40">
         <v>1</v>
@@ -2590,10 +2590,10 @@
         <v>-0.5</v>
       </c>
       <c r="F41" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G41" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H41">
         <v>4049.2</v>
@@ -2602,7 +2602,7 @@
         <v>13.3</v>
       </c>
       <c r="J41" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K41">
         <v>3</v>
@@ -2640,10 +2640,10 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G42" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H42">
         <v>124.98</v>
@@ -2652,7 +2652,7 @@
         <v>14.6</v>
       </c>
       <c r="J42" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K42">
         <v>1</v>
@@ -2690,10 +2690,10 @@
         <v>2.4</v>
       </c>
       <c r="F43" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G43" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H43">
         <v>1388.7</v>
@@ -2702,7 +2702,7 @@
         <v>0.9000000000000057</v>
       </c>
       <c r="J43" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K43">
         <v>8</v>
@@ -2740,10 +2740,10 @@
         <v>0</v>
       </c>
       <c r="F44" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G44" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H44">
         <v>404.8</v>
@@ -2752,7 +2752,7 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K44">
         <v>8</v>
@@ -2790,10 +2790,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G45" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H45">
         <v>3845.7</v>
@@ -2802,7 +2802,7 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K45">
         <v>2</v>
@@ -2840,10 +2840,10 @@
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G46" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H46">
         <v>213.03</v>
@@ -2852,7 +2852,7 @@
         <v>1.5</v>
       </c>
       <c r="J46" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K46">
         <v>2</v>
@@ -2890,10 +2890,10 @@
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G47" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H47">
         <v>4477</v>
@@ -2902,7 +2902,7 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J47" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K47">
         <v>8</v>
@@ -2940,10 +2940,10 @@
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G48" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H48">
         <v>88.98999999999999</v>
@@ -2952,7 +2952,7 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J48" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K48">
         <v>2</v>
@@ -2990,10 +2990,10 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G49" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H49">
         <v>1288.9</v>
@@ -3002,7 +3002,7 @@
         <v>3.400000000000006</v>
       </c>
       <c r="J49" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K49">
         <v>2</v>
@@ -3040,10 +3040,10 @@
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G50" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H50">
         <v>1419</v>
@@ -3052,7 +3052,7 @@
         <v>5.900000000000006</v>
       </c>
       <c r="J50" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K50">
         <v>3</v>
@@ -3090,10 +3090,10 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G51" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H51">
         <v>9758</v>
@@ -3102,7 +3102,7 @@
         <v>6.299999999999997</v>
       </c>
       <c r="J51" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K51">
         <v>8</v>
@@ -3140,10 +3140,10 @@
         <v>0</v>
       </c>
       <c r="F52" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G52" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H52">
         <v>125.98</v>
@@ -3152,7 +3152,7 @@
         <v>7.299999999999997</v>
       </c>
       <c r="J52" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K52">
         <v>2</v>
@@ -3190,10 +3190,10 @@
         <v>0</v>
       </c>
       <c r="F53" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G53" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H53">
         <v>1182</v>
@@ -3202,7 +3202,7 @@
         <v>7.899999999999999</v>
       </c>
       <c r="J53" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K53">
         <v>2</v>
@@ -3240,10 +3240,10 @@
         <v>0</v>
       </c>
       <c r="F54" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G54" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H54">
         <v>1040</v>
@@ -3252,7 +3252,7 @@
         <v>9.299999999999997</v>
       </c>
       <c r="J54" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K54">
         <v>8</v>
@@ -3290,10 +3290,10 @@
         <v>0</v>
       </c>
       <c r="F55" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G55" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H55">
         <v>320.2</v>
@@ -3302,7 +3302,7 @@
         <v>11.4</v>
       </c>
       <c r="J55" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K55">
         <v>8</v>
@@ -3340,10 +3340,10 @@
         <v>0</v>
       </c>
       <c r="F56" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G56" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H56">
         <v>2314.8</v>
@@ -3352,7 +3352,7 @@
         <v>11.7</v>
       </c>
       <c r="J56" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K56">
         <v>2</v>
@@ -3390,10 +3390,10 @@
         <v>0</v>
       </c>
       <c r="F57" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G57" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H57">
         <v>3716.5</v>
@@ -3402,7 +3402,7 @@
         <v>11.7</v>
       </c>
       <c r="J57" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K57">
         <v>2</v>
@@ -3440,10 +3440,10 @@
         <v>0</v>
       </c>
       <c r="F58" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G58" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H58">
         <v>4043</v>
@@ -3452,7 +3452,7 @@
         <v>13.3</v>
       </c>
       <c r="J58" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K58">
         <v>4</v>
@@ -3490,10 +3490,10 @@
         <v>0</v>
       </c>
       <c r="F59" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G59" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H59">
         <v>125.04</v>
@@ -3502,7 +3502,7 @@
         <v>14.6</v>
       </c>
       <c r="J59" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K59">
         <v>2</v>
@@ -3540,10 +3540,10 @@
         <v>0</v>
       </c>
       <c r="F60" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G60" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H60">
         <v>3852.5</v>
@@ -3587,10 +3587,10 @@
         <v>0.5</v>
       </c>
       <c r="F61" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G61" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H61">
         <v>1388.5</v>
@@ -3599,7 +3599,7 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J61" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K61">
         <v>9</v>
@@ -3637,10 +3637,10 @@
         <v>0.5</v>
       </c>
       <c r="F62" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G62" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H62">
         <v>406.1</v>
@@ -3649,7 +3649,7 @@
         <v>0.5</v>
       </c>
       <c r="J62" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K62">
         <v>9</v>
@@ -3687,10 +3687,10 @@
         <v>0.5</v>
       </c>
       <c r="F63" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G63" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H63">
         <v>213.6</v>
@@ -3699,7 +3699,7 @@
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K63">
         <v>3</v>
@@ -3737,10 +3737,10 @@
         <v>0.5</v>
       </c>
       <c r="F64" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G64" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H64">
         <v>4478</v>
@@ -3749,7 +3749,7 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J64" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K64">
         <v>9</v>
@@ -3787,10 +3787,10 @@
         <v>6.5</v>
       </c>
       <c r="F65" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G65" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H65">
         <v>1050.05</v>
@@ -3799,7 +3799,7 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J65" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K65">
         <v>9</v>
@@ -3837,10 +3837,10 @@
         <v>0.5</v>
       </c>
       <c r="F66" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G66" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H66">
         <v>88.59</v>
@@ -3849,7 +3849,7 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J66" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K66">
         <v>3</v>
@@ -3887,10 +3887,10 @@
         <v>0.5</v>
       </c>
       <c r="F67" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G67" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H67">
         <v>1291.7</v>
@@ -3899,7 +3899,7 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J67" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K67">
         <v>3</v>
@@ -3937,10 +3937,10 @@
         <v>0.5</v>
       </c>
       <c r="F68" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G68" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H68">
         <v>1405.3</v>
@@ -3949,7 +3949,7 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J68" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K68">
         <v>4</v>
@@ -3987,10 +3987,10 @@
         <v>0.5</v>
       </c>
       <c r="F69" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G69" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H69">
         <v>125.89</v>
@@ -3999,7 +3999,7 @@
         <v>6.799999999999997</v>
       </c>
       <c r="J69" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K69">
         <v>3</v>
@@ -4037,10 +4037,10 @@
         <v>0.5</v>
       </c>
       <c r="F70" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G70" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H70">
         <v>1190.45</v>
@@ -4049,7 +4049,7 @@
         <v>7.399999999999999</v>
       </c>
       <c r="J70" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K70">
         <v>3</v>
@@ -4087,10 +4087,10 @@
         <v>-3.1</v>
       </c>
       <c r="F71" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G71" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H71">
         <v>9700</v>
@@ -4099,7 +4099,7 @@
         <v>9.399999999999999</v>
       </c>
       <c r="J71" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K71">
         <v>9</v>
@@ -4137,10 +4137,10 @@
         <v>0.5</v>
       </c>
       <c r="F72" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G72" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H72">
         <v>319.85</v>
@@ -4149,7 +4149,7 @@
         <v>10.9</v>
       </c>
       <c r="J72" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K72">
         <v>9</v>
@@ -4187,10 +4187,10 @@
         <v>0.5</v>
       </c>
       <c r="F73" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G73" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H73">
         <v>2305.6</v>
@@ -4199,7 +4199,7 @@
         <v>11.2</v>
       </c>
       <c r="J73" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K73">
         <v>3</v>
@@ -4237,10 +4237,10 @@
         <v>0.5</v>
       </c>
       <c r="F74" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G74" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H74">
         <v>3703.3</v>
@@ -4249,7 +4249,7 @@
         <v>11.2</v>
       </c>
       <c r="J74" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K74">
         <v>3</v>
@@ -4287,10 +4287,10 @@
         <v>0.5</v>
       </c>
       <c r="F75" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G75" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H75">
         <v>4023.5</v>
@@ -4299,7 +4299,7 @@
         <v>12.8</v>
       </c>
       <c r="J75" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K75">
         <v>5</v>
@@ -4337,10 +4337,10 @@
         <v>0</v>
       </c>
       <c r="F76" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G76" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H76">
         <v>7196</v>
@@ -4349,7 +4349,7 @@
         <v>13.2</v>
       </c>
       <c r="J76" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K76">
         <v>1</v>
@@ -4387,10 +4387,10 @@
         <v>0.5</v>
       </c>
       <c r="F77" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G77" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H77">
         <v>125</v>
@@ -4399,7 +4399,7 @@
         <v>14.1</v>
       </c>
       <c r="J77" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K77">
         <v>3</v>
@@ -4421,8 +4421,8 @@
       </c>
     </row>
     <row r="78" spans="1:16">
-      <c r="A78" t="s">
-        <v>16</v>
+      <c r="A78">
+        <v>20260422</v>
       </c>
       <c r="B78" t="s">
         <v>51</v>
@@ -4433,14 +4433,14 @@
       <c r="D78">
         <v>73.7</v>
       </c>
-      <c r="E78" t="s">
-        <v>58</v>
+      <c r="E78">
+        <v>0</v>
       </c>
       <c r="F78" t="s">
+        <v>60</v>
+      </c>
+      <c r="G78" t="s">
         <v>62</v>
-      </c>
-      <c r="G78" t="s">
-        <v>64</v>
       </c>
       <c r="H78">
         <v>1449.1</v>
@@ -4468,8 +4468,8 @@
       </c>
     </row>
     <row r="79" spans="1:16">
-      <c r="A79" t="s">
-        <v>16</v>
+      <c r="A79">
+        <v>20260422</v>
       </c>
       <c r="B79" t="s">
         <v>40</v>
@@ -4480,14 +4480,14 @@
       <c r="D79">
         <v>71.5</v>
       </c>
-      <c r="E79" t="s">
-        <v>58</v>
+      <c r="E79">
+        <v>0</v>
       </c>
       <c r="F79" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G79" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H79">
         <v>3844.3</v>
@@ -4515,8 +4515,8 @@
       </c>
     </row>
     <row r="80" spans="1:16">
-      <c r="A80" t="s">
-        <v>16</v>
+      <c r="A80">
+        <v>20260422</v>
       </c>
       <c r="B80" t="s">
         <v>52</v>
@@ -4527,14 +4527,14 @@
       <c r="D80">
         <v>71.09999999999999</v>
       </c>
-      <c r="E80" t="s">
-        <v>58</v>
+      <c r="E80">
+        <v>0</v>
       </c>
       <c r="F80" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G80" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H80">
         <v>1330.5</v>
@@ -4562,8 +4562,8 @@
       </c>
     </row>
     <row r="81" spans="1:16">
-      <c r="A81" t="s">
-        <v>16</v>
+      <c r="A81">
+        <v>20260422</v>
       </c>
       <c r="B81" t="s">
         <v>39</v>
@@ -4574,14 +4574,14 @@
       <c r="D81">
         <v>70.5</v>
       </c>
-      <c r="E81" t="s">
-        <v>58</v>
+      <c r="E81">
+        <v>0</v>
       </c>
       <c r="F81" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G81" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H81">
         <v>405.4</v>
@@ -4609,8 +4609,8 @@
       </c>
     </row>
     <row r="82" spans="1:16">
-      <c r="A82" t="s">
-        <v>16</v>
+      <c r="A82">
+        <v>20260422</v>
       </c>
       <c r="B82" t="s">
         <v>53</v>
@@ -4621,14 +4621,14 @@
       <c r="D82">
         <v>69.59999999999999</v>
       </c>
-      <c r="E82" t="s">
-        <v>58</v>
+      <c r="E82">
+        <v>0</v>
       </c>
       <c r="F82" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G82" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H82">
         <v>554.7</v>
@@ -4637,7 +4637,7 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J82" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K82">
         <v>1</v>
@@ -4659,8 +4659,8 @@
       </c>
     </row>
     <row r="83" spans="1:16">
-      <c r="A83" t="s">
-        <v>16</v>
+      <c r="A83">
+        <v>20260422</v>
       </c>
       <c r="B83" t="s">
         <v>41</v>
@@ -4671,14 +4671,14 @@
       <c r="D83">
         <v>69</v>
       </c>
-      <c r="E83" t="s">
-        <v>58</v>
+      <c r="E83">
+        <v>0</v>
       </c>
       <c r="F83" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G83" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H83">
         <v>215.65</v>
@@ -4687,7 +4687,7 @@
         <v>1</v>
       </c>
       <c r="J83" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K83">
         <v>4</v>
@@ -4709,8 +4709,8 @@
       </c>
     </row>
     <row r="84" spans="1:16">
-      <c r="A84" t="s">
-        <v>16</v>
+      <c r="A84">
+        <v>20260422</v>
       </c>
       <c r="B84" t="s">
         <v>22</v>
@@ -4721,14 +4721,14 @@
       <c r="D84">
         <v>67.2</v>
       </c>
-      <c r="E84" t="s">
-        <v>59</v>
+      <c r="E84">
+        <v>-2.4</v>
       </c>
       <c r="F84" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G84" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H84">
         <v>1379.6</v>
@@ -4737,7 +4737,7 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J84" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K84">
         <v>10</v>
@@ -4759,8 +4759,8 @@
       </c>
     </row>
     <row r="85" spans="1:16">
-      <c r="A85" t="s">
-        <v>16</v>
+      <c r="A85">
+        <v>20260422</v>
       </c>
       <c r="B85" t="s">
         <v>23</v>
@@ -4771,14 +4771,14 @@
       <c r="D85">
         <v>67.2</v>
       </c>
-      <c r="E85" t="s">
-        <v>58</v>
+      <c r="E85">
+        <v>0</v>
       </c>
       <c r="F85" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G85" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H85">
         <v>4454.6</v>
@@ -4787,7 +4787,7 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J85" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K85">
         <v>10</v>
@@ -4809,8 +4809,8 @@
       </c>
     </row>
     <row r="86" spans="1:16">
-      <c r="A86" t="s">
-        <v>16</v>
+      <c r="A86">
+        <v>20260422</v>
       </c>
       <c r="B86" t="s">
         <v>24</v>
@@ -4821,14 +4821,14 @@
       <c r="D86">
         <v>67.2</v>
       </c>
-      <c r="E86" t="s">
-        <v>58</v>
+      <c r="E86">
+        <v>0</v>
       </c>
       <c r="F86" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G86" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H86">
         <v>1044.55</v>
@@ -4837,7 +4837,7 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J86" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K86">
         <v>10</v>
@@ -4859,8 +4859,8 @@
       </c>
     </row>
     <row r="87" spans="1:16">
-      <c r="A87" t="s">
-        <v>16</v>
+      <c r="A87">
+        <v>20260422</v>
       </c>
       <c r="B87" t="s">
         <v>42</v>
@@ -4871,14 +4871,14 @@
       <c r="D87">
         <v>67.2</v>
       </c>
-      <c r="E87" t="s">
-        <v>58</v>
+      <c r="E87">
+        <v>0</v>
       </c>
       <c r="F87" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G87" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H87">
         <v>88.59</v>
@@ -4887,7 +4887,7 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J87" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K87">
         <v>4</v>
@@ -4909,8 +4909,8 @@
       </c>
     </row>
     <row r="88" spans="1:16">
-      <c r="A88" t="s">
-        <v>16</v>
+      <c r="A88">
+        <v>20260422</v>
       </c>
       <c r="B88" t="s">
         <v>54</v>
@@ -4921,14 +4921,14 @@
       <c r="D88">
         <v>65.2</v>
       </c>
-      <c r="E88" t="s">
-        <v>58</v>
+      <c r="E88">
+        <v>0</v>
       </c>
       <c r="F88" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G88" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H88">
         <v>556.95</v>
@@ -4937,7 +4937,7 @@
         <v>4.799999999999997</v>
       </c>
       <c r="J88" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K88">
         <v>1</v>
@@ -4959,8 +4959,8 @@
       </c>
     </row>
     <row r="89" spans="1:16">
-      <c r="A89" t="s">
-        <v>16</v>
+      <c r="A89">
+        <v>20260422</v>
       </c>
       <c r="B89" t="s">
         <v>32</v>
@@ -4971,14 +4971,14 @@
       <c r="D89">
         <v>64.59999999999999</v>
       </c>
-      <c r="E89" t="s">
-        <v>58</v>
+      <c r="E89">
+        <v>0</v>
       </c>
       <c r="F89" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G89" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H89">
         <v>1395.8</v>
@@ -4987,7 +4987,7 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J89" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K89">
         <v>5</v>
@@ -5009,8 +5009,8 @@
       </c>
     </row>
     <row r="90" spans="1:16">
-      <c r="A90" t="s">
-        <v>16</v>
+      <c r="A90">
+        <v>20260422</v>
       </c>
       <c r="B90" t="s">
         <v>55</v>
@@ -5021,14 +5021,14 @@
       <c r="D90">
         <v>64.59999999999999</v>
       </c>
-      <c r="E90" t="s">
-        <v>58</v>
+      <c r="E90">
+        <v>0</v>
       </c>
       <c r="F90" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G90" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H90">
         <v>5977</v>
@@ -5037,7 +5037,7 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J90" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K90">
         <v>1</v>
@@ -5059,8 +5059,8 @@
       </c>
     </row>
     <row r="91" spans="1:16">
-      <c r="A91" t="s">
-        <v>16</v>
+      <c r="A91">
+        <v>20260422</v>
       </c>
       <c r="B91" t="s">
         <v>45</v>
@@ -5071,14 +5071,14 @@
       <c r="D91">
         <v>63.6</v>
       </c>
-      <c r="E91" t="s">
-        <v>60</v>
+      <c r="E91">
+        <v>1</v>
       </c>
       <c r="F91" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G91" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H91">
         <v>1198.95</v>
@@ -5087,7 +5087,7 @@
         <v>6.399999999999999</v>
       </c>
       <c r="J91" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K91">
         <v>4</v>
@@ -5109,8 +5109,8 @@
       </c>
     </row>
     <row r="92" spans="1:16">
-      <c r="A92" t="s">
-        <v>16</v>
+      <c r="A92">
+        <v>20260422</v>
       </c>
       <c r="B92" t="s">
         <v>43</v>
@@ -5121,14 +5121,14 @@
       <c r="D92">
         <v>61.1</v>
       </c>
-      <c r="E92" t="s">
-        <v>61</v>
+      <c r="E92">
+        <v>-6</v>
       </c>
       <c r="F92" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G92" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H92">
         <v>1278.6</v>
@@ -5137,7 +5137,7 @@
         <v>8.899999999999999</v>
       </c>
       <c r="J92" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K92">
         <v>4</v>
@@ -5159,8 +5159,8 @@
       </c>
     </row>
     <row r="93" spans="1:16">
-      <c r="A93" t="s">
-        <v>16</v>
+      <c r="A93">
+        <v>20260422</v>
       </c>
       <c r="B93" t="s">
         <v>33</v>
@@ -5171,14 +5171,14 @@
       <c r="D93">
         <v>60.6</v>
       </c>
-      <c r="E93" t="s">
-        <v>58</v>
+      <c r="E93">
+        <v>0</v>
       </c>
       <c r="F93" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G93" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H93">
         <v>9602</v>
@@ -5187,7 +5187,7 @@
         <v>9.399999999999999</v>
       </c>
       <c r="J93" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K93">
         <v>10</v>
@@ -5209,8 +5209,8 @@
       </c>
     </row>
     <row r="94" spans="1:16">
-      <c r="A94" t="s">
-        <v>16</v>
+      <c r="A94">
+        <v>20260422</v>
       </c>
       <c r="B94" t="s">
         <v>37</v>
@@ -5221,14 +5221,14 @@
       <c r="D94">
         <v>59.1</v>
       </c>
-      <c r="E94" t="s">
-        <v>58</v>
+      <c r="E94">
+        <v>0</v>
       </c>
       <c r="F94" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G94" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H94">
         <v>319.75</v>
@@ -5237,7 +5237,7 @@
         <v>10.9</v>
       </c>
       <c r="J94" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="K94">
         <v>10</v>
@@ -5259,8 +5259,8 @@
       </c>
     </row>
     <row r="95" spans="1:16">
-      <c r="A95" t="s">
-        <v>16</v>
+      <c r="A95">
+        <v>20260422</v>
       </c>
       <c r="B95" t="s">
         <v>46</v>
@@ -5271,14 +5271,14 @@
       <c r="D95">
         <v>58.8</v>
       </c>
-      <c r="E95" t="s">
-        <v>58</v>
+      <c r="E95">
+        <v>0</v>
       </c>
       <c r="F95" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G95" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H95">
         <v>2307.9</v>
@@ -5287,7 +5287,7 @@
         <v>11.2</v>
       </c>
       <c r="J95" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K95">
         <v>4</v>
@@ -5309,8 +5309,8 @@
       </c>
     </row>
     <row r="96" spans="1:16">
-      <c r="A96" t="s">
-        <v>16</v>
+      <c r="A96">
+        <v>20260422</v>
       </c>
       <c r="B96" t="s">
         <v>48</v>
@@ -5321,14 +5321,14 @@
       <c r="D96">
         <v>57.2</v>
       </c>
-      <c r="E96" t="s">
-        <v>58</v>
+      <c r="E96">
+        <v>0</v>
       </c>
       <c r="F96" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G96" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H96">
         <v>4021.1</v>
@@ -5337,7 +5337,7 @@
         <v>12.8</v>
       </c>
       <c r="J96" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="K96">
         <v>6</v>
@@ -5359,8 +5359,8 @@
       </c>
     </row>
     <row r="97" spans="1:16">
-      <c r="A97" t="s">
-        <v>16</v>
+      <c r="A97">
+        <v>20260422</v>
       </c>
       <c r="B97" t="s">
         <v>50</v>
@@ -5371,14 +5371,14 @@
       <c r="D97">
         <v>56.8</v>
       </c>
-      <c r="E97" t="s">
-        <v>58</v>
+      <c r="E97">
+        <v>0</v>
       </c>
       <c r="F97" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G97" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="H97">
         <v>7230</v>
@@ -5387,7 +5387,7 @@
         <v>13.2</v>
       </c>
       <c r="J97" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K97">
         <v>2</v>
@@ -5405,6 +5405,953 @@
         <v>18.3</v>
       </c>
       <c r="P97">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="98" spans="1:16">
+      <c r="A98" t="s">
+        <v>16</v>
+      </c>
+      <c r="B98" t="s">
+        <v>40</v>
+      </c>
+      <c r="C98" t="s">
+        <v>56</v>
+      </c>
+      <c r="D98">
+        <v>70.3</v>
+      </c>
+      <c r="E98" t="s">
+        <v>58</v>
+      </c>
+      <c r="F98" t="s">
+        <v>60</v>
+      </c>
+      <c r="G98" t="s">
+        <v>61</v>
+      </c>
+      <c r="H98">
+        <v>3844.3</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>1</v>
+      </c>
+      <c r="L98" t="s">
+        <v>16</v>
+      </c>
+      <c r="M98" t="s">
+        <v>74</v>
+      </c>
+      <c r="N98" t="s">
+        <v>78</v>
+      </c>
+      <c r="O98">
+        <v>18.3</v>
+      </c>
+      <c r="P98">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="99" spans="1:16">
+      <c r="A99" t="s">
+        <v>16</v>
+      </c>
+      <c r="B99" t="s">
+        <v>52</v>
+      </c>
+      <c r="C99" t="s">
+        <v>57</v>
+      </c>
+      <c r="D99">
+        <v>69.90000000000001</v>
+      </c>
+      <c r="E99" t="s">
+        <v>58</v>
+      </c>
+      <c r="F99" t="s">
+        <v>60</v>
+      </c>
+      <c r="G99" t="s">
+        <v>61</v>
+      </c>
+      <c r="H99">
+        <v>1330.5</v>
+      </c>
+      <c r="I99">
+        <v>0.09999999999999432</v>
+      </c>
+      <c r="J99" t="s">
+        <v>68</v>
+      </c>
+      <c r="K99">
+        <v>1</v>
+      </c>
+      <c r="L99" t="s">
+        <v>73</v>
+      </c>
+      <c r="M99" t="s">
+        <v>74</v>
+      </c>
+      <c r="N99" t="s">
+        <v>78</v>
+      </c>
+      <c r="O99">
+        <v>18.3</v>
+      </c>
+      <c r="P99">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="100" spans="1:16">
+      <c r="A100" t="s">
+        <v>16</v>
+      </c>
+      <c r="B100" t="s">
+        <v>39</v>
+      </c>
+      <c r="C100" t="s">
+        <v>57</v>
+      </c>
+      <c r="D100">
+        <v>69.3</v>
+      </c>
+      <c r="E100" t="s">
+        <v>58</v>
+      </c>
+      <c r="F100" t="s">
+        <v>60</v>
+      </c>
+      <c r="G100" t="s">
+        <v>61</v>
+      </c>
+      <c r="H100">
+        <v>405.4</v>
+      </c>
+      <c r="I100">
+        <v>0.7000000000000028</v>
+      </c>
+      <c r="J100" t="s">
+        <v>63</v>
+      </c>
+      <c r="K100">
+        <v>1</v>
+      </c>
+      <c r="L100" t="s">
+        <v>73</v>
+      </c>
+      <c r="M100" t="s">
+        <v>74</v>
+      </c>
+      <c r="N100" t="s">
+        <v>78</v>
+      </c>
+      <c r="O100">
+        <v>18.3</v>
+      </c>
+      <c r="P100">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="101" spans="1:16">
+      <c r="A101" t="s">
+        <v>16</v>
+      </c>
+      <c r="B101" t="s">
+        <v>53</v>
+      </c>
+      <c r="C101" t="s">
+        <v>57</v>
+      </c>
+      <c r="D101">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="E101" t="s">
+        <v>59</v>
+      </c>
+      <c r="F101" t="s">
+        <v>60</v>
+      </c>
+      <c r="G101" t="s">
+        <v>61</v>
+      </c>
+      <c r="H101">
+        <v>554.7</v>
+      </c>
+      <c r="I101">
+        <v>1.599999999999994</v>
+      </c>
+      <c r="J101" t="s">
+        <v>64</v>
+      </c>
+      <c r="K101">
+        <v>2</v>
+      </c>
+      <c r="L101" t="s">
+        <v>73</v>
+      </c>
+      <c r="M101" t="s">
+        <v>74</v>
+      </c>
+      <c r="N101" t="s">
+        <v>78</v>
+      </c>
+      <c r="O101">
+        <v>18.3</v>
+      </c>
+      <c r="P101">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="102" spans="1:16">
+      <c r="A102" t="s">
+        <v>16</v>
+      </c>
+      <c r="B102" t="s">
+        <v>41</v>
+      </c>
+      <c r="C102" t="s">
+        <v>57</v>
+      </c>
+      <c r="D102">
+        <v>67.8</v>
+      </c>
+      <c r="E102" t="s">
+        <v>59</v>
+      </c>
+      <c r="F102" t="s">
+        <v>60</v>
+      </c>
+      <c r="G102" t="s">
+        <v>61</v>
+      </c>
+      <c r="H102">
+        <v>215.65</v>
+      </c>
+      <c r="I102">
+        <v>2.200000000000003</v>
+      </c>
+      <c r="J102" t="s">
+        <v>65</v>
+      </c>
+      <c r="K102">
+        <v>5</v>
+      </c>
+      <c r="L102" t="s">
+        <v>73</v>
+      </c>
+      <c r="M102" t="s">
+        <v>74</v>
+      </c>
+      <c r="N102" t="s">
+        <v>78</v>
+      </c>
+      <c r="O102">
+        <v>18.3</v>
+      </c>
+      <c r="P102">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="103" spans="1:16">
+      <c r="A103" t="s">
+        <v>16</v>
+      </c>
+      <c r="B103" t="s">
+        <v>22</v>
+      </c>
+      <c r="C103" t="s">
+        <v>57</v>
+      </c>
+      <c r="D103">
+        <v>66</v>
+      </c>
+      <c r="E103" t="s">
+        <v>59</v>
+      </c>
+      <c r="F103" t="s">
+        <v>60</v>
+      </c>
+      <c r="G103" t="s">
+        <v>61</v>
+      </c>
+      <c r="H103">
+        <v>1379.6</v>
+      </c>
+      <c r="I103">
+        <v>4</v>
+      </c>
+      <c r="J103" t="s">
+        <v>63</v>
+      </c>
+      <c r="K103">
+        <v>11</v>
+      </c>
+      <c r="L103" t="s">
+        <v>72</v>
+      </c>
+      <c r="M103" t="s">
+        <v>74</v>
+      </c>
+      <c r="N103" t="s">
+        <v>78</v>
+      </c>
+      <c r="O103">
+        <v>18.3</v>
+      </c>
+      <c r="P103">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="104" spans="1:16">
+      <c r="A104" t="s">
+        <v>16</v>
+      </c>
+      <c r="B104" t="s">
+        <v>23</v>
+      </c>
+      <c r="C104" t="s">
+        <v>57</v>
+      </c>
+      <c r="D104">
+        <v>66</v>
+      </c>
+      <c r="E104" t="s">
+        <v>59</v>
+      </c>
+      <c r="F104" t="s">
+        <v>60</v>
+      </c>
+      <c r="G104" t="s">
+        <v>61</v>
+      </c>
+      <c r="H104">
+        <v>4454.6</v>
+      </c>
+      <c r="I104">
+        <v>4</v>
+      </c>
+      <c r="J104" t="s">
+        <v>63</v>
+      </c>
+      <c r="K104">
+        <v>11</v>
+      </c>
+      <c r="L104" t="s">
+        <v>72</v>
+      </c>
+      <c r="M104" t="s">
+        <v>74</v>
+      </c>
+      <c r="N104" t="s">
+        <v>78</v>
+      </c>
+      <c r="O104">
+        <v>18.3</v>
+      </c>
+      <c r="P104">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="105" spans="1:16">
+      <c r="A105" t="s">
+        <v>16</v>
+      </c>
+      <c r="B105" t="s">
+        <v>24</v>
+      </c>
+      <c r="C105" t="s">
+        <v>57</v>
+      </c>
+      <c r="D105">
+        <v>66</v>
+      </c>
+      <c r="E105" t="s">
+        <v>59</v>
+      </c>
+      <c r="F105" t="s">
+        <v>60</v>
+      </c>
+      <c r="G105" t="s">
+        <v>61</v>
+      </c>
+      <c r="H105">
+        <v>1044.55</v>
+      </c>
+      <c r="I105">
+        <v>4</v>
+      </c>
+      <c r="J105" t="s">
+        <v>63</v>
+      </c>
+      <c r="K105">
+        <v>11</v>
+      </c>
+      <c r="L105" t="s">
+        <v>72</v>
+      </c>
+      <c r="M105" t="s">
+        <v>74</v>
+      </c>
+      <c r="N105" t="s">
+        <v>78</v>
+      </c>
+      <c r="O105">
+        <v>18.3</v>
+      </c>
+      <c r="P105">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="106" spans="1:16">
+      <c r="A106" t="s">
+        <v>16</v>
+      </c>
+      <c r="B106" t="s">
+        <v>42</v>
+      </c>
+      <c r="C106" t="s">
+        <v>57</v>
+      </c>
+      <c r="D106">
+        <v>66</v>
+      </c>
+      <c r="E106" t="s">
+        <v>59</v>
+      </c>
+      <c r="F106" t="s">
+        <v>60</v>
+      </c>
+      <c r="G106" t="s">
+        <v>61</v>
+      </c>
+      <c r="H106">
+        <v>88.59</v>
+      </c>
+      <c r="I106">
+        <v>4</v>
+      </c>
+      <c r="J106" t="s">
+        <v>63</v>
+      </c>
+      <c r="K106">
+        <v>5</v>
+      </c>
+      <c r="L106" t="s">
+        <v>73</v>
+      </c>
+      <c r="M106" t="s">
+        <v>74</v>
+      </c>
+      <c r="N106" t="s">
+        <v>78</v>
+      </c>
+      <c r="O106">
+        <v>18.3</v>
+      </c>
+      <c r="P106">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="107" spans="1:16">
+      <c r="A107" t="s">
+        <v>16</v>
+      </c>
+      <c r="B107" t="s">
+        <v>54</v>
+      </c>
+      <c r="C107" t="s">
+        <v>57</v>
+      </c>
+      <c r="D107">
+        <v>64</v>
+      </c>
+      <c r="E107" t="s">
+        <v>59</v>
+      </c>
+      <c r="F107" t="s">
+        <v>60</v>
+      </c>
+      <c r="G107" t="s">
+        <v>61</v>
+      </c>
+      <c r="H107">
+        <v>556.95</v>
+      </c>
+      <c r="I107">
+        <v>6</v>
+      </c>
+      <c r="J107" t="s">
+        <v>69</v>
+      </c>
+      <c r="K107">
+        <v>2</v>
+      </c>
+      <c r="L107" t="s">
+        <v>73</v>
+      </c>
+      <c r="M107" t="s">
+        <v>74</v>
+      </c>
+      <c r="N107" t="s">
+        <v>78</v>
+      </c>
+      <c r="O107">
+        <v>18.3</v>
+      </c>
+      <c r="P107">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="108" spans="1:16">
+      <c r="A108" t="s">
+        <v>16</v>
+      </c>
+      <c r="B108" t="s">
+        <v>32</v>
+      </c>
+      <c r="C108" t="s">
+        <v>57</v>
+      </c>
+      <c r="D108">
+        <v>63.4</v>
+      </c>
+      <c r="E108" t="s">
+        <v>59</v>
+      </c>
+      <c r="F108" t="s">
+        <v>60</v>
+      </c>
+      <c r="G108" t="s">
+        <v>61</v>
+      </c>
+      <c r="H108">
+        <v>1395.8</v>
+      </c>
+      <c r="I108">
+        <v>6.600000000000001</v>
+      </c>
+      <c r="J108" t="s">
+        <v>65</v>
+      </c>
+      <c r="K108">
+        <v>6</v>
+      </c>
+      <c r="L108" t="s">
+        <v>71</v>
+      </c>
+      <c r="M108" t="s">
+        <v>74</v>
+      </c>
+      <c r="N108" t="s">
+        <v>78</v>
+      </c>
+      <c r="O108">
+        <v>18.3</v>
+      </c>
+      <c r="P108">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="109" spans="1:16">
+      <c r="A109" t="s">
+        <v>16</v>
+      </c>
+      <c r="B109" t="s">
+        <v>55</v>
+      </c>
+      <c r="C109" t="s">
+        <v>57</v>
+      </c>
+      <c r="D109">
+        <v>63.4</v>
+      </c>
+      <c r="E109" t="s">
+        <v>59</v>
+      </c>
+      <c r="F109" t="s">
+        <v>60</v>
+      </c>
+      <c r="G109" t="s">
+        <v>61</v>
+      </c>
+      <c r="H109">
+        <v>5977</v>
+      </c>
+      <c r="I109">
+        <v>6.600000000000001</v>
+      </c>
+      <c r="J109" t="s">
+        <v>65</v>
+      </c>
+      <c r="K109">
+        <v>2</v>
+      </c>
+      <c r="L109" t="s">
+        <v>73</v>
+      </c>
+      <c r="M109" t="s">
+        <v>74</v>
+      </c>
+      <c r="N109" t="s">
+        <v>78</v>
+      </c>
+      <c r="O109">
+        <v>18.3</v>
+      </c>
+      <c r="P109">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="110" spans="1:16">
+      <c r="A110" t="s">
+        <v>16</v>
+      </c>
+      <c r="B110" t="s">
+        <v>45</v>
+      </c>
+      <c r="C110" t="s">
+        <v>57</v>
+      </c>
+      <c r="D110">
+        <v>62.4</v>
+      </c>
+      <c r="E110" t="s">
+        <v>59</v>
+      </c>
+      <c r="F110" t="s">
+        <v>60</v>
+      </c>
+      <c r="G110" t="s">
+        <v>61</v>
+      </c>
+      <c r="H110">
+        <v>1198.95</v>
+      </c>
+      <c r="I110">
+        <v>7.600000000000001</v>
+      </c>
+      <c r="J110" t="s">
+        <v>65</v>
+      </c>
+      <c r="K110">
+        <v>5</v>
+      </c>
+      <c r="L110" t="s">
+        <v>73</v>
+      </c>
+      <c r="M110" t="s">
+        <v>74</v>
+      </c>
+      <c r="N110" t="s">
+        <v>78</v>
+      </c>
+      <c r="O110">
+        <v>18.3</v>
+      </c>
+      <c r="P110">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="111" spans="1:16">
+      <c r="A111" t="s">
+        <v>16</v>
+      </c>
+      <c r="B111" t="s">
+        <v>43</v>
+      </c>
+      <c r="C111" t="s">
+        <v>57</v>
+      </c>
+      <c r="D111">
+        <v>59.9</v>
+      </c>
+      <c r="E111" t="s">
+        <v>59</v>
+      </c>
+      <c r="F111" t="s">
+        <v>60</v>
+      </c>
+      <c r="G111" t="s">
+        <v>61</v>
+      </c>
+      <c r="H111">
+        <v>1278.6</v>
+      </c>
+      <c r="I111">
+        <v>10.1</v>
+      </c>
+      <c r="J111" t="s">
+        <v>63</v>
+      </c>
+      <c r="K111">
+        <v>5</v>
+      </c>
+      <c r="L111" t="s">
+        <v>73</v>
+      </c>
+      <c r="M111" t="s">
+        <v>74</v>
+      </c>
+      <c r="N111" t="s">
+        <v>78</v>
+      </c>
+      <c r="O111">
+        <v>18.3</v>
+      </c>
+      <c r="P111">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="112" spans="1:16">
+      <c r="A112" t="s">
+        <v>16</v>
+      </c>
+      <c r="B112" t="s">
+        <v>33</v>
+      </c>
+      <c r="C112" t="s">
+        <v>57</v>
+      </c>
+      <c r="D112">
+        <v>59.4</v>
+      </c>
+      <c r="E112" t="s">
+        <v>59</v>
+      </c>
+      <c r="F112" t="s">
+        <v>60</v>
+      </c>
+      <c r="G112" t="s">
+        <v>61</v>
+      </c>
+      <c r="H112">
+        <v>9602</v>
+      </c>
+      <c r="I112">
+        <v>10.6</v>
+      </c>
+      <c r="J112" t="s">
+        <v>63</v>
+      </c>
+      <c r="K112">
+        <v>11</v>
+      </c>
+      <c r="L112" t="s">
+        <v>72</v>
+      </c>
+      <c r="M112" t="s">
+        <v>74</v>
+      </c>
+      <c r="N112" t="s">
+        <v>78</v>
+      </c>
+      <c r="O112">
+        <v>18.3</v>
+      </c>
+      <c r="P112">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="113" spans="1:16">
+      <c r="A113" t="s">
+        <v>16</v>
+      </c>
+      <c r="B113" t="s">
+        <v>37</v>
+      </c>
+      <c r="C113" t="s">
+        <v>57</v>
+      </c>
+      <c r="D113">
+        <v>57.9</v>
+      </c>
+      <c r="E113" t="s">
+        <v>59</v>
+      </c>
+      <c r="F113" t="s">
+        <v>60</v>
+      </c>
+      <c r="G113" t="s">
+        <v>61</v>
+      </c>
+      <c r="H113">
+        <v>319.75</v>
+      </c>
+      <c r="I113">
+        <v>12.1</v>
+      </c>
+      <c r="J113" t="s">
+        <v>67</v>
+      </c>
+      <c r="K113">
+        <v>11</v>
+      </c>
+      <c r="L113" t="s">
+        <v>72</v>
+      </c>
+      <c r="M113" t="s">
+        <v>74</v>
+      </c>
+      <c r="N113" t="s">
+        <v>78</v>
+      </c>
+      <c r="O113">
+        <v>18.3</v>
+      </c>
+      <c r="P113">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="114" spans="1:16">
+      <c r="A114" t="s">
+        <v>16</v>
+      </c>
+      <c r="B114" t="s">
+        <v>46</v>
+      </c>
+      <c r="C114" t="s">
+        <v>57</v>
+      </c>
+      <c r="D114">
+        <v>57.6</v>
+      </c>
+      <c r="E114" t="s">
+        <v>59</v>
+      </c>
+      <c r="F114" t="s">
+        <v>60</v>
+      </c>
+      <c r="G114" t="s">
+        <v>61</v>
+      </c>
+      <c r="H114">
+        <v>2307.9</v>
+      </c>
+      <c r="I114">
+        <v>12.4</v>
+      </c>
+      <c r="J114" t="s">
+        <v>65</v>
+      </c>
+      <c r="K114">
+        <v>5</v>
+      </c>
+      <c r="L114" t="s">
+        <v>73</v>
+      </c>
+      <c r="M114" t="s">
+        <v>74</v>
+      </c>
+      <c r="N114" t="s">
+        <v>78</v>
+      </c>
+      <c r="O114">
+        <v>18.3</v>
+      </c>
+      <c r="P114">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="115" spans="1:16">
+      <c r="A115" t="s">
+        <v>16</v>
+      </c>
+      <c r="B115" t="s">
+        <v>48</v>
+      </c>
+      <c r="C115" t="s">
+        <v>57</v>
+      </c>
+      <c r="D115">
+        <v>56</v>
+      </c>
+      <c r="E115" t="s">
+        <v>59</v>
+      </c>
+      <c r="F115" t="s">
+        <v>60</v>
+      </c>
+      <c r="G115" t="s">
+        <v>61</v>
+      </c>
+      <c r="H115">
+        <v>4021.1</v>
+      </c>
+      <c r="I115">
+        <v>14</v>
+      </c>
+      <c r="J115" t="s">
+        <v>65</v>
+      </c>
+      <c r="K115">
+        <v>7</v>
+      </c>
+      <c r="L115" t="s">
+        <v>71</v>
+      </c>
+      <c r="M115" t="s">
+        <v>74</v>
+      </c>
+      <c r="N115" t="s">
+        <v>78</v>
+      </c>
+      <c r="O115">
+        <v>18.3</v>
+      </c>
+      <c r="P115">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="116" spans="1:16">
+      <c r="A116" t="s">
+        <v>16</v>
+      </c>
+      <c r="B116" t="s">
+        <v>50</v>
+      </c>
+      <c r="C116" t="s">
+        <v>57</v>
+      </c>
+      <c r="D116">
+        <v>55.6</v>
+      </c>
+      <c r="E116" t="s">
+        <v>59</v>
+      </c>
+      <c r="F116" t="s">
+        <v>60</v>
+      </c>
+      <c r="G116" t="s">
+        <v>61</v>
+      </c>
+      <c r="H116">
+        <v>7230</v>
+      </c>
+      <c r="I116">
+        <v>14.4</v>
+      </c>
+      <c r="J116" t="s">
+        <v>64</v>
+      </c>
+      <c r="K116">
+        <v>3</v>
+      </c>
+      <c r="L116" t="s">
+        <v>73</v>
+      </c>
+      <c r="M116" t="s">
+        <v>74</v>
+      </c>
+      <c r="N116" t="s">
+        <v>78</v>
+      </c>
+      <c r="O116">
+        <v>18.3</v>
+      </c>
+      <c r="P116">
         <v>45</v>
       </c>
     </row>

--- a/reports/watchlist_history.xlsx
+++ b/reports/watchlist_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="93">
   <si>
     <t>Date</t>
   </si>
@@ -64,180 +64,219 @@
     <t>FII Cr</t>
   </si>
   <si>
+    <t>20260423</t>
+  </si>
+  <si>
+    <t>APARINDS</t>
+  </si>
+  <si>
+    <t>STARHEALTH</t>
+  </si>
+  <si>
+    <t>TORNTPOWER</t>
+  </si>
+  <si>
+    <t>UNIONBANK</t>
+  </si>
+  <si>
+    <t>ANURAS</t>
+  </si>
+  <si>
+    <t>AXISBANK</t>
+  </si>
+  <si>
+    <t>TITAN</t>
+  </si>
+  <si>
+    <t>SHRIRAMFIN</t>
+  </si>
+  <si>
+    <t>NATCOPHARM</t>
+  </si>
+  <si>
+    <t>SONACOMS</t>
+  </si>
+  <si>
+    <t>BAJAJCON</t>
+  </si>
+  <si>
+    <t>DCBBANK</t>
+  </si>
+  <si>
+    <t>SCHAEFFLER</t>
+  </si>
+  <si>
+    <t>NAVINFLUOR</t>
+  </si>
+  <si>
+    <t>CCL</t>
+  </si>
+  <si>
+    <t>NESTLEIND</t>
+  </si>
+  <si>
+    <t>BAJAJ-AUTO</t>
+  </si>
+  <si>
+    <t>POLYCAB</t>
+  </si>
+  <si>
+    <t>ABSLAMC</t>
+  </si>
+  <si>
+    <t>PNBHOUSING</t>
+  </si>
+  <si>
+    <t>POWERGRID</t>
+  </si>
+  <si>
+    <t>MARICO</t>
+  </si>
+  <si>
+    <t>NTPC</t>
+  </si>
+  <si>
+    <t>SIEMENS</t>
+  </si>
+  <si>
+    <t>ADANIPOWER</t>
+  </si>
+  <si>
+    <t>NMDC</t>
+  </si>
+  <si>
+    <t>JINDALSTEL</t>
+  </si>
+  <si>
+    <t>ICICIB22</t>
+  </si>
+  <si>
+    <t>ADANIGREEN</t>
+  </si>
+  <si>
+    <t>LUPIN</t>
+  </si>
+  <si>
+    <t>TVSMOTOR</t>
+  </si>
+  <si>
+    <t>LT</t>
+  </si>
+  <si>
+    <t>GOLDBEES</t>
+  </si>
+  <si>
+    <t>EICHERMOT</t>
+  </si>
+  <si>
+    <t>GESHIP</t>
+  </si>
+  <si>
+    <t>HAPPYFORGE</t>
+  </si>
+  <si>
+    <t>ELGIEQUIP</t>
+  </si>
+  <si>
+    <t>HINDCOPPER</t>
+  </si>
+  <si>
+    <t>ESABINDIA</t>
+  </si>
+  <si>
+    <t>COALINDIA</t>
+  </si>
+  <si>
+    <t>BUY</t>
+  </si>
+  <si>
+    <t>WATCH</t>
+  </si>
+  <si>
+    <t>+6.5</t>
+  </si>
+  <si>
+    <t>+0.0</t>
+  </si>
+  <si>
+    <t>-2.0</t>
+  </si>
+  <si>
+    <t>+6.4</t>
+  </si>
+  <si>
+    <t>-5.4</t>
+  </si>
+  <si>
+    <t>+4.0</t>
+  </si>
+  <si>
+    <t>-6.4</t>
+  </si>
+  <si>
+    <t>-5.0</t>
+  </si>
+  <si>
+    <t>-4.0</t>
+  </si>
+  <si>
+    <t>-3.0</t>
+  </si>
+  <si>
+    <t>-3.8</t>
+  </si>
+  <si>
+    <t>Stage 2 — Uptrend ✓</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>VCP incomplete — price range still wide, wait for tighter base (3 contractions)</t>
+  </si>
+  <si>
+    <t>Price below 100/200 DMA — wait for MA alignment</t>
+  </si>
+  <si>
+    <t>VCP incomplete — price range still wide, wait for tighter base (3 contractions),</t>
+  </si>
+  <si>
+    <t>Score 65/100 — need macro improvement or volume surge</t>
+  </si>
+  <si>
+    <t>Price below 100/200 DMA — wait for MA alignment, RSI outside 50-70 zone</t>
+  </si>
+  <si>
+    <t>Score 70/100 — need macro improvement or volume surge</t>
+  </si>
+  <si>
+    <t>Score 64/100 — need macro improvement or volume surge</t>
+  </si>
+  <si>
+    <t>MACD bearish — wait for bullish crossover</t>
+  </si>
+  <si>
+    <t>20260421</t>
+  </si>
+  <si>
+    <t>2026-04-21</t>
+  </si>
+  <si>
+    <t>2026-04-20</t>
+  </si>
+  <si>
     <t>20260422</t>
   </si>
   <si>
-    <t>APARINDS</t>
-  </si>
-  <si>
-    <t>STARHEALTH</t>
-  </si>
-  <si>
-    <t>TORNTPOWER</t>
-  </si>
-  <si>
-    <t>UNIONBANK</t>
-  </si>
-  <si>
-    <t>ANURAS</t>
-  </si>
-  <si>
-    <t>AXISBANK</t>
-  </si>
-  <si>
-    <t>TITAN</t>
-  </si>
-  <si>
-    <t>SHRIRAMFIN</t>
-  </si>
-  <si>
-    <t>NATCOPHARM</t>
-  </si>
-  <si>
-    <t>SONACOMS</t>
-  </si>
-  <si>
-    <t>BAJAJCON</t>
-  </si>
-  <si>
-    <t>DCBBANK</t>
-  </si>
-  <si>
-    <t>SCHAEFFLER</t>
-  </si>
-  <si>
-    <t>NAVINFLUOR</t>
-  </si>
-  <si>
-    <t>CCL</t>
-  </si>
-  <si>
-    <t>NESTLEIND</t>
-  </si>
-  <si>
-    <t>BAJAJ-AUTO</t>
-  </si>
-  <si>
-    <t>POLYCAB</t>
-  </si>
-  <si>
-    <t>ABSLAMC</t>
-  </si>
-  <si>
-    <t>PNBHOUSING</t>
-  </si>
-  <si>
-    <t>POWERGRID</t>
-  </si>
-  <si>
-    <t>MARICO</t>
-  </si>
-  <si>
-    <t>NTPC</t>
-  </si>
-  <si>
-    <t>SIEMENS</t>
-  </si>
-  <si>
-    <t>ADANIPOWER</t>
-  </si>
-  <si>
-    <t>NMDC</t>
-  </si>
-  <si>
-    <t>JINDALSTEL</t>
-  </si>
-  <si>
-    <t>ICICIB22</t>
-  </si>
-  <si>
-    <t>ADANIGREEN</t>
-  </si>
-  <si>
-    <t>LUPIN</t>
-  </si>
-  <si>
-    <t>TVSMOTOR</t>
-  </si>
-  <si>
-    <t>LT</t>
-  </si>
-  <si>
-    <t>GOLDBEES</t>
-  </si>
-  <si>
-    <t>EICHERMOT</t>
-  </si>
-  <si>
-    <t>GESHIP</t>
-  </si>
-  <si>
-    <t>HAPPYFORGE</t>
-  </si>
-  <si>
-    <t>ELGIEQUIP</t>
-  </si>
-  <si>
-    <t>HINDCOPPER</t>
-  </si>
-  <si>
-    <t>ESABINDIA</t>
-  </si>
-  <si>
-    <t>BUY</t>
-  </si>
-  <si>
-    <t>WATCH</t>
-  </si>
-  <si>
-    <t>+0.0</t>
-  </si>
-  <si>
-    <t>-1.2</t>
-  </si>
-  <si>
-    <t>Stage 2 — Uptrend ✓</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>VCP incomplete — price range still wide, wait for tighter base (3 contractions)</t>
-  </si>
-  <si>
-    <t>Price below 100/200 DMA — wait for MA alignment</t>
-  </si>
-  <si>
-    <t>VCP incomplete — price range still wide, wait for tighter base (3 contractions),</t>
-  </si>
-  <si>
-    <t>Score 65/100 — need macro improvement or volume surge</t>
-  </si>
-  <si>
-    <t>Price below 100/200 DMA — wait for MA alignment, RSI outside 50-70 zone</t>
-  </si>
-  <si>
-    <t>Score 70/100 — need macro improvement or volume surge</t>
-  </si>
-  <si>
-    <t>Score 64/100 — need macro improvement or volume surge</t>
-  </si>
-  <si>
-    <t>20260421</t>
-  </si>
-  <si>
-    <t>2026-04-21</t>
-  </si>
-  <si>
-    <t>2026-04-20</t>
-  </si>
-  <si>
     <t>2026-04-22</t>
   </si>
   <si>
+    <t>2026-04-23</t>
+  </si>
+  <si>
     <t>B</t>
   </si>
   <si>
@@ -251,6 +290,9 @@
   </si>
   <si>
     <t>-3.0%</t>
+  </si>
+  <si>
+    <t>-3.7%</t>
   </si>
 </sst>
 </file>
@@ -582,7 +624,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P116"/>
+  <dimension ref="A1:P132"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -643,7 +685,7 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D2">
         <v>77.09999999999999</v>
@@ -652,10 +694,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G2" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H2">
         <v>11714</v>
@@ -667,13 +709,13 @@
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="M2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N2" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O2">
         <v>17.53</v>
@@ -690,7 +732,7 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D3">
         <v>74</v>
@@ -699,10 +741,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G3" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H3">
         <v>514.05</v>
@@ -714,13 +756,13 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="M3" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N3" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O3">
         <v>17.53</v>
@@ -737,7 +779,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D4">
         <v>72</v>
@@ -746,10 +788,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G4" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H4">
         <v>1621.5</v>
@@ -761,13 +803,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="M4" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N4" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O4">
         <v>17.53</v>
@@ -784,7 +826,7 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D5">
         <v>69.59999999999999</v>
@@ -793,10 +835,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G5" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H5">
         <v>191.38</v>
@@ -805,19 +847,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J5" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M5" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N5" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O5">
         <v>17.53</v>
@@ -834,7 +876,7 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D6">
         <v>69.09999999999999</v>
@@ -843,10 +885,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G6" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H6">
         <v>1318.1</v>
@@ -855,19 +897,19 @@
         <v>0.9000000000000057</v>
       </c>
       <c r="J6" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M6" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N6" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O6">
         <v>17.53</v>
@@ -884,7 +926,7 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D7">
         <v>67.2</v>
@@ -893,10 +935,10 @@
         <v>-0.5</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G7" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H7">
         <v>1377.7</v>
@@ -905,19 +947,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J7" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K7">
         <v>6</v>
       </c>
       <c r="L7" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M7" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N7" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O7">
         <v>17.53</v>
@@ -934,7 +976,7 @@
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D8">
         <v>67.2</v>
@@ -943,10 +985,10 @@
         <v>-0.5</v>
       </c>
       <c r="F8" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G8" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H8">
         <v>4479.7</v>
@@ -955,19 +997,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J8" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K8">
         <v>6</v>
       </c>
       <c r="L8" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M8" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N8" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O8">
         <v>17.53</v>
@@ -984,7 +1026,7 @@
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D9">
         <v>67.2</v>
@@ -993,10 +1035,10 @@
         <v>-0.5</v>
       </c>
       <c r="F9" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G9" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H9">
         <v>1045.3</v>
@@ -1005,19 +1047,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J9" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K9">
         <v>6</v>
       </c>
       <c r="L9" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M9" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N9" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O9">
         <v>17.53</v>
@@ -1034,7 +1076,7 @@
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D10">
         <v>67.2</v>
@@ -1043,10 +1085,10 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G10" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H10">
         <v>1055.65</v>
@@ -1055,19 +1097,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J10" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M10" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N10" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O10">
         <v>17.53</v>
@@ -1084,7 +1126,7 @@
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D11">
         <v>67.2</v>
@@ -1093,10 +1135,10 @@
         <v>-0.5</v>
       </c>
       <c r="F11" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G11" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H11">
         <v>1045.3</v>
@@ -1105,19 +1147,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J11" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K11">
         <v>6</v>
       </c>
       <c r="L11" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M11" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N11" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O11">
         <v>17.53</v>
@@ -1134,7 +1176,7 @@
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D12">
         <v>67.2</v>
@@ -1143,10 +1185,10 @@
         <v>-0.5</v>
       </c>
       <c r="F12" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G12" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H12">
         <v>4479.7</v>
@@ -1155,19 +1197,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J12" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K12">
         <v>6</v>
       </c>
       <c r="L12" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M12" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N12" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O12">
         <v>17.53</v>
@@ -1184,7 +1226,7 @@
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D13">
         <v>67.09999999999999</v>
@@ -1193,10 +1235,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G13" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H13">
         <v>581.3</v>
@@ -1205,19 +1247,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J13" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K13">
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M13" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N13" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O13">
         <v>17.53</v>
@@ -1234,7 +1276,7 @@
         <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D14">
         <v>67.09999999999999</v>
@@ -1243,10 +1285,10 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G14" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H14">
         <v>458.9</v>
@@ -1255,19 +1297,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J14" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M14" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N14" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O14">
         <v>17.53</v>
@@ -1284,7 +1326,7 @@
         <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D15">
         <v>65.59999999999999</v>
@@ -1293,10 +1335,10 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G15" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H15">
         <v>196.02</v>
@@ -1305,19 +1347,19 @@
         <v>4.400000000000006</v>
       </c>
       <c r="J15" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M15" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N15" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O15">
         <v>17.53</v>
@@ -1334,7 +1376,7 @@
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16">
         <v>65</v>
@@ -1343,10 +1385,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G16" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H16">
         <v>4172.9</v>
@@ -1355,19 +1397,19 @@
         <v>5</v>
       </c>
       <c r="J16" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K16">
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M16" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N16" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O16">
         <v>17.53</v>
@@ -1384,7 +1426,7 @@
         <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D17">
         <v>64.7</v>
@@ -1393,10 +1435,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G17" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H17">
         <v>6373.5</v>
@@ -1405,19 +1447,19 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J17" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="K17">
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M17" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N17" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O17">
         <v>17.53</v>
@@ -1434,7 +1476,7 @@
         <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D18">
         <v>64.7</v>
@@ -1443,10 +1485,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G18" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H18">
         <v>1113.1</v>
@@ -1455,19 +1497,19 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J18" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M18" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N18" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O18">
         <v>17.53</v>
@@ -1484,7 +1526,7 @@
         <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D19">
         <v>64.59999999999999</v>
@@ -1493,10 +1535,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G19" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H19">
         <v>1379.9</v>
@@ -1505,19 +1547,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J19" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K19">
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M19" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N19" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O19">
         <v>17.53</v>
@@ -1534,7 +1576,7 @@
         <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D20">
         <v>64.2</v>
@@ -1543,10 +1585,10 @@
         <v>-0.5</v>
       </c>
       <c r="F20" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G20" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H20">
         <v>9793</v>
@@ -1555,19 +1597,19 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J20" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K20">
         <v>6</v>
       </c>
       <c r="L20" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M20" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N20" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O20">
         <v>17.53</v>
@@ -1584,7 +1626,7 @@
         <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D21">
         <v>64.2</v>
@@ -1593,10 +1635,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G21" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H21">
         <v>7955.5</v>
@@ -1605,19 +1647,19 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J21" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K21">
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M21" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N21" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O21">
         <v>17.53</v>
@@ -1634,7 +1676,7 @@
         <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D22">
         <v>63.6</v>
@@ -1643,10 +1685,10 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G22" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H22">
         <v>1037.85</v>
@@ -1655,19 +1697,19 @@
         <v>6.399999999999999</v>
       </c>
       <c r="J22" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K22">
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M22" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N22" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O22">
         <v>17.53</v>
@@ -1684,7 +1726,7 @@
         <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D23">
         <v>61.6</v>
@@ -1693,10 +1735,10 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G23" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H23">
         <v>979.1</v>
@@ -1705,19 +1747,19 @@
         <v>8.399999999999999</v>
       </c>
       <c r="J23" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K23">
         <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M23" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N23" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O23">
         <v>17.53</v>
@@ -1734,7 +1776,7 @@
         <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D24">
         <v>61.5</v>
@@ -1743,10 +1785,10 @@
         <v>-0.5</v>
       </c>
       <c r="F24" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G24" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H24">
         <v>319.35</v>
@@ -1755,19 +1797,19 @@
         <v>8.5</v>
       </c>
       <c r="J24" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="K24">
         <v>6</v>
       </c>
       <c r="L24" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M24" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N24" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="O24">
         <v>17.53</v>
@@ -1784,7 +1826,7 @@
         <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D25">
         <v>70</v>
@@ -1793,10 +1835,10 @@
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G25" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H25">
         <v>767.65</v>
@@ -1808,13 +1850,13 @@
         <v>1</v>
       </c>
       <c r="L25" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="M25" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N25" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O25">
         <v>18.27</v>
@@ -1831,7 +1873,7 @@
         <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D26">
         <v>69</v>
@@ -1840,10 +1882,10 @@
         <v>7.8</v>
       </c>
       <c r="F26" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G26" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H26">
         <v>404.1</v>
@@ -1852,19 +1894,19 @@
         <v>1</v>
       </c>
       <c r="J26" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K26">
         <v>7</v>
       </c>
       <c r="L26" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M26" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N26" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O26">
         <v>18.27</v>
@@ -1881,7 +1923,7 @@
         <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D27">
         <v>69</v>
@@ -1890,10 +1932,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G27" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H27">
         <v>3847</v>
@@ -1902,19 +1944,19 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K27">
         <v>1</v>
       </c>
       <c r="L27" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M27" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N27" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O27">
         <v>18.27</v>
@@ -1931,7 +1973,7 @@
         <v>41</v>
       </c>
       <c r="C28" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D28">
         <v>67.5</v>
@@ -1940,10 +1982,10 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G28" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H28">
         <v>211.75</v>
@@ -1952,19 +1994,19 @@
         <v>2.5</v>
       </c>
       <c r="J28" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K28">
         <v>1</v>
       </c>
       <c r="L28" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M28" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N28" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O28">
         <v>18.27</v>
@@ -1981,7 +2023,7 @@
         <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D29">
         <v>66.7</v>
@@ -1990,10 +2032,10 @@
         <v>-0.5</v>
       </c>
       <c r="F29" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G29" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H29">
         <v>1381.5</v>
@@ -2002,19 +2044,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J29" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K29">
         <v>7</v>
       </c>
       <c r="L29" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M29" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N29" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O29">
         <v>18.27</v>
@@ -2031,7 +2073,7 @@
         <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D30">
         <v>66.7</v>
@@ -2040,10 +2082,10 @@
         <v>-0.5</v>
       </c>
       <c r="F30" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G30" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H30">
         <v>4483</v>
@@ -2052,19 +2094,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J30" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K30">
         <v>7</v>
       </c>
       <c r="L30" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M30" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N30" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O30">
         <v>18.27</v>
@@ -2081,7 +2123,7 @@
         <v>42</v>
       </c>
       <c r="C31" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D31">
         <v>66.7</v>
@@ -2090,10 +2132,10 @@
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G31" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H31">
         <v>89.05</v>
@@ -2102,19 +2144,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J31" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K31">
         <v>1</v>
       </c>
       <c r="L31" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M31" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N31" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O31">
         <v>18.27</v>
@@ -2131,7 +2173,7 @@
         <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D32">
         <v>66.59999999999999</v>
@@ -2140,10 +2182,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G32" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H32">
         <v>1291.1</v>
@@ -2152,19 +2194,19 @@
         <v>3.400000000000006</v>
       </c>
       <c r="J32" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K32">
         <v>1</v>
       </c>
       <c r="L32" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M32" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N32" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O32">
         <v>18.27</v>
@@ -2181,7 +2223,7 @@
         <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D33">
         <v>64.09999999999999</v>
@@ -2190,10 +2232,10 @@
         <v>-0.5</v>
       </c>
       <c r="F33" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G33" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H33">
         <v>1414.6</v>
@@ -2202,19 +2244,19 @@
         <v>5.900000000000006</v>
       </c>
       <c r="J33" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K33">
         <v>2</v>
       </c>
       <c r="L33" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M33" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N33" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O33">
         <v>18.27</v>
@@ -2231,7 +2273,7 @@
         <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D34">
         <v>63.7</v>
@@ -2240,10 +2282,10 @@
         <v>-0.5</v>
       </c>
       <c r="F34" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G34" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H34">
         <v>9760</v>
@@ -2252,19 +2294,19 @@
         <v>6.299999999999997</v>
       </c>
       <c r="J34" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K34">
         <v>7</v>
       </c>
       <c r="L34" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M34" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N34" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O34">
         <v>18.27</v>
@@ -2281,7 +2323,7 @@
         <v>44</v>
       </c>
       <c r="C35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D35">
         <v>62.7</v>
@@ -2290,10 +2332,10 @@
         <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G35" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H35">
         <v>125.85</v>
@@ -2302,19 +2344,19 @@
         <v>7.299999999999997</v>
       </c>
       <c r="J35" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K35">
         <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M35" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N35" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O35">
         <v>18.27</v>
@@ -2331,7 +2373,7 @@
         <v>45</v>
       </c>
       <c r="C36" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D36">
         <v>62.1</v>
@@ -2340,10 +2382,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G36" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H36">
         <v>1171.95</v>
@@ -2352,19 +2394,19 @@
         <v>7.899999999999999</v>
       </c>
       <c r="J36" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K36">
         <v>1</v>
       </c>
       <c r="L36" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M36" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N36" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O36">
         <v>18.27</v>
@@ -2381,7 +2423,7 @@
         <v>24</v>
       </c>
       <c r="C37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D37">
         <v>60.7</v>
@@ -2390,10 +2432,10 @@
         <v>-6.5</v>
       </c>
       <c r="F37" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G37" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H37">
         <v>1038.1</v>
@@ -2402,19 +2444,19 @@
         <v>9.299999999999997</v>
       </c>
       <c r="J37" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K37">
         <v>7</v>
       </c>
       <c r="L37" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M37" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N37" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O37">
         <v>18.27</v>
@@ -2431,7 +2473,7 @@
         <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D38">
         <v>58.6</v>
@@ -2440,10 +2482,10 @@
         <v>-2.9</v>
       </c>
       <c r="F38" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G38" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H38">
         <v>319.6</v>
@@ -2452,19 +2494,19 @@
         <v>11.4</v>
       </c>
       <c r="J38" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="K38">
         <v>7</v>
       </c>
       <c r="L38" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M38" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N38" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O38">
         <v>18.27</v>
@@ -2481,7 +2523,7 @@
         <v>46</v>
       </c>
       <c r="C39" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D39">
         <v>58.3</v>
@@ -2490,10 +2532,10 @@
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G39" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H39">
         <v>2314.1</v>
@@ -2502,19 +2544,19 @@
         <v>11.7</v>
       </c>
       <c r="J39" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K39">
         <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M39" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N39" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O39">
         <v>18.27</v>
@@ -2531,7 +2573,7 @@
         <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D40">
         <v>58.3</v>
@@ -2540,10 +2582,10 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G40" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H40">
         <v>3723.6</v>
@@ -2552,19 +2594,19 @@
         <v>11.7</v>
       </c>
       <c r="J40" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K40">
         <v>1</v>
       </c>
       <c r="L40" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M40" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N40" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O40">
         <v>18.27</v>
@@ -2581,7 +2623,7 @@
         <v>48</v>
       </c>
       <c r="C41" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D41">
         <v>56.7</v>
@@ -2590,10 +2632,10 @@
         <v>-0.5</v>
       </c>
       <c r="F41" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G41" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H41">
         <v>4049.2</v>
@@ -2602,19 +2644,19 @@
         <v>13.3</v>
       </c>
       <c r="J41" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K41">
         <v>3</v>
       </c>
       <c r="L41" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M41" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N41" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O41">
         <v>18.27</v>
@@ -2631,7 +2673,7 @@
         <v>49</v>
       </c>
       <c r="C42" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D42">
         <v>55.4</v>
@@ -2640,10 +2682,10 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G42" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H42">
         <v>124.98</v>
@@ -2652,19 +2694,19 @@
         <v>14.6</v>
       </c>
       <c r="J42" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="K42">
         <v>1</v>
       </c>
       <c r="L42" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M42" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N42" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O42">
         <v>18.27</v>
@@ -2681,7 +2723,7 @@
         <v>22</v>
       </c>
       <c r="C43" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D43">
         <v>69.09999999999999</v>
@@ -2690,10 +2732,10 @@
         <v>2.4</v>
       </c>
       <c r="F43" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G43" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H43">
         <v>1388.7</v>
@@ -2702,19 +2744,19 @@
         <v>0.9000000000000057</v>
       </c>
       <c r="J43" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K43">
         <v>8</v>
       </c>
       <c r="L43" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M43" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N43" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O43">
         <v>18.23</v>
@@ -2731,7 +2773,7 @@
         <v>39</v>
       </c>
       <c r="C44" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D44">
         <v>69</v>
@@ -2740,10 +2782,10 @@
         <v>0</v>
       </c>
       <c r="F44" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G44" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H44">
         <v>404.8</v>
@@ -2752,19 +2794,19 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K44">
         <v>8</v>
       </c>
       <c r="L44" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M44" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N44" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O44">
         <v>18.23</v>
@@ -2781,7 +2823,7 @@
         <v>40</v>
       </c>
       <c r="C45" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D45">
         <v>69</v>
@@ -2790,10 +2832,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G45" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H45">
         <v>3845.7</v>
@@ -2802,19 +2844,19 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K45">
         <v>2</v>
       </c>
       <c r="L45" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M45" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N45" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O45">
         <v>18.23</v>
@@ -2831,7 +2873,7 @@
         <v>41</v>
       </c>
       <c r="C46" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D46">
         <v>68.5</v>
@@ -2840,10 +2882,10 @@
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G46" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H46">
         <v>213.03</v>
@@ -2852,19 +2894,19 @@
         <v>1.5</v>
       </c>
       <c r="J46" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K46">
         <v>2</v>
       </c>
       <c r="L46" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M46" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N46" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O46">
         <v>18.23</v>
@@ -2881,7 +2923,7 @@
         <v>23</v>
       </c>
       <c r="C47" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D47">
         <v>66.7</v>
@@ -2890,10 +2932,10 @@
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G47" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H47">
         <v>4477</v>
@@ -2902,19 +2944,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J47" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K47">
         <v>8</v>
       </c>
       <c r="L47" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M47" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N47" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O47">
         <v>18.23</v>
@@ -2931,7 +2973,7 @@
         <v>42</v>
       </c>
       <c r="C48" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D48">
         <v>66.7</v>
@@ -2940,10 +2982,10 @@
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G48" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H48">
         <v>88.98999999999999</v>
@@ -2952,19 +2994,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J48" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K48">
         <v>2</v>
       </c>
       <c r="L48" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M48" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N48" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O48">
         <v>18.23</v>
@@ -2981,7 +3023,7 @@
         <v>43</v>
       </c>
       <c r="C49" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D49">
         <v>66.59999999999999</v>
@@ -2990,10 +3032,10 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G49" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H49">
         <v>1288.9</v>
@@ -3002,19 +3044,19 @@
         <v>3.400000000000006</v>
       </c>
       <c r="J49" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K49">
         <v>2</v>
       </c>
       <c r="L49" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M49" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N49" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O49">
         <v>18.23</v>
@@ -3031,7 +3073,7 @@
         <v>32</v>
       </c>
       <c r="C50" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D50">
         <v>64.09999999999999</v>
@@ -3040,10 +3082,10 @@
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G50" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H50">
         <v>1419</v>
@@ -3052,19 +3094,19 @@
         <v>5.900000000000006</v>
       </c>
       <c r="J50" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K50">
         <v>3</v>
       </c>
       <c r="L50" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M50" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N50" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O50">
         <v>18.23</v>
@@ -3081,7 +3123,7 @@
         <v>33</v>
       </c>
       <c r="C51" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D51">
         <v>63.7</v>
@@ -3090,10 +3132,10 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G51" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H51">
         <v>9758</v>
@@ -3102,19 +3144,19 @@
         <v>6.299999999999997</v>
       </c>
       <c r="J51" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K51">
         <v>8</v>
       </c>
       <c r="L51" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M51" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N51" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O51">
         <v>18.23</v>
@@ -3131,7 +3173,7 @@
         <v>44</v>
       </c>
       <c r="C52" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D52">
         <v>62.7</v>
@@ -3140,10 +3182,10 @@
         <v>0</v>
       </c>
       <c r="F52" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G52" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H52">
         <v>125.98</v>
@@ -3152,19 +3194,19 @@
         <v>7.299999999999997</v>
       </c>
       <c r="J52" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K52">
         <v>2</v>
       </c>
       <c r="L52" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M52" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N52" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O52">
         <v>18.23</v>
@@ -3181,7 +3223,7 @@
         <v>45</v>
       </c>
       <c r="C53" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D53">
         <v>62.1</v>
@@ -3190,10 +3232,10 @@
         <v>0</v>
       </c>
       <c r="F53" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G53" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H53">
         <v>1182</v>
@@ -3202,19 +3244,19 @@
         <v>7.899999999999999</v>
       </c>
       <c r="J53" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K53">
         <v>2</v>
       </c>
       <c r="L53" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M53" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N53" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O53">
         <v>18.23</v>
@@ -3231,7 +3273,7 @@
         <v>24</v>
       </c>
       <c r="C54" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D54">
         <v>60.7</v>
@@ -3240,10 +3282,10 @@
         <v>0</v>
       </c>
       <c r="F54" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G54" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H54">
         <v>1040</v>
@@ -3252,19 +3294,19 @@
         <v>9.299999999999997</v>
       </c>
       <c r="J54" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K54">
         <v>8</v>
       </c>
       <c r="L54" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M54" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N54" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O54">
         <v>18.23</v>
@@ -3281,7 +3323,7 @@
         <v>37</v>
       </c>
       <c r="C55" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D55">
         <v>58.6</v>
@@ -3290,10 +3332,10 @@
         <v>0</v>
       </c>
       <c r="F55" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G55" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H55">
         <v>320.2</v>
@@ -3302,19 +3344,19 @@
         <v>11.4</v>
       </c>
       <c r="J55" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="K55">
         <v>8</v>
       </c>
       <c r="L55" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M55" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N55" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O55">
         <v>18.23</v>
@@ -3331,7 +3373,7 @@
         <v>46</v>
       </c>
       <c r="C56" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D56">
         <v>58.3</v>
@@ -3340,10 +3382,10 @@
         <v>0</v>
       </c>
       <c r="F56" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G56" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H56">
         <v>2314.8</v>
@@ -3352,19 +3394,19 @@
         <v>11.7</v>
       </c>
       <c r="J56" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K56">
         <v>2</v>
       </c>
       <c r="L56" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M56" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N56" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O56">
         <v>18.23</v>
@@ -3381,7 +3423,7 @@
         <v>47</v>
       </c>
       <c r="C57" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D57">
         <v>58.3</v>
@@ -3390,10 +3432,10 @@
         <v>0</v>
       </c>
       <c r="F57" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G57" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H57">
         <v>3716.5</v>
@@ -3402,19 +3444,19 @@
         <v>11.7</v>
       </c>
       <c r="J57" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K57">
         <v>2</v>
       </c>
       <c r="L57" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M57" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N57" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O57">
         <v>18.23</v>
@@ -3431,7 +3473,7 @@
         <v>48</v>
       </c>
       <c r="C58" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D58">
         <v>56.7</v>
@@ -3440,10 +3482,10 @@
         <v>0</v>
       </c>
       <c r="F58" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G58" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H58">
         <v>4043</v>
@@ -3452,19 +3494,19 @@
         <v>13.3</v>
       </c>
       <c r="J58" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K58">
         <v>4</v>
       </c>
       <c r="L58" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M58" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N58" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O58">
         <v>18.23</v>
@@ -3481,7 +3523,7 @@
         <v>49</v>
       </c>
       <c r="C59" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D59">
         <v>55.4</v>
@@ -3490,10 +3532,10 @@
         <v>0</v>
       </c>
       <c r="F59" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G59" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H59">
         <v>125.04</v>
@@ -3502,19 +3544,19 @@
         <v>14.6</v>
       </c>
       <c r="J59" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="K59">
         <v>2</v>
       </c>
       <c r="L59" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M59" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N59" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="O59">
         <v>18.23</v>
@@ -3531,7 +3573,7 @@
         <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D60">
         <v>71.5</v>
@@ -3540,10 +3582,10 @@
         <v>0</v>
       </c>
       <c r="F60" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G60" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H60">
         <v>3852.5</v>
@@ -3555,13 +3597,13 @@
         <v>1</v>
       </c>
       <c r="L60" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="M60" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N60" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O60">
         <v>18.08</v>
@@ -3578,7 +3620,7 @@
         <v>22</v>
       </c>
       <c r="C61" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D61">
         <v>69.59999999999999</v>
@@ -3587,10 +3629,10 @@
         <v>0.5</v>
       </c>
       <c r="F61" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G61" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H61">
         <v>1388.5</v>
@@ -3599,19 +3641,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J61" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K61">
         <v>9</v>
       </c>
       <c r="L61" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M61" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N61" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O61">
         <v>18.08</v>
@@ -3628,7 +3670,7 @@
         <v>39</v>
       </c>
       <c r="C62" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D62">
         <v>69.5</v>
@@ -3637,10 +3679,10 @@
         <v>0.5</v>
       </c>
       <c r="F62" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G62" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H62">
         <v>406.1</v>
@@ -3649,19 +3691,19 @@
         <v>0.5</v>
       </c>
       <c r="J62" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K62">
         <v>9</v>
       </c>
       <c r="L62" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M62" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N62" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O62">
         <v>18.08</v>
@@ -3678,7 +3720,7 @@
         <v>41</v>
       </c>
       <c r="C63" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D63">
         <v>69</v>
@@ -3687,10 +3729,10 @@
         <v>0.5</v>
       </c>
       <c r="F63" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G63" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H63">
         <v>213.6</v>
@@ -3699,19 +3741,19 @@
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K63">
         <v>3</v>
       </c>
       <c r="L63" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M63" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N63" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O63">
         <v>18.08</v>
@@ -3728,7 +3770,7 @@
         <v>23</v>
       </c>
       <c r="C64" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D64">
         <v>67.2</v>
@@ -3737,10 +3779,10 @@
         <v>0.5</v>
       </c>
       <c r="F64" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G64" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H64">
         <v>4478</v>
@@ -3749,19 +3791,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J64" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K64">
         <v>9</v>
       </c>
       <c r="L64" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M64" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N64" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O64">
         <v>18.08</v>
@@ -3778,7 +3820,7 @@
         <v>24</v>
       </c>
       <c r="C65" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D65">
         <v>67.2</v>
@@ -3787,10 +3829,10 @@
         <v>6.5</v>
       </c>
       <c r="F65" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G65" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H65">
         <v>1050.05</v>
@@ -3799,19 +3841,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J65" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K65">
         <v>9</v>
       </c>
       <c r="L65" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M65" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N65" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O65">
         <v>18.08</v>
@@ -3828,7 +3870,7 @@
         <v>42</v>
       </c>
       <c r="C66" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D66">
         <v>67.2</v>
@@ -3837,10 +3879,10 @@
         <v>0.5</v>
       </c>
       <c r="F66" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G66" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H66">
         <v>88.59</v>
@@ -3849,19 +3891,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J66" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K66">
         <v>3</v>
       </c>
       <c r="L66" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M66" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N66" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O66">
         <v>18.08</v>
@@ -3878,7 +3920,7 @@
         <v>43</v>
       </c>
       <c r="C67" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D67">
         <v>67.09999999999999</v>
@@ -3887,10 +3929,10 @@
         <v>0.5</v>
       </c>
       <c r="F67" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G67" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H67">
         <v>1291.7</v>
@@ -3899,19 +3941,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J67" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K67">
         <v>3</v>
       </c>
       <c r="L67" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M67" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N67" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O67">
         <v>18.08</v>
@@ -3928,7 +3970,7 @@
         <v>32</v>
       </c>
       <c r="C68" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D68">
         <v>64.59999999999999</v>
@@ -3937,10 +3979,10 @@
         <v>0.5</v>
       </c>
       <c r="F68" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G68" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H68">
         <v>1405.3</v>
@@ -3949,19 +3991,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J68" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K68">
         <v>4</v>
       </c>
       <c r="L68" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M68" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N68" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O68">
         <v>18.08</v>
@@ -3978,7 +4020,7 @@
         <v>44</v>
       </c>
       <c r="C69" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D69">
         <v>63.2</v>
@@ -3987,10 +4029,10 @@
         <v>0.5</v>
       </c>
       <c r="F69" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G69" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H69">
         <v>125.89</v>
@@ -3999,19 +4041,19 @@
         <v>6.799999999999997</v>
       </c>
       <c r="J69" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K69">
         <v>3</v>
       </c>
       <c r="L69" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M69" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N69" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O69">
         <v>18.08</v>
@@ -4028,7 +4070,7 @@
         <v>45</v>
       </c>
       <c r="C70" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D70">
         <v>62.6</v>
@@ -4037,10 +4079,10 @@
         <v>0.5</v>
       </c>
       <c r="F70" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G70" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H70">
         <v>1190.45</v>
@@ -4049,19 +4091,19 @@
         <v>7.399999999999999</v>
       </c>
       <c r="J70" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K70">
         <v>3</v>
       </c>
       <c r="L70" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M70" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N70" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O70">
         <v>18.08</v>
@@ -4078,7 +4120,7 @@
         <v>33</v>
       </c>
       <c r="C71" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D71">
         <v>60.6</v>
@@ -4087,10 +4129,10 @@
         <v>-3.1</v>
       </c>
       <c r="F71" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G71" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H71">
         <v>9700</v>
@@ -4099,19 +4141,19 @@
         <v>9.399999999999999</v>
       </c>
       <c r="J71" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K71">
         <v>9</v>
       </c>
       <c r="L71" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M71" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N71" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O71">
         <v>18.08</v>
@@ -4128,7 +4170,7 @@
         <v>37</v>
       </c>
       <c r="C72" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D72">
         <v>59.1</v>
@@ -4137,10 +4179,10 @@
         <v>0.5</v>
       </c>
       <c r="F72" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G72" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H72">
         <v>319.85</v>
@@ -4149,19 +4191,19 @@
         <v>10.9</v>
       </c>
       <c r="J72" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="K72">
         <v>9</v>
       </c>
       <c r="L72" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M72" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N72" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O72">
         <v>18.08</v>
@@ -4178,7 +4220,7 @@
         <v>46</v>
       </c>
       <c r="C73" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D73">
         <v>58.8</v>
@@ -4187,10 +4229,10 @@
         <v>0.5</v>
       </c>
       <c r="F73" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G73" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H73">
         <v>2305.6</v>
@@ -4199,19 +4241,19 @@
         <v>11.2</v>
       </c>
       <c r="J73" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K73">
         <v>3</v>
       </c>
       <c r="L73" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M73" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N73" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O73">
         <v>18.08</v>
@@ -4228,7 +4270,7 @@
         <v>47</v>
       </c>
       <c r="C74" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D74">
         <v>58.8</v>
@@ -4237,10 +4279,10 @@
         <v>0.5</v>
       </c>
       <c r="F74" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G74" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H74">
         <v>3703.3</v>
@@ -4249,19 +4291,19 @@
         <v>11.2</v>
       </c>
       <c r="J74" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K74">
         <v>3</v>
       </c>
       <c r="L74" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M74" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N74" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O74">
         <v>18.08</v>
@@ -4278,7 +4320,7 @@
         <v>48</v>
       </c>
       <c r="C75" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D75">
         <v>57.2</v>
@@ -4287,10 +4329,10 @@
         <v>0.5</v>
       </c>
       <c r="F75" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G75" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H75">
         <v>4023.5</v>
@@ -4299,19 +4341,19 @@
         <v>12.8</v>
       </c>
       <c r="J75" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K75">
         <v>5</v>
       </c>
       <c r="L75" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M75" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N75" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O75">
         <v>18.08</v>
@@ -4328,7 +4370,7 @@
         <v>50</v>
       </c>
       <c r="C76" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D76">
         <v>56.8</v>
@@ -4337,10 +4379,10 @@
         <v>0</v>
       </c>
       <c r="F76" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G76" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H76">
         <v>7196</v>
@@ -4349,19 +4391,19 @@
         <v>13.2</v>
       </c>
       <c r="J76" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="K76">
         <v>1</v>
       </c>
       <c r="L76" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M76" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N76" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O76">
         <v>18.08</v>
@@ -4378,7 +4420,7 @@
         <v>49</v>
       </c>
       <c r="C77" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D77">
         <v>55.9</v>
@@ -4387,10 +4429,10 @@
         <v>0.5</v>
       </c>
       <c r="F77" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G77" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H77">
         <v>125</v>
@@ -4399,19 +4441,19 @@
         <v>14.1</v>
       </c>
       <c r="J77" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="K77">
         <v>3</v>
       </c>
       <c r="L77" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M77" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N77" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="O77">
         <v>18.08</v>
@@ -4428,7 +4470,7 @@
         <v>51</v>
       </c>
       <c r="C78" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D78">
         <v>73.7</v>
@@ -4437,10 +4479,10 @@
         <v>0</v>
       </c>
       <c r="F78" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G78" t="s">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="H78">
         <v>1449.1</v>
@@ -4452,13 +4494,13 @@
         <v>1</v>
       </c>
       <c r="L78" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="M78" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N78" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O78">
         <v>18.3</v>
@@ -4475,7 +4517,7 @@
         <v>40</v>
       </c>
       <c r="C79" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D79">
         <v>71.5</v>
@@ -4484,10 +4526,10 @@
         <v>0</v>
       </c>
       <c r="F79" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G79" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H79">
         <v>3844.3</v>
@@ -4499,13 +4541,13 @@
         <v>1</v>
       </c>
       <c r="L79" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="M79" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N79" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O79">
         <v>18.3</v>
@@ -4522,7 +4564,7 @@
         <v>52</v>
       </c>
       <c r="C80" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D80">
         <v>71.09999999999999</v>
@@ -4531,10 +4573,10 @@
         <v>0</v>
       </c>
       <c r="F80" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G80" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H80">
         <v>1330.5</v>
@@ -4546,13 +4588,13 @@
         <v>1</v>
       </c>
       <c r="L80" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="M80" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N80" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O80">
         <v>18.3</v>
@@ -4569,7 +4611,7 @@
         <v>39</v>
       </c>
       <c r="C81" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D81">
         <v>70.5</v>
@@ -4578,10 +4620,10 @@
         <v>0</v>
       </c>
       <c r="F81" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G81" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H81">
         <v>405.4</v>
@@ -4593,13 +4635,13 @@
         <v>1</v>
       </c>
       <c r="L81" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="M81" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N81" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O81">
         <v>18.3</v>
@@ -4616,7 +4658,7 @@
         <v>53</v>
       </c>
       <c r="C82" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D82">
         <v>69.59999999999999</v>
@@ -4625,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="F82" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G82" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H82">
         <v>554.7</v>
@@ -4637,19 +4679,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J82" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="K82">
         <v>1</v>
       </c>
       <c r="L82" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M82" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N82" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O82">
         <v>18.3</v>
@@ -4666,7 +4708,7 @@
         <v>41</v>
       </c>
       <c r="C83" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D83">
         <v>69</v>
@@ -4675,10 +4717,10 @@
         <v>0</v>
       </c>
       <c r="F83" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G83" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H83">
         <v>215.65</v>
@@ -4687,19 +4729,19 @@
         <v>1</v>
       </c>
       <c r="J83" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K83">
         <v>4</v>
       </c>
       <c r="L83" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M83" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N83" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O83">
         <v>18.3</v>
@@ -4716,7 +4758,7 @@
         <v>22</v>
       </c>
       <c r="C84" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D84">
         <v>67.2</v>
@@ -4725,10 +4767,10 @@
         <v>-2.4</v>
       </c>
       <c r="F84" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G84" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H84">
         <v>1379.6</v>
@@ -4737,19 +4779,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J84" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K84">
         <v>10</v>
       </c>
       <c r="L84" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M84" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N84" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O84">
         <v>18.3</v>
@@ -4766,7 +4808,7 @@
         <v>23</v>
       </c>
       <c r="C85" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D85">
         <v>67.2</v>
@@ -4775,10 +4817,10 @@
         <v>0</v>
       </c>
       <c r="F85" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G85" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H85">
         <v>4454.6</v>
@@ -4787,19 +4829,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J85" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K85">
         <v>10</v>
       </c>
       <c r="L85" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M85" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N85" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O85">
         <v>18.3</v>
@@ -4816,7 +4858,7 @@
         <v>24</v>
       </c>
       <c r="C86" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D86">
         <v>67.2</v>
@@ -4825,10 +4867,10 @@
         <v>0</v>
       </c>
       <c r="F86" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G86" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H86">
         <v>1044.55</v>
@@ -4837,19 +4879,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J86" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K86">
         <v>10</v>
       </c>
       <c r="L86" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M86" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N86" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O86">
         <v>18.3</v>
@@ -4866,7 +4908,7 @@
         <v>42</v>
       </c>
       <c r="C87" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D87">
         <v>67.2</v>
@@ -4875,10 +4917,10 @@
         <v>0</v>
       </c>
       <c r="F87" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G87" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H87">
         <v>88.59</v>
@@ -4887,19 +4929,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J87" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K87">
         <v>4</v>
       </c>
       <c r="L87" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M87" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N87" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O87">
         <v>18.3</v>
@@ -4916,7 +4958,7 @@
         <v>54</v>
       </c>
       <c r="C88" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D88">
         <v>65.2</v>
@@ -4925,10 +4967,10 @@
         <v>0</v>
       </c>
       <c r="F88" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G88" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H88">
         <v>556.95</v>
@@ -4937,19 +4979,19 @@
         <v>4.799999999999997</v>
       </c>
       <c r="J88" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="K88">
         <v>1</v>
       </c>
       <c r="L88" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M88" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N88" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O88">
         <v>18.3</v>
@@ -4966,7 +5008,7 @@
         <v>32</v>
       </c>
       <c r="C89" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D89">
         <v>64.59999999999999</v>
@@ -4975,10 +5017,10 @@
         <v>0</v>
       </c>
       <c r="F89" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G89" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H89">
         <v>1395.8</v>
@@ -4987,19 +5029,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J89" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K89">
         <v>5</v>
       </c>
       <c r="L89" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M89" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N89" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O89">
         <v>18.3</v>
@@ -5016,7 +5058,7 @@
         <v>55</v>
       </c>
       <c r="C90" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D90">
         <v>64.59999999999999</v>
@@ -5025,10 +5067,10 @@
         <v>0</v>
       </c>
       <c r="F90" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G90" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H90">
         <v>5977</v>
@@ -5037,19 +5079,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J90" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K90">
         <v>1</v>
       </c>
       <c r="L90" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M90" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N90" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O90">
         <v>18.3</v>
@@ -5066,7 +5108,7 @@
         <v>45</v>
       </c>
       <c r="C91" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D91">
         <v>63.6</v>
@@ -5075,10 +5117,10 @@
         <v>1</v>
       </c>
       <c r="F91" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G91" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H91">
         <v>1198.95</v>
@@ -5087,19 +5129,19 @@
         <v>6.399999999999999</v>
       </c>
       <c r="J91" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K91">
         <v>4</v>
       </c>
       <c r="L91" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M91" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N91" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O91">
         <v>18.3</v>
@@ -5116,7 +5158,7 @@
         <v>43</v>
       </c>
       <c r="C92" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D92">
         <v>61.1</v>
@@ -5125,10 +5167,10 @@
         <v>-6</v>
       </c>
       <c r="F92" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G92" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H92">
         <v>1278.6</v>
@@ -5137,19 +5179,19 @@
         <v>8.899999999999999</v>
       </c>
       <c r="J92" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K92">
         <v>4</v>
       </c>
       <c r="L92" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M92" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N92" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O92">
         <v>18.3</v>
@@ -5166,7 +5208,7 @@
         <v>33</v>
       </c>
       <c r="C93" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D93">
         <v>60.6</v>
@@ -5175,10 +5217,10 @@
         <v>0</v>
       </c>
       <c r="F93" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G93" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H93">
         <v>9602</v>
@@ -5187,19 +5229,19 @@
         <v>9.399999999999999</v>
       </c>
       <c r="J93" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K93">
         <v>10</v>
       </c>
       <c r="L93" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M93" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N93" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O93">
         <v>18.3</v>
@@ -5216,7 +5258,7 @@
         <v>37</v>
       </c>
       <c r="C94" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D94">
         <v>59.1</v>
@@ -5225,10 +5267,10 @@
         <v>0</v>
       </c>
       <c r="F94" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G94" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H94">
         <v>319.75</v>
@@ -5237,19 +5279,19 @@
         <v>10.9</v>
       </c>
       <c r="J94" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="K94">
         <v>10</v>
       </c>
       <c r="L94" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M94" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N94" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O94">
         <v>18.3</v>
@@ -5266,7 +5308,7 @@
         <v>46</v>
       </c>
       <c r="C95" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D95">
         <v>58.8</v>
@@ -5275,10 +5317,10 @@
         <v>0</v>
       </c>
       <c r="F95" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G95" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H95">
         <v>2307.9</v>
@@ -5287,19 +5329,19 @@
         <v>11.2</v>
       </c>
       <c r="J95" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K95">
         <v>4</v>
       </c>
       <c r="L95" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M95" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N95" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O95">
         <v>18.3</v>
@@ -5316,7 +5358,7 @@
         <v>48</v>
       </c>
       <c r="C96" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D96">
         <v>57.2</v>
@@ -5325,10 +5367,10 @@
         <v>0</v>
       </c>
       <c r="F96" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G96" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H96">
         <v>4021.1</v>
@@ -5337,19 +5379,19 @@
         <v>12.8</v>
       </c>
       <c r="J96" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K96">
         <v>6</v>
       </c>
       <c r="L96" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M96" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N96" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O96">
         <v>18.3</v>
@@ -5366,7 +5408,7 @@
         <v>50</v>
       </c>
       <c r="C97" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D97">
         <v>56.8</v>
@@ -5375,10 +5417,10 @@
         <v>0</v>
       </c>
       <c r="F97" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G97" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H97">
         <v>7230</v>
@@ -5387,19 +5429,19 @@
         <v>13.2</v>
       </c>
       <c r="J97" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="K97">
         <v>2</v>
       </c>
       <c r="L97" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M97" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N97" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O97">
         <v>18.3</v>
@@ -5409,26 +5451,26 @@
       </c>
     </row>
     <row r="98" spans="1:16">
-      <c r="A98" t="s">
-        <v>16</v>
+      <c r="A98">
+        <v>20260422</v>
       </c>
       <c r="B98" t="s">
         <v>40</v>
       </c>
       <c r="C98" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D98">
         <v>70.3</v>
       </c>
-      <c r="E98" t="s">
-        <v>58</v>
+      <c r="E98">
+        <v>0</v>
       </c>
       <c r="F98" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G98" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H98">
         <v>3844.3</v>
@@ -5440,13 +5482,13 @@
         <v>1</v>
       </c>
       <c r="L98" t="s">
-        <v>16</v>
+        <v>84</v>
       </c>
       <c r="M98" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N98" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O98">
         <v>18.3</v>
@@ -5456,26 +5498,26 @@
       </c>
     </row>
     <row r="99" spans="1:16">
-      <c r="A99" t="s">
-        <v>16</v>
+      <c r="A99">
+        <v>20260422</v>
       </c>
       <c r="B99" t="s">
         <v>52</v>
       </c>
       <c r="C99" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D99">
         <v>69.90000000000001</v>
       </c>
-      <c r="E99" t="s">
-        <v>58</v>
+      <c r="E99">
+        <v>0</v>
       </c>
       <c r="F99" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G99" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H99">
         <v>1330.5</v>
@@ -5484,19 +5526,19 @@
         <v>0.09999999999999432</v>
       </c>
       <c r="J99" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="K99">
         <v>1</v>
       </c>
       <c r="L99" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M99" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N99" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O99">
         <v>18.3</v>
@@ -5506,26 +5548,26 @@
       </c>
     </row>
     <row r="100" spans="1:16">
-      <c r="A100" t="s">
-        <v>16</v>
+      <c r="A100">
+        <v>20260422</v>
       </c>
       <c r="B100" t="s">
         <v>39</v>
       </c>
       <c r="C100" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D100">
         <v>69.3</v>
       </c>
-      <c r="E100" t="s">
-        <v>58</v>
+      <c r="E100">
+        <v>0</v>
       </c>
       <c r="F100" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G100" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H100">
         <v>405.4</v>
@@ -5534,19 +5576,19 @@
         <v>0.7000000000000028</v>
       </c>
       <c r="J100" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K100">
         <v>1</v>
       </c>
       <c r="L100" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M100" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N100" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O100">
         <v>18.3</v>
@@ -5556,26 +5598,26 @@
       </c>
     </row>
     <row r="101" spans="1:16">
-      <c r="A101" t="s">
-        <v>16</v>
+      <c r="A101">
+        <v>20260422</v>
       </c>
       <c r="B101" t="s">
         <v>53</v>
       </c>
       <c r="C101" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D101">
         <v>68.40000000000001</v>
       </c>
-      <c r="E101" t="s">
-        <v>59</v>
+      <c r="E101">
+        <v>-1.2</v>
       </c>
       <c r="F101" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G101" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H101">
         <v>554.7</v>
@@ -5584,19 +5626,19 @@
         <v>1.599999999999994</v>
       </c>
       <c r="J101" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="K101">
         <v>2</v>
       </c>
       <c r="L101" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M101" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N101" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O101">
         <v>18.3</v>
@@ -5606,26 +5648,26 @@
       </c>
     </row>
     <row r="102" spans="1:16">
-      <c r="A102" t="s">
-        <v>16</v>
+      <c r="A102">
+        <v>20260422</v>
       </c>
       <c r="B102" t="s">
         <v>41</v>
       </c>
       <c r="C102" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D102">
         <v>67.8</v>
       </c>
-      <c r="E102" t="s">
-        <v>59</v>
+      <c r="E102">
+        <v>-1.2</v>
       </c>
       <c r="F102" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G102" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H102">
         <v>215.65</v>
@@ -5634,19 +5676,19 @@
         <v>2.200000000000003</v>
       </c>
       <c r="J102" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K102">
         <v>5</v>
       </c>
       <c r="L102" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M102" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N102" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O102">
         <v>18.3</v>
@@ -5656,26 +5698,26 @@
       </c>
     </row>
     <row r="103" spans="1:16">
-      <c r="A103" t="s">
-        <v>16</v>
+      <c r="A103">
+        <v>20260422</v>
       </c>
       <c r="B103" t="s">
         <v>22</v>
       </c>
       <c r="C103" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D103">
         <v>66</v>
       </c>
-      <c r="E103" t="s">
-        <v>59</v>
+      <c r="E103">
+        <v>-1.2</v>
       </c>
       <c r="F103" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G103" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H103">
         <v>1379.6</v>
@@ -5684,19 +5726,19 @@
         <v>4</v>
       </c>
       <c r="J103" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K103">
         <v>11</v>
       </c>
       <c r="L103" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M103" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N103" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O103">
         <v>18.3</v>
@@ -5706,26 +5748,26 @@
       </c>
     </row>
     <row r="104" spans="1:16">
-      <c r="A104" t="s">
-        <v>16</v>
+      <c r="A104">
+        <v>20260422</v>
       </c>
       <c r="B104" t="s">
         <v>23</v>
       </c>
       <c r="C104" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D104">
         <v>66</v>
       </c>
-      <c r="E104" t="s">
-        <v>59</v>
+      <c r="E104">
+        <v>-1.2</v>
       </c>
       <c r="F104" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G104" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H104">
         <v>4454.6</v>
@@ -5734,19 +5776,19 @@
         <v>4</v>
       </c>
       <c r="J104" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K104">
         <v>11</v>
       </c>
       <c r="L104" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M104" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N104" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O104">
         <v>18.3</v>
@@ -5756,26 +5798,26 @@
       </c>
     </row>
     <row r="105" spans="1:16">
-      <c r="A105" t="s">
-        <v>16</v>
+      <c r="A105">
+        <v>20260422</v>
       </c>
       <c r="B105" t="s">
         <v>24</v>
       </c>
       <c r="C105" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D105">
         <v>66</v>
       </c>
-      <c r="E105" t="s">
-        <v>59</v>
+      <c r="E105">
+        <v>-1.2</v>
       </c>
       <c r="F105" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G105" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H105">
         <v>1044.55</v>
@@ -5784,19 +5826,19 @@
         <v>4</v>
       </c>
       <c r="J105" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K105">
         <v>11</v>
       </c>
       <c r="L105" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M105" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N105" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O105">
         <v>18.3</v>
@@ -5806,26 +5848,26 @@
       </c>
     </row>
     <row r="106" spans="1:16">
-      <c r="A106" t="s">
-        <v>16</v>
+      <c r="A106">
+        <v>20260422</v>
       </c>
       <c r="B106" t="s">
         <v>42</v>
       </c>
       <c r="C106" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D106">
         <v>66</v>
       </c>
-      <c r="E106" t="s">
-        <v>59</v>
+      <c r="E106">
+        <v>-1.2</v>
       </c>
       <c r="F106" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G106" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H106">
         <v>88.59</v>
@@ -5834,19 +5876,19 @@
         <v>4</v>
       </c>
       <c r="J106" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K106">
         <v>5</v>
       </c>
       <c r="L106" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M106" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N106" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O106">
         <v>18.3</v>
@@ -5856,26 +5898,26 @@
       </c>
     </row>
     <row r="107" spans="1:16">
-      <c r="A107" t="s">
-        <v>16</v>
+      <c r="A107">
+        <v>20260422</v>
       </c>
       <c r="B107" t="s">
         <v>54</v>
       </c>
       <c r="C107" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D107">
         <v>64</v>
       </c>
-      <c r="E107" t="s">
-        <v>59</v>
+      <c r="E107">
+        <v>-1.2</v>
       </c>
       <c r="F107" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G107" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H107">
         <v>556.95</v>
@@ -5884,19 +5926,19 @@
         <v>6</v>
       </c>
       <c r="J107" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="K107">
         <v>2</v>
       </c>
       <c r="L107" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M107" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N107" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O107">
         <v>18.3</v>
@@ -5906,26 +5948,26 @@
       </c>
     </row>
     <row r="108" spans="1:16">
-      <c r="A108" t="s">
-        <v>16</v>
+      <c r="A108">
+        <v>20260422</v>
       </c>
       <c r="B108" t="s">
         <v>32</v>
       </c>
       <c r="C108" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D108">
         <v>63.4</v>
       </c>
-      <c r="E108" t="s">
-        <v>59</v>
+      <c r="E108">
+        <v>-1.2</v>
       </c>
       <c r="F108" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G108" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H108">
         <v>1395.8</v>
@@ -5934,19 +5976,19 @@
         <v>6.600000000000001</v>
       </c>
       <c r="J108" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K108">
         <v>6</v>
       </c>
       <c r="L108" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M108" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N108" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O108">
         <v>18.3</v>
@@ -5956,26 +5998,26 @@
       </c>
     </row>
     <row r="109" spans="1:16">
-      <c r="A109" t="s">
-        <v>16</v>
+      <c r="A109">
+        <v>20260422</v>
       </c>
       <c r="B109" t="s">
         <v>55</v>
       </c>
       <c r="C109" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D109">
         <v>63.4</v>
       </c>
-      <c r="E109" t="s">
-        <v>59</v>
+      <c r="E109">
+        <v>-1.2</v>
       </c>
       <c r="F109" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G109" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H109">
         <v>5977</v>
@@ -5984,19 +6026,19 @@
         <v>6.600000000000001</v>
       </c>
       <c r="J109" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K109">
         <v>2</v>
       </c>
       <c r="L109" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M109" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N109" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O109">
         <v>18.3</v>
@@ -6006,26 +6048,26 @@
       </c>
     </row>
     <row r="110" spans="1:16">
-      <c r="A110" t="s">
-        <v>16</v>
+      <c r="A110">
+        <v>20260422</v>
       </c>
       <c r="B110" t="s">
         <v>45</v>
       </c>
       <c r="C110" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D110">
         <v>62.4</v>
       </c>
-      <c r="E110" t="s">
-        <v>59</v>
+      <c r="E110">
+        <v>-1.2</v>
       </c>
       <c r="F110" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G110" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H110">
         <v>1198.95</v>
@@ -6034,19 +6076,19 @@
         <v>7.600000000000001</v>
       </c>
       <c r="J110" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K110">
         <v>5</v>
       </c>
       <c r="L110" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M110" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N110" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O110">
         <v>18.3</v>
@@ -6056,26 +6098,26 @@
       </c>
     </row>
     <row r="111" spans="1:16">
-      <c r="A111" t="s">
-        <v>16</v>
+      <c r="A111">
+        <v>20260422</v>
       </c>
       <c r="B111" t="s">
         <v>43</v>
       </c>
       <c r="C111" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D111">
         <v>59.9</v>
       </c>
-      <c r="E111" t="s">
-        <v>59</v>
+      <c r="E111">
+        <v>-1.2</v>
       </c>
       <c r="F111" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G111" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H111">
         <v>1278.6</v>
@@ -6084,19 +6126,19 @@
         <v>10.1</v>
       </c>
       <c r="J111" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K111">
         <v>5</v>
       </c>
       <c r="L111" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M111" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N111" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O111">
         <v>18.3</v>
@@ -6106,26 +6148,26 @@
       </c>
     </row>
     <row r="112" spans="1:16">
-      <c r="A112" t="s">
-        <v>16</v>
+      <c r="A112">
+        <v>20260422</v>
       </c>
       <c r="B112" t="s">
         <v>33</v>
       </c>
       <c r="C112" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D112">
         <v>59.4</v>
       </c>
-      <c r="E112" t="s">
-        <v>59</v>
+      <c r="E112">
+        <v>-1.2</v>
       </c>
       <c r="F112" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G112" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H112">
         <v>9602</v>
@@ -6134,19 +6176,19 @@
         <v>10.6</v>
       </c>
       <c r="J112" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="K112">
         <v>11</v>
       </c>
       <c r="L112" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M112" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N112" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O112">
         <v>18.3</v>
@@ -6156,26 +6198,26 @@
       </c>
     </row>
     <row r="113" spans="1:16">
-      <c r="A113" t="s">
-        <v>16</v>
+      <c r="A113">
+        <v>20260422</v>
       </c>
       <c r="B113" t="s">
         <v>37</v>
       </c>
       <c r="C113" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D113">
         <v>57.9</v>
       </c>
-      <c r="E113" t="s">
-        <v>59</v>
+      <c r="E113">
+        <v>-1.2</v>
       </c>
       <c r="F113" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G113" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H113">
         <v>319.75</v>
@@ -6184,19 +6226,19 @@
         <v>12.1</v>
       </c>
       <c r="J113" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="K113">
         <v>11</v>
       </c>
       <c r="L113" t="s">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="M113" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N113" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O113">
         <v>18.3</v>
@@ -6206,26 +6248,26 @@
       </c>
     </row>
     <row r="114" spans="1:16">
-      <c r="A114" t="s">
-        <v>16</v>
+      <c r="A114">
+        <v>20260422</v>
       </c>
       <c r="B114" t="s">
         <v>46</v>
       </c>
       <c r="C114" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D114">
         <v>57.6</v>
       </c>
-      <c r="E114" t="s">
-        <v>59</v>
+      <c r="E114">
+        <v>-1.2</v>
       </c>
       <c r="F114" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G114" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H114">
         <v>2307.9</v>
@@ -6234,19 +6276,19 @@
         <v>12.4</v>
       </c>
       <c r="J114" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K114">
         <v>5</v>
       </c>
       <c r="L114" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M114" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N114" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O114">
         <v>18.3</v>
@@ -6256,26 +6298,26 @@
       </c>
     </row>
     <row r="115" spans="1:16">
-      <c r="A115" t="s">
-        <v>16</v>
+      <c r="A115">
+        <v>20260422</v>
       </c>
       <c r="B115" t="s">
         <v>48</v>
       </c>
       <c r="C115" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D115">
         <v>56</v>
       </c>
-      <c r="E115" t="s">
-        <v>59</v>
+      <c r="E115">
+        <v>-1.2</v>
       </c>
       <c r="F115" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G115" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H115">
         <v>4021.1</v>
@@ -6284,19 +6326,19 @@
         <v>14</v>
       </c>
       <c r="J115" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="K115">
         <v>7</v>
       </c>
       <c r="L115" t="s">
-        <v>71</v>
+        <v>82</v>
       </c>
       <c r="M115" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N115" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O115">
         <v>18.3</v>
@@ -6306,26 +6348,26 @@
       </c>
     </row>
     <row r="116" spans="1:16">
-      <c r="A116" t="s">
-        <v>16</v>
+      <c r="A116">
+        <v>20260422</v>
       </c>
       <c r="B116" t="s">
         <v>50</v>
       </c>
       <c r="C116" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D116">
         <v>55.6</v>
       </c>
-      <c r="E116" t="s">
-        <v>59</v>
+      <c r="E116">
+        <v>-1.2</v>
       </c>
       <c r="F116" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="G116" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="H116">
         <v>7230</v>
@@ -6334,25 +6376,825 @@
         <v>14.4</v>
       </c>
       <c r="J116" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="K116">
         <v>3</v>
       </c>
       <c r="L116" t="s">
-        <v>73</v>
+        <v>85</v>
       </c>
       <c r="M116" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="N116" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="O116">
         <v>18.3</v>
       </c>
       <c r="P116">
         <v>45</v>
+      </c>
+    </row>
+    <row r="117" spans="1:16">
+      <c r="A117" t="s">
+        <v>16</v>
+      </c>
+      <c r="B117" t="s">
+        <v>43</v>
+      </c>
+      <c r="C117" t="s">
+        <v>58</v>
+      </c>
+      <c r="D117">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="E117" t="s">
+        <v>59</v>
+      </c>
+      <c r="F117" t="s">
+        <v>70</v>
+      </c>
+      <c r="G117" t="s">
+        <v>71</v>
+      </c>
+      <c r="H117">
+        <v>1263</v>
+      </c>
+      <c r="I117">
+        <v>3.599999999999994</v>
+      </c>
+      <c r="J117" t="s">
+        <v>73</v>
+      </c>
+      <c r="K117">
+        <v>6</v>
+      </c>
+      <c r="L117" t="s">
+        <v>85</v>
+      </c>
+      <c r="M117" t="s">
+        <v>87</v>
+      </c>
+      <c r="N117" t="s">
+        <v>92</v>
+      </c>
+      <c r="O117">
+        <v>18.7</v>
+      </c>
+      <c r="P117">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="118" spans="1:16">
+      <c r="A118" t="s">
+        <v>16</v>
+      </c>
+      <c r="B118" t="s">
+        <v>49</v>
+      </c>
+      <c r="C118" t="s">
+        <v>58</v>
+      </c>
+      <c r="D118">
+        <v>64.5</v>
+      </c>
+      <c r="E118" t="s">
+        <v>60</v>
+      </c>
+      <c r="F118" t="s">
+        <v>70</v>
+      </c>
+      <c r="G118" t="s">
+        <v>71</v>
+      </c>
+      <c r="H118">
+        <v>123.95</v>
+      </c>
+      <c r="I118">
+        <v>5.5</v>
+      </c>
+      <c r="J118" t="s">
+        <v>74</v>
+      </c>
+      <c r="K118">
+        <v>1</v>
+      </c>
+      <c r="L118" t="s">
+        <v>86</v>
+      </c>
+      <c r="M118" t="s">
+        <v>87</v>
+      </c>
+      <c r="N118" t="s">
+        <v>92</v>
+      </c>
+      <c r="O118">
+        <v>18.7</v>
+      </c>
+      <c r="P118">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="119" spans="1:16">
+      <c r="A119" t="s">
+        <v>16</v>
+      </c>
+      <c r="B119" t="s">
+        <v>22</v>
+      </c>
+      <c r="C119" t="s">
+        <v>58</v>
+      </c>
+      <c r="D119">
+        <v>64</v>
+      </c>
+      <c r="E119" t="s">
+        <v>61</v>
+      </c>
+      <c r="F119" t="s">
+        <v>70</v>
+      </c>
+      <c r="G119" t="s">
+        <v>71</v>
+      </c>
+      <c r="H119">
+        <v>1371.6</v>
+      </c>
+      <c r="I119">
+        <v>6</v>
+      </c>
+      <c r="J119" t="s">
+        <v>73</v>
+      </c>
+      <c r="K119">
+        <v>12</v>
+      </c>
+      <c r="L119" t="s">
+        <v>83</v>
+      </c>
+      <c r="M119" t="s">
+        <v>87</v>
+      </c>
+      <c r="N119" t="s">
+        <v>92</v>
+      </c>
+      <c r="O119">
+        <v>18.7</v>
+      </c>
+      <c r="P119">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="120" spans="1:16">
+      <c r="A120" t="s">
+        <v>16</v>
+      </c>
+      <c r="B120" t="s">
+        <v>23</v>
+      </c>
+      <c r="C120" t="s">
+        <v>58</v>
+      </c>
+      <c r="D120">
+        <v>64</v>
+      </c>
+      <c r="E120" t="s">
+        <v>61</v>
+      </c>
+      <c r="F120" t="s">
+        <v>70</v>
+      </c>
+      <c r="G120" t="s">
+        <v>71</v>
+      </c>
+      <c r="H120">
+        <v>4460</v>
+      </c>
+      <c r="I120">
+        <v>6</v>
+      </c>
+      <c r="J120" t="s">
+        <v>73</v>
+      </c>
+      <c r="K120">
+        <v>12</v>
+      </c>
+      <c r="L120" t="s">
+        <v>83</v>
+      </c>
+      <c r="M120" t="s">
+        <v>87</v>
+      </c>
+      <c r="N120" t="s">
+        <v>92</v>
+      </c>
+      <c r="O120">
+        <v>18.7</v>
+      </c>
+      <c r="P120">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="121" spans="1:16">
+      <c r="A121" t="s">
+        <v>16</v>
+      </c>
+      <c r="B121" t="s">
+        <v>46</v>
+      </c>
+      <c r="C121" t="s">
+        <v>58</v>
+      </c>
+      <c r="D121">
+        <v>64</v>
+      </c>
+      <c r="E121" t="s">
+        <v>62</v>
+      </c>
+      <c r="F121" t="s">
+        <v>70</v>
+      </c>
+      <c r="G121" t="s">
+        <v>71</v>
+      </c>
+      <c r="H121">
+        <v>2358.2</v>
+      </c>
+      <c r="I121">
+        <v>6</v>
+      </c>
+      <c r="J121" t="s">
+        <v>73</v>
+      </c>
+      <c r="K121">
+        <v>6</v>
+      </c>
+      <c r="L121" t="s">
+        <v>85</v>
+      </c>
+      <c r="M121" t="s">
+        <v>87</v>
+      </c>
+      <c r="N121" t="s">
+        <v>92</v>
+      </c>
+      <c r="O121">
+        <v>18.7</v>
+      </c>
+      <c r="P121">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="122" spans="1:16">
+      <c r="A122" t="s">
+        <v>16</v>
+      </c>
+      <c r="B122" t="s">
+        <v>39</v>
+      </c>
+      <c r="C122" t="s">
+        <v>58</v>
+      </c>
+      <c r="D122">
+        <v>63.9</v>
+      </c>
+      <c r="E122" t="s">
+        <v>63</v>
+      </c>
+      <c r="F122" t="s">
+        <v>70</v>
+      </c>
+      <c r="G122" t="s">
+        <v>71</v>
+      </c>
+      <c r="H122">
+        <v>402.65</v>
+      </c>
+      <c r="I122">
+        <v>6.100000000000001</v>
+      </c>
+      <c r="J122" t="s">
+        <v>73</v>
+      </c>
+      <c r="K122">
+        <v>2</v>
+      </c>
+      <c r="L122" t="s">
+        <v>85</v>
+      </c>
+      <c r="M122" t="s">
+        <v>87</v>
+      </c>
+      <c r="N122" t="s">
+        <v>92</v>
+      </c>
+      <c r="O122">
+        <v>18.7</v>
+      </c>
+      <c r="P122">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="123" spans="1:16">
+      <c r="A123" t="s">
+        <v>16</v>
+      </c>
+      <c r="B123" t="s">
+        <v>40</v>
+      </c>
+      <c r="C123" t="s">
+        <v>58</v>
+      </c>
+      <c r="D123">
+        <v>63.9</v>
+      </c>
+      <c r="E123" t="s">
+        <v>60</v>
+      </c>
+      <c r="F123" t="s">
+        <v>70</v>
+      </c>
+      <c r="G123" t="s">
+        <v>71</v>
+      </c>
+      <c r="H123">
+        <v>3858.9</v>
+      </c>
+      <c r="I123">
+        <v>6.100000000000001</v>
+      </c>
+      <c r="J123" t="s">
+        <v>73</v>
+      </c>
+      <c r="K123">
+        <v>1</v>
+      </c>
+      <c r="L123" t="s">
+        <v>86</v>
+      </c>
+      <c r="M123" t="s">
+        <v>87</v>
+      </c>
+      <c r="N123" t="s">
+        <v>92</v>
+      </c>
+      <c r="O123">
+        <v>18.7</v>
+      </c>
+      <c r="P123">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="124" spans="1:16">
+      <c r="A124" t="s">
+        <v>16</v>
+      </c>
+      <c r="B124" t="s">
+        <v>37</v>
+      </c>
+      <c r="C124" t="s">
+        <v>58</v>
+      </c>
+      <c r="D124">
+        <v>61.9</v>
+      </c>
+      <c r="E124" t="s">
+        <v>64</v>
+      </c>
+      <c r="F124" t="s">
+        <v>70</v>
+      </c>
+      <c r="G124" t="s">
+        <v>71</v>
+      </c>
+      <c r="H124">
+        <v>320.55</v>
+      </c>
+      <c r="I124">
+        <v>8.100000000000001</v>
+      </c>
+      <c r="J124" t="s">
+        <v>77</v>
+      </c>
+      <c r="K124">
+        <v>12</v>
+      </c>
+      <c r="L124" t="s">
+        <v>83</v>
+      </c>
+      <c r="M124" t="s">
+        <v>87</v>
+      </c>
+      <c r="N124" t="s">
+        <v>92</v>
+      </c>
+      <c r="O124">
+        <v>18.7</v>
+      </c>
+      <c r="P124">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="125" spans="1:16">
+      <c r="A125" t="s">
+        <v>16</v>
+      </c>
+      <c r="B125" t="s">
+        <v>41</v>
+      </c>
+      <c r="C125" t="s">
+        <v>58</v>
+      </c>
+      <c r="D125">
+        <v>61.4</v>
+      </c>
+      <c r="E125" t="s">
+        <v>65</v>
+      </c>
+      <c r="F125" t="s">
+        <v>70</v>
+      </c>
+      <c r="G125" t="s">
+        <v>71</v>
+      </c>
+      <c r="H125">
+        <v>214.68</v>
+      </c>
+      <c r="I125">
+        <v>8.600000000000001</v>
+      </c>
+      <c r="J125" t="s">
+        <v>75</v>
+      </c>
+      <c r="K125">
+        <v>6</v>
+      </c>
+      <c r="L125" t="s">
+        <v>85</v>
+      </c>
+      <c r="M125" t="s">
+        <v>87</v>
+      </c>
+      <c r="N125" t="s">
+        <v>92</v>
+      </c>
+      <c r="O125">
+        <v>18.7</v>
+      </c>
+      <c r="P125">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="126" spans="1:16">
+      <c r="A126" t="s">
+        <v>16</v>
+      </c>
+      <c r="B126" t="s">
+        <v>24</v>
+      </c>
+      <c r="C126" t="s">
+        <v>58</v>
+      </c>
+      <c r="D126">
+        <v>61</v>
+      </c>
+      <c r="E126" t="s">
+        <v>66</v>
+      </c>
+      <c r="F126" t="s">
+        <v>70</v>
+      </c>
+      <c r="G126" t="s">
+        <v>71</v>
+      </c>
+      <c r="H126">
+        <v>1019.75</v>
+      </c>
+      <c r="I126">
+        <v>9</v>
+      </c>
+      <c r="J126" t="s">
+        <v>73</v>
+      </c>
+      <c r="K126">
+        <v>12</v>
+      </c>
+      <c r="L126" t="s">
+        <v>83</v>
+      </c>
+      <c r="M126" t="s">
+        <v>87</v>
+      </c>
+      <c r="N126" t="s">
+        <v>92</v>
+      </c>
+      <c r="O126">
+        <v>18.7</v>
+      </c>
+      <c r="P126">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="127" spans="1:16">
+      <c r="A127" t="s">
+        <v>16</v>
+      </c>
+      <c r="B127" t="s">
+        <v>42</v>
+      </c>
+      <c r="C127" t="s">
+        <v>58</v>
+      </c>
+      <c r="D127">
+        <v>61</v>
+      </c>
+      <c r="E127" t="s">
+        <v>66</v>
+      </c>
+      <c r="F127" t="s">
+        <v>70</v>
+      </c>
+      <c r="G127" t="s">
+        <v>71</v>
+      </c>
+      <c r="H127">
+        <v>86.98</v>
+      </c>
+      <c r="I127">
+        <v>9</v>
+      </c>
+      <c r="J127" t="s">
+        <v>73</v>
+      </c>
+      <c r="K127">
+        <v>6</v>
+      </c>
+      <c r="L127" t="s">
+        <v>85</v>
+      </c>
+      <c r="M127" t="s">
+        <v>87</v>
+      </c>
+      <c r="N127" t="s">
+        <v>92</v>
+      </c>
+      <c r="O127">
+        <v>18.7</v>
+      </c>
+      <c r="P127">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="128" spans="1:16">
+      <c r="A128" t="s">
+        <v>16</v>
+      </c>
+      <c r="B128" t="s">
+        <v>44</v>
+      </c>
+      <c r="C128" t="s">
+        <v>58</v>
+      </c>
+      <c r="D128">
+        <v>60</v>
+      </c>
+      <c r="E128" t="s">
+        <v>60</v>
+      </c>
+      <c r="F128" t="s">
+        <v>70</v>
+      </c>
+      <c r="G128" t="s">
+        <v>71</v>
+      </c>
+      <c r="H128">
+        <v>125.61</v>
+      </c>
+      <c r="I128">
+        <v>10</v>
+      </c>
+      <c r="J128" t="s">
+        <v>73</v>
+      </c>
+      <c r="K128">
+        <v>1</v>
+      </c>
+      <c r="L128" t="s">
+        <v>86</v>
+      </c>
+      <c r="M128" t="s">
+        <v>87</v>
+      </c>
+      <c r="N128" t="s">
+        <v>92</v>
+      </c>
+      <c r="O128">
+        <v>18.7</v>
+      </c>
+      <c r="P128">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="129" spans="1:16">
+      <c r="A129" t="s">
+        <v>16</v>
+      </c>
+      <c r="B129" t="s">
+        <v>32</v>
+      </c>
+      <c r="C129" t="s">
+        <v>58</v>
+      </c>
+      <c r="D129">
+        <v>59.4</v>
+      </c>
+      <c r="E129" t="s">
+        <v>67</v>
+      </c>
+      <c r="F129" t="s">
+        <v>70</v>
+      </c>
+      <c r="G129" t="s">
+        <v>71</v>
+      </c>
+      <c r="H129">
+        <v>1404.6</v>
+      </c>
+      <c r="I129">
+        <v>10.6</v>
+      </c>
+      <c r="J129" t="s">
+        <v>75</v>
+      </c>
+      <c r="K129">
+        <v>7</v>
+      </c>
+      <c r="L129" t="s">
+        <v>82</v>
+      </c>
+      <c r="M129" t="s">
+        <v>87</v>
+      </c>
+      <c r="N129" t="s">
+        <v>92</v>
+      </c>
+      <c r="O129">
+        <v>18.7</v>
+      </c>
+      <c r="P129">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="130" spans="1:16">
+      <c r="A130" t="s">
+        <v>16</v>
+      </c>
+      <c r="B130" t="s">
+        <v>45</v>
+      </c>
+      <c r="C130" t="s">
+        <v>58</v>
+      </c>
+      <c r="D130">
+        <v>59.4</v>
+      </c>
+      <c r="E130" t="s">
+        <v>68</v>
+      </c>
+      <c r="F130" t="s">
+        <v>70</v>
+      </c>
+      <c r="G130" t="s">
+        <v>71</v>
+      </c>
+      <c r="H130">
+        <v>1217.2</v>
+      </c>
+      <c r="I130">
+        <v>10.6</v>
+      </c>
+      <c r="J130" t="s">
+        <v>75</v>
+      </c>
+      <c r="K130">
+        <v>6</v>
+      </c>
+      <c r="L130" t="s">
+        <v>85</v>
+      </c>
+      <c r="M130" t="s">
+        <v>87</v>
+      </c>
+      <c r="N130" t="s">
+        <v>92</v>
+      </c>
+      <c r="O130">
+        <v>18.7</v>
+      </c>
+      <c r="P130">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="131" spans="1:16">
+      <c r="A131" t="s">
+        <v>16</v>
+      </c>
+      <c r="B131" t="s">
+        <v>56</v>
+      </c>
+      <c r="C131" t="s">
+        <v>58</v>
+      </c>
+      <c r="D131">
+        <v>57.3</v>
+      </c>
+      <c r="E131" t="s">
+        <v>60</v>
+      </c>
+      <c r="F131" t="s">
+        <v>70</v>
+      </c>
+      <c r="G131" t="s">
+        <v>71</v>
+      </c>
+      <c r="H131">
+        <v>445.5</v>
+      </c>
+      <c r="I131">
+        <v>12.7</v>
+      </c>
+      <c r="J131" t="s">
+        <v>80</v>
+      </c>
+      <c r="K131">
+        <v>1</v>
+      </c>
+      <c r="L131" t="s">
+        <v>86</v>
+      </c>
+      <c r="M131" t="s">
+        <v>87</v>
+      </c>
+      <c r="N131" t="s">
+        <v>92</v>
+      </c>
+      <c r="O131">
+        <v>18.7</v>
+      </c>
+      <c r="P131">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="132" spans="1:16">
+      <c r="A132" t="s">
+        <v>16</v>
+      </c>
+      <c r="B132" t="s">
+        <v>33</v>
+      </c>
+      <c r="C132" t="s">
+        <v>58</v>
+      </c>
+      <c r="D132">
+        <v>55.6</v>
+      </c>
+      <c r="E132" t="s">
+        <v>69</v>
+      </c>
+      <c r="F132" t="s">
+        <v>70</v>
+      </c>
+      <c r="G132" t="s">
+        <v>71</v>
+      </c>
+      <c r="H132">
+        <v>9519</v>
+      </c>
+      <c r="I132">
+        <v>14.4</v>
+      </c>
+      <c r="J132" t="s">
+        <v>73</v>
+      </c>
+      <c r="K132">
+        <v>12</v>
+      </c>
+      <c r="L132" t="s">
+        <v>83</v>
+      </c>
+      <c r="M132" t="s">
+        <v>87</v>
+      </c>
+      <c r="N132" t="s">
+        <v>92</v>
+      </c>
+      <c r="O132">
+        <v>18.7</v>
+      </c>
+      <c r="P132">
+        <v>334</v>
       </c>
     </row>
   </sheetData>

--- a/reports/watchlist_history.xlsx
+++ b/reports/watchlist_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="85">
   <si>
     <t>Date</t>
   </si>
@@ -193,37 +193,10 @@
     <t>WATCH</t>
   </si>
   <si>
-    <t>+6.5</t>
-  </si>
-  <si>
     <t>+0.0</t>
   </si>
   <si>
-    <t>-2.0</t>
-  </si>
-  <si>
-    <t>+6.4</t>
-  </si>
-  <si>
-    <t>-5.4</t>
-  </si>
-  <si>
-    <t>+4.0</t>
-  </si>
-  <si>
-    <t>-6.4</t>
-  </si>
-  <si>
-    <t>-5.0</t>
-  </si>
-  <si>
-    <t>-4.0</t>
-  </si>
-  <si>
-    <t>-3.0</t>
-  </si>
-  <si>
-    <t>-3.8</t>
+    <t>-6.0</t>
   </si>
   <si>
     <t>Stage 2 — Uptrend ✓</t>
@@ -293,6 +266,9 @@
   </si>
   <si>
     <t>-3.7%</t>
+  </si>
+  <si>
+    <t>-3.8%</t>
   </si>
 </sst>
 </file>
@@ -624,7 +600,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P132"/>
+  <dimension ref="A1:P148"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -694,10 +670,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G2" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H2">
         <v>11714</v>
@@ -709,13 +685,13 @@
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="M2" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N2" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O2">
         <v>17.53</v>
@@ -741,10 +717,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G3" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H3">
         <v>514.05</v>
@@ -756,13 +732,13 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="M3" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N3" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O3">
         <v>17.53</v>
@@ -788,10 +764,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G4" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H4">
         <v>1621.5</v>
@@ -803,13 +779,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>81</v>
+        <v>72</v>
       </c>
       <c r="M4" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N4" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O4">
         <v>17.53</v>
@@ -835,10 +811,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G5" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H5">
         <v>191.38</v>
@@ -847,19 +823,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J5" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M5" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N5" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O5">
         <v>17.53</v>
@@ -885,10 +861,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G6" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H6">
         <v>1318.1</v>
@@ -897,19 +873,19 @@
         <v>0.9000000000000057</v>
       </c>
       <c r="J6" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M6" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N6" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O6">
         <v>17.53</v>
@@ -935,10 +911,10 @@
         <v>-0.5</v>
       </c>
       <c r="F7" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G7" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H7">
         <v>1377.7</v>
@@ -947,19 +923,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J7" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K7">
         <v>6</v>
       </c>
       <c r="L7" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M7" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N7" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O7">
         <v>17.53</v>
@@ -985,10 +961,10 @@
         <v>-0.5</v>
       </c>
       <c r="F8" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G8" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H8">
         <v>4479.7</v>
@@ -997,19 +973,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J8" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K8">
         <v>6</v>
       </c>
       <c r="L8" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M8" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N8" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O8">
         <v>17.53</v>
@@ -1035,10 +1011,10 @@
         <v>-0.5</v>
       </c>
       <c r="F9" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G9" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H9">
         <v>1045.3</v>
@@ -1047,19 +1023,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J9" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K9">
         <v>6</v>
       </c>
       <c r="L9" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M9" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N9" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O9">
         <v>17.53</v>
@@ -1085,10 +1061,10 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G10" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H10">
         <v>1055.65</v>
@@ -1097,19 +1073,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J10" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M10" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N10" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O10">
         <v>17.53</v>
@@ -1135,10 +1111,10 @@
         <v>-0.5</v>
       </c>
       <c r="F11" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G11" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H11">
         <v>1045.3</v>
@@ -1147,19 +1123,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J11" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K11">
         <v>6</v>
       </c>
       <c r="L11" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M11" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N11" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O11">
         <v>17.53</v>
@@ -1185,10 +1161,10 @@
         <v>-0.5</v>
       </c>
       <c r="F12" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G12" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H12">
         <v>4479.7</v>
@@ -1197,19 +1173,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J12" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K12">
         <v>6</v>
       </c>
       <c r="L12" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M12" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N12" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O12">
         <v>17.53</v>
@@ -1235,10 +1211,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G13" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H13">
         <v>581.3</v>
@@ -1247,19 +1223,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J13" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K13">
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M13" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N13" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O13">
         <v>17.53</v>
@@ -1285,10 +1261,10 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G14" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H14">
         <v>458.9</v>
@@ -1297,19 +1273,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J14" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M14" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N14" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O14">
         <v>17.53</v>
@@ -1335,10 +1311,10 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G15" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H15">
         <v>196.02</v>
@@ -1347,19 +1323,19 @@
         <v>4.400000000000006</v>
       </c>
       <c r="J15" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M15" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N15" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O15">
         <v>17.53</v>
@@ -1385,10 +1361,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G16" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H16">
         <v>4172.9</v>
@@ -1397,19 +1373,19 @@
         <v>5</v>
       </c>
       <c r="J16" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K16">
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M16" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N16" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O16">
         <v>17.53</v>
@@ -1435,10 +1411,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G17" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H17">
         <v>6373.5</v>
@@ -1447,19 +1423,19 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J17" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="K17">
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M17" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N17" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O17">
         <v>17.53</v>
@@ -1485,10 +1461,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H18">
         <v>1113.1</v>
@@ -1497,19 +1473,19 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J18" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M18" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N18" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O18">
         <v>17.53</v>
@@ -1535,10 +1511,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G19" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H19">
         <v>1379.9</v>
@@ -1547,19 +1523,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J19" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K19">
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M19" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N19" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O19">
         <v>17.53</v>
@@ -1585,10 +1561,10 @@
         <v>-0.5</v>
       </c>
       <c r="F20" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G20" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H20">
         <v>9793</v>
@@ -1597,19 +1573,19 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J20" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K20">
         <v>6</v>
       </c>
       <c r="L20" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M20" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N20" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O20">
         <v>17.53</v>
@@ -1635,10 +1611,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G21" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H21">
         <v>7955.5</v>
@@ -1647,19 +1623,19 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J21" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K21">
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M21" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N21" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O21">
         <v>17.53</v>
@@ -1685,10 +1661,10 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G22" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H22">
         <v>1037.85</v>
@@ -1697,19 +1673,19 @@
         <v>6.399999999999999</v>
       </c>
       <c r="J22" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K22">
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M22" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N22" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O22">
         <v>17.53</v>
@@ -1735,10 +1711,10 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G23" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H23">
         <v>979.1</v>
@@ -1747,19 +1723,19 @@
         <v>8.399999999999999</v>
       </c>
       <c r="J23" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K23">
         <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M23" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N23" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O23">
         <v>17.53</v>
@@ -1785,10 +1761,10 @@
         <v>-0.5</v>
       </c>
       <c r="F24" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G24" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H24">
         <v>319.35</v>
@@ -1797,19 +1773,19 @@
         <v>8.5</v>
       </c>
       <c r="J24" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="K24">
         <v>6</v>
       </c>
       <c r="L24" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M24" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N24" t="s">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="O24">
         <v>17.53</v>
@@ -1835,10 +1811,10 @@
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G25" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H25">
         <v>767.65</v>
@@ -1850,13 +1826,13 @@
         <v>1</v>
       </c>
       <c r="L25" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="M25" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N25" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O25">
         <v>18.27</v>
@@ -1882,10 +1858,10 @@
         <v>7.8</v>
       </c>
       <c r="F26" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G26" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H26">
         <v>404.1</v>
@@ -1894,19 +1870,19 @@
         <v>1</v>
       </c>
       <c r="J26" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K26">
         <v>7</v>
       </c>
       <c r="L26" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M26" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N26" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O26">
         <v>18.27</v>
@@ -1932,10 +1908,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G27" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H27">
         <v>3847</v>
@@ -1944,19 +1920,19 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K27">
         <v>1</v>
       </c>
       <c r="L27" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M27" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N27" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O27">
         <v>18.27</v>
@@ -1982,10 +1958,10 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G28" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H28">
         <v>211.75</v>
@@ -1994,19 +1970,19 @@
         <v>2.5</v>
       </c>
       <c r="J28" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K28">
         <v>1</v>
       </c>
       <c r="L28" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M28" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N28" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O28">
         <v>18.27</v>
@@ -2032,10 +2008,10 @@
         <v>-0.5</v>
       </c>
       <c r="F29" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G29" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H29">
         <v>1381.5</v>
@@ -2044,19 +2020,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J29" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K29">
         <v>7</v>
       </c>
       <c r="L29" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M29" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N29" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O29">
         <v>18.27</v>
@@ -2082,10 +2058,10 @@
         <v>-0.5</v>
       </c>
       <c r="F30" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G30" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H30">
         <v>4483</v>
@@ -2094,19 +2070,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J30" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K30">
         <v>7</v>
       </c>
       <c r="L30" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M30" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N30" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O30">
         <v>18.27</v>
@@ -2132,10 +2108,10 @@
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G31" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H31">
         <v>89.05</v>
@@ -2144,19 +2120,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J31" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K31">
         <v>1</v>
       </c>
       <c r="L31" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M31" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N31" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O31">
         <v>18.27</v>
@@ -2182,10 +2158,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G32" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H32">
         <v>1291.1</v>
@@ -2194,19 +2170,19 @@
         <v>3.400000000000006</v>
       </c>
       <c r="J32" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K32">
         <v>1</v>
       </c>
       <c r="L32" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M32" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N32" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O32">
         <v>18.27</v>
@@ -2232,10 +2208,10 @@
         <v>-0.5</v>
       </c>
       <c r="F33" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G33" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H33">
         <v>1414.6</v>
@@ -2244,19 +2220,19 @@
         <v>5.900000000000006</v>
       </c>
       <c r="J33" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K33">
         <v>2</v>
       </c>
       <c r="L33" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M33" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N33" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O33">
         <v>18.27</v>
@@ -2282,10 +2258,10 @@
         <v>-0.5</v>
       </c>
       <c r="F34" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G34" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H34">
         <v>9760</v>
@@ -2294,19 +2270,19 @@
         <v>6.299999999999997</v>
       </c>
       <c r="J34" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K34">
         <v>7</v>
       </c>
       <c r="L34" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M34" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N34" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O34">
         <v>18.27</v>
@@ -2332,10 +2308,10 @@
         <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G35" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H35">
         <v>125.85</v>
@@ -2344,19 +2320,19 @@
         <v>7.299999999999997</v>
       </c>
       <c r="J35" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K35">
         <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M35" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N35" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O35">
         <v>18.27</v>
@@ -2382,10 +2358,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G36" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H36">
         <v>1171.95</v>
@@ -2394,19 +2370,19 @@
         <v>7.899999999999999</v>
       </c>
       <c r="J36" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K36">
         <v>1</v>
       </c>
       <c r="L36" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M36" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N36" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O36">
         <v>18.27</v>
@@ -2432,10 +2408,10 @@
         <v>-6.5</v>
       </c>
       <c r="F37" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G37" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H37">
         <v>1038.1</v>
@@ -2444,19 +2420,19 @@
         <v>9.299999999999997</v>
       </c>
       <c r="J37" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K37">
         <v>7</v>
       </c>
       <c r="L37" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M37" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N37" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O37">
         <v>18.27</v>
@@ -2482,10 +2458,10 @@
         <v>-2.9</v>
       </c>
       <c r="F38" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G38" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H38">
         <v>319.6</v>
@@ -2494,19 +2470,19 @@
         <v>11.4</v>
       </c>
       <c r="J38" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="K38">
         <v>7</v>
       </c>
       <c r="L38" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M38" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N38" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O38">
         <v>18.27</v>
@@ -2532,10 +2508,10 @@
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G39" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H39">
         <v>2314.1</v>
@@ -2544,19 +2520,19 @@
         <v>11.7</v>
       </c>
       <c r="J39" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K39">
         <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M39" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N39" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O39">
         <v>18.27</v>
@@ -2582,10 +2558,10 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G40" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H40">
         <v>3723.6</v>
@@ -2594,19 +2570,19 @@
         <v>11.7</v>
       </c>
       <c r="J40" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K40">
         <v>1</v>
       </c>
       <c r="L40" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M40" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N40" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O40">
         <v>18.27</v>
@@ -2632,10 +2608,10 @@
         <v>-0.5</v>
       </c>
       <c r="F41" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G41" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H41">
         <v>4049.2</v>
@@ -2644,19 +2620,19 @@
         <v>13.3</v>
       </c>
       <c r="J41" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K41">
         <v>3</v>
       </c>
       <c r="L41" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M41" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N41" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O41">
         <v>18.27</v>
@@ -2682,10 +2658,10 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G42" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H42">
         <v>124.98</v>
@@ -2694,19 +2670,19 @@
         <v>14.6</v>
       </c>
       <c r="J42" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="K42">
         <v>1</v>
       </c>
       <c r="L42" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M42" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N42" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O42">
         <v>18.27</v>
@@ -2732,10 +2708,10 @@
         <v>2.4</v>
       </c>
       <c r="F43" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G43" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H43">
         <v>1388.7</v>
@@ -2744,19 +2720,19 @@
         <v>0.9000000000000057</v>
       </c>
       <c r="J43" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K43">
         <v>8</v>
       </c>
       <c r="L43" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M43" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N43" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O43">
         <v>18.23</v>
@@ -2782,10 +2758,10 @@
         <v>0</v>
       </c>
       <c r="F44" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G44" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H44">
         <v>404.8</v>
@@ -2794,19 +2770,19 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K44">
         <v>8</v>
       </c>
       <c r="L44" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M44" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N44" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O44">
         <v>18.23</v>
@@ -2832,10 +2808,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G45" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H45">
         <v>3845.7</v>
@@ -2844,19 +2820,19 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K45">
         <v>2</v>
       </c>
       <c r="L45" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M45" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N45" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O45">
         <v>18.23</v>
@@ -2882,10 +2858,10 @@
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G46" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H46">
         <v>213.03</v>
@@ -2894,19 +2870,19 @@
         <v>1.5</v>
       </c>
       <c r="J46" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K46">
         <v>2</v>
       </c>
       <c r="L46" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M46" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N46" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O46">
         <v>18.23</v>
@@ -2932,10 +2908,10 @@
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G47" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H47">
         <v>4477</v>
@@ -2944,19 +2920,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J47" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K47">
         <v>8</v>
       </c>
       <c r="L47" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M47" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N47" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O47">
         <v>18.23</v>
@@ -2982,10 +2958,10 @@
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G48" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H48">
         <v>88.98999999999999</v>
@@ -2994,19 +2970,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J48" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K48">
         <v>2</v>
       </c>
       <c r="L48" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M48" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N48" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O48">
         <v>18.23</v>
@@ -3032,10 +3008,10 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G49" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H49">
         <v>1288.9</v>
@@ -3044,19 +3020,19 @@
         <v>3.400000000000006</v>
       </c>
       <c r="J49" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K49">
         <v>2</v>
       </c>
       <c r="L49" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M49" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N49" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O49">
         <v>18.23</v>
@@ -3082,10 +3058,10 @@
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G50" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H50">
         <v>1419</v>
@@ -3094,19 +3070,19 @@
         <v>5.900000000000006</v>
       </c>
       <c r="J50" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K50">
         <v>3</v>
       </c>
       <c r="L50" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M50" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N50" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O50">
         <v>18.23</v>
@@ -3132,10 +3108,10 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G51" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H51">
         <v>9758</v>
@@ -3144,19 +3120,19 @@
         <v>6.299999999999997</v>
       </c>
       <c r="J51" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K51">
         <v>8</v>
       </c>
       <c r="L51" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M51" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N51" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O51">
         <v>18.23</v>
@@ -3182,10 +3158,10 @@
         <v>0</v>
       </c>
       <c r="F52" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G52" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H52">
         <v>125.98</v>
@@ -3194,19 +3170,19 @@
         <v>7.299999999999997</v>
       </c>
       <c r="J52" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K52">
         <v>2</v>
       </c>
       <c r="L52" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M52" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N52" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O52">
         <v>18.23</v>
@@ -3232,10 +3208,10 @@
         <v>0</v>
       </c>
       <c r="F53" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G53" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H53">
         <v>1182</v>
@@ -3244,19 +3220,19 @@
         <v>7.899999999999999</v>
       </c>
       <c r="J53" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K53">
         <v>2</v>
       </c>
       <c r="L53" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M53" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N53" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O53">
         <v>18.23</v>
@@ -3282,10 +3258,10 @@
         <v>0</v>
       </c>
       <c r="F54" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G54" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H54">
         <v>1040</v>
@@ -3294,19 +3270,19 @@
         <v>9.299999999999997</v>
       </c>
       <c r="J54" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K54">
         <v>8</v>
       </c>
       <c r="L54" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M54" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N54" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O54">
         <v>18.23</v>
@@ -3332,10 +3308,10 @@
         <v>0</v>
       </c>
       <c r="F55" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G55" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H55">
         <v>320.2</v>
@@ -3344,19 +3320,19 @@
         <v>11.4</v>
       </c>
       <c r="J55" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="K55">
         <v>8</v>
       </c>
       <c r="L55" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M55" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N55" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O55">
         <v>18.23</v>
@@ -3382,10 +3358,10 @@
         <v>0</v>
       </c>
       <c r="F56" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G56" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H56">
         <v>2314.8</v>
@@ -3394,19 +3370,19 @@
         <v>11.7</v>
       </c>
       <c r="J56" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K56">
         <v>2</v>
       </c>
       <c r="L56" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M56" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N56" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O56">
         <v>18.23</v>
@@ -3432,10 +3408,10 @@
         <v>0</v>
       </c>
       <c r="F57" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G57" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H57">
         <v>3716.5</v>
@@ -3444,19 +3420,19 @@
         <v>11.7</v>
       </c>
       <c r="J57" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K57">
         <v>2</v>
       </c>
       <c r="L57" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M57" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N57" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O57">
         <v>18.23</v>
@@ -3482,10 +3458,10 @@
         <v>0</v>
       </c>
       <c r="F58" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G58" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H58">
         <v>4043</v>
@@ -3494,19 +3470,19 @@
         <v>13.3</v>
       </c>
       <c r="J58" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K58">
         <v>4</v>
       </c>
       <c r="L58" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M58" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N58" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O58">
         <v>18.23</v>
@@ -3532,10 +3508,10 @@
         <v>0</v>
       </c>
       <c r="F59" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G59" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H59">
         <v>125.04</v>
@@ -3544,19 +3520,19 @@
         <v>14.6</v>
       </c>
       <c r="J59" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="K59">
         <v>2</v>
       </c>
       <c r="L59" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M59" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N59" t="s">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="O59">
         <v>18.23</v>
@@ -3582,10 +3558,10 @@
         <v>0</v>
       </c>
       <c r="F60" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G60" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H60">
         <v>3852.5</v>
@@ -3597,13 +3573,13 @@
         <v>1</v>
       </c>
       <c r="L60" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="M60" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N60" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="O60">
         <v>18.08</v>
@@ -3629,10 +3605,10 @@
         <v>0.5</v>
       </c>
       <c r="F61" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G61" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H61">
         <v>1388.5</v>
@@ -3641,19 +3617,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J61" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K61">
         <v>9</v>
       </c>
       <c r="L61" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M61" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N61" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="O61">
         <v>18.08</v>
@@ -3679,10 +3655,10 @@
         <v>0.5</v>
       </c>
       <c r="F62" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G62" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H62">
         <v>406.1</v>
@@ -3691,19 +3667,19 @@
         <v>0.5</v>
       </c>
       <c r="J62" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K62">
         <v>9</v>
       </c>
       <c r="L62" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M62" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N62" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="O62">
         <v>18.08</v>
@@ -3729,10 +3705,10 @@
         <v>0.5</v>
       </c>
       <c r="F63" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G63" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H63">
         <v>213.6</v>
@@ -3741,19 +3717,19 @@
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K63">
         <v>3</v>
       </c>
       <c r="L63" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M63" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N63" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="O63">
         <v>18.08</v>
@@ -3779,10 +3755,10 @@
         <v>0.5</v>
       </c>
       <c r="F64" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G64" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H64">
         <v>4478</v>
@@ -3791,19 +3767,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J64" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K64">
         <v>9</v>
       </c>
       <c r="L64" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M64" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N64" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="O64">
         <v>18.08</v>
@@ -3829,10 +3805,10 @@
         <v>6.5</v>
       </c>
       <c r="F65" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G65" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H65">
         <v>1050.05</v>
@@ -3841,19 +3817,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J65" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K65">
         <v>9</v>
       </c>
       <c r="L65" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M65" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N65" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="O65">
         <v>18.08</v>
@@ -3879,10 +3855,10 @@
         <v>0.5</v>
       </c>
       <c r="F66" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G66" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H66">
         <v>88.59</v>
@@ -3891,19 +3867,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J66" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K66">
         <v>3</v>
       </c>
       <c r="L66" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M66" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N66" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="O66">
         <v>18.08</v>
@@ -3929,10 +3905,10 @@
         <v>0.5</v>
       </c>
       <c r="F67" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G67" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H67">
         <v>1291.7</v>
@@ -3941,19 +3917,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J67" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K67">
         <v>3</v>
       </c>
       <c r="L67" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M67" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N67" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="O67">
         <v>18.08</v>
@@ -3979,10 +3955,10 @@
         <v>0.5</v>
       </c>
       <c r="F68" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G68" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H68">
         <v>1405.3</v>
@@ -3991,19 +3967,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J68" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K68">
         <v>4</v>
       </c>
       <c r="L68" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M68" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N68" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="O68">
         <v>18.08</v>
@@ -4029,10 +4005,10 @@
         <v>0.5</v>
       </c>
       <c r="F69" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G69" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H69">
         <v>125.89</v>
@@ -4041,19 +4017,19 @@
         <v>6.799999999999997</v>
       </c>
       <c r="J69" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K69">
         <v>3</v>
       </c>
       <c r="L69" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M69" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N69" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="O69">
         <v>18.08</v>
@@ -4079,10 +4055,10 @@
         <v>0.5</v>
       </c>
       <c r="F70" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G70" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H70">
         <v>1190.45</v>
@@ -4091,19 +4067,19 @@
         <v>7.399999999999999</v>
       </c>
       <c r="J70" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K70">
         <v>3</v>
       </c>
       <c r="L70" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M70" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N70" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="O70">
         <v>18.08</v>
@@ -4129,10 +4105,10 @@
         <v>-3.1</v>
       </c>
       <c r="F71" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G71" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H71">
         <v>9700</v>
@@ -4141,19 +4117,19 @@
         <v>9.399999999999999</v>
       </c>
       <c r="J71" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K71">
         <v>9</v>
       </c>
       <c r="L71" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M71" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N71" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="O71">
         <v>18.08</v>
@@ -4179,10 +4155,10 @@
         <v>0.5</v>
       </c>
       <c r="F72" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G72" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H72">
         <v>319.85</v>
@@ -4191,19 +4167,19 @@
         <v>10.9</v>
       </c>
       <c r="J72" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="K72">
         <v>9</v>
       </c>
       <c r="L72" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M72" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N72" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="O72">
         <v>18.08</v>
@@ -4229,10 +4205,10 @@
         <v>0.5</v>
       </c>
       <c r="F73" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G73" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H73">
         <v>2305.6</v>
@@ -4241,19 +4217,19 @@
         <v>11.2</v>
       </c>
       <c r="J73" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K73">
         <v>3</v>
       </c>
       <c r="L73" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M73" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N73" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="O73">
         <v>18.08</v>
@@ -4279,10 +4255,10 @@
         <v>0.5</v>
       </c>
       <c r="F74" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G74" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H74">
         <v>3703.3</v>
@@ -4291,19 +4267,19 @@
         <v>11.2</v>
       </c>
       <c r="J74" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K74">
         <v>3</v>
       </c>
       <c r="L74" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M74" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N74" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="O74">
         <v>18.08</v>
@@ -4329,10 +4305,10 @@
         <v>0.5</v>
       </c>
       <c r="F75" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G75" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H75">
         <v>4023.5</v>
@@ -4341,19 +4317,19 @@
         <v>12.8</v>
       </c>
       <c r="J75" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K75">
         <v>5</v>
       </c>
       <c r="L75" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M75" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N75" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="O75">
         <v>18.08</v>
@@ -4379,10 +4355,10 @@
         <v>0</v>
       </c>
       <c r="F76" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G76" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H76">
         <v>7196</v>
@@ -4391,19 +4367,19 @@
         <v>13.2</v>
       </c>
       <c r="J76" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="K76">
         <v>1</v>
       </c>
       <c r="L76" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M76" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N76" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="O76">
         <v>18.08</v>
@@ -4429,10 +4405,10 @@
         <v>0.5</v>
       </c>
       <c r="F77" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G77" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H77">
         <v>125</v>
@@ -4441,19 +4417,19 @@
         <v>14.1</v>
       </c>
       <c r="J77" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="K77">
         <v>3</v>
       </c>
       <c r="L77" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M77" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N77" t="s">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="O77">
         <v>18.08</v>
@@ -4479,10 +4455,10 @@
         <v>0</v>
       </c>
       <c r="F78" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G78" t="s">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="H78">
         <v>1449.1</v>
@@ -4494,13 +4470,13 @@
         <v>1</v>
       </c>
       <c r="L78" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="M78" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N78" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O78">
         <v>18.3</v>
@@ -4526,10 +4502,10 @@
         <v>0</v>
       </c>
       <c r="F79" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G79" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H79">
         <v>3844.3</v>
@@ -4541,13 +4517,13 @@
         <v>1</v>
       </c>
       <c r="L79" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="M79" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N79" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O79">
         <v>18.3</v>
@@ -4573,10 +4549,10 @@
         <v>0</v>
       </c>
       <c r="F80" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G80" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H80">
         <v>1330.5</v>
@@ -4588,13 +4564,13 @@
         <v>1</v>
       </c>
       <c r="L80" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="M80" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N80" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O80">
         <v>18.3</v>
@@ -4620,10 +4596,10 @@
         <v>0</v>
       </c>
       <c r="F81" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G81" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H81">
         <v>405.4</v>
@@ -4635,13 +4611,13 @@
         <v>1</v>
       </c>
       <c r="L81" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="M81" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N81" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O81">
         <v>18.3</v>
@@ -4667,10 +4643,10 @@
         <v>0</v>
       </c>
       <c r="F82" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G82" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H82">
         <v>554.7</v>
@@ -4679,19 +4655,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J82" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="K82">
         <v>1</v>
       </c>
       <c r="L82" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M82" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N82" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O82">
         <v>18.3</v>
@@ -4717,10 +4693,10 @@
         <v>0</v>
       </c>
       <c r="F83" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G83" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H83">
         <v>215.65</v>
@@ -4729,19 +4705,19 @@
         <v>1</v>
       </c>
       <c r="J83" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K83">
         <v>4</v>
       </c>
       <c r="L83" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M83" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N83" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O83">
         <v>18.3</v>
@@ -4767,10 +4743,10 @@
         <v>-2.4</v>
       </c>
       <c r="F84" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G84" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H84">
         <v>1379.6</v>
@@ -4779,19 +4755,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J84" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K84">
         <v>10</v>
       </c>
       <c r="L84" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M84" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N84" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O84">
         <v>18.3</v>
@@ -4817,10 +4793,10 @@
         <v>0</v>
       </c>
       <c r="F85" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G85" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H85">
         <v>4454.6</v>
@@ -4829,19 +4805,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J85" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K85">
         <v>10</v>
       </c>
       <c r="L85" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M85" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N85" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O85">
         <v>18.3</v>
@@ -4867,10 +4843,10 @@
         <v>0</v>
       </c>
       <c r="F86" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G86" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H86">
         <v>1044.55</v>
@@ -4879,19 +4855,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J86" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K86">
         <v>10</v>
       </c>
       <c r="L86" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M86" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N86" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O86">
         <v>18.3</v>
@@ -4917,10 +4893,10 @@
         <v>0</v>
       </c>
       <c r="F87" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G87" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H87">
         <v>88.59</v>
@@ -4929,19 +4905,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J87" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K87">
         <v>4</v>
       </c>
       <c r="L87" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M87" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N87" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O87">
         <v>18.3</v>
@@ -4967,10 +4943,10 @@
         <v>0</v>
       </c>
       <c r="F88" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G88" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H88">
         <v>556.95</v>
@@ -4979,19 +4955,19 @@
         <v>4.799999999999997</v>
       </c>
       <c r="J88" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="K88">
         <v>1</v>
       </c>
       <c r="L88" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M88" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N88" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O88">
         <v>18.3</v>
@@ -5017,10 +4993,10 @@
         <v>0</v>
       </c>
       <c r="F89" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G89" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H89">
         <v>1395.8</v>
@@ -5029,19 +5005,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J89" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K89">
         <v>5</v>
       </c>
       <c r="L89" t="s">
+        <v>73</v>
+      </c>
+      <c r="M89" t="s">
+        <v>78</v>
+      </c>
+      <c r="N89" t="s">
         <v>82</v>
-      </c>
-      <c r="M89" t="s">
-        <v>87</v>
-      </c>
-      <c r="N89" t="s">
-        <v>91</v>
       </c>
       <c r="O89">
         <v>18.3</v>
@@ -5067,10 +5043,10 @@
         <v>0</v>
       </c>
       <c r="F90" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G90" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H90">
         <v>5977</v>
@@ -5079,19 +5055,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J90" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K90">
         <v>1</v>
       </c>
       <c r="L90" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M90" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N90" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O90">
         <v>18.3</v>
@@ -5117,10 +5093,10 @@
         <v>1</v>
       </c>
       <c r="F91" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G91" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H91">
         <v>1198.95</v>
@@ -5129,19 +5105,19 @@
         <v>6.399999999999999</v>
       </c>
       <c r="J91" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K91">
         <v>4</v>
       </c>
       <c r="L91" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M91" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N91" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O91">
         <v>18.3</v>
@@ -5167,10 +5143,10 @@
         <v>-6</v>
       </c>
       <c r="F92" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G92" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H92">
         <v>1278.6</v>
@@ -5179,19 +5155,19 @@
         <v>8.899999999999999</v>
       </c>
       <c r="J92" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K92">
         <v>4</v>
       </c>
       <c r="L92" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M92" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N92" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O92">
         <v>18.3</v>
@@ -5217,10 +5193,10 @@
         <v>0</v>
       </c>
       <c r="F93" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G93" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H93">
         <v>9602</v>
@@ -5229,19 +5205,19 @@
         <v>9.399999999999999</v>
       </c>
       <c r="J93" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K93">
         <v>10</v>
       </c>
       <c r="L93" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M93" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N93" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O93">
         <v>18.3</v>
@@ -5267,10 +5243,10 @@
         <v>0</v>
       </c>
       <c r="F94" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G94" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H94">
         <v>319.75</v>
@@ -5279,19 +5255,19 @@
         <v>10.9</v>
       </c>
       <c r="J94" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="K94">
         <v>10</v>
       </c>
       <c r="L94" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M94" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N94" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O94">
         <v>18.3</v>
@@ -5317,10 +5293,10 @@
         <v>0</v>
       </c>
       <c r="F95" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G95" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H95">
         <v>2307.9</v>
@@ -5329,19 +5305,19 @@
         <v>11.2</v>
       </c>
       <c r="J95" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K95">
         <v>4</v>
       </c>
       <c r="L95" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M95" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N95" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O95">
         <v>18.3</v>
@@ -5367,10 +5343,10 @@
         <v>0</v>
       </c>
       <c r="F96" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G96" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H96">
         <v>4021.1</v>
@@ -5379,19 +5355,19 @@
         <v>12.8</v>
       </c>
       <c r="J96" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K96">
         <v>6</v>
       </c>
       <c r="L96" t="s">
+        <v>73</v>
+      </c>
+      <c r="M96" t="s">
+        <v>78</v>
+      </c>
+      <c r="N96" t="s">
         <v>82</v>
-      </c>
-      <c r="M96" t="s">
-        <v>87</v>
-      </c>
-      <c r="N96" t="s">
-        <v>91</v>
       </c>
       <c r="O96">
         <v>18.3</v>
@@ -5417,10 +5393,10 @@
         <v>0</v>
       </c>
       <c r="F97" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G97" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H97">
         <v>7230</v>
@@ -5429,19 +5405,19 @@
         <v>13.2</v>
       </c>
       <c r="J97" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="K97">
         <v>2</v>
       </c>
       <c r="L97" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M97" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N97" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O97">
         <v>18.3</v>
@@ -5467,10 +5443,10 @@
         <v>0</v>
       </c>
       <c r="F98" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G98" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H98">
         <v>3844.3</v>
@@ -5482,13 +5458,13 @@
         <v>1</v>
       </c>
       <c r="L98" t="s">
-        <v>84</v>
+        <v>75</v>
       </c>
       <c r="M98" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N98" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O98">
         <v>18.3</v>
@@ -5514,10 +5490,10 @@
         <v>0</v>
       </c>
       <c r="F99" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G99" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H99">
         <v>1330.5</v>
@@ -5526,19 +5502,19 @@
         <v>0.09999999999999432</v>
       </c>
       <c r="J99" t="s">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="K99">
         <v>1</v>
       </c>
       <c r="L99" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M99" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N99" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O99">
         <v>18.3</v>
@@ -5564,10 +5540,10 @@
         <v>0</v>
       </c>
       <c r="F100" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G100" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H100">
         <v>405.4</v>
@@ -5576,19 +5552,19 @@
         <v>0.7000000000000028</v>
       </c>
       <c r="J100" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K100">
         <v>1</v>
       </c>
       <c r="L100" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M100" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N100" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O100">
         <v>18.3</v>
@@ -5614,10 +5590,10 @@
         <v>-1.2</v>
       </c>
       <c r="F101" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G101" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H101">
         <v>554.7</v>
@@ -5626,19 +5602,19 @@
         <v>1.599999999999994</v>
       </c>
       <c r="J101" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="K101">
         <v>2</v>
       </c>
       <c r="L101" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M101" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N101" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O101">
         <v>18.3</v>
@@ -5664,10 +5640,10 @@
         <v>-1.2</v>
       </c>
       <c r="F102" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G102" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H102">
         <v>215.65</v>
@@ -5676,19 +5652,19 @@
         <v>2.200000000000003</v>
       </c>
       <c r="J102" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K102">
         <v>5</v>
       </c>
       <c r="L102" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M102" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N102" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O102">
         <v>18.3</v>
@@ -5714,10 +5690,10 @@
         <v>-1.2</v>
       </c>
       <c r="F103" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G103" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H103">
         <v>1379.6</v>
@@ -5726,19 +5702,19 @@
         <v>4</v>
       </c>
       <c r="J103" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K103">
         <v>11</v>
       </c>
       <c r="L103" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M103" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N103" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O103">
         <v>18.3</v>
@@ -5764,10 +5740,10 @@
         <v>-1.2</v>
       </c>
       <c r="F104" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G104" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H104">
         <v>4454.6</v>
@@ -5776,19 +5752,19 @@
         <v>4</v>
       </c>
       <c r="J104" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K104">
         <v>11</v>
       </c>
       <c r="L104" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M104" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N104" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O104">
         <v>18.3</v>
@@ -5814,10 +5790,10 @@
         <v>-1.2</v>
       </c>
       <c r="F105" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G105" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H105">
         <v>1044.55</v>
@@ -5826,19 +5802,19 @@
         <v>4</v>
       </c>
       <c r="J105" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K105">
         <v>11</v>
       </c>
       <c r="L105" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M105" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N105" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O105">
         <v>18.3</v>
@@ -5864,10 +5840,10 @@
         <v>-1.2</v>
       </c>
       <c r="F106" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G106" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H106">
         <v>88.59</v>
@@ -5876,19 +5852,19 @@
         <v>4</v>
       </c>
       <c r="J106" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K106">
         <v>5</v>
       </c>
       <c r="L106" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M106" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N106" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O106">
         <v>18.3</v>
@@ -5914,10 +5890,10 @@
         <v>-1.2</v>
       </c>
       <c r="F107" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G107" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H107">
         <v>556.95</v>
@@ -5926,19 +5902,19 @@
         <v>6</v>
       </c>
       <c r="J107" t="s">
-        <v>79</v>
+        <v>70</v>
       </c>
       <c r="K107">
         <v>2</v>
       </c>
       <c r="L107" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M107" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N107" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O107">
         <v>18.3</v>
@@ -5964,10 +5940,10 @@
         <v>-1.2</v>
       </c>
       <c r="F108" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G108" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H108">
         <v>1395.8</v>
@@ -5976,19 +5952,19 @@
         <v>6.600000000000001</v>
       </c>
       <c r="J108" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K108">
         <v>6</v>
       </c>
       <c r="L108" t="s">
+        <v>73</v>
+      </c>
+      <c r="M108" t="s">
+        <v>78</v>
+      </c>
+      <c r="N108" t="s">
         <v>82</v>
-      </c>
-      <c r="M108" t="s">
-        <v>87</v>
-      </c>
-      <c r="N108" t="s">
-        <v>91</v>
       </c>
       <c r="O108">
         <v>18.3</v>
@@ -6014,10 +5990,10 @@
         <v>-1.2</v>
       </c>
       <c r="F109" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G109" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H109">
         <v>5977</v>
@@ -6026,19 +6002,19 @@
         <v>6.600000000000001</v>
       </c>
       <c r="J109" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K109">
         <v>2</v>
       </c>
       <c r="L109" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M109" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N109" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O109">
         <v>18.3</v>
@@ -6064,10 +6040,10 @@
         <v>-1.2</v>
       </c>
       <c r="F110" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G110" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H110">
         <v>1198.95</v>
@@ -6076,19 +6052,19 @@
         <v>7.600000000000001</v>
       </c>
       <c r="J110" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K110">
         <v>5</v>
       </c>
       <c r="L110" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M110" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N110" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O110">
         <v>18.3</v>
@@ -6114,10 +6090,10 @@
         <v>-1.2</v>
       </c>
       <c r="F111" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G111" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H111">
         <v>1278.6</v>
@@ -6126,19 +6102,19 @@
         <v>10.1</v>
       </c>
       <c r="J111" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K111">
         <v>5</v>
       </c>
       <c r="L111" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M111" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N111" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O111">
         <v>18.3</v>
@@ -6164,10 +6140,10 @@
         <v>-1.2</v>
       </c>
       <c r="F112" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G112" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H112">
         <v>9602</v>
@@ -6176,19 +6152,19 @@
         <v>10.6</v>
       </c>
       <c r="J112" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K112">
         <v>11</v>
       </c>
       <c r="L112" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M112" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N112" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O112">
         <v>18.3</v>
@@ -6214,10 +6190,10 @@
         <v>-1.2</v>
       </c>
       <c r="F113" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G113" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H113">
         <v>319.75</v>
@@ -6226,19 +6202,19 @@
         <v>12.1</v>
       </c>
       <c r="J113" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="K113">
         <v>11</v>
       </c>
       <c r="L113" t="s">
-        <v>83</v>
+        <v>74</v>
       </c>
       <c r="M113" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N113" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O113">
         <v>18.3</v>
@@ -6264,10 +6240,10 @@
         <v>-1.2</v>
       </c>
       <c r="F114" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G114" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H114">
         <v>2307.9</v>
@@ -6276,19 +6252,19 @@
         <v>12.4</v>
       </c>
       <c r="J114" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K114">
         <v>5</v>
       </c>
       <c r="L114" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M114" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N114" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O114">
         <v>18.3</v>
@@ -6314,10 +6290,10 @@
         <v>-1.2</v>
       </c>
       <c r="F115" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G115" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H115">
         <v>4021.1</v>
@@ -6326,19 +6302,19 @@
         <v>14</v>
       </c>
       <c r="J115" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K115">
         <v>7</v>
       </c>
       <c r="L115" t="s">
+        <v>73</v>
+      </c>
+      <c r="M115" t="s">
+        <v>78</v>
+      </c>
+      <c r="N115" t="s">
         <v>82</v>
-      </c>
-      <c r="M115" t="s">
-        <v>87</v>
-      </c>
-      <c r="N115" t="s">
-        <v>91</v>
       </c>
       <c r="O115">
         <v>18.3</v>
@@ -6364,10 +6340,10 @@
         <v>-1.2</v>
       </c>
       <c r="F116" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G116" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H116">
         <v>7230</v>
@@ -6376,19 +6352,19 @@
         <v>14.4</v>
       </c>
       <c r="J116" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="K116">
         <v>3</v>
       </c>
       <c r="L116" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M116" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N116" t="s">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="O116">
         <v>18.3</v>
@@ -6398,8 +6374,8 @@
       </c>
     </row>
     <row r="117" spans="1:16">
-      <c r="A117" t="s">
-        <v>16</v>
+      <c r="A117">
+        <v>20260423</v>
       </c>
       <c r="B117" t="s">
         <v>43</v>
@@ -6410,14 +6386,14 @@
       <c r="D117">
         <v>66.40000000000001</v>
       </c>
-      <c r="E117" t="s">
-        <v>59</v>
+      <c r="E117">
+        <v>6.5</v>
       </c>
       <c r="F117" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G117" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H117">
         <v>1263</v>
@@ -6426,19 +6402,19 @@
         <v>3.599999999999994</v>
       </c>
       <c r="J117" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K117">
         <v>6</v>
       </c>
       <c r="L117" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M117" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N117" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O117">
         <v>18.7</v>
@@ -6448,8 +6424,8 @@
       </c>
     </row>
     <row r="118" spans="1:16">
-      <c r="A118" t="s">
-        <v>16</v>
+      <c r="A118">
+        <v>20260423</v>
       </c>
       <c r="B118" t="s">
         <v>49</v>
@@ -6460,14 +6436,14 @@
       <c r="D118">
         <v>64.5</v>
       </c>
-      <c r="E118" t="s">
-        <v>60</v>
+      <c r="E118">
+        <v>0</v>
       </c>
       <c r="F118" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G118" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H118">
         <v>123.95</v>
@@ -6476,19 +6452,19 @@
         <v>5.5</v>
       </c>
       <c r="J118" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="K118">
         <v>1</v>
       </c>
       <c r="L118" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="M118" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N118" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O118">
         <v>18.7</v>
@@ -6498,8 +6474,8 @@
       </c>
     </row>
     <row r="119" spans="1:16">
-      <c r="A119" t="s">
-        <v>16</v>
+      <c r="A119">
+        <v>20260423</v>
       </c>
       <c r="B119" t="s">
         <v>22</v>
@@ -6510,14 +6486,14 @@
       <c r="D119">
         <v>64</v>
       </c>
-      <c r="E119" t="s">
-        <v>61</v>
+      <c r="E119">
+        <v>-2</v>
       </c>
       <c r="F119" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G119" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H119">
         <v>1371.6</v>
@@ -6526,19 +6502,19 @@
         <v>6</v>
       </c>
       <c r="J119" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K119">
         <v>12</v>
       </c>
       <c r="L119" t="s">
+        <v>74</v>
+      </c>
+      <c r="M119" t="s">
+        <v>78</v>
+      </c>
+      <c r="N119" t="s">
         <v>83</v>
-      </c>
-      <c r="M119" t="s">
-        <v>87</v>
-      </c>
-      <c r="N119" t="s">
-        <v>92</v>
       </c>
       <c r="O119">
         <v>18.7</v>
@@ -6548,8 +6524,8 @@
       </c>
     </row>
     <row r="120" spans="1:16">
-      <c r="A120" t="s">
-        <v>16</v>
+      <c r="A120">
+        <v>20260423</v>
       </c>
       <c r="B120" t="s">
         <v>23</v>
@@ -6560,14 +6536,14 @@
       <c r="D120">
         <v>64</v>
       </c>
-      <c r="E120" t="s">
-        <v>61</v>
+      <c r="E120">
+        <v>-2</v>
       </c>
       <c r="F120" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G120" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H120">
         <v>4460</v>
@@ -6576,19 +6552,19 @@
         <v>6</v>
       </c>
       <c r="J120" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K120">
         <v>12</v>
       </c>
       <c r="L120" t="s">
+        <v>74</v>
+      </c>
+      <c r="M120" t="s">
+        <v>78</v>
+      </c>
+      <c r="N120" t="s">
         <v>83</v>
-      </c>
-      <c r="M120" t="s">
-        <v>87</v>
-      </c>
-      <c r="N120" t="s">
-        <v>92</v>
       </c>
       <c r="O120">
         <v>18.7</v>
@@ -6598,8 +6574,8 @@
       </c>
     </row>
     <row r="121" spans="1:16">
-      <c r="A121" t="s">
-        <v>16</v>
+      <c r="A121">
+        <v>20260423</v>
       </c>
       <c r="B121" t="s">
         <v>46</v>
@@ -6610,14 +6586,14 @@
       <c r="D121">
         <v>64</v>
       </c>
-      <c r="E121" t="s">
-        <v>62</v>
+      <c r="E121">
+        <v>6.4</v>
       </c>
       <c r="F121" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G121" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H121">
         <v>2358.2</v>
@@ -6626,19 +6602,19 @@
         <v>6</v>
       </c>
       <c r="J121" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K121">
         <v>6</v>
       </c>
       <c r="L121" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M121" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N121" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O121">
         <v>18.7</v>
@@ -6648,8 +6624,8 @@
       </c>
     </row>
     <row r="122" spans="1:16">
-      <c r="A122" t="s">
-        <v>16</v>
+      <c r="A122">
+        <v>20260423</v>
       </c>
       <c r="B122" t="s">
         <v>39</v>
@@ -6660,14 +6636,14 @@
       <c r="D122">
         <v>63.9</v>
       </c>
-      <c r="E122" t="s">
-        <v>63</v>
+      <c r="E122">
+        <v>-5.4</v>
       </c>
       <c r="F122" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G122" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H122">
         <v>402.65</v>
@@ -6676,19 +6652,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J122" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K122">
         <v>2</v>
       </c>
       <c r="L122" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M122" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N122" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O122">
         <v>18.7</v>
@@ -6698,8 +6674,8 @@
       </c>
     </row>
     <row r="123" spans="1:16">
-      <c r="A123" t="s">
-        <v>16</v>
+      <c r="A123">
+        <v>20260423</v>
       </c>
       <c r="B123" t="s">
         <v>40</v>
@@ -6710,14 +6686,14 @@
       <c r="D123">
         <v>63.9</v>
       </c>
-      <c r="E123" t="s">
-        <v>60</v>
+      <c r="E123">
+        <v>0</v>
       </c>
       <c r="F123" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G123" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H123">
         <v>3858.9</v>
@@ -6726,19 +6702,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J123" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K123">
         <v>1</v>
       </c>
       <c r="L123" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="M123" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N123" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O123">
         <v>18.7</v>
@@ -6748,8 +6724,8 @@
       </c>
     </row>
     <row r="124" spans="1:16">
-      <c r="A124" t="s">
-        <v>16</v>
+      <c r="A124">
+        <v>20260423</v>
       </c>
       <c r="B124" t="s">
         <v>37</v>
@@ -6760,14 +6736,14 @@
       <c r="D124">
         <v>61.9</v>
       </c>
-      <c r="E124" t="s">
-        <v>64</v>
+      <c r="E124">
+        <v>4</v>
       </c>
       <c r="F124" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G124" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H124">
         <v>320.55</v>
@@ -6776,19 +6752,19 @@
         <v>8.100000000000001</v>
       </c>
       <c r="J124" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="K124">
         <v>12</v>
       </c>
       <c r="L124" t="s">
+        <v>74</v>
+      </c>
+      <c r="M124" t="s">
+        <v>78</v>
+      </c>
+      <c r="N124" t="s">
         <v>83</v>
-      </c>
-      <c r="M124" t="s">
-        <v>87</v>
-      </c>
-      <c r="N124" t="s">
-        <v>92</v>
       </c>
       <c r="O124">
         <v>18.7</v>
@@ -6798,8 +6774,8 @@
       </c>
     </row>
     <row r="125" spans="1:16">
-      <c r="A125" t="s">
-        <v>16</v>
+      <c r="A125">
+        <v>20260423</v>
       </c>
       <c r="B125" t="s">
         <v>41</v>
@@ -6810,14 +6786,14 @@
       <c r="D125">
         <v>61.4</v>
       </c>
-      <c r="E125" t="s">
-        <v>65</v>
+      <c r="E125">
+        <v>-6.4</v>
       </c>
       <c r="F125" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G125" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H125">
         <v>214.68</v>
@@ -6826,19 +6802,19 @@
         <v>8.600000000000001</v>
       </c>
       <c r="J125" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K125">
         <v>6</v>
       </c>
       <c r="L125" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M125" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N125" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O125">
         <v>18.7</v>
@@ -6848,8 +6824,8 @@
       </c>
     </row>
     <row r="126" spans="1:16">
-      <c r="A126" t="s">
-        <v>16</v>
+      <c r="A126">
+        <v>20260423</v>
       </c>
       <c r="B126" t="s">
         <v>24</v>
@@ -6860,14 +6836,14 @@
       <c r="D126">
         <v>61</v>
       </c>
-      <c r="E126" t="s">
-        <v>66</v>
+      <c r="E126">
+        <v>-5</v>
       </c>
       <c r="F126" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G126" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H126">
         <v>1019.75</v>
@@ -6876,19 +6852,19 @@
         <v>9</v>
       </c>
       <c r="J126" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K126">
         <v>12</v>
       </c>
       <c r="L126" t="s">
+        <v>74</v>
+      </c>
+      <c r="M126" t="s">
+        <v>78</v>
+      </c>
+      <c r="N126" t="s">
         <v>83</v>
-      </c>
-      <c r="M126" t="s">
-        <v>87</v>
-      </c>
-      <c r="N126" t="s">
-        <v>92</v>
       </c>
       <c r="O126">
         <v>18.7</v>
@@ -6898,8 +6874,8 @@
       </c>
     </row>
     <row r="127" spans="1:16">
-      <c r="A127" t="s">
-        <v>16</v>
+      <c r="A127">
+        <v>20260423</v>
       </c>
       <c r="B127" t="s">
         <v>42</v>
@@ -6910,14 +6886,14 @@
       <c r="D127">
         <v>61</v>
       </c>
-      <c r="E127" t="s">
-        <v>66</v>
+      <c r="E127">
+        <v>-5</v>
       </c>
       <c r="F127" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G127" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H127">
         <v>86.98</v>
@@ -6926,19 +6902,19 @@
         <v>9</v>
       </c>
       <c r="J127" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K127">
         <v>6</v>
       </c>
       <c r="L127" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M127" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N127" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O127">
         <v>18.7</v>
@@ -6948,8 +6924,8 @@
       </c>
     </row>
     <row r="128" spans="1:16">
-      <c r="A128" t="s">
-        <v>16</v>
+      <c r="A128">
+        <v>20260423</v>
       </c>
       <c r="B128" t="s">
         <v>44</v>
@@ -6960,14 +6936,14 @@
       <c r="D128">
         <v>60</v>
       </c>
-      <c r="E128" t="s">
-        <v>60</v>
+      <c r="E128">
+        <v>0</v>
       </c>
       <c r="F128" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G128" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H128">
         <v>125.61</v>
@@ -6976,19 +6952,19 @@
         <v>10</v>
       </c>
       <c r="J128" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K128">
         <v>1</v>
       </c>
       <c r="L128" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="M128" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N128" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O128">
         <v>18.7</v>
@@ -6998,8 +6974,8 @@
       </c>
     </row>
     <row r="129" spans="1:16">
-      <c r="A129" t="s">
-        <v>16</v>
+      <c r="A129">
+        <v>20260423</v>
       </c>
       <c r="B129" t="s">
         <v>32</v>
@@ -7010,14 +6986,14 @@
       <c r="D129">
         <v>59.4</v>
       </c>
-      <c r="E129" t="s">
-        <v>67</v>
+      <c r="E129">
+        <v>-4</v>
       </c>
       <c r="F129" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G129" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H129">
         <v>1404.6</v>
@@ -7026,19 +7002,19 @@
         <v>10.6</v>
       </c>
       <c r="J129" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K129">
         <v>7</v>
       </c>
       <c r="L129" t="s">
-        <v>82</v>
+        <v>73</v>
       </c>
       <c r="M129" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N129" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O129">
         <v>18.7</v>
@@ -7048,8 +7024,8 @@
       </c>
     </row>
     <row r="130" spans="1:16">
-      <c r="A130" t="s">
-        <v>16</v>
+      <c r="A130">
+        <v>20260423</v>
       </c>
       <c r="B130" t="s">
         <v>45</v>
@@ -7060,14 +7036,14 @@
       <c r="D130">
         <v>59.4</v>
       </c>
-      <c r="E130" t="s">
-        <v>68</v>
+      <c r="E130">
+        <v>-3</v>
       </c>
       <c r="F130" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G130" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H130">
         <v>1217.2</v>
@@ -7076,19 +7052,19 @@
         <v>10.6</v>
       </c>
       <c r="J130" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="K130">
         <v>6</v>
       </c>
       <c r="L130" t="s">
-        <v>85</v>
+        <v>76</v>
       </c>
       <c r="M130" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N130" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O130">
         <v>18.7</v>
@@ -7098,8 +7074,8 @@
       </c>
     </row>
     <row r="131" spans="1:16">
-      <c r="A131" t="s">
-        <v>16</v>
+      <c r="A131">
+        <v>20260423</v>
       </c>
       <c r="B131" t="s">
         <v>56</v>
@@ -7110,14 +7086,14 @@
       <c r="D131">
         <v>57.3</v>
       </c>
-      <c r="E131" t="s">
-        <v>60</v>
+      <c r="E131">
+        <v>0</v>
       </c>
       <c r="F131" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G131" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H131">
         <v>445.5</v>
@@ -7126,19 +7102,19 @@
         <v>12.7</v>
       </c>
       <c r="J131" t="s">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="K131">
         <v>1</v>
       </c>
       <c r="L131" t="s">
-        <v>86</v>
+        <v>77</v>
       </c>
       <c r="M131" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="N131" t="s">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="O131">
         <v>18.7</v>
@@ -7148,8 +7124,8 @@
       </c>
     </row>
     <row r="132" spans="1:16">
-      <c r="A132" t="s">
-        <v>16</v>
+      <c r="A132">
+        <v>20260423</v>
       </c>
       <c r="B132" t="s">
         <v>33</v>
@@ -7160,14 +7136,14 @@
       <c r="D132">
         <v>55.6</v>
       </c>
-      <c r="E132" t="s">
-        <v>69</v>
+      <c r="E132">
+        <v>-3.8</v>
       </c>
       <c r="F132" t="s">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="G132" t="s">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="H132">
         <v>9519</v>
@@ -7176,25 +7152,825 @@
         <v>14.4</v>
       </c>
       <c r="J132" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="K132">
         <v>12</v>
       </c>
       <c r="L132" t="s">
+        <v>74</v>
+      </c>
+      <c r="M132" t="s">
+        <v>78</v>
+      </c>
+      <c r="N132" t="s">
         <v>83</v>
-      </c>
-      <c r="M132" t="s">
-        <v>87</v>
-      </c>
-      <c r="N132" t="s">
-        <v>92</v>
       </c>
       <c r="O132">
         <v>18.7</v>
       </c>
       <c r="P132">
         <v>334</v>
+      </c>
+    </row>
+    <row r="133" spans="1:16">
+      <c r="A133" t="s">
+        <v>16</v>
+      </c>
+      <c r="B133" t="s">
+        <v>43</v>
+      </c>
+      <c r="C133" t="s">
+        <v>58</v>
+      </c>
+      <c r="D133">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="E133" t="s">
+        <v>59</v>
+      </c>
+      <c r="F133" t="s">
+        <v>61</v>
+      </c>
+      <c r="G133" t="s">
+        <v>62</v>
+      </c>
+      <c r="H133">
+        <v>1263.2</v>
+      </c>
+      <c r="I133">
+        <v>3.599999999999994</v>
+      </c>
+      <c r="J133" t="s">
+        <v>64</v>
+      </c>
+      <c r="K133">
+        <v>7</v>
+      </c>
+      <c r="L133" t="s">
+        <v>76</v>
+      </c>
+      <c r="M133" t="s">
+        <v>78</v>
+      </c>
+      <c r="N133" t="s">
+        <v>84</v>
+      </c>
+      <c r="O133">
+        <v>18.84</v>
+      </c>
+      <c r="P133">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="134" spans="1:16">
+      <c r="A134" t="s">
+        <v>16</v>
+      </c>
+      <c r="B134" t="s">
+        <v>49</v>
+      </c>
+      <c r="C134" t="s">
+        <v>58</v>
+      </c>
+      <c r="D134">
+        <v>64.5</v>
+      </c>
+      <c r="E134" t="s">
+        <v>59</v>
+      </c>
+      <c r="F134" t="s">
+        <v>61</v>
+      </c>
+      <c r="G134" t="s">
+        <v>62</v>
+      </c>
+      <c r="H134">
+        <v>124.1</v>
+      </c>
+      <c r="I134">
+        <v>5.5</v>
+      </c>
+      <c r="J134" t="s">
+        <v>65</v>
+      </c>
+      <c r="K134">
+        <v>2</v>
+      </c>
+      <c r="L134" t="s">
+        <v>77</v>
+      </c>
+      <c r="M134" t="s">
+        <v>78</v>
+      </c>
+      <c r="N134" t="s">
+        <v>84</v>
+      </c>
+      <c r="O134">
+        <v>18.84</v>
+      </c>
+      <c r="P134">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="135" spans="1:16">
+      <c r="A135" t="s">
+        <v>16</v>
+      </c>
+      <c r="B135" t="s">
+        <v>22</v>
+      </c>
+      <c r="C135" t="s">
+        <v>58</v>
+      </c>
+      <c r="D135">
+        <v>64</v>
+      </c>
+      <c r="E135" t="s">
+        <v>59</v>
+      </c>
+      <c r="F135" t="s">
+        <v>61</v>
+      </c>
+      <c r="G135" t="s">
+        <v>62</v>
+      </c>
+      <c r="H135">
+        <v>1371.2</v>
+      </c>
+      <c r="I135">
+        <v>6</v>
+      </c>
+      <c r="J135" t="s">
+        <v>64</v>
+      </c>
+      <c r="K135">
+        <v>13</v>
+      </c>
+      <c r="L135" t="s">
+        <v>74</v>
+      </c>
+      <c r="M135" t="s">
+        <v>78</v>
+      </c>
+      <c r="N135" t="s">
+        <v>84</v>
+      </c>
+      <c r="O135">
+        <v>18.84</v>
+      </c>
+      <c r="P135">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="136" spans="1:16">
+      <c r="A136" t="s">
+        <v>16</v>
+      </c>
+      <c r="B136" t="s">
+        <v>23</v>
+      </c>
+      <c r="C136" t="s">
+        <v>58</v>
+      </c>
+      <c r="D136">
+        <v>64</v>
+      </c>
+      <c r="E136" t="s">
+        <v>59</v>
+      </c>
+      <c r="F136" t="s">
+        <v>61</v>
+      </c>
+      <c r="G136" t="s">
+        <v>62</v>
+      </c>
+      <c r="H136">
+        <v>4440.2</v>
+      </c>
+      <c r="I136">
+        <v>6</v>
+      </c>
+      <c r="J136" t="s">
+        <v>64</v>
+      </c>
+      <c r="K136">
+        <v>13</v>
+      </c>
+      <c r="L136" t="s">
+        <v>74</v>
+      </c>
+      <c r="M136" t="s">
+        <v>78</v>
+      </c>
+      <c r="N136" t="s">
+        <v>84</v>
+      </c>
+      <c r="O136">
+        <v>18.84</v>
+      </c>
+      <c r="P136">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="137" spans="1:16">
+      <c r="A137" t="s">
+        <v>16</v>
+      </c>
+      <c r="B137" t="s">
+        <v>46</v>
+      </c>
+      <c r="C137" t="s">
+        <v>58</v>
+      </c>
+      <c r="D137">
+        <v>64</v>
+      </c>
+      <c r="E137" t="s">
+        <v>59</v>
+      </c>
+      <c r="F137" t="s">
+        <v>61</v>
+      </c>
+      <c r="G137" t="s">
+        <v>62</v>
+      </c>
+      <c r="H137">
+        <v>2353.4</v>
+      </c>
+      <c r="I137">
+        <v>6</v>
+      </c>
+      <c r="J137" t="s">
+        <v>64</v>
+      </c>
+      <c r="K137">
+        <v>7</v>
+      </c>
+      <c r="L137" t="s">
+        <v>76</v>
+      </c>
+      <c r="M137" t="s">
+        <v>78</v>
+      </c>
+      <c r="N137" t="s">
+        <v>84</v>
+      </c>
+      <c r="O137">
+        <v>18.84</v>
+      </c>
+      <c r="P137">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="138" spans="1:16">
+      <c r="A138" t="s">
+        <v>16</v>
+      </c>
+      <c r="B138" t="s">
+        <v>39</v>
+      </c>
+      <c r="C138" t="s">
+        <v>58</v>
+      </c>
+      <c r="D138">
+        <v>63.9</v>
+      </c>
+      <c r="E138" t="s">
+        <v>59</v>
+      </c>
+      <c r="F138" t="s">
+        <v>61</v>
+      </c>
+      <c r="G138" t="s">
+        <v>62</v>
+      </c>
+      <c r="H138">
+        <v>400.9</v>
+      </c>
+      <c r="I138">
+        <v>6.100000000000001</v>
+      </c>
+      <c r="J138" t="s">
+        <v>64</v>
+      </c>
+      <c r="K138">
+        <v>3</v>
+      </c>
+      <c r="L138" t="s">
+        <v>76</v>
+      </c>
+      <c r="M138" t="s">
+        <v>78</v>
+      </c>
+      <c r="N138" t="s">
+        <v>84</v>
+      </c>
+      <c r="O138">
+        <v>18.84</v>
+      </c>
+      <c r="P138">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="139" spans="1:16">
+      <c r="A139" t="s">
+        <v>16</v>
+      </c>
+      <c r="B139" t="s">
+        <v>40</v>
+      </c>
+      <c r="C139" t="s">
+        <v>58</v>
+      </c>
+      <c r="D139">
+        <v>63.9</v>
+      </c>
+      <c r="E139" t="s">
+        <v>59</v>
+      </c>
+      <c r="F139" t="s">
+        <v>61</v>
+      </c>
+      <c r="G139" t="s">
+        <v>62</v>
+      </c>
+      <c r="H139">
+        <v>3856.3</v>
+      </c>
+      <c r="I139">
+        <v>6.100000000000001</v>
+      </c>
+      <c r="J139" t="s">
+        <v>64</v>
+      </c>
+      <c r="K139">
+        <v>2</v>
+      </c>
+      <c r="L139" t="s">
+        <v>77</v>
+      </c>
+      <c r="M139" t="s">
+        <v>78</v>
+      </c>
+      <c r="N139" t="s">
+        <v>84</v>
+      </c>
+      <c r="O139">
+        <v>18.84</v>
+      </c>
+      <c r="P139">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="140" spans="1:16">
+      <c r="A140" t="s">
+        <v>16</v>
+      </c>
+      <c r="B140" t="s">
+        <v>41</v>
+      </c>
+      <c r="C140" t="s">
+        <v>58</v>
+      </c>
+      <c r="D140">
+        <v>61.4</v>
+      </c>
+      <c r="E140" t="s">
+        <v>59</v>
+      </c>
+      <c r="F140" t="s">
+        <v>61</v>
+      </c>
+      <c r="G140" t="s">
+        <v>62</v>
+      </c>
+      <c r="H140">
+        <v>214.69</v>
+      </c>
+      <c r="I140">
+        <v>8.600000000000001</v>
+      </c>
+      <c r="J140" t="s">
+        <v>66</v>
+      </c>
+      <c r="K140">
+        <v>7</v>
+      </c>
+      <c r="L140" t="s">
+        <v>76</v>
+      </c>
+      <c r="M140" t="s">
+        <v>78</v>
+      </c>
+      <c r="N140" t="s">
+        <v>84</v>
+      </c>
+      <c r="O140">
+        <v>18.84</v>
+      </c>
+      <c r="P140">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="141" spans="1:16">
+      <c r="A141" t="s">
+        <v>16</v>
+      </c>
+      <c r="B141" t="s">
+        <v>24</v>
+      </c>
+      <c r="C141" t="s">
+        <v>58</v>
+      </c>
+      <c r="D141">
+        <v>61</v>
+      </c>
+      <c r="E141" t="s">
+        <v>59</v>
+      </c>
+      <c r="F141" t="s">
+        <v>61</v>
+      </c>
+      <c r="G141" t="s">
+        <v>62</v>
+      </c>
+      <c r="H141">
+        <v>1020.55</v>
+      </c>
+      <c r="I141">
+        <v>9</v>
+      </c>
+      <c r="J141" t="s">
+        <v>64</v>
+      </c>
+      <c r="K141">
+        <v>13</v>
+      </c>
+      <c r="L141" t="s">
+        <v>74</v>
+      </c>
+      <c r="M141" t="s">
+        <v>78</v>
+      </c>
+      <c r="N141" t="s">
+        <v>84</v>
+      </c>
+      <c r="O141">
+        <v>18.84</v>
+      </c>
+      <c r="P141">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="142" spans="1:16">
+      <c r="A142" t="s">
+        <v>16</v>
+      </c>
+      <c r="B142" t="s">
+        <v>42</v>
+      </c>
+      <c r="C142" t="s">
+        <v>58</v>
+      </c>
+      <c r="D142">
+        <v>61</v>
+      </c>
+      <c r="E142" t="s">
+        <v>59</v>
+      </c>
+      <c r="F142" t="s">
+        <v>61</v>
+      </c>
+      <c r="G142" t="s">
+        <v>62</v>
+      </c>
+      <c r="H142">
+        <v>87.06999999999999</v>
+      </c>
+      <c r="I142">
+        <v>9</v>
+      </c>
+      <c r="J142" t="s">
+        <v>64</v>
+      </c>
+      <c r="K142">
+        <v>7</v>
+      </c>
+      <c r="L142" t="s">
+        <v>76</v>
+      </c>
+      <c r="M142" t="s">
+        <v>78</v>
+      </c>
+      <c r="N142" t="s">
+        <v>84</v>
+      </c>
+      <c r="O142">
+        <v>18.84</v>
+      </c>
+      <c r="P142">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="143" spans="1:16">
+      <c r="A143" t="s">
+        <v>16</v>
+      </c>
+      <c r="B143" t="s">
+        <v>44</v>
+      </c>
+      <c r="C143" t="s">
+        <v>58</v>
+      </c>
+      <c r="D143">
+        <v>60</v>
+      </c>
+      <c r="E143" t="s">
+        <v>59</v>
+      </c>
+      <c r="F143" t="s">
+        <v>61</v>
+      </c>
+      <c r="G143" t="s">
+        <v>62</v>
+      </c>
+      <c r="H143">
+        <v>125.46</v>
+      </c>
+      <c r="I143">
+        <v>10</v>
+      </c>
+      <c r="J143" t="s">
+        <v>64</v>
+      </c>
+      <c r="K143">
+        <v>2</v>
+      </c>
+      <c r="L143" t="s">
+        <v>77</v>
+      </c>
+      <c r="M143" t="s">
+        <v>78</v>
+      </c>
+      <c r="N143" t="s">
+        <v>84</v>
+      </c>
+      <c r="O143">
+        <v>18.84</v>
+      </c>
+      <c r="P143">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="144" spans="1:16">
+      <c r="A144" t="s">
+        <v>16</v>
+      </c>
+      <c r="B144" t="s">
+        <v>32</v>
+      </c>
+      <c r="C144" t="s">
+        <v>58</v>
+      </c>
+      <c r="D144">
+        <v>59.4</v>
+      </c>
+      <c r="E144" t="s">
+        <v>59</v>
+      </c>
+      <c r="F144" t="s">
+        <v>61</v>
+      </c>
+      <c r="G144" t="s">
+        <v>62</v>
+      </c>
+      <c r="H144">
+        <v>1401.1</v>
+      </c>
+      <c r="I144">
+        <v>10.6</v>
+      </c>
+      <c r="J144" t="s">
+        <v>66</v>
+      </c>
+      <c r="K144">
+        <v>8</v>
+      </c>
+      <c r="L144" t="s">
+        <v>73</v>
+      </c>
+      <c r="M144" t="s">
+        <v>78</v>
+      </c>
+      <c r="N144" t="s">
+        <v>84</v>
+      </c>
+      <c r="O144">
+        <v>18.84</v>
+      </c>
+      <c r="P144">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="145" spans="1:16">
+      <c r="A145" t="s">
+        <v>16</v>
+      </c>
+      <c r="B145" t="s">
+        <v>45</v>
+      </c>
+      <c r="C145" t="s">
+        <v>58</v>
+      </c>
+      <c r="D145">
+        <v>59.4</v>
+      </c>
+      <c r="E145" t="s">
+        <v>59</v>
+      </c>
+      <c r="F145" t="s">
+        <v>61</v>
+      </c>
+      <c r="G145" t="s">
+        <v>62</v>
+      </c>
+      <c r="H145">
+        <v>1218.2</v>
+      </c>
+      <c r="I145">
+        <v>10.6</v>
+      </c>
+      <c r="J145" t="s">
+        <v>66</v>
+      </c>
+      <c r="K145">
+        <v>7</v>
+      </c>
+      <c r="L145" t="s">
+        <v>76</v>
+      </c>
+      <c r="M145" t="s">
+        <v>78</v>
+      </c>
+      <c r="N145" t="s">
+        <v>84</v>
+      </c>
+      <c r="O145">
+        <v>18.84</v>
+      </c>
+      <c r="P145">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="146" spans="1:16">
+      <c r="A146" t="s">
+        <v>16</v>
+      </c>
+      <c r="B146" t="s">
+        <v>56</v>
+      </c>
+      <c r="C146" t="s">
+        <v>58</v>
+      </c>
+      <c r="D146">
+        <v>57.3</v>
+      </c>
+      <c r="E146" t="s">
+        <v>59</v>
+      </c>
+      <c r="F146" t="s">
+        <v>61</v>
+      </c>
+      <c r="G146" t="s">
+        <v>62</v>
+      </c>
+      <c r="H146">
+        <v>445.65</v>
+      </c>
+      <c r="I146">
+        <v>12.7</v>
+      </c>
+      <c r="J146" t="s">
+        <v>71</v>
+      </c>
+      <c r="K146">
+        <v>2</v>
+      </c>
+      <c r="L146" t="s">
+        <v>77</v>
+      </c>
+      <c r="M146" t="s">
+        <v>78</v>
+      </c>
+      <c r="N146" t="s">
+        <v>84</v>
+      </c>
+      <c r="O146">
+        <v>18.84</v>
+      </c>
+      <c r="P146">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="147" spans="1:16">
+      <c r="A147" t="s">
+        <v>16</v>
+      </c>
+      <c r="B147" t="s">
+        <v>37</v>
+      </c>
+      <c r="C147" t="s">
+        <v>58</v>
+      </c>
+      <c r="D147">
+        <v>55.9</v>
+      </c>
+      <c r="E147" t="s">
+        <v>60</v>
+      </c>
+      <c r="F147" t="s">
+        <v>61</v>
+      </c>
+      <c r="G147" t="s">
+        <v>62</v>
+      </c>
+      <c r="H147">
+        <v>319.85</v>
+      </c>
+      <c r="I147">
+        <v>14.1</v>
+      </c>
+      <c r="J147" t="s">
+        <v>68</v>
+      </c>
+      <c r="K147">
+        <v>13</v>
+      </c>
+      <c r="L147" t="s">
+        <v>74</v>
+      </c>
+      <c r="M147" t="s">
+        <v>78</v>
+      </c>
+      <c r="N147" t="s">
+        <v>84</v>
+      </c>
+      <c r="O147">
+        <v>18.84</v>
+      </c>
+      <c r="P147">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="148" spans="1:16">
+      <c r="A148" t="s">
+        <v>16</v>
+      </c>
+      <c r="B148" t="s">
+        <v>33</v>
+      </c>
+      <c r="C148" t="s">
+        <v>58</v>
+      </c>
+      <c r="D148">
+        <v>55.6</v>
+      </c>
+      <c r="E148" t="s">
+        <v>59</v>
+      </c>
+      <c r="F148" t="s">
+        <v>61</v>
+      </c>
+      <c r="G148" t="s">
+        <v>62</v>
+      </c>
+      <c r="H148">
+        <v>9545.5</v>
+      </c>
+      <c r="I148">
+        <v>14.4</v>
+      </c>
+      <c r="J148" t="s">
+        <v>64</v>
+      </c>
+      <c r="K148">
+        <v>13</v>
+      </c>
+      <c r="L148" t="s">
+        <v>74</v>
+      </c>
+      <c r="M148" t="s">
+        <v>78</v>
+      </c>
+      <c r="N148" t="s">
+        <v>84</v>
+      </c>
+      <c r="O148">
+        <v>18.84</v>
+      </c>
+      <c r="P148">
+        <v>320</v>
       </c>
     </row>
   </sheetData>

--- a/reports/watchlist_history.xlsx
+++ b/reports/watchlist_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1214" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="87">
   <si>
     <t>Date</t>
   </si>
@@ -193,10 +193,16 @@
     <t>WATCH</t>
   </si>
   <si>
-    <t>+0.0</t>
+    <t>+0.5</t>
   </si>
   <si>
-    <t>-6.0</t>
+    <t>+2.9</t>
+  </si>
+  <si>
+    <t>+3.9</t>
+  </si>
+  <si>
+    <t>+1.5</t>
   </si>
   <si>
     <t>Stage 2 — Uptrend ✓</t>
@@ -600,7 +606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P148"/>
+  <dimension ref="A1:P164"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -670,10 +676,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H2">
         <v>11714</v>
@@ -685,13 +691,13 @@
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O2">
         <v>17.53</v>
@@ -717,10 +723,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H3">
         <v>514.05</v>
@@ -732,13 +738,13 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M3" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N3" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O3">
         <v>17.53</v>
@@ -764,10 +770,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G4" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H4">
         <v>1621.5</v>
@@ -779,13 +785,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="M4" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N4" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O4">
         <v>17.53</v>
@@ -811,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G5" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H5">
         <v>191.38</v>
@@ -823,19 +829,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J5" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M5" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O5">
         <v>17.53</v>
@@ -861,10 +867,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G6" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H6">
         <v>1318.1</v>
@@ -873,19 +879,19 @@
         <v>0.9000000000000057</v>
       </c>
       <c r="J6" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M6" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N6" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O6">
         <v>17.53</v>
@@ -911,10 +917,10 @@
         <v>-0.5</v>
       </c>
       <c r="F7" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G7" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H7">
         <v>1377.7</v>
@@ -923,19 +929,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K7">
         <v>6</v>
       </c>
       <c r="L7" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M7" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N7" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O7">
         <v>17.53</v>
@@ -961,10 +967,10 @@
         <v>-0.5</v>
       </c>
       <c r="F8" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G8" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H8">
         <v>4479.7</v>
@@ -973,19 +979,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J8" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K8">
         <v>6</v>
       </c>
       <c r="L8" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N8" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O8">
         <v>17.53</v>
@@ -1011,10 +1017,10 @@
         <v>-0.5</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H9">
         <v>1045.3</v>
@@ -1023,19 +1029,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K9">
         <v>6</v>
       </c>
       <c r="L9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O9">
         <v>17.53</v>
@@ -1061,10 +1067,10 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G10" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H10">
         <v>1055.65</v>
@@ -1073,19 +1079,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J10" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M10" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N10" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O10">
         <v>17.53</v>
@@ -1111,10 +1117,10 @@
         <v>-0.5</v>
       </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H11">
         <v>1045.3</v>
@@ -1123,19 +1129,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J11" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K11">
         <v>6</v>
       </c>
       <c r="L11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M11" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O11">
         <v>17.53</v>
@@ -1161,10 +1167,10 @@
         <v>-0.5</v>
       </c>
       <c r="F12" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G12" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H12">
         <v>4479.7</v>
@@ -1173,19 +1179,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J12" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K12">
         <v>6</v>
       </c>
       <c r="L12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M12" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N12" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O12">
         <v>17.53</v>
@@ -1211,10 +1217,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G13" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H13">
         <v>581.3</v>
@@ -1223,19 +1229,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J13" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K13">
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M13" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N13" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O13">
         <v>17.53</v>
@@ -1261,10 +1267,10 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G14" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H14">
         <v>458.9</v>
@@ -1273,19 +1279,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J14" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M14" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N14" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O14">
         <v>17.53</v>
@@ -1311,10 +1317,10 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G15" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H15">
         <v>196.02</v>
@@ -1323,19 +1329,19 @@
         <v>4.400000000000006</v>
       </c>
       <c r="J15" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N15" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O15">
         <v>17.53</v>
@@ -1361,10 +1367,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G16" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H16">
         <v>4172.9</v>
@@ -1373,19 +1379,19 @@
         <v>5</v>
       </c>
       <c r="J16" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K16">
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M16" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O16">
         <v>17.53</v>
@@ -1411,10 +1417,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G17" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H17">
         <v>6373.5</v>
@@ -1423,19 +1429,19 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J17" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K17">
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N17" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O17">
         <v>17.53</v>
@@ -1461,10 +1467,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G18" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H18">
         <v>1113.1</v>
@@ -1473,19 +1479,19 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J18" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M18" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O18">
         <v>17.53</v>
@@ -1511,10 +1517,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G19" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H19">
         <v>1379.9</v>
@@ -1523,19 +1529,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J19" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K19">
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M19" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N19" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O19">
         <v>17.53</v>
@@ -1561,10 +1567,10 @@
         <v>-0.5</v>
       </c>
       <c r="F20" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G20" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H20">
         <v>9793</v>
@@ -1573,19 +1579,19 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J20" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K20">
         <v>6</v>
       </c>
       <c r="L20" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M20" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N20" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O20">
         <v>17.53</v>
@@ -1611,10 +1617,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H21">
         <v>7955.5</v>
@@ -1623,19 +1629,19 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J21" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K21">
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M21" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N21" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O21">
         <v>17.53</v>
@@ -1661,10 +1667,10 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G22" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H22">
         <v>1037.85</v>
@@ -1673,19 +1679,19 @@
         <v>6.399999999999999</v>
       </c>
       <c r="J22" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K22">
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M22" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N22" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O22">
         <v>17.53</v>
@@ -1711,10 +1717,10 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G23" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H23">
         <v>979.1</v>
@@ -1723,19 +1729,19 @@
         <v>8.399999999999999</v>
       </c>
       <c r="J23" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K23">
         <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M23" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N23" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O23">
         <v>17.53</v>
@@ -1761,10 +1767,10 @@
         <v>-0.5</v>
       </c>
       <c r="F24" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G24" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H24">
         <v>319.35</v>
@@ -1773,19 +1779,19 @@
         <v>8.5</v>
       </c>
       <c r="J24" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K24">
         <v>6</v>
       </c>
       <c r="L24" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M24" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N24" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="O24">
         <v>17.53</v>
@@ -1811,10 +1817,10 @@
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G25" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H25">
         <v>767.65</v>
@@ -1826,13 +1832,13 @@
         <v>1</v>
       </c>
       <c r="L25" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M25" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N25" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O25">
         <v>18.27</v>
@@ -1858,10 +1864,10 @@
         <v>7.8</v>
       </c>
       <c r="F26" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G26" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H26">
         <v>404.1</v>
@@ -1870,19 +1876,19 @@
         <v>1</v>
       </c>
       <c r="J26" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K26">
         <v>7</v>
       </c>
       <c r="L26" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M26" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N26" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O26">
         <v>18.27</v>
@@ -1908,10 +1914,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G27" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H27">
         <v>3847</v>
@@ -1920,19 +1926,19 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K27">
         <v>1</v>
       </c>
       <c r="L27" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M27" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N27" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O27">
         <v>18.27</v>
@@ -1958,10 +1964,10 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G28" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H28">
         <v>211.75</v>
@@ -1970,19 +1976,19 @@
         <v>2.5</v>
       </c>
       <c r="J28" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K28">
         <v>1</v>
       </c>
       <c r="L28" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M28" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N28" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O28">
         <v>18.27</v>
@@ -2008,10 +2014,10 @@
         <v>-0.5</v>
       </c>
       <c r="F29" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G29" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H29">
         <v>1381.5</v>
@@ -2020,19 +2026,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J29" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K29">
         <v>7</v>
       </c>
       <c r="L29" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M29" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N29" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O29">
         <v>18.27</v>
@@ -2058,10 +2064,10 @@
         <v>-0.5</v>
       </c>
       <c r="F30" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G30" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H30">
         <v>4483</v>
@@ -2070,19 +2076,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J30" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K30">
         <v>7</v>
       </c>
       <c r="L30" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M30" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N30" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O30">
         <v>18.27</v>
@@ -2108,10 +2114,10 @@
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G31" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H31">
         <v>89.05</v>
@@ -2120,19 +2126,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J31" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K31">
         <v>1</v>
       </c>
       <c r="L31" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M31" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N31" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O31">
         <v>18.27</v>
@@ -2158,10 +2164,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G32" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H32">
         <v>1291.1</v>
@@ -2170,19 +2176,19 @@
         <v>3.400000000000006</v>
       </c>
       <c r="J32" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K32">
         <v>1</v>
       </c>
       <c r="L32" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M32" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N32" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O32">
         <v>18.27</v>
@@ -2208,10 +2214,10 @@
         <v>-0.5</v>
       </c>
       <c r="F33" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G33" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H33">
         <v>1414.6</v>
@@ -2220,19 +2226,19 @@
         <v>5.900000000000006</v>
       </c>
       <c r="J33" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K33">
         <v>2</v>
       </c>
       <c r="L33" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M33" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N33" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O33">
         <v>18.27</v>
@@ -2258,10 +2264,10 @@
         <v>-0.5</v>
       </c>
       <c r="F34" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G34" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H34">
         <v>9760</v>
@@ -2270,19 +2276,19 @@
         <v>6.299999999999997</v>
       </c>
       <c r="J34" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K34">
         <v>7</v>
       </c>
       <c r="L34" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M34" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N34" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O34">
         <v>18.27</v>
@@ -2308,10 +2314,10 @@
         <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G35" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H35">
         <v>125.85</v>
@@ -2320,19 +2326,19 @@
         <v>7.299999999999997</v>
       </c>
       <c r="J35" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K35">
         <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M35" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N35" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O35">
         <v>18.27</v>
@@ -2358,10 +2364,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G36" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H36">
         <v>1171.95</v>
@@ -2370,19 +2376,19 @@
         <v>7.899999999999999</v>
       </c>
       <c r="J36" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K36">
         <v>1</v>
       </c>
       <c r="L36" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M36" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N36" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O36">
         <v>18.27</v>
@@ -2408,10 +2414,10 @@
         <v>-6.5</v>
       </c>
       <c r="F37" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G37" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H37">
         <v>1038.1</v>
@@ -2420,19 +2426,19 @@
         <v>9.299999999999997</v>
       </c>
       <c r="J37" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K37">
         <v>7</v>
       </c>
       <c r="L37" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M37" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N37" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O37">
         <v>18.27</v>
@@ -2458,10 +2464,10 @@
         <v>-2.9</v>
       </c>
       <c r="F38" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G38" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H38">
         <v>319.6</v>
@@ -2470,19 +2476,19 @@
         <v>11.4</v>
       </c>
       <c r="J38" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K38">
         <v>7</v>
       </c>
       <c r="L38" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M38" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N38" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O38">
         <v>18.27</v>
@@ -2508,10 +2514,10 @@
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G39" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H39">
         <v>2314.1</v>
@@ -2520,19 +2526,19 @@
         <v>11.7</v>
       </c>
       <c r="J39" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K39">
         <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M39" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N39" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O39">
         <v>18.27</v>
@@ -2558,10 +2564,10 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G40" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H40">
         <v>3723.6</v>
@@ -2570,19 +2576,19 @@
         <v>11.7</v>
       </c>
       <c r="J40" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K40">
         <v>1</v>
       </c>
       <c r="L40" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M40" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N40" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O40">
         <v>18.27</v>
@@ -2608,10 +2614,10 @@
         <v>-0.5</v>
       </c>
       <c r="F41" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G41" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H41">
         <v>4049.2</v>
@@ -2620,19 +2626,19 @@
         <v>13.3</v>
       </c>
       <c r="J41" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K41">
         <v>3</v>
       </c>
       <c r="L41" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M41" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N41" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O41">
         <v>18.27</v>
@@ -2658,10 +2664,10 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G42" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H42">
         <v>124.98</v>
@@ -2670,19 +2676,19 @@
         <v>14.6</v>
       </c>
       <c r="J42" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K42">
         <v>1</v>
       </c>
       <c r="L42" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M42" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N42" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O42">
         <v>18.27</v>
@@ -2708,10 +2714,10 @@
         <v>2.4</v>
       </c>
       <c r="F43" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G43" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H43">
         <v>1388.7</v>
@@ -2720,19 +2726,19 @@
         <v>0.9000000000000057</v>
       </c>
       <c r="J43" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K43">
         <v>8</v>
       </c>
       <c r="L43" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M43" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N43" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O43">
         <v>18.23</v>
@@ -2758,10 +2764,10 @@
         <v>0</v>
       </c>
       <c r="F44" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G44" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H44">
         <v>404.8</v>
@@ -2770,19 +2776,19 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K44">
         <v>8</v>
       </c>
       <c r="L44" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M44" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N44" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O44">
         <v>18.23</v>
@@ -2808,10 +2814,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G45" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H45">
         <v>3845.7</v>
@@ -2820,19 +2826,19 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K45">
         <v>2</v>
       </c>
       <c r="L45" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M45" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N45" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O45">
         <v>18.23</v>
@@ -2858,10 +2864,10 @@
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G46" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H46">
         <v>213.03</v>
@@ -2870,19 +2876,19 @@
         <v>1.5</v>
       </c>
       <c r="J46" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K46">
         <v>2</v>
       </c>
       <c r="L46" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M46" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N46" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O46">
         <v>18.23</v>
@@ -2908,10 +2914,10 @@
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G47" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H47">
         <v>4477</v>
@@ -2920,19 +2926,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J47" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K47">
         <v>8</v>
       </c>
       <c r="L47" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M47" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N47" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O47">
         <v>18.23</v>
@@ -2958,10 +2964,10 @@
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G48" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H48">
         <v>88.98999999999999</v>
@@ -2970,19 +2976,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J48" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K48">
         <v>2</v>
       </c>
       <c r="L48" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M48" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N48" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O48">
         <v>18.23</v>
@@ -3008,10 +3014,10 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G49" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H49">
         <v>1288.9</v>
@@ -3020,19 +3026,19 @@
         <v>3.400000000000006</v>
       </c>
       <c r="J49" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K49">
         <v>2</v>
       </c>
       <c r="L49" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M49" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N49" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O49">
         <v>18.23</v>
@@ -3058,10 +3064,10 @@
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G50" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H50">
         <v>1419</v>
@@ -3070,19 +3076,19 @@
         <v>5.900000000000006</v>
       </c>
       <c r="J50" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K50">
         <v>3</v>
       </c>
       <c r="L50" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M50" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N50" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O50">
         <v>18.23</v>
@@ -3108,10 +3114,10 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G51" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H51">
         <v>9758</v>
@@ -3120,19 +3126,19 @@
         <v>6.299999999999997</v>
       </c>
       <c r="J51" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K51">
         <v>8</v>
       </c>
       <c r="L51" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M51" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N51" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O51">
         <v>18.23</v>
@@ -3158,10 +3164,10 @@
         <v>0</v>
       </c>
       <c r="F52" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G52" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H52">
         <v>125.98</v>
@@ -3170,19 +3176,19 @@
         <v>7.299999999999997</v>
       </c>
       <c r="J52" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K52">
         <v>2</v>
       </c>
       <c r="L52" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M52" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N52" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O52">
         <v>18.23</v>
@@ -3208,10 +3214,10 @@
         <v>0</v>
       </c>
       <c r="F53" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G53" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H53">
         <v>1182</v>
@@ -3220,19 +3226,19 @@
         <v>7.899999999999999</v>
       </c>
       <c r="J53" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K53">
         <v>2</v>
       </c>
       <c r="L53" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M53" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N53" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O53">
         <v>18.23</v>
@@ -3258,10 +3264,10 @@
         <v>0</v>
       </c>
       <c r="F54" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G54" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H54">
         <v>1040</v>
@@ -3270,19 +3276,19 @@
         <v>9.299999999999997</v>
       </c>
       <c r="J54" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K54">
         <v>8</v>
       </c>
       <c r="L54" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M54" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N54" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O54">
         <v>18.23</v>
@@ -3308,10 +3314,10 @@
         <v>0</v>
       </c>
       <c r="F55" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G55" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H55">
         <v>320.2</v>
@@ -3320,19 +3326,19 @@
         <v>11.4</v>
       </c>
       <c r="J55" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K55">
         <v>8</v>
       </c>
       <c r="L55" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M55" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N55" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O55">
         <v>18.23</v>
@@ -3358,10 +3364,10 @@
         <v>0</v>
       </c>
       <c r="F56" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G56" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H56">
         <v>2314.8</v>
@@ -3370,19 +3376,19 @@
         <v>11.7</v>
       </c>
       <c r="J56" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K56">
         <v>2</v>
       </c>
       <c r="L56" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M56" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N56" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O56">
         <v>18.23</v>
@@ -3408,10 +3414,10 @@
         <v>0</v>
       </c>
       <c r="F57" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G57" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H57">
         <v>3716.5</v>
@@ -3420,19 +3426,19 @@
         <v>11.7</v>
       </c>
       <c r="J57" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K57">
         <v>2</v>
       </c>
       <c r="L57" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M57" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N57" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O57">
         <v>18.23</v>
@@ -3458,10 +3464,10 @@
         <v>0</v>
       </c>
       <c r="F58" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G58" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H58">
         <v>4043</v>
@@ -3470,19 +3476,19 @@
         <v>13.3</v>
       </c>
       <c r="J58" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K58">
         <v>4</v>
       </c>
       <c r="L58" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M58" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N58" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O58">
         <v>18.23</v>
@@ -3508,10 +3514,10 @@
         <v>0</v>
       </c>
       <c r="F59" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G59" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H59">
         <v>125.04</v>
@@ -3520,19 +3526,19 @@
         <v>14.6</v>
       </c>
       <c r="J59" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K59">
         <v>2</v>
       </c>
       <c r="L59" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M59" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N59" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O59">
         <v>18.23</v>
@@ -3558,10 +3564,10 @@
         <v>0</v>
       </c>
       <c r="F60" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G60" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H60">
         <v>3852.5</v>
@@ -3573,13 +3579,13 @@
         <v>1</v>
       </c>
       <c r="L60" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M60" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N60" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O60">
         <v>18.08</v>
@@ -3605,10 +3611,10 @@
         <v>0.5</v>
       </c>
       <c r="F61" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G61" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H61">
         <v>1388.5</v>
@@ -3617,19 +3623,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J61" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K61">
         <v>9</v>
       </c>
       <c r="L61" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M61" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N61" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O61">
         <v>18.08</v>
@@ -3655,10 +3661,10 @@
         <v>0.5</v>
       </c>
       <c r="F62" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G62" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H62">
         <v>406.1</v>
@@ -3667,19 +3673,19 @@
         <v>0.5</v>
       </c>
       <c r="J62" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K62">
         <v>9</v>
       </c>
       <c r="L62" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M62" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N62" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O62">
         <v>18.08</v>
@@ -3705,10 +3711,10 @@
         <v>0.5</v>
       </c>
       <c r="F63" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G63" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H63">
         <v>213.6</v>
@@ -3717,19 +3723,19 @@
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K63">
         <v>3</v>
       </c>
       <c r="L63" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M63" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N63" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O63">
         <v>18.08</v>
@@ -3755,10 +3761,10 @@
         <v>0.5</v>
       </c>
       <c r="F64" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G64" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H64">
         <v>4478</v>
@@ -3767,19 +3773,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J64" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K64">
         <v>9</v>
       </c>
       <c r="L64" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M64" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N64" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O64">
         <v>18.08</v>
@@ -3805,10 +3811,10 @@
         <v>6.5</v>
       </c>
       <c r="F65" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G65" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H65">
         <v>1050.05</v>
@@ -3817,19 +3823,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J65" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K65">
         <v>9</v>
       </c>
       <c r="L65" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M65" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N65" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O65">
         <v>18.08</v>
@@ -3855,10 +3861,10 @@
         <v>0.5</v>
       </c>
       <c r="F66" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G66" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H66">
         <v>88.59</v>
@@ -3867,19 +3873,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J66" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K66">
         <v>3</v>
       </c>
       <c r="L66" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M66" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N66" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O66">
         <v>18.08</v>
@@ -3905,10 +3911,10 @@
         <v>0.5</v>
       </c>
       <c r="F67" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G67" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H67">
         <v>1291.7</v>
@@ -3917,19 +3923,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J67" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K67">
         <v>3</v>
       </c>
       <c r="L67" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M67" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N67" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O67">
         <v>18.08</v>
@@ -3955,10 +3961,10 @@
         <v>0.5</v>
       </c>
       <c r="F68" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G68" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H68">
         <v>1405.3</v>
@@ -3967,19 +3973,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J68" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K68">
         <v>4</v>
       </c>
       <c r="L68" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M68" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N68" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O68">
         <v>18.08</v>
@@ -4005,10 +4011,10 @@
         <v>0.5</v>
       </c>
       <c r="F69" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G69" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H69">
         <v>125.89</v>
@@ -4017,19 +4023,19 @@
         <v>6.799999999999997</v>
       </c>
       <c r="J69" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K69">
         <v>3</v>
       </c>
       <c r="L69" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M69" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N69" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O69">
         <v>18.08</v>
@@ -4055,10 +4061,10 @@
         <v>0.5</v>
       </c>
       <c r="F70" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G70" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H70">
         <v>1190.45</v>
@@ -4067,19 +4073,19 @@
         <v>7.399999999999999</v>
       </c>
       <c r="J70" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K70">
         <v>3</v>
       </c>
       <c r="L70" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M70" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N70" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O70">
         <v>18.08</v>
@@ -4105,10 +4111,10 @@
         <v>-3.1</v>
       </c>
       <c r="F71" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G71" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H71">
         <v>9700</v>
@@ -4117,19 +4123,19 @@
         <v>9.399999999999999</v>
       </c>
       <c r="J71" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K71">
         <v>9</v>
       </c>
       <c r="L71" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M71" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N71" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O71">
         <v>18.08</v>
@@ -4155,10 +4161,10 @@
         <v>0.5</v>
       </c>
       <c r="F72" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G72" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H72">
         <v>319.85</v>
@@ -4167,19 +4173,19 @@
         <v>10.9</v>
       </c>
       <c r="J72" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K72">
         <v>9</v>
       </c>
       <c r="L72" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M72" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N72" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O72">
         <v>18.08</v>
@@ -4205,10 +4211,10 @@
         <v>0.5</v>
       </c>
       <c r="F73" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G73" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H73">
         <v>2305.6</v>
@@ -4217,19 +4223,19 @@
         <v>11.2</v>
       </c>
       <c r="J73" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K73">
         <v>3</v>
       </c>
       <c r="L73" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M73" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N73" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O73">
         <v>18.08</v>
@@ -4255,10 +4261,10 @@
         <v>0.5</v>
       </c>
       <c r="F74" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G74" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H74">
         <v>3703.3</v>
@@ -4267,19 +4273,19 @@
         <v>11.2</v>
       </c>
       <c r="J74" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K74">
         <v>3</v>
       </c>
       <c r="L74" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M74" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N74" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O74">
         <v>18.08</v>
@@ -4305,10 +4311,10 @@
         <v>0.5</v>
       </c>
       <c r="F75" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G75" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H75">
         <v>4023.5</v>
@@ -4317,19 +4323,19 @@
         <v>12.8</v>
       </c>
       <c r="J75" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K75">
         <v>5</v>
       </c>
       <c r="L75" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M75" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N75" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O75">
         <v>18.08</v>
@@ -4355,10 +4361,10 @@
         <v>0</v>
       </c>
       <c r="F76" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G76" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H76">
         <v>7196</v>
@@ -4367,19 +4373,19 @@
         <v>13.2</v>
       </c>
       <c r="J76" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K76">
         <v>1</v>
       </c>
       <c r="L76" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M76" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N76" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O76">
         <v>18.08</v>
@@ -4405,10 +4411,10 @@
         <v>0.5</v>
       </c>
       <c r="F77" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G77" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H77">
         <v>125</v>
@@ -4417,19 +4423,19 @@
         <v>14.1</v>
       </c>
       <c r="J77" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K77">
         <v>3</v>
       </c>
       <c r="L77" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M77" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N77" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="O77">
         <v>18.08</v>
@@ -4455,10 +4461,10 @@
         <v>0</v>
       </c>
       <c r="F78" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G78" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H78">
         <v>1449.1</v>
@@ -4470,13 +4476,13 @@
         <v>1</v>
       </c>
       <c r="L78" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M78" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N78" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O78">
         <v>18.3</v>
@@ -4502,10 +4508,10 @@
         <v>0</v>
       </c>
       <c r="F79" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G79" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H79">
         <v>3844.3</v>
@@ -4517,13 +4523,13 @@
         <v>1</v>
       </c>
       <c r="L79" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M79" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N79" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O79">
         <v>18.3</v>
@@ -4549,10 +4555,10 @@
         <v>0</v>
       </c>
       <c r="F80" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G80" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H80">
         <v>1330.5</v>
@@ -4564,13 +4570,13 @@
         <v>1</v>
       </c>
       <c r="L80" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M80" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N80" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O80">
         <v>18.3</v>
@@ -4596,10 +4602,10 @@
         <v>0</v>
       </c>
       <c r="F81" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G81" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H81">
         <v>405.4</v>
@@ -4611,13 +4617,13 @@
         <v>1</v>
       </c>
       <c r="L81" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M81" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N81" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O81">
         <v>18.3</v>
@@ -4643,10 +4649,10 @@
         <v>0</v>
       </c>
       <c r="F82" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G82" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H82">
         <v>554.7</v>
@@ -4655,19 +4661,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J82" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K82">
         <v>1</v>
       </c>
       <c r="L82" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M82" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N82" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O82">
         <v>18.3</v>
@@ -4693,10 +4699,10 @@
         <v>0</v>
       </c>
       <c r="F83" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G83" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H83">
         <v>215.65</v>
@@ -4705,19 +4711,19 @@
         <v>1</v>
       </c>
       <c r="J83" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K83">
         <v>4</v>
       </c>
       <c r="L83" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M83" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N83" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O83">
         <v>18.3</v>
@@ -4743,10 +4749,10 @@
         <v>-2.4</v>
       </c>
       <c r="F84" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G84" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H84">
         <v>1379.6</v>
@@ -4755,19 +4761,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J84" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K84">
         <v>10</v>
       </c>
       <c r="L84" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M84" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N84" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O84">
         <v>18.3</v>
@@ -4793,10 +4799,10 @@
         <v>0</v>
       </c>
       <c r="F85" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G85" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H85">
         <v>4454.6</v>
@@ -4805,19 +4811,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J85" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K85">
         <v>10</v>
       </c>
       <c r="L85" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M85" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N85" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O85">
         <v>18.3</v>
@@ -4843,10 +4849,10 @@
         <v>0</v>
       </c>
       <c r="F86" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G86" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H86">
         <v>1044.55</v>
@@ -4855,19 +4861,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J86" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K86">
         <v>10</v>
       </c>
       <c r="L86" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M86" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N86" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O86">
         <v>18.3</v>
@@ -4893,10 +4899,10 @@
         <v>0</v>
       </c>
       <c r="F87" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G87" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H87">
         <v>88.59</v>
@@ -4905,19 +4911,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J87" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K87">
         <v>4</v>
       </c>
       <c r="L87" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M87" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N87" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O87">
         <v>18.3</v>
@@ -4943,10 +4949,10 @@
         <v>0</v>
       </c>
       <c r="F88" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G88" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H88">
         <v>556.95</v>
@@ -4955,19 +4961,19 @@
         <v>4.799999999999997</v>
       </c>
       <c r="J88" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="K88">
         <v>1</v>
       </c>
       <c r="L88" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M88" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N88" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O88">
         <v>18.3</v>
@@ -4993,10 +4999,10 @@
         <v>0</v>
       </c>
       <c r="F89" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G89" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H89">
         <v>1395.8</v>
@@ -5005,19 +5011,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J89" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K89">
         <v>5</v>
       </c>
       <c r="L89" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M89" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N89" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O89">
         <v>18.3</v>
@@ -5043,10 +5049,10 @@
         <v>0</v>
       </c>
       <c r="F90" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G90" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H90">
         <v>5977</v>
@@ -5055,19 +5061,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J90" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K90">
         <v>1</v>
       </c>
       <c r="L90" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M90" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N90" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O90">
         <v>18.3</v>
@@ -5093,10 +5099,10 @@
         <v>1</v>
       </c>
       <c r="F91" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G91" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H91">
         <v>1198.95</v>
@@ -5105,19 +5111,19 @@
         <v>6.399999999999999</v>
       </c>
       <c r="J91" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K91">
         <v>4</v>
       </c>
       <c r="L91" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M91" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N91" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O91">
         <v>18.3</v>
@@ -5143,10 +5149,10 @@
         <v>-6</v>
       </c>
       <c r="F92" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G92" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H92">
         <v>1278.6</v>
@@ -5155,19 +5161,19 @@
         <v>8.899999999999999</v>
       </c>
       <c r="J92" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K92">
         <v>4</v>
       </c>
       <c r="L92" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M92" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N92" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O92">
         <v>18.3</v>
@@ -5193,10 +5199,10 @@
         <v>0</v>
       </c>
       <c r="F93" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G93" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H93">
         <v>9602</v>
@@ -5205,19 +5211,19 @@
         <v>9.399999999999999</v>
       </c>
       <c r="J93" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K93">
         <v>10</v>
       </c>
       <c r="L93" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M93" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N93" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O93">
         <v>18.3</v>
@@ -5243,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="F94" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G94" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H94">
         <v>319.75</v>
@@ -5255,19 +5261,19 @@
         <v>10.9</v>
       </c>
       <c r="J94" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K94">
         <v>10</v>
       </c>
       <c r="L94" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M94" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N94" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O94">
         <v>18.3</v>
@@ -5293,10 +5299,10 @@
         <v>0</v>
       </c>
       <c r="F95" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G95" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H95">
         <v>2307.9</v>
@@ -5305,19 +5311,19 @@
         <v>11.2</v>
       </c>
       <c r="J95" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K95">
         <v>4</v>
       </c>
       <c r="L95" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M95" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N95" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O95">
         <v>18.3</v>
@@ -5343,10 +5349,10 @@
         <v>0</v>
       </c>
       <c r="F96" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G96" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H96">
         <v>4021.1</v>
@@ -5355,19 +5361,19 @@
         <v>12.8</v>
       </c>
       <c r="J96" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K96">
         <v>6</v>
       </c>
       <c r="L96" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M96" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N96" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O96">
         <v>18.3</v>
@@ -5393,10 +5399,10 @@
         <v>0</v>
       </c>
       <c r="F97" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G97" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H97">
         <v>7230</v>
@@ -5405,19 +5411,19 @@
         <v>13.2</v>
       </c>
       <c r="J97" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K97">
         <v>2</v>
       </c>
       <c r="L97" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M97" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N97" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O97">
         <v>18.3</v>
@@ -5443,10 +5449,10 @@
         <v>0</v>
       </c>
       <c r="F98" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G98" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H98">
         <v>3844.3</v>
@@ -5458,13 +5464,13 @@
         <v>1</v>
       </c>
       <c r="L98" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M98" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N98" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O98">
         <v>18.3</v>
@@ -5490,10 +5496,10 @@
         <v>0</v>
       </c>
       <c r="F99" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G99" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H99">
         <v>1330.5</v>
@@ -5502,19 +5508,19 @@
         <v>0.09999999999999432</v>
       </c>
       <c r="J99" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K99">
         <v>1</v>
       </c>
       <c r="L99" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M99" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N99" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O99">
         <v>18.3</v>
@@ -5540,10 +5546,10 @@
         <v>0</v>
       </c>
       <c r="F100" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G100" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H100">
         <v>405.4</v>
@@ -5552,19 +5558,19 @@
         <v>0.7000000000000028</v>
       </c>
       <c r="J100" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K100">
         <v>1</v>
       </c>
       <c r="L100" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M100" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N100" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O100">
         <v>18.3</v>
@@ -5590,10 +5596,10 @@
         <v>-1.2</v>
       </c>
       <c r="F101" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G101" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H101">
         <v>554.7</v>
@@ -5602,19 +5608,19 @@
         <v>1.599999999999994</v>
       </c>
       <c r="J101" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K101">
         <v>2</v>
       </c>
       <c r="L101" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M101" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N101" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O101">
         <v>18.3</v>
@@ -5640,10 +5646,10 @@
         <v>-1.2</v>
       </c>
       <c r="F102" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G102" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H102">
         <v>215.65</v>
@@ -5652,19 +5658,19 @@
         <v>2.200000000000003</v>
       </c>
       <c r="J102" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K102">
         <v>5</v>
       </c>
       <c r="L102" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M102" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N102" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O102">
         <v>18.3</v>
@@ -5690,10 +5696,10 @@
         <v>-1.2</v>
       </c>
       <c r="F103" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G103" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H103">
         <v>1379.6</v>
@@ -5702,19 +5708,19 @@
         <v>4</v>
       </c>
       <c r="J103" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K103">
         <v>11</v>
       </c>
       <c r="L103" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M103" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N103" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O103">
         <v>18.3</v>
@@ -5740,10 +5746,10 @@
         <v>-1.2</v>
       </c>
       <c r="F104" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G104" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H104">
         <v>4454.6</v>
@@ -5752,19 +5758,19 @@
         <v>4</v>
       </c>
       <c r="J104" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K104">
         <v>11</v>
       </c>
       <c r="L104" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M104" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N104" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O104">
         <v>18.3</v>
@@ -5790,10 +5796,10 @@
         <v>-1.2</v>
       </c>
       <c r="F105" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G105" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H105">
         <v>1044.55</v>
@@ -5802,19 +5808,19 @@
         <v>4</v>
       </c>
       <c r="J105" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K105">
         <v>11</v>
       </c>
       <c r="L105" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M105" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N105" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O105">
         <v>18.3</v>
@@ -5840,10 +5846,10 @@
         <v>-1.2</v>
       </c>
       <c r="F106" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G106" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H106">
         <v>88.59</v>
@@ -5852,19 +5858,19 @@
         <v>4</v>
       </c>
       <c r="J106" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K106">
         <v>5</v>
       </c>
       <c r="L106" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M106" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N106" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O106">
         <v>18.3</v>
@@ -5890,10 +5896,10 @@
         <v>-1.2</v>
       </c>
       <c r="F107" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G107" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H107">
         <v>556.95</v>
@@ -5902,19 +5908,19 @@
         <v>6</v>
       </c>
       <c r="J107" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="K107">
         <v>2</v>
       </c>
       <c r="L107" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M107" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N107" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O107">
         <v>18.3</v>
@@ -5940,10 +5946,10 @@
         <v>-1.2</v>
       </c>
       <c r="F108" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G108" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H108">
         <v>1395.8</v>
@@ -5952,19 +5958,19 @@
         <v>6.600000000000001</v>
       </c>
       <c r="J108" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K108">
         <v>6</v>
       </c>
       <c r="L108" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M108" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N108" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O108">
         <v>18.3</v>
@@ -5990,10 +5996,10 @@
         <v>-1.2</v>
       </c>
       <c r="F109" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G109" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H109">
         <v>5977</v>
@@ -6002,19 +6008,19 @@
         <v>6.600000000000001</v>
       </c>
       <c r="J109" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K109">
         <v>2</v>
       </c>
       <c r="L109" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M109" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N109" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O109">
         <v>18.3</v>
@@ -6040,10 +6046,10 @@
         <v>-1.2</v>
       </c>
       <c r="F110" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G110" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H110">
         <v>1198.95</v>
@@ -6052,19 +6058,19 @@
         <v>7.600000000000001</v>
       </c>
       <c r="J110" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K110">
         <v>5</v>
       </c>
       <c r="L110" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M110" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N110" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O110">
         <v>18.3</v>
@@ -6090,10 +6096,10 @@
         <v>-1.2</v>
       </c>
       <c r="F111" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G111" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H111">
         <v>1278.6</v>
@@ -6102,19 +6108,19 @@
         <v>10.1</v>
       </c>
       <c r="J111" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K111">
         <v>5</v>
       </c>
       <c r="L111" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M111" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N111" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O111">
         <v>18.3</v>
@@ -6140,10 +6146,10 @@
         <v>-1.2</v>
       </c>
       <c r="F112" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G112" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H112">
         <v>9602</v>
@@ -6152,19 +6158,19 @@
         <v>10.6</v>
       </c>
       <c r="J112" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K112">
         <v>11</v>
       </c>
       <c r="L112" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M112" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N112" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O112">
         <v>18.3</v>
@@ -6190,10 +6196,10 @@
         <v>-1.2</v>
       </c>
       <c r="F113" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G113" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H113">
         <v>319.75</v>
@@ -6202,19 +6208,19 @@
         <v>12.1</v>
       </c>
       <c r="J113" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K113">
         <v>11</v>
       </c>
       <c r="L113" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M113" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N113" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O113">
         <v>18.3</v>
@@ -6240,10 +6246,10 @@
         <v>-1.2</v>
       </c>
       <c r="F114" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G114" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H114">
         <v>2307.9</v>
@@ -6252,19 +6258,19 @@
         <v>12.4</v>
       </c>
       <c r="J114" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K114">
         <v>5</v>
       </c>
       <c r="L114" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M114" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N114" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O114">
         <v>18.3</v>
@@ -6290,10 +6296,10 @@
         <v>-1.2</v>
       </c>
       <c r="F115" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G115" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H115">
         <v>4021.1</v>
@@ -6302,19 +6308,19 @@
         <v>14</v>
       </c>
       <c r="J115" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K115">
         <v>7</v>
       </c>
       <c r="L115" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M115" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N115" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O115">
         <v>18.3</v>
@@ -6340,10 +6346,10 @@
         <v>-1.2</v>
       </c>
       <c r="F116" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G116" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H116">
         <v>7230</v>
@@ -6352,19 +6358,19 @@
         <v>14.4</v>
       </c>
       <c r="J116" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K116">
         <v>3</v>
       </c>
       <c r="L116" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M116" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N116" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="O116">
         <v>18.3</v>
@@ -6390,10 +6396,10 @@
         <v>6.5</v>
       </c>
       <c r="F117" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G117" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H117">
         <v>1263</v>
@@ -6402,19 +6408,19 @@
         <v>3.599999999999994</v>
       </c>
       <c r="J117" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K117">
         <v>6</v>
       </c>
       <c r="L117" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M117" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N117" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O117">
         <v>18.7</v>
@@ -6440,10 +6446,10 @@
         <v>0</v>
       </c>
       <c r="F118" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G118" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H118">
         <v>123.95</v>
@@ -6452,19 +6458,19 @@
         <v>5.5</v>
       </c>
       <c r="J118" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K118">
         <v>1</v>
       </c>
       <c r="L118" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M118" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N118" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O118">
         <v>18.7</v>
@@ -6490,10 +6496,10 @@
         <v>-2</v>
       </c>
       <c r="F119" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G119" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H119">
         <v>1371.6</v>
@@ -6502,19 +6508,19 @@
         <v>6</v>
       </c>
       <c r="J119" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K119">
         <v>12</v>
       </c>
       <c r="L119" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M119" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N119" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O119">
         <v>18.7</v>
@@ -6540,10 +6546,10 @@
         <v>-2</v>
       </c>
       <c r="F120" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G120" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H120">
         <v>4460</v>
@@ -6552,19 +6558,19 @@
         <v>6</v>
       </c>
       <c r="J120" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K120">
         <v>12</v>
       </c>
       <c r="L120" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M120" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N120" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O120">
         <v>18.7</v>
@@ -6590,10 +6596,10 @@
         <v>6.4</v>
       </c>
       <c r="F121" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G121" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H121">
         <v>2358.2</v>
@@ -6602,19 +6608,19 @@
         <v>6</v>
       </c>
       <c r="J121" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K121">
         <v>6</v>
       </c>
       <c r="L121" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M121" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N121" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O121">
         <v>18.7</v>
@@ -6640,10 +6646,10 @@
         <v>-5.4</v>
       </c>
       <c r="F122" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G122" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H122">
         <v>402.65</v>
@@ -6652,19 +6658,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J122" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K122">
         <v>2</v>
       </c>
       <c r="L122" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M122" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N122" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O122">
         <v>18.7</v>
@@ -6690,10 +6696,10 @@
         <v>0</v>
       </c>
       <c r="F123" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G123" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H123">
         <v>3858.9</v>
@@ -6702,19 +6708,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J123" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K123">
         <v>1</v>
       </c>
       <c r="L123" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M123" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N123" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O123">
         <v>18.7</v>
@@ -6740,10 +6746,10 @@
         <v>4</v>
       </c>
       <c r="F124" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G124" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H124">
         <v>320.55</v>
@@ -6752,19 +6758,19 @@
         <v>8.100000000000001</v>
       </c>
       <c r="J124" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K124">
         <v>12</v>
       </c>
       <c r="L124" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M124" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N124" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O124">
         <v>18.7</v>
@@ -6790,10 +6796,10 @@
         <v>-6.4</v>
       </c>
       <c r="F125" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G125" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H125">
         <v>214.68</v>
@@ -6802,19 +6808,19 @@
         <v>8.600000000000001</v>
       </c>
       <c r="J125" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K125">
         <v>6</v>
       </c>
       <c r="L125" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M125" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N125" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O125">
         <v>18.7</v>
@@ -6840,10 +6846,10 @@
         <v>-5</v>
       </c>
       <c r="F126" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G126" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H126">
         <v>1019.75</v>
@@ -6852,19 +6858,19 @@
         <v>9</v>
       </c>
       <c r="J126" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K126">
         <v>12</v>
       </c>
       <c r="L126" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M126" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N126" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O126">
         <v>18.7</v>
@@ -6890,10 +6896,10 @@
         <v>-5</v>
       </c>
       <c r="F127" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G127" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H127">
         <v>86.98</v>
@@ -6902,19 +6908,19 @@
         <v>9</v>
       </c>
       <c r="J127" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K127">
         <v>6</v>
       </c>
       <c r="L127" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M127" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N127" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O127">
         <v>18.7</v>
@@ -6940,10 +6946,10 @@
         <v>0</v>
       </c>
       <c r="F128" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G128" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H128">
         <v>125.61</v>
@@ -6952,19 +6958,19 @@
         <v>10</v>
       </c>
       <c r="J128" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K128">
         <v>1</v>
       </c>
       <c r="L128" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M128" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N128" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O128">
         <v>18.7</v>
@@ -6990,10 +6996,10 @@
         <v>-4</v>
       </c>
       <c r="F129" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G129" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H129">
         <v>1404.6</v>
@@ -7002,19 +7008,19 @@
         <v>10.6</v>
       </c>
       <c r="J129" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K129">
         <v>7</v>
       </c>
       <c r="L129" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M129" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N129" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O129">
         <v>18.7</v>
@@ -7040,10 +7046,10 @@
         <v>-3</v>
       </c>
       <c r="F130" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G130" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H130">
         <v>1217.2</v>
@@ -7052,19 +7058,19 @@
         <v>10.6</v>
       </c>
       <c r="J130" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K130">
         <v>6</v>
       </c>
       <c r="L130" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M130" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N130" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O130">
         <v>18.7</v>
@@ -7090,10 +7096,10 @@
         <v>0</v>
       </c>
       <c r="F131" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G131" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H131">
         <v>445.5</v>
@@ -7102,19 +7108,19 @@
         <v>12.7</v>
       </c>
       <c r="J131" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K131">
         <v>1</v>
       </c>
       <c r="L131" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M131" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N131" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O131">
         <v>18.7</v>
@@ -7140,10 +7146,10 @@
         <v>-3.8</v>
       </c>
       <c r="F132" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G132" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H132">
         <v>9519</v>
@@ -7152,19 +7158,19 @@
         <v>14.4</v>
       </c>
       <c r="J132" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K132">
         <v>12</v>
       </c>
       <c r="L132" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M132" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N132" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="O132">
         <v>18.7</v>
@@ -7174,8 +7180,8 @@
       </c>
     </row>
     <row r="133" spans="1:16">
-      <c r="A133" t="s">
-        <v>16</v>
+      <c r="A133">
+        <v>20260423</v>
       </c>
       <c r="B133" t="s">
         <v>43</v>
@@ -7186,14 +7192,14 @@
       <c r="D133">
         <v>66.40000000000001</v>
       </c>
-      <c r="E133" t="s">
-        <v>59</v>
+      <c r="E133">
+        <v>0</v>
       </c>
       <c r="F133" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G133" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H133">
         <v>1263.2</v>
@@ -7202,19 +7208,19 @@
         <v>3.599999999999994</v>
       </c>
       <c r="J133" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K133">
         <v>7</v>
       </c>
       <c r="L133" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M133" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N133" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O133">
         <v>18.84</v>
@@ -7224,8 +7230,8 @@
       </c>
     </row>
     <row r="134" spans="1:16">
-      <c r="A134" t="s">
-        <v>16</v>
+      <c r="A134">
+        <v>20260423</v>
       </c>
       <c r="B134" t="s">
         <v>49</v>
@@ -7236,14 +7242,14 @@
       <c r="D134">
         <v>64.5</v>
       </c>
-      <c r="E134" t="s">
-        <v>59</v>
+      <c r="E134">
+        <v>0</v>
       </c>
       <c r="F134" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G134" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H134">
         <v>124.1</v>
@@ -7252,19 +7258,19 @@
         <v>5.5</v>
       </c>
       <c r="J134" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K134">
         <v>2</v>
       </c>
       <c r="L134" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M134" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N134" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O134">
         <v>18.84</v>
@@ -7274,8 +7280,8 @@
       </c>
     </row>
     <row r="135" spans="1:16">
-      <c r="A135" t="s">
-        <v>16</v>
+      <c r="A135">
+        <v>20260423</v>
       </c>
       <c r="B135" t="s">
         <v>22</v>
@@ -7286,14 +7292,14 @@
       <c r="D135">
         <v>64</v>
       </c>
-      <c r="E135" t="s">
-        <v>59</v>
+      <c r="E135">
+        <v>0</v>
       </c>
       <c r="F135" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G135" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H135">
         <v>1371.2</v>
@@ -7302,19 +7308,19 @@
         <v>6</v>
       </c>
       <c r="J135" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K135">
         <v>13</v>
       </c>
       <c r="L135" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M135" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N135" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O135">
         <v>18.84</v>
@@ -7324,8 +7330,8 @@
       </c>
     </row>
     <row r="136" spans="1:16">
-      <c r="A136" t="s">
-        <v>16</v>
+      <c r="A136">
+        <v>20260423</v>
       </c>
       <c r="B136" t="s">
         <v>23</v>
@@ -7336,14 +7342,14 @@
       <c r="D136">
         <v>64</v>
       </c>
-      <c r="E136" t="s">
-        <v>59</v>
+      <c r="E136">
+        <v>0</v>
       </c>
       <c r="F136" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G136" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H136">
         <v>4440.2</v>
@@ -7352,19 +7358,19 @@
         <v>6</v>
       </c>
       <c r="J136" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K136">
         <v>13</v>
       </c>
       <c r="L136" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M136" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N136" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O136">
         <v>18.84</v>
@@ -7374,8 +7380,8 @@
       </c>
     </row>
     <row r="137" spans="1:16">
-      <c r="A137" t="s">
-        <v>16</v>
+      <c r="A137">
+        <v>20260423</v>
       </c>
       <c r="B137" t="s">
         <v>46</v>
@@ -7386,14 +7392,14 @@
       <c r="D137">
         <v>64</v>
       </c>
-      <c r="E137" t="s">
-        <v>59</v>
+      <c r="E137">
+        <v>0</v>
       </c>
       <c r="F137" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G137" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H137">
         <v>2353.4</v>
@@ -7402,19 +7408,19 @@
         <v>6</v>
       </c>
       <c r="J137" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K137">
         <v>7</v>
       </c>
       <c r="L137" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M137" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N137" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O137">
         <v>18.84</v>
@@ -7424,8 +7430,8 @@
       </c>
     </row>
     <row r="138" spans="1:16">
-      <c r="A138" t="s">
-        <v>16</v>
+      <c r="A138">
+        <v>20260423</v>
       </c>
       <c r="B138" t="s">
         <v>39</v>
@@ -7436,14 +7442,14 @@
       <c r="D138">
         <v>63.9</v>
       </c>
-      <c r="E138" t="s">
-        <v>59</v>
+      <c r="E138">
+        <v>0</v>
       </c>
       <c r="F138" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G138" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H138">
         <v>400.9</v>
@@ -7452,19 +7458,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J138" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K138">
         <v>3</v>
       </c>
       <c r="L138" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M138" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N138" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O138">
         <v>18.84</v>
@@ -7474,8 +7480,8 @@
       </c>
     </row>
     <row r="139" spans="1:16">
-      <c r="A139" t="s">
-        <v>16</v>
+      <c r="A139">
+        <v>20260423</v>
       </c>
       <c r="B139" t="s">
         <v>40</v>
@@ -7486,14 +7492,14 @@
       <c r="D139">
         <v>63.9</v>
       </c>
-      <c r="E139" t="s">
-        <v>59</v>
+      <c r="E139">
+        <v>0</v>
       </c>
       <c r="F139" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G139" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H139">
         <v>3856.3</v>
@@ -7502,19 +7508,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J139" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K139">
         <v>2</v>
       </c>
       <c r="L139" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M139" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N139" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O139">
         <v>18.84</v>
@@ -7524,8 +7530,8 @@
       </c>
     </row>
     <row r="140" spans="1:16">
-      <c r="A140" t="s">
-        <v>16</v>
+      <c r="A140">
+        <v>20260423</v>
       </c>
       <c r="B140" t="s">
         <v>41</v>
@@ -7536,14 +7542,14 @@
       <c r="D140">
         <v>61.4</v>
       </c>
-      <c r="E140" t="s">
-        <v>59</v>
+      <c r="E140">
+        <v>0</v>
       </c>
       <c r="F140" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G140" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H140">
         <v>214.69</v>
@@ -7552,19 +7558,19 @@
         <v>8.600000000000001</v>
       </c>
       <c r="J140" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K140">
         <v>7</v>
       </c>
       <c r="L140" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M140" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N140" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O140">
         <v>18.84</v>
@@ -7574,8 +7580,8 @@
       </c>
     </row>
     <row r="141" spans="1:16">
-      <c r="A141" t="s">
-        <v>16</v>
+      <c r="A141">
+        <v>20260423</v>
       </c>
       <c r="B141" t="s">
         <v>24</v>
@@ -7586,14 +7592,14 @@
       <c r="D141">
         <v>61</v>
       </c>
-      <c r="E141" t="s">
-        <v>59</v>
+      <c r="E141">
+        <v>0</v>
       </c>
       <c r="F141" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G141" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H141">
         <v>1020.55</v>
@@ -7602,19 +7608,19 @@
         <v>9</v>
       </c>
       <c r="J141" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K141">
         <v>13</v>
       </c>
       <c r="L141" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M141" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N141" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O141">
         <v>18.84</v>
@@ -7624,8 +7630,8 @@
       </c>
     </row>
     <row r="142" spans="1:16">
-      <c r="A142" t="s">
-        <v>16</v>
+      <c r="A142">
+        <v>20260423</v>
       </c>
       <c r="B142" t="s">
         <v>42</v>
@@ -7636,14 +7642,14 @@
       <c r="D142">
         <v>61</v>
       </c>
-      <c r="E142" t="s">
-        <v>59</v>
+      <c r="E142">
+        <v>0</v>
       </c>
       <c r="F142" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G142" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H142">
         <v>87.06999999999999</v>
@@ -7652,19 +7658,19 @@
         <v>9</v>
       </c>
       <c r="J142" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K142">
         <v>7</v>
       </c>
       <c r="L142" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M142" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N142" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O142">
         <v>18.84</v>
@@ -7674,8 +7680,8 @@
       </c>
     </row>
     <row r="143" spans="1:16">
-      <c r="A143" t="s">
-        <v>16</v>
+      <c r="A143">
+        <v>20260423</v>
       </c>
       <c r="B143" t="s">
         <v>44</v>
@@ -7686,14 +7692,14 @@
       <c r="D143">
         <v>60</v>
       </c>
-      <c r="E143" t="s">
-        <v>59</v>
+      <c r="E143">
+        <v>0</v>
       </c>
       <c r="F143" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G143" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H143">
         <v>125.46</v>
@@ -7702,19 +7708,19 @@
         <v>10</v>
       </c>
       <c r="J143" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K143">
         <v>2</v>
       </c>
       <c r="L143" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M143" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N143" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O143">
         <v>18.84</v>
@@ -7724,8 +7730,8 @@
       </c>
     </row>
     <row r="144" spans="1:16">
-      <c r="A144" t="s">
-        <v>16</v>
+      <c r="A144">
+        <v>20260423</v>
       </c>
       <c r="B144" t="s">
         <v>32</v>
@@ -7736,14 +7742,14 @@
       <c r="D144">
         <v>59.4</v>
       </c>
-      <c r="E144" t="s">
-        <v>59</v>
+      <c r="E144">
+        <v>0</v>
       </c>
       <c r="F144" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G144" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H144">
         <v>1401.1</v>
@@ -7752,19 +7758,19 @@
         <v>10.6</v>
       </c>
       <c r="J144" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K144">
         <v>8</v>
       </c>
       <c r="L144" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="M144" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N144" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O144">
         <v>18.84</v>
@@ -7774,8 +7780,8 @@
       </c>
     </row>
     <row r="145" spans="1:16">
-      <c r="A145" t="s">
-        <v>16</v>
+      <c r="A145">
+        <v>20260423</v>
       </c>
       <c r="B145" t="s">
         <v>45</v>
@@ -7786,14 +7792,14 @@
       <c r="D145">
         <v>59.4</v>
       </c>
-      <c r="E145" t="s">
-        <v>59</v>
+      <c r="E145">
+        <v>0</v>
       </c>
       <c r="F145" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G145" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H145">
         <v>1218.2</v>
@@ -7802,19 +7808,19 @@
         <v>10.6</v>
       </c>
       <c r="J145" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K145">
         <v>7</v>
       </c>
       <c r="L145" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M145" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N145" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O145">
         <v>18.84</v>
@@ -7824,8 +7830,8 @@
       </c>
     </row>
     <row r="146" spans="1:16">
-      <c r="A146" t="s">
-        <v>16</v>
+      <c r="A146">
+        <v>20260423</v>
       </c>
       <c r="B146" t="s">
         <v>56</v>
@@ -7836,14 +7842,14 @@
       <c r="D146">
         <v>57.3</v>
       </c>
-      <c r="E146" t="s">
-        <v>59</v>
+      <c r="E146">
+        <v>0</v>
       </c>
       <c r="F146" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G146" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H146">
         <v>445.65</v>
@@ -7852,19 +7858,19 @@
         <v>12.7</v>
       </c>
       <c r="J146" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K146">
         <v>2</v>
       </c>
       <c r="L146" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="M146" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N146" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O146">
         <v>18.84</v>
@@ -7874,8 +7880,8 @@
       </c>
     </row>
     <row r="147" spans="1:16">
-      <c r="A147" t="s">
-        <v>16</v>
+      <c r="A147">
+        <v>20260423</v>
       </c>
       <c r="B147" t="s">
         <v>37</v>
@@ -7886,14 +7892,14 @@
       <c r="D147">
         <v>55.9</v>
       </c>
-      <c r="E147" t="s">
-        <v>60</v>
+      <c r="E147">
+        <v>-6</v>
       </c>
       <c r="F147" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G147" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H147">
         <v>319.85</v>
@@ -7902,19 +7908,19 @@
         <v>14.1</v>
       </c>
       <c r="J147" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="K147">
         <v>13</v>
       </c>
       <c r="L147" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M147" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N147" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O147">
         <v>18.84</v>
@@ -7924,8 +7930,8 @@
       </c>
     </row>
     <row r="148" spans="1:16">
-      <c r="A148" t="s">
-        <v>16</v>
+      <c r="A148">
+        <v>20260423</v>
       </c>
       <c r="B148" t="s">
         <v>33</v>
@@ -7936,14 +7942,14 @@
       <c r="D148">
         <v>55.6</v>
       </c>
-      <c r="E148" t="s">
-        <v>59</v>
+      <c r="E148">
+        <v>0</v>
       </c>
       <c r="F148" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="G148" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="H148">
         <v>9545.5</v>
@@ -7952,25 +7958,825 @@
         <v>14.4</v>
       </c>
       <c r="J148" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K148">
         <v>13</v>
       </c>
       <c r="L148" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="M148" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N148" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="O148">
         <v>18.84</v>
       </c>
       <c r="P148">
         <v>320</v>
+      </c>
+    </row>
+    <row r="149" spans="1:16">
+      <c r="A149" t="s">
+        <v>16</v>
+      </c>
+      <c r="B149" t="s">
+        <v>43</v>
+      </c>
+      <c r="C149" t="s">
+        <v>58</v>
+      </c>
+      <c r="D149">
+        <v>66.90000000000001</v>
+      </c>
+      <c r="E149" t="s">
+        <v>59</v>
+      </c>
+      <c r="F149" t="s">
+        <v>63</v>
+      </c>
+      <c r="G149" t="s">
+        <v>64</v>
+      </c>
+      <c r="H149">
+        <v>1262.7</v>
+      </c>
+      <c r="I149">
+        <v>3.099999999999994</v>
+      </c>
+      <c r="J149" t="s">
+        <v>66</v>
+      </c>
+      <c r="K149">
+        <v>8</v>
+      </c>
+      <c r="L149" t="s">
+        <v>78</v>
+      </c>
+      <c r="M149" t="s">
+        <v>80</v>
+      </c>
+      <c r="N149" t="s">
+        <v>85</v>
+      </c>
+      <c r="O149">
+        <v>18.44</v>
+      </c>
+      <c r="P149">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="150" spans="1:16">
+      <c r="A150" t="s">
+        <v>16</v>
+      </c>
+      <c r="B150" t="s">
+        <v>39</v>
+      </c>
+      <c r="C150" t="s">
+        <v>58</v>
+      </c>
+      <c r="D150">
+        <v>66.8</v>
+      </c>
+      <c r="E150" t="s">
+        <v>60</v>
+      </c>
+      <c r="F150" t="s">
+        <v>63</v>
+      </c>
+      <c r="G150" t="s">
+        <v>64</v>
+      </c>
+      <c r="H150">
+        <v>404.6</v>
+      </c>
+      <c r="I150">
+        <v>3.200000000000003</v>
+      </c>
+      <c r="J150" t="s">
+        <v>66</v>
+      </c>
+      <c r="K150">
+        <v>4</v>
+      </c>
+      <c r="L150" t="s">
+        <v>78</v>
+      </c>
+      <c r="M150" t="s">
+        <v>80</v>
+      </c>
+      <c r="N150" t="s">
+        <v>85</v>
+      </c>
+      <c r="O150">
+        <v>18.44</v>
+      </c>
+      <c r="P150">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="151" spans="1:16">
+      <c r="A151" t="s">
+        <v>16</v>
+      </c>
+      <c r="B151" t="s">
+        <v>49</v>
+      </c>
+      <c r="C151" t="s">
+        <v>58</v>
+      </c>
+      <c r="D151">
+        <v>65</v>
+      </c>
+      <c r="E151" t="s">
+        <v>59</v>
+      </c>
+      <c r="F151" t="s">
+        <v>63</v>
+      </c>
+      <c r="G151" t="s">
+        <v>64</v>
+      </c>
+      <c r="H151">
+        <v>124.38</v>
+      </c>
+      <c r="I151">
+        <v>5</v>
+      </c>
+      <c r="J151" t="s">
+        <v>67</v>
+      </c>
+      <c r="K151">
+        <v>3</v>
+      </c>
+      <c r="L151" t="s">
+        <v>79</v>
+      </c>
+      <c r="M151" t="s">
+        <v>80</v>
+      </c>
+      <c r="N151" t="s">
+        <v>85</v>
+      </c>
+      <c r="O151">
+        <v>18.44</v>
+      </c>
+      <c r="P151">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="152" spans="1:16">
+      <c r="A152" t="s">
+        <v>16</v>
+      </c>
+      <c r="B152" t="s">
+        <v>22</v>
+      </c>
+      <c r="C152" t="s">
+        <v>58</v>
+      </c>
+      <c r="D152">
+        <v>64.5</v>
+      </c>
+      <c r="E152" t="s">
+        <v>59</v>
+      </c>
+      <c r="F152" t="s">
+        <v>63</v>
+      </c>
+      <c r="G152" t="s">
+        <v>64</v>
+      </c>
+      <c r="H152">
+        <v>1376.9</v>
+      </c>
+      <c r="I152">
+        <v>5.5</v>
+      </c>
+      <c r="J152" t="s">
+        <v>66</v>
+      </c>
+      <c r="K152">
+        <v>14</v>
+      </c>
+      <c r="L152" t="s">
+        <v>76</v>
+      </c>
+      <c r="M152" t="s">
+        <v>80</v>
+      </c>
+      <c r="N152" t="s">
+        <v>85</v>
+      </c>
+      <c r="O152">
+        <v>18.44</v>
+      </c>
+      <c r="P152">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="153" spans="1:16">
+      <c r="A153" t="s">
+        <v>16</v>
+      </c>
+      <c r="B153" t="s">
+        <v>23</v>
+      </c>
+      <c r="C153" t="s">
+        <v>58</v>
+      </c>
+      <c r="D153">
+        <v>64.5</v>
+      </c>
+      <c r="E153" t="s">
+        <v>59</v>
+      </c>
+      <c r="F153" t="s">
+        <v>63</v>
+      </c>
+      <c r="G153" t="s">
+        <v>64</v>
+      </c>
+      <c r="H153">
+        <v>4456.2</v>
+      </c>
+      <c r="I153">
+        <v>5.5</v>
+      </c>
+      <c r="J153" t="s">
+        <v>66</v>
+      </c>
+      <c r="K153">
+        <v>14</v>
+      </c>
+      <c r="L153" t="s">
+        <v>76</v>
+      </c>
+      <c r="M153" t="s">
+        <v>80</v>
+      </c>
+      <c r="N153" t="s">
+        <v>85</v>
+      </c>
+      <c r="O153">
+        <v>18.44</v>
+      </c>
+      <c r="P153">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="154" spans="1:16">
+      <c r="A154" t="s">
+        <v>16</v>
+      </c>
+      <c r="B154" t="s">
+        <v>46</v>
+      </c>
+      <c r="C154" t="s">
+        <v>58</v>
+      </c>
+      <c r="D154">
+        <v>64.5</v>
+      </c>
+      <c r="E154" t="s">
+        <v>59</v>
+      </c>
+      <c r="F154" t="s">
+        <v>63</v>
+      </c>
+      <c r="G154" t="s">
+        <v>64</v>
+      </c>
+      <c r="H154">
+        <v>2358.9</v>
+      </c>
+      <c r="I154">
+        <v>5.5</v>
+      </c>
+      <c r="J154" t="s">
+        <v>66</v>
+      </c>
+      <c r="K154">
+        <v>8</v>
+      </c>
+      <c r="L154" t="s">
+        <v>78</v>
+      </c>
+      <c r="M154" t="s">
+        <v>80</v>
+      </c>
+      <c r="N154" t="s">
+        <v>85</v>
+      </c>
+      <c r="O154">
+        <v>18.44</v>
+      </c>
+      <c r="P154">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="155" spans="1:16">
+      <c r="A155" t="s">
+        <v>16</v>
+      </c>
+      <c r="B155" t="s">
+        <v>40</v>
+      </c>
+      <c r="C155" t="s">
+        <v>58</v>
+      </c>
+      <c r="D155">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="E155" t="s">
+        <v>59</v>
+      </c>
+      <c r="F155" t="s">
+        <v>63</v>
+      </c>
+      <c r="G155" t="s">
+        <v>64</v>
+      </c>
+      <c r="H155">
+        <v>3875.6</v>
+      </c>
+      <c r="I155">
+        <v>5.599999999999994</v>
+      </c>
+      <c r="J155" t="s">
+        <v>66</v>
+      </c>
+      <c r="K155">
+        <v>3</v>
+      </c>
+      <c r="L155" t="s">
+        <v>79</v>
+      </c>
+      <c r="M155" t="s">
+        <v>80</v>
+      </c>
+      <c r="N155" t="s">
+        <v>85</v>
+      </c>
+      <c r="O155">
+        <v>18.44</v>
+      </c>
+      <c r="P155">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="156" spans="1:16">
+      <c r="A156" t="s">
+        <v>16</v>
+      </c>
+      <c r="B156" t="s">
+        <v>45</v>
+      </c>
+      <c r="C156" t="s">
+        <v>58</v>
+      </c>
+      <c r="D156">
+        <v>63.3</v>
+      </c>
+      <c r="E156" t="s">
+        <v>61</v>
+      </c>
+      <c r="F156" t="s">
+        <v>63</v>
+      </c>
+      <c r="G156" t="s">
+        <v>64</v>
+      </c>
+      <c r="H156">
+        <v>1231.65</v>
+      </c>
+      <c r="I156">
+        <v>6.700000000000003</v>
+      </c>
+      <c r="J156" t="s">
+        <v>68</v>
+      </c>
+      <c r="K156">
+        <v>8</v>
+      </c>
+      <c r="L156" t="s">
+        <v>78</v>
+      </c>
+      <c r="M156" t="s">
+        <v>80</v>
+      </c>
+      <c r="N156" t="s">
+        <v>85</v>
+      </c>
+      <c r="O156">
+        <v>18.44</v>
+      </c>
+      <c r="P156">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="157" spans="1:16">
+      <c r="A157" t="s">
+        <v>16</v>
+      </c>
+      <c r="B157" t="s">
+        <v>41</v>
+      </c>
+      <c r="C157" t="s">
+        <v>58</v>
+      </c>
+      <c r="D157">
+        <v>62.9</v>
+      </c>
+      <c r="E157" t="s">
+        <v>62</v>
+      </c>
+      <c r="F157" t="s">
+        <v>63</v>
+      </c>
+      <c r="G157" t="s">
+        <v>64</v>
+      </c>
+      <c r="H157">
+        <v>215.19</v>
+      </c>
+      <c r="I157">
+        <v>7.100000000000001</v>
+      </c>
+      <c r="J157" t="s">
+        <v>68</v>
+      </c>
+      <c r="K157">
+        <v>8</v>
+      </c>
+      <c r="L157" t="s">
+        <v>78</v>
+      </c>
+      <c r="M157" t="s">
+        <v>80</v>
+      </c>
+      <c r="N157" t="s">
+        <v>85</v>
+      </c>
+      <c r="O157">
+        <v>18.44</v>
+      </c>
+      <c r="P157">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16">
+      <c r="A158" t="s">
+        <v>16</v>
+      </c>
+      <c r="B158" t="s">
+        <v>24</v>
+      </c>
+      <c r="C158" t="s">
+        <v>58</v>
+      </c>
+      <c r="D158">
+        <v>61.5</v>
+      </c>
+      <c r="E158" t="s">
+        <v>59</v>
+      </c>
+      <c r="F158" t="s">
+        <v>63</v>
+      </c>
+      <c r="G158" t="s">
+        <v>64</v>
+      </c>
+      <c r="H158">
+        <v>1016.45</v>
+      </c>
+      <c r="I158">
+        <v>8.5</v>
+      </c>
+      <c r="J158" t="s">
+        <v>66</v>
+      </c>
+      <c r="K158">
+        <v>14</v>
+      </c>
+      <c r="L158" t="s">
+        <v>76</v>
+      </c>
+      <c r="M158" t="s">
+        <v>80</v>
+      </c>
+      <c r="N158" t="s">
+        <v>85</v>
+      </c>
+      <c r="O158">
+        <v>18.44</v>
+      </c>
+      <c r="P158">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16">
+      <c r="A159" t="s">
+        <v>16</v>
+      </c>
+      <c r="B159" t="s">
+        <v>42</v>
+      </c>
+      <c r="C159" t="s">
+        <v>58</v>
+      </c>
+      <c r="D159">
+        <v>61.5</v>
+      </c>
+      <c r="E159" t="s">
+        <v>59</v>
+      </c>
+      <c r="F159" t="s">
+        <v>63</v>
+      </c>
+      <c r="G159" t="s">
+        <v>64</v>
+      </c>
+      <c r="H159">
+        <v>87.40000000000001</v>
+      </c>
+      <c r="I159">
+        <v>8.5</v>
+      </c>
+      <c r="J159" t="s">
+        <v>66</v>
+      </c>
+      <c r="K159">
+        <v>8</v>
+      </c>
+      <c r="L159" t="s">
+        <v>78</v>
+      </c>
+      <c r="M159" t="s">
+        <v>80</v>
+      </c>
+      <c r="N159" t="s">
+        <v>85</v>
+      </c>
+      <c r="O159">
+        <v>18.44</v>
+      </c>
+      <c r="P159">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="160" spans="1:16">
+      <c r="A160" t="s">
+        <v>16</v>
+      </c>
+      <c r="B160" t="s">
+        <v>32</v>
+      </c>
+      <c r="C160" t="s">
+        <v>58</v>
+      </c>
+      <c r="D160">
+        <v>60.9</v>
+      </c>
+      <c r="E160" t="s">
+        <v>62</v>
+      </c>
+      <c r="F160" t="s">
+        <v>63</v>
+      </c>
+      <c r="G160" t="s">
+        <v>64</v>
+      </c>
+      <c r="H160">
+        <v>1408.8</v>
+      </c>
+      <c r="I160">
+        <v>9.100000000000001</v>
+      </c>
+      <c r="J160" t="s">
+        <v>68</v>
+      </c>
+      <c r="K160">
+        <v>9</v>
+      </c>
+      <c r="L160" t="s">
+        <v>75</v>
+      </c>
+      <c r="M160" t="s">
+        <v>80</v>
+      </c>
+      <c r="N160" t="s">
+        <v>85</v>
+      </c>
+      <c r="O160">
+        <v>18.44</v>
+      </c>
+      <c r="P160">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16">
+      <c r="A161" t="s">
+        <v>16</v>
+      </c>
+      <c r="B161" t="s">
+        <v>44</v>
+      </c>
+      <c r="C161" t="s">
+        <v>58</v>
+      </c>
+      <c r="D161">
+        <v>60.5</v>
+      </c>
+      <c r="E161" t="s">
+        <v>59</v>
+      </c>
+      <c r="F161" t="s">
+        <v>63</v>
+      </c>
+      <c r="G161" t="s">
+        <v>64</v>
+      </c>
+      <c r="H161">
+        <v>125.82</v>
+      </c>
+      <c r="I161">
+        <v>9.5</v>
+      </c>
+      <c r="J161" t="s">
+        <v>66</v>
+      </c>
+      <c r="K161">
+        <v>3</v>
+      </c>
+      <c r="L161" t="s">
+        <v>79</v>
+      </c>
+      <c r="M161" t="s">
+        <v>80</v>
+      </c>
+      <c r="N161" t="s">
+        <v>85</v>
+      </c>
+      <c r="O161">
+        <v>18.44</v>
+      </c>
+      <c r="P161">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="162" spans="1:16">
+      <c r="A162" t="s">
+        <v>16</v>
+      </c>
+      <c r="B162" t="s">
+        <v>56</v>
+      </c>
+      <c r="C162" t="s">
+        <v>58</v>
+      </c>
+      <c r="D162">
+        <v>57.8</v>
+      </c>
+      <c r="E162" t="s">
+        <v>59</v>
+      </c>
+      <c r="F162" t="s">
+        <v>63</v>
+      </c>
+      <c r="G162" t="s">
+        <v>64</v>
+      </c>
+      <c r="H162">
+        <v>451.3</v>
+      </c>
+      <c r="I162">
+        <v>12.2</v>
+      </c>
+      <c r="J162" t="s">
+        <v>73</v>
+      </c>
+      <c r="K162">
+        <v>3</v>
+      </c>
+      <c r="L162" t="s">
+        <v>79</v>
+      </c>
+      <c r="M162" t="s">
+        <v>80</v>
+      </c>
+      <c r="N162" t="s">
+        <v>85</v>
+      </c>
+      <c r="O162">
+        <v>18.44</v>
+      </c>
+      <c r="P162">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16">
+      <c r="A163" t="s">
+        <v>16</v>
+      </c>
+      <c r="B163" t="s">
+        <v>37</v>
+      </c>
+      <c r="C163" t="s">
+        <v>58</v>
+      </c>
+      <c r="D163">
+        <v>56.4</v>
+      </c>
+      <c r="E163" t="s">
+        <v>59</v>
+      </c>
+      <c r="F163" t="s">
+        <v>63</v>
+      </c>
+      <c r="G163" t="s">
+        <v>64</v>
+      </c>
+      <c r="H163">
+        <v>320.1</v>
+      </c>
+      <c r="I163">
+        <v>13.6</v>
+      </c>
+      <c r="J163" t="s">
+        <v>70</v>
+      </c>
+      <c r="K163">
+        <v>14</v>
+      </c>
+      <c r="L163" t="s">
+        <v>76</v>
+      </c>
+      <c r="M163" t="s">
+        <v>80</v>
+      </c>
+      <c r="N163" t="s">
+        <v>85</v>
+      </c>
+      <c r="O163">
+        <v>18.44</v>
+      </c>
+      <c r="P163">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16">
+      <c r="A164" t="s">
+        <v>16</v>
+      </c>
+      <c r="B164" t="s">
+        <v>33</v>
+      </c>
+      <c r="C164" t="s">
+        <v>58</v>
+      </c>
+      <c r="D164">
+        <v>56.1</v>
+      </c>
+      <c r="E164" t="s">
+        <v>59</v>
+      </c>
+      <c r="F164" t="s">
+        <v>63</v>
+      </c>
+      <c r="G164" t="s">
+        <v>64</v>
+      </c>
+      <c r="H164">
+        <v>9549.5</v>
+      </c>
+      <c r="I164">
+        <v>13.9</v>
+      </c>
+      <c r="J164" t="s">
+        <v>66</v>
+      </c>
+      <c r="K164">
+        <v>14</v>
+      </c>
+      <c r="L164" t="s">
+        <v>76</v>
+      </c>
+      <c r="M164" t="s">
+        <v>80</v>
+      </c>
+      <c r="N164" t="s">
+        <v>85</v>
+      </c>
+      <c r="O164">
+        <v>18.44</v>
+      </c>
+      <c r="P164">
+        <v>250</v>
       </c>
     </row>
   </sheetData>

--- a/reports/watchlist_history.xlsx
+++ b/reports/watchlist_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1342" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="100">
   <si>
     <t>Date</t>
   </si>
@@ -187,22 +187,61 @@
     <t>COALINDIA</t>
   </si>
   <si>
+    <t>ATUL</t>
+  </si>
+  <si>
+    <t>DATAPATTNS</t>
+  </si>
+  <si>
+    <t>KARURVYSYA</t>
+  </si>
+  <si>
+    <t>GLENMARK</t>
+  </si>
+  <si>
+    <t>FEDERALBNK</t>
+  </si>
+  <si>
+    <t>AUROPHARMA</t>
+  </si>
+  <si>
+    <t>AVANTIFEED</t>
+  </si>
+  <si>
+    <t>APLAPOLLO</t>
+  </si>
+  <si>
+    <t>AUBANK</t>
+  </si>
+  <si>
+    <t>MRPL</t>
+  </si>
+  <si>
+    <t>CESC</t>
+  </si>
+  <si>
+    <t>ENGINERSIN</t>
+  </si>
+  <si>
+    <t>HFCL</t>
+  </si>
+  <si>
     <t>BUY</t>
   </si>
   <si>
     <t>WATCH</t>
   </si>
   <si>
+    <t>+0.0</t>
+  </si>
+  <si>
+    <t>-0.5</t>
+  </si>
+  <si>
+    <t>-2.9</t>
+  </si>
+  <si>
     <t>+0.5</t>
-  </si>
-  <si>
-    <t>+2.9</t>
-  </si>
-  <si>
-    <t>+3.9</t>
-  </si>
-  <si>
-    <t>+1.5</t>
   </si>
   <si>
     <t>Stage 2 — Uptrend ✓</t>
@@ -606,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P164"/>
+  <dimension ref="A1:P184"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -667,7 +706,7 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D2">
         <v>77.09999999999999</v>
@@ -676,10 +715,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G2" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H2">
         <v>11714</v>
@@ -691,13 +730,13 @@
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="M2" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N2" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O2">
         <v>17.53</v>
@@ -714,7 +753,7 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D3">
         <v>74</v>
@@ -723,10 +762,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G3" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H3">
         <v>514.05</v>
@@ -738,13 +777,13 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="M3" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N3" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O3">
         <v>17.53</v>
@@ -761,7 +800,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D4">
         <v>72</v>
@@ -770,10 +809,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G4" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H4">
         <v>1621.5</v>
@@ -785,13 +824,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>74</v>
+        <v>87</v>
       </c>
       <c r="M4" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N4" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O4">
         <v>17.53</v>
@@ -808,7 +847,7 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D5">
         <v>69.59999999999999</v>
@@ -817,10 +856,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G5" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H5">
         <v>191.38</v>
@@ -829,19 +868,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J5" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M5" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N5" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O5">
         <v>17.53</v>
@@ -858,7 +897,7 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D6">
         <v>69.09999999999999</v>
@@ -867,10 +906,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G6" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H6">
         <v>1318.1</v>
@@ -879,19 +918,19 @@
         <v>0.9000000000000057</v>
       </c>
       <c r="J6" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M6" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N6" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O6">
         <v>17.53</v>
@@ -908,7 +947,7 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D7">
         <v>67.2</v>
@@ -917,10 +956,10 @@
         <v>-0.5</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G7" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H7">
         <v>1377.7</v>
@@ -929,19 +968,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J7" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K7">
         <v>6</v>
       </c>
       <c r="L7" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M7" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N7" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O7">
         <v>17.53</v>
@@ -958,7 +997,7 @@
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D8">
         <v>67.2</v>
@@ -967,10 +1006,10 @@
         <v>-0.5</v>
       </c>
       <c r="F8" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G8" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H8">
         <v>4479.7</v>
@@ -979,19 +1018,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J8" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K8">
         <v>6</v>
       </c>
       <c r="L8" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M8" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N8" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O8">
         <v>17.53</v>
@@ -1008,7 +1047,7 @@
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D9">
         <v>67.2</v>
@@ -1017,10 +1056,10 @@
         <v>-0.5</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G9" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H9">
         <v>1045.3</v>
@@ -1029,19 +1068,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J9" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K9">
         <v>6</v>
       </c>
       <c r="L9" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M9" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N9" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O9">
         <v>17.53</v>
@@ -1058,7 +1097,7 @@
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D10">
         <v>67.2</v>
@@ -1067,10 +1106,10 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G10" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H10">
         <v>1055.65</v>
@@ -1079,19 +1118,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J10" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M10" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N10" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O10">
         <v>17.53</v>
@@ -1108,7 +1147,7 @@
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D11">
         <v>67.2</v>
@@ -1117,10 +1156,10 @@
         <v>-0.5</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G11" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H11">
         <v>1045.3</v>
@@ -1129,19 +1168,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J11" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K11">
         <v>6</v>
       </c>
       <c r="L11" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M11" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N11" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O11">
         <v>17.53</v>
@@ -1158,7 +1197,7 @@
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D12">
         <v>67.2</v>
@@ -1167,10 +1206,10 @@
         <v>-0.5</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G12" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H12">
         <v>4479.7</v>
@@ -1179,19 +1218,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J12" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K12">
         <v>6</v>
       </c>
       <c r="L12" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M12" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N12" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O12">
         <v>17.53</v>
@@ -1208,7 +1247,7 @@
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D13">
         <v>67.09999999999999</v>
@@ -1217,10 +1256,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G13" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H13">
         <v>581.3</v>
@@ -1229,19 +1268,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J13" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K13">
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M13" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N13" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O13">
         <v>17.53</v>
@@ -1258,7 +1297,7 @@
         <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D14">
         <v>67.09999999999999</v>
@@ -1267,10 +1306,10 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G14" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H14">
         <v>458.9</v>
@@ -1279,19 +1318,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J14" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M14" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N14" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O14">
         <v>17.53</v>
@@ -1308,7 +1347,7 @@
         <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D15">
         <v>65.59999999999999</v>
@@ -1317,10 +1356,10 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G15" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H15">
         <v>196.02</v>
@@ -1329,19 +1368,19 @@
         <v>4.400000000000006</v>
       </c>
       <c r="J15" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M15" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N15" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O15">
         <v>17.53</v>
@@ -1358,7 +1397,7 @@
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D16">
         <v>65</v>
@@ -1367,10 +1406,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G16" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H16">
         <v>4172.9</v>
@@ -1379,19 +1418,19 @@
         <v>5</v>
       </c>
       <c r="J16" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K16">
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M16" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N16" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O16">
         <v>17.53</v>
@@ -1408,7 +1447,7 @@
         <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D17">
         <v>64.7</v>
@@ -1417,10 +1456,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G17" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H17">
         <v>6373.5</v>
@@ -1429,19 +1468,19 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J17" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="K17">
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M17" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N17" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O17">
         <v>17.53</v>
@@ -1458,7 +1497,7 @@
         <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D18">
         <v>64.7</v>
@@ -1467,10 +1506,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G18" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H18">
         <v>1113.1</v>
@@ -1479,19 +1518,19 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J18" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M18" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N18" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O18">
         <v>17.53</v>
@@ -1508,7 +1547,7 @@
         <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D19">
         <v>64.59999999999999</v>
@@ -1517,10 +1556,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G19" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H19">
         <v>1379.9</v>
@@ -1529,19 +1568,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J19" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K19">
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M19" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N19" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O19">
         <v>17.53</v>
@@ -1558,7 +1597,7 @@
         <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D20">
         <v>64.2</v>
@@ -1567,10 +1606,10 @@
         <v>-0.5</v>
       </c>
       <c r="F20" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G20" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H20">
         <v>9793</v>
@@ -1579,19 +1618,19 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J20" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K20">
         <v>6</v>
       </c>
       <c r="L20" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M20" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N20" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O20">
         <v>17.53</v>
@@ -1608,7 +1647,7 @@
         <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D21">
         <v>64.2</v>
@@ -1617,10 +1656,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G21" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H21">
         <v>7955.5</v>
@@ -1629,19 +1668,19 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J21" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K21">
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M21" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N21" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O21">
         <v>17.53</v>
@@ -1658,7 +1697,7 @@
         <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D22">
         <v>63.6</v>
@@ -1667,10 +1706,10 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G22" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H22">
         <v>1037.85</v>
@@ -1679,19 +1718,19 @@
         <v>6.399999999999999</v>
       </c>
       <c r="J22" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K22">
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M22" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N22" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O22">
         <v>17.53</v>
@@ -1708,7 +1747,7 @@
         <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D23">
         <v>61.6</v>
@@ -1717,10 +1756,10 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G23" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H23">
         <v>979.1</v>
@@ -1729,19 +1768,19 @@
         <v>8.399999999999999</v>
       </c>
       <c r="J23" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K23">
         <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M23" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N23" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O23">
         <v>17.53</v>
@@ -1758,7 +1797,7 @@
         <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D24">
         <v>61.5</v>
@@ -1767,10 +1806,10 @@
         <v>-0.5</v>
       </c>
       <c r="F24" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G24" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H24">
         <v>319.35</v>
@@ -1779,19 +1818,19 @@
         <v>8.5</v>
       </c>
       <c r="J24" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="K24">
         <v>6</v>
       </c>
       <c r="L24" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M24" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N24" t="s">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="O24">
         <v>17.53</v>
@@ -1808,7 +1847,7 @@
         <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D25">
         <v>70</v>
@@ -1817,10 +1856,10 @@
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G25" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H25">
         <v>767.65</v>
@@ -1832,13 +1871,13 @@
         <v>1</v>
       </c>
       <c r="L25" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="M25" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N25" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O25">
         <v>18.27</v>
@@ -1855,7 +1894,7 @@
         <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D26">
         <v>69</v>
@@ -1864,10 +1903,10 @@
         <v>7.8</v>
       </c>
       <c r="F26" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G26" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H26">
         <v>404.1</v>
@@ -1876,19 +1915,19 @@
         <v>1</v>
       </c>
       <c r="J26" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K26">
         <v>7</v>
       </c>
       <c r="L26" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M26" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N26" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O26">
         <v>18.27</v>
@@ -1905,7 +1944,7 @@
         <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D27">
         <v>69</v>
@@ -1914,10 +1953,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G27" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H27">
         <v>3847</v>
@@ -1926,19 +1965,19 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K27">
         <v>1</v>
       </c>
       <c r="L27" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M27" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N27" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O27">
         <v>18.27</v>
@@ -1955,7 +1994,7 @@
         <v>41</v>
       </c>
       <c r="C28" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D28">
         <v>67.5</v>
@@ -1964,10 +2003,10 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G28" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H28">
         <v>211.75</v>
@@ -1976,19 +2015,19 @@
         <v>2.5</v>
       </c>
       <c r="J28" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K28">
         <v>1</v>
       </c>
       <c r="L28" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M28" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N28" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O28">
         <v>18.27</v>
@@ -2005,7 +2044,7 @@
         <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D29">
         <v>66.7</v>
@@ -2014,10 +2053,10 @@
         <v>-0.5</v>
       </c>
       <c r="F29" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G29" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H29">
         <v>1381.5</v>
@@ -2026,19 +2065,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J29" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K29">
         <v>7</v>
       </c>
       <c r="L29" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M29" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N29" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O29">
         <v>18.27</v>
@@ -2055,7 +2094,7 @@
         <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D30">
         <v>66.7</v>
@@ -2064,10 +2103,10 @@
         <v>-0.5</v>
       </c>
       <c r="F30" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G30" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H30">
         <v>4483</v>
@@ -2076,19 +2115,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J30" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K30">
         <v>7</v>
       </c>
       <c r="L30" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M30" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N30" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O30">
         <v>18.27</v>
@@ -2105,7 +2144,7 @@
         <v>42</v>
       </c>
       <c r="C31" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D31">
         <v>66.7</v>
@@ -2114,10 +2153,10 @@
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G31" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H31">
         <v>89.05</v>
@@ -2126,19 +2165,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J31" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K31">
         <v>1</v>
       </c>
       <c r="L31" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M31" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N31" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O31">
         <v>18.27</v>
@@ -2155,7 +2194,7 @@
         <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D32">
         <v>66.59999999999999</v>
@@ -2164,10 +2203,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G32" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H32">
         <v>1291.1</v>
@@ -2176,19 +2215,19 @@
         <v>3.400000000000006</v>
       </c>
       <c r="J32" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K32">
         <v>1</v>
       </c>
       <c r="L32" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M32" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N32" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O32">
         <v>18.27</v>
@@ -2205,7 +2244,7 @@
         <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D33">
         <v>64.09999999999999</v>
@@ -2214,10 +2253,10 @@
         <v>-0.5</v>
       </c>
       <c r="F33" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G33" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H33">
         <v>1414.6</v>
@@ -2226,19 +2265,19 @@
         <v>5.900000000000006</v>
       </c>
       <c r="J33" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K33">
         <v>2</v>
       </c>
       <c r="L33" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M33" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N33" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O33">
         <v>18.27</v>
@@ -2255,7 +2294,7 @@
         <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D34">
         <v>63.7</v>
@@ -2264,10 +2303,10 @@
         <v>-0.5</v>
       </c>
       <c r="F34" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G34" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H34">
         <v>9760</v>
@@ -2276,19 +2315,19 @@
         <v>6.299999999999997</v>
       </c>
       <c r="J34" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K34">
         <v>7</v>
       </c>
       <c r="L34" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M34" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N34" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O34">
         <v>18.27</v>
@@ -2305,7 +2344,7 @@
         <v>44</v>
       </c>
       <c r="C35" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D35">
         <v>62.7</v>
@@ -2314,10 +2353,10 @@
         <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G35" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H35">
         <v>125.85</v>
@@ -2326,19 +2365,19 @@
         <v>7.299999999999997</v>
       </c>
       <c r="J35" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K35">
         <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M35" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N35" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O35">
         <v>18.27</v>
@@ -2355,7 +2394,7 @@
         <v>45</v>
       </c>
       <c r="C36" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D36">
         <v>62.1</v>
@@ -2364,10 +2403,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G36" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H36">
         <v>1171.95</v>
@@ -2376,19 +2415,19 @@
         <v>7.899999999999999</v>
       </c>
       <c r="J36" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K36">
         <v>1</v>
       </c>
       <c r="L36" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M36" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N36" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O36">
         <v>18.27</v>
@@ -2405,7 +2444,7 @@
         <v>24</v>
       </c>
       <c r="C37" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D37">
         <v>60.7</v>
@@ -2414,10 +2453,10 @@
         <v>-6.5</v>
       </c>
       <c r="F37" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G37" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H37">
         <v>1038.1</v>
@@ -2426,19 +2465,19 @@
         <v>9.299999999999997</v>
       </c>
       <c r="J37" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K37">
         <v>7</v>
       </c>
       <c r="L37" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M37" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N37" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O37">
         <v>18.27</v>
@@ -2455,7 +2494,7 @@
         <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D38">
         <v>58.6</v>
@@ -2464,10 +2503,10 @@
         <v>-2.9</v>
       </c>
       <c r="F38" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G38" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H38">
         <v>319.6</v>
@@ -2476,19 +2515,19 @@
         <v>11.4</v>
       </c>
       <c r="J38" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="K38">
         <v>7</v>
       </c>
       <c r="L38" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M38" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N38" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O38">
         <v>18.27</v>
@@ -2505,7 +2544,7 @@
         <v>46</v>
       </c>
       <c r="C39" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D39">
         <v>58.3</v>
@@ -2514,10 +2553,10 @@
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G39" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H39">
         <v>2314.1</v>
@@ -2526,19 +2565,19 @@
         <v>11.7</v>
       </c>
       <c r="J39" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K39">
         <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M39" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N39" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O39">
         <v>18.27</v>
@@ -2555,7 +2594,7 @@
         <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D40">
         <v>58.3</v>
@@ -2564,10 +2603,10 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G40" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H40">
         <v>3723.6</v>
@@ -2576,19 +2615,19 @@
         <v>11.7</v>
       </c>
       <c r="J40" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K40">
         <v>1</v>
       </c>
       <c r="L40" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M40" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N40" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O40">
         <v>18.27</v>
@@ -2605,7 +2644,7 @@
         <v>48</v>
       </c>
       <c r="C41" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D41">
         <v>56.7</v>
@@ -2614,10 +2653,10 @@
         <v>-0.5</v>
       </c>
       <c r="F41" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G41" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H41">
         <v>4049.2</v>
@@ -2626,19 +2665,19 @@
         <v>13.3</v>
       </c>
       <c r="J41" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K41">
         <v>3</v>
       </c>
       <c r="L41" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M41" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N41" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O41">
         <v>18.27</v>
@@ -2655,7 +2694,7 @@
         <v>49</v>
       </c>
       <c r="C42" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D42">
         <v>55.4</v>
@@ -2664,10 +2703,10 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G42" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H42">
         <v>124.98</v>
@@ -2676,19 +2715,19 @@
         <v>14.6</v>
       </c>
       <c r="J42" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="K42">
         <v>1</v>
       </c>
       <c r="L42" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M42" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N42" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O42">
         <v>18.27</v>
@@ -2705,7 +2744,7 @@
         <v>22</v>
       </c>
       <c r="C43" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D43">
         <v>69.09999999999999</v>
@@ -2714,10 +2753,10 @@
         <v>2.4</v>
       </c>
       <c r="F43" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G43" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H43">
         <v>1388.7</v>
@@ -2726,19 +2765,19 @@
         <v>0.9000000000000057</v>
       </c>
       <c r="J43" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K43">
         <v>8</v>
       </c>
       <c r="L43" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M43" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N43" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O43">
         <v>18.23</v>
@@ -2755,7 +2794,7 @@
         <v>39</v>
       </c>
       <c r="C44" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D44">
         <v>69</v>
@@ -2764,10 +2803,10 @@
         <v>0</v>
       </c>
       <c r="F44" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G44" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H44">
         <v>404.8</v>
@@ -2776,19 +2815,19 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K44">
         <v>8</v>
       </c>
       <c r="L44" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M44" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N44" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O44">
         <v>18.23</v>
@@ -2805,7 +2844,7 @@
         <v>40</v>
       </c>
       <c r="C45" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D45">
         <v>69</v>
@@ -2814,10 +2853,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G45" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H45">
         <v>3845.7</v>
@@ -2826,19 +2865,19 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K45">
         <v>2</v>
       </c>
       <c r="L45" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M45" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N45" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O45">
         <v>18.23</v>
@@ -2855,7 +2894,7 @@
         <v>41</v>
       </c>
       <c r="C46" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D46">
         <v>68.5</v>
@@ -2864,10 +2903,10 @@
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G46" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H46">
         <v>213.03</v>
@@ -2876,19 +2915,19 @@
         <v>1.5</v>
       </c>
       <c r="J46" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K46">
         <v>2</v>
       </c>
       <c r="L46" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M46" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N46" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O46">
         <v>18.23</v>
@@ -2905,7 +2944,7 @@
         <v>23</v>
       </c>
       <c r="C47" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D47">
         <v>66.7</v>
@@ -2914,10 +2953,10 @@
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G47" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H47">
         <v>4477</v>
@@ -2926,19 +2965,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J47" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K47">
         <v>8</v>
       </c>
       <c r="L47" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M47" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N47" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O47">
         <v>18.23</v>
@@ -2955,7 +2994,7 @@
         <v>42</v>
       </c>
       <c r="C48" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D48">
         <v>66.7</v>
@@ -2964,10 +3003,10 @@
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G48" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H48">
         <v>88.98999999999999</v>
@@ -2976,19 +3015,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J48" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K48">
         <v>2</v>
       </c>
       <c r="L48" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M48" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N48" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O48">
         <v>18.23</v>
@@ -3005,7 +3044,7 @@
         <v>43</v>
       </c>
       <c r="C49" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D49">
         <v>66.59999999999999</v>
@@ -3014,10 +3053,10 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G49" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H49">
         <v>1288.9</v>
@@ -3026,19 +3065,19 @@
         <v>3.400000000000006</v>
       </c>
       <c r="J49" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K49">
         <v>2</v>
       </c>
       <c r="L49" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M49" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N49" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O49">
         <v>18.23</v>
@@ -3055,7 +3094,7 @@
         <v>32</v>
       </c>
       <c r="C50" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D50">
         <v>64.09999999999999</v>
@@ -3064,10 +3103,10 @@
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G50" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H50">
         <v>1419</v>
@@ -3076,19 +3115,19 @@
         <v>5.900000000000006</v>
       </c>
       <c r="J50" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K50">
         <v>3</v>
       </c>
       <c r="L50" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M50" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N50" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O50">
         <v>18.23</v>
@@ -3105,7 +3144,7 @@
         <v>33</v>
       </c>
       <c r="C51" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D51">
         <v>63.7</v>
@@ -3114,10 +3153,10 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G51" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H51">
         <v>9758</v>
@@ -3126,19 +3165,19 @@
         <v>6.299999999999997</v>
       </c>
       <c r="J51" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K51">
         <v>8</v>
       </c>
       <c r="L51" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M51" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N51" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O51">
         <v>18.23</v>
@@ -3155,7 +3194,7 @@
         <v>44</v>
       </c>
       <c r="C52" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D52">
         <v>62.7</v>
@@ -3164,10 +3203,10 @@
         <v>0</v>
       </c>
       <c r="F52" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G52" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H52">
         <v>125.98</v>
@@ -3176,19 +3215,19 @@
         <v>7.299999999999997</v>
       </c>
       <c r="J52" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K52">
         <v>2</v>
       </c>
       <c r="L52" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M52" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N52" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O52">
         <v>18.23</v>
@@ -3205,7 +3244,7 @@
         <v>45</v>
       </c>
       <c r="C53" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D53">
         <v>62.1</v>
@@ -3214,10 +3253,10 @@
         <v>0</v>
       </c>
       <c r="F53" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G53" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H53">
         <v>1182</v>
@@ -3226,19 +3265,19 @@
         <v>7.899999999999999</v>
       </c>
       <c r="J53" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K53">
         <v>2</v>
       </c>
       <c r="L53" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M53" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N53" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O53">
         <v>18.23</v>
@@ -3255,7 +3294,7 @@
         <v>24</v>
       </c>
       <c r="C54" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D54">
         <v>60.7</v>
@@ -3264,10 +3303,10 @@
         <v>0</v>
       </c>
       <c r="F54" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G54" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H54">
         <v>1040</v>
@@ -3276,19 +3315,19 @@
         <v>9.299999999999997</v>
       </c>
       <c r="J54" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K54">
         <v>8</v>
       </c>
       <c r="L54" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M54" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N54" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O54">
         <v>18.23</v>
@@ -3305,7 +3344,7 @@
         <v>37</v>
       </c>
       <c r="C55" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D55">
         <v>58.6</v>
@@ -3314,10 +3353,10 @@
         <v>0</v>
       </c>
       <c r="F55" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G55" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H55">
         <v>320.2</v>
@@ -3326,19 +3365,19 @@
         <v>11.4</v>
       </c>
       <c r="J55" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="K55">
         <v>8</v>
       </c>
       <c r="L55" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M55" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N55" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O55">
         <v>18.23</v>
@@ -3355,7 +3394,7 @@
         <v>46</v>
       </c>
       <c r="C56" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D56">
         <v>58.3</v>
@@ -3364,10 +3403,10 @@
         <v>0</v>
       </c>
       <c r="F56" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G56" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H56">
         <v>2314.8</v>
@@ -3376,19 +3415,19 @@
         <v>11.7</v>
       </c>
       <c r="J56" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K56">
         <v>2</v>
       </c>
       <c r="L56" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M56" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N56" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O56">
         <v>18.23</v>
@@ -3405,7 +3444,7 @@
         <v>47</v>
       </c>
       <c r="C57" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D57">
         <v>58.3</v>
@@ -3414,10 +3453,10 @@
         <v>0</v>
       </c>
       <c r="F57" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G57" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H57">
         <v>3716.5</v>
@@ -3426,19 +3465,19 @@
         <v>11.7</v>
       </c>
       <c r="J57" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K57">
         <v>2</v>
       </c>
       <c r="L57" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M57" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N57" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O57">
         <v>18.23</v>
@@ -3455,7 +3494,7 @@
         <v>48</v>
       </c>
       <c r="C58" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D58">
         <v>56.7</v>
@@ -3464,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="F58" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G58" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H58">
         <v>4043</v>
@@ -3476,19 +3515,19 @@
         <v>13.3</v>
       </c>
       <c r="J58" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K58">
         <v>4</v>
       </c>
       <c r="L58" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M58" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N58" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O58">
         <v>18.23</v>
@@ -3505,7 +3544,7 @@
         <v>49</v>
       </c>
       <c r="C59" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D59">
         <v>55.4</v>
@@ -3514,10 +3553,10 @@
         <v>0</v>
       </c>
       <c r="F59" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G59" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H59">
         <v>125.04</v>
@@ -3526,19 +3565,19 @@
         <v>14.6</v>
       </c>
       <c r="J59" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="K59">
         <v>2</v>
       </c>
       <c r="L59" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M59" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N59" t="s">
-        <v>82</v>
+        <v>95</v>
       </c>
       <c r="O59">
         <v>18.23</v>
@@ -3555,7 +3594,7 @@
         <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D60">
         <v>71.5</v>
@@ -3564,10 +3603,10 @@
         <v>0</v>
       </c>
       <c r="F60" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G60" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H60">
         <v>3852.5</v>
@@ -3579,13 +3618,13 @@
         <v>1</v>
       </c>
       <c r="L60" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="M60" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N60" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="O60">
         <v>18.08</v>
@@ -3602,7 +3641,7 @@
         <v>22</v>
       </c>
       <c r="C61" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D61">
         <v>69.59999999999999</v>
@@ -3611,10 +3650,10 @@
         <v>0.5</v>
       </c>
       <c r="F61" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G61" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H61">
         <v>1388.5</v>
@@ -3623,19 +3662,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J61" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K61">
         <v>9</v>
       </c>
       <c r="L61" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M61" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N61" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="O61">
         <v>18.08</v>
@@ -3652,7 +3691,7 @@
         <v>39</v>
       </c>
       <c r="C62" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D62">
         <v>69.5</v>
@@ -3661,10 +3700,10 @@
         <v>0.5</v>
       </c>
       <c r="F62" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G62" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H62">
         <v>406.1</v>
@@ -3673,19 +3712,19 @@
         <v>0.5</v>
       </c>
       <c r="J62" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K62">
         <v>9</v>
       </c>
       <c r="L62" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M62" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N62" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="O62">
         <v>18.08</v>
@@ -3702,7 +3741,7 @@
         <v>41</v>
       </c>
       <c r="C63" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D63">
         <v>69</v>
@@ -3711,10 +3750,10 @@
         <v>0.5</v>
       </c>
       <c r="F63" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G63" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H63">
         <v>213.6</v>
@@ -3723,19 +3762,19 @@
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K63">
         <v>3</v>
       </c>
       <c r="L63" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M63" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N63" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="O63">
         <v>18.08</v>
@@ -3752,7 +3791,7 @@
         <v>23</v>
       </c>
       <c r="C64" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D64">
         <v>67.2</v>
@@ -3761,10 +3800,10 @@
         <v>0.5</v>
       </c>
       <c r="F64" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G64" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H64">
         <v>4478</v>
@@ -3773,19 +3812,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J64" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K64">
         <v>9</v>
       </c>
       <c r="L64" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M64" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N64" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="O64">
         <v>18.08</v>
@@ -3802,7 +3841,7 @@
         <v>24</v>
       </c>
       <c r="C65" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D65">
         <v>67.2</v>
@@ -3811,10 +3850,10 @@
         <v>6.5</v>
       </c>
       <c r="F65" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G65" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H65">
         <v>1050.05</v>
@@ -3823,19 +3862,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J65" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K65">
         <v>9</v>
       </c>
       <c r="L65" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M65" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N65" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="O65">
         <v>18.08</v>
@@ -3852,7 +3891,7 @@
         <v>42</v>
       </c>
       <c r="C66" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D66">
         <v>67.2</v>
@@ -3861,10 +3900,10 @@
         <v>0.5</v>
       </c>
       <c r="F66" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G66" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H66">
         <v>88.59</v>
@@ -3873,19 +3912,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J66" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K66">
         <v>3</v>
       </c>
       <c r="L66" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M66" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N66" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="O66">
         <v>18.08</v>
@@ -3902,7 +3941,7 @@
         <v>43</v>
       </c>
       <c r="C67" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D67">
         <v>67.09999999999999</v>
@@ -3911,10 +3950,10 @@
         <v>0.5</v>
       </c>
       <c r="F67" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G67" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H67">
         <v>1291.7</v>
@@ -3923,19 +3962,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J67" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K67">
         <v>3</v>
       </c>
       <c r="L67" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M67" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N67" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="O67">
         <v>18.08</v>
@@ -3952,7 +3991,7 @@
         <v>32</v>
       </c>
       <c r="C68" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D68">
         <v>64.59999999999999</v>
@@ -3961,10 +4000,10 @@
         <v>0.5</v>
       </c>
       <c r="F68" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G68" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H68">
         <v>1405.3</v>
@@ -3973,19 +4012,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J68" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K68">
         <v>4</v>
       </c>
       <c r="L68" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M68" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N68" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="O68">
         <v>18.08</v>
@@ -4002,7 +4041,7 @@
         <v>44</v>
       </c>
       <c r="C69" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D69">
         <v>63.2</v>
@@ -4011,10 +4050,10 @@
         <v>0.5</v>
       </c>
       <c r="F69" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G69" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H69">
         <v>125.89</v>
@@ -4023,19 +4062,19 @@
         <v>6.799999999999997</v>
       </c>
       <c r="J69" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K69">
         <v>3</v>
       </c>
       <c r="L69" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M69" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N69" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="O69">
         <v>18.08</v>
@@ -4052,7 +4091,7 @@
         <v>45</v>
       </c>
       <c r="C70" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D70">
         <v>62.6</v>
@@ -4061,10 +4100,10 @@
         <v>0.5</v>
       </c>
       <c r="F70" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G70" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H70">
         <v>1190.45</v>
@@ -4073,19 +4112,19 @@
         <v>7.399999999999999</v>
       </c>
       <c r="J70" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K70">
         <v>3</v>
       </c>
       <c r="L70" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M70" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N70" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="O70">
         <v>18.08</v>
@@ -4102,7 +4141,7 @@
         <v>33</v>
       </c>
       <c r="C71" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D71">
         <v>60.6</v>
@@ -4111,10 +4150,10 @@
         <v>-3.1</v>
       </c>
       <c r="F71" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G71" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H71">
         <v>9700</v>
@@ -4123,19 +4162,19 @@
         <v>9.399999999999999</v>
       </c>
       <c r="J71" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K71">
         <v>9</v>
       </c>
       <c r="L71" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M71" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N71" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="O71">
         <v>18.08</v>
@@ -4152,7 +4191,7 @@
         <v>37</v>
       </c>
       <c r="C72" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D72">
         <v>59.1</v>
@@ -4161,10 +4200,10 @@
         <v>0.5</v>
       </c>
       <c r="F72" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G72" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H72">
         <v>319.85</v>
@@ -4173,19 +4212,19 @@
         <v>10.9</v>
       </c>
       <c r="J72" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="K72">
         <v>9</v>
       </c>
       <c r="L72" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M72" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N72" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="O72">
         <v>18.08</v>
@@ -4202,7 +4241,7 @@
         <v>46</v>
       </c>
       <c r="C73" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D73">
         <v>58.8</v>
@@ -4211,10 +4250,10 @@
         <v>0.5</v>
       </c>
       <c r="F73" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G73" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H73">
         <v>2305.6</v>
@@ -4223,19 +4262,19 @@
         <v>11.2</v>
       </c>
       <c r="J73" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K73">
         <v>3</v>
       </c>
       <c r="L73" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M73" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N73" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="O73">
         <v>18.08</v>
@@ -4252,7 +4291,7 @@
         <v>47</v>
       </c>
       <c r="C74" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D74">
         <v>58.8</v>
@@ -4261,10 +4300,10 @@
         <v>0.5</v>
       </c>
       <c r="F74" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G74" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H74">
         <v>3703.3</v>
@@ -4273,19 +4312,19 @@
         <v>11.2</v>
       </c>
       <c r="J74" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K74">
         <v>3</v>
       </c>
       <c r="L74" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M74" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N74" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="O74">
         <v>18.08</v>
@@ -4302,7 +4341,7 @@
         <v>48</v>
       </c>
       <c r="C75" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D75">
         <v>57.2</v>
@@ -4311,10 +4350,10 @@
         <v>0.5</v>
       </c>
       <c r="F75" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G75" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H75">
         <v>4023.5</v>
@@ -4323,19 +4362,19 @@
         <v>12.8</v>
       </c>
       <c r="J75" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K75">
         <v>5</v>
       </c>
       <c r="L75" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M75" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N75" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="O75">
         <v>18.08</v>
@@ -4352,7 +4391,7 @@
         <v>50</v>
       </c>
       <c r="C76" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D76">
         <v>56.8</v>
@@ -4361,10 +4400,10 @@
         <v>0</v>
       </c>
       <c r="F76" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G76" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H76">
         <v>7196</v>
@@ -4373,19 +4412,19 @@
         <v>13.2</v>
       </c>
       <c r="J76" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="K76">
         <v>1</v>
       </c>
       <c r="L76" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M76" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N76" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="O76">
         <v>18.08</v>
@@ -4402,7 +4441,7 @@
         <v>49</v>
       </c>
       <c r="C77" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D77">
         <v>55.9</v>
@@ -4411,10 +4450,10 @@
         <v>0.5</v>
       </c>
       <c r="F77" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G77" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H77">
         <v>125</v>
@@ -4423,19 +4462,19 @@
         <v>14.1</v>
       </c>
       <c r="J77" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="K77">
         <v>3</v>
       </c>
       <c r="L77" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M77" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N77" t="s">
-        <v>83</v>
+        <v>96</v>
       </c>
       <c r="O77">
         <v>18.08</v>
@@ -4452,7 +4491,7 @@
         <v>51</v>
       </c>
       <c r="C78" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D78">
         <v>73.7</v>
@@ -4461,10 +4500,10 @@
         <v>0</v>
       </c>
       <c r="F78" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G78" t="s">
-        <v>65</v>
+        <v>78</v>
       </c>
       <c r="H78">
         <v>1449.1</v>
@@ -4476,13 +4515,13 @@
         <v>1</v>
       </c>
       <c r="L78" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="M78" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N78" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O78">
         <v>18.3</v>
@@ -4499,7 +4538,7 @@
         <v>40</v>
       </c>
       <c r="C79" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D79">
         <v>71.5</v>
@@ -4508,10 +4547,10 @@
         <v>0</v>
       </c>
       <c r="F79" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G79" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H79">
         <v>3844.3</v>
@@ -4523,13 +4562,13 @@
         <v>1</v>
       </c>
       <c r="L79" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="M79" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N79" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O79">
         <v>18.3</v>
@@ -4546,7 +4585,7 @@
         <v>52</v>
       </c>
       <c r="C80" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D80">
         <v>71.09999999999999</v>
@@ -4555,10 +4594,10 @@
         <v>0</v>
       </c>
       <c r="F80" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G80" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H80">
         <v>1330.5</v>
@@ -4570,13 +4609,13 @@
         <v>1</v>
       </c>
       <c r="L80" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="M80" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N80" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O80">
         <v>18.3</v>
@@ -4593,7 +4632,7 @@
         <v>39</v>
       </c>
       <c r="C81" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D81">
         <v>70.5</v>
@@ -4602,10 +4641,10 @@
         <v>0</v>
       </c>
       <c r="F81" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G81" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H81">
         <v>405.4</v>
@@ -4617,13 +4656,13 @@
         <v>1</v>
       </c>
       <c r="L81" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="M81" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N81" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O81">
         <v>18.3</v>
@@ -4640,7 +4679,7 @@
         <v>53</v>
       </c>
       <c r="C82" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D82">
         <v>69.59999999999999</v>
@@ -4649,10 +4688,10 @@
         <v>0</v>
       </c>
       <c r="F82" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G82" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H82">
         <v>554.7</v>
@@ -4661,19 +4700,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J82" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="K82">
         <v>1</v>
       </c>
       <c r="L82" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M82" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N82" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O82">
         <v>18.3</v>
@@ -4690,7 +4729,7 @@
         <v>41</v>
       </c>
       <c r="C83" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D83">
         <v>69</v>
@@ -4699,10 +4738,10 @@
         <v>0</v>
       </c>
       <c r="F83" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G83" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H83">
         <v>215.65</v>
@@ -4711,19 +4750,19 @@
         <v>1</v>
       </c>
       <c r="J83" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K83">
         <v>4</v>
       </c>
       <c r="L83" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M83" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N83" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O83">
         <v>18.3</v>
@@ -4740,7 +4779,7 @@
         <v>22</v>
       </c>
       <c r="C84" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D84">
         <v>67.2</v>
@@ -4749,10 +4788,10 @@
         <v>-2.4</v>
       </c>
       <c r="F84" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G84" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H84">
         <v>1379.6</v>
@@ -4761,19 +4800,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J84" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K84">
         <v>10</v>
       </c>
       <c r="L84" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M84" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N84" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O84">
         <v>18.3</v>
@@ -4790,7 +4829,7 @@
         <v>23</v>
       </c>
       <c r="C85" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D85">
         <v>67.2</v>
@@ -4799,10 +4838,10 @@
         <v>0</v>
       </c>
       <c r="F85" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G85" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H85">
         <v>4454.6</v>
@@ -4811,19 +4850,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J85" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K85">
         <v>10</v>
       </c>
       <c r="L85" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M85" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N85" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O85">
         <v>18.3</v>
@@ -4840,7 +4879,7 @@
         <v>24</v>
       </c>
       <c r="C86" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D86">
         <v>67.2</v>
@@ -4849,10 +4888,10 @@
         <v>0</v>
       </c>
       <c r="F86" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G86" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H86">
         <v>1044.55</v>
@@ -4861,19 +4900,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J86" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K86">
         <v>10</v>
       </c>
       <c r="L86" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M86" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N86" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O86">
         <v>18.3</v>
@@ -4890,7 +4929,7 @@
         <v>42</v>
       </c>
       <c r="C87" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D87">
         <v>67.2</v>
@@ -4899,10 +4938,10 @@
         <v>0</v>
       </c>
       <c r="F87" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G87" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H87">
         <v>88.59</v>
@@ -4911,19 +4950,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J87" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K87">
         <v>4</v>
       </c>
       <c r="L87" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M87" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N87" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O87">
         <v>18.3</v>
@@ -4940,7 +4979,7 @@
         <v>54</v>
       </c>
       <c r="C88" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D88">
         <v>65.2</v>
@@ -4949,10 +4988,10 @@
         <v>0</v>
       </c>
       <c r="F88" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G88" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H88">
         <v>556.95</v>
@@ -4961,19 +5000,19 @@
         <v>4.799999999999997</v>
       </c>
       <c r="J88" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="K88">
         <v>1</v>
       </c>
       <c r="L88" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M88" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N88" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O88">
         <v>18.3</v>
@@ -4990,7 +5029,7 @@
         <v>32</v>
       </c>
       <c r="C89" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D89">
         <v>64.59999999999999</v>
@@ -4999,10 +5038,10 @@
         <v>0</v>
       </c>
       <c r="F89" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G89" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H89">
         <v>1395.8</v>
@@ -5011,19 +5050,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J89" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K89">
         <v>5</v>
       </c>
       <c r="L89" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M89" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N89" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O89">
         <v>18.3</v>
@@ -5040,7 +5079,7 @@
         <v>55</v>
       </c>
       <c r="C90" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D90">
         <v>64.59999999999999</v>
@@ -5049,10 +5088,10 @@
         <v>0</v>
       </c>
       <c r="F90" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G90" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H90">
         <v>5977</v>
@@ -5061,19 +5100,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J90" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K90">
         <v>1</v>
       </c>
       <c r="L90" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M90" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N90" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O90">
         <v>18.3</v>
@@ -5090,7 +5129,7 @@
         <v>45</v>
       </c>
       <c r="C91" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D91">
         <v>63.6</v>
@@ -5099,10 +5138,10 @@
         <v>1</v>
       </c>
       <c r="F91" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G91" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H91">
         <v>1198.95</v>
@@ -5111,19 +5150,19 @@
         <v>6.399999999999999</v>
       </c>
       <c r="J91" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K91">
         <v>4</v>
       </c>
       <c r="L91" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M91" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N91" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O91">
         <v>18.3</v>
@@ -5140,7 +5179,7 @@
         <v>43</v>
       </c>
       <c r="C92" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D92">
         <v>61.1</v>
@@ -5149,10 +5188,10 @@
         <v>-6</v>
       </c>
       <c r="F92" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G92" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H92">
         <v>1278.6</v>
@@ -5161,19 +5200,19 @@
         <v>8.899999999999999</v>
       </c>
       <c r="J92" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K92">
         <v>4</v>
       </c>
       <c r="L92" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M92" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N92" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O92">
         <v>18.3</v>
@@ -5190,7 +5229,7 @@
         <v>33</v>
       </c>
       <c r="C93" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D93">
         <v>60.6</v>
@@ -5199,10 +5238,10 @@
         <v>0</v>
       </c>
       <c r="F93" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G93" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H93">
         <v>9602</v>
@@ -5211,19 +5250,19 @@
         <v>9.399999999999999</v>
       </c>
       <c r="J93" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K93">
         <v>10</v>
       </c>
       <c r="L93" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M93" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N93" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O93">
         <v>18.3</v>
@@ -5240,7 +5279,7 @@
         <v>37</v>
       </c>
       <c r="C94" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D94">
         <v>59.1</v>
@@ -5249,10 +5288,10 @@
         <v>0</v>
       </c>
       <c r="F94" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G94" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H94">
         <v>319.75</v>
@@ -5261,19 +5300,19 @@
         <v>10.9</v>
       </c>
       <c r="J94" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="K94">
         <v>10</v>
       </c>
       <c r="L94" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M94" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N94" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O94">
         <v>18.3</v>
@@ -5290,7 +5329,7 @@
         <v>46</v>
       </c>
       <c r="C95" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D95">
         <v>58.8</v>
@@ -5299,10 +5338,10 @@
         <v>0</v>
       </c>
       <c r="F95" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G95" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H95">
         <v>2307.9</v>
@@ -5311,19 +5350,19 @@
         <v>11.2</v>
       </c>
       <c r="J95" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K95">
         <v>4</v>
       </c>
       <c r="L95" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M95" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N95" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O95">
         <v>18.3</v>
@@ -5340,7 +5379,7 @@
         <v>48</v>
       </c>
       <c r="C96" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D96">
         <v>57.2</v>
@@ -5349,10 +5388,10 @@
         <v>0</v>
       </c>
       <c r="F96" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G96" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H96">
         <v>4021.1</v>
@@ -5361,19 +5400,19 @@
         <v>12.8</v>
       </c>
       <c r="J96" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K96">
         <v>6</v>
       </c>
       <c r="L96" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M96" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N96" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O96">
         <v>18.3</v>
@@ -5390,7 +5429,7 @@
         <v>50</v>
       </c>
       <c r="C97" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D97">
         <v>56.8</v>
@@ -5399,10 +5438,10 @@
         <v>0</v>
       </c>
       <c r="F97" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G97" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H97">
         <v>7230</v>
@@ -5411,19 +5450,19 @@
         <v>13.2</v>
       </c>
       <c r="J97" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="K97">
         <v>2</v>
       </c>
       <c r="L97" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M97" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N97" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O97">
         <v>18.3</v>
@@ -5440,7 +5479,7 @@
         <v>40</v>
       </c>
       <c r="C98" t="s">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="D98">
         <v>70.3</v>
@@ -5449,10 +5488,10 @@
         <v>0</v>
       </c>
       <c r="F98" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G98" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H98">
         <v>3844.3</v>
@@ -5464,13 +5503,13 @@
         <v>1</v>
       </c>
       <c r="L98" t="s">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="M98" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N98" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O98">
         <v>18.3</v>
@@ -5487,7 +5526,7 @@
         <v>52</v>
       </c>
       <c r="C99" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D99">
         <v>69.90000000000001</v>
@@ -5496,10 +5535,10 @@
         <v>0</v>
       </c>
       <c r="F99" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G99" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H99">
         <v>1330.5</v>
@@ -5508,19 +5547,19 @@
         <v>0.09999999999999432</v>
       </c>
       <c r="J99" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="K99">
         <v>1</v>
       </c>
       <c r="L99" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M99" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N99" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O99">
         <v>18.3</v>
@@ -5537,7 +5576,7 @@
         <v>39</v>
       </c>
       <c r="C100" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D100">
         <v>69.3</v>
@@ -5546,10 +5585,10 @@
         <v>0</v>
       </c>
       <c r="F100" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G100" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H100">
         <v>405.4</v>
@@ -5558,19 +5597,19 @@
         <v>0.7000000000000028</v>
       </c>
       <c r="J100" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K100">
         <v>1</v>
       </c>
       <c r="L100" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M100" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N100" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O100">
         <v>18.3</v>
@@ -5587,7 +5626,7 @@
         <v>53</v>
       </c>
       <c r="C101" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D101">
         <v>68.40000000000001</v>
@@ -5596,10 +5635,10 @@
         <v>-1.2</v>
       </c>
       <c r="F101" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G101" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H101">
         <v>554.7</v>
@@ -5608,19 +5647,19 @@
         <v>1.599999999999994</v>
       </c>
       <c r="J101" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="K101">
         <v>2</v>
       </c>
       <c r="L101" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M101" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N101" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O101">
         <v>18.3</v>
@@ -5637,7 +5676,7 @@
         <v>41</v>
       </c>
       <c r="C102" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D102">
         <v>67.8</v>
@@ -5646,10 +5685,10 @@
         <v>-1.2</v>
       </c>
       <c r="F102" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G102" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H102">
         <v>215.65</v>
@@ -5658,19 +5697,19 @@
         <v>2.200000000000003</v>
       </c>
       <c r="J102" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K102">
         <v>5</v>
       </c>
       <c r="L102" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M102" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N102" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O102">
         <v>18.3</v>
@@ -5687,7 +5726,7 @@
         <v>22</v>
       </c>
       <c r="C103" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D103">
         <v>66</v>
@@ -5696,10 +5735,10 @@
         <v>-1.2</v>
       </c>
       <c r="F103" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G103" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H103">
         <v>1379.6</v>
@@ -5708,19 +5747,19 @@
         <v>4</v>
       </c>
       <c r="J103" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K103">
         <v>11</v>
       </c>
       <c r="L103" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M103" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N103" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O103">
         <v>18.3</v>
@@ -5737,7 +5776,7 @@
         <v>23</v>
       </c>
       <c r="C104" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D104">
         <v>66</v>
@@ -5746,10 +5785,10 @@
         <v>-1.2</v>
       </c>
       <c r="F104" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G104" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H104">
         <v>4454.6</v>
@@ -5758,19 +5797,19 @@
         <v>4</v>
       </c>
       <c r="J104" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K104">
         <v>11</v>
       </c>
       <c r="L104" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M104" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N104" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O104">
         <v>18.3</v>
@@ -5787,7 +5826,7 @@
         <v>24</v>
       </c>
       <c r="C105" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D105">
         <v>66</v>
@@ -5796,10 +5835,10 @@
         <v>-1.2</v>
       </c>
       <c r="F105" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G105" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H105">
         <v>1044.55</v>
@@ -5808,19 +5847,19 @@
         <v>4</v>
       </c>
       <c r="J105" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K105">
         <v>11</v>
       </c>
       <c r="L105" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M105" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N105" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O105">
         <v>18.3</v>
@@ -5837,7 +5876,7 @@
         <v>42</v>
       </c>
       <c r="C106" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D106">
         <v>66</v>
@@ -5846,10 +5885,10 @@
         <v>-1.2</v>
       </c>
       <c r="F106" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G106" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H106">
         <v>88.59</v>
@@ -5858,19 +5897,19 @@
         <v>4</v>
       </c>
       <c r="J106" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K106">
         <v>5</v>
       </c>
       <c r="L106" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M106" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N106" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O106">
         <v>18.3</v>
@@ -5887,7 +5926,7 @@
         <v>54</v>
       </c>
       <c r="C107" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D107">
         <v>64</v>
@@ -5896,10 +5935,10 @@
         <v>-1.2</v>
       </c>
       <c r="F107" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G107" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H107">
         <v>556.95</v>
@@ -5908,19 +5947,19 @@
         <v>6</v>
       </c>
       <c r="J107" t="s">
-        <v>72</v>
+        <v>85</v>
       </c>
       <c r="K107">
         <v>2</v>
       </c>
       <c r="L107" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M107" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N107" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O107">
         <v>18.3</v>
@@ -5937,7 +5976,7 @@
         <v>32</v>
       </c>
       <c r="C108" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D108">
         <v>63.4</v>
@@ -5946,10 +5985,10 @@
         <v>-1.2</v>
       </c>
       <c r="F108" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G108" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H108">
         <v>1395.8</v>
@@ -5958,19 +5997,19 @@
         <v>6.600000000000001</v>
       </c>
       <c r="J108" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K108">
         <v>6</v>
       </c>
       <c r="L108" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M108" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N108" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O108">
         <v>18.3</v>
@@ -5987,7 +6026,7 @@
         <v>55</v>
       </c>
       <c r="C109" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D109">
         <v>63.4</v>
@@ -5996,10 +6035,10 @@
         <v>-1.2</v>
       </c>
       <c r="F109" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G109" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H109">
         <v>5977</v>
@@ -6008,19 +6047,19 @@
         <v>6.600000000000001</v>
       </c>
       <c r="J109" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K109">
         <v>2</v>
       </c>
       <c r="L109" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M109" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N109" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O109">
         <v>18.3</v>
@@ -6037,7 +6076,7 @@
         <v>45</v>
       </c>
       <c r="C110" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D110">
         <v>62.4</v>
@@ -6046,10 +6085,10 @@
         <v>-1.2</v>
       </c>
       <c r="F110" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G110" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H110">
         <v>1198.95</v>
@@ -6058,19 +6097,19 @@
         <v>7.600000000000001</v>
       </c>
       <c r="J110" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K110">
         <v>5</v>
       </c>
       <c r="L110" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M110" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N110" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O110">
         <v>18.3</v>
@@ -6087,7 +6126,7 @@
         <v>43</v>
       </c>
       <c r="C111" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D111">
         <v>59.9</v>
@@ -6096,10 +6135,10 @@
         <v>-1.2</v>
       </c>
       <c r="F111" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G111" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H111">
         <v>1278.6</v>
@@ -6108,19 +6147,19 @@
         <v>10.1</v>
       </c>
       <c r="J111" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K111">
         <v>5</v>
       </c>
       <c r="L111" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M111" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N111" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O111">
         <v>18.3</v>
@@ -6137,7 +6176,7 @@
         <v>33</v>
       </c>
       <c r="C112" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D112">
         <v>59.4</v>
@@ -6146,10 +6185,10 @@
         <v>-1.2</v>
       </c>
       <c r="F112" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G112" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H112">
         <v>9602</v>
@@ -6158,19 +6197,19 @@
         <v>10.6</v>
       </c>
       <c r="J112" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K112">
         <v>11</v>
       </c>
       <c r="L112" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M112" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N112" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O112">
         <v>18.3</v>
@@ -6187,7 +6226,7 @@
         <v>37</v>
       </c>
       <c r="C113" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D113">
         <v>57.9</v>
@@ -6196,10 +6235,10 @@
         <v>-1.2</v>
       </c>
       <c r="F113" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G113" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H113">
         <v>319.75</v>
@@ -6208,19 +6247,19 @@
         <v>12.1</v>
       </c>
       <c r="J113" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="K113">
         <v>11</v>
       </c>
       <c r="L113" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M113" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N113" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O113">
         <v>18.3</v>
@@ -6237,7 +6276,7 @@
         <v>46</v>
       </c>
       <c r="C114" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D114">
         <v>57.6</v>
@@ -6246,10 +6285,10 @@
         <v>-1.2</v>
       </c>
       <c r="F114" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G114" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H114">
         <v>2307.9</v>
@@ -6258,19 +6297,19 @@
         <v>12.4</v>
       </c>
       <c r="J114" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K114">
         <v>5</v>
       </c>
       <c r="L114" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M114" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N114" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O114">
         <v>18.3</v>
@@ -6287,7 +6326,7 @@
         <v>48</v>
       </c>
       <c r="C115" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D115">
         <v>56</v>
@@ -6296,10 +6335,10 @@
         <v>-1.2</v>
       </c>
       <c r="F115" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G115" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H115">
         <v>4021.1</v>
@@ -6308,19 +6347,19 @@
         <v>14</v>
       </c>
       <c r="J115" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K115">
         <v>7</v>
       </c>
       <c r="L115" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M115" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N115" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O115">
         <v>18.3</v>
@@ -6337,7 +6376,7 @@
         <v>50</v>
       </c>
       <c r="C116" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D116">
         <v>55.6</v>
@@ -6346,10 +6385,10 @@
         <v>-1.2</v>
       </c>
       <c r="F116" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G116" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H116">
         <v>7230</v>
@@ -6358,19 +6397,19 @@
         <v>14.4</v>
       </c>
       <c r="J116" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="K116">
         <v>3</v>
       </c>
       <c r="L116" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M116" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N116" t="s">
-        <v>84</v>
+        <v>97</v>
       </c>
       <c r="O116">
         <v>18.3</v>
@@ -6387,7 +6426,7 @@
         <v>43</v>
       </c>
       <c r="C117" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D117">
         <v>66.40000000000001</v>
@@ -6396,10 +6435,10 @@
         <v>6.5</v>
       </c>
       <c r="F117" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G117" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H117">
         <v>1263</v>
@@ -6408,19 +6447,19 @@
         <v>3.599999999999994</v>
       </c>
       <c r="J117" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K117">
         <v>6</v>
       </c>
       <c r="L117" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M117" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N117" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O117">
         <v>18.7</v>
@@ -6437,7 +6476,7 @@
         <v>49</v>
       </c>
       <c r="C118" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D118">
         <v>64.5</v>
@@ -6446,10 +6485,10 @@
         <v>0</v>
       </c>
       <c r="F118" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G118" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H118">
         <v>123.95</v>
@@ -6458,19 +6497,19 @@
         <v>5.5</v>
       </c>
       <c r="J118" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="K118">
         <v>1</v>
       </c>
       <c r="L118" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="M118" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N118" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O118">
         <v>18.7</v>
@@ -6487,7 +6526,7 @@
         <v>22</v>
       </c>
       <c r="C119" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D119">
         <v>64</v>
@@ -6496,10 +6535,10 @@
         <v>-2</v>
       </c>
       <c r="F119" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G119" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H119">
         <v>1371.6</v>
@@ -6508,19 +6547,19 @@
         <v>6</v>
       </c>
       <c r="J119" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K119">
         <v>12</v>
       </c>
       <c r="L119" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M119" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N119" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O119">
         <v>18.7</v>
@@ -6537,7 +6576,7 @@
         <v>23</v>
       </c>
       <c r="C120" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D120">
         <v>64</v>
@@ -6546,10 +6585,10 @@
         <v>-2</v>
       </c>
       <c r="F120" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G120" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H120">
         <v>4460</v>
@@ -6558,19 +6597,19 @@
         <v>6</v>
       </c>
       <c r="J120" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K120">
         <v>12</v>
       </c>
       <c r="L120" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M120" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N120" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O120">
         <v>18.7</v>
@@ -6587,7 +6626,7 @@
         <v>46</v>
       </c>
       <c r="C121" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D121">
         <v>64</v>
@@ -6596,10 +6635,10 @@
         <v>6.4</v>
       </c>
       <c r="F121" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G121" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H121">
         <v>2358.2</v>
@@ -6608,19 +6647,19 @@
         <v>6</v>
       </c>
       <c r="J121" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K121">
         <v>6</v>
       </c>
       <c r="L121" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M121" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N121" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O121">
         <v>18.7</v>
@@ -6637,7 +6676,7 @@
         <v>39</v>
       </c>
       <c r="C122" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D122">
         <v>63.9</v>
@@ -6646,10 +6685,10 @@
         <v>-5.4</v>
       </c>
       <c r="F122" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G122" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H122">
         <v>402.65</v>
@@ -6658,19 +6697,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J122" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K122">
         <v>2</v>
       </c>
       <c r="L122" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M122" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N122" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O122">
         <v>18.7</v>
@@ -6687,7 +6726,7 @@
         <v>40</v>
       </c>
       <c r="C123" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D123">
         <v>63.9</v>
@@ -6696,10 +6735,10 @@
         <v>0</v>
       </c>
       <c r="F123" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G123" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H123">
         <v>3858.9</v>
@@ -6708,19 +6747,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J123" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K123">
         <v>1</v>
       </c>
       <c r="L123" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="M123" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N123" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O123">
         <v>18.7</v>
@@ -6737,7 +6776,7 @@
         <v>37</v>
       </c>
       <c r="C124" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D124">
         <v>61.9</v>
@@ -6746,10 +6785,10 @@
         <v>4</v>
       </c>
       <c r="F124" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G124" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H124">
         <v>320.55</v>
@@ -6758,19 +6797,19 @@
         <v>8.100000000000001</v>
       </c>
       <c r="J124" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="K124">
         <v>12</v>
       </c>
       <c r="L124" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M124" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N124" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O124">
         <v>18.7</v>
@@ -6787,7 +6826,7 @@
         <v>41</v>
       </c>
       <c r="C125" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D125">
         <v>61.4</v>
@@ -6796,10 +6835,10 @@
         <v>-6.4</v>
       </c>
       <c r="F125" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G125" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H125">
         <v>214.68</v>
@@ -6808,19 +6847,19 @@
         <v>8.600000000000001</v>
       </c>
       <c r="J125" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K125">
         <v>6</v>
       </c>
       <c r="L125" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M125" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N125" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O125">
         <v>18.7</v>
@@ -6837,7 +6876,7 @@
         <v>24</v>
       </c>
       <c r="C126" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D126">
         <v>61</v>
@@ -6846,10 +6885,10 @@
         <v>-5</v>
       </c>
       <c r="F126" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G126" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H126">
         <v>1019.75</v>
@@ -6858,19 +6897,19 @@
         <v>9</v>
       </c>
       <c r="J126" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K126">
         <v>12</v>
       </c>
       <c r="L126" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M126" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N126" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O126">
         <v>18.7</v>
@@ -6887,7 +6926,7 @@
         <v>42</v>
       </c>
       <c r="C127" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D127">
         <v>61</v>
@@ -6896,10 +6935,10 @@
         <v>-5</v>
       </c>
       <c r="F127" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G127" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H127">
         <v>86.98</v>
@@ -6908,19 +6947,19 @@
         <v>9</v>
       </c>
       <c r="J127" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K127">
         <v>6</v>
       </c>
       <c r="L127" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M127" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N127" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O127">
         <v>18.7</v>
@@ -6937,7 +6976,7 @@
         <v>44</v>
       </c>
       <c r="C128" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D128">
         <v>60</v>
@@ -6946,10 +6985,10 @@
         <v>0</v>
       </c>
       <c r="F128" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G128" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H128">
         <v>125.61</v>
@@ -6958,19 +6997,19 @@
         <v>10</v>
       </c>
       <c r="J128" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K128">
         <v>1</v>
       </c>
       <c r="L128" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="M128" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N128" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O128">
         <v>18.7</v>
@@ -6987,7 +7026,7 @@
         <v>32</v>
       </c>
       <c r="C129" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D129">
         <v>59.4</v>
@@ -6996,10 +7035,10 @@
         <v>-4</v>
       </c>
       <c r="F129" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G129" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H129">
         <v>1404.6</v>
@@ -7008,19 +7047,19 @@
         <v>10.6</v>
       </c>
       <c r="J129" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K129">
         <v>7</v>
       </c>
       <c r="L129" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M129" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N129" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O129">
         <v>18.7</v>
@@ -7037,7 +7076,7 @@
         <v>45</v>
       </c>
       <c r="C130" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D130">
         <v>59.4</v>
@@ -7046,10 +7085,10 @@
         <v>-3</v>
       </c>
       <c r="F130" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G130" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H130">
         <v>1217.2</v>
@@ -7058,19 +7097,19 @@
         <v>10.6</v>
       </c>
       <c r="J130" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K130">
         <v>6</v>
       </c>
       <c r="L130" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M130" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N130" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O130">
         <v>18.7</v>
@@ -7087,7 +7126,7 @@
         <v>56</v>
       </c>
       <c r="C131" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D131">
         <v>57.3</v>
@@ -7096,10 +7135,10 @@
         <v>0</v>
       </c>
       <c r="F131" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G131" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H131">
         <v>445.5</v>
@@ -7108,19 +7147,19 @@
         <v>12.7</v>
       </c>
       <c r="J131" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="K131">
         <v>1</v>
       </c>
       <c r="L131" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="M131" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N131" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O131">
         <v>18.7</v>
@@ -7137,7 +7176,7 @@
         <v>33</v>
       </c>
       <c r="C132" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D132">
         <v>55.6</v>
@@ -7146,10 +7185,10 @@
         <v>-3.8</v>
       </c>
       <c r="F132" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G132" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H132">
         <v>9519</v>
@@ -7158,19 +7197,19 @@
         <v>14.4</v>
       </c>
       <c r="J132" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K132">
         <v>12</v>
       </c>
       <c r="L132" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M132" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N132" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O132">
         <v>18.7</v>
@@ -7187,7 +7226,7 @@
         <v>43</v>
       </c>
       <c r="C133" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D133">
         <v>66.40000000000001</v>
@@ -7196,10 +7235,10 @@
         <v>0</v>
       </c>
       <c r="F133" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G133" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H133">
         <v>1263.2</v>
@@ -7208,19 +7247,19 @@
         <v>3.599999999999994</v>
       </c>
       <c r="J133" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K133">
         <v>7</v>
       </c>
       <c r="L133" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M133" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N133" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="O133">
         <v>18.84</v>
@@ -7237,7 +7276,7 @@
         <v>49</v>
       </c>
       <c r="C134" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D134">
         <v>64.5</v>
@@ -7246,10 +7285,10 @@
         <v>0</v>
       </c>
       <c r="F134" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G134" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H134">
         <v>124.1</v>
@@ -7258,19 +7297,19 @@
         <v>5.5</v>
       </c>
       <c r="J134" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="K134">
         <v>2</v>
       </c>
       <c r="L134" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="M134" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N134" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="O134">
         <v>18.84</v>
@@ -7287,7 +7326,7 @@
         <v>22</v>
       </c>
       <c r="C135" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D135">
         <v>64</v>
@@ -7296,10 +7335,10 @@
         <v>0</v>
       </c>
       <c r="F135" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G135" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H135">
         <v>1371.2</v>
@@ -7308,19 +7347,19 @@
         <v>6</v>
       </c>
       <c r="J135" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K135">
         <v>13</v>
       </c>
       <c r="L135" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M135" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N135" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="O135">
         <v>18.84</v>
@@ -7337,7 +7376,7 @@
         <v>23</v>
       </c>
       <c r="C136" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D136">
         <v>64</v>
@@ -7346,10 +7385,10 @@
         <v>0</v>
       </c>
       <c r="F136" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G136" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H136">
         <v>4440.2</v>
@@ -7358,19 +7397,19 @@
         <v>6</v>
       </c>
       <c r="J136" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K136">
         <v>13</v>
       </c>
       <c r="L136" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M136" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N136" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="O136">
         <v>18.84</v>
@@ -7387,7 +7426,7 @@
         <v>46</v>
       </c>
       <c r="C137" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D137">
         <v>64</v>
@@ -7396,10 +7435,10 @@
         <v>0</v>
       </c>
       <c r="F137" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G137" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H137">
         <v>2353.4</v>
@@ -7408,19 +7447,19 @@
         <v>6</v>
       </c>
       <c r="J137" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K137">
         <v>7</v>
       </c>
       <c r="L137" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M137" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N137" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="O137">
         <v>18.84</v>
@@ -7437,7 +7476,7 @@
         <v>39</v>
       </c>
       <c r="C138" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D138">
         <v>63.9</v>
@@ -7446,10 +7485,10 @@
         <v>0</v>
       </c>
       <c r="F138" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G138" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H138">
         <v>400.9</v>
@@ -7458,19 +7497,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J138" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K138">
         <v>3</v>
       </c>
       <c r="L138" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M138" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N138" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="O138">
         <v>18.84</v>
@@ -7487,7 +7526,7 @@
         <v>40</v>
       </c>
       <c r="C139" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D139">
         <v>63.9</v>
@@ -7496,10 +7535,10 @@
         <v>0</v>
       </c>
       <c r="F139" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G139" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H139">
         <v>3856.3</v>
@@ -7508,19 +7547,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J139" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K139">
         <v>2</v>
       </c>
       <c r="L139" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="M139" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N139" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="O139">
         <v>18.84</v>
@@ -7537,7 +7576,7 @@
         <v>41</v>
       </c>
       <c r="C140" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D140">
         <v>61.4</v>
@@ -7546,10 +7585,10 @@
         <v>0</v>
       </c>
       <c r="F140" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G140" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H140">
         <v>214.69</v>
@@ -7558,19 +7597,19 @@
         <v>8.600000000000001</v>
       </c>
       <c r="J140" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K140">
         <v>7</v>
       </c>
       <c r="L140" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M140" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N140" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="O140">
         <v>18.84</v>
@@ -7587,7 +7626,7 @@
         <v>24</v>
       </c>
       <c r="C141" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D141">
         <v>61</v>
@@ -7596,10 +7635,10 @@
         <v>0</v>
       </c>
       <c r="F141" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G141" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H141">
         <v>1020.55</v>
@@ -7608,19 +7647,19 @@
         <v>9</v>
       </c>
       <c r="J141" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K141">
         <v>13</v>
       </c>
       <c r="L141" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M141" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N141" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="O141">
         <v>18.84</v>
@@ -7637,7 +7676,7 @@
         <v>42</v>
       </c>
       <c r="C142" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D142">
         <v>61</v>
@@ -7646,10 +7685,10 @@
         <v>0</v>
       </c>
       <c r="F142" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G142" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H142">
         <v>87.06999999999999</v>
@@ -7658,19 +7697,19 @@
         <v>9</v>
       </c>
       <c r="J142" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K142">
         <v>7</v>
       </c>
       <c r="L142" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M142" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N142" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="O142">
         <v>18.84</v>
@@ -7687,7 +7726,7 @@
         <v>44</v>
       </c>
       <c r="C143" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D143">
         <v>60</v>
@@ -7696,10 +7735,10 @@
         <v>0</v>
       </c>
       <c r="F143" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G143" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H143">
         <v>125.46</v>
@@ -7708,19 +7747,19 @@
         <v>10</v>
       </c>
       <c r="J143" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K143">
         <v>2</v>
       </c>
       <c r="L143" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="M143" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N143" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="O143">
         <v>18.84</v>
@@ -7737,7 +7776,7 @@
         <v>32</v>
       </c>
       <c r="C144" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D144">
         <v>59.4</v>
@@ -7746,10 +7785,10 @@
         <v>0</v>
       </c>
       <c r="F144" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G144" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H144">
         <v>1401.1</v>
@@ -7758,19 +7797,19 @@
         <v>10.6</v>
       </c>
       <c r="J144" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K144">
         <v>8</v>
       </c>
       <c r="L144" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M144" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N144" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="O144">
         <v>18.84</v>
@@ -7787,7 +7826,7 @@
         <v>45</v>
       </c>
       <c r="C145" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D145">
         <v>59.4</v>
@@ -7796,10 +7835,10 @@
         <v>0</v>
       </c>
       <c r="F145" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G145" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H145">
         <v>1218.2</v>
@@ -7808,19 +7847,19 @@
         <v>10.6</v>
       </c>
       <c r="J145" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K145">
         <v>7</v>
       </c>
       <c r="L145" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M145" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N145" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="O145">
         <v>18.84</v>
@@ -7837,7 +7876,7 @@
         <v>56</v>
       </c>
       <c r="C146" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D146">
         <v>57.3</v>
@@ -7846,10 +7885,10 @@
         <v>0</v>
       </c>
       <c r="F146" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G146" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H146">
         <v>445.65</v>
@@ -7858,19 +7897,19 @@
         <v>12.7</v>
       </c>
       <c r="J146" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="K146">
         <v>2</v>
       </c>
       <c r="L146" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="M146" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N146" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="O146">
         <v>18.84</v>
@@ -7887,7 +7926,7 @@
         <v>37</v>
       </c>
       <c r="C147" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D147">
         <v>55.9</v>
@@ -7896,10 +7935,10 @@
         <v>-6</v>
       </c>
       <c r="F147" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G147" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H147">
         <v>319.85</v>
@@ -7908,19 +7947,19 @@
         <v>14.1</v>
       </c>
       <c r="J147" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="K147">
         <v>13</v>
       </c>
       <c r="L147" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M147" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N147" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="O147">
         <v>18.84</v>
@@ -7937,7 +7976,7 @@
         <v>33</v>
       </c>
       <c r="C148" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D148">
         <v>55.6</v>
@@ -7946,10 +7985,10 @@
         <v>0</v>
       </c>
       <c r="F148" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G148" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H148">
         <v>9545.5</v>
@@ -7958,19 +7997,19 @@
         <v>14.4</v>
       </c>
       <c r="J148" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K148">
         <v>13</v>
       </c>
       <c r="L148" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M148" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N148" t="s">
-        <v>86</v>
+        <v>99</v>
       </c>
       <c r="O148">
         <v>18.84</v>
@@ -7980,26 +8019,26 @@
       </c>
     </row>
     <row r="149" spans="1:16">
-      <c r="A149" t="s">
-        <v>16</v>
+      <c r="A149">
+        <v>20260423</v>
       </c>
       <c r="B149" t="s">
         <v>43</v>
       </c>
       <c r="C149" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D149">
         <v>66.90000000000001</v>
       </c>
-      <c r="E149" t="s">
-        <v>59</v>
+      <c r="E149">
+        <v>0.5</v>
       </c>
       <c r="F149" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G149" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H149">
         <v>1262.7</v>
@@ -8008,19 +8047,19 @@
         <v>3.099999999999994</v>
       </c>
       <c r="J149" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K149">
         <v>8</v>
       </c>
       <c r="L149" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M149" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N149" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O149">
         <v>18.44</v>
@@ -8030,26 +8069,26 @@
       </c>
     </row>
     <row r="150" spans="1:16">
-      <c r="A150" t="s">
-        <v>16</v>
+      <c r="A150">
+        <v>20260423</v>
       </c>
       <c r="B150" t="s">
         <v>39</v>
       </c>
       <c r="C150" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D150">
         <v>66.8</v>
       </c>
-      <c r="E150" t="s">
-        <v>60</v>
+      <c r="E150">
+        <v>2.9</v>
       </c>
       <c r="F150" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G150" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H150">
         <v>404.6</v>
@@ -8058,19 +8097,19 @@
         <v>3.200000000000003</v>
       </c>
       <c r="J150" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K150">
         <v>4</v>
       </c>
       <c r="L150" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M150" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N150" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O150">
         <v>18.44</v>
@@ -8080,26 +8119,26 @@
       </c>
     </row>
     <row r="151" spans="1:16">
-      <c r="A151" t="s">
-        <v>16</v>
+      <c r="A151">
+        <v>20260423</v>
       </c>
       <c r="B151" t="s">
         <v>49</v>
       </c>
       <c r="C151" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D151">
         <v>65</v>
       </c>
-      <c r="E151" t="s">
-        <v>59</v>
+      <c r="E151">
+        <v>0.5</v>
       </c>
       <c r="F151" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G151" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H151">
         <v>124.38</v>
@@ -8108,19 +8147,19 @@
         <v>5</v>
       </c>
       <c r="J151" t="s">
-        <v>67</v>
+        <v>80</v>
       </c>
       <c r="K151">
         <v>3</v>
       </c>
       <c r="L151" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="M151" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N151" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O151">
         <v>18.44</v>
@@ -8130,26 +8169,26 @@
       </c>
     </row>
     <row r="152" spans="1:16">
-      <c r="A152" t="s">
-        <v>16</v>
+      <c r="A152">
+        <v>20260423</v>
       </c>
       <c r="B152" t="s">
         <v>22</v>
       </c>
       <c r="C152" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D152">
         <v>64.5</v>
       </c>
-      <c r="E152" t="s">
-        <v>59</v>
+      <c r="E152">
+        <v>0.5</v>
       </c>
       <c r="F152" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G152" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H152">
         <v>1376.9</v>
@@ -8158,19 +8197,19 @@
         <v>5.5</v>
       </c>
       <c r="J152" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K152">
         <v>14</v>
       </c>
       <c r="L152" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M152" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N152" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O152">
         <v>18.44</v>
@@ -8180,26 +8219,26 @@
       </c>
     </row>
     <row r="153" spans="1:16">
-      <c r="A153" t="s">
-        <v>16</v>
+      <c r="A153">
+        <v>20260423</v>
       </c>
       <c r="B153" t="s">
         <v>23</v>
       </c>
       <c r="C153" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D153">
         <v>64.5</v>
       </c>
-      <c r="E153" t="s">
-        <v>59</v>
+      <c r="E153">
+        <v>0.5</v>
       </c>
       <c r="F153" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G153" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H153">
         <v>4456.2</v>
@@ -8208,19 +8247,19 @@
         <v>5.5</v>
       </c>
       <c r="J153" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K153">
         <v>14</v>
       </c>
       <c r="L153" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M153" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N153" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O153">
         <v>18.44</v>
@@ -8230,26 +8269,26 @@
       </c>
     </row>
     <row r="154" spans="1:16">
-      <c r="A154" t="s">
-        <v>16</v>
+      <c r="A154">
+        <v>20260423</v>
       </c>
       <c r="B154" t="s">
         <v>46</v>
       </c>
       <c r="C154" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D154">
         <v>64.5</v>
       </c>
-      <c r="E154" t="s">
-        <v>59</v>
+      <c r="E154">
+        <v>0.5</v>
       </c>
       <c r="F154" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G154" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H154">
         <v>2358.9</v>
@@ -8258,19 +8297,19 @@
         <v>5.5</v>
       </c>
       <c r="J154" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K154">
         <v>8</v>
       </c>
       <c r="L154" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M154" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N154" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O154">
         <v>18.44</v>
@@ -8280,26 +8319,26 @@
       </c>
     </row>
     <row r="155" spans="1:16">
-      <c r="A155" t="s">
-        <v>16</v>
+      <c r="A155">
+        <v>20260423</v>
       </c>
       <c r="B155" t="s">
         <v>40</v>
       </c>
       <c r="C155" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D155">
         <v>64.40000000000001</v>
       </c>
-      <c r="E155" t="s">
-        <v>59</v>
+      <c r="E155">
+        <v>0.5</v>
       </c>
       <c r="F155" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G155" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H155">
         <v>3875.6</v>
@@ -8308,19 +8347,19 @@
         <v>5.599999999999994</v>
       </c>
       <c r="J155" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K155">
         <v>3</v>
       </c>
       <c r="L155" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="M155" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N155" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O155">
         <v>18.44</v>
@@ -8330,26 +8369,26 @@
       </c>
     </row>
     <row r="156" spans="1:16">
-      <c r="A156" t="s">
-        <v>16</v>
+      <c r="A156">
+        <v>20260423</v>
       </c>
       <c r="B156" t="s">
         <v>45</v>
       </c>
       <c r="C156" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D156">
         <v>63.3</v>
       </c>
-      <c r="E156" t="s">
-        <v>61</v>
+      <c r="E156">
+        <v>3.9</v>
       </c>
       <c r="F156" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G156" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H156">
         <v>1231.65</v>
@@ -8358,19 +8397,19 @@
         <v>6.700000000000003</v>
       </c>
       <c r="J156" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K156">
         <v>8</v>
       </c>
       <c r="L156" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M156" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N156" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O156">
         <v>18.44</v>
@@ -8380,26 +8419,26 @@
       </c>
     </row>
     <row r="157" spans="1:16">
-      <c r="A157" t="s">
-        <v>16</v>
+      <c r="A157">
+        <v>20260423</v>
       </c>
       <c r="B157" t="s">
         <v>41</v>
       </c>
       <c r="C157" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D157">
         <v>62.9</v>
       </c>
-      <c r="E157" t="s">
-        <v>62</v>
+      <c r="E157">
+        <v>1.5</v>
       </c>
       <c r="F157" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G157" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H157">
         <v>215.19</v>
@@ -8408,19 +8447,19 @@
         <v>7.100000000000001</v>
       </c>
       <c r="J157" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K157">
         <v>8</v>
       </c>
       <c r="L157" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M157" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N157" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O157">
         <v>18.44</v>
@@ -8430,26 +8469,26 @@
       </c>
     </row>
     <row r="158" spans="1:16">
-      <c r="A158" t="s">
-        <v>16</v>
+      <c r="A158">
+        <v>20260423</v>
       </c>
       <c r="B158" t="s">
         <v>24</v>
       </c>
       <c r="C158" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D158">
         <v>61.5</v>
       </c>
-      <c r="E158" t="s">
-        <v>59</v>
+      <c r="E158">
+        <v>0.5</v>
       </c>
       <c r="F158" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G158" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H158">
         <v>1016.45</v>
@@ -8458,19 +8497,19 @@
         <v>8.5</v>
       </c>
       <c r="J158" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K158">
         <v>14</v>
       </c>
       <c r="L158" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M158" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N158" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O158">
         <v>18.44</v>
@@ -8480,26 +8519,26 @@
       </c>
     </row>
     <row r="159" spans="1:16">
-      <c r="A159" t="s">
-        <v>16</v>
+      <c r="A159">
+        <v>20260423</v>
       </c>
       <c r="B159" t="s">
         <v>42</v>
       </c>
       <c r="C159" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D159">
         <v>61.5</v>
       </c>
-      <c r="E159" t="s">
-        <v>59</v>
+      <c r="E159">
+        <v>0.5</v>
       </c>
       <c r="F159" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G159" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H159">
         <v>87.40000000000001</v>
@@ -8508,19 +8547,19 @@
         <v>8.5</v>
       </c>
       <c r="J159" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K159">
         <v>8</v>
       </c>
       <c r="L159" t="s">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="M159" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N159" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O159">
         <v>18.44</v>
@@ -8530,26 +8569,26 @@
       </c>
     </row>
     <row r="160" spans="1:16">
-      <c r="A160" t="s">
-        <v>16</v>
+      <c r="A160">
+        <v>20260423</v>
       </c>
       <c r="B160" t="s">
         <v>32</v>
       </c>
       <c r="C160" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D160">
         <v>60.9</v>
       </c>
-      <c r="E160" t="s">
-        <v>62</v>
+      <c r="E160">
+        <v>1.5</v>
       </c>
       <c r="F160" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G160" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H160">
         <v>1408.8</v>
@@ -8558,19 +8597,19 @@
         <v>9.100000000000001</v>
       </c>
       <c r="J160" t="s">
-        <v>68</v>
+        <v>81</v>
       </c>
       <c r="K160">
         <v>9</v>
       </c>
       <c r="L160" t="s">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="M160" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N160" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O160">
         <v>18.44</v>
@@ -8580,26 +8619,26 @@
       </c>
     </row>
     <row r="161" spans="1:16">
-      <c r="A161" t="s">
-        <v>16</v>
+      <c r="A161">
+        <v>20260423</v>
       </c>
       <c r="B161" t="s">
         <v>44</v>
       </c>
       <c r="C161" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D161">
         <v>60.5</v>
       </c>
-      <c r="E161" t="s">
-        <v>59</v>
+      <c r="E161">
+        <v>0.5</v>
       </c>
       <c r="F161" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G161" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H161">
         <v>125.82</v>
@@ -8608,19 +8647,19 @@
         <v>9.5</v>
       </c>
       <c r="J161" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K161">
         <v>3</v>
       </c>
       <c r="L161" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="M161" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N161" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O161">
         <v>18.44</v>
@@ -8630,26 +8669,26 @@
       </c>
     </row>
     <row r="162" spans="1:16">
-      <c r="A162" t="s">
-        <v>16</v>
+      <c r="A162">
+        <v>20260423</v>
       </c>
       <c r="B162" t="s">
         <v>56</v>
       </c>
       <c r="C162" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D162">
         <v>57.8</v>
       </c>
-      <c r="E162" t="s">
-        <v>59</v>
+      <c r="E162">
+        <v>0.5</v>
       </c>
       <c r="F162" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G162" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H162">
         <v>451.3</v>
@@ -8658,19 +8697,19 @@
         <v>12.2</v>
       </c>
       <c r="J162" t="s">
-        <v>73</v>
+        <v>86</v>
       </c>
       <c r="K162">
         <v>3</v>
       </c>
       <c r="L162" t="s">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="M162" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N162" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O162">
         <v>18.44</v>
@@ -8680,26 +8719,26 @@
       </c>
     </row>
     <row r="163" spans="1:16">
-      <c r="A163" t="s">
-        <v>16</v>
+      <c r="A163">
+        <v>20260423</v>
       </c>
       <c r="B163" t="s">
         <v>37</v>
       </c>
       <c r="C163" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D163">
         <v>56.4</v>
       </c>
-      <c r="E163" t="s">
-        <v>59</v>
+      <c r="E163">
+        <v>0.5</v>
       </c>
       <c r="F163" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G163" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H163">
         <v>320.1</v>
@@ -8708,19 +8747,19 @@
         <v>13.6</v>
       </c>
       <c r="J163" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="K163">
         <v>14</v>
       </c>
       <c r="L163" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M163" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N163" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O163">
         <v>18.44</v>
@@ -8730,26 +8769,26 @@
       </c>
     </row>
     <row r="164" spans="1:16">
-      <c r="A164" t="s">
-        <v>16</v>
+      <c r="A164">
+        <v>20260423</v>
       </c>
       <c r="B164" t="s">
         <v>33</v>
       </c>
       <c r="C164" t="s">
-        <v>58</v>
+        <v>71</v>
       </c>
       <c r="D164">
         <v>56.1</v>
       </c>
-      <c r="E164" t="s">
-        <v>59</v>
+      <c r="E164">
+        <v>0.5</v>
       </c>
       <c r="F164" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="G164" t="s">
-        <v>64</v>
+        <v>77</v>
       </c>
       <c r="H164">
         <v>9549.5</v>
@@ -8758,25 +8797,1019 @@
         <v>13.9</v>
       </c>
       <c r="J164" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="K164">
         <v>14</v>
       </c>
       <c r="L164" t="s">
-        <v>76</v>
+        <v>89</v>
       </c>
       <c r="M164" t="s">
-        <v>80</v>
+        <v>93</v>
       </c>
       <c r="N164" t="s">
-        <v>85</v>
+        <v>98</v>
       </c>
       <c r="O164">
         <v>18.44</v>
       </c>
       <c r="P164">
         <v>250</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16">
+      <c r="A165" t="s">
+        <v>16</v>
+      </c>
+      <c r="B165" t="s">
+        <v>57</v>
+      </c>
+      <c r="C165" t="s">
+        <v>70</v>
+      </c>
+      <c r="D165">
+        <v>78.8</v>
+      </c>
+      <c r="E165" t="s">
+        <v>72</v>
+      </c>
+      <c r="F165" t="s">
+        <v>76</v>
+      </c>
+      <c r="G165" t="s">
+        <v>78</v>
+      </c>
+      <c r="H165">
+        <v>6727</v>
+      </c>
+      <c r="I165">
+        <v>0</v>
+      </c>
+      <c r="K165">
+        <v>1</v>
+      </c>
+      <c r="L165" t="s">
+        <v>16</v>
+      </c>
+      <c r="M165" t="s">
+        <v>93</v>
+      </c>
+      <c r="N165" t="s">
+        <v>99</v>
+      </c>
+      <c r="O165">
+        <v>18.59</v>
+      </c>
+      <c r="P165">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16">
+      <c r="A166" t="s">
+        <v>16</v>
+      </c>
+      <c r="B166" t="s">
+        <v>58</v>
+      </c>
+      <c r="C166" t="s">
+        <v>70</v>
+      </c>
+      <c r="D166">
+        <v>75.8</v>
+      </c>
+      <c r="E166" t="s">
+        <v>72</v>
+      </c>
+      <c r="F166" t="s">
+        <v>76</v>
+      </c>
+      <c r="G166" t="s">
+        <v>77</v>
+      </c>
+      <c r="H166">
+        <v>4135.1</v>
+      </c>
+      <c r="I166">
+        <v>0</v>
+      </c>
+      <c r="K166">
+        <v>1</v>
+      </c>
+      <c r="L166" t="s">
+        <v>16</v>
+      </c>
+      <c r="M166" t="s">
+        <v>93</v>
+      </c>
+      <c r="N166" t="s">
+        <v>99</v>
+      </c>
+      <c r="O166">
+        <v>18.59</v>
+      </c>
+      <c r="P166">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16">
+      <c r="A167" t="s">
+        <v>16</v>
+      </c>
+      <c r="B167" t="s">
+        <v>59</v>
+      </c>
+      <c r="C167" t="s">
+        <v>71</v>
+      </c>
+      <c r="D167">
+        <v>69.3</v>
+      </c>
+      <c r="E167" t="s">
+        <v>72</v>
+      </c>
+      <c r="F167" t="s">
+        <v>76</v>
+      </c>
+      <c r="G167" t="s">
+        <v>77</v>
+      </c>
+      <c r="H167">
+        <v>297</v>
+      </c>
+      <c r="I167">
+        <v>0.7000000000000028</v>
+      </c>
+      <c r="J167" t="s">
+        <v>80</v>
+      </c>
+      <c r="K167">
+        <v>1</v>
+      </c>
+      <c r="L167" t="s">
+        <v>92</v>
+      </c>
+      <c r="M167" t="s">
+        <v>93</v>
+      </c>
+      <c r="N167" t="s">
+        <v>99</v>
+      </c>
+      <c r="O167">
+        <v>18.59</v>
+      </c>
+      <c r="P167">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16">
+      <c r="A168" t="s">
+        <v>16</v>
+      </c>
+      <c r="B168" t="s">
+        <v>60</v>
+      </c>
+      <c r="C168" t="s">
+        <v>71</v>
+      </c>
+      <c r="D168">
+        <v>68.3</v>
+      </c>
+      <c r="E168" t="s">
+        <v>72</v>
+      </c>
+      <c r="F168" t="s">
+        <v>76</v>
+      </c>
+      <c r="G168" t="s">
+        <v>77</v>
+      </c>
+      <c r="H168">
+        <v>2335</v>
+      </c>
+      <c r="I168">
+        <v>1.700000000000003</v>
+      </c>
+      <c r="J168" t="s">
+        <v>79</v>
+      </c>
+      <c r="K168">
+        <v>1</v>
+      </c>
+      <c r="L168" t="s">
+        <v>92</v>
+      </c>
+      <c r="M168" t="s">
+        <v>93</v>
+      </c>
+      <c r="N168" t="s">
+        <v>99</v>
+      </c>
+      <c r="O168">
+        <v>18.59</v>
+      </c>
+      <c r="P168">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16">
+      <c r="A169" t="s">
+        <v>16</v>
+      </c>
+      <c r="B169" t="s">
+        <v>61</v>
+      </c>
+      <c r="C169" t="s">
+        <v>71</v>
+      </c>
+      <c r="D169">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="E169" t="s">
+        <v>72</v>
+      </c>
+      <c r="F169" t="s">
+        <v>76</v>
+      </c>
+      <c r="G169" t="s">
+        <v>77</v>
+      </c>
+      <c r="H169">
+        <v>295.4</v>
+      </c>
+      <c r="I169">
+        <v>3.599999999999994</v>
+      </c>
+      <c r="J169" t="s">
+        <v>79</v>
+      </c>
+      <c r="K169">
+        <v>1</v>
+      </c>
+      <c r="L169" t="s">
+        <v>92</v>
+      </c>
+      <c r="M169" t="s">
+        <v>93</v>
+      </c>
+      <c r="N169" t="s">
+        <v>99</v>
+      </c>
+      <c r="O169">
+        <v>18.59</v>
+      </c>
+      <c r="P169">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16">
+      <c r="A170" t="s">
+        <v>16</v>
+      </c>
+      <c r="B170" t="s">
+        <v>62</v>
+      </c>
+      <c r="C170" t="s">
+        <v>71</v>
+      </c>
+      <c r="D170">
+        <v>66.3</v>
+      </c>
+      <c r="E170" t="s">
+        <v>72</v>
+      </c>
+      <c r="F170" t="s">
+        <v>76</v>
+      </c>
+      <c r="G170" t="s">
+        <v>77</v>
+      </c>
+      <c r="H170">
+        <v>1435.4</v>
+      </c>
+      <c r="I170">
+        <v>3.700000000000003</v>
+      </c>
+      <c r="J170" t="s">
+        <v>79</v>
+      </c>
+      <c r="K170">
+        <v>1</v>
+      </c>
+      <c r="L170" t="s">
+        <v>92</v>
+      </c>
+      <c r="M170" t="s">
+        <v>93</v>
+      </c>
+      <c r="N170" t="s">
+        <v>99</v>
+      </c>
+      <c r="O170">
+        <v>18.59</v>
+      </c>
+      <c r="P170">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16">
+      <c r="A171" t="s">
+        <v>16</v>
+      </c>
+      <c r="B171" t="s">
+        <v>63</v>
+      </c>
+      <c r="C171" t="s">
+        <v>71</v>
+      </c>
+      <c r="D171">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="E171" t="s">
+        <v>72</v>
+      </c>
+      <c r="F171" t="s">
+        <v>76</v>
+      </c>
+      <c r="G171" t="s">
+        <v>77</v>
+      </c>
+      <c r="H171">
+        <v>1460.2</v>
+      </c>
+      <c r="I171">
+        <v>4.599999999999994</v>
+      </c>
+      <c r="J171" t="s">
+        <v>82</v>
+      </c>
+      <c r="K171">
+        <v>1</v>
+      </c>
+      <c r="L171" t="s">
+        <v>92</v>
+      </c>
+      <c r="M171" t="s">
+        <v>93</v>
+      </c>
+      <c r="N171" t="s">
+        <v>99</v>
+      </c>
+      <c r="O171">
+        <v>18.59</v>
+      </c>
+      <c r="P171">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16">
+      <c r="A172" t="s">
+        <v>16</v>
+      </c>
+      <c r="B172" t="s">
+        <v>22</v>
+      </c>
+      <c r="C172" t="s">
+        <v>71</v>
+      </c>
+      <c r="D172">
+        <v>64</v>
+      </c>
+      <c r="E172" t="s">
+        <v>73</v>
+      </c>
+      <c r="F172" t="s">
+        <v>76</v>
+      </c>
+      <c r="G172" t="s">
+        <v>77</v>
+      </c>
+      <c r="H172">
+        <v>1369.6</v>
+      </c>
+      <c r="I172">
+        <v>6</v>
+      </c>
+      <c r="J172" t="s">
+        <v>79</v>
+      </c>
+      <c r="K172">
+        <v>15</v>
+      </c>
+      <c r="L172" t="s">
+        <v>89</v>
+      </c>
+      <c r="M172" t="s">
+        <v>93</v>
+      </c>
+      <c r="N172" t="s">
+        <v>99</v>
+      </c>
+      <c r="O172">
+        <v>18.59</v>
+      </c>
+      <c r="P172">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16">
+      <c r="A173" t="s">
+        <v>16</v>
+      </c>
+      <c r="B173" t="s">
+        <v>23</v>
+      </c>
+      <c r="C173" t="s">
+        <v>71</v>
+      </c>
+      <c r="D173">
+        <v>64</v>
+      </c>
+      <c r="E173" t="s">
+        <v>73</v>
+      </c>
+      <c r="F173" t="s">
+        <v>76</v>
+      </c>
+      <c r="G173" t="s">
+        <v>77</v>
+      </c>
+      <c r="H173">
+        <v>4456.5</v>
+      </c>
+      <c r="I173">
+        <v>6</v>
+      </c>
+      <c r="J173" t="s">
+        <v>79</v>
+      </c>
+      <c r="K173">
+        <v>15</v>
+      </c>
+      <c r="L173" t="s">
+        <v>89</v>
+      </c>
+      <c r="M173" t="s">
+        <v>93</v>
+      </c>
+      <c r="N173" t="s">
+        <v>99</v>
+      </c>
+      <c r="O173">
+        <v>18.59</v>
+      </c>
+      <c r="P173">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16">
+      <c r="A174" t="s">
+        <v>16</v>
+      </c>
+      <c r="B174" t="s">
+        <v>39</v>
+      </c>
+      <c r="C174" t="s">
+        <v>71</v>
+      </c>
+      <c r="D174">
+        <v>63.9</v>
+      </c>
+      <c r="E174" t="s">
+        <v>74</v>
+      </c>
+      <c r="F174" t="s">
+        <v>76</v>
+      </c>
+      <c r="G174" t="s">
+        <v>77</v>
+      </c>
+      <c r="H174">
+        <v>402.25</v>
+      </c>
+      <c r="I174">
+        <v>6.100000000000001</v>
+      </c>
+      <c r="J174" t="s">
+        <v>79</v>
+      </c>
+      <c r="K174">
+        <v>5</v>
+      </c>
+      <c r="L174" t="s">
+        <v>91</v>
+      </c>
+      <c r="M174" t="s">
+        <v>93</v>
+      </c>
+      <c r="N174" t="s">
+        <v>99</v>
+      </c>
+      <c r="O174">
+        <v>18.59</v>
+      </c>
+      <c r="P174">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16">
+      <c r="A175" t="s">
+        <v>16</v>
+      </c>
+      <c r="B175" t="s">
+        <v>64</v>
+      </c>
+      <c r="C175" t="s">
+        <v>71</v>
+      </c>
+      <c r="D175">
+        <v>61.5</v>
+      </c>
+      <c r="E175" t="s">
+        <v>72</v>
+      </c>
+      <c r="F175" t="s">
+        <v>76</v>
+      </c>
+      <c r="G175" t="s">
+        <v>77</v>
+      </c>
+      <c r="H175">
+        <v>2022.9</v>
+      </c>
+      <c r="I175">
+        <v>8.5</v>
+      </c>
+      <c r="J175" t="s">
+        <v>80</v>
+      </c>
+      <c r="K175">
+        <v>1</v>
+      </c>
+      <c r="L175" t="s">
+        <v>92</v>
+      </c>
+      <c r="M175" t="s">
+        <v>93</v>
+      </c>
+      <c r="N175" t="s">
+        <v>99</v>
+      </c>
+      <c r="O175">
+        <v>18.59</v>
+      </c>
+      <c r="P175">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16">
+      <c r="A176" t="s">
+        <v>16</v>
+      </c>
+      <c r="B176" t="s">
+        <v>32</v>
+      </c>
+      <c r="C176" t="s">
+        <v>71</v>
+      </c>
+      <c r="D176">
+        <v>61.4</v>
+      </c>
+      <c r="E176" t="s">
+        <v>75</v>
+      </c>
+      <c r="F176" t="s">
+        <v>76</v>
+      </c>
+      <c r="G176" t="s">
+        <v>77</v>
+      </c>
+      <c r="H176">
+        <v>1410.5</v>
+      </c>
+      <c r="I176">
+        <v>8.600000000000001</v>
+      </c>
+      <c r="J176" t="s">
+        <v>81</v>
+      </c>
+      <c r="K176">
+        <v>10</v>
+      </c>
+      <c r="L176" t="s">
+        <v>88</v>
+      </c>
+      <c r="M176" t="s">
+        <v>93</v>
+      </c>
+      <c r="N176" t="s">
+        <v>99</v>
+      </c>
+      <c r="O176">
+        <v>18.59</v>
+      </c>
+      <c r="P176">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="177" spans="1:16">
+      <c r="A177" t="s">
+        <v>16</v>
+      </c>
+      <c r="B177" t="s">
+        <v>65</v>
+      </c>
+      <c r="C177" t="s">
+        <v>71</v>
+      </c>
+      <c r="D177">
+        <v>61.4</v>
+      </c>
+      <c r="E177" t="s">
+        <v>72</v>
+      </c>
+      <c r="F177" t="s">
+        <v>76</v>
+      </c>
+      <c r="G177" t="s">
+        <v>77</v>
+      </c>
+      <c r="H177">
+        <v>1056.25</v>
+      </c>
+      <c r="I177">
+        <v>8.600000000000001</v>
+      </c>
+      <c r="J177" t="s">
+        <v>81</v>
+      </c>
+      <c r="K177">
+        <v>1</v>
+      </c>
+      <c r="L177" t="s">
+        <v>92</v>
+      </c>
+      <c r="M177" t="s">
+        <v>93</v>
+      </c>
+      <c r="N177" t="s">
+        <v>99</v>
+      </c>
+      <c r="O177">
+        <v>18.59</v>
+      </c>
+      <c r="P177">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="178" spans="1:16">
+      <c r="A178" t="s">
+        <v>16</v>
+      </c>
+      <c r="B178" t="s">
+        <v>66</v>
+      </c>
+      <c r="C178" t="s">
+        <v>71</v>
+      </c>
+      <c r="D178">
+        <v>60.9</v>
+      </c>
+      <c r="E178" t="s">
+        <v>72</v>
+      </c>
+      <c r="F178" t="s">
+        <v>76</v>
+      </c>
+      <c r="G178" t="s">
+        <v>77</v>
+      </c>
+      <c r="H178">
+        <v>187.01</v>
+      </c>
+      <c r="I178">
+        <v>9.100000000000001</v>
+      </c>
+      <c r="J178" t="s">
+        <v>80</v>
+      </c>
+      <c r="K178">
+        <v>1</v>
+      </c>
+      <c r="L178" t="s">
+        <v>92</v>
+      </c>
+      <c r="M178" t="s">
+        <v>93</v>
+      </c>
+      <c r="N178" t="s">
+        <v>99</v>
+      </c>
+      <c r="O178">
+        <v>18.59</v>
+      </c>
+      <c r="P178">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="179" spans="1:16">
+      <c r="A179" t="s">
+        <v>16</v>
+      </c>
+      <c r="B179" t="s">
+        <v>67</v>
+      </c>
+      <c r="C179" t="s">
+        <v>71</v>
+      </c>
+      <c r="D179">
+        <v>59.4</v>
+      </c>
+      <c r="E179" t="s">
+        <v>72</v>
+      </c>
+      <c r="F179" t="s">
+        <v>76</v>
+      </c>
+      <c r="G179" t="s">
+        <v>77</v>
+      </c>
+      <c r="H179">
+        <v>180.18</v>
+      </c>
+      <c r="I179">
+        <v>10.6</v>
+      </c>
+      <c r="J179" t="s">
+        <v>81</v>
+      </c>
+      <c r="K179">
+        <v>1</v>
+      </c>
+      <c r="L179" t="s">
+        <v>92</v>
+      </c>
+      <c r="M179" t="s">
+        <v>93</v>
+      </c>
+      <c r="N179" t="s">
+        <v>99</v>
+      </c>
+      <c r="O179">
+        <v>18.59</v>
+      </c>
+      <c r="P179">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="180" spans="1:16">
+      <c r="A180" t="s">
+        <v>16</v>
+      </c>
+      <c r="B180" t="s">
+        <v>68</v>
+      </c>
+      <c r="C180" t="s">
+        <v>71</v>
+      </c>
+      <c r="D180">
+        <v>59.4</v>
+      </c>
+      <c r="E180" t="s">
+        <v>72</v>
+      </c>
+      <c r="F180" t="s">
+        <v>76</v>
+      </c>
+      <c r="G180" t="s">
+        <v>77</v>
+      </c>
+      <c r="H180">
+        <v>243.68</v>
+      </c>
+      <c r="I180">
+        <v>10.6</v>
+      </c>
+      <c r="J180" t="s">
+        <v>81</v>
+      </c>
+      <c r="K180">
+        <v>1</v>
+      </c>
+      <c r="L180" t="s">
+        <v>92</v>
+      </c>
+      <c r="M180" t="s">
+        <v>93</v>
+      </c>
+      <c r="N180" t="s">
+        <v>99</v>
+      </c>
+      <c r="O180">
+        <v>18.59</v>
+      </c>
+      <c r="P180">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="181" spans="1:16">
+      <c r="A181" t="s">
+        <v>16</v>
+      </c>
+      <c r="B181" t="s">
+        <v>56</v>
+      </c>
+      <c r="C181" t="s">
+        <v>71</v>
+      </c>
+      <c r="D181">
+        <v>57.3</v>
+      </c>
+      <c r="E181" t="s">
+        <v>73</v>
+      </c>
+      <c r="F181" t="s">
+        <v>76</v>
+      </c>
+      <c r="G181" t="s">
+        <v>77</v>
+      </c>
+      <c r="H181">
+        <v>450.65</v>
+      </c>
+      <c r="I181">
+        <v>12.7</v>
+      </c>
+      <c r="J181" t="s">
+        <v>86</v>
+      </c>
+      <c r="K181">
+        <v>4</v>
+      </c>
+      <c r="L181" t="s">
+        <v>92</v>
+      </c>
+      <c r="M181" t="s">
+        <v>93</v>
+      </c>
+      <c r="N181" t="s">
+        <v>99</v>
+      </c>
+      <c r="O181">
+        <v>18.59</v>
+      </c>
+      <c r="P181">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="182" spans="1:16">
+      <c r="A182" t="s">
+        <v>16</v>
+      </c>
+      <c r="B182" t="s">
+        <v>69</v>
+      </c>
+      <c r="C182" t="s">
+        <v>71</v>
+      </c>
+      <c r="D182">
+        <v>56.9</v>
+      </c>
+      <c r="E182" t="s">
+        <v>72</v>
+      </c>
+      <c r="F182" t="s">
+        <v>76</v>
+      </c>
+      <c r="G182" t="s">
+        <v>77</v>
+      </c>
+      <c r="H182">
+        <v>97.75</v>
+      </c>
+      <c r="I182">
+        <v>13.1</v>
+      </c>
+      <c r="J182" t="s">
+        <v>81</v>
+      </c>
+      <c r="K182">
+        <v>1</v>
+      </c>
+      <c r="L182" t="s">
+        <v>92</v>
+      </c>
+      <c r="M182" t="s">
+        <v>93</v>
+      </c>
+      <c r="N182" t="s">
+        <v>99</v>
+      </c>
+      <c r="O182">
+        <v>18.59</v>
+      </c>
+      <c r="P182">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="183" spans="1:16">
+      <c r="A183" t="s">
+        <v>16</v>
+      </c>
+      <c r="B183" t="s">
+        <v>33</v>
+      </c>
+      <c r="C183" t="s">
+        <v>71</v>
+      </c>
+      <c r="D183">
+        <v>56.6</v>
+      </c>
+      <c r="E183" t="s">
+        <v>75</v>
+      </c>
+      <c r="F183" t="s">
+        <v>76</v>
+      </c>
+      <c r="G183" t="s">
+        <v>77</v>
+      </c>
+      <c r="H183">
+        <v>9550.5</v>
+      </c>
+      <c r="I183">
+        <v>13.4</v>
+      </c>
+      <c r="J183" t="s">
+        <v>79</v>
+      </c>
+      <c r="K183">
+        <v>15</v>
+      </c>
+      <c r="L183" t="s">
+        <v>89</v>
+      </c>
+      <c r="M183" t="s">
+        <v>93</v>
+      </c>
+      <c r="N183" t="s">
+        <v>99</v>
+      </c>
+      <c r="O183">
+        <v>18.59</v>
+      </c>
+      <c r="P183">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="184" spans="1:16">
+      <c r="A184" t="s">
+        <v>16</v>
+      </c>
+      <c r="B184" t="s">
+        <v>37</v>
+      </c>
+      <c r="C184" t="s">
+        <v>71</v>
+      </c>
+      <c r="D184">
+        <v>55.9</v>
+      </c>
+      <c r="E184" t="s">
+        <v>73</v>
+      </c>
+      <c r="F184" t="s">
+        <v>76</v>
+      </c>
+      <c r="G184" t="s">
+        <v>77</v>
+      </c>
+      <c r="H184">
+        <v>319.15</v>
+      </c>
+      <c r="I184">
+        <v>14.1</v>
+      </c>
+      <c r="J184" t="s">
+        <v>83</v>
+      </c>
+      <c r="K184">
+        <v>15</v>
+      </c>
+      <c r="L184" t="s">
+        <v>89</v>
+      </c>
+      <c r="M184" t="s">
+        <v>93</v>
+      </c>
+      <c r="N184" t="s">
+        <v>99</v>
+      </c>
+      <c r="O184">
+        <v>18.59</v>
+      </c>
+      <c r="P184">
+        <v>128</v>
       </c>
     </row>
   </sheetData>

--- a/reports/watchlist_history.xlsx
+++ b/reports/watchlist_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1508" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="97">
   <si>
     <t>Date</t>
   </si>
@@ -233,15 +233,6 @@
   </si>
   <si>
     <t>+0.0</t>
-  </si>
-  <si>
-    <t>-0.5</t>
-  </si>
-  <si>
-    <t>-2.9</t>
-  </si>
-  <si>
-    <t>+0.5</t>
   </si>
   <si>
     <t>Stage 2 — Uptrend ✓</t>
@@ -645,7 +636,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P184"/>
+  <dimension ref="A1:P204"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -715,10 +706,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H2">
         <v>11714</v>
@@ -730,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O2">
         <v>17.53</v>
@@ -762,10 +753,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H3">
         <v>514.05</v>
@@ -777,13 +768,13 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M3" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N3" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O3">
         <v>17.53</v>
@@ -809,10 +800,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H4">
         <v>1621.5</v>
@@ -824,13 +815,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="M4" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N4" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O4">
         <v>17.53</v>
@@ -856,10 +847,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G5" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H5">
         <v>191.38</v>
@@ -868,19 +859,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J5" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M5" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O5">
         <v>17.53</v>
@@ -906,10 +897,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G6" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H6">
         <v>1318.1</v>
@@ -918,19 +909,19 @@
         <v>0.9000000000000057</v>
       </c>
       <c r="J6" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M6" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O6">
         <v>17.53</v>
@@ -956,10 +947,10 @@
         <v>-0.5</v>
       </c>
       <c r="F7" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G7" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H7">
         <v>1377.7</v>
@@ -968,19 +959,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K7">
         <v>6</v>
       </c>
       <c r="L7" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O7">
         <v>17.53</v>
@@ -1006,10 +997,10 @@
         <v>-0.5</v>
       </c>
       <c r="F8" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G8" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H8">
         <v>4479.7</v>
@@ -1018,19 +1009,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J8" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K8">
         <v>6</v>
       </c>
       <c r="L8" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M8" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O8">
         <v>17.53</v>
@@ -1056,10 +1047,10 @@
         <v>-0.5</v>
       </c>
       <c r="F9" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H9">
         <v>1045.3</v>
@@ -1068,19 +1059,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J9" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K9">
         <v>6</v>
       </c>
       <c r="L9" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M9" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N9" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O9">
         <v>17.53</v>
@@ -1106,10 +1097,10 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G10" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H10">
         <v>1055.65</v>
@@ -1118,19 +1109,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J10" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M10" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N10" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O10">
         <v>17.53</v>
@@ -1156,10 +1147,10 @@
         <v>-0.5</v>
       </c>
       <c r="F11" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H11">
         <v>1045.3</v>
@@ -1168,19 +1159,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J11" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K11">
         <v>6</v>
       </c>
       <c r="L11" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M11" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N11" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O11">
         <v>17.53</v>
@@ -1206,10 +1197,10 @@
         <v>-0.5</v>
       </c>
       <c r="F12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H12">
         <v>4479.7</v>
@@ -1218,19 +1209,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J12" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K12">
         <v>6</v>
       </c>
       <c r="L12" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M12" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N12" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O12">
         <v>17.53</v>
@@ -1256,10 +1247,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G13" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H13">
         <v>581.3</v>
@@ -1268,19 +1259,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J13" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K13">
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M13" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N13" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O13">
         <v>17.53</v>
@@ -1306,10 +1297,10 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G14" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H14">
         <v>458.9</v>
@@ -1318,19 +1309,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J14" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M14" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N14" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O14">
         <v>17.53</v>
@@ -1356,10 +1347,10 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G15" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H15">
         <v>196.02</v>
@@ -1368,19 +1359,19 @@
         <v>4.400000000000006</v>
       </c>
       <c r="J15" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M15" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N15" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O15">
         <v>17.53</v>
@@ -1406,10 +1397,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G16" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H16">
         <v>4172.9</v>
@@ -1418,19 +1409,19 @@
         <v>5</v>
       </c>
       <c r="J16" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K16">
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M16" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N16" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O16">
         <v>17.53</v>
@@ -1456,10 +1447,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G17" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H17">
         <v>6373.5</v>
@@ -1468,19 +1459,19 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K17">
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M17" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O17">
         <v>17.53</v>
@@ -1506,10 +1497,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G18" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H18">
         <v>1113.1</v>
@@ -1518,19 +1509,19 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J18" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M18" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N18" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O18">
         <v>17.53</v>
@@ -1556,10 +1547,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G19" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H19">
         <v>1379.9</v>
@@ -1568,19 +1559,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J19" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K19">
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M19" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N19" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O19">
         <v>17.53</v>
@@ -1606,10 +1597,10 @@
         <v>-0.5</v>
       </c>
       <c r="F20" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G20" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H20">
         <v>9793</v>
@@ -1618,19 +1609,19 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J20" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K20">
         <v>6</v>
       </c>
       <c r="L20" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M20" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N20" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O20">
         <v>17.53</v>
@@ -1656,10 +1647,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G21" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H21">
         <v>7955.5</v>
@@ -1668,19 +1659,19 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J21" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K21">
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M21" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N21" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O21">
         <v>17.53</v>
@@ -1706,10 +1697,10 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G22" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H22">
         <v>1037.85</v>
@@ -1718,19 +1709,19 @@
         <v>6.399999999999999</v>
       </c>
       <c r="J22" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K22">
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M22" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N22" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O22">
         <v>17.53</v>
@@ -1756,10 +1747,10 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G23" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H23">
         <v>979.1</v>
@@ -1768,19 +1759,19 @@
         <v>8.399999999999999</v>
       </c>
       <c r="J23" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K23">
         <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M23" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N23" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O23">
         <v>17.53</v>
@@ -1806,10 +1797,10 @@
         <v>-0.5</v>
       </c>
       <c r="F24" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G24" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H24">
         <v>319.35</v>
@@ -1818,19 +1809,19 @@
         <v>8.5</v>
       </c>
       <c r="J24" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K24">
         <v>6</v>
       </c>
       <c r="L24" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M24" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N24" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="O24">
         <v>17.53</v>
@@ -1856,10 +1847,10 @@
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G25" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H25">
         <v>767.65</v>
@@ -1871,13 +1862,13 @@
         <v>1</v>
       </c>
       <c r="L25" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="M25" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N25" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O25">
         <v>18.27</v>
@@ -1903,10 +1894,10 @@
         <v>7.8</v>
       </c>
       <c r="F26" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G26" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H26">
         <v>404.1</v>
@@ -1915,19 +1906,19 @@
         <v>1</v>
       </c>
       <c r="J26" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K26">
         <v>7</v>
       </c>
       <c r="L26" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M26" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N26" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O26">
         <v>18.27</v>
@@ -1953,10 +1944,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G27" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H27">
         <v>3847</v>
@@ -1965,19 +1956,19 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K27">
         <v>1</v>
       </c>
       <c r="L27" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M27" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N27" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O27">
         <v>18.27</v>
@@ -2003,10 +1994,10 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G28" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H28">
         <v>211.75</v>
@@ -2015,19 +2006,19 @@
         <v>2.5</v>
       </c>
       <c r="J28" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K28">
         <v>1</v>
       </c>
       <c r="L28" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M28" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N28" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O28">
         <v>18.27</v>
@@ -2053,10 +2044,10 @@
         <v>-0.5</v>
       </c>
       <c r="F29" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G29" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H29">
         <v>1381.5</v>
@@ -2065,19 +2056,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J29" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K29">
         <v>7</v>
       </c>
       <c r="L29" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M29" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N29" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O29">
         <v>18.27</v>
@@ -2103,10 +2094,10 @@
         <v>-0.5</v>
       </c>
       <c r="F30" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G30" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H30">
         <v>4483</v>
@@ -2115,19 +2106,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J30" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K30">
         <v>7</v>
       </c>
       <c r="L30" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M30" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N30" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O30">
         <v>18.27</v>
@@ -2153,10 +2144,10 @@
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G31" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H31">
         <v>89.05</v>
@@ -2165,19 +2156,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J31" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K31">
         <v>1</v>
       </c>
       <c r="L31" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M31" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N31" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O31">
         <v>18.27</v>
@@ -2203,10 +2194,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G32" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H32">
         <v>1291.1</v>
@@ -2215,19 +2206,19 @@
         <v>3.400000000000006</v>
       </c>
       <c r="J32" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K32">
         <v>1</v>
       </c>
       <c r="L32" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M32" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N32" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O32">
         <v>18.27</v>
@@ -2253,10 +2244,10 @@
         <v>-0.5</v>
       </c>
       <c r="F33" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G33" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H33">
         <v>1414.6</v>
@@ -2265,19 +2256,19 @@
         <v>5.900000000000006</v>
       </c>
       <c r="J33" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K33">
         <v>2</v>
       </c>
       <c r="L33" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M33" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N33" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O33">
         <v>18.27</v>
@@ -2303,10 +2294,10 @@
         <v>-0.5</v>
       </c>
       <c r="F34" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G34" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H34">
         <v>9760</v>
@@ -2315,19 +2306,19 @@
         <v>6.299999999999997</v>
       </c>
       <c r="J34" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K34">
         <v>7</v>
       </c>
       <c r="L34" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M34" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N34" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O34">
         <v>18.27</v>
@@ -2353,10 +2344,10 @@
         <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G35" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H35">
         <v>125.85</v>
@@ -2365,19 +2356,19 @@
         <v>7.299999999999997</v>
       </c>
       <c r="J35" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K35">
         <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M35" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N35" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O35">
         <v>18.27</v>
@@ -2403,10 +2394,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G36" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H36">
         <v>1171.95</v>
@@ -2415,19 +2406,19 @@
         <v>7.899999999999999</v>
       </c>
       <c r="J36" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K36">
         <v>1</v>
       </c>
       <c r="L36" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M36" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N36" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O36">
         <v>18.27</v>
@@ -2453,10 +2444,10 @@
         <v>-6.5</v>
       </c>
       <c r="F37" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G37" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H37">
         <v>1038.1</v>
@@ -2465,19 +2456,19 @@
         <v>9.299999999999997</v>
       </c>
       <c r="J37" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K37">
         <v>7</v>
       </c>
       <c r="L37" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M37" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N37" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O37">
         <v>18.27</v>
@@ -2503,10 +2494,10 @@
         <v>-2.9</v>
       </c>
       <c r="F38" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G38" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H38">
         <v>319.6</v>
@@ -2515,19 +2506,19 @@
         <v>11.4</v>
       </c>
       <c r="J38" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K38">
         <v>7</v>
       </c>
       <c r="L38" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M38" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N38" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O38">
         <v>18.27</v>
@@ -2553,10 +2544,10 @@
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G39" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H39">
         <v>2314.1</v>
@@ -2565,19 +2556,19 @@
         <v>11.7</v>
       </c>
       <c r="J39" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K39">
         <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M39" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N39" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O39">
         <v>18.27</v>
@@ -2603,10 +2594,10 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G40" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H40">
         <v>3723.6</v>
@@ -2615,19 +2606,19 @@
         <v>11.7</v>
       </c>
       <c r="J40" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K40">
         <v>1</v>
       </c>
       <c r="L40" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M40" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N40" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O40">
         <v>18.27</v>
@@ -2653,10 +2644,10 @@
         <v>-0.5</v>
       </c>
       <c r="F41" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G41" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H41">
         <v>4049.2</v>
@@ -2665,19 +2656,19 @@
         <v>13.3</v>
       </c>
       <c r="J41" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K41">
         <v>3</v>
       </c>
       <c r="L41" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M41" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N41" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O41">
         <v>18.27</v>
@@ -2703,10 +2694,10 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G42" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H42">
         <v>124.98</v>
@@ -2715,19 +2706,19 @@
         <v>14.6</v>
       </c>
       <c r="J42" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K42">
         <v>1</v>
       </c>
       <c r="L42" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M42" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N42" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O42">
         <v>18.27</v>
@@ -2753,10 +2744,10 @@
         <v>2.4</v>
       </c>
       <c r="F43" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G43" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H43">
         <v>1388.7</v>
@@ -2765,19 +2756,19 @@
         <v>0.9000000000000057</v>
       </c>
       <c r="J43" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K43">
         <v>8</v>
       </c>
       <c r="L43" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M43" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N43" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O43">
         <v>18.23</v>
@@ -2803,10 +2794,10 @@
         <v>0</v>
       </c>
       <c r="F44" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G44" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H44">
         <v>404.8</v>
@@ -2815,19 +2806,19 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K44">
         <v>8</v>
       </c>
       <c r="L44" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M44" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N44" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O44">
         <v>18.23</v>
@@ -2853,10 +2844,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G45" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H45">
         <v>3845.7</v>
@@ -2865,19 +2856,19 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K45">
         <v>2</v>
       </c>
       <c r="L45" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M45" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N45" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O45">
         <v>18.23</v>
@@ -2903,10 +2894,10 @@
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G46" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H46">
         <v>213.03</v>
@@ -2915,19 +2906,19 @@
         <v>1.5</v>
       </c>
       <c r="J46" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K46">
         <v>2</v>
       </c>
       <c r="L46" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M46" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N46" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O46">
         <v>18.23</v>
@@ -2953,10 +2944,10 @@
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G47" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H47">
         <v>4477</v>
@@ -2965,19 +2956,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J47" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K47">
         <v>8</v>
       </c>
       <c r="L47" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M47" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N47" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O47">
         <v>18.23</v>
@@ -3003,10 +2994,10 @@
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G48" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H48">
         <v>88.98999999999999</v>
@@ -3015,19 +3006,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J48" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K48">
         <v>2</v>
       </c>
       <c r="L48" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M48" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N48" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O48">
         <v>18.23</v>
@@ -3053,10 +3044,10 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G49" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H49">
         <v>1288.9</v>
@@ -3065,19 +3056,19 @@
         <v>3.400000000000006</v>
       </c>
       <c r="J49" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K49">
         <v>2</v>
       </c>
       <c r="L49" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M49" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N49" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O49">
         <v>18.23</v>
@@ -3103,10 +3094,10 @@
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G50" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H50">
         <v>1419</v>
@@ -3115,19 +3106,19 @@
         <v>5.900000000000006</v>
       </c>
       <c r="J50" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K50">
         <v>3</v>
       </c>
       <c r="L50" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M50" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N50" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O50">
         <v>18.23</v>
@@ -3153,10 +3144,10 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G51" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H51">
         <v>9758</v>
@@ -3165,19 +3156,19 @@
         <v>6.299999999999997</v>
       </c>
       <c r="J51" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K51">
         <v>8</v>
       </c>
       <c r="L51" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M51" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N51" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O51">
         <v>18.23</v>
@@ -3203,10 +3194,10 @@
         <v>0</v>
       </c>
       <c r="F52" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G52" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H52">
         <v>125.98</v>
@@ -3215,19 +3206,19 @@
         <v>7.299999999999997</v>
       </c>
       <c r="J52" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K52">
         <v>2</v>
       </c>
       <c r="L52" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M52" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N52" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O52">
         <v>18.23</v>
@@ -3253,10 +3244,10 @@
         <v>0</v>
       </c>
       <c r="F53" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G53" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H53">
         <v>1182</v>
@@ -3265,19 +3256,19 @@
         <v>7.899999999999999</v>
       </c>
       <c r="J53" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K53">
         <v>2</v>
       </c>
       <c r="L53" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M53" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N53" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O53">
         <v>18.23</v>
@@ -3303,10 +3294,10 @@
         <v>0</v>
       </c>
       <c r="F54" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G54" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H54">
         <v>1040</v>
@@ -3315,19 +3306,19 @@
         <v>9.299999999999997</v>
       </c>
       <c r="J54" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K54">
         <v>8</v>
       </c>
       <c r="L54" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M54" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N54" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O54">
         <v>18.23</v>
@@ -3353,10 +3344,10 @@
         <v>0</v>
       </c>
       <c r="F55" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G55" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H55">
         <v>320.2</v>
@@ -3365,19 +3356,19 @@
         <v>11.4</v>
       </c>
       <c r="J55" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K55">
         <v>8</v>
       </c>
       <c r="L55" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M55" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N55" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O55">
         <v>18.23</v>
@@ -3403,10 +3394,10 @@
         <v>0</v>
       </c>
       <c r="F56" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G56" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H56">
         <v>2314.8</v>
@@ -3415,19 +3406,19 @@
         <v>11.7</v>
       </c>
       <c r="J56" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K56">
         <v>2</v>
       </c>
       <c r="L56" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M56" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N56" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O56">
         <v>18.23</v>
@@ -3453,10 +3444,10 @@
         <v>0</v>
       </c>
       <c r="F57" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G57" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H57">
         <v>3716.5</v>
@@ -3465,19 +3456,19 @@
         <v>11.7</v>
       </c>
       <c r="J57" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K57">
         <v>2</v>
       </c>
       <c r="L57" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M57" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N57" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O57">
         <v>18.23</v>
@@ -3503,10 +3494,10 @@
         <v>0</v>
       </c>
       <c r="F58" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G58" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H58">
         <v>4043</v>
@@ -3515,19 +3506,19 @@
         <v>13.3</v>
       </c>
       <c r="J58" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K58">
         <v>4</v>
       </c>
       <c r="L58" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M58" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N58" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O58">
         <v>18.23</v>
@@ -3553,10 +3544,10 @@
         <v>0</v>
       </c>
       <c r="F59" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G59" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H59">
         <v>125.04</v>
@@ -3565,19 +3556,19 @@
         <v>14.6</v>
       </c>
       <c r="J59" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K59">
         <v>2</v>
       </c>
       <c r="L59" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M59" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N59" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="O59">
         <v>18.23</v>
@@ -3603,10 +3594,10 @@
         <v>0</v>
       </c>
       <c r="F60" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G60" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H60">
         <v>3852.5</v>
@@ -3618,13 +3609,13 @@
         <v>1</v>
       </c>
       <c r="L60" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="M60" t="s">
+        <v>90</v>
+      </c>
+      <c r="N60" t="s">
         <v>93</v>
-      </c>
-      <c r="N60" t="s">
-        <v>96</v>
       </c>
       <c r="O60">
         <v>18.08</v>
@@ -3650,10 +3641,10 @@
         <v>0.5</v>
       </c>
       <c r="F61" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G61" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H61">
         <v>1388.5</v>
@@ -3662,19 +3653,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J61" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K61">
         <v>9</v>
       </c>
       <c r="L61" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M61" t="s">
+        <v>90</v>
+      </c>
+      <c r="N61" t="s">
         <v>93</v>
-      </c>
-      <c r="N61" t="s">
-        <v>96</v>
       </c>
       <c r="O61">
         <v>18.08</v>
@@ -3700,10 +3691,10 @@
         <v>0.5</v>
       </c>
       <c r="F62" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G62" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H62">
         <v>406.1</v>
@@ -3712,19 +3703,19 @@
         <v>0.5</v>
       </c>
       <c r="J62" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K62">
         <v>9</v>
       </c>
       <c r="L62" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M62" t="s">
+        <v>90</v>
+      </c>
+      <c r="N62" t="s">
         <v>93</v>
-      </c>
-      <c r="N62" t="s">
-        <v>96</v>
       </c>
       <c r="O62">
         <v>18.08</v>
@@ -3750,10 +3741,10 @@
         <v>0.5</v>
       </c>
       <c r="F63" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G63" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H63">
         <v>213.6</v>
@@ -3762,19 +3753,19 @@
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K63">
         <v>3</v>
       </c>
       <c r="L63" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M63" t="s">
+        <v>90</v>
+      </c>
+      <c r="N63" t="s">
         <v>93</v>
-      </c>
-      <c r="N63" t="s">
-        <v>96</v>
       </c>
       <c r="O63">
         <v>18.08</v>
@@ -3800,10 +3791,10 @@
         <v>0.5</v>
       </c>
       <c r="F64" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G64" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H64">
         <v>4478</v>
@@ -3812,19 +3803,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J64" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K64">
         <v>9</v>
       </c>
       <c r="L64" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M64" t="s">
+        <v>90</v>
+      </c>
+      <c r="N64" t="s">
         <v>93</v>
-      </c>
-      <c r="N64" t="s">
-        <v>96</v>
       </c>
       <c r="O64">
         <v>18.08</v>
@@ -3850,10 +3841,10 @@
         <v>6.5</v>
       </c>
       <c r="F65" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G65" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H65">
         <v>1050.05</v>
@@ -3862,19 +3853,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J65" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K65">
         <v>9</v>
       </c>
       <c r="L65" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M65" t="s">
+        <v>90</v>
+      </c>
+      <c r="N65" t="s">
         <v>93</v>
-      </c>
-      <c r="N65" t="s">
-        <v>96</v>
       </c>
       <c r="O65">
         <v>18.08</v>
@@ -3900,10 +3891,10 @@
         <v>0.5</v>
       </c>
       <c r="F66" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G66" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H66">
         <v>88.59</v>
@@ -3912,19 +3903,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J66" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K66">
         <v>3</v>
       </c>
       <c r="L66" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M66" t="s">
+        <v>90</v>
+      </c>
+      <c r="N66" t="s">
         <v>93</v>
-      </c>
-      <c r="N66" t="s">
-        <v>96</v>
       </c>
       <c r="O66">
         <v>18.08</v>
@@ -3950,10 +3941,10 @@
         <v>0.5</v>
       </c>
       <c r="F67" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G67" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H67">
         <v>1291.7</v>
@@ -3962,19 +3953,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J67" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K67">
         <v>3</v>
       </c>
       <c r="L67" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M67" t="s">
+        <v>90</v>
+      </c>
+      <c r="N67" t="s">
         <v>93</v>
-      </c>
-      <c r="N67" t="s">
-        <v>96</v>
       </c>
       <c r="O67">
         <v>18.08</v>
@@ -4000,10 +3991,10 @@
         <v>0.5</v>
       </c>
       <c r="F68" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G68" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H68">
         <v>1405.3</v>
@@ -4012,19 +4003,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J68" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K68">
         <v>4</v>
       </c>
       <c r="L68" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M68" t="s">
+        <v>90</v>
+      </c>
+      <c r="N68" t="s">
         <v>93</v>
-      </c>
-      <c r="N68" t="s">
-        <v>96</v>
       </c>
       <c r="O68">
         <v>18.08</v>
@@ -4050,10 +4041,10 @@
         <v>0.5</v>
       </c>
       <c r="F69" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G69" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H69">
         <v>125.89</v>
@@ -4062,19 +4053,19 @@
         <v>6.799999999999997</v>
       </c>
       <c r="J69" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K69">
         <v>3</v>
       </c>
       <c r="L69" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M69" t="s">
+        <v>90</v>
+      </c>
+      <c r="N69" t="s">
         <v>93</v>
-      </c>
-      <c r="N69" t="s">
-        <v>96</v>
       </c>
       <c r="O69">
         <v>18.08</v>
@@ -4100,10 +4091,10 @@
         <v>0.5</v>
       </c>
       <c r="F70" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G70" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H70">
         <v>1190.45</v>
@@ -4112,19 +4103,19 @@
         <v>7.399999999999999</v>
       </c>
       <c r="J70" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K70">
         <v>3</v>
       </c>
       <c r="L70" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M70" t="s">
+        <v>90</v>
+      </c>
+      <c r="N70" t="s">
         <v>93</v>
-      </c>
-      <c r="N70" t="s">
-        <v>96</v>
       </c>
       <c r="O70">
         <v>18.08</v>
@@ -4150,10 +4141,10 @@
         <v>-3.1</v>
       </c>
       <c r="F71" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G71" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H71">
         <v>9700</v>
@@ -4162,19 +4153,19 @@
         <v>9.399999999999999</v>
       </c>
       <c r="J71" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K71">
         <v>9</v>
       </c>
       <c r="L71" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M71" t="s">
+        <v>90</v>
+      </c>
+      <c r="N71" t="s">
         <v>93</v>
-      </c>
-      <c r="N71" t="s">
-        <v>96</v>
       </c>
       <c r="O71">
         <v>18.08</v>
@@ -4200,10 +4191,10 @@
         <v>0.5</v>
       </c>
       <c r="F72" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G72" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H72">
         <v>319.85</v>
@@ -4212,19 +4203,19 @@
         <v>10.9</v>
       </c>
       <c r="J72" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K72">
         <v>9</v>
       </c>
       <c r="L72" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M72" t="s">
+        <v>90</v>
+      </c>
+      <c r="N72" t="s">
         <v>93</v>
-      </c>
-      <c r="N72" t="s">
-        <v>96</v>
       </c>
       <c r="O72">
         <v>18.08</v>
@@ -4250,10 +4241,10 @@
         <v>0.5</v>
       </c>
       <c r="F73" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G73" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H73">
         <v>2305.6</v>
@@ -4262,19 +4253,19 @@
         <v>11.2</v>
       </c>
       <c r="J73" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K73">
         <v>3</v>
       </c>
       <c r="L73" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M73" t="s">
+        <v>90</v>
+      </c>
+      <c r="N73" t="s">
         <v>93</v>
-      </c>
-      <c r="N73" t="s">
-        <v>96</v>
       </c>
       <c r="O73">
         <v>18.08</v>
@@ -4300,10 +4291,10 @@
         <v>0.5</v>
       </c>
       <c r="F74" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G74" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H74">
         <v>3703.3</v>
@@ -4312,19 +4303,19 @@
         <v>11.2</v>
       </c>
       <c r="J74" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K74">
         <v>3</v>
       </c>
       <c r="L74" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M74" t="s">
+        <v>90</v>
+      </c>
+      <c r="N74" t="s">
         <v>93</v>
-      </c>
-      <c r="N74" t="s">
-        <v>96</v>
       </c>
       <c r="O74">
         <v>18.08</v>
@@ -4350,10 +4341,10 @@
         <v>0.5</v>
       </c>
       <c r="F75" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G75" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H75">
         <v>4023.5</v>
@@ -4362,19 +4353,19 @@
         <v>12.8</v>
       </c>
       <c r="J75" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K75">
         <v>5</v>
       </c>
       <c r="L75" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M75" t="s">
+        <v>90</v>
+      </c>
+      <c r="N75" t="s">
         <v>93</v>
-      </c>
-      <c r="N75" t="s">
-        <v>96</v>
       </c>
       <c r="O75">
         <v>18.08</v>
@@ -4400,10 +4391,10 @@
         <v>0</v>
       </c>
       <c r="F76" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G76" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H76">
         <v>7196</v>
@@ -4412,19 +4403,19 @@
         <v>13.2</v>
       </c>
       <c r="J76" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K76">
         <v>1</v>
       </c>
       <c r="L76" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M76" t="s">
+        <v>90</v>
+      </c>
+      <c r="N76" t="s">
         <v>93</v>
-      </c>
-      <c r="N76" t="s">
-        <v>96</v>
       </c>
       <c r="O76">
         <v>18.08</v>
@@ -4450,10 +4441,10 @@
         <v>0.5</v>
       </c>
       <c r="F77" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G77" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H77">
         <v>125</v>
@@ -4462,19 +4453,19 @@
         <v>14.1</v>
       </c>
       <c r="J77" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K77">
         <v>3</v>
       </c>
       <c r="L77" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M77" t="s">
+        <v>90</v>
+      </c>
+      <c r="N77" t="s">
         <v>93</v>
-      </c>
-      <c r="N77" t="s">
-        <v>96</v>
       </c>
       <c r="O77">
         <v>18.08</v>
@@ -4500,10 +4491,10 @@
         <v>0</v>
       </c>
       <c r="F78" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G78" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H78">
         <v>1449.1</v>
@@ -4515,13 +4506,13 @@
         <v>1</v>
       </c>
       <c r="L78" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="M78" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N78" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O78">
         <v>18.3</v>
@@ -4547,10 +4538,10 @@
         <v>0</v>
       </c>
       <c r="F79" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G79" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H79">
         <v>3844.3</v>
@@ -4562,13 +4553,13 @@
         <v>1</v>
       </c>
       <c r="L79" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="M79" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N79" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O79">
         <v>18.3</v>
@@ -4594,10 +4585,10 @@
         <v>0</v>
       </c>
       <c r="F80" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G80" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H80">
         <v>1330.5</v>
@@ -4609,13 +4600,13 @@
         <v>1</v>
       </c>
       <c r="L80" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="M80" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N80" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O80">
         <v>18.3</v>
@@ -4641,10 +4632,10 @@
         <v>0</v>
       </c>
       <c r="F81" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G81" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H81">
         <v>405.4</v>
@@ -4656,13 +4647,13 @@
         <v>1</v>
       </c>
       <c r="L81" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="M81" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N81" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O81">
         <v>18.3</v>
@@ -4688,10 +4679,10 @@
         <v>0</v>
       </c>
       <c r="F82" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G82" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H82">
         <v>554.7</v>
@@ -4700,19 +4691,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J82" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K82">
         <v>1</v>
       </c>
       <c r="L82" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M82" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N82" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O82">
         <v>18.3</v>
@@ -4738,10 +4729,10 @@
         <v>0</v>
       </c>
       <c r="F83" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G83" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H83">
         <v>215.65</v>
@@ -4750,19 +4741,19 @@
         <v>1</v>
       </c>
       <c r="J83" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K83">
         <v>4</v>
       </c>
       <c r="L83" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M83" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N83" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O83">
         <v>18.3</v>
@@ -4788,10 +4779,10 @@
         <v>-2.4</v>
       </c>
       <c r="F84" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G84" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H84">
         <v>1379.6</v>
@@ -4800,19 +4791,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J84" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K84">
         <v>10</v>
       </c>
       <c r="L84" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M84" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N84" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O84">
         <v>18.3</v>
@@ -4838,10 +4829,10 @@
         <v>0</v>
       </c>
       <c r="F85" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G85" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H85">
         <v>4454.6</v>
@@ -4850,19 +4841,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J85" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K85">
         <v>10</v>
       </c>
       <c r="L85" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M85" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N85" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O85">
         <v>18.3</v>
@@ -4888,10 +4879,10 @@
         <v>0</v>
       </c>
       <c r="F86" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G86" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H86">
         <v>1044.55</v>
@@ -4900,19 +4891,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J86" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K86">
         <v>10</v>
       </c>
       <c r="L86" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M86" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N86" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O86">
         <v>18.3</v>
@@ -4938,10 +4929,10 @@
         <v>0</v>
       </c>
       <c r="F87" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G87" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H87">
         <v>88.59</v>
@@ -4950,19 +4941,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J87" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K87">
         <v>4</v>
       </c>
       <c r="L87" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M87" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N87" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O87">
         <v>18.3</v>
@@ -4988,10 +4979,10 @@
         <v>0</v>
       </c>
       <c r="F88" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G88" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H88">
         <v>556.95</v>
@@ -5000,19 +4991,19 @@
         <v>4.799999999999997</v>
       </c>
       <c r="J88" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K88">
         <v>1</v>
       </c>
       <c r="L88" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M88" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N88" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O88">
         <v>18.3</v>
@@ -5038,10 +5029,10 @@
         <v>0</v>
       </c>
       <c r="F89" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G89" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H89">
         <v>1395.8</v>
@@ -5050,19 +5041,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J89" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K89">
         <v>5</v>
       </c>
       <c r="L89" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M89" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N89" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O89">
         <v>18.3</v>
@@ -5088,10 +5079,10 @@
         <v>0</v>
       </c>
       <c r="F90" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G90" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H90">
         <v>5977</v>
@@ -5100,19 +5091,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J90" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K90">
         <v>1</v>
       </c>
       <c r="L90" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M90" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N90" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O90">
         <v>18.3</v>
@@ -5138,10 +5129,10 @@
         <v>1</v>
       </c>
       <c r="F91" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G91" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H91">
         <v>1198.95</v>
@@ -5150,19 +5141,19 @@
         <v>6.399999999999999</v>
       </c>
       <c r="J91" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K91">
         <v>4</v>
       </c>
       <c r="L91" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M91" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N91" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O91">
         <v>18.3</v>
@@ -5188,10 +5179,10 @@
         <v>-6</v>
       </c>
       <c r="F92" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G92" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H92">
         <v>1278.6</v>
@@ -5200,19 +5191,19 @@
         <v>8.899999999999999</v>
       </c>
       <c r="J92" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K92">
         <v>4</v>
       </c>
       <c r="L92" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M92" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N92" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O92">
         <v>18.3</v>
@@ -5238,10 +5229,10 @@
         <v>0</v>
       </c>
       <c r="F93" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G93" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H93">
         <v>9602</v>
@@ -5250,19 +5241,19 @@
         <v>9.399999999999999</v>
       </c>
       <c r="J93" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K93">
         <v>10</v>
       </c>
       <c r="L93" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M93" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N93" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O93">
         <v>18.3</v>
@@ -5288,10 +5279,10 @@
         <v>0</v>
       </c>
       <c r="F94" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G94" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H94">
         <v>319.75</v>
@@ -5300,19 +5291,19 @@
         <v>10.9</v>
       </c>
       <c r="J94" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K94">
         <v>10</v>
       </c>
       <c r="L94" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M94" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N94" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O94">
         <v>18.3</v>
@@ -5338,10 +5329,10 @@
         <v>0</v>
       </c>
       <c r="F95" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G95" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H95">
         <v>2307.9</v>
@@ -5350,19 +5341,19 @@
         <v>11.2</v>
       </c>
       <c r="J95" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K95">
         <v>4</v>
       </c>
       <c r="L95" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M95" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N95" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O95">
         <v>18.3</v>
@@ -5388,10 +5379,10 @@
         <v>0</v>
       </c>
       <c r="F96" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G96" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H96">
         <v>4021.1</v>
@@ -5400,19 +5391,19 @@
         <v>12.8</v>
       </c>
       <c r="J96" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K96">
         <v>6</v>
       </c>
       <c r="L96" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M96" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N96" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O96">
         <v>18.3</v>
@@ -5438,10 +5429,10 @@
         <v>0</v>
       </c>
       <c r="F97" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G97" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H97">
         <v>7230</v>
@@ -5450,19 +5441,19 @@
         <v>13.2</v>
       </c>
       <c r="J97" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K97">
         <v>2</v>
       </c>
       <c r="L97" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M97" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N97" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O97">
         <v>18.3</v>
@@ -5488,10 +5479,10 @@
         <v>0</v>
       </c>
       <c r="F98" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G98" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H98">
         <v>3844.3</v>
@@ -5503,13 +5494,13 @@
         <v>1</v>
       </c>
       <c r="L98" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="M98" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N98" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O98">
         <v>18.3</v>
@@ -5535,10 +5526,10 @@
         <v>0</v>
       </c>
       <c r="F99" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G99" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H99">
         <v>1330.5</v>
@@ -5547,19 +5538,19 @@
         <v>0.09999999999999432</v>
       </c>
       <c r="J99" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="K99">
         <v>1</v>
       </c>
       <c r="L99" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M99" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N99" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O99">
         <v>18.3</v>
@@ -5585,10 +5576,10 @@
         <v>0</v>
       </c>
       <c r="F100" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G100" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H100">
         <v>405.4</v>
@@ -5597,19 +5588,19 @@
         <v>0.7000000000000028</v>
       </c>
       <c r="J100" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K100">
         <v>1</v>
       </c>
       <c r="L100" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M100" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N100" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O100">
         <v>18.3</v>
@@ -5635,10 +5626,10 @@
         <v>-1.2</v>
       </c>
       <c r="F101" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G101" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H101">
         <v>554.7</v>
@@ -5647,19 +5638,19 @@
         <v>1.599999999999994</v>
       </c>
       <c r="J101" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K101">
         <v>2</v>
       </c>
       <c r="L101" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M101" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N101" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O101">
         <v>18.3</v>
@@ -5685,10 +5676,10 @@
         <v>-1.2</v>
       </c>
       <c r="F102" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G102" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H102">
         <v>215.65</v>
@@ -5697,19 +5688,19 @@
         <v>2.200000000000003</v>
       </c>
       <c r="J102" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K102">
         <v>5</v>
       </c>
       <c r="L102" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M102" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N102" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O102">
         <v>18.3</v>
@@ -5735,10 +5726,10 @@
         <v>-1.2</v>
       </c>
       <c r="F103" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G103" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H103">
         <v>1379.6</v>
@@ -5747,19 +5738,19 @@
         <v>4</v>
       </c>
       <c r="J103" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K103">
         <v>11</v>
       </c>
       <c r="L103" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M103" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N103" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O103">
         <v>18.3</v>
@@ -5785,10 +5776,10 @@
         <v>-1.2</v>
       </c>
       <c r="F104" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G104" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H104">
         <v>4454.6</v>
@@ -5797,19 +5788,19 @@
         <v>4</v>
       </c>
       <c r="J104" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K104">
         <v>11</v>
       </c>
       <c r="L104" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M104" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N104" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O104">
         <v>18.3</v>
@@ -5835,10 +5826,10 @@
         <v>-1.2</v>
       </c>
       <c r="F105" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G105" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H105">
         <v>1044.55</v>
@@ -5847,19 +5838,19 @@
         <v>4</v>
       </c>
       <c r="J105" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K105">
         <v>11</v>
       </c>
       <c r="L105" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M105" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N105" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O105">
         <v>18.3</v>
@@ -5885,10 +5876,10 @@
         <v>-1.2</v>
       </c>
       <c r="F106" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G106" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H106">
         <v>88.59</v>
@@ -5897,19 +5888,19 @@
         <v>4</v>
       </c>
       <c r="J106" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K106">
         <v>5</v>
       </c>
       <c r="L106" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M106" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N106" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O106">
         <v>18.3</v>
@@ -5935,10 +5926,10 @@
         <v>-1.2</v>
       </c>
       <c r="F107" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G107" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H107">
         <v>556.95</v>
@@ -5947,19 +5938,19 @@
         <v>6</v>
       </c>
       <c r="J107" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="K107">
         <v>2</v>
       </c>
       <c r="L107" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M107" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N107" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O107">
         <v>18.3</v>
@@ -5985,10 +5976,10 @@
         <v>-1.2</v>
       </c>
       <c r="F108" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G108" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H108">
         <v>1395.8</v>
@@ -5997,19 +5988,19 @@
         <v>6.600000000000001</v>
       </c>
       <c r="J108" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K108">
         <v>6</v>
       </c>
       <c r="L108" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M108" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N108" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O108">
         <v>18.3</v>
@@ -6035,10 +6026,10 @@
         <v>-1.2</v>
       </c>
       <c r="F109" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G109" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H109">
         <v>5977</v>
@@ -6047,19 +6038,19 @@
         <v>6.600000000000001</v>
       </c>
       <c r="J109" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K109">
         <v>2</v>
       </c>
       <c r="L109" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M109" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N109" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O109">
         <v>18.3</v>
@@ -6085,10 +6076,10 @@
         <v>-1.2</v>
       </c>
       <c r="F110" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G110" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H110">
         <v>1198.95</v>
@@ -6097,19 +6088,19 @@
         <v>7.600000000000001</v>
       </c>
       <c r="J110" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K110">
         <v>5</v>
       </c>
       <c r="L110" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M110" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N110" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O110">
         <v>18.3</v>
@@ -6135,10 +6126,10 @@
         <v>-1.2</v>
       </c>
       <c r="F111" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G111" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H111">
         <v>1278.6</v>
@@ -6147,19 +6138,19 @@
         <v>10.1</v>
       </c>
       <c r="J111" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K111">
         <v>5</v>
       </c>
       <c r="L111" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M111" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N111" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O111">
         <v>18.3</v>
@@ -6185,10 +6176,10 @@
         <v>-1.2</v>
       </c>
       <c r="F112" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G112" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H112">
         <v>9602</v>
@@ -6197,19 +6188,19 @@
         <v>10.6</v>
       </c>
       <c r="J112" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K112">
         <v>11</v>
       </c>
       <c r="L112" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M112" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N112" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O112">
         <v>18.3</v>
@@ -6235,10 +6226,10 @@
         <v>-1.2</v>
       </c>
       <c r="F113" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G113" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H113">
         <v>319.75</v>
@@ -6247,19 +6238,19 @@
         <v>12.1</v>
       </c>
       <c r="J113" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K113">
         <v>11</v>
       </c>
       <c r="L113" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M113" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N113" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O113">
         <v>18.3</v>
@@ -6285,10 +6276,10 @@
         <v>-1.2</v>
       </c>
       <c r="F114" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G114" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H114">
         <v>2307.9</v>
@@ -6297,19 +6288,19 @@
         <v>12.4</v>
       </c>
       <c r="J114" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K114">
         <v>5</v>
       </c>
       <c r="L114" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M114" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N114" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O114">
         <v>18.3</v>
@@ -6335,10 +6326,10 @@
         <v>-1.2</v>
       </c>
       <c r="F115" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G115" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H115">
         <v>4021.1</v>
@@ -6347,19 +6338,19 @@
         <v>14</v>
       </c>
       <c r="J115" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K115">
         <v>7</v>
       </c>
       <c r="L115" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M115" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N115" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O115">
         <v>18.3</v>
@@ -6385,10 +6376,10 @@
         <v>-1.2</v>
       </c>
       <c r="F116" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G116" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H116">
         <v>7230</v>
@@ -6397,19 +6388,19 @@
         <v>14.4</v>
       </c>
       <c r="J116" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K116">
         <v>3</v>
       </c>
       <c r="L116" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M116" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N116" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="O116">
         <v>18.3</v>
@@ -6435,10 +6426,10 @@
         <v>6.5</v>
       </c>
       <c r="F117" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G117" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H117">
         <v>1263</v>
@@ -6447,19 +6438,19 @@
         <v>3.599999999999994</v>
       </c>
       <c r="J117" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K117">
         <v>6</v>
       </c>
       <c r="L117" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M117" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N117" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O117">
         <v>18.7</v>
@@ -6485,10 +6476,10 @@
         <v>0</v>
       </c>
       <c r="F118" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G118" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H118">
         <v>123.95</v>
@@ -6497,19 +6488,19 @@
         <v>5.5</v>
       </c>
       <c r="J118" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K118">
         <v>1</v>
       </c>
       <c r="L118" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M118" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N118" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O118">
         <v>18.7</v>
@@ -6535,10 +6526,10 @@
         <v>-2</v>
       </c>
       <c r="F119" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G119" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H119">
         <v>1371.6</v>
@@ -6547,19 +6538,19 @@
         <v>6</v>
       </c>
       <c r="J119" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K119">
         <v>12</v>
       </c>
       <c r="L119" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M119" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N119" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O119">
         <v>18.7</v>
@@ -6585,10 +6576,10 @@
         <v>-2</v>
       </c>
       <c r="F120" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G120" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H120">
         <v>4460</v>
@@ -6597,19 +6588,19 @@
         <v>6</v>
       </c>
       <c r="J120" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K120">
         <v>12</v>
       </c>
       <c r="L120" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M120" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N120" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O120">
         <v>18.7</v>
@@ -6635,10 +6626,10 @@
         <v>6.4</v>
       </c>
       <c r="F121" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G121" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H121">
         <v>2358.2</v>
@@ -6647,19 +6638,19 @@
         <v>6</v>
       </c>
       <c r="J121" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K121">
         <v>6</v>
       </c>
       <c r="L121" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M121" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N121" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O121">
         <v>18.7</v>
@@ -6685,10 +6676,10 @@
         <v>-5.4</v>
       </c>
       <c r="F122" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G122" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H122">
         <v>402.65</v>
@@ -6697,19 +6688,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J122" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K122">
         <v>2</v>
       </c>
       <c r="L122" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M122" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N122" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O122">
         <v>18.7</v>
@@ -6735,10 +6726,10 @@
         <v>0</v>
       </c>
       <c r="F123" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G123" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H123">
         <v>3858.9</v>
@@ -6747,19 +6738,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J123" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K123">
         <v>1</v>
       </c>
       <c r="L123" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M123" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N123" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O123">
         <v>18.7</v>
@@ -6785,10 +6776,10 @@
         <v>4</v>
       </c>
       <c r="F124" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G124" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H124">
         <v>320.55</v>
@@ -6797,19 +6788,19 @@
         <v>8.100000000000001</v>
       </c>
       <c r="J124" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K124">
         <v>12</v>
       </c>
       <c r="L124" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M124" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N124" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O124">
         <v>18.7</v>
@@ -6835,10 +6826,10 @@
         <v>-6.4</v>
       </c>
       <c r="F125" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G125" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H125">
         <v>214.68</v>
@@ -6847,19 +6838,19 @@
         <v>8.600000000000001</v>
       </c>
       <c r="J125" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K125">
         <v>6</v>
       </c>
       <c r="L125" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M125" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N125" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O125">
         <v>18.7</v>
@@ -6885,10 +6876,10 @@
         <v>-5</v>
       </c>
       <c r="F126" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G126" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H126">
         <v>1019.75</v>
@@ -6897,19 +6888,19 @@
         <v>9</v>
       </c>
       <c r="J126" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K126">
         <v>12</v>
       </c>
       <c r="L126" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M126" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N126" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O126">
         <v>18.7</v>
@@ -6935,10 +6926,10 @@
         <v>-5</v>
       </c>
       <c r="F127" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G127" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H127">
         <v>86.98</v>
@@ -6947,19 +6938,19 @@
         <v>9</v>
       </c>
       <c r="J127" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K127">
         <v>6</v>
       </c>
       <c r="L127" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M127" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N127" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O127">
         <v>18.7</v>
@@ -6985,10 +6976,10 @@
         <v>0</v>
       </c>
       <c r="F128" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G128" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H128">
         <v>125.61</v>
@@ -6997,19 +6988,19 @@
         <v>10</v>
       </c>
       <c r="J128" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K128">
         <v>1</v>
       </c>
       <c r="L128" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M128" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N128" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O128">
         <v>18.7</v>
@@ -7035,10 +7026,10 @@
         <v>-4</v>
       </c>
       <c r="F129" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G129" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H129">
         <v>1404.6</v>
@@ -7047,19 +7038,19 @@
         <v>10.6</v>
       </c>
       <c r="J129" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K129">
         <v>7</v>
       </c>
       <c r="L129" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M129" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N129" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O129">
         <v>18.7</v>
@@ -7085,10 +7076,10 @@
         <v>-3</v>
       </c>
       <c r="F130" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G130" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H130">
         <v>1217.2</v>
@@ -7097,19 +7088,19 @@
         <v>10.6</v>
       </c>
       <c r="J130" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K130">
         <v>6</v>
       </c>
       <c r="L130" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M130" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N130" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O130">
         <v>18.7</v>
@@ -7135,10 +7126,10 @@
         <v>0</v>
       </c>
       <c r="F131" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G131" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H131">
         <v>445.5</v>
@@ -7147,19 +7138,19 @@
         <v>12.7</v>
       </c>
       <c r="J131" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="K131">
         <v>1</v>
       </c>
       <c r="L131" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M131" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N131" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O131">
         <v>18.7</v>
@@ -7185,10 +7176,10 @@
         <v>-3.8</v>
       </c>
       <c r="F132" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G132" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H132">
         <v>9519</v>
@@ -7197,19 +7188,19 @@
         <v>14.4</v>
       </c>
       <c r="J132" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K132">
         <v>12</v>
       </c>
       <c r="L132" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M132" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N132" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O132">
         <v>18.7</v>
@@ -7235,10 +7226,10 @@
         <v>0</v>
       </c>
       <c r="F133" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G133" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H133">
         <v>1263.2</v>
@@ -7247,19 +7238,19 @@
         <v>3.599999999999994</v>
       </c>
       <c r="J133" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K133">
         <v>7</v>
       </c>
       <c r="L133" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M133" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N133" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O133">
         <v>18.84</v>
@@ -7285,10 +7276,10 @@
         <v>0</v>
       </c>
       <c r="F134" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G134" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H134">
         <v>124.1</v>
@@ -7297,19 +7288,19 @@
         <v>5.5</v>
       </c>
       <c r="J134" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K134">
         <v>2</v>
       </c>
       <c r="L134" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M134" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N134" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O134">
         <v>18.84</v>
@@ -7335,10 +7326,10 @@
         <v>0</v>
       </c>
       <c r="F135" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G135" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H135">
         <v>1371.2</v>
@@ -7347,19 +7338,19 @@
         <v>6</v>
       </c>
       <c r="J135" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K135">
         <v>13</v>
       </c>
       <c r="L135" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M135" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N135" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O135">
         <v>18.84</v>
@@ -7385,10 +7376,10 @@
         <v>0</v>
       </c>
       <c r="F136" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G136" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H136">
         <v>4440.2</v>
@@ -7397,19 +7388,19 @@
         <v>6</v>
       </c>
       <c r="J136" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K136">
         <v>13</v>
       </c>
       <c r="L136" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M136" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N136" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O136">
         <v>18.84</v>
@@ -7435,10 +7426,10 @@
         <v>0</v>
       </c>
       <c r="F137" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G137" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H137">
         <v>2353.4</v>
@@ -7447,19 +7438,19 @@
         <v>6</v>
       </c>
       <c r="J137" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K137">
         <v>7</v>
       </c>
       <c r="L137" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M137" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N137" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O137">
         <v>18.84</v>
@@ -7485,10 +7476,10 @@
         <v>0</v>
       </c>
       <c r="F138" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G138" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H138">
         <v>400.9</v>
@@ -7497,19 +7488,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J138" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K138">
         <v>3</v>
       </c>
       <c r="L138" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M138" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N138" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O138">
         <v>18.84</v>
@@ -7535,10 +7526,10 @@
         <v>0</v>
       </c>
       <c r="F139" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G139" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H139">
         <v>3856.3</v>
@@ -7547,19 +7538,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J139" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K139">
         <v>2</v>
       </c>
       <c r="L139" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M139" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N139" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O139">
         <v>18.84</v>
@@ -7585,10 +7576,10 @@
         <v>0</v>
       </c>
       <c r="F140" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G140" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H140">
         <v>214.69</v>
@@ -7597,19 +7588,19 @@
         <v>8.600000000000001</v>
       </c>
       <c r="J140" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K140">
         <v>7</v>
       </c>
       <c r="L140" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M140" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N140" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O140">
         <v>18.84</v>
@@ -7635,10 +7626,10 @@
         <v>0</v>
       </c>
       <c r="F141" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G141" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H141">
         <v>1020.55</v>
@@ -7647,19 +7638,19 @@
         <v>9</v>
       </c>
       <c r="J141" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K141">
         <v>13</v>
       </c>
       <c r="L141" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M141" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N141" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O141">
         <v>18.84</v>
@@ -7685,10 +7676,10 @@
         <v>0</v>
       </c>
       <c r="F142" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G142" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H142">
         <v>87.06999999999999</v>
@@ -7697,19 +7688,19 @@
         <v>9</v>
       </c>
       <c r="J142" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K142">
         <v>7</v>
       </c>
       <c r="L142" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M142" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N142" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O142">
         <v>18.84</v>
@@ -7735,10 +7726,10 @@
         <v>0</v>
       </c>
       <c r="F143" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G143" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H143">
         <v>125.46</v>
@@ -7747,19 +7738,19 @@
         <v>10</v>
       </c>
       <c r="J143" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K143">
         <v>2</v>
       </c>
       <c r="L143" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M143" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N143" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O143">
         <v>18.84</v>
@@ -7785,10 +7776,10 @@
         <v>0</v>
       </c>
       <c r="F144" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G144" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H144">
         <v>1401.1</v>
@@ -7797,19 +7788,19 @@
         <v>10.6</v>
       </c>
       <c r="J144" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K144">
         <v>8</v>
       </c>
       <c r="L144" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M144" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N144" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O144">
         <v>18.84</v>
@@ -7835,10 +7826,10 @@
         <v>0</v>
       </c>
       <c r="F145" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G145" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H145">
         <v>1218.2</v>
@@ -7847,19 +7838,19 @@
         <v>10.6</v>
       </c>
       <c r="J145" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K145">
         <v>7</v>
       </c>
       <c r="L145" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M145" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N145" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O145">
         <v>18.84</v>
@@ -7885,10 +7876,10 @@
         <v>0</v>
       </c>
       <c r="F146" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G146" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H146">
         <v>445.65</v>
@@ -7897,19 +7888,19 @@
         <v>12.7</v>
       </c>
       <c r="J146" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="K146">
         <v>2</v>
       </c>
       <c r="L146" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M146" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N146" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O146">
         <v>18.84</v>
@@ -7935,10 +7926,10 @@
         <v>-6</v>
       </c>
       <c r="F147" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G147" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H147">
         <v>319.85</v>
@@ -7947,19 +7938,19 @@
         <v>14.1</v>
       </c>
       <c r="J147" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K147">
         <v>13</v>
       </c>
       <c r="L147" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M147" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N147" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O147">
         <v>18.84</v>
@@ -7985,10 +7976,10 @@
         <v>0</v>
       </c>
       <c r="F148" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G148" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H148">
         <v>9545.5</v>
@@ -7997,19 +7988,19 @@
         <v>14.4</v>
       </c>
       <c r="J148" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K148">
         <v>13</v>
       </c>
       <c r="L148" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M148" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N148" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O148">
         <v>18.84</v>
@@ -8035,10 +8026,10 @@
         <v>0.5</v>
       </c>
       <c r="F149" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G149" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H149">
         <v>1262.7</v>
@@ -8047,19 +8038,19 @@
         <v>3.099999999999994</v>
       </c>
       <c r="J149" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K149">
         <v>8</v>
       </c>
       <c r="L149" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M149" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N149" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O149">
         <v>18.44</v>
@@ -8085,10 +8076,10 @@
         <v>2.9</v>
       </c>
       <c r="F150" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G150" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H150">
         <v>404.6</v>
@@ -8097,19 +8088,19 @@
         <v>3.200000000000003</v>
       </c>
       <c r="J150" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K150">
         <v>4</v>
       </c>
       <c r="L150" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M150" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N150" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O150">
         <v>18.44</v>
@@ -8135,10 +8126,10 @@
         <v>0.5</v>
       </c>
       <c r="F151" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G151" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H151">
         <v>124.38</v>
@@ -8147,19 +8138,19 @@
         <v>5</v>
       </c>
       <c r="J151" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K151">
         <v>3</v>
       </c>
       <c r="L151" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M151" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N151" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O151">
         <v>18.44</v>
@@ -8185,10 +8176,10 @@
         <v>0.5</v>
       </c>
       <c r="F152" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G152" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H152">
         <v>1376.9</v>
@@ -8197,19 +8188,19 @@
         <v>5.5</v>
       </c>
       <c r="J152" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K152">
         <v>14</v>
       </c>
       <c r="L152" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M152" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N152" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O152">
         <v>18.44</v>
@@ -8235,10 +8226,10 @@
         <v>0.5</v>
       </c>
       <c r="F153" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G153" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H153">
         <v>4456.2</v>
@@ -8247,19 +8238,19 @@
         <v>5.5</v>
       </c>
       <c r="J153" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K153">
         <v>14</v>
       </c>
       <c r="L153" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M153" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N153" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O153">
         <v>18.44</v>
@@ -8285,10 +8276,10 @@
         <v>0.5</v>
       </c>
       <c r="F154" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G154" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H154">
         <v>2358.9</v>
@@ -8297,19 +8288,19 @@
         <v>5.5</v>
       </c>
       <c r="J154" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K154">
         <v>8</v>
       </c>
       <c r="L154" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M154" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N154" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O154">
         <v>18.44</v>
@@ -8335,10 +8326,10 @@
         <v>0.5</v>
       </c>
       <c r="F155" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G155" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H155">
         <v>3875.6</v>
@@ -8347,19 +8338,19 @@
         <v>5.599999999999994</v>
       </c>
       <c r="J155" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K155">
         <v>3</v>
       </c>
       <c r="L155" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M155" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N155" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O155">
         <v>18.44</v>
@@ -8385,10 +8376,10 @@
         <v>3.9</v>
       </c>
       <c r="F156" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G156" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H156">
         <v>1231.65</v>
@@ -8397,19 +8388,19 @@
         <v>6.700000000000003</v>
       </c>
       <c r="J156" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K156">
         <v>8</v>
       </c>
       <c r="L156" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M156" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N156" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O156">
         <v>18.44</v>
@@ -8435,10 +8426,10 @@
         <v>1.5</v>
       </c>
       <c r="F157" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G157" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H157">
         <v>215.19</v>
@@ -8447,19 +8438,19 @@
         <v>7.100000000000001</v>
       </c>
       <c r="J157" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K157">
         <v>8</v>
       </c>
       <c r="L157" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M157" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N157" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O157">
         <v>18.44</v>
@@ -8485,10 +8476,10 @@
         <v>0.5</v>
       </c>
       <c r="F158" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G158" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H158">
         <v>1016.45</v>
@@ -8497,19 +8488,19 @@
         <v>8.5</v>
       </c>
       <c r="J158" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K158">
         <v>14</v>
       </c>
       <c r="L158" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M158" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N158" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O158">
         <v>18.44</v>
@@ -8535,10 +8526,10 @@
         <v>0.5</v>
       </c>
       <c r="F159" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G159" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H159">
         <v>87.40000000000001</v>
@@ -8547,19 +8538,19 @@
         <v>8.5</v>
       </c>
       <c r="J159" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K159">
         <v>8</v>
       </c>
       <c r="L159" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M159" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N159" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O159">
         <v>18.44</v>
@@ -8585,10 +8576,10 @@
         <v>1.5</v>
       </c>
       <c r="F160" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G160" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H160">
         <v>1408.8</v>
@@ -8597,19 +8588,19 @@
         <v>9.100000000000001</v>
       </c>
       <c r="J160" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K160">
         <v>9</v>
       </c>
       <c r="L160" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M160" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N160" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O160">
         <v>18.44</v>
@@ -8635,10 +8626,10 @@
         <v>0.5</v>
       </c>
       <c r="F161" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G161" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H161">
         <v>125.82</v>
@@ -8647,19 +8638,19 @@
         <v>9.5</v>
       </c>
       <c r="J161" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K161">
         <v>3</v>
       </c>
       <c r="L161" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M161" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N161" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O161">
         <v>18.44</v>
@@ -8685,10 +8676,10 @@
         <v>0.5</v>
       </c>
       <c r="F162" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G162" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H162">
         <v>451.3</v>
@@ -8697,19 +8688,19 @@
         <v>12.2</v>
       </c>
       <c r="J162" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="K162">
         <v>3</v>
       </c>
       <c r="L162" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M162" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N162" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O162">
         <v>18.44</v>
@@ -8735,10 +8726,10 @@
         <v>0.5</v>
       </c>
       <c r="F163" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G163" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H163">
         <v>320.1</v>
@@ -8747,19 +8738,19 @@
         <v>13.6</v>
       </c>
       <c r="J163" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K163">
         <v>14</v>
       </c>
       <c r="L163" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M163" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N163" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O163">
         <v>18.44</v>
@@ -8785,10 +8776,10 @@
         <v>0.5</v>
       </c>
       <c r="F164" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G164" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H164">
         <v>9549.5</v>
@@ -8797,19 +8788,19 @@
         <v>13.9</v>
       </c>
       <c r="J164" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K164">
         <v>14</v>
       </c>
       <c r="L164" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M164" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N164" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O164">
         <v>18.44</v>
@@ -8819,8 +8810,8 @@
       </c>
     </row>
     <row r="165" spans="1:16">
-      <c r="A165" t="s">
-        <v>16</v>
+      <c r="A165">
+        <v>20260423</v>
       </c>
       <c r="B165" t="s">
         <v>57</v>
@@ -8831,14 +8822,14 @@
       <c r="D165">
         <v>78.8</v>
       </c>
-      <c r="E165" t="s">
-        <v>72</v>
+      <c r="E165">
+        <v>0</v>
       </c>
       <c r="F165" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G165" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="H165">
         <v>6727</v>
@@ -8853,10 +8844,10 @@
         <v>16</v>
       </c>
       <c r="M165" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N165" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O165">
         <v>18.59</v>
@@ -8866,8 +8857,8 @@
       </c>
     </row>
     <row r="166" spans="1:16">
-      <c r="A166" t="s">
-        <v>16</v>
+      <c r="A166">
+        <v>20260423</v>
       </c>
       <c r="B166" t="s">
         <v>58</v>
@@ -8878,14 +8869,14 @@
       <c r="D166">
         <v>75.8</v>
       </c>
-      <c r="E166" t="s">
-        <v>72</v>
+      <c r="E166">
+        <v>0</v>
       </c>
       <c r="F166" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G166" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H166">
         <v>4135.1</v>
@@ -8900,10 +8891,10 @@
         <v>16</v>
       </c>
       <c r="M166" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N166" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O166">
         <v>18.59</v>
@@ -8913,8 +8904,8 @@
       </c>
     </row>
     <row r="167" spans="1:16">
-      <c r="A167" t="s">
-        <v>16</v>
+      <c r="A167">
+        <v>20260423</v>
       </c>
       <c r="B167" t="s">
         <v>59</v>
@@ -8925,14 +8916,14 @@
       <c r="D167">
         <v>69.3</v>
       </c>
-      <c r="E167" t="s">
-        <v>72</v>
+      <c r="E167">
+        <v>0</v>
       </c>
       <c r="F167" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G167" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H167">
         <v>297</v>
@@ -8941,19 +8932,19 @@
         <v>0.7000000000000028</v>
       </c>
       <c r="J167" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K167">
         <v>1</v>
       </c>
       <c r="L167" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M167" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N167" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O167">
         <v>18.59</v>
@@ -8963,8 +8954,8 @@
       </c>
     </row>
     <row r="168" spans="1:16">
-      <c r="A168" t="s">
-        <v>16</v>
+      <c r="A168">
+        <v>20260423</v>
       </c>
       <c r="B168" t="s">
         <v>60</v>
@@ -8975,14 +8966,14 @@
       <c r="D168">
         <v>68.3</v>
       </c>
-      <c r="E168" t="s">
-        <v>72</v>
+      <c r="E168">
+        <v>0</v>
       </c>
       <c r="F168" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G168" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H168">
         <v>2335</v>
@@ -8991,19 +8982,19 @@
         <v>1.700000000000003</v>
       </c>
       <c r="J168" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K168">
         <v>1</v>
       </c>
       <c r="L168" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M168" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N168" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O168">
         <v>18.59</v>
@@ -9013,8 +9004,8 @@
       </c>
     </row>
     <row r="169" spans="1:16">
-      <c r="A169" t="s">
-        <v>16</v>
+      <c r="A169">
+        <v>20260423</v>
       </c>
       <c r="B169" t="s">
         <v>61</v>
@@ -9025,14 +9016,14 @@
       <c r="D169">
         <v>66.40000000000001</v>
       </c>
-      <c r="E169" t="s">
-        <v>72</v>
+      <c r="E169">
+        <v>0</v>
       </c>
       <c r="F169" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G169" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H169">
         <v>295.4</v>
@@ -9041,19 +9032,19 @@
         <v>3.599999999999994</v>
       </c>
       <c r="J169" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K169">
         <v>1</v>
       </c>
       <c r="L169" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M169" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N169" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O169">
         <v>18.59</v>
@@ -9063,8 +9054,8 @@
       </c>
     </row>
     <row r="170" spans="1:16">
-      <c r="A170" t="s">
-        <v>16</v>
+      <c r="A170">
+        <v>20260423</v>
       </c>
       <c r="B170" t="s">
         <v>62</v>
@@ -9075,14 +9066,14 @@
       <c r="D170">
         <v>66.3</v>
       </c>
-      <c r="E170" t="s">
-        <v>72</v>
+      <c r="E170">
+        <v>0</v>
       </c>
       <c r="F170" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G170" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H170">
         <v>1435.4</v>
@@ -9091,19 +9082,19 @@
         <v>3.700000000000003</v>
       </c>
       <c r="J170" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K170">
         <v>1</v>
       </c>
       <c r="L170" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M170" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N170" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O170">
         <v>18.59</v>
@@ -9113,8 +9104,8 @@
       </c>
     </row>
     <row r="171" spans="1:16">
-      <c r="A171" t="s">
-        <v>16</v>
+      <c r="A171">
+        <v>20260423</v>
       </c>
       <c r="B171" t="s">
         <v>63</v>
@@ -9125,14 +9116,14 @@
       <c r="D171">
         <v>65.40000000000001</v>
       </c>
-      <c r="E171" t="s">
-        <v>72</v>
+      <c r="E171">
+        <v>0</v>
       </c>
       <c r="F171" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G171" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H171">
         <v>1460.2</v>
@@ -9141,19 +9132,19 @@
         <v>4.599999999999994</v>
       </c>
       <c r="J171" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="K171">
         <v>1</v>
       </c>
       <c r="L171" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M171" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N171" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O171">
         <v>18.59</v>
@@ -9163,8 +9154,8 @@
       </c>
     </row>
     <row r="172" spans="1:16">
-      <c r="A172" t="s">
-        <v>16</v>
+      <c r="A172">
+        <v>20260423</v>
       </c>
       <c r="B172" t="s">
         <v>22</v>
@@ -9175,14 +9166,14 @@
       <c r="D172">
         <v>64</v>
       </c>
-      <c r="E172" t="s">
-        <v>73</v>
+      <c r="E172">
+        <v>-0.5</v>
       </c>
       <c r="F172" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G172" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H172">
         <v>1369.6</v>
@@ -9191,19 +9182,19 @@
         <v>6</v>
       </c>
       <c r="J172" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K172">
         <v>15</v>
       </c>
       <c r="L172" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M172" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N172" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O172">
         <v>18.59</v>
@@ -9213,8 +9204,8 @@
       </c>
     </row>
     <row r="173" spans="1:16">
-      <c r="A173" t="s">
-        <v>16</v>
+      <c r="A173">
+        <v>20260423</v>
       </c>
       <c r="B173" t="s">
         <v>23</v>
@@ -9225,14 +9216,14 @@
       <c r="D173">
         <v>64</v>
       </c>
-      <c r="E173" t="s">
-        <v>73</v>
+      <c r="E173">
+        <v>-0.5</v>
       </c>
       <c r="F173" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G173" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H173">
         <v>4456.5</v>
@@ -9241,19 +9232,19 @@
         <v>6</v>
       </c>
       <c r="J173" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K173">
         <v>15</v>
       </c>
       <c r="L173" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M173" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N173" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O173">
         <v>18.59</v>
@@ -9263,8 +9254,8 @@
       </c>
     </row>
     <row r="174" spans="1:16">
-      <c r="A174" t="s">
-        <v>16</v>
+      <c r="A174">
+        <v>20260423</v>
       </c>
       <c r="B174" t="s">
         <v>39</v>
@@ -9275,14 +9266,14 @@
       <c r="D174">
         <v>63.9</v>
       </c>
-      <c r="E174" t="s">
-        <v>74</v>
+      <c r="E174">
+        <v>-2.9</v>
       </c>
       <c r="F174" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G174" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H174">
         <v>402.25</v>
@@ -9291,19 +9282,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J174" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K174">
         <v>5</v>
       </c>
       <c r="L174" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="M174" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N174" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O174">
         <v>18.59</v>
@@ -9313,8 +9304,8 @@
       </c>
     </row>
     <row r="175" spans="1:16">
-      <c r="A175" t="s">
-        <v>16</v>
+      <c r="A175">
+        <v>20260423</v>
       </c>
       <c r="B175" t="s">
         <v>64</v>
@@ -9325,14 +9316,14 @@
       <c r="D175">
         <v>61.5</v>
       </c>
-      <c r="E175" t="s">
-        <v>72</v>
+      <c r="E175">
+        <v>0</v>
       </c>
       <c r="F175" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G175" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H175">
         <v>2022.9</v>
@@ -9341,19 +9332,19 @@
         <v>8.5</v>
       </c>
       <c r="J175" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K175">
         <v>1</v>
       </c>
       <c r="L175" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M175" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N175" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O175">
         <v>18.59</v>
@@ -9363,8 +9354,8 @@
       </c>
     </row>
     <row r="176" spans="1:16">
-      <c r="A176" t="s">
-        <v>16</v>
+      <c r="A176">
+        <v>20260423</v>
       </c>
       <c r="B176" t="s">
         <v>32</v>
@@ -9375,14 +9366,14 @@
       <c r="D176">
         <v>61.4</v>
       </c>
-      <c r="E176" t="s">
-        <v>75</v>
+      <c r="E176">
+        <v>0.5</v>
       </c>
       <c r="F176" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G176" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H176">
         <v>1410.5</v>
@@ -9391,19 +9382,19 @@
         <v>8.600000000000001</v>
       </c>
       <c r="J176" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K176">
         <v>10</v>
       </c>
       <c r="L176" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="M176" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N176" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O176">
         <v>18.59</v>
@@ -9413,8 +9404,8 @@
       </c>
     </row>
     <row r="177" spans="1:16">
-      <c r="A177" t="s">
-        <v>16</v>
+      <c r="A177">
+        <v>20260423</v>
       </c>
       <c r="B177" t="s">
         <v>65</v>
@@ -9425,14 +9416,14 @@
       <c r="D177">
         <v>61.4</v>
       </c>
-      <c r="E177" t="s">
-        <v>72</v>
+      <c r="E177">
+        <v>0</v>
       </c>
       <c r="F177" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G177" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H177">
         <v>1056.25</v>
@@ -9441,19 +9432,19 @@
         <v>8.600000000000001</v>
       </c>
       <c r="J177" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K177">
         <v>1</v>
       </c>
       <c r="L177" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M177" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N177" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O177">
         <v>18.59</v>
@@ -9463,8 +9454,8 @@
       </c>
     </row>
     <row r="178" spans="1:16">
-      <c r="A178" t="s">
-        <v>16</v>
+      <c r="A178">
+        <v>20260423</v>
       </c>
       <c r="B178" t="s">
         <v>66</v>
@@ -9475,14 +9466,14 @@
       <c r="D178">
         <v>60.9</v>
       </c>
-      <c r="E178" t="s">
-        <v>72</v>
+      <c r="E178">
+        <v>0</v>
       </c>
       <c r="F178" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G178" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H178">
         <v>187.01</v>
@@ -9491,19 +9482,19 @@
         <v>9.100000000000001</v>
       </c>
       <c r="J178" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="K178">
         <v>1</v>
       </c>
       <c r="L178" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M178" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N178" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O178">
         <v>18.59</v>
@@ -9513,8 +9504,8 @@
       </c>
     </row>
     <row r="179" spans="1:16">
-      <c r="A179" t="s">
-        <v>16</v>
+      <c r="A179">
+        <v>20260423</v>
       </c>
       <c r="B179" t="s">
         <v>67</v>
@@ -9525,14 +9516,14 @@
       <c r="D179">
         <v>59.4</v>
       </c>
-      <c r="E179" t="s">
-        <v>72</v>
+      <c r="E179">
+        <v>0</v>
       </c>
       <c r="F179" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G179" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H179">
         <v>180.18</v>
@@ -9541,19 +9532,19 @@
         <v>10.6</v>
       </c>
       <c r="J179" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K179">
         <v>1</v>
       </c>
       <c r="L179" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M179" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N179" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O179">
         <v>18.59</v>
@@ -9563,8 +9554,8 @@
       </c>
     </row>
     <row r="180" spans="1:16">
-      <c r="A180" t="s">
-        <v>16</v>
+      <c r="A180">
+        <v>20260423</v>
       </c>
       <c r="B180" t="s">
         <v>68</v>
@@ -9575,14 +9566,14 @@
       <c r="D180">
         <v>59.4</v>
       </c>
-      <c r="E180" t="s">
-        <v>72</v>
+      <c r="E180">
+        <v>0</v>
       </c>
       <c r="F180" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G180" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H180">
         <v>243.68</v>
@@ -9591,19 +9582,19 @@
         <v>10.6</v>
       </c>
       <c r="J180" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K180">
         <v>1</v>
       </c>
       <c r="L180" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M180" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N180" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O180">
         <v>18.59</v>
@@ -9613,8 +9604,8 @@
       </c>
     </row>
     <row r="181" spans="1:16">
-      <c r="A181" t="s">
-        <v>16</v>
+      <c r="A181">
+        <v>20260423</v>
       </c>
       <c r="B181" t="s">
         <v>56</v>
@@ -9625,14 +9616,14 @@
       <c r="D181">
         <v>57.3</v>
       </c>
-      <c r="E181" t="s">
-        <v>73</v>
+      <c r="E181">
+        <v>-0.5</v>
       </c>
       <c r="F181" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G181" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H181">
         <v>450.65</v>
@@ -9641,19 +9632,19 @@
         <v>12.7</v>
       </c>
       <c r="J181" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="K181">
         <v>4</v>
       </c>
       <c r="L181" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M181" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N181" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O181">
         <v>18.59</v>
@@ -9663,8 +9654,8 @@
       </c>
     </row>
     <row r="182" spans="1:16">
-      <c r="A182" t="s">
-        <v>16</v>
+      <c r="A182">
+        <v>20260423</v>
       </c>
       <c r="B182" t="s">
         <v>69</v>
@@ -9675,14 +9666,14 @@
       <c r="D182">
         <v>56.9</v>
       </c>
-      <c r="E182" t="s">
-        <v>72</v>
+      <c r="E182">
+        <v>0</v>
       </c>
       <c r="F182" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G182" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H182">
         <v>97.75</v>
@@ -9691,19 +9682,19 @@
         <v>13.1</v>
       </c>
       <c r="J182" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="K182">
         <v>1</v>
       </c>
       <c r="L182" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="M182" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N182" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O182">
         <v>18.59</v>
@@ -9713,8 +9704,8 @@
       </c>
     </row>
     <row r="183" spans="1:16">
-      <c r="A183" t="s">
-        <v>16</v>
+      <c r="A183">
+        <v>20260423</v>
       </c>
       <c r="B183" t="s">
         <v>33</v>
@@ -9725,14 +9716,14 @@
       <c r="D183">
         <v>56.6</v>
       </c>
-      <c r="E183" t="s">
-        <v>75</v>
+      <c r="E183">
+        <v>0.5</v>
       </c>
       <c r="F183" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G183" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H183">
         <v>9550.5</v>
@@ -9741,19 +9732,19 @@
         <v>13.4</v>
       </c>
       <c r="J183" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="K183">
         <v>15</v>
       </c>
       <c r="L183" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M183" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N183" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O183">
         <v>18.59</v>
@@ -9763,8 +9754,8 @@
       </c>
     </row>
     <row r="184" spans="1:16">
-      <c r="A184" t="s">
-        <v>16</v>
+      <c r="A184">
+        <v>20260423</v>
       </c>
       <c r="B184" t="s">
         <v>37</v>
@@ -9775,14 +9766,14 @@
       <c r="D184">
         <v>55.9</v>
       </c>
-      <c r="E184" t="s">
-        <v>73</v>
+      <c r="E184">
+        <v>-0.5</v>
       </c>
       <c r="F184" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="G184" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="H184">
         <v>319.15</v>
@@ -9791,24 +9782,1018 @@
         <v>14.1</v>
       </c>
       <c r="J184" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="K184">
         <v>15</v>
       </c>
       <c r="L184" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="M184" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N184" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O184">
         <v>18.59</v>
       </c>
       <c r="P184">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="185" spans="1:16">
+      <c r="A185" t="s">
+        <v>16</v>
+      </c>
+      <c r="B185" t="s">
+        <v>57</v>
+      </c>
+      <c r="C185" t="s">
+        <v>70</v>
+      </c>
+      <c r="D185">
+        <v>78.8</v>
+      </c>
+      <c r="E185" t="s">
+        <v>72</v>
+      </c>
+      <c r="F185" t="s">
+        <v>73</v>
+      </c>
+      <c r="G185" t="s">
+        <v>75</v>
+      </c>
+      <c r="H185">
+        <v>6727</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="K185">
+        <v>1</v>
+      </c>
+      <c r="L185" t="s">
+        <v>16</v>
+      </c>
+      <c r="M185" t="s">
+        <v>90</v>
+      </c>
+      <c r="N185" t="s">
+        <v>96</v>
+      </c>
+      <c r="O185">
+        <v>18.59</v>
+      </c>
+      <c r="P185">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="186" spans="1:16">
+      <c r="A186" t="s">
+        <v>16</v>
+      </c>
+      <c r="B186" t="s">
+        <v>58</v>
+      </c>
+      <c r="C186" t="s">
+        <v>70</v>
+      </c>
+      <c r="D186">
+        <v>75.8</v>
+      </c>
+      <c r="E186" t="s">
+        <v>72</v>
+      </c>
+      <c r="F186" t="s">
+        <v>73</v>
+      </c>
+      <c r="G186" t="s">
+        <v>74</v>
+      </c>
+      <c r="H186">
+        <v>4135.1</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+      <c r="K186">
+        <v>1</v>
+      </c>
+      <c r="L186" t="s">
+        <v>16</v>
+      </c>
+      <c r="M186" t="s">
+        <v>90</v>
+      </c>
+      <c r="N186" t="s">
+        <v>96</v>
+      </c>
+      <c r="O186">
+        <v>18.59</v>
+      </c>
+      <c r="P186">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="187" spans="1:16">
+      <c r="A187" t="s">
+        <v>16</v>
+      </c>
+      <c r="B187" t="s">
+        <v>59</v>
+      </c>
+      <c r="C187" t="s">
+        <v>71</v>
+      </c>
+      <c r="D187">
+        <v>69.3</v>
+      </c>
+      <c r="E187" t="s">
+        <v>72</v>
+      </c>
+      <c r="F187" t="s">
+        <v>73</v>
+      </c>
+      <c r="G187" t="s">
+        <v>74</v>
+      </c>
+      <c r="H187">
+        <v>297</v>
+      </c>
+      <c r="I187">
+        <v>0.7000000000000028</v>
+      </c>
+      <c r="J187" t="s">
+        <v>77</v>
+      </c>
+      <c r="K187">
+        <v>2</v>
+      </c>
+      <c r="L187" t="s">
+        <v>89</v>
+      </c>
+      <c r="M187" t="s">
+        <v>90</v>
+      </c>
+      <c r="N187" t="s">
+        <v>96</v>
+      </c>
+      <c r="O187">
+        <v>18.59</v>
+      </c>
+      <c r="P187">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="188" spans="1:16">
+      <c r="A188" t="s">
+        <v>16</v>
+      </c>
+      <c r="B188" t="s">
+        <v>60</v>
+      </c>
+      <c r="C188" t="s">
+        <v>71</v>
+      </c>
+      <c r="D188">
+        <v>68.3</v>
+      </c>
+      <c r="E188" t="s">
+        <v>72</v>
+      </c>
+      <c r="F188" t="s">
+        <v>73</v>
+      </c>
+      <c r="G188" t="s">
+        <v>74</v>
+      </c>
+      <c r="H188">
+        <v>2335</v>
+      </c>
+      <c r="I188">
+        <v>1.700000000000003</v>
+      </c>
+      <c r="J188" t="s">
+        <v>76</v>
+      </c>
+      <c r="K188">
+        <v>2</v>
+      </c>
+      <c r="L188" t="s">
+        <v>89</v>
+      </c>
+      <c r="M188" t="s">
+        <v>90</v>
+      </c>
+      <c r="N188" t="s">
+        <v>96</v>
+      </c>
+      <c r="O188">
+        <v>18.59</v>
+      </c>
+      <c r="P188">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="189" spans="1:16">
+      <c r="A189" t="s">
+        <v>16</v>
+      </c>
+      <c r="B189" t="s">
+        <v>61</v>
+      </c>
+      <c r="C189" t="s">
+        <v>71</v>
+      </c>
+      <c r="D189">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="E189" t="s">
+        <v>72</v>
+      </c>
+      <c r="F189" t="s">
+        <v>73</v>
+      </c>
+      <c r="G189" t="s">
+        <v>74</v>
+      </c>
+      <c r="H189">
+        <v>295.4</v>
+      </c>
+      <c r="I189">
+        <v>3.599999999999994</v>
+      </c>
+      <c r="J189" t="s">
+        <v>76</v>
+      </c>
+      <c r="K189">
+        <v>2</v>
+      </c>
+      <c r="L189" t="s">
+        <v>89</v>
+      </c>
+      <c r="M189" t="s">
+        <v>90</v>
+      </c>
+      <c r="N189" t="s">
+        <v>96</v>
+      </c>
+      <c r="O189">
+        <v>18.59</v>
+      </c>
+      <c r="P189">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="190" spans="1:16">
+      <c r="A190" t="s">
+        <v>16</v>
+      </c>
+      <c r="B190" t="s">
+        <v>62</v>
+      </c>
+      <c r="C190" t="s">
+        <v>71</v>
+      </c>
+      <c r="D190">
+        <v>66.3</v>
+      </c>
+      <c r="E190" t="s">
+        <v>72</v>
+      </c>
+      <c r="F190" t="s">
+        <v>73</v>
+      </c>
+      <c r="G190" t="s">
+        <v>74</v>
+      </c>
+      <c r="H190">
+        <v>1435.4</v>
+      </c>
+      <c r="I190">
+        <v>3.700000000000003</v>
+      </c>
+      <c r="J190" t="s">
+        <v>76</v>
+      </c>
+      <c r="K190">
+        <v>2</v>
+      </c>
+      <c r="L190" t="s">
+        <v>89</v>
+      </c>
+      <c r="M190" t="s">
+        <v>90</v>
+      </c>
+      <c r="N190" t="s">
+        <v>96</v>
+      </c>
+      <c r="O190">
+        <v>18.59</v>
+      </c>
+      <c r="P190">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="191" spans="1:16">
+      <c r="A191" t="s">
+        <v>16</v>
+      </c>
+      <c r="B191" t="s">
+        <v>63</v>
+      </c>
+      <c r="C191" t="s">
+        <v>71</v>
+      </c>
+      <c r="D191">
+        <v>65.40000000000001</v>
+      </c>
+      <c r="E191" t="s">
+        <v>72</v>
+      </c>
+      <c r="F191" t="s">
+        <v>73</v>
+      </c>
+      <c r="G191" t="s">
+        <v>74</v>
+      </c>
+      <c r="H191">
+        <v>1460.2</v>
+      </c>
+      <c r="I191">
+        <v>4.599999999999994</v>
+      </c>
+      <c r="J191" t="s">
+        <v>79</v>
+      </c>
+      <c r="K191">
+        <v>2</v>
+      </c>
+      <c r="L191" t="s">
+        <v>89</v>
+      </c>
+      <c r="M191" t="s">
+        <v>90</v>
+      </c>
+      <c r="N191" t="s">
+        <v>96</v>
+      </c>
+      <c r="O191">
+        <v>18.59</v>
+      </c>
+      <c r="P191">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="192" spans="1:16">
+      <c r="A192" t="s">
+        <v>16</v>
+      </c>
+      <c r="B192" t="s">
+        <v>22</v>
+      </c>
+      <c r="C192" t="s">
+        <v>71</v>
+      </c>
+      <c r="D192">
+        <v>64</v>
+      </c>
+      <c r="E192" t="s">
+        <v>72</v>
+      </c>
+      <c r="F192" t="s">
+        <v>73</v>
+      </c>
+      <c r="G192" t="s">
+        <v>74</v>
+      </c>
+      <c r="H192">
+        <v>1369.6</v>
+      </c>
+      <c r="I192">
+        <v>6</v>
+      </c>
+      <c r="J192" t="s">
+        <v>76</v>
+      </c>
+      <c r="K192">
+        <v>16</v>
+      </c>
+      <c r="L192" t="s">
+        <v>86</v>
+      </c>
+      <c r="M192" t="s">
+        <v>90</v>
+      </c>
+      <c r="N192" t="s">
+        <v>96</v>
+      </c>
+      <c r="O192">
+        <v>18.59</v>
+      </c>
+      <c r="P192">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="193" spans="1:16">
+      <c r="A193" t="s">
+        <v>16</v>
+      </c>
+      <c r="B193" t="s">
+        <v>23</v>
+      </c>
+      <c r="C193" t="s">
+        <v>71</v>
+      </c>
+      <c r="D193">
+        <v>64</v>
+      </c>
+      <c r="E193" t="s">
+        <v>72</v>
+      </c>
+      <c r="F193" t="s">
+        <v>73</v>
+      </c>
+      <c r="G193" t="s">
+        <v>74</v>
+      </c>
+      <c r="H193">
+        <v>4456.5</v>
+      </c>
+      <c r="I193">
+        <v>6</v>
+      </c>
+      <c r="J193" t="s">
+        <v>76</v>
+      </c>
+      <c r="K193">
+        <v>16</v>
+      </c>
+      <c r="L193" t="s">
+        <v>86</v>
+      </c>
+      <c r="M193" t="s">
+        <v>90</v>
+      </c>
+      <c r="N193" t="s">
+        <v>96</v>
+      </c>
+      <c r="O193">
+        <v>18.59</v>
+      </c>
+      <c r="P193">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="194" spans="1:16">
+      <c r="A194" t="s">
+        <v>16</v>
+      </c>
+      <c r="B194" t="s">
+        <v>39</v>
+      </c>
+      <c r="C194" t="s">
+        <v>71</v>
+      </c>
+      <c r="D194">
+        <v>63.9</v>
+      </c>
+      <c r="E194" t="s">
+        <v>72</v>
+      </c>
+      <c r="F194" t="s">
+        <v>73</v>
+      </c>
+      <c r="G194" t="s">
+        <v>74</v>
+      </c>
+      <c r="H194">
+        <v>402.25</v>
+      </c>
+      <c r="I194">
+        <v>6.100000000000001</v>
+      </c>
+      <c r="J194" t="s">
+        <v>76</v>
+      </c>
+      <c r="K194">
+        <v>6</v>
+      </c>
+      <c r="L194" t="s">
+        <v>88</v>
+      </c>
+      <c r="M194" t="s">
+        <v>90</v>
+      </c>
+      <c r="N194" t="s">
+        <v>96</v>
+      </c>
+      <c r="O194">
+        <v>18.59</v>
+      </c>
+      <c r="P194">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="195" spans="1:16">
+      <c r="A195" t="s">
+        <v>16</v>
+      </c>
+      <c r="B195" t="s">
+        <v>64</v>
+      </c>
+      <c r="C195" t="s">
+        <v>71</v>
+      </c>
+      <c r="D195">
+        <v>61.5</v>
+      </c>
+      <c r="E195" t="s">
+        <v>72</v>
+      </c>
+      <c r="F195" t="s">
+        <v>73</v>
+      </c>
+      <c r="G195" t="s">
+        <v>74</v>
+      </c>
+      <c r="H195">
+        <v>2022.9</v>
+      </c>
+      <c r="I195">
+        <v>8.5</v>
+      </c>
+      <c r="J195" t="s">
+        <v>77</v>
+      </c>
+      <c r="K195">
+        <v>2</v>
+      </c>
+      <c r="L195" t="s">
+        <v>89</v>
+      </c>
+      <c r="M195" t="s">
+        <v>90</v>
+      </c>
+      <c r="N195" t="s">
+        <v>96</v>
+      </c>
+      <c r="O195">
+        <v>18.59</v>
+      </c>
+      <c r="P195">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="196" spans="1:16">
+      <c r="A196" t="s">
+        <v>16</v>
+      </c>
+      <c r="B196" t="s">
+        <v>32</v>
+      </c>
+      <c r="C196" t="s">
+        <v>71</v>
+      </c>
+      <c r="D196">
+        <v>61.4</v>
+      </c>
+      <c r="E196" t="s">
+        <v>72</v>
+      </c>
+      <c r="F196" t="s">
+        <v>73</v>
+      </c>
+      <c r="G196" t="s">
+        <v>74</v>
+      </c>
+      <c r="H196">
+        <v>1410.5</v>
+      </c>
+      <c r="I196">
+        <v>8.600000000000001</v>
+      </c>
+      <c r="J196" t="s">
+        <v>78</v>
+      </c>
+      <c r="K196">
+        <v>11</v>
+      </c>
+      <c r="L196" t="s">
+        <v>85</v>
+      </c>
+      <c r="M196" t="s">
+        <v>90</v>
+      </c>
+      <c r="N196" t="s">
+        <v>96</v>
+      </c>
+      <c r="O196">
+        <v>18.59</v>
+      </c>
+      <c r="P196">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="197" spans="1:16">
+      <c r="A197" t="s">
+        <v>16</v>
+      </c>
+      <c r="B197" t="s">
+        <v>65</v>
+      </c>
+      <c r="C197" t="s">
+        <v>71</v>
+      </c>
+      <c r="D197">
+        <v>61.4</v>
+      </c>
+      <c r="E197" t="s">
+        <v>72</v>
+      </c>
+      <c r="F197" t="s">
+        <v>73</v>
+      </c>
+      <c r="G197" t="s">
+        <v>74</v>
+      </c>
+      <c r="H197">
+        <v>1056.25</v>
+      </c>
+      <c r="I197">
+        <v>8.600000000000001</v>
+      </c>
+      <c r="J197" t="s">
+        <v>78</v>
+      </c>
+      <c r="K197">
+        <v>2</v>
+      </c>
+      <c r="L197" t="s">
+        <v>89</v>
+      </c>
+      <c r="M197" t="s">
+        <v>90</v>
+      </c>
+      <c r="N197" t="s">
+        <v>96</v>
+      </c>
+      <c r="O197">
+        <v>18.59</v>
+      </c>
+      <c r="P197">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="198" spans="1:16">
+      <c r="A198" t="s">
+        <v>16</v>
+      </c>
+      <c r="B198" t="s">
+        <v>66</v>
+      </c>
+      <c r="C198" t="s">
+        <v>71</v>
+      </c>
+      <c r="D198">
+        <v>60.9</v>
+      </c>
+      <c r="E198" t="s">
+        <v>72</v>
+      </c>
+      <c r="F198" t="s">
+        <v>73</v>
+      </c>
+      <c r="G198" t="s">
+        <v>74</v>
+      </c>
+      <c r="H198">
+        <v>187.01</v>
+      </c>
+      <c r="I198">
+        <v>9.100000000000001</v>
+      </c>
+      <c r="J198" t="s">
+        <v>77</v>
+      </c>
+      <c r="K198">
+        <v>2</v>
+      </c>
+      <c r="L198" t="s">
+        <v>89</v>
+      </c>
+      <c r="M198" t="s">
+        <v>90</v>
+      </c>
+      <c r="N198" t="s">
+        <v>96</v>
+      </c>
+      <c r="O198">
+        <v>18.59</v>
+      </c>
+      <c r="P198">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="199" spans="1:16">
+      <c r="A199" t="s">
+        <v>16</v>
+      </c>
+      <c r="B199" t="s">
+        <v>67</v>
+      </c>
+      <c r="C199" t="s">
+        <v>71</v>
+      </c>
+      <c r="D199">
+        <v>59.4</v>
+      </c>
+      <c r="E199" t="s">
+        <v>72</v>
+      </c>
+      <c r="F199" t="s">
+        <v>73</v>
+      </c>
+      <c r="G199" t="s">
+        <v>74</v>
+      </c>
+      <c r="H199">
+        <v>180.18</v>
+      </c>
+      <c r="I199">
+        <v>10.6</v>
+      </c>
+      <c r="J199" t="s">
+        <v>78</v>
+      </c>
+      <c r="K199">
+        <v>2</v>
+      </c>
+      <c r="L199" t="s">
+        <v>89</v>
+      </c>
+      <c r="M199" t="s">
+        <v>90</v>
+      </c>
+      <c r="N199" t="s">
+        <v>96</v>
+      </c>
+      <c r="O199">
+        <v>18.59</v>
+      </c>
+      <c r="P199">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="200" spans="1:16">
+      <c r="A200" t="s">
+        <v>16</v>
+      </c>
+      <c r="B200" t="s">
+        <v>68</v>
+      </c>
+      <c r="C200" t="s">
+        <v>71</v>
+      </c>
+      <c r="D200">
+        <v>59.4</v>
+      </c>
+      <c r="E200" t="s">
+        <v>72</v>
+      </c>
+      <c r="F200" t="s">
+        <v>73</v>
+      </c>
+      <c r="G200" t="s">
+        <v>74</v>
+      </c>
+      <c r="H200">
+        <v>243.68</v>
+      </c>
+      <c r="I200">
+        <v>10.6</v>
+      </c>
+      <c r="J200" t="s">
+        <v>78</v>
+      </c>
+      <c r="K200">
+        <v>2</v>
+      </c>
+      <c r="L200" t="s">
+        <v>89</v>
+      </c>
+      <c r="M200" t="s">
+        <v>90</v>
+      </c>
+      <c r="N200" t="s">
+        <v>96</v>
+      </c>
+      <c r="O200">
+        <v>18.59</v>
+      </c>
+      <c r="P200">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="201" spans="1:16">
+      <c r="A201" t="s">
+        <v>16</v>
+      </c>
+      <c r="B201" t="s">
+        <v>56</v>
+      </c>
+      <c r="C201" t="s">
+        <v>71</v>
+      </c>
+      <c r="D201">
+        <v>57.3</v>
+      </c>
+      <c r="E201" t="s">
+        <v>72</v>
+      </c>
+      <c r="F201" t="s">
+        <v>73</v>
+      </c>
+      <c r="G201" t="s">
+        <v>74</v>
+      </c>
+      <c r="H201">
+        <v>450.65</v>
+      </c>
+      <c r="I201">
+        <v>12.7</v>
+      </c>
+      <c r="J201" t="s">
+        <v>83</v>
+      </c>
+      <c r="K201">
+        <v>5</v>
+      </c>
+      <c r="L201" t="s">
+        <v>89</v>
+      </c>
+      <c r="M201" t="s">
+        <v>90</v>
+      </c>
+      <c r="N201" t="s">
+        <v>96</v>
+      </c>
+      <c r="O201">
+        <v>18.59</v>
+      </c>
+      <c r="P201">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="202" spans="1:16">
+      <c r="A202" t="s">
+        <v>16</v>
+      </c>
+      <c r="B202" t="s">
+        <v>69</v>
+      </c>
+      <c r="C202" t="s">
+        <v>71</v>
+      </c>
+      <c r="D202">
+        <v>56.9</v>
+      </c>
+      <c r="E202" t="s">
+        <v>72</v>
+      </c>
+      <c r="F202" t="s">
+        <v>73</v>
+      </c>
+      <c r="G202" t="s">
+        <v>74</v>
+      </c>
+      <c r="H202">
+        <v>97.75</v>
+      </c>
+      <c r="I202">
+        <v>13.1</v>
+      </c>
+      <c r="J202" t="s">
+        <v>78</v>
+      </c>
+      <c r="K202">
+        <v>2</v>
+      </c>
+      <c r="L202" t="s">
+        <v>89</v>
+      </c>
+      <c r="M202" t="s">
+        <v>90</v>
+      </c>
+      <c r="N202" t="s">
+        <v>96</v>
+      </c>
+      <c r="O202">
+        <v>18.59</v>
+      </c>
+      <c r="P202">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="203" spans="1:16">
+      <c r="A203" t="s">
+        <v>16</v>
+      </c>
+      <c r="B203" t="s">
+        <v>33</v>
+      </c>
+      <c r="C203" t="s">
+        <v>71</v>
+      </c>
+      <c r="D203">
+        <v>56.6</v>
+      </c>
+      <c r="E203" t="s">
+        <v>72</v>
+      </c>
+      <c r="F203" t="s">
+        <v>73</v>
+      </c>
+      <c r="G203" t="s">
+        <v>74</v>
+      </c>
+      <c r="H203">
+        <v>9550.5</v>
+      </c>
+      <c r="I203">
+        <v>13.4</v>
+      </c>
+      <c r="J203" t="s">
+        <v>76</v>
+      </c>
+      <c r="K203">
+        <v>16</v>
+      </c>
+      <c r="L203" t="s">
+        <v>86</v>
+      </c>
+      <c r="M203" t="s">
+        <v>90</v>
+      </c>
+      <c r="N203" t="s">
+        <v>96</v>
+      </c>
+      <c r="O203">
+        <v>18.59</v>
+      </c>
+      <c r="P203">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="204" spans="1:16">
+      <c r="A204" t="s">
+        <v>16</v>
+      </c>
+      <c r="B204" t="s">
+        <v>37</v>
+      </c>
+      <c r="C204" t="s">
+        <v>71</v>
+      </c>
+      <c r="D204">
+        <v>55.9</v>
+      </c>
+      <c r="E204" t="s">
+        <v>72</v>
+      </c>
+      <c r="F204" t="s">
+        <v>73</v>
+      </c>
+      <c r="G204" t="s">
+        <v>74</v>
+      </c>
+      <c r="H204">
+        <v>319.15</v>
+      </c>
+      <c r="I204">
+        <v>14.1</v>
+      </c>
+      <c r="J204" t="s">
+        <v>80</v>
+      </c>
+      <c r="K204">
+        <v>16</v>
+      </c>
+      <c r="L204" t="s">
+        <v>86</v>
+      </c>
+      <c r="M204" t="s">
+        <v>90</v>
+      </c>
+      <c r="N204" t="s">
+        <v>96</v>
+      </c>
+      <c r="O204">
+        <v>18.59</v>
+      </c>
+      <c r="P204">
         <v>128</v>
       </c>
     </row>

--- a/reports/watchlist_history.xlsx
+++ b/reports/watchlist_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1666" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1766" uniqueCount="107">
   <si>
     <t>Date</t>
   </si>
@@ -64,7 +64,7 @@
     <t>FII Cr</t>
   </si>
   <si>
-    <t>20260423</t>
+    <t>20260424</t>
   </si>
   <si>
     <t>APARINDS</t>
@@ -235,6 +235,24 @@
     <t>+0.0</t>
   </si>
   <si>
+    <t>-2.4</t>
+  </si>
+  <si>
+    <t>-3.0</t>
+  </si>
+  <si>
+    <t>+4.4</t>
+  </si>
+  <si>
+    <t>+2.4</t>
+  </si>
+  <si>
+    <t>-2.0</t>
+  </si>
+  <si>
+    <t>+2.5</t>
+  </si>
+  <si>
     <t>Stage 2 — Uptrend ✓</t>
   </si>
   <si>
@@ -268,6 +286,9 @@
     <t>MACD bearish — wait for bullish crossover</t>
   </si>
   <si>
+    <t>Score 60/100 — need macro improvement or volume surge</t>
+  </si>
+  <si>
     <t>20260421</t>
   </si>
   <si>
@@ -284,6 +305,12 @@
   </si>
   <si>
     <t>2026-04-23</t>
+  </si>
+  <si>
+    <t>20260423</t>
+  </si>
+  <si>
+    <t>2026-04-24</t>
   </si>
   <si>
     <t>B</t>
@@ -305,6 +332,9 @@
   </si>
   <si>
     <t>-3.8%</t>
+  </si>
+  <si>
+    <t>-4.8%</t>
   </si>
 </sst>
 </file>
@@ -636,7 +666,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P204"/>
+  <dimension ref="A1:P218"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -706,10 +736,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G2" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H2">
         <v>11714</v>
@@ -721,13 +751,13 @@
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="M2" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N2" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O2">
         <v>17.53</v>
@@ -753,10 +783,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G3" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H3">
         <v>514.05</v>
@@ -768,13 +798,13 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="M3" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N3" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O3">
         <v>17.53</v>
@@ -800,10 +830,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H4">
         <v>1621.5</v>
@@ -815,13 +845,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="M4" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N4" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O4">
         <v>17.53</v>
@@ -847,10 +877,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G5" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H5">
         <v>191.38</v>
@@ -859,19 +889,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J5" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M5" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N5" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O5">
         <v>17.53</v>
@@ -897,10 +927,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G6" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H6">
         <v>1318.1</v>
@@ -909,19 +939,19 @@
         <v>0.9000000000000057</v>
       </c>
       <c r="J6" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M6" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N6" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O6">
         <v>17.53</v>
@@ -947,10 +977,10 @@
         <v>-0.5</v>
       </c>
       <c r="F7" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G7" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H7">
         <v>1377.7</v>
@@ -959,19 +989,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J7" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K7">
         <v>6</v>
       </c>
       <c r="L7" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M7" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N7" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O7">
         <v>17.53</v>
@@ -997,10 +1027,10 @@
         <v>-0.5</v>
       </c>
       <c r="F8" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G8" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H8">
         <v>4479.7</v>
@@ -1009,19 +1039,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J8" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K8">
         <v>6</v>
       </c>
       <c r="L8" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M8" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N8" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O8">
         <v>17.53</v>
@@ -1047,10 +1077,10 @@
         <v>-0.5</v>
       </c>
       <c r="F9" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G9" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H9">
         <v>1045.3</v>
@@ -1059,19 +1089,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J9" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K9">
         <v>6</v>
       </c>
       <c r="L9" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M9" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N9" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O9">
         <v>17.53</v>
@@ -1097,10 +1127,10 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G10" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H10">
         <v>1055.65</v>
@@ -1109,19 +1139,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J10" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M10" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N10" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O10">
         <v>17.53</v>
@@ -1147,10 +1177,10 @@
         <v>-0.5</v>
       </c>
       <c r="F11" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G11" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H11">
         <v>1045.3</v>
@@ -1159,19 +1189,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J11" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K11">
         <v>6</v>
       </c>
       <c r="L11" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M11" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N11" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O11">
         <v>17.53</v>
@@ -1197,10 +1227,10 @@
         <v>-0.5</v>
       </c>
       <c r="F12" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G12" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H12">
         <v>4479.7</v>
@@ -1209,19 +1239,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J12" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K12">
         <v>6</v>
       </c>
       <c r="L12" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M12" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N12" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O12">
         <v>17.53</v>
@@ -1247,10 +1277,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G13" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H13">
         <v>581.3</v>
@@ -1259,19 +1289,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J13" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K13">
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M13" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N13" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O13">
         <v>17.53</v>
@@ -1297,10 +1327,10 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G14" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H14">
         <v>458.9</v>
@@ -1309,19 +1339,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J14" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M14" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N14" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O14">
         <v>17.53</v>
@@ -1347,10 +1377,10 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G15" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H15">
         <v>196.02</v>
@@ -1359,19 +1389,19 @@
         <v>4.400000000000006</v>
       </c>
       <c r="J15" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M15" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N15" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O15">
         <v>17.53</v>
@@ -1397,10 +1427,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G16" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H16">
         <v>4172.9</v>
@@ -1409,19 +1439,19 @@
         <v>5</v>
       </c>
       <c r="J16" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K16">
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M16" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N16" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O16">
         <v>17.53</v>
@@ -1447,10 +1477,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G17" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H17">
         <v>6373.5</v>
@@ -1459,19 +1489,19 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J17" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="K17">
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M17" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N17" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O17">
         <v>17.53</v>
@@ -1497,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G18" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H18">
         <v>1113.1</v>
@@ -1509,19 +1539,19 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J18" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M18" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N18" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O18">
         <v>17.53</v>
@@ -1547,10 +1577,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G19" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H19">
         <v>1379.9</v>
@@ -1559,19 +1589,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J19" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K19">
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M19" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N19" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O19">
         <v>17.53</v>
@@ -1597,10 +1627,10 @@
         <v>-0.5</v>
       </c>
       <c r="F20" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H20">
         <v>9793</v>
@@ -1609,19 +1639,19 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J20" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K20">
         <v>6</v>
       </c>
       <c r="L20" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M20" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N20" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O20">
         <v>17.53</v>
@@ -1647,10 +1677,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G21" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H21">
         <v>7955.5</v>
@@ -1659,19 +1689,19 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J21" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K21">
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M21" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N21" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O21">
         <v>17.53</v>
@@ -1697,10 +1727,10 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G22" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H22">
         <v>1037.85</v>
@@ -1709,19 +1739,19 @@
         <v>6.399999999999999</v>
       </c>
       <c r="J22" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K22">
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M22" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N22" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O22">
         <v>17.53</v>
@@ -1747,10 +1777,10 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G23" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H23">
         <v>979.1</v>
@@ -1759,19 +1789,19 @@
         <v>8.399999999999999</v>
       </c>
       <c r="J23" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K23">
         <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M23" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N23" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O23">
         <v>17.53</v>
@@ -1797,10 +1827,10 @@
         <v>-0.5</v>
       </c>
       <c r="F24" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G24" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H24">
         <v>319.35</v>
@@ -1809,19 +1839,19 @@
         <v>8.5</v>
       </c>
       <c r="J24" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K24">
         <v>6</v>
       </c>
       <c r="L24" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M24" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N24" t="s">
-        <v>91</v>
+        <v>100</v>
       </c>
       <c r="O24">
         <v>17.53</v>
@@ -1847,10 +1877,10 @@
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G25" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H25">
         <v>767.65</v>
@@ -1862,13 +1892,13 @@
         <v>1</v>
       </c>
       <c r="L25" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="M25" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N25" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O25">
         <v>18.27</v>
@@ -1894,10 +1924,10 @@
         <v>7.8</v>
       </c>
       <c r="F26" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H26">
         <v>404.1</v>
@@ -1906,19 +1936,19 @@
         <v>1</v>
       </c>
       <c r="J26" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K26">
         <v>7</v>
       </c>
       <c r="L26" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M26" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N26" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O26">
         <v>18.27</v>
@@ -1944,10 +1974,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H27">
         <v>3847</v>
@@ -1956,19 +1986,19 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K27">
         <v>1</v>
       </c>
       <c r="L27" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M27" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N27" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O27">
         <v>18.27</v>
@@ -1994,10 +2024,10 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G28" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H28">
         <v>211.75</v>
@@ -2006,19 +2036,19 @@
         <v>2.5</v>
       </c>
       <c r="J28" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K28">
         <v>1</v>
       </c>
       <c r="L28" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M28" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N28" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O28">
         <v>18.27</v>
@@ -2044,10 +2074,10 @@
         <v>-0.5</v>
       </c>
       <c r="F29" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H29">
         <v>1381.5</v>
@@ -2056,19 +2086,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J29" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K29">
         <v>7</v>
       </c>
       <c r="L29" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M29" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N29" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O29">
         <v>18.27</v>
@@ -2094,10 +2124,10 @@
         <v>-0.5</v>
       </c>
       <c r="F30" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G30" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H30">
         <v>4483</v>
@@ -2106,19 +2136,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J30" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K30">
         <v>7</v>
       </c>
       <c r="L30" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M30" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N30" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O30">
         <v>18.27</v>
@@ -2144,10 +2174,10 @@
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G31" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H31">
         <v>89.05</v>
@@ -2156,19 +2186,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J31" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K31">
         <v>1</v>
       </c>
       <c r="L31" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M31" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N31" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O31">
         <v>18.27</v>
@@ -2194,10 +2224,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H32">
         <v>1291.1</v>
@@ -2206,19 +2236,19 @@
         <v>3.400000000000006</v>
       </c>
       <c r="J32" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K32">
         <v>1</v>
       </c>
       <c r="L32" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M32" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N32" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O32">
         <v>18.27</v>
@@ -2244,10 +2274,10 @@
         <v>-0.5</v>
       </c>
       <c r="F33" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G33" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H33">
         <v>1414.6</v>
@@ -2256,19 +2286,19 @@
         <v>5.900000000000006</v>
       </c>
       <c r="J33" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K33">
         <v>2</v>
       </c>
       <c r="L33" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M33" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N33" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O33">
         <v>18.27</v>
@@ -2294,10 +2324,10 @@
         <v>-0.5</v>
       </c>
       <c r="F34" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G34" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H34">
         <v>9760</v>
@@ -2306,19 +2336,19 @@
         <v>6.299999999999997</v>
       </c>
       <c r="J34" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K34">
         <v>7</v>
       </c>
       <c r="L34" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M34" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N34" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O34">
         <v>18.27</v>
@@ -2344,10 +2374,10 @@
         <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G35" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H35">
         <v>125.85</v>
@@ -2356,19 +2386,19 @@
         <v>7.299999999999997</v>
       </c>
       <c r="J35" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K35">
         <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M35" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N35" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O35">
         <v>18.27</v>
@@ -2394,10 +2424,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G36" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H36">
         <v>1171.95</v>
@@ -2406,19 +2436,19 @@
         <v>7.899999999999999</v>
       </c>
       <c r="J36" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K36">
         <v>1</v>
       </c>
       <c r="L36" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M36" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N36" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O36">
         <v>18.27</v>
@@ -2444,10 +2474,10 @@
         <v>-6.5</v>
       </c>
       <c r="F37" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H37">
         <v>1038.1</v>
@@ -2456,19 +2486,19 @@
         <v>9.299999999999997</v>
       </c>
       <c r="J37" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K37">
         <v>7</v>
       </c>
       <c r="L37" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M37" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N37" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O37">
         <v>18.27</v>
@@ -2494,10 +2524,10 @@
         <v>-2.9</v>
       </c>
       <c r="F38" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G38" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H38">
         <v>319.6</v>
@@ -2506,19 +2536,19 @@
         <v>11.4</v>
       </c>
       <c r="J38" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K38">
         <v>7</v>
       </c>
       <c r="L38" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M38" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N38" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O38">
         <v>18.27</v>
@@ -2544,10 +2574,10 @@
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G39" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H39">
         <v>2314.1</v>
@@ -2556,19 +2586,19 @@
         <v>11.7</v>
       </c>
       <c r="J39" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K39">
         <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M39" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N39" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O39">
         <v>18.27</v>
@@ -2594,10 +2624,10 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H40">
         <v>3723.6</v>
@@ -2606,19 +2636,19 @@
         <v>11.7</v>
       </c>
       <c r="J40" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K40">
         <v>1</v>
       </c>
       <c r="L40" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M40" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N40" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O40">
         <v>18.27</v>
@@ -2644,10 +2674,10 @@
         <v>-0.5</v>
       </c>
       <c r="F41" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G41" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H41">
         <v>4049.2</v>
@@ -2656,19 +2686,19 @@
         <v>13.3</v>
       </c>
       <c r="J41" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K41">
         <v>3</v>
       </c>
       <c r="L41" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M41" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N41" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O41">
         <v>18.27</v>
@@ -2694,10 +2724,10 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G42" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H42">
         <v>124.98</v>
@@ -2706,19 +2736,19 @@
         <v>14.6</v>
       </c>
       <c r="J42" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K42">
         <v>1</v>
       </c>
       <c r="L42" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M42" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N42" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O42">
         <v>18.27</v>
@@ -2744,10 +2774,10 @@
         <v>2.4</v>
       </c>
       <c r="F43" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G43" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H43">
         <v>1388.7</v>
@@ -2756,19 +2786,19 @@
         <v>0.9000000000000057</v>
       </c>
       <c r="J43" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K43">
         <v>8</v>
       </c>
       <c r="L43" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M43" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N43" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O43">
         <v>18.23</v>
@@ -2794,10 +2824,10 @@
         <v>0</v>
       </c>
       <c r="F44" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G44" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H44">
         <v>404.8</v>
@@ -2806,19 +2836,19 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K44">
         <v>8</v>
       </c>
       <c r="L44" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M44" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N44" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O44">
         <v>18.23</v>
@@ -2844,10 +2874,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G45" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H45">
         <v>3845.7</v>
@@ -2856,19 +2886,19 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K45">
         <v>2</v>
       </c>
       <c r="L45" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M45" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N45" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O45">
         <v>18.23</v>
@@ -2894,10 +2924,10 @@
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G46" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H46">
         <v>213.03</v>
@@ -2906,19 +2936,19 @@
         <v>1.5</v>
       </c>
       <c r="J46" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K46">
         <v>2</v>
       </c>
       <c r="L46" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M46" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N46" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O46">
         <v>18.23</v>
@@ -2944,10 +2974,10 @@
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G47" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H47">
         <v>4477</v>
@@ -2956,19 +2986,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J47" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K47">
         <v>8</v>
       </c>
       <c r="L47" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M47" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N47" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O47">
         <v>18.23</v>
@@ -2994,10 +3024,10 @@
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G48" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H48">
         <v>88.98999999999999</v>
@@ -3006,19 +3036,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J48" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K48">
         <v>2</v>
       </c>
       <c r="L48" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M48" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N48" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O48">
         <v>18.23</v>
@@ -3044,10 +3074,10 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G49" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H49">
         <v>1288.9</v>
@@ -3056,19 +3086,19 @@
         <v>3.400000000000006</v>
       </c>
       <c r="J49" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K49">
         <v>2</v>
       </c>
       <c r="L49" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M49" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N49" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O49">
         <v>18.23</v>
@@ -3094,10 +3124,10 @@
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G50" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H50">
         <v>1419</v>
@@ -3106,19 +3136,19 @@
         <v>5.900000000000006</v>
       </c>
       <c r="J50" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K50">
         <v>3</v>
       </c>
       <c r="L50" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M50" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N50" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O50">
         <v>18.23</v>
@@ -3144,10 +3174,10 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G51" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H51">
         <v>9758</v>
@@ -3156,19 +3186,19 @@
         <v>6.299999999999997</v>
       </c>
       <c r="J51" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K51">
         <v>8</v>
       </c>
       <c r="L51" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M51" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N51" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O51">
         <v>18.23</v>
@@ -3194,10 +3224,10 @@
         <v>0</v>
       </c>
       <c r="F52" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G52" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H52">
         <v>125.98</v>
@@ -3206,19 +3236,19 @@
         <v>7.299999999999997</v>
       </c>
       <c r="J52" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K52">
         <v>2</v>
       </c>
       <c r="L52" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M52" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N52" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O52">
         <v>18.23</v>
@@ -3244,10 +3274,10 @@
         <v>0</v>
       </c>
       <c r="F53" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G53" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H53">
         <v>1182</v>
@@ -3256,19 +3286,19 @@
         <v>7.899999999999999</v>
       </c>
       <c r="J53" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K53">
         <v>2</v>
       </c>
       <c r="L53" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M53" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N53" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O53">
         <v>18.23</v>
@@ -3294,10 +3324,10 @@
         <v>0</v>
       </c>
       <c r="F54" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G54" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H54">
         <v>1040</v>
@@ -3306,19 +3336,19 @@
         <v>9.299999999999997</v>
       </c>
       <c r="J54" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K54">
         <v>8</v>
       </c>
       <c r="L54" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M54" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N54" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O54">
         <v>18.23</v>
@@ -3344,10 +3374,10 @@
         <v>0</v>
       </c>
       <c r="F55" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G55" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H55">
         <v>320.2</v>
@@ -3356,19 +3386,19 @@
         <v>11.4</v>
       </c>
       <c r="J55" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K55">
         <v>8</v>
       </c>
       <c r="L55" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M55" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N55" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O55">
         <v>18.23</v>
@@ -3394,10 +3424,10 @@
         <v>0</v>
       </c>
       <c r="F56" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G56" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H56">
         <v>2314.8</v>
@@ -3406,19 +3436,19 @@
         <v>11.7</v>
       </c>
       <c r="J56" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K56">
         <v>2</v>
       </c>
       <c r="L56" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M56" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N56" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O56">
         <v>18.23</v>
@@ -3444,10 +3474,10 @@
         <v>0</v>
       </c>
       <c r="F57" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G57" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H57">
         <v>3716.5</v>
@@ -3456,19 +3486,19 @@
         <v>11.7</v>
       </c>
       <c r="J57" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K57">
         <v>2</v>
       </c>
       <c r="L57" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M57" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N57" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O57">
         <v>18.23</v>
@@ -3494,10 +3524,10 @@
         <v>0</v>
       </c>
       <c r="F58" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G58" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H58">
         <v>4043</v>
@@ -3506,19 +3536,19 @@
         <v>13.3</v>
       </c>
       <c r="J58" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K58">
         <v>4</v>
       </c>
       <c r="L58" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M58" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N58" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O58">
         <v>18.23</v>
@@ -3544,10 +3574,10 @@
         <v>0</v>
       </c>
       <c r="F59" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G59" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H59">
         <v>125.04</v>
@@ -3556,19 +3586,19 @@
         <v>14.6</v>
       </c>
       <c r="J59" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K59">
         <v>2</v>
       </c>
       <c r="L59" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M59" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N59" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="O59">
         <v>18.23</v>
@@ -3594,10 +3624,10 @@
         <v>0</v>
       </c>
       <c r="F60" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G60" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H60">
         <v>3852.5</v>
@@ -3609,13 +3639,13 @@
         <v>1</v>
       </c>
       <c r="L60" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="M60" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N60" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="O60">
         <v>18.08</v>
@@ -3641,10 +3671,10 @@
         <v>0.5</v>
       </c>
       <c r="F61" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G61" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H61">
         <v>1388.5</v>
@@ -3653,19 +3683,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J61" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K61">
         <v>9</v>
       </c>
       <c r="L61" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M61" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N61" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="O61">
         <v>18.08</v>
@@ -3691,10 +3721,10 @@
         <v>0.5</v>
       </c>
       <c r="F62" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G62" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H62">
         <v>406.1</v>
@@ -3703,19 +3733,19 @@
         <v>0.5</v>
       </c>
       <c r="J62" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K62">
         <v>9</v>
       </c>
       <c r="L62" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M62" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N62" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="O62">
         <v>18.08</v>
@@ -3741,10 +3771,10 @@
         <v>0.5</v>
       </c>
       <c r="F63" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G63" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H63">
         <v>213.6</v>
@@ -3753,19 +3783,19 @@
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K63">
         <v>3</v>
       </c>
       <c r="L63" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M63" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N63" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="O63">
         <v>18.08</v>
@@ -3791,10 +3821,10 @@
         <v>0.5</v>
       </c>
       <c r="F64" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G64" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H64">
         <v>4478</v>
@@ -3803,19 +3833,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J64" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K64">
         <v>9</v>
       </c>
       <c r="L64" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M64" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N64" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="O64">
         <v>18.08</v>
@@ -3841,10 +3871,10 @@
         <v>6.5</v>
       </c>
       <c r="F65" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G65" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H65">
         <v>1050.05</v>
@@ -3853,19 +3883,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J65" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K65">
         <v>9</v>
       </c>
       <c r="L65" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M65" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N65" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="O65">
         <v>18.08</v>
@@ -3891,10 +3921,10 @@
         <v>0.5</v>
       </c>
       <c r="F66" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G66" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H66">
         <v>88.59</v>
@@ -3903,19 +3933,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J66" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K66">
         <v>3</v>
       </c>
       <c r="L66" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M66" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N66" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="O66">
         <v>18.08</v>
@@ -3941,10 +3971,10 @@
         <v>0.5</v>
       </c>
       <c r="F67" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G67" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H67">
         <v>1291.7</v>
@@ -3953,19 +3983,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J67" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K67">
         <v>3</v>
       </c>
       <c r="L67" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M67" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N67" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="O67">
         <v>18.08</v>
@@ -3991,10 +4021,10 @@
         <v>0.5</v>
       </c>
       <c r="F68" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G68" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H68">
         <v>1405.3</v>
@@ -4003,19 +4033,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J68" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K68">
         <v>4</v>
       </c>
       <c r="L68" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M68" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N68" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="O68">
         <v>18.08</v>
@@ -4041,10 +4071,10 @@
         <v>0.5</v>
       </c>
       <c r="F69" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G69" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H69">
         <v>125.89</v>
@@ -4053,19 +4083,19 @@
         <v>6.799999999999997</v>
       </c>
       <c r="J69" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K69">
         <v>3</v>
       </c>
       <c r="L69" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M69" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N69" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="O69">
         <v>18.08</v>
@@ -4091,10 +4121,10 @@
         <v>0.5</v>
       </c>
       <c r="F70" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G70" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H70">
         <v>1190.45</v>
@@ -4103,19 +4133,19 @@
         <v>7.399999999999999</v>
       </c>
       <c r="J70" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K70">
         <v>3</v>
       </c>
       <c r="L70" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M70" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N70" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="O70">
         <v>18.08</v>
@@ -4141,10 +4171,10 @@
         <v>-3.1</v>
       </c>
       <c r="F71" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G71" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H71">
         <v>9700</v>
@@ -4153,19 +4183,19 @@
         <v>9.399999999999999</v>
       </c>
       <c r="J71" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K71">
         <v>9</v>
       </c>
       <c r="L71" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M71" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N71" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="O71">
         <v>18.08</v>
@@ -4191,10 +4221,10 @@
         <v>0.5</v>
       </c>
       <c r="F72" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G72" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H72">
         <v>319.85</v>
@@ -4203,19 +4233,19 @@
         <v>10.9</v>
       </c>
       <c r="J72" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K72">
         <v>9</v>
       </c>
       <c r="L72" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M72" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N72" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="O72">
         <v>18.08</v>
@@ -4241,10 +4271,10 @@
         <v>0.5</v>
       </c>
       <c r="F73" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G73" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H73">
         <v>2305.6</v>
@@ -4253,19 +4283,19 @@
         <v>11.2</v>
       </c>
       <c r="J73" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K73">
         <v>3</v>
       </c>
       <c r="L73" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M73" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N73" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="O73">
         <v>18.08</v>
@@ -4291,10 +4321,10 @@
         <v>0.5</v>
       </c>
       <c r="F74" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G74" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H74">
         <v>3703.3</v>
@@ -4303,19 +4333,19 @@
         <v>11.2</v>
       </c>
       <c r="J74" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K74">
         <v>3</v>
       </c>
       <c r="L74" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M74" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N74" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="O74">
         <v>18.08</v>
@@ -4341,10 +4371,10 @@
         <v>0.5</v>
       </c>
       <c r="F75" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G75" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H75">
         <v>4023.5</v>
@@ -4353,19 +4383,19 @@
         <v>12.8</v>
       </c>
       <c r="J75" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K75">
         <v>5</v>
       </c>
       <c r="L75" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M75" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N75" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="O75">
         <v>18.08</v>
@@ -4391,10 +4421,10 @@
         <v>0</v>
       </c>
       <c r="F76" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G76" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H76">
         <v>7196</v>
@@ -4403,19 +4433,19 @@
         <v>13.2</v>
       </c>
       <c r="J76" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K76">
         <v>1</v>
       </c>
       <c r="L76" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M76" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N76" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="O76">
         <v>18.08</v>
@@ -4441,10 +4471,10 @@
         <v>0.5</v>
       </c>
       <c r="F77" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G77" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H77">
         <v>125</v>
@@ -4453,19 +4483,19 @@
         <v>14.1</v>
       </c>
       <c r="J77" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K77">
         <v>3</v>
       </c>
       <c r="L77" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M77" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N77" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="O77">
         <v>18.08</v>
@@ -4491,10 +4521,10 @@
         <v>0</v>
       </c>
       <c r="F78" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G78" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H78">
         <v>1449.1</v>
@@ -4506,13 +4536,13 @@
         <v>1</v>
       </c>
       <c r="L78" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="M78" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N78" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O78">
         <v>18.3</v>
@@ -4538,10 +4568,10 @@
         <v>0</v>
       </c>
       <c r="F79" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G79" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H79">
         <v>3844.3</v>
@@ -4553,13 +4583,13 @@
         <v>1</v>
       </c>
       <c r="L79" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="M79" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N79" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O79">
         <v>18.3</v>
@@ -4585,10 +4615,10 @@
         <v>0</v>
       </c>
       <c r="F80" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G80" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H80">
         <v>1330.5</v>
@@ -4600,13 +4630,13 @@
         <v>1</v>
       </c>
       <c r="L80" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="M80" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N80" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O80">
         <v>18.3</v>
@@ -4632,10 +4662,10 @@
         <v>0</v>
       </c>
       <c r="F81" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G81" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H81">
         <v>405.4</v>
@@ -4647,13 +4677,13 @@
         <v>1</v>
       </c>
       <c r="L81" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="M81" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N81" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O81">
         <v>18.3</v>
@@ -4679,10 +4709,10 @@
         <v>0</v>
       </c>
       <c r="F82" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G82" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H82">
         <v>554.7</v>
@@ -4691,19 +4721,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J82" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K82">
         <v>1</v>
       </c>
       <c r="L82" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M82" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N82" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O82">
         <v>18.3</v>
@@ -4729,10 +4759,10 @@
         <v>0</v>
       </c>
       <c r="F83" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G83" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H83">
         <v>215.65</v>
@@ -4741,19 +4771,19 @@
         <v>1</v>
       </c>
       <c r="J83" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K83">
         <v>4</v>
       </c>
       <c r="L83" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M83" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N83" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O83">
         <v>18.3</v>
@@ -4779,10 +4809,10 @@
         <v>-2.4</v>
       </c>
       <c r="F84" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G84" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H84">
         <v>1379.6</v>
@@ -4791,19 +4821,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J84" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K84">
         <v>10</v>
       </c>
       <c r="L84" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M84" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N84" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O84">
         <v>18.3</v>
@@ -4829,10 +4859,10 @@
         <v>0</v>
       </c>
       <c r="F85" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G85" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H85">
         <v>4454.6</v>
@@ -4841,19 +4871,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J85" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K85">
         <v>10</v>
       </c>
       <c r="L85" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M85" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N85" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O85">
         <v>18.3</v>
@@ -4879,10 +4909,10 @@
         <v>0</v>
       </c>
       <c r="F86" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G86" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H86">
         <v>1044.55</v>
@@ -4891,19 +4921,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J86" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K86">
         <v>10</v>
       </c>
       <c r="L86" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M86" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N86" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O86">
         <v>18.3</v>
@@ -4929,10 +4959,10 @@
         <v>0</v>
       </c>
       <c r="F87" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G87" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H87">
         <v>88.59</v>
@@ -4941,19 +4971,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J87" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K87">
         <v>4</v>
       </c>
       <c r="L87" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M87" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N87" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O87">
         <v>18.3</v>
@@ -4979,10 +5009,10 @@
         <v>0</v>
       </c>
       <c r="F88" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G88" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H88">
         <v>556.95</v>
@@ -4991,19 +5021,19 @@
         <v>4.799999999999997</v>
       </c>
       <c r="J88" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="K88">
         <v>1</v>
       </c>
       <c r="L88" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M88" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N88" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O88">
         <v>18.3</v>
@@ -5029,10 +5059,10 @@
         <v>0</v>
       </c>
       <c r="F89" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G89" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H89">
         <v>1395.8</v>
@@ -5041,19 +5071,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J89" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K89">
         <v>5</v>
       </c>
       <c r="L89" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M89" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N89" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O89">
         <v>18.3</v>
@@ -5079,10 +5109,10 @@
         <v>0</v>
       </c>
       <c r="F90" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G90" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H90">
         <v>5977</v>
@@ -5091,19 +5121,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J90" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K90">
         <v>1</v>
       </c>
       <c r="L90" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M90" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N90" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O90">
         <v>18.3</v>
@@ -5129,10 +5159,10 @@
         <v>1</v>
       </c>
       <c r="F91" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G91" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H91">
         <v>1198.95</v>
@@ -5141,19 +5171,19 @@
         <v>6.399999999999999</v>
       </c>
       <c r="J91" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K91">
         <v>4</v>
       </c>
       <c r="L91" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M91" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N91" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O91">
         <v>18.3</v>
@@ -5179,10 +5209,10 @@
         <v>-6</v>
       </c>
       <c r="F92" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G92" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H92">
         <v>1278.6</v>
@@ -5191,19 +5221,19 @@
         <v>8.899999999999999</v>
       </c>
       <c r="J92" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K92">
         <v>4</v>
       </c>
       <c r="L92" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M92" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N92" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O92">
         <v>18.3</v>
@@ -5229,10 +5259,10 @@
         <v>0</v>
       </c>
       <c r="F93" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G93" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H93">
         <v>9602</v>
@@ -5241,19 +5271,19 @@
         <v>9.399999999999999</v>
       </c>
       <c r="J93" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K93">
         <v>10</v>
       </c>
       <c r="L93" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M93" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N93" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O93">
         <v>18.3</v>
@@ -5279,10 +5309,10 @@
         <v>0</v>
       </c>
       <c r="F94" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G94" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H94">
         <v>319.75</v>
@@ -5291,19 +5321,19 @@
         <v>10.9</v>
       </c>
       <c r="J94" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K94">
         <v>10</v>
       </c>
       <c r="L94" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M94" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N94" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O94">
         <v>18.3</v>
@@ -5329,10 +5359,10 @@
         <v>0</v>
       </c>
       <c r="F95" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G95" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H95">
         <v>2307.9</v>
@@ -5341,19 +5371,19 @@
         <v>11.2</v>
       </c>
       <c r="J95" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K95">
         <v>4</v>
       </c>
       <c r="L95" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M95" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N95" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O95">
         <v>18.3</v>
@@ -5379,10 +5409,10 @@
         <v>0</v>
       </c>
       <c r="F96" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G96" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H96">
         <v>4021.1</v>
@@ -5391,19 +5421,19 @@
         <v>12.8</v>
       </c>
       <c r="J96" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K96">
         <v>6</v>
       </c>
       <c r="L96" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M96" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N96" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O96">
         <v>18.3</v>
@@ -5429,10 +5459,10 @@
         <v>0</v>
       </c>
       <c r="F97" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G97" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H97">
         <v>7230</v>
@@ -5441,19 +5471,19 @@
         <v>13.2</v>
       </c>
       <c r="J97" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K97">
         <v>2</v>
       </c>
       <c r="L97" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M97" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N97" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O97">
         <v>18.3</v>
@@ -5479,10 +5509,10 @@
         <v>0</v>
       </c>
       <c r="F98" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G98" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H98">
         <v>3844.3</v>
@@ -5494,13 +5524,13 @@
         <v>1</v>
       </c>
       <c r="L98" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="M98" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N98" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O98">
         <v>18.3</v>
@@ -5526,10 +5556,10 @@
         <v>0</v>
       </c>
       <c r="F99" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G99" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H99">
         <v>1330.5</v>
@@ -5538,19 +5568,19 @@
         <v>0.09999999999999432</v>
       </c>
       <c r="J99" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="K99">
         <v>1</v>
       </c>
       <c r="L99" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M99" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N99" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O99">
         <v>18.3</v>
@@ -5576,10 +5606,10 @@
         <v>0</v>
       </c>
       <c r="F100" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G100" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H100">
         <v>405.4</v>
@@ -5588,19 +5618,19 @@
         <v>0.7000000000000028</v>
       </c>
       <c r="J100" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K100">
         <v>1</v>
       </c>
       <c r="L100" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M100" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N100" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O100">
         <v>18.3</v>
@@ -5626,10 +5656,10 @@
         <v>-1.2</v>
       </c>
       <c r="F101" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G101" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H101">
         <v>554.7</v>
@@ -5638,19 +5668,19 @@
         <v>1.599999999999994</v>
       </c>
       <c r="J101" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K101">
         <v>2</v>
       </c>
       <c r="L101" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M101" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N101" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O101">
         <v>18.3</v>
@@ -5676,10 +5706,10 @@
         <v>-1.2</v>
       </c>
       <c r="F102" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G102" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H102">
         <v>215.65</v>
@@ -5688,19 +5718,19 @@
         <v>2.200000000000003</v>
       </c>
       <c r="J102" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K102">
         <v>5</v>
       </c>
       <c r="L102" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M102" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N102" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O102">
         <v>18.3</v>
@@ -5726,10 +5756,10 @@
         <v>-1.2</v>
       </c>
       <c r="F103" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G103" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H103">
         <v>1379.6</v>
@@ -5738,19 +5768,19 @@
         <v>4</v>
       </c>
       <c r="J103" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K103">
         <v>11</v>
       </c>
       <c r="L103" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M103" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N103" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O103">
         <v>18.3</v>
@@ -5776,10 +5806,10 @@
         <v>-1.2</v>
       </c>
       <c r="F104" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G104" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H104">
         <v>4454.6</v>
@@ -5788,19 +5818,19 @@
         <v>4</v>
       </c>
       <c r="J104" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K104">
         <v>11</v>
       </c>
       <c r="L104" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M104" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N104" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O104">
         <v>18.3</v>
@@ -5826,10 +5856,10 @@
         <v>-1.2</v>
       </c>
       <c r="F105" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G105" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H105">
         <v>1044.55</v>
@@ -5838,19 +5868,19 @@
         <v>4</v>
       </c>
       <c r="J105" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K105">
         <v>11</v>
       </c>
       <c r="L105" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M105" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N105" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O105">
         <v>18.3</v>
@@ -5876,10 +5906,10 @@
         <v>-1.2</v>
       </c>
       <c r="F106" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G106" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H106">
         <v>88.59</v>
@@ -5888,19 +5918,19 @@
         <v>4</v>
       </c>
       <c r="J106" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K106">
         <v>5</v>
       </c>
       <c r="L106" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M106" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N106" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O106">
         <v>18.3</v>
@@ -5926,10 +5956,10 @@
         <v>-1.2</v>
       </c>
       <c r="F107" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G107" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H107">
         <v>556.95</v>
@@ -5938,19 +5968,19 @@
         <v>6</v>
       </c>
       <c r="J107" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="K107">
         <v>2</v>
       </c>
       <c r="L107" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M107" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N107" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O107">
         <v>18.3</v>
@@ -5976,10 +6006,10 @@
         <v>-1.2</v>
       </c>
       <c r="F108" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G108" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H108">
         <v>1395.8</v>
@@ -5988,19 +6018,19 @@
         <v>6.600000000000001</v>
       </c>
       <c r="J108" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K108">
         <v>6</v>
       </c>
       <c r="L108" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M108" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N108" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O108">
         <v>18.3</v>
@@ -6026,10 +6056,10 @@
         <v>-1.2</v>
       </c>
       <c r="F109" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G109" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H109">
         <v>5977</v>
@@ -6038,19 +6068,19 @@
         <v>6.600000000000001</v>
       </c>
       <c r="J109" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K109">
         <v>2</v>
       </c>
       <c r="L109" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M109" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N109" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O109">
         <v>18.3</v>
@@ -6076,10 +6106,10 @@
         <v>-1.2</v>
       </c>
       <c r="F110" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G110" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H110">
         <v>1198.95</v>
@@ -6088,19 +6118,19 @@
         <v>7.600000000000001</v>
       </c>
       <c r="J110" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K110">
         <v>5</v>
       </c>
       <c r="L110" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M110" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N110" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O110">
         <v>18.3</v>
@@ -6126,10 +6156,10 @@
         <v>-1.2</v>
       </c>
       <c r="F111" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G111" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H111">
         <v>1278.6</v>
@@ -6138,19 +6168,19 @@
         <v>10.1</v>
       </c>
       <c r="J111" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K111">
         <v>5</v>
       </c>
       <c r="L111" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M111" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N111" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O111">
         <v>18.3</v>
@@ -6176,10 +6206,10 @@
         <v>-1.2</v>
       </c>
       <c r="F112" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G112" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H112">
         <v>9602</v>
@@ -6188,19 +6218,19 @@
         <v>10.6</v>
       </c>
       <c r="J112" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K112">
         <v>11</v>
       </c>
       <c r="L112" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M112" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N112" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O112">
         <v>18.3</v>
@@ -6226,10 +6256,10 @@
         <v>-1.2</v>
       </c>
       <c r="F113" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G113" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H113">
         <v>319.75</v>
@@ -6238,19 +6268,19 @@
         <v>12.1</v>
       </c>
       <c r="J113" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K113">
         <v>11</v>
       </c>
       <c r="L113" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M113" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N113" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O113">
         <v>18.3</v>
@@ -6276,10 +6306,10 @@
         <v>-1.2</v>
       </c>
       <c r="F114" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G114" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H114">
         <v>2307.9</v>
@@ -6288,19 +6318,19 @@
         <v>12.4</v>
       </c>
       <c r="J114" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K114">
         <v>5</v>
       </c>
       <c r="L114" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M114" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N114" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O114">
         <v>18.3</v>
@@ -6326,10 +6356,10 @@
         <v>-1.2</v>
       </c>
       <c r="F115" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G115" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H115">
         <v>4021.1</v>
@@ -6338,19 +6368,19 @@
         <v>14</v>
       </c>
       <c r="J115" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K115">
         <v>7</v>
       </c>
       <c r="L115" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M115" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N115" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O115">
         <v>18.3</v>
@@ -6376,10 +6406,10 @@
         <v>-1.2</v>
       </c>
       <c r="F116" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G116" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H116">
         <v>7230</v>
@@ -6388,19 +6418,19 @@
         <v>14.4</v>
       </c>
       <c r="J116" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K116">
         <v>3</v>
       </c>
       <c r="L116" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M116" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N116" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="O116">
         <v>18.3</v>
@@ -6426,10 +6456,10 @@
         <v>6.5</v>
       </c>
       <c r="F117" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G117" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H117">
         <v>1263</v>
@@ -6438,19 +6468,19 @@
         <v>3.599999999999994</v>
       </c>
       <c r="J117" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K117">
         <v>6</v>
       </c>
       <c r="L117" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M117" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N117" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O117">
         <v>18.7</v>
@@ -6476,10 +6506,10 @@
         <v>0</v>
       </c>
       <c r="F118" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G118" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H118">
         <v>123.95</v>
@@ -6488,19 +6518,19 @@
         <v>5.5</v>
       </c>
       <c r="J118" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K118">
         <v>1</v>
       </c>
       <c r="L118" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M118" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N118" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O118">
         <v>18.7</v>
@@ -6526,10 +6556,10 @@
         <v>-2</v>
       </c>
       <c r="F119" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G119" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H119">
         <v>1371.6</v>
@@ -6538,19 +6568,19 @@
         <v>6</v>
       </c>
       <c r="J119" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K119">
         <v>12</v>
       </c>
       <c r="L119" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M119" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N119" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O119">
         <v>18.7</v>
@@ -6576,10 +6606,10 @@
         <v>-2</v>
       </c>
       <c r="F120" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G120" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H120">
         <v>4460</v>
@@ -6588,19 +6618,19 @@
         <v>6</v>
       </c>
       <c r="J120" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K120">
         <v>12</v>
       </c>
       <c r="L120" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M120" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N120" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O120">
         <v>18.7</v>
@@ -6626,10 +6656,10 @@
         <v>6.4</v>
       </c>
       <c r="F121" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G121" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H121">
         <v>2358.2</v>
@@ -6638,19 +6668,19 @@
         <v>6</v>
       </c>
       <c r="J121" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K121">
         <v>6</v>
       </c>
       <c r="L121" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M121" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N121" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O121">
         <v>18.7</v>
@@ -6676,10 +6706,10 @@
         <v>-5.4</v>
       </c>
       <c r="F122" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G122" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H122">
         <v>402.65</v>
@@ -6688,19 +6718,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J122" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K122">
         <v>2</v>
       </c>
       <c r="L122" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M122" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N122" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O122">
         <v>18.7</v>
@@ -6726,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="F123" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G123" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H123">
         <v>3858.9</v>
@@ -6738,19 +6768,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J123" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K123">
         <v>1</v>
       </c>
       <c r="L123" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M123" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N123" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O123">
         <v>18.7</v>
@@ -6776,10 +6806,10 @@
         <v>4</v>
       </c>
       <c r="F124" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G124" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H124">
         <v>320.55</v>
@@ -6788,19 +6818,19 @@
         <v>8.100000000000001</v>
       </c>
       <c r="J124" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K124">
         <v>12</v>
       </c>
       <c r="L124" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M124" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N124" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O124">
         <v>18.7</v>
@@ -6826,10 +6856,10 @@
         <v>-6.4</v>
       </c>
       <c r="F125" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G125" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H125">
         <v>214.68</v>
@@ -6838,19 +6868,19 @@
         <v>8.600000000000001</v>
       </c>
       <c r="J125" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K125">
         <v>6</v>
       </c>
       <c r="L125" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M125" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N125" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O125">
         <v>18.7</v>
@@ -6876,10 +6906,10 @@
         <v>-5</v>
       </c>
       <c r="F126" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G126" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H126">
         <v>1019.75</v>
@@ -6888,19 +6918,19 @@
         <v>9</v>
       </c>
       <c r="J126" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K126">
         <v>12</v>
       </c>
       <c r="L126" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M126" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N126" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O126">
         <v>18.7</v>
@@ -6926,10 +6956,10 @@
         <v>-5</v>
       </c>
       <c r="F127" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G127" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H127">
         <v>86.98</v>
@@ -6938,19 +6968,19 @@
         <v>9</v>
       </c>
       <c r="J127" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K127">
         <v>6</v>
       </c>
       <c r="L127" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M127" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N127" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O127">
         <v>18.7</v>
@@ -6976,10 +7006,10 @@
         <v>0</v>
       </c>
       <c r="F128" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G128" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H128">
         <v>125.61</v>
@@ -6988,19 +7018,19 @@
         <v>10</v>
       </c>
       <c r="J128" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K128">
         <v>1</v>
       </c>
       <c r="L128" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M128" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N128" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O128">
         <v>18.7</v>
@@ -7026,10 +7056,10 @@
         <v>-4</v>
       </c>
       <c r="F129" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G129" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H129">
         <v>1404.6</v>
@@ -7038,19 +7068,19 @@
         <v>10.6</v>
       </c>
       <c r="J129" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K129">
         <v>7</v>
       </c>
       <c r="L129" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M129" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N129" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O129">
         <v>18.7</v>
@@ -7076,10 +7106,10 @@
         <v>-3</v>
       </c>
       <c r="F130" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G130" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H130">
         <v>1217.2</v>
@@ -7088,19 +7118,19 @@
         <v>10.6</v>
       </c>
       <c r="J130" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K130">
         <v>6</v>
       </c>
       <c r="L130" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M130" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N130" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O130">
         <v>18.7</v>
@@ -7126,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="F131" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G131" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H131">
         <v>445.5</v>
@@ -7138,19 +7168,19 @@
         <v>12.7</v>
       </c>
       <c r="J131" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="K131">
         <v>1</v>
       </c>
       <c r="L131" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M131" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N131" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O131">
         <v>18.7</v>
@@ -7176,10 +7206,10 @@
         <v>-3.8</v>
       </c>
       <c r="F132" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G132" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H132">
         <v>9519</v>
@@ -7188,19 +7218,19 @@
         <v>14.4</v>
       </c>
       <c r="J132" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K132">
         <v>12</v>
       </c>
       <c r="L132" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M132" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N132" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O132">
         <v>18.7</v>
@@ -7226,10 +7256,10 @@
         <v>0</v>
       </c>
       <c r="F133" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G133" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H133">
         <v>1263.2</v>
@@ -7238,19 +7268,19 @@
         <v>3.599999999999994</v>
       </c>
       <c r="J133" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K133">
         <v>7</v>
       </c>
       <c r="L133" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M133" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N133" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O133">
         <v>18.84</v>
@@ -7276,10 +7306,10 @@
         <v>0</v>
       </c>
       <c r="F134" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G134" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H134">
         <v>124.1</v>
@@ -7288,19 +7318,19 @@
         <v>5.5</v>
       </c>
       <c r="J134" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K134">
         <v>2</v>
       </c>
       <c r="L134" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M134" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N134" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O134">
         <v>18.84</v>
@@ -7326,10 +7356,10 @@
         <v>0</v>
       </c>
       <c r="F135" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G135" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H135">
         <v>1371.2</v>
@@ -7338,19 +7368,19 @@
         <v>6</v>
       </c>
       <c r="J135" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K135">
         <v>13</v>
       </c>
       <c r="L135" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M135" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N135" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O135">
         <v>18.84</v>
@@ -7376,10 +7406,10 @@
         <v>0</v>
       </c>
       <c r="F136" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G136" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H136">
         <v>4440.2</v>
@@ -7388,19 +7418,19 @@
         <v>6</v>
       </c>
       <c r="J136" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K136">
         <v>13</v>
       </c>
       <c r="L136" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M136" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N136" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O136">
         <v>18.84</v>
@@ -7426,10 +7456,10 @@
         <v>0</v>
       </c>
       <c r="F137" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G137" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H137">
         <v>2353.4</v>
@@ -7438,19 +7468,19 @@
         <v>6</v>
       </c>
       <c r="J137" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K137">
         <v>7</v>
       </c>
       <c r="L137" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M137" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N137" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O137">
         <v>18.84</v>
@@ -7476,10 +7506,10 @@
         <v>0</v>
       </c>
       <c r="F138" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G138" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H138">
         <v>400.9</v>
@@ -7488,19 +7518,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J138" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K138">
         <v>3</v>
       </c>
       <c r="L138" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M138" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N138" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O138">
         <v>18.84</v>
@@ -7526,10 +7556,10 @@
         <v>0</v>
       </c>
       <c r="F139" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G139" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H139">
         <v>3856.3</v>
@@ -7538,19 +7568,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J139" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K139">
         <v>2</v>
       </c>
       <c r="L139" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M139" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N139" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O139">
         <v>18.84</v>
@@ -7576,10 +7606,10 @@
         <v>0</v>
       </c>
       <c r="F140" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G140" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H140">
         <v>214.69</v>
@@ -7588,19 +7618,19 @@
         <v>8.600000000000001</v>
       </c>
       <c r="J140" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K140">
         <v>7</v>
       </c>
       <c r="L140" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M140" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N140" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O140">
         <v>18.84</v>
@@ -7626,10 +7656,10 @@
         <v>0</v>
       </c>
       <c r="F141" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G141" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H141">
         <v>1020.55</v>
@@ -7638,19 +7668,19 @@
         <v>9</v>
       </c>
       <c r="J141" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K141">
         <v>13</v>
       </c>
       <c r="L141" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M141" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N141" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O141">
         <v>18.84</v>
@@ -7676,10 +7706,10 @@
         <v>0</v>
       </c>
       <c r="F142" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G142" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H142">
         <v>87.06999999999999</v>
@@ -7688,19 +7718,19 @@
         <v>9</v>
       </c>
       <c r="J142" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K142">
         <v>7</v>
       </c>
       <c r="L142" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M142" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N142" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O142">
         <v>18.84</v>
@@ -7726,10 +7756,10 @@
         <v>0</v>
       </c>
       <c r="F143" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G143" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H143">
         <v>125.46</v>
@@ -7738,19 +7768,19 @@
         <v>10</v>
       </c>
       <c r="J143" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K143">
         <v>2</v>
       </c>
       <c r="L143" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M143" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N143" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O143">
         <v>18.84</v>
@@ -7776,10 +7806,10 @@
         <v>0</v>
       </c>
       <c r="F144" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G144" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H144">
         <v>1401.1</v>
@@ -7788,19 +7818,19 @@
         <v>10.6</v>
       </c>
       <c r="J144" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K144">
         <v>8</v>
       </c>
       <c r="L144" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M144" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N144" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O144">
         <v>18.84</v>
@@ -7826,10 +7856,10 @@
         <v>0</v>
       </c>
       <c r="F145" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G145" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H145">
         <v>1218.2</v>
@@ -7838,19 +7868,19 @@
         <v>10.6</v>
       </c>
       <c r="J145" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K145">
         <v>7</v>
       </c>
       <c r="L145" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M145" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N145" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O145">
         <v>18.84</v>
@@ -7876,10 +7906,10 @@
         <v>0</v>
       </c>
       <c r="F146" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G146" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H146">
         <v>445.65</v>
@@ -7888,19 +7918,19 @@
         <v>12.7</v>
       </c>
       <c r="J146" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="K146">
         <v>2</v>
       </c>
       <c r="L146" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M146" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N146" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O146">
         <v>18.84</v>
@@ -7926,10 +7956,10 @@
         <v>-6</v>
       </c>
       <c r="F147" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G147" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H147">
         <v>319.85</v>
@@ -7938,19 +7968,19 @@
         <v>14.1</v>
       </c>
       <c r="J147" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K147">
         <v>13</v>
       </c>
       <c r="L147" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M147" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N147" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O147">
         <v>18.84</v>
@@ -7976,10 +8006,10 @@
         <v>0</v>
       </c>
       <c r="F148" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G148" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H148">
         <v>9545.5</v>
@@ -7988,19 +8018,19 @@
         <v>14.4</v>
       </c>
       <c r="J148" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K148">
         <v>13</v>
       </c>
       <c r="L148" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M148" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N148" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O148">
         <v>18.84</v>
@@ -8026,10 +8056,10 @@
         <v>0.5</v>
       </c>
       <c r="F149" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G149" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H149">
         <v>1262.7</v>
@@ -8038,19 +8068,19 @@
         <v>3.099999999999994</v>
       </c>
       <c r="J149" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K149">
         <v>8</v>
       </c>
       <c r="L149" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M149" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N149" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O149">
         <v>18.44</v>
@@ -8076,10 +8106,10 @@
         <v>2.9</v>
       </c>
       <c r="F150" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G150" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H150">
         <v>404.6</v>
@@ -8088,19 +8118,19 @@
         <v>3.200000000000003</v>
       </c>
       <c r="J150" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K150">
         <v>4</v>
       </c>
       <c r="L150" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M150" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N150" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O150">
         <v>18.44</v>
@@ -8126,10 +8156,10 @@
         <v>0.5</v>
       </c>
       <c r="F151" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G151" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H151">
         <v>124.38</v>
@@ -8138,19 +8168,19 @@
         <v>5</v>
       </c>
       <c r="J151" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K151">
         <v>3</v>
       </c>
       <c r="L151" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M151" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N151" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O151">
         <v>18.44</v>
@@ -8176,10 +8206,10 @@
         <v>0.5</v>
       </c>
       <c r="F152" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G152" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H152">
         <v>1376.9</v>
@@ -8188,19 +8218,19 @@
         <v>5.5</v>
       </c>
       <c r="J152" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K152">
         <v>14</v>
       </c>
       <c r="L152" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M152" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N152" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O152">
         <v>18.44</v>
@@ -8226,10 +8256,10 @@
         <v>0.5</v>
       </c>
       <c r="F153" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G153" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H153">
         <v>4456.2</v>
@@ -8238,19 +8268,19 @@
         <v>5.5</v>
       </c>
       <c r="J153" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K153">
         <v>14</v>
       </c>
       <c r="L153" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M153" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N153" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O153">
         <v>18.44</v>
@@ -8276,10 +8306,10 @@
         <v>0.5</v>
       </c>
       <c r="F154" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G154" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H154">
         <v>2358.9</v>
@@ -8288,19 +8318,19 @@
         <v>5.5</v>
       </c>
       <c r="J154" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K154">
         <v>8</v>
       </c>
       <c r="L154" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M154" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N154" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O154">
         <v>18.44</v>
@@ -8326,10 +8356,10 @@
         <v>0.5</v>
       </c>
       <c r="F155" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G155" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H155">
         <v>3875.6</v>
@@ -8338,19 +8368,19 @@
         <v>5.599999999999994</v>
       </c>
       <c r="J155" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K155">
         <v>3</v>
       </c>
       <c r="L155" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M155" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N155" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O155">
         <v>18.44</v>
@@ -8376,10 +8406,10 @@
         <v>3.9</v>
       </c>
       <c r="F156" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G156" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H156">
         <v>1231.65</v>
@@ -8388,19 +8418,19 @@
         <v>6.700000000000003</v>
       </c>
       <c r="J156" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K156">
         <v>8</v>
       </c>
       <c r="L156" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M156" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N156" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O156">
         <v>18.44</v>
@@ -8426,10 +8456,10 @@
         <v>1.5</v>
       </c>
       <c r="F157" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G157" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H157">
         <v>215.19</v>
@@ -8438,19 +8468,19 @@
         <v>7.100000000000001</v>
       </c>
       <c r="J157" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K157">
         <v>8</v>
       </c>
       <c r="L157" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M157" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N157" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O157">
         <v>18.44</v>
@@ -8476,10 +8506,10 @@
         <v>0.5</v>
       </c>
       <c r="F158" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G158" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H158">
         <v>1016.45</v>
@@ -8488,19 +8518,19 @@
         <v>8.5</v>
       </c>
       <c r="J158" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K158">
         <v>14</v>
       </c>
       <c r="L158" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M158" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N158" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O158">
         <v>18.44</v>
@@ -8526,10 +8556,10 @@
         <v>0.5</v>
       </c>
       <c r="F159" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G159" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H159">
         <v>87.40000000000001</v>
@@ -8538,19 +8568,19 @@
         <v>8.5</v>
       </c>
       <c r="J159" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K159">
         <v>8</v>
       </c>
       <c r="L159" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M159" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N159" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O159">
         <v>18.44</v>
@@ -8576,10 +8606,10 @@
         <v>1.5</v>
       </c>
       <c r="F160" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G160" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H160">
         <v>1408.8</v>
@@ -8588,19 +8618,19 @@
         <v>9.100000000000001</v>
       </c>
       <c r="J160" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K160">
         <v>9</v>
       </c>
       <c r="L160" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M160" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N160" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O160">
         <v>18.44</v>
@@ -8626,10 +8656,10 @@
         <v>0.5</v>
       </c>
       <c r="F161" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G161" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H161">
         <v>125.82</v>
@@ -8638,19 +8668,19 @@
         <v>9.5</v>
       </c>
       <c r="J161" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K161">
         <v>3</v>
       </c>
       <c r="L161" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M161" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N161" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O161">
         <v>18.44</v>
@@ -8676,10 +8706,10 @@
         <v>0.5</v>
       </c>
       <c r="F162" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G162" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H162">
         <v>451.3</v>
@@ -8688,19 +8718,19 @@
         <v>12.2</v>
       </c>
       <c r="J162" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="K162">
         <v>3</v>
       </c>
       <c r="L162" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M162" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N162" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O162">
         <v>18.44</v>
@@ -8726,10 +8756,10 @@
         <v>0.5</v>
       </c>
       <c r="F163" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G163" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H163">
         <v>320.1</v>
@@ -8738,19 +8768,19 @@
         <v>13.6</v>
       </c>
       <c r="J163" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K163">
         <v>14</v>
       </c>
       <c r="L163" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M163" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N163" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O163">
         <v>18.44</v>
@@ -8776,10 +8806,10 @@
         <v>0.5</v>
       </c>
       <c r="F164" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G164" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H164">
         <v>9549.5</v>
@@ -8788,19 +8818,19 @@
         <v>13.9</v>
       </c>
       <c r="J164" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K164">
         <v>14</v>
       </c>
       <c r="L164" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M164" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N164" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="O164">
         <v>18.44</v>
@@ -8826,10 +8856,10 @@
         <v>0</v>
       </c>
       <c r="F165" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G165" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H165">
         <v>6727</v>
@@ -8841,13 +8871,13 @@
         <v>1</v>
       </c>
       <c r="L165" t="s">
-        <v>16</v>
+        <v>97</v>
       </c>
       <c r="M165" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N165" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O165">
         <v>18.59</v>
@@ -8873,10 +8903,10 @@
         <v>0</v>
       </c>
       <c r="F166" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G166" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H166">
         <v>4135.1</v>
@@ -8888,13 +8918,13 @@
         <v>1</v>
       </c>
       <c r="L166" t="s">
-        <v>16</v>
+        <v>97</v>
       </c>
       <c r="M166" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N166" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O166">
         <v>18.59</v>
@@ -8920,10 +8950,10 @@
         <v>0</v>
       </c>
       <c r="F167" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G167" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H167">
         <v>297</v>
@@ -8932,19 +8962,19 @@
         <v>0.7000000000000028</v>
       </c>
       <c r="J167" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K167">
         <v>1</v>
       </c>
       <c r="L167" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M167" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N167" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O167">
         <v>18.59</v>
@@ -8970,10 +9000,10 @@
         <v>0</v>
       </c>
       <c r="F168" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G168" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H168">
         <v>2335</v>
@@ -8982,19 +9012,19 @@
         <v>1.700000000000003</v>
       </c>
       <c r="J168" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K168">
         <v>1</v>
       </c>
       <c r="L168" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M168" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N168" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O168">
         <v>18.59</v>
@@ -9020,10 +9050,10 @@
         <v>0</v>
       </c>
       <c r="F169" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G169" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H169">
         <v>295.4</v>
@@ -9032,19 +9062,19 @@
         <v>3.599999999999994</v>
       </c>
       <c r="J169" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K169">
         <v>1</v>
       </c>
       <c r="L169" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M169" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N169" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O169">
         <v>18.59</v>
@@ -9070,10 +9100,10 @@
         <v>0</v>
       </c>
       <c r="F170" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G170" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H170">
         <v>1435.4</v>
@@ -9082,19 +9112,19 @@
         <v>3.700000000000003</v>
       </c>
       <c r="J170" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K170">
         <v>1</v>
       </c>
       <c r="L170" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M170" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N170" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O170">
         <v>18.59</v>
@@ -9120,10 +9150,10 @@
         <v>0</v>
       </c>
       <c r="F171" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G171" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H171">
         <v>1460.2</v>
@@ -9132,19 +9162,19 @@
         <v>4.599999999999994</v>
       </c>
       <c r="J171" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="K171">
         <v>1</v>
       </c>
       <c r="L171" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M171" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N171" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O171">
         <v>18.59</v>
@@ -9170,10 +9200,10 @@
         <v>-0.5</v>
       </c>
       <c r="F172" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G172" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H172">
         <v>1369.6</v>
@@ -9182,19 +9212,19 @@
         <v>6</v>
       </c>
       <c r="J172" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K172">
         <v>15</v>
       </c>
       <c r="L172" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M172" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N172" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O172">
         <v>18.59</v>
@@ -9220,10 +9250,10 @@
         <v>-0.5</v>
       </c>
       <c r="F173" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G173" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H173">
         <v>4456.5</v>
@@ -9232,19 +9262,19 @@
         <v>6</v>
       </c>
       <c r="J173" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K173">
         <v>15</v>
       </c>
       <c r="L173" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M173" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N173" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O173">
         <v>18.59</v>
@@ -9270,10 +9300,10 @@
         <v>-2.9</v>
       </c>
       <c r="F174" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G174" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H174">
         <v>402.25</v>
@@ -9282,19 +9312,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J174" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K174">
         <v>5</v>
       </c>
       <c r="L174" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M174" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N174" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O174">
         <v>18.59</v>
@@ -9320,10 +9350,10 @@
         <v>0</v>
       </c>
       <c r="F175" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G175" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H175">
         <v>2022.9</v>
@@ -9332,19 +9362,19 @@
         <v>8.5</v>
       </c>
       <c r="J175" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K175">
         <v>1</v>
       </c>
       <c r="L175" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M175" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N175" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O175">
         <v>18.59</v>
@@ -9370,10 +9400,10 @@
         <v>0.5</v>
       </c>
       <c r="F176" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G176" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H176">
         <v>1410.5</v>
@@ -9382,19 +9412,19 @@
         <v>8.600000000000001</v>
       </c>
       <c r="J176" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K176">
         <v>10</v>
       </c>
       <c r="L176" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M176" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N176" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O176">
         <v>18.59</v>
@@ -9420,10 +9450,10 @@
         <v>0</v>
       </c>
       <c r="F177" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G177" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H177">
         <v>1056.25</v>
@@ -9432,19 +9462,19 @@
         <v>8.600000000000001</v>
       </c>
       <c r="J177" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K177">
         <v>1</v>
       </c>
       <c r="L177" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M177" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N177" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O177">
         <v>18.59</v>
@@ -9470,10 +9500,10 @@
         <v>0</v>
       </c>
       <c r="F178" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G178" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H178">
         <v>187.01</v>
@@ -9482,19 +9512,19 @@
         <v>9.100000000000001</v>
       </c>
       <c r="J178" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K178">
         <v>1</v>
       </c>
       <c r="L178" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M178" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N178" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O178">
         <v>18.59</v>
@@ -9520,10 +9550,10 @@
         <v>0</v>
       </c>
       <c r="F179" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G179" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H179">
         <v>180.18</v>
@@ -9532,19 +9562,19 @@
         <v>10.6</v>
       </c>
       <c r="J179" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K179">
         <v>1</v>
       </c>
       <c r="L179" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M179" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N179" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O179">
         <v>18.59</v>
@@ -9570,10 +9600,10 @@
         <v>0</v>
       </c>
       <c r="F180" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G180" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H180">
         <v>243.68</v>
@@ -9582,19 +9612,19 @@
         <v>10.6</v>
       </c>
       <c r="J180" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K180">
         <v>1</v>
       </c>
       <c r="L180" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M180" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N180" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O180">
         <v>18.59</v>
@@ -9620,10 +9650,10 @@
         <v>-0.5</v>
       </c>
       <c r="F181" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G181" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H181">
         <v>450.65</v>
@@ -9632,19 +9662,19 @@
         <v>12.7</v>
       </c>
       <c r="J181" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="K181">
         <v>4</v>
       </c>
       <c r="L181" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M181" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N181" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O181">
         <v>18.59</v>
@@ -9670,10 +9700,10 @@
         <v>0</v>
       </c>
       <c r="F182" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G182" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H182">
         <v>97.75</v>
@@ -9682,19 +9712,19 @@
         <v>13.1</v>
       </c>
       <c r="J182" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K182">
         <v>1</v>
       </c>
       <c r="L182" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M182" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N182" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O182">
         <v>18.59</v>
@@ -9720,10 +9750,10 @@
         <v>0.5</v>
       </c>
       <c r="F183" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G183" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H183">
         <v>9550.5</v>
@@ -9732,19 +9762,19 @@
         <v>13.4</v>
       </c>
       <c r="J183" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K183">
         <v>15</v>
       </c>
       <c r="L183" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M183" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N183" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O183">
         <v>18.59</v>
@@ -9770,10 +9800,10 @@
         <v>-0.5</v>
       </c>
       <c r="F184" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G184" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H184">
         <v>319.15</v>
@@ -9782,19 +9812,19 @@
         <v>14.1</v>
       </c>
       <c r="J184" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K184">
         <v>15</v>
       </c>
       <c r="L184" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M184" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N184" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O184">
         <v>18.59</v>
@@ -9804,8 +9834,8 @@
       </c>
     </row>
     <row r="185" spans="1:16">
-      <c r="A185" t="s">
-        <v>16</v>
+      <c r="A185">
+        <v>20260423</v>
       </c>
       <c r="B185" t="s">
         <v>57</v>
@@ -9816,14 +9846,14 @@
       <c r="D185">
         <v>78.8</v>
       </c>
-      <c r="E185" t="s">
-        <v>72</v>
+      <c r="E185">
+        <v>0</v>
       </c>
       <c r="F185" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G185" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H185">
         <v>6727</v>
@@ -9835,13 +9865,13 @@
         <v>1</v>
       </c>
       <c r="L185" t="s">
-        <v>16</v>
+        <v>97</v>
       </c>
       <c r="M185" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N185" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O185">
         <v>18.59</v>
@@ -9851,8 +9881,8 @@
       </c>
     </row>
     <row r="186" spans="1:16">
-      <c r="A186" t="s">
-        <v>16</v>
+      <c r="A186">
+        <v>20260423</v>
       </c>
       <c r="B186" t="s">
         <v>58</v>
@@ -9863,14 +9893,14 @@
       <c r="D186">
         <v>75.8</v>
       </c>
-      <c r="E186" t="s">
-        <v>72</v>
+      <c r="E186">
+        <v>0</v>
       </c>
       <c r="F186" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G186" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H186">
         <v>4135.1</v>
@@ -9882,13 +9912,13 @@
         <v>1</v>
       </c>
       <c r="L186" t="s">
-        <v>16</v>
+        <v>97</v>
       </c>
       <c r="M186" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N186" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O186">
         <v>18.59</v>
@@ -9898,8 +9928,8 @@
       </c>
     </row>
     <row r="187" spans="1:16">
-      <c r="A187" t="s">
-        <v>16</v>
+      <c r="A187">
+        <v>20260423</v>
       </c>
       <c r="B187" t="s">
         <v>59</v>
@@ -9910,14 +9940,14 @@
       <c r="D187">
         <v>69.3</v>
       </c>
-      <c r="E187" t="s">
-        <v>72</v>
+      <c r="E187">
+        <v>0</v>
       </c>
       <c r="F187" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G187" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H187">
         <v>297</v>
@@ -9926,19 +9956,19 @@
         <v>0.7000000000000028</v>
       </c>
       <c r="J187" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K187">
         <v>2</v>
       </c>
       <c r="L187" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M187" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N187" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O187">
         <v>18.59</v>
@@ -9948,8 +9978,8 @@
       </c>
     </row>
     <row r="188" spans="1:16">
-      <c r="A188" t="s">
-        <v>16</v>
+      <c r="A188">
+        <v>20260423</v>
       </c>
       <c r="B188" t="s">
         <v>60</v>
@@ -9960,14 +9990,14 @@
       <c r="D188">
         <v>68.3</v>
       </c>
-      <c r="E188" t="s">
-        <v>72</v>
+      <c r="E188">
+        <v>0</v>
       </c>
       <c r="F188" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G188" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H188">
         <v>2335</v>
@@ -9976,19 +10006,19 @@
         <v>1.700000000000003</v>
       </c>
       <c r="J188" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K188">
         <v>2</v>
       </c>
       <c r="L188" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M188" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N188" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O188">
         <v>18.59</v>
@@ -9998,8 +10028,8 @@
       </c>
     </row>
     <row r="189" spans="1:16">
-      <c r="A189" t="s">
-        <v>16</v>
+      <c r="A189">
+        <v>20260423</v>
       </c>
       <c r="B189" t="s">
         <v>61</v>
@@ -10010,14 +10040,14 @@
       <c r="D189">
         <v>66.40000000000001</v>
       </c>
-      <c r="E189" t="s">
-        <v>72</v>
+      <c r="E189">
+        <v>0</v>
       </c>
       <c r="F189" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G189" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H189">
         <v>295.4</v>
@@ -10026,19 +10056,19 @@
         <v>3.599999999999994</v>
       </c>
       <c r="J189" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K189">
         <v>2</v>
       </c>
       <c r="L189" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M189" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N189" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O189">
         <v>18.59</v>
@@ -10048,8 +10078,8 @@
       </c>
     </row>
     <row r="190" spans="1:16">
-      <c r="A190" t="s">
-        <v>16</v>
+      <c r="A190">
+        <v>20260423</v>
       </c>
       <c r="B190" t="s">
         <v>62</v>
@@ -10060,14 +10090,14 @@
       <c r="D190">
         <v>66.3</v>
       </c>
-      <c r="E190" t="s">
-        <v>72</v>
+      <c r="E190">
+        <v>0</v>
       </c>
       <c r="F190" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G190" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H190">
         <v>1435.4</v>
@@ -10076,19 +10106,19 @@
         <v>3.700000000000003</v>
       </c>
       <c r="J190" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K190">
         <v>2</v>
       </c>
       <c r="L190" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M190" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N190" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O190">
         <v>18.59</v>
@@ -10098,8 +10128,8 @@
       </c>
     </row>
     <row r="191" spans="1:16">
-      <c r="A191" t="s">
-        <v>16</v>
+      <c r="A191">
+        <v>20260423</v>
       </c>
       <c r="B191" t="s">
         <v>63</v>
@@ -10110,14 +10140,14 @@
       <c r="D191">
         <v>65.40000000000001</v>
       </c>
-      <c r="E191" t="s">
-        <v>72</v>
+      <c r="E191">
+        <v>0</v>
       </c>
       <c r="F191" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G191" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H191">
         <v>1460.2</v>
@@ -10126,19 +10156,19 @@
         <v>4.599999999999994</v>
       </c>
       <c r="J191" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="K191">
         <v>2</v>
       </c>
       <c r="L191" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M191" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N191" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O191">
         <v>18.59</v>
@@ -10148,8 +10178,8 @@
       </c>
     </row>
     <row r="192" spans="1:16">
-      <c r="A192" t="s">
-        <v>16</v>
+      <c r="A192">
+        <v>20260423</v>
       </c>
       <c r="B192" t="s">
         <v>22</v>
@@ -10160,14 +10190,14 @@
       <c r="D192">
         <v>64</v>
       </c>
-      <c r="E192" t="s">
-        <v>72</v>
+      <c r="E192">
+        <v>0</v>
       </c>
       <c r="F192" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G192" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H192">
         <v>1369.6</v>
@@ -10176,19 +10206,19 @@
         <v>6</v>
       </c>
       <c r="J192" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K192">
         <v>16</v>
       </c>
       <c r="L192" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M192" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N192" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O192">
         <v>18.59</v>
@@ -10198,8 +10228,8 @@
       </c>
     </row>
     <row r="193" spans="1:16">
-      <c r="A193" t="s">
-        <v>16</v>
+      <c r="A193">
+        <v>20260423</v>
       </c>
       <c r="B193" t="s">
         <v>23</v>
@@ -10210,14 +10240,14 @@
       <c r="D193">
         <v>64</v>
       </c>
-      <c r="E193" t="s">
-        <v>72</v>
+      <c r="E193">
+        <v>0</v>
       </c>
       <c r="F193" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G193" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H193">
         <v>4456.5</v>
@@ -10226,19 +10256,19 @@
         <v>6</v>
       </c>
       <c r="J193" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K193">
         <v>16</v>
       </c>
       <c r="L193" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M193" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N193" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O193">
         <v>18.59</v>
@@ -10248,8 +10278,8 @@
       </c>
     </row>
     <row r="194" spans="1:16">
-      <c r="A194" t="s">
-        <v>16</v>
+      <c r="A194">
+        <v>20260423</v>
       </c>
       <c r="B194" t="s">
         <v>39</v>
@@ -10260,14 +10290,14 @@
       <c r="D194">
         <v>63.9</v>
       </c>
-      <c r="E194" t="s">
-        <v>72</v>
+      <c r="E194">
+        <v>0</v>
       </c>
       <c r="F194" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G194" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H194">
         <v>402.25</v>
@@ -10276,19 +10306,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J194" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K194">
         <v>6</v>
       </c>
       <c r="L194" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="M194" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N194" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O194">
         <v>18.59</v>
@@ -10298,8 +10328,8 @@
       </c>
     </row>
     <row r="195" spans="1:16">
-      <c r="A195" t="s">
-        <v>16</v>
+      <c r="A195">
+        <v>20260423</v>
       </c>
       <c r="B195" t="s">
         <v>64</v>
@@ -10310,14 +10340,14 @@
       <c r="D195">
         <v>61.5</v>
       </c>
-      <c r="E195" t="s">
-        <v>72</v>
+      <c r="E195">
+        <v>0</v>
       </c>
       <c r="F195" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G195" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H195">
         <v>2022.9</v>
@@ -10326,19 +10356,19 @@
         <v>8.5</v>
       </c>
       <c r="J195" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K195">
         <v>2</v>
       </c>
       <c r="L195" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M195" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N195" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O195">
         <v>18.59</v>
@@ -10348,8 +10378,8 @@
       </c>
     </row>
     <row r="196" spans="1:16">
-      <c r="A196" t="s">
-        <v>16</v>
+      <c r="A196">
+        <v>20260423</v>
       </c>
       <c r="B196" t="s">
         <v>32</v>
@@ -10360,14 +10390,14 @@
       <c r="D196">
         <v>61.4</v>
       </c>
-      <c r="E196" t="s">
-        <v>72</v>
+      <c r="E196">
+        <v>0</v>
       </c>
       <c r="F196" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G196" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H196">
         <v>1410.5</v>
@@ -10376,19 +10406,19 @@
         <v>8.600000000000001</v>
       </c>
       <c r="J196" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K196">
         <v>11</v>
       </c>
       <c r="L196" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="M196" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N196" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O196">
         <v>18.59</v>
@@ -10398,8 +10428,8 @@
       </c>
     </row>
     <row r="197" spans="1:16">
-      <c r="A197" t="s">
-        <v>16</v>
+      <c r="A197">
+        <v>20260423</v>
       </c>
       <c r="B197" t="s">
         <v>65</v>
@@ -10410,14 +10440,14 @@
       <c r="D197">
         <v>61.4</v>
       </c>
-      <c r="E197" t="s">
-        <v>72</v>
+      <c r="E197">
+        <v>0</v>
       </c>
       <c r="F197" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G197" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H197">
         <v>1056.25</v>
@@ -10426,19 +10456,19 @@
         <v>8.600000000000001</v>
       </c>
       <c r="J197" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K197">
         <v>2</v>
       </c>
       <c r="L197" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M197" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N197" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O197">
         <v>18.59</v>
@@ -10448,8 +10478,8 @@
       </c>
     </row>
     <row r="198" spans="1:16">
-      <c r="A198" t="s">
-        <v>16</v>
+      <c r="A198">
+        <v>20260423</v>
       </c>
       <c r="B198" t="s">
         <v>66</v>
@@ -10460,14 +10490,14 @@
       <c r="D198">
         <v>60.9</v>
       </c>
-      <c r="E198" t="s">
-        <v>72</v>
+      <c r="E198">
+        <v>0</v>
       </c>
       <c r="F198" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G198" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H198">
         <v>187.01</v>
@@ -10476,19 +10506,19 @@
         <v>9.100000000000001</v>
       </c>
       <c r="J198" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="K198">
         <v>2</v>
       </c>
       <c r="L198" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M198" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N198" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O198">
         <v>18.59</v>
@@ -10498,8 +10528,8 @@
       </c>
     </row>
     <row r="199" spans="1:16">
-      <c r="A199" t="s">
-        <v>16</v>
+      <c r="A199">
+        <v>20260423</v>
       </c>
       <c r="B199" t="s">
         <v>67</v>
@@ -10510,14 +10540,14 @@
       <c r="D199">
         <v>59.4</v>
       </c>
-      <c r="E199" t="s">
-        <v>72</v>
+      <c r="E199">
+        <v>0</v>
       </c>
       <c r="F199" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G199" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H199">
         <v>180.18</v>
@@ -10526,19 +10556,19 @@
         <v>10.6</v>
       </c>
       <c r="J199" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K199">
         <v>2</v>
       </c>
       <c r="L199" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M199" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N199" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O199">
         <v>18.59</v>
@@ -10548,8 +10578,8 @@
       </c>
     </row>
     <row r="200" spans="1:16">
-      <c r="A200" t="s">
-        <v>16</v>
+      <c r="A200">
+        <v>20260423</v>
       </c>
       <c r="B200" t="s">
         <v>68</v>
@@ -10560,14 +10590,14 @@
       <c r="D200">
         <v>59.4</v>
       </c>
-      <c r="E200" t="s">
-        <v>72</v>
+      <c r="E200">
+        <v>0</v>
       </c>
       <c r="F200" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G200" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H200">
         <v>243.68</v>
@@ -10576,19 +10606,19 @@
         <v>10.6</v>
       </c>
       <c r="J200" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K200">
         <v>2</v>
       </c>
       <c r="L200" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M200" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N200" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O200">
         <v>18.59</v>
@@ -10598,8 +10628,8 @@
       </c>
     </row>
     <row r="201" spans="1:16">
-      <c r="A201" t="s">
-        <v>16</v>
+      <c r="A201">
+        <v>20260423</v>
       </c>
       <c r="B201" t="s">
         <v>56</v>
@@ -10610,14 +10640,14 @@
       <c r="D201">
         <v>57.3</v>
       </c>
-      <c r="E201" t="s">
-        <v>72</v>
+      <c r="E201">
+        <v>0</v>
       </c>
       <c r="F201" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G201" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H201">
         <v>450.65</v>
@@ -10626,19 +10656,19 @@
         <v>12.7</v>
       </c>
       <c r="J201" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="K201">
         <v>5</v>
       </c>
       <c r="L201" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M201" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N201" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O201">
         <v>18.59</v>
@@ -10648,8 +10678,8 @@
       </c>
     </row>
     <row r="202" spans="1:16">
-      <c r="A202" t="s">
-        <v>16</v>
+      <c r="A202">
+        <v>20260423</v>
       </c>
       <c r="B202" t="s">
         <v>69</v>
@@ -10660,14 +10690,14 @@
       <c r="D202">
         <v>56.9</v>
       </c>
-      <c r="E202" t="s">
-        <v>72</v>
+      <c r="E202">
+        <v>0</v>
       </c>
       <c r="F202" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G202" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H202">
         <v>97.75</v>
@@ -10676,19 +10706,19 @@
         <v>13.1</v>
       </c>
       <c r="J202" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K202">
         <v>2</v>
       </c>
       <c r="L202" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="M202" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N202" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O202">
         <v>18.59</v>
@@ -10698,8 +10728,8 @@
       </c>
     </row>
     <row r="203" spans="1:16">
-      <c r="A203" t="s">
-        <v>16</v>
+      <c r="A203">
+        <v>20260423</v>
       </c>
       <c r="B203" t="s">
         <v>33</v>
@@ -10710,14 +10740,14 @@
       <c r="D203">
         <v>56.6</v>
       </c>
-      <c r="E203" t="s">
-        <v>72</v>
+      <c r="E203">
+        <v>0</v>
       </c>
       <c r="F203" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G203" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H203">
         <v>9550.5</v>
@@ -10726,19 +10756,19 @@
         <v>13.4</v>
       </c>
       <c r="J203" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="K203">
         <v>16</v>
       </c>
       <c r="L203" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M203" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N203" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O203">
         <v>18.59</v>
@@ -10748,8 +10778,8 @@
       </c>
     </row>
     <row r="204" spans="1:16">
-      <c r="A204" t="s">
-        <v>16</v>
+      <c r="A204">
+        <v>20260423</v>
       </c>
       <c r="B204" t="s">
         <v>37</v>
@@ -10760,14 +10790,14 @@
       <c r="D204">
         <v>55.9</v>
       </c>
-      <c r="E204" t="s">
-        <v>72</v>
+      <c r="E204">
+        <v>0</v>
       </c>
       <c r="F204" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="G204" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="H204">
         <v>319.15</v>
@@ -10776,25 +10806,725 @@
         <v>14.1</v>
       </c>
       <c r="J204" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="K204">
         <v>16</v>
       </c>
       <c r="L204" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="M204" t="s">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="N204" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O204">
         <v>18.59</v>
       </c>
       <c r="P204">
         <v>128</v>
+      </c>
+    </row>
+    <row r="205" spans="1:16">
+      <c r="A205" t="s">
+        <v>16</v>
+      </c>
+      <c r="B205" t="s">
+        <v>40</v>
+      </c>
+      <c r="C205" t="s">
+        <v>71</v>
+      </c>
+      <c r="D205">
+        <v>63.9</v>
+      </c>
+      <c r="E205" t="s">
+        <v>72</v>
+      </c>
+      <c r="F205" t="s">
+        <v>79</v>
+      </c>
+      <c r="G205" t="s">
+        <v>80</v>
+      </c>
+      <c r="H205">
+        <v>3774</v>
+      </c>
+      <c r="I205">
+        <v>6.100000000000001</v>
+      </c>
+      <c r="J205" t="s">
+        <v>82</v>
+      </c>
+      <c r="K205">
+        <v>1</v>
+      </c>
+      <c r="L205" t="s">
+        <v>98</v>
+      </c>
+      <c r="M205" t="s">
+        <v>99</v>
+      </c>
+      <c r="N205" t="s">
+        <v>106</v>
+      </c>
+      <c r="O205">
+        <v>19.3</v>
+      </c>
+      <c r="P205">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="206" spans="1:16">
+      <c r="A206" t="s">
+        <v>16</v>
+      </c>
+      <c r="B206" t="s">
+        <v>39</v>
+      </c>
+      <c r="C206" t="s">
+        <v>71</v>
+      </c>
+      <c r="D206">
+        <v>61.5</v>
+      </c>
+      <c r="E206" t="s">
+        <v>73</v>
+      </c>
+      <c r="F206" t="s">
+        <v>79</v>
+      </c>
+      <c r="G206" t="s">
+        <v>80</v>
+      </c>
+      <c r="H206">
+        <v>399.75</v>
+      </c>
+      <c r="I206">
+        <v>8.5</v>
+      </c>
+      <c r="J206" t="s">
+        <v>82</v>
+      </c>
+      <c r="K206">
+        <v>7</v>
+      </c>
+      <c r="L206" t="s">
+        <v>95</v>
+      </c>
+      <c r="M206" t="s">
+        <v>99</v>
+      </c>
+      <c r="N206" t="s">
+        <v>106</v>
+      </c>
+      <c r="O206">
+        <v>19.3</v>
+      </c>
+      <c r="P206">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="207" spans="1:16">
+      <c r="A207" t="s">
+        <v>16</v>
+      </c>
+      <c r="B207" t="s">
+        <v>49</v>
+      </c>
+      <c r="C207" t="s">
+        <v>71</v>
+      </c>
+      <c r="D207">
+        <v>61.5</v>
+      </c>
+      <c r="E207" t="s">
+        <v>72</v>
+      </c>
+      <c r="F207" t="s">
+        <v>79</v>
+      </c>
+      <c r="G207" t="s">
+        <v>80</v>
+      </c>
+      <c r="H207">
+        <v>123.77</v>
+      </c>
+      <c r="I207">
+        <v>8.5</v>
+      </c>
+      <c r="J207" t="s">
+        <v>83</v>
+      </c>
+      <c r="K207">
+        <v>1</v>
+      </c>
+      <c r="L207" t="s">
+        <v>98</v>
+      </c>
+      <c r="M207" t="s">
+        <v>99</v>
+      </c>
+      <c r="N207" t="s">
+        <v>106</v>
+      </c>
+      <c r="O207">
+        <v>19.3</v>
+      </c>
+      <c r="P207">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="208" spans="1:16">
+      <c r="A208" t="s">
+        <v>16</v>
+      </c>
+      <c r="B208" t="s">
+        <v>41</v>
+      </c>
+      <c r="C208" t="s">
+        <v>71</v>
+      </c>
+      <c r="D208">
+        <v>61.4</v>
+      </c>
+      <c r="E208" t="s">
+        <v>72</v>
+      </c>
+      <c r="F208" t="s">
+        <v>79</v>
+      </c>
+      <c r="G208" t="s">
+        <v>80</v>
+      </c>
+      <c r="H208">
+        <v>210.85</v>
+      </c>
+      <c r="I208">
+        <v>8.600000000000001</v>
+      </c>
+      <c r="J208" t="s">
+        <v>84</v>
+      </c>
+      <c r="K208">
+        <v>1</v>
+      </c>
+      <c r="L208" t="s">
+        <v>98</v>
+      </c>
+      <c r="M208" t="s">
+        <v>99</v>
+      </c>
+      <c r="N208" t="s">
+        <v>106</v>
+      </c>
+      <c r="O208">
+        <v>19.3</v>
+      </c>
+      <c r="P208">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="209" spans="1:16">
+      <c r="A209" t="s">
+        <v>16</v>
+      </c>
+      <c r="B209" t="s">
+        <v>22</v>
+      </c>
+      <c r="C209" t="s">
+        <v>71</v>
+      </c>
+      <c r="D209">
+        <v>61</v>
+      </c>
+      <c r="E209" t="s">
+        <v>74</v>
+      </c>
+      <c r="F209" t="s">
+        <v>79</v>
+      </c>
+      <c r="G209" t="s">
+        <v>80</v>
+      </c>
+      <c r="H209">
+        <v>1353.9</v>
+      </c>
+      <c r="I209">
+        <v>9</v>
+      </c>
+      <c r="J209" t="s">
+        <v>82</v>
+      </c>
+      <c r="K209">
+        <v>17</v>
+      </c>
+      <c r="L209" t="s">
+        <v>93</v>
+      </c>
+      <c r="M209" t="s">
+        <v>99</v>
+      </c>
+      <c r="N209" t="s">
+        <v>106</v>
+      </c>
+      <c r="O209">
+        <v>19.3</v>
+      </c>
+      <c r="P209">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="210" spans="1:16">
+      <c r="A210" t="s">
+        <v>16</v>
+      </c>
+      <c r="B210" t="s">
+        <v>23</v>
+      </c>
+      <c r="C210" t="s">
+        <v>71</v>
+      </c>
+      <c r="D210">
+        <v>61</v>
+      </c>
+      <c r="E210" t="s">
+        <v>74</v>
+      </c>
+      <c r="F210" t="s">
+        <v>79</v>
+      </c>
+      <c r="G210" t="s">
+        <v>80</v>
+      </c>
+      <c r="H210">
+        <v>4397.1</v>
+      </c>
+      <c r="I210">
+        <v>9</v>
+      </c>
+      <c r="J210" t="s">
+        <v>82</v>
+      </c>
+      <c r="K210">
+        <v>17</v>
+      </c>
+      <c r="L210" t="s">
+        <v>93</v>
+      </c>
+      <c r="M210" t="s">
+        <v>99</v>
+      </c>
+      <c r="N210" t="s">
+        <v>106</v>
+      </c>
+      <c r="O210">
+        <v>19.3</v>
+      </c>
+      <c r="P210">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="211" spans="1:16">
+      <c r="A211" t="s">
+        <v>16</v>
+      </c>
+      <c r="B211" t="s">
+        <v>33</v>
+      </c>
+      <c r="C211" t="s">
+        <v>71</v>
+      </c>
+      <c r="D211">
+        <v>61</v>
+      </c>
+      <c r="E211" t="s">
+        <v>75</v>
+      </c>
+      <c r="F211" t="s">
+        <v>79</v>
+      </c>
+      <c r="G211" t="s">
+        <v>80</v>
+      </c>
+      <c r="H211">
+        <v>9597.5</v>
+      </c>
+      <c r="I211">
+        <v>9</v>
+      </c>
+      <c r="J211" t="s">
+        <v>82</v>
+      </c>
+      <c r="K211">
+        <v>17</v>
+      </c>
+      <c r="L211" t="s">
+        <v>93</v>
+      </c>
+      <c r="M211" t="s">
+        <v>99</v>
+      </c>
+      <c r="N211" t="s">
+        <v>106</v>
+      </c>
+      <c r="O211">
+        <v>19.3</v>
+      </c>
+      <c r="P211">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="212" spans="1:16">
+      <c r="A212" t="s">
+        <v>16</v>
+      </c>
+      <c r="B212" t="s">
+        <v>42</v>
+      </c>
+      <c r="C212" t="s">
+        <v>71</v>
+      </c>
+      <c r="D212">
+        <v>61</v>
+      </c>
+      <c r="E212" t="s">
+        <v>72</v>
+      </c>
+      <c r="F212" t="s">
+        <v>79</v>
+      </c>
+      <c r="G212" t="s">
+        <v>80</v>
+      </c>
+      <c r="H212">
+        <v>86.84999999999999</v>
+      </c>
+      <c r="I212">
+        <v>9</v>
+      </c>
+      <c r="J212" t="s">
+        <v>82</v>
+      </c>
+      <c r="K212">
+        <v>1</v>
+      </c>
+      <c r="L212" t="s">
+        <v>98</v>
+      </c>
+      <c r="M212" t="s">
+        <v>99</v>
+      </c>
+      <c r="N212" t="s">
+        <v>106</v>
+      </c>
+      <c r="O212">
+        <v>19.3</v>
+      </c>
+      <c r="P212">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="213" spans="1:16">
+      <c r="A213" t="s">
+        <v>16</v>
+      </c>
+      <c r="B213" t="s">
+        <v>43</v>
+      </c>
+      <c r="C213" t="s">
+        <v>71</v>
+      </c>
+      <c r="D213">
+        <v>60.4</v>
+      </c>
+      <c r="E213" t="s">
+        <v>72</v>
+      </c>
+      <c r="F213" t="s">
+        <v>79</v>
+      </c>
+      <c r="G213" t="s">
+        <v>80</v>
+      </c>
+      <c r="H213">
+        <v>1246</v>
+      </c>
+      <c r="I213">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="J213" t="s">
+        <v>82</v>
+      </c>
+      <c r="K213">
+        <v>1</v>
+      </c>
+      <c r="L213" t="s">
+        <v>98</v>
+      </c>
+      <c r="M213" t="s">
+        <v>99</v>
+      </c>
+      <c r="N213" t="s">
+        <v>106</v>
+      </c>
+      <c r="O213">
+        <v>19.3</v>
+      </c>
+      <c r="P213">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="214" spans="1:16">
+      <c r="A214" t="s">
+        <v>16</v>
+      </c>
+      <c r="B214" t="s">
+        <v>44</v>
+      </c>
+      <c r="C214" t="s">
+        <v>71</v>
+      </c>
+      <c r="D214">
+        <v>60</v>
+      </c>
+      <c r="E214" t="s">
+        <v>72</v>
+      </c>
+      <c r="F214" t="s">
+        <v>79</v>
+      </c>
+      <c r="G214" t="s">
+        <v>80</v>
+      </c>
+      <c r="H214">
+        <v>124.57</v>
+      </c>
+      <c r="I214">
+        <v>10</v>
+      </c>
+      <c r="J214" t="s">
+        <v>82</v>
+      </c>
+      <c r="K214">
+        <v>1</v>
+      </c>
+      <c r="L214" t="s">
+        <v>98</v>
+      </c>
+      <c r="M214" t="s">
+        <v>99</v>
+      </c>
+      <c r="N214" t="s">
+        <v>106</v>
+      </c>
+      <c r="O214">
+        <v>19.3</v>
+      </c>
+      <c r="P214">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="215" spans="1:16">
+      <c r="A215" t="s">
+        <v>16</v>
+      </c>
+      <c r="B215" t="s">
+        <v>56</v>
+      </c>
+      <c r="C215" t="s">
+        <v>71</v>
+      </c>
+      <c r="D215">
+        <v>59.7</v>
+      </c>
+      <c r="E215" t="s">
+        <v>76</v>
+      </c>
+      <c r="F215" t="s">
+        <v>79</v>
+      </c>
+      <c r="G215" t="s">
+        <v>80</v>
+      </c>
+      <c r="H215">
+        <v>454.95</v>
+      </c>
+      <c r="I215">
+        <v>10.3</v>
+      </c>
+      <c r="J215" t="s">
+        <v>90</v>
+      </c>
+      <c r="K215">
+        <v>6</v>
+      </c>
+      <c r="L215" t="s">
+        <v>96</v>
+      </c>
+      <c r="M215" t="s">
+        <v>99</v>
+      </c>
+      <c r="N215" t="s">
+        <v>106</v>
+      </c>
+      <c r="O215">
+        <v>19.3</v>
+      </c>
+      <c r="P215">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="216" spans="1:16">
+      <c r="A216" t="s">
+        <v>16</v>
+      </c>
+      <c r="B216" t="s">
+        <v>32</v>
+      </c>
+      <c r="C216" t="s">
+        <v>71</v>
+      </c>
+      <c r="D216">
+        <v>59.4</v>
+      </c>
+      <c r="E216" t="s">
+        <v>77</v>
+      </c>
+      <c r="F216" t="s">
+        <v>79</v>
+      </c>
+      <c r="G216" t="s">
+        <v>80</v>
+      </c>
+      <c r="H216">
+        <v>1417.3</v>
+      </c>
+      <c r="I216">
+        <v>10.6</v>
+      </c>
+      <c r="J216" t="s">
+        <v>84</v>
+      </c>
+      <c r="K216">
+        <v>12</v>
+      </c>
+      <c r="L216" t="s">
+        <v>92</v>
+      </c>
+      <c r="M216" t="s">
+        <v>99</v>
+      </c>
+      <c r="N216" t="s">
+        <v>106</v>
+      </c>
+      <c r="O216">
+        <v>19.3</v>
+      </c>
+      <c r="P216">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="217" spans="1:16">
+      <c r="A217" t="s">
+        <v>16</v>
+      </c>
+      <c r="B217" t="s">
+        <v>45</v>
+      </c>
+      <c r="C217" t="s">
+        <v>71</v>
+      </c>
+      <c r="D217">
+        <v>59.4</v>
+      </c>
+      <c r="E217" t="s">
+        <v>72</v>
+      </c>
+      <c r="F217" t="s">
+        <v>79</v>
+      </c>
+      <c r="G217" t="s">
+        <v>80</v>
+      </c>
+      <c r="H217">
+        <v>1167.1</v>
+      </c>
+      <c r="I217">
+        <v>10.6</v>
+      </c>
+      <c r="J217" t="s">
+        <v>84</v>
+      </c>
+      <c r="K217">
+        <v>1</v>
+      </c>
+      <c r="L217" t="s">
+        <v>98</v>
+      </c>
+      <c r="M217" t="s">
+        <v>99</v>
+      </c>
+      <c r="N217" t="s">
+        <v>106</v>
+      </c>
+      <c r="O217">
+        <v>19.3</v>
+      </c>
+      <c r="P217">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="218" spans="1:16">
+      <c r="A218" t="s">
+        <v>16</v>
+      </c>
+      <c r="B218" t="s">
+        <v>37</v>
+      </c>
+      <c r="C218" t="s">
+        <v>71</v>
+      </c>
+      <c r="D218">
+        <v>58.4</v>
+      </c>
+      <c r="E218" t="s">
+        <v>78</v>
+      </c>
+      <c r="F218" t="s">
+        <v>79</v>
+      </c>
+      <c r="G218" t="s">
+        <v>80</v>
+      </c>
+      <c r="H218">
+        <v>314.95</v>
+      </c>
+      <c r="I218">
+        <v>11.6</v>
+      </c>
+      <c r="J218" t="s">
+        <v>83</v>
+      </c>
+      <c r="K218">
+        <v>17</v>
+      </c>
+      <c r="L218" t="s">
+        <v>93</v>
+      </c>
+      <c r="M218" t="s">
+        <v>99</v>
+      </c>
+      <c r="N218" t="s">
+        <v>106</v>
+      </c>
+      <c r="O218">
+        <v>19.3</v>
+      </c>
+      <c r="P218">
+        <v>208</v>
       </c>
     </row>
   </sheetData>

--- a/reports/watchlist_history.xlsx
+++ b/reports/watchlist_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1766" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1878" uniqueCount="103">
   <si>
     <t>Date</t>
   </si>
@@ -232,25 +232,13 @@
     <t>WATCH</t>
   </si>
   <si>
+    <t>+2.4</t>
+  </si>
+  <si>
     <t>+0.0</t>
   </si>
   <si>
-    <t>-2.4</t>
-  </si>
-  <si>
-    <t>-3.0</t>
-  </si>
-  <si>
-    <t>+4.4</t>
-  </si>
-  <si>
-    <t>+2.4</t>
-  </si>
-  <si>
-    <t>-2.0</t>
-  </si>
-  <si>
-    <t>+2.5</t>
+    <t>-2.5</t>
   </si>
   <si>
     <t>Stage 2 — Uptrend ✓</t>
@@ -666,7 +654,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P218"/>
+  <dimension ref="A1:P232"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -736,10 +724,10 @@
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H2">
         <v>11714</v>
@@ -751,13 +739,13 @@
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="M2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N2" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O2">
         <v>17.53</v>
@@ -783,10 +771,10 @@
         <v>0</v>
       </c>
       <c r="F3" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G3" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H3">
         <v>514.05</v>
@@ -798,13 +786,13 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="M3" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N3" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O3">
         <v>17.53</v>
@@ -830,10 +818,10 @@
         <v>0</v>
       </c>
       <c r="F4" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G4" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H4">
         <v>1621.5</v>
@@ -845,13 +833,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="M4" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N4" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O4">
         <v>17.53</v>
@@ -877,10 +865,10 @@
         <v>0</v>
       </c>
       <c r="F5" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G5" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H5">
         <v>191.38</v>
@@ -889,19 +877,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J5" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K5">
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M5" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N5" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O5">
         <v>17.53</v>
@@ -927,10 +915,10 @@
         <v>0</v>
       </c>
       <c r="F6" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H6">
         <v>1318.1</v>
@@ -939,19 +927,19 @@
         <v>0.9000000000000057</v>
       </c>
       <c r="J6" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M6" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N6" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O6">
         <v>17.53</v>
@@ -977,10 +965,10 @@
         <v>-0.5</v>
       </c>
       <c r="F7" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H7">
         <v>1377.7</v>
@@ -989,19 +977,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J7" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K7">
         <v>6</v>
       </c>
       <c r="L7" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M7" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N7" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O7">
         <v>17.53</v>
@@ -1027,10 +1015,10 @@
         <v>-0.5</v>
       </c>
       <c r="F8" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G8" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H8">
         <v>4479.7</v>
@@ -1039,19 +1027,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J8" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K8">
         <v>6</v>
       </c>
       <c r="L8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M8" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N8" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O8">
         <v>17.53</v>
@@ -1077,10 +1065,10 @@
         <v>-0.5</v>
       </c>
       <c r="F9" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H9">
         <v>1045.3</v>
@@ -1089,19 +1077,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J9" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K9">
         <v>6</v>
       </c>
       <c r="L9" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M9" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N9" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O9">
         <v>17.53</v>
@@ -1127,10 +1115,10 @@
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G10" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H10">
         <v>1055.65</v>
@@ -1139,19 +1127,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J10" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K10">
         <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M10" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N10" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O10">
         <v>17.53</v>
@@ -1177,10 +1165,10 @@
         <v>-0.5</v>
       </c>
       <c r="F11" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G11" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H11">
         <v>1045.3</v>
@@ -1189,19 +1177,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J11" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K11">
         <v>6</v>
       </c>
       <c r="L11" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M11" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N11" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O11">
         <v>17.53</v>
@@ -1227,10 +1215,10 @@
         <v>-0.5</v>
       </c>
       <c r="F12" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G12" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H12">
         <v>4479.7</v>
@@ -1239,19 +1227,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J12" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K12">
         <v>6</v>
       </c>
       <c r="L12" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M12" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N12" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O12">
         <v>17.53</v>
@@ -1277,10 +1265,10 @@
         <v>0</v>
       </c>
       <c r="F13" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H13">
         <v>581.3</v>
@@ -1289,19 +1277,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J13" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K13">
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M13" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N13" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O13">
         <v>17.53</v>
@@ -1327,10 +1315,10 @@
         <v>0</v>
       </c>
       <c r="F14" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G14" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H14">
         <v>458.9</v>
@@ -1339,19 +1327,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J14" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M14" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N14" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O14">
         <v>17.53</v>
@@ -1377,10 +1365,10 @@
         <v>0</v>
       </c>
       <c r="F15" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G15" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H15">
         <v>196.02</v>
@@ -1389,19 +1377,19 @@
         <v>4.400000000000006</v>
       </c>
       <c r="J15" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N15" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O15">
         <v>17.53</v>
@@ -1427,10 +1415,10 @@
         <v>0</v>
       </c>
       <c r="F16" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G16" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H16">
         <v>4172.9</v>
@@ -1439,19 +1427,19 @@
         <v>5</v>
       </c>
       <c r="J16" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K16">
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M16" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N16" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O16">
         <v>17.53</v>
@@ -1477,10 +1465,10 @@
         <v>0</v>
       </c>
       <c r="F17" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G17" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H17">
         <v>6373.5</v>
@@ -1489,19 +1477,19 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J17" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K17">
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M17" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N17" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O17">
         <v>17.53</v>
@@ -1527,10 +1515,10 @@
         <v>0</v>
       </c>
       <c r="F18" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G18" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H18">
         <v>1113.1</v>
@@ -1539,19 +1527,19 @@
         <v>5.299999999999997</v>
       </c>
       <c r="J18" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K18">
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M18" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N18" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O18">
         <v>17.53</v>
@@ -1577,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="F19" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G19" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H19">
         <v>1379.9</v>
@@ -1589,19 +1577,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J19" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K19">
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M19" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N19" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O19">
         <v>17.53</v>
@@ -1627,10 +1615,10 @@
         <v>-0.5</v>
       </c>
       <c r="F20" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G20" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H20">
         <v>9793</v>
@@ -1639,19 +1627,19 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J20" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K20">
         <v>6</v>
       </c>
       <c r="L20" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M20" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N20" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O20">
         <v>17.53</v>
@@ -1677,10 +1665,10 @@
         <v>0</v>
       </c>
       <c r="F21" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G21" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H21">
         <v>7955.5</v>
@@ -1689,19 +1677,19 @@
         <v>5.799999999999997</v>
       </c>
       <c r="J21" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K21">
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M21" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N21" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O21">
         <v>17.53</v>
@@ -1727,10 +1715,10 @@
         <v>0</v>
       </c>
       <c r="F22" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G22" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H22">
         <v>1037.85</v>
@@ -1739,19 +1727,19 @@
         <v>6.399999999999999</v>
       </c>
       <c r="J22" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K22">
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M22" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N22" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O22">
         <v>17.53</v>
@@ -1777,10 +1765,10 @@
         <v>0</v>
       </c>
       <c r="F23" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G23" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H23">
         <v>979.1</v>
@@ -1789,19 +1777,19 @@
         <v>8.399999999999999</v>
       </c>
       <c r="J23" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K23">
         <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M23" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N23" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O23">
         <v>17.53</v>
@@ -1827,10 +1815,10 @@
         <v>-0.5</v>
       </c>
       <c r="F24" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G24" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H24">
         <v>319.35</v>
@@ -1839,19 +1827,19 @@
         <v>8.5</v>
       </c>
       <c r="J24" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K24">
         <v>6</v>
       </c>
       <c r="L24" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M24" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N24" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="O24">
         <v>17.53</v>
@@ -1877,10 +1865,10 @@
         <v>0</v>
       </c>
       <c r="F25" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G25" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H25">
         <v>767.65</v>
@@ -1892,13 +1880,13 @@
         <v>1</v>
       </c>
       <c r="L25" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M25" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N25" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O25">
         <v>18.27</v>
@@ -1924,10 +1912,10 @@
         <v>7.8</v>
       </c>
       <c r="F26" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G26" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H26">
         <v>404.1</v>
@@ -1936,19 +1924,19 @@
         <v>1</v>
       </c>
       <c r="J26" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K26">
         <v>7</v>
       </c>
       <c r="L26" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M26" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N26" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O26">
         <v>18.27</v>
@@ -1974,10 +1962,10 @@
         <v>0</v>
       </c>
       <c r="F27" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G27" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H27">
         <v>3847</v>
@@ -1986,19 +1974,19 @@
         <v>1</v>
       </c>
       <c r="J27" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K27">
         <v>1</v>
       </c>
       <c r="L27" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M27" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N27" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O27">
         <v>18.27</v>
@@ -2024,10 +2012,10 @@
         <v>0</v>
       </c>
       <c r="F28" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G28" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H28">
         <v>211.75</v>
@@ -2036,19 +2024,19 @@
         <v>2.5</v>
       </c>
       <c r="J28" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K28">
         <v>1</v>
       </c>
       <c r="L28" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M28" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N28" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O28">
         <v>18.27</v>
@@ -2074,10 +2062,10 @@
         <v>-0.5</v>
       </c>
       <c r="F29" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G29" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H29">
         <v>1381.5</v>
@@ -2086,19 +2074,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J29" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K29">
         <v>7</v>
       </c>
       <c r="L29" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M29" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N29" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O29">
         <v>18.27</v>
@@ -2124,10 +2112,10 @@
         <v>-0.5</v>
       </c>
       <c r="F30" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H30">
         <v>4483</v>
@@ -2136,19 +2124,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J30" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K30">
         <v>7</v>
       </c>
       <c r="L30" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M30" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N30" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O30">
         <v>18.27</v>
@@ -2174,10 +2162,10 @@
         <v>0</v>
       </c>
       <c r="F31" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G31" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H31">
         <v>89.05</v>
@@ -2186,19 +2174,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J31" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K31">
         <v>1</v>
       </c>
       <c r="L31" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M31" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N31" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O31">
         <v>18.27</v>
@@ -2224,10 +2212,10 @@
         <v>0</v>
       </c>
       <c r="F32" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G32" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H32">
         <v>1291.1</v>
@@ -2236,19 +2224,19 @@
         <v>3.400000000000006</v>
       </c>
       <c r="J32" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K32">
         <v>1</v>
       </c>
       <c r="L32" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M32" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N32" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O32">
         <v>18.27</v>
@@ -2274,10 +2262,10 @@
         <v>-0.5</v>
       </c>
       <c r="F33" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G33" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H33">
         <v>1414.6</v>
@@ -2286,19 +2274,19 @@
         <v>5.900000000000006</v>
       </c>
       <c r="J33" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K33">
         <v>2</v>
       </c>
       <c r="L33" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M33" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N33" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O33">
         <v>18.27</v>
@@ -2324,10 +2312,10 @@
         <v>-0.5</v>
       </c>
       <c r="F34" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G34" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H34">
         <v>9760</v>
@@ -2336,19 +2324,19 @@
         <v>6.299999999999997</v>
       </c>
       <c r="J34" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K34">
         <v>7</v>
       </c>
       <c r="L34" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M34" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N34" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O34">
         <v>18.27</v>
@@ -2374,10 +2362,10 @@
         <v>0</v>
       </c>
       <c r="F35" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G35" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H35">
         <v>125.85</v>
@@ -2386,19 +2374,19 @@
         <v>7.299999999999997</v>
       </c>
       <c r="J35" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K35">
         <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M35" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N35" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O35">
         <v>18.27</v>
@@ -2424,10 +2412,10 @@
         <v>0</v>
       </c>
       <c r="F36" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H36">
         <v>1171.95</v>
@@ -2436,19 +2424,19 @@
         <v>7.899999999999999</v>
       </c>
       <c r="J36" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K36">
         <v>1</v>
       </c>
       <c r="L36" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M36" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N36" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O36">
         <v>18.27</v>
@@ -2474,10 +2462,10 @@
         <v>-6.5</v>
       </c>
       <c r="F37" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G37" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H37">
         <v>1038.1</v>
@@ -2486,19 +2474,19 @@
         <v>9.299999999999997</v>
       </c>
       <c r="J37" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K37">
         <v>7</v>
       </c>
       <c r="L37" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M37" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N37" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O37">
         <v>18.27</v>
@@ -2524,10 +2512,10 @@
         <v>-2.9</v>
       </c>
       <c r="F38" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G38" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H38">
         <v>319.6</v>
@@ -2536,19 +2524,19 @@
         <v>11.4</v>
       </c>
       <c r="J38" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K38">
         <v>7</v>
       </c>
       <c r="L38" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M38" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N38" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O38">
         <v>18.27</v>
@@ -2574,10 +2562,10 @@
         <v>0</v>
       </c>
       <c r="F39" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G39" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H39">
         <v>2314.1</v>
@@ -2586,19 +2574,19 @@
         <v>11.7</v>
       </c>
       <c r="J39" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K39">
         <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M39" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N39" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O39">
         <v>18.27</v>
@@ -2624,10 +2612,10 @@
         <v>0</v>
       </c>
       <c r="F40" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G40" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H40">
         <v>3723.6</v>
@@ -2636,19 +2624,19 @@
         <v>11.7</v>
       </c>
       <c r="J40" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K40">
         <v>1</v>
       </c>
       <c r="L40" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M40" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N40" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O40">
         <v>18.27</v>
@@ -2674,10 +2662,10 @@
         <v>-0.5</v>
       </c>
       <c r="F41" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G41" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H41">
         <v>4049.2</v>
@@ -2686,19 +2674,19 @@
         <v>13.3</v>
       </c>
       <c r="J41" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K41">
         <v>3</v>
       </c>
       <c r="L41" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M41" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N41" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O41">
         <v>18.27</v>
@@ -2724,10 +2712,10 @@
         <v>0</v>
       </c>
       <c r="F42" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G42" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H42">
         <v>124.98</v>
@@ -2736,19 +2724,19 @@
         <v>14.6</v>
       </c>
       <c r="J42" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K42">
         <v>1</v>
       </c>
       <c r="L42" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M42" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N42" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O42">
         <v>18.27</v>
@@ -2774,10 +2762,10 @@
         <v>2.4</v>
       </c>
       <c r="F43" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G43" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H43">
         <v>1388.7</v>
@@ -2786,19 +2774,19 @@
         <v>0.9000000000000057</v>
       </c>
       <c r="J43" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K43">
         <v>8</v>
       </c>
       <c r="L43" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M43" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N43" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O43">
         <v>18.23</v>
@@ -2824,10 +2812,10 @@
         <v>0</v>
       </c>
       <c r="F44" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G44" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H44">
         <v>404.8</v>
@@ -2836,19 +2824,19 @@
         <v>1</v>
       </c>
       <c r="J44" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K44">
         <v>8</v>
       </c>
       <c r="L44" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M44" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N44" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O44">
         <v>18.23</v>
@@ -2874,10 +2862,10 @@
         <v>0</v>
       </c>
       <c r="F45" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G45" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H45">
         <v>3845.7</v>
@@ -2886,19 +2874,19 @@
         <v>1</v>
       </c>
       <c r="J45" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K45">
         <v>2</v>
       </c>
       <c r="L45" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M45" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N45" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O45">
         <v>18.23</v>
@@ -2924,10 +2912,10 @@
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G46" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H46">
         <v>213.03</v>
@@ -2936,19 +2924,19 @@
         <v>1.5</v>
       </c>
       <c r="J46" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K46">
         <v>2</v>
       </c>
       <c r="L46" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M46" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N46" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O46">
         <v>18.23</v>
@@ -2974,10 +2962,10 @@
         <v>0</v>
       </c>
       <c r="F47" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G47" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H47">
         <v>4477</v>
@@ -2986,19 +2974,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J47" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K47">
         <v>8</v>
       </c>
       <c r="L47" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M47" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N47" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O47">
         <v>18.23</v>
@@ -3024,10 +3012,10 @@
         <v>0</v>
       </c>
       <c r="F48" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G48" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H48">
         <v>88.98999999999999</v>
@@ -3036,19 +3024,19 @@
         <v>3.299999999999997</v>
       </c>
       <c r="J48" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K48">
         <v>2</v>
       </c>
       <c r="L48" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M48" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N48" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O48">
         <v>18.23</v>
@@ -3074,10 +3062,10 @@
         <v>0</v>
       </c>
       <c r="F49" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G49" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H49">
         <v>1288.9</v>
@@ -3086,19 +3074,19 @@
         <v>3.400000000000006</v>
       </c>
       <c r="J49" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K49">
         <v>2</v>
       </c>
       <c r="L49" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M49" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N49" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O49">
         <v>18.23</v>
@@ -3124,10 +3112,10 @@
         <v>0</v>
       </c>
       <c r="F50" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G50" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H50">
         <v>1419</v>
@@ -3136,19 +3124,19 @@
         <v>5.900000000000006</v>
       </c>
       <c r="J50" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K50">
         <v>3</v>
       </c>
       <c r="L50" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M50" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N50" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O50">
         <v>18.23</v>
@@ -3174,10 +3162,10 @@
         <v>0</v>
       </c>
       <c r="F51" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G51" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H51">
         <v>9758</v>
@@ -3186,19 +3174,19 @@
         <v>6.299999999999997</v>
       </c>
       <c r="J51" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K51">
         <v>8</v>
       </c>
       <c r="L51" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M51" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N51" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O51">
         <v>18.23</v>
@@ -3224,10 +3212,10 @@
         <v>0</v>
       </c>
       <c r="F52" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G52" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H52">
         <v>125.98</v>
@@ -3236,19 +3224,19 @@
         <v>7.299999999999997</v>
       </c>
       <c r="J52" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K52">
         <v>2</v>
       </c>
       <c r="L52" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M52" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N52" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O52">
         <v>18.23</v>
@@ -3274,10 +3262,10 @@
         <v>0</v>
       </c>
       <c r="F53" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G53" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H53">
         <v>1182</v>
@@ -3286,19 +3274,19 @@
         <v>7.899999999999999</v>
       </c>
       <c r="J53" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K53">
         <v>2</v>
       </c>
       <c r="L53" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M53" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N53" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O53">
         <v>18.23</v>
@@ -3324,10 +3312,10 @@
         <v>0</v>
       </c>
       <c r="F54" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G54" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H54">
         <v>1040</v>
@@ -3336,19 +3324,19 @@
         <v>9.299999999999997</v>
       </c>
       <c r="J54" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K54">
         <v>8</v>
       </c>
       <c r="L54" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M54" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N54" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O54">
         <v>18.23</v>
@@ -3374,10 +3362,10 @@
         <v>0</v>
       </c>
       <c r="F55" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G55" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H55">
         <v>320.2</v>
@@ -3386,19 +3374,19 @@
         <v>11.4</v>
       </c>
       <c r="J55" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K55">
         <v>8</v>
       </c>
       <c r="L55" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M55" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N55" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O55">
         <v>18.23</v>
@@ -3424,10 +3412,10 @@
         <v>0</v>
       </c>
       <c r="F56" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G56" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H56">
         <v>2314.8</v>
@@ -3436,19 +3424,19 @@
         <v>11.7</v>
       </c>
       <c r="J56" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K56">
         <v>2</v>
       </c>
       <c r="L56" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M56" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N56" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O56">
         <v>18.23</v>
@@ -3474,10 +3462,10 @@
         <v>0</v>
       </c>
       <c r="F57" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G57" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H57">
         <v>3716.5</v>
@@ -3486,19 +3474,19 @@
         <v>11.7</v>
       </c>
       <c r="J57" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K57">
         <v>2</v>
       </c>
       <c r="L57" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M57" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N57" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O57">
         <v>18.23</v>
@@ -3524,10 +3512,10 @@
         <v>0</v>
       </c>
       <c r="F58" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G58" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H58">
         <v>4043</v>
@@ -3536,19 +3524,19 @@
         <v>13.3</v>
       </c>
       <c r="J58" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K58">
         <v>4</v>
       </c>
       <c r="L58" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M58" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N58" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O58">
         <v>18.23</v>
@@ -3574,10 +3562,10 @@
         <v>0</v>
       </c>
       <c r="F59" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G59" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H59">
         <v>125.04</v>
@@ -3586,19 +3574,19 @@
         <v>14.6</v>
       </c>
       <c r="J59" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K59">
         <v>2</v>
       </c>
       <c r="L59" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M59" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N59" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O59">
         <v>18.23</v>
@@ -3624,10 +3612,10 @@
         <v>0</v>
       </c>
       <c r="F60" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G60" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H60">
         <v>3852.5</v>
@@ -3639,13 +3627,13 @@
         <v>1</v>
       </c>
       <c r="L60" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M60" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N60" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O60">
         <v>18.08</v>
@@ -3671,10 +3659,10 @@
         <v>0.5</v>
       </c>
       <c r="F61" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G61" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H61">
         <v>1388.5</v>
@@ -3683,19 +3671,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J61" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K61">
         <v>9</v>
       </c>
       <c r="L61" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M61" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N61" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O61">
         <v>18.08</v>
@@ -3721,10 +3709,10 @@
         <v>0.5</v>
       </c>
       <c r="F62" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G62" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H62">
         <v>406.1</v>
@@ -3733,19 +3721,19 @@
         <v>0.5</v>
       </c>
       <c r="J62" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K62">
         <v>9</v>
       </c>
       <c r="L62" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M62" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N62" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O62">
         <v>18.08</v>
@@ -3771,10 +3759,10 @@
         <v>0.5</v>
       </c>
       <c r="F63" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G63" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H63">
         <v>213.6</v>
@@ -3783,19 +3771,19 @@
         <v>1</v>
       </c>
       <c r="J63" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K63">
         <v>3</v>
       </c>
       <c r="L63" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M63" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N63" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O63">
         <v>18.08</v>
@@ -3821,10 +3809,10 @@
         <v>0.5</v>
       </c>
       <c r="F64" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G64" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H64">
         <v>4478</v>
@@ -3833,19 +3821,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J64" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K64">
         <v>9</v>
       </c>
       <c r="L64" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M64" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N64" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O64">
         <v>18.08</v>
@@ -3871,10 +3859,10 @@
         <v>6.5</v>
       </c>
       <c r="F65" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G65" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H65">
         <v>1050.05</v>
@@ -3883,19 +3871,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J65" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K65">
         <v>9</v>
       </c>
       <c r="L65" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M65" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N65" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O65">
         <v>18.08</v>
@@ -3921,10 +3909,10 @@
         <v>0.5</v>
       </c>
       <c r="F66" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G66" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H66">
         <v>88.59</v>
@@ -3933,19 +3921,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J66" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K66">
         <v>3</v>
       </c>
       <c r="L66" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M66" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N66" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O66">
         <v>18.08</v>
@@ -3971,10 +3959,10 @@
         <v>0.5</v>
       </c>
       <c r="F67" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G67" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H67">
         <v>1291.7</v>
@@ -3983,19 +3971,19 @@
         <v>2.900000000000006</v>
       </c>
       <c r="J67" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K67">
         <v>3</v>
       </c>
       <c r="L67" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M67" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N67" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O67">
         <v>18.08</v>
@@ -4021,10 +4009,10 @@
         <v>0.5</v>
       </c>
       <c r="F68" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G68" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H68">
         <v>1405.3</v>
@@ -4033,19 +4021,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J68" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K68">
         <v>4</v>
       </c>
       <c r="L68" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M68" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N68" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O68">
         <v>18.08</v>
@@ -4071,10 +4059,10 @@
         <v>0.5</v>
       </c>
       <c r="F69" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G69" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H69">
         <v>125.89</v>
@@ -4083,19 +4071,19 @@
         <v>6.799999999999997</v>
       </c>
       <c r="J69" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K69">
         <v>3</v>
       </c>
       <c r="L69" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M69" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N69" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O69">
         <v>18.08</v>
@@ -4121,10 +4109,10 @@
         <v>0.5</v>
       </c>
       <c r="F70" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G70" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H70">
         <v>1190.45</v>
@@ -4133,19 +4121,19 @@
         <v>7.399999999999999</v>
       </c>
       <c r="J70" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K70">
         <v>3</v>
       </c>
       <c r="L70" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M70" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N70" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O70">
         <v>18.08</v>
@@ -4171,10 +4159,10 @@
         <v>-3.1</v>
       </c>
       <c r="F71" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G71" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H71">
         <v>9700</v>
@@ -4183,19 +4171,19 @@
         <v>9.399999999999999</v>
       </c>
       <c r="J71" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K71">
         <v>9</v>
       </c>
       <c r="L71" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M71" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N71" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O71">
         <v>18.08</v>
@@ -4221,10 +4209,10 @@
         <v>0.5</v>
       </c>
       <c r="F72" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G72" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H72">
         <v>319.85</v>
@@ -4233,19 +4221,19 @@
         <v>10.9</v>
       </c>
       <c r="J72" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K72">
         <v>9</v>
       </c>
       <c r="L72" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M72" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N72" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O72">
         <v>18.08</v>
@@ -4271,10 +4259,10 @@
         <v>0.5</v>
       </c>
       <c r="F73" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G73" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H73">
         <v>2305.6</v>
@@ -4283,19 +4271,19 @@
         <v>11.2</v>
       </c>
       <c r="J73" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K73">
         <v>3</v>
       </c>
       <c r="L73" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M73" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N73" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O73">
         <v>18.08</v>
@@ -4321,10 +4309,10 @@
         <v>0.5</v>
       </c>
       <c r="F74" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G74" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H74">
         <v>3703.3</v>
@@ -4333,19 +4321,19 @@
         <v>11.2</v>
       </c>
       <c r="J74" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K74">
         <v>3</v>
       </c>
       <c r="L74" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M74" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N74" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O74">
         <v>18.08</v>
@@ -4371,10 +4359,10 @@
         <v>0.5</v>
       </c>
       <c r="F75" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G75" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H75">
         <v>4023.5</v>
@@ -4383,19 +4371,19 @@
         <v>12.8</v>
       </c>
       <c r="J75" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K75">
         <v>5</v>
       </c>
       <c r="L75" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M75" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N75" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O75">
         <v>18.08</v>
@@ -4421,10 +4409,10 @@
         <v>0</v>
       </c>
       <c r="F76" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G76" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H76">
         <v>7196</v>
@@ -4433,19 +4421,19 @@
         <v>13.2</v>
       </c>
       <c r="J76" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K76">
         <v>1</v>
       </c>
       <c r="L76" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M76" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N76" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O76">
         <v>18.08</v>
@@ -4471,10 +4459,10 @@
         <v>0.5</v>
       </c>
       <c r="F77" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G77" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H77">
         <v>125</v>
@@ -4483,19 +4471,19 @@
         <v>14.1</v>
       </c>
       <c r="J77" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K77">
         <v>3</v>
       </c>
       <c r="L77" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M77" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N77" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O77">
         <v>18.08</v>
@@ -4521,10 +4509,10 @@
         <v>0</v>
       </c>
       <c r="F78" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G78" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H78">
         <v>1449.1</v>
@@ -4536,13 +4524,13 @@
         <v>1</v>
       </c>
       <c r="L78" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M78" t="s">
+        <v>95</v>
+      </c>
+      <c r="N78" t="s">
         <v>99</v>
-      </c>
-      <c r="N78" t="s">
-        <v>103</v>
       </c>
       <c r="O78">
         <v>18.3</v>
@@ -4568,10 +4556,10 @@
         <v>0</v>
       </c>
       <c r="F79" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G79" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H79">
         <v>3844.3</v>
@@ -4583,13 +4571,13 @@
         <v>1</v>
       </c>
       <c r="L79" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M79" t="s">
+        <v>95</v>
+      </c>
+      <c r="N79" t="s">
         <v>99</v>
-      </c>
-      <c r="N79" t="s">
-        <v>103</v>
       </c>
       <c r="O79">
         <v>18.3</v>
@@ -4615,10 +4603,10 @@
         <v>0</v>
       </c>
       <c r="F80" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G80" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H80">
         <v>1330.5</v>
@@ -4630,13 +4618,13 @@
         <v>1</v>
       </c>
       <c r="L80" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M80" t="s">
+        <v>95</v>
+      </c>
+      <c r="N80" t="s">
         <v>99</v>
-      </c>
-      <c r="N80" t="s">
-        <v>103</v>
       </c>
       <c r="O80">
         <v>18.3</v>
@@ -4662,10 +4650,10 @@
         <v>0</v>
       </c>
       <c r="F81" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G81" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H81">
         <v>405.4</v>
@@ -4677,13 +4665,13 @@
         <v>1</v>
       </c>
       <c r="L81" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M81" t="s">
+        <v>95</v>
+      </c>
+      <c r="N81" t="s">
         <v>99</v>
-      </c>
-      <c r="N81" t="s">
-        <v>103</v>
       </c>
       <c r="O81">
         <v>18.3</v>
@@ -4709,10 +4697,10 @@
         <v>0</v>
       </c>
       <c r="F82" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G82" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H82">
         <v>554.7</v>
@@ -4721,19 +4709,19 @@
         <v>0.4000000000000057</v>
       </c>
       <c r="J82" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K82">
         <v>1</v>
       </c>
       <c r="L82" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M82" t="s">
+        <v>95</v>
+      </c>
+      <c r="N82" t="s">
         <v>99</v>
-      </c>
-      <c r="N82" t="s">
-        <v>103</v>
       </c>
       <c r="O82">
         <v>18.3</v>
@@ -4759,10 +4747,10 @@
         <v>0</v>
       </c>
       <c r="F83" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G83" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H83">
         <v>215.65</v>
@@ -4771,19 +4759,19 @@
         <v>1</v>
       </c>
       <c r="J83" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K83">
         <v>4</v>
       </c>
       <c r="L83" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M83" t="s">
+        <v>95</v>
+      </c>
+      <c r="N83" t="s">
         <v>99</v>
-      </c>
-      <c r="N83" t="s">
-        <v>103</v>
       </c>
       <c r="O83">
         <v>18.3</v>
@@ -4809,10 +4797,10 @@
         <v>-2.4</v>
       </c>
       <c r="F84" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G84" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H84">
         <v>1379.6</v>
@@ -4821,19 +4809,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J84" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K84">
         <v>10</v>
       </c>
       <c r="L84" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M84" t="s">
+        <v>95</v>
+      </c>
+      <c r="N84" t="s">
         <v>99</v>
-      </c>
-      <c r="N84" t="s">
-        <v>103</v>
       </c>
       <c r="O84">
         <v>18.3</v>
@@ -4859,10 +4847,10 @@
         <v>0</v>
       </c>
       <c r="F85" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G85" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H85">
         <v>4454.6</v>
@@ -4871,19 +4859,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J85" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K85">
         <v>10</v>
       </c>
       <c r="L85" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M85" t="s">
+        <v>95</v>
+      </c>
+      <c r="N85" t="s">
         <v>99</v>
-      </c>
-      <c r="N85" t="s">
-        <v>103</v>
       </c>
       <c r="O85">
         <v>18.3</v>
@@ -4909,10 +4897,10 @@
         <v>0</v>
       </c>
       <c r="F86" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G86" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H86">
         <v>1044.55</v>
@@ -4921,19 +4909,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J86" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K86">
         <v>10</v>
       </c>
       <c r="L86" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M86" t="s">
+        <v>95</v>
+      </c>
+      <c r="N86" t="s">
         <v>99</v>
-      </c>
-      <c r="N86" t="s">
-        <v>103</v>
       </c>
       <c r="O86">
         <v>18.3</v>
@@ -4959,10 +4947,10 @@
         <v>0</v>
       </c>
       <c r="F87" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G87" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H87">
         <v>88.59</v>
@@ -4971,19 +4959,19 @@
         <v>2.799999999999997</v>
       </c>
       <c r="J87" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K87">
         <v>4</v>
       </c>
       <c r="L87" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M87" t="s">
+        <v>95</v>
+      </c>
+      <c r="N87" t="s">
         <v>99</v>
-      </c>
-      <c r="N87" t="s">
-        <v>103</v>
       </c>
       <c r="O87">
         <v>18.3</v>
@@ -5009,10 +4997,10 @@
         <v>0</v>
       </c>
       <c r="F88" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G88" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H88">
         <v>556.95</v>
@@ -5021,19 +5009,19 @@
         <v>4.799999999999997</v>
       </c>
       <c r="J88" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K88">
         <v>1</v>
       </c>
       <c r="L88" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M88" t="s">
+        <v>95</v>
+      </c>
+      <c r="N88" t="s">
         <v>99</v>
-      </c>
-      <c r="N88" t="s">
-        <v>103</v>
       </c>
       <c r="O88">
         <v>18.3</v>
@@ -5059,10 +5047,10 @@
         <v>0</v>
       </c>
       <c r="F89" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G89" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H89">
         <v>1395.8</v>
@@ -5071,19 +5059,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J89" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K89">
         <v>5</v>
       </c>
       <c r="L89" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M89" t="s">
+        <v>95</v>
+      </c>
+      <c r="N89" t="s">
         <v>99</v>
-      </c>
-      <c r="N89" t="s">
-        <v>103</v>
       </c>
       <c r="O89">
         <v>18.3</v>
@@ -5109,10 +5097,10 @@
         <v>0</v>
       </c>
       <c r="F90" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G90" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H90">
         <v>5977</v>
@@ -5121,19 +5109,19 @@
         <v>5.400000000000006</v>
       </c>
       <c r="J90" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K90">
         <v>1</v>
       </c>
       <c r="L90" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M90" t="s">
+        <v>95</v>
+      </c>
+      <c r="N90" t="s">
         <v>99</v>
-      </c>
-      <c r="N90" t="s">
-        <v>103</v>
       </c>
       <c r="O90">
         <v>18.3</v>
@@ -5159,10 +5147,10 @@
         <v>1</v>
       </c>
       <c r="F91" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G91" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H91">
         <v>1198.95</v>
@@ -5171,19 +5159,19 @@
         <v>6.399999999999999</v>
       </c>
       <c r="J91" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K91">
         <v>4</v>
       </c>
       <c r="L91" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M91" t="s">
+        <v>95</v>
+      </c>
+      <c r="N91" t="s">
         <v>99</v>
-      </c>
-      <c r="N91" t="s">
-        <v>103</v>
       </c>
       <c r="O91">
         <v>18.3</v>
@@ -5209,10 +5197,10 @@
         <v>-6</v>
       </c>
       <c r="F92" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G92" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H92">
         <v>1278.6</v>
@@ -5221,19 +5209,19 @@
         <v>8.899999999999999</v>
       </c>
       <c r="J92" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K92">
         <v>4</v>
       </c>
       <c r="L92" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M92" t="s">
+        <v>95</v>
+      </c>
+      <c r="N92" t="s">
         <v>99</v>
-      </c>
-      <c r="N92" t="s">
-        <v>103</v>
       </c>
       <c r="O92">
         <v>18.3</v>
@@ -5259,10 +5247,10 @@
         <v>0</v>
       </c>
       <c r="F93" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G93" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H93">
         <v>9602</v>
@@ -5271,19 +5259,19 @@
         <v>9.399999999999999</v>
       </c>
       <c r="J93" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K93">
         <v>10</v>
       </c>
       <c r="L93" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M93" t="s">
+        <v>95</v>
+      </c>
+      <c r="N93" t="s">
         <v>99</v>
-      </c>
-      <c r="N93" t="s">
-        <v>103</v>
       </c>
       <c r="O93">
         <v>18.3</v>
@@ -5309,10 +5297,10 @@
         <v>0</v>
       </c>
       <c r="F94" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G94" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H94">
         <v>319.75</v>
@@ -5321,19 +5309,19 @@
         <v>10.9</v>
       </c>
       <c r="J94" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K94">
         <v>10</v>
       </c>
       <c r="L94" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M94" t="s">
+        <v>95</v>
+      </c>
+      <c r="N94" t="s">
         <v>99</v>
-      </c>
-      <c r="N94" t="s">
-        <v>103</v>
       </c>
       <c r="O94">
         <v>18.3</v>
@@ -5359,10 +5347,10 @@
         <v>0</v>
       </c>
       <c r="F95" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G95" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H95">
         <v>2307.9</v>
@@ -5371,19 +5359,19 @@
         <v>11.2</v>
       </c>
       <c r="J95" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K95">
         <v>4</v>
       </c>
       <c r="L95" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M95" t="s">
+        <v>95</v>
+      </c>
+      <c r="N95" t="s">
         <v>99</v>
-      </c>
-      <c r="N95" t="s">
-        <v>103</v>
       </c>
       <c r="O95">
         <v>18.3</v>
@@ -5409,10 +5397,10 @@
         <v>0</v>
       </c>
       <c r="F96" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G96" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H96">
         <v>4021.1</v>
@@ -5421,19 +5409,19 @@
         <v>12.8</v>
       </c>
       <c r="J96" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K96">
         <v>6</v>
       </c>
       <c r="L96" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M96" t="s">
+        <v>95</v>
+      </c>
+      <c r="N96" t="s">
         <v>99</v>
-      </c>
-      <c r="N96" t="s">
-        <v>103</v>
       </c>
       <c r="O96">
         <v>18.3</v>
@@ -5459,10 +5447,10 @@
         <v>0</v>
       </c>
       <c r="F97" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G97" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H97">
         <v>7230</v>
@@ -5471,19 +5459,19 @@
         <v>13.2</v>
       </c>
       <c r="J97" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K97">
         <v>2</v>
       </c>
       <c r="L97" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M97" t="s">
+        <v>95</v>
+      </c>
+      <c r="N97" t="s">
         <v>99</v>
-      </c>
-      <c r="N97" t="s">
-        <v>103</v>
       </c>
       <c r="O97">
         <v>18.3</v>
@@ -5509,10 +5497,10 @@
         <v>0</v>
       </c>
       <c r="F98" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G98" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H98">
         <v>3844.3</v>
@@ -5524,13 +5512,13 @@
         <v>1</v>
       </c>
       <c r="L98" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="M98" t="s">
+        <v>95</v>
+      </c>
+      <c r="N98" t="s">
         <v>99</v>
-      </c>
-      <c r="N98" t="s">
-        <v>103</v>
       </c>
       <c r="O98">
         <v>18.3</v>
@@ -5556,10 +5544,10 @@
         <v>0</v>
       </c>
       <c r="F99" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G99" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H99">
         <v>1330.5</v>
@@ -5568,19 +5556,19 @@
         <v>0.09999999999999432</v>
       </c>
       <c r="J99" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="K99">
         <v>1</v>
       </c>
       <c r="L99" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M99" t="s">
+        <v>95</v>
+      </c>
+      <c r="N99" t="s">
         <v>99</v>
-      </c>
-      <c r="N99" t="s">
-        <v>103</v>
       </c>
       <c r="O99">
         <v>18.3</v>
@@ -5606,10 +5594,10 @@
         <v>0</v>
       </c>
       <c r="F100" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G100" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H100">
         <v>405.4</v>
@@ -5618,19 +5606,19 @@
         <v>0.7000000000000028</v>
       </c>
       <c r="J100" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K100">
         <v>1</v>
       </c>
       <c r="L100" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M100" t="s">
+        <v>95</v>
+      </c>
+      <c r="N100" t="s">
         <v>99</v>
-      </c>
-      <c r="N100" t="s">
-        <v>103</v>
       </c>
       <c r="O100">
         <v>18.3</v>
@@ -5656,10 +5644,10 @@
         <v>-1.2</v>
       </c>
       <c r="F101" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G101" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H101">
         <v>554.7</v>
@@ -5668,19 +5656,19 @@
         <v>1.599999999999994</v>
       </c>
       <c r="J101" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K101">
         <v>2</v>
       </c>
       <c r="L101" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M101" t="s">
+        <v>95</v>
+      </c>
+      <c r="N101" t="s">
         <v>99</v>
-      </c>
-      <c r="N101" t="s">
-        <v>103</v>
       </c>
       <c r="O101">
         <v>18.3</v>
@@ -5706,10 +5694,10 @@
         <v>-1.2</v>
       </c>
       <c r="F102" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G102" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H102">
         <v>215.65</v>
@@ -5718,19 +5706,19 @@
         <v>2.200000000000003</v>
       </c>
       <c r="J102" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K102">
         <v>5</v>
       </c>
       <c r="L102" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M102" t="s">
+        <v>95</v>
+      </c>
+      <c r="N102" t="s">
         <v>99</v>
-      </c>
-      <c r="N102" t="s">
-        <v>103</v>
       </c>
       <c r="O102">
         <v>18.3</v>
@@ -5756,10 +5744,10 @@
         <v>-1.2</v>
       </c>
       <c r="F103" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G103" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H103">
         <v>1379.6</v>
@@ -5768,19 +5756,19 @@
         <v>4</v>
       </c>
       <c r="J103" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K103">
         <v>11</v>
       </c>
       <c r="L103" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M103" t="s">
+        <v>95</v>
+      </c>
+      <c r="N103" t="s">
         <v>99</v>
-      </c>
-      <c r="N103" t="s">
-        <v>103</v>
       </c>
       <c r="O103">
         <v>18.3</v>
@@ -5806,10 +5794,10 @@
         <v>-1.2</v>
       </c>
       <c r="F104" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G104" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H104">
         <v>4454.6</v>
@@ -5818,19 +5806,19 @@
         <v>4</v>
       </c>
       <c r="J104" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K104">
         <v>11</v>
       </c>
       <c r="L104" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M104" t="s">
+        <v>95</v>
+      </c>
+      <c r="N104" t="s">
         <v>99</v>
-      </c>
-      <c r="N104" t="s">
-        <v>103</v>
       </c>
       <c r="O104">
         <v>18.3</v>
@@ -5856,10 +5844,10 @@
         <v>-1.2</v>
       </c>
       <c r="F105" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G105" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H105">
         <v>1044.55</v>
@@ -5868,19 +5856,19 @@
         <v>4</v>
       </c>
       <c r="J105" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K105">
         <v>11</v>
       </c>
       <c r="L105" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M105" t="s">
+        <v>95</v>
+      </c>
+      <c r="N105" t="s">
         <v>99</v>
-      </c>
-      <c r="N105" t="s">
-        <v>103</v>
       </c>
       <c r="O105">
         <v>18.3</v>
@@ -5906,10 +5894,10 @@
         <v>-1.2</v>
       </c>
       <c r="F106" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G106" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H106">
         <v>88.59</v>
@@ -5918,19 +5906,19 @@
         <v>4</v>
       </c>
       <c r="J106" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K106">
         <v>5</v>
       </c>
       <c r="L106" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M106" t="s">
+        <v>95</v>
+      </c>
+      <c r="N106" t="s">
         <v>99</v>
-      </c>
-      <c r="N106" t="s">
-        <v>103</v>
       </c>
       <c r="O106">
         <v>18.3</v>
@@ -5956,10 +5944,10 @@
         <v>-1.2</v>
       </c>
       <c r="F107" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G107" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H107">
         <v>556.95</v>
@@ -5968,19 +5956,19 @@
         <v>6</v>
       </c>
       <c r="J107" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="K107">
         <v>2</v>
       </c>
       <c r="L107" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M107" t="s">
+        <v>95</v>
+      </c>
+      <c r="N107" t="s">
         <v>99</v>
-      </c>
-      <c r="N107" t="s">
-        <v>103</v>
       </c>
       <c r="O107">
         <v>18.3</v>
@@ -6006,10 +5994,10 @@
         <v>-1.2</v>
       </c>
       <c r="F108" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G108" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H108">
         <v>1395.8</v>
@@ -6018,19 +6006,19 @@
         <v>6.600000000000001</v>
       </c>
       <c r="J108" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K108">
         <v>6</v>
       </c>
       <c r="L108" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M108" t="s">
+        <v>95</v>
+      </c>
+      <c r="N108" t="s">
         <v>99</v>
-      </c>
-      <c r="N108" t="s">
-        <v>103</v>
       </c>
       <c r="O108">
         <v>18.3</v>
@@ -6056,10 +6044,10 @@
         <v>-1.2</v>
       </c>
       <c r="F109" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G109" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H109">
         <v>5977</v>
@@ -6068,19 +6056,19 @@
         <v>6.600000000000001</v>
       </c>
       <c r="J109" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K109">
         <v>2</v>
       </c>
       <c r="L109" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M109" t="s">
+        <v>95</v>
+      </c>
+      <c r="N109" t="s">
         <v>99</v>
-      </c>
-      <c r="N109" t="s">
-        <v>103</v>
       </c>
       <c r="O109">
         <v>18.3</v>
@@ -6106,10 +6094,10 @@
         <v>-1.2</v>
       </c>
       <c r="F110" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G110" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H110">
         <v>1198.95</v>
@@ -6118,19 +6106,19 @@
         <v>7.600000000000001</v>
       </c>
       <c r="J110" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K110">
         <v>5</v>
       </c>
       <c r="L110" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M110" t="s">
+        <v>95</v>
+      </c>
+      <c r="N110" t="s">
         <v>99</v>
-      </c>
-      <c r="N110" t="s">
-        <v>103</v>
       </c>
       <c r="O110">
         <v>18.3</v>
@@ -6156,10 +6144,10 @@
         <v>-1.2</v>
       </c>
       <c r="F111" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G111" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H111">
         <v>1278.6</v>
@@ -6168,19 +6156,19 @@
         <v>10.1</v>
       </c>
       <c r="J111" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K111">
         <v>5</v>
       </c>
       <c r="L111" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M111" t="s">
+        <v>95</v>
+      </c>
+      <c r="N111" t="s">
         <v>99</v>
-      </c>
-      <c r="N111" t="s">
-        <v>103</v>
       </c>
       <c r="O111">
         <v>18.3</v>
@@ -6206,10 +6194,10 @@
         <v>-1.2</v>
       </c>
       <c r="F112" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G112" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H112">
         <v>9602</v>
@@ -6218,19 +6206,19 @@
         <v>10.6</v>
       </c>
       <c r="J112" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K112">
         <v>11</v>
       </c>
       <c r="L112" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M112" t="s">
+        <v>95</v>
+      </c>
+      <c r="N112" t="s">
         <v>99</v>
-      </c>
-      <c r="N112" t="s">
-        <v>103</v>
       </c>
       <c r="O112">
         <v>18.3</v>
@@ -6256,10 +6244,10 @@
         <v>-1.2</v>
       </c>
       <c r="F113" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G113" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H113">
         <v>319.75</v>
@@ -6268,19 +6256,19 @@
         <v>12.1</v>
       </c>
       <c r="J113" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K113">
         <v>11</v>
       </c>
       <c r="L113" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M113" t="s">
+        <v>95</v>
+      </c>
+      <c r="N113" t="s">
         <v>99</v>
-      </c>
-      <c r="N113" t="s">
-        <v>103</v>
       </c>
       <c r="O113">
         <v>18.3</v>
@@ -6306,10 +6294,10 @@
         <v>-1.2</v>
       </c>
       <c r="F114" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G114" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H114">
         <v>2307.9</v>
@@ -6318,19 +6306,19 @@
         <v>12.4</v>
       </c>
       <c r="J114" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K114">
         <v>5</v>
       </c>
       <c r="L114" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M114" t="s">
+        <v>95</v>
+      </c>
+      <c r="N114" t="s">
         <v>99</v>
-      </c>
-      <c r="N114" t="s">
-        <v>103</v>
       </c>
       <c r="O114">
         <v>18.3</v>
@@ -6356,10 +6344,10 @@
         <v>-1.2</v>
       </c>
       <c r="F115" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G115" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H115">
         <v>4021.1</v>
@@ -6368,19 +6356,19 @@
         <v>14</v>
       </c>
       <c r="J115" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K115">
         <v>7</v>
       </c>
       <c r="L115" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M115" t="s">
+        <v>95</v>
+      </c>
+      <c r="N115" t="s">
         <v>99</v>
-      </c>
-      <c r="N115" t="s">
-        <v>103</v>
       </c>
       <c r="O115">
         <v>18.3</v>
@@ -6406,10 +6394,10 @@
         <v>-1.2</v>
       </c>
       <c r="F116" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G116" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H116">
         <v>7230</v>
@@ -6418,19 +6406,19 @@
         <v>14.4</v>
       </c>
       <c r="J116" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K116">
         <v>3</v>
       </c>
       <c r="L116" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M116" t="s">
+        <v>95</v>
+      </c>
+      <c r="N116" t="s">
         <v>99</v>
-      </c>
-      <c r="N116" t="s">
-        <v>103</v>
       </c>
       <c r="O116">
         <v>18.3</v>
@@ -6456,10 +6444,10 @@
         <v>6.5</v>
       </c>
       <c r="F117" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G117" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H117">
         <v>1263</v>
@@ -6468,19 +6456,19 @@
         <v>3.599999999999994</v>
       </c>
       <c r="J117" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K117">
         <v>6</v>
       </c>
       <c r="L117" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M117" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N117" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O117">
         <v>18.7</v>
@@ -6506,10 +6494,10 @@
         <v>0</v>
       </c>
       <c r="F118" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G118" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H118">
         <v>123.95</v>
@@ -6518,19 +6506,19 @@
         <v>5.5</v>
       </c>
       <c r="J118" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K118">
         <v>1</v>
       </c>
       <c r="L118" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M118" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N118" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O118">
         <v>18.7</v>
@@ -6556,10 +6544,10 @@
         <v>-2</v>
       </c>
       <c r="F119" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G119" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H119">
         <v>1371.6</v>
@@ -6568,19 +6556,19 @@
         <v>6</v>
       </c>
       <c r="J119" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K119">
         <v>12</v>
       </c>
       <c r="L119" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M119" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N119" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O119">
         <v>18.7</v>
@@ -6606,10 +6594,10 @@
         <v>-2</v>
       </c>
       <c r="F120" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G120" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H120">
         <v>4460</v>
@@ -6618,19 +6606,19 @@
         <v>6</v>
       </c>
       <c r="J120" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K120">
         <v>12</v>
       </c>
       <c r="L120" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M120" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N120" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O120">
         <v>18.7</v>
@@ -6656,10 +6644,10 @@
         <v>6.4</v>
       </c>
       <c r="F121" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G121" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H121">
         <v>2358.2</v>
@@ -6668,19 +6656,19 @@
         <v>6</v>
       </c>
       <c r="J121" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K121">
         <v>6</v>
       </c>
       <c r="L121" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M121" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N121" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O121">
         <v>18.7</v>
@@ -6706,10 +6694,10 @@
         <v>-5.4</v>
       </c>
       <c r="F122" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G122" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H122">
         <v>402.65</v>
@@ -6718,19 +6706,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J122" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K122">
         <v>2</v>
       </c>
       <c r="L122" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M122" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N122" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O122">
         <v>18.7</v>
@@ -6756,10 +6744,10 @@
         <v>0</v>
       </c>
       <c r="F123" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G123" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H123">
         <v>3858.9</v>
@@ -6768,19 +6756,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J123" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K123">
         <v>1</v>
       </c>
       <c r="L123" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M123" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N123" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O123">
         <v>18.7</v>
@@ -6806,10 +6794,10 @@
         <v>4</v>
       </c>
       <c r="F124" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G124" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H124">
         <v>320.55</v>
@@ -6818,19 +6806,19 @@
         <v>8.100000000000001</v>
       </c>
       <c r="J124" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K124">
         <v>12</v>
       </c>
       <c r="L124" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M124" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N124" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O124">
         <v>18.7</v>
@@ -6856,10 +6844,10 @@
         <v>-6.4</v>
       </c>
       <c r="F125" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G125" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H125">
         <v>214.68</v>
@@ -6868,19 +6856,19 @@
         <v>8.600000000000001</v>
       </c>
       <c r="J125" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K125">
         <v>6</v>
       </c>
       <c r="L125" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M125" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N125" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O125">
         <v>18.7</v>
@@ -6906,10 +6894,10 @@
         <v>-5</v>
       </c>
       <c r="F126" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G126" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H126">
         <v>1019.75</v>
@@ -6918,19 +6906,19 @@
         <v>9</v>
       </c>
       <c r="J126" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K126">
         <v>12</v>
       </c>
       <c r="L126" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M126" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N126" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O126">
         <v>18.7</v>
@@ -6956,10 +6944,10 @@
         <v>-5</v>
       </c>
       <c r="F127" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G127" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H127">
         <v>86.98</v>
@@ -6968,19 +6956,19 @@
         <v>9</v>
       </c>
       <c r="J127" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K127">
         <v>6</v>
       </c>
       <c r="L127" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M127" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N127" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O127">
         <v>18.7</v>
@@ -7006,10 +6994,10 @@
         <v>0</v>
       </c>
       <c r="F128" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G128" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H128">
         <v>125.61</v>
@@ -7018,19 +7006,19 @@
         <v>10</v>
       </c>
       <c r="J128" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K128">
         <v>1</v>
       </c>
       <c r="L128" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M128" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N128" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O128">
         <v>18.7</v>
@@ -7056,10 +7044,10 @@
         <v>-4</v>
       </c>
       <c r="F129" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G129" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H129">
         <v>1404.6</v>
@@ -7068,19 +7056,19 @@
         <v>10.6</v>
       </c>
       <c r="J129" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K129">
         <v>7</v>
       </c>
       <c r="L129" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M129" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N129" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O129">
         <v>18.7</v>
@@ -7106,10 +7094,10 @@
         <v>-3</v>
       </c>
       <c r="F130" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G130" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H130">
         <v>1217.2</v>
@@ -7118,19 +7106,19 @@
         <v>10.6</v>
       </c>
       <c r="J130" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K130">
         <v>6</v>
       </c>
       <c r="L130" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M130" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N130" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O130">
         <v>18.7</v>
@@ -7156,10 +7144,10 @@
         <v>0</v>
       </c>
       <c r="F131" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G131" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H131">
         <v>445.5</v>
@@ -7168,19 +7156,19 @@
         <v>12.7</v>
       </c>
       <c r="J131" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="K131">
         <v>1</v>
       </c>
       <c r="L131" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M131" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N131" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O131">
         <v>18.7</v>
@@ -7206,10 +7194,10 @@
         <v>-3.8</v>
       </c>
       <c r="F132" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G132" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H132">
         <v>9519</v>
@@ -7218,19 +7206,19 @@
         <v>14.4</v>
       </c>
       <c r="J132" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K132">
         <v>12</v>
       </c>
       <c r="L132" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M132" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N132" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O132">
         <v>18.7</v>
@@ -7256,10 +7244,10 @@
         <v>0</v>
       </c>
       <c r="F133" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G133" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H133">
         <v>1263.2</v>
@@ -7268,19 +7256,19 @@
         <v>3.599999999999994</v>
       </c>
       <c r="J133" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K133">
         <v>7</v>
       </c>
       <c r="L133" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M133" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N133" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O133">
         <v>18.84</v>
@@ -7306,10 +7294,10 @@
         <v>0</v>
       </c>
       <c r="F134" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G134" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H134">
         <v>124.1</v>
@@ -7318,19 +7306,19 @@
         <v>5.5</v>
       </c>
       <c r="J134" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K134">
         <v>2</v>
       </c>
       <c r="L134" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M134" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N134" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O134">
         <v>18.84</v>
@@ -7356,10 +7344,10 @@
         <v>0</v>
       </c>
       <c r="F135" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G135" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H135">
         <v>1371.2</v>
@@ -7368,19 +7356,19 @@
         <v>6</v>
       </c>
       <c r="J135" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K135">
         <v>13</v>
       </c>
       <c r="L135" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M135" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N135" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O135">
         <v>18.84</v>
@@ -7406,10 +7394,10 @@
         <v>0</v>
       </c>
       <c r="F136" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G136" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H136">
         <v>4440.2</v>
@@ -7418,19 +7406,19 @@
         <v>6</v>
       </c>
       <c r="J136" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K136">
         <v>13</v>
       </c>
       <c r="L136" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M136" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N136" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O136">
         <v>18.84</v>
@@ -7456,10 +7444,10 @@
         <v>0</v>
       </c>
       <c r="F137" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G137" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H137">
         <v>2353.4</v>
@@ -7468,19 +7456,19 @@
         <v>6</v>
       </c>
       <c r="J137" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K137">
         <v>7</v>
       </c>
       <c r="L137" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M137" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N137" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O137">
         <v>18.84</v>
@@ -7506,10 +7494,10 @@
         <v>0</v>
       </c>
       <c r="F138" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G138" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H138">
         <v>400.9</v>
@@ -7518,19 +7506,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J138" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K138">
         <v>3</v>
       </c>
       <c r="L138" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M138" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N138" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O138">
         <v>18.84</v>
@@ -7556,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="F139" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G139" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H139">
         <v>3856.3</v>
@@ -7568,19 +7556,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J139" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K139">
         <v>2</v>
       </c>
       <c r="L139" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M139" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N139" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O139">
         <v>18.84</v>
@@ -7606,10 +7594,10 @@
         <v>0</v>
       </c>
       <c r="F140" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G140" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H140">
         <v>214.69</v>
@@ -7618,19 +7606,19 @@
         <v>8.600000000000001</v>
       </c>
       <c r="J140" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K140">
         <v>7</v>
       </c>
       <c r="L140" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M140" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N140" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O140">
         <v>18.84</v>
@@ -7656,10 +7644,10 @@
         <v>0</v>
       </c>
       <c r="F141" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G141" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H141">
         <v>1020.55</v>
@@ -7668,19 +7656,19 @@
         <v>9</v>
       </c>
       <c r="J141" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K141">
         <v>13</v>
       </c>
       <c r="L141" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M141" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N141" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O141">
         <v>18.84</v>
@@ -7706,10 +7694,10 @@
         <v>0</v>
       </c>
       <c r="F142" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G142" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H142">
         <v>87.06999999999999</v>
@@ -7718,19 +7706,19 @@
         <v>9</v>
       </c>
       <c r="J142" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K142">
         <v>7</v>
       </c>
       <c r="L142" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M142" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N142" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O142">
         <v>18.84</v>
@@ -7756,10 +7744,10 @@
         <v>0</v>
       </c>
       <c r="F143" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G143" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H143">
         <v>125.46</v>
@@ -7768,19 +7756,19 @@
         <v>10</v>
       </c>
       <c r="J143" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K143">
         <v>2</v>
       </c>
       <c r="L143" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M143" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N143" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O143">
         <v>18.84</v>
@@ -7806,10 +7794,10 @@
         <v>0</v>
       </c>
       <c r="F144" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G144" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H144">
         <v>1401.1</v>
@@ -7818,19 +7806,19 @@
         <v>10.6</v>
       </c>
       <c r="J144" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K144">
         <v>8</v>
       </c>
       <c r="L144" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M144" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N144" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O144">
         <v>18.84</v>
@@ -7856,10 +7844,10 @@
         <v>0</v>
       </c>
       <c r="F145" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G145" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H145">
         <v>1218.2</v>
@@ -7868,19 +7856,19 @@
         <v>10.6</v>
       </c>
       <c r="J145" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K145">
         <v>7</v>
       </c>
       <c r="L145" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M145" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N145" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O145">
         <v>18.84</v>
@@ -7906,10 +7894,10 @@
         <v>0</v>
       </c>
       <c r="F146" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G146" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H146">
         <v>445.65</v>
@@ -7918,19 +7906,19 @@
         <v>12.7</v>
       </c>
       <c r="J146" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="K146">
         <v>2</v>
       </c>
       <c r="L146" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M146" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N146" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O146">
         <v>18.84</v>
@@ -7956,10 +7944,10 @@
         <v>-6</v>
       </c>
       <c r="F147" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G147" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H147">
         <v>319.85</v>
@@ -7968,19 +7956,19 @@
         <v>14.1</v>
       </c>
       <c r="J147" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K147">
         <v>13</v>
       </c>
       <c r="L147" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M147" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N147" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O147">
         <v>18.84</v>
@@ -8006,10 +7994,10 @@
         <v>0</v>
       </c>
       <c r="F148" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G148" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H148">
         <v>9545.5</v>
@@ -8018,19 +8006,19 @@
         <v>14.4</v>
       </c>
       <c r="J148" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K148">
         <v>13</v>
       </c>
       <c r="L148" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M148" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N148" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O148">
         <v>18.84</v>
@@ -8056,10 +8044,10 @@
         <v>0.5</v>
       </c>
       <c r="F149" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G149" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H149">
         <v>1262.7</v>
@@ -8068,19 +8056,19 @@
         <v>3.099999999999994</v>
       </c>
       <c r="J149" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K149">
         <v>8</v>
       </c>
       <c r="L149" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M149" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N149" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O149">
         <v>18.44</v>
@@ -8106,10 +8094,10 @@
         <v>2.9</v>
       </c>
       <c r="F150" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G150" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H150">
         <v>404.6</v>
@@ -8118,19 +8106,19 @@
         <v>3.200000000000003</v>
       </c>
       <c r="J150" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K150">
         <v>4</v>
       </c>
       <c r="L150" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M150" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N150" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O150">
         <v>18.44</v>
@@ -8156,10 +8144,10 @@
         <v>0.5</v>
       </c>
       <c r="F151" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G151" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H151">
         <v>124.38</v>
@@ -8168,19 +8156,19 @@
         <v>5</v>
       </c>
       <c r="J151" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K151">
         <v>3</v>
       </c>
       <c r="L151" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M151" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N151" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O151">
         <v>18.44</v>
@@ -8206,10 +8194,10 @@
         <v>0.5</v>
       </c>
       <c r="F152" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G152" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H152">
         <v>1376.9</v>
@@ -8218,19 +8206,19 @@
         <v>5.5</v>
       </c>
       <c r="J152" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K152">
         <v>14</v>
       </c>
       <c r="L152" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M152" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N152" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O152">
         <v>18.44</v>
@@ -8256,10 +8244,10 @@
         <v>0.5</v>
       </c>
       <c r="F153" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G153" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H153">
         <v>4456.2</v>
@@ -8268,19 +8256,19 @@
         <v>5.5</v>
       </c>
       <c r="J153" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K153">
         <v>14</v>
       </c>
       <c r="L153" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M153" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N153" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O153">
         <v>18.44</v>
@@ -8306,10 +8294,10 @@
         <v>0.5</v>
       </c>
       <c r="F154" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G154" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H154">
         <v>2358.9</v>
@@ -8318,19 +8306,19 @@
         <v>5.5</v>
       </c>
       <c r="J154" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K154">
         <v>8</v>
       </c>
       <c r="L154" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M154" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N154" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O154">
         <v>18.44</v>
@@ -8356,10 +8344,10 @@
         <v>0.5</v>
       </c>
       <c r="F155" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G155" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H155">
         <v>3875.6</v>
@@ -8368,19 +8356,19 @@
         <v>5.599999999999994</v>
       </c>
       <c r="J155" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K155">
         <v>3</v>
       </c>
       <c r="L155" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M155" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N155" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O155">
         <v>18.44</v>
@@ -8406,10 +8394,10 @@
         <v>3.9</v>
       </c>
       <c r="F156" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G156" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H156">
         <v>1231.65</v>
@@ -8418,19 +8406,19 @@
         <v>6.700000000000003</v>
       </c>
       <c r="J156" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K156">
         <v>8</v>
       </c>
       <c r="L156" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M156" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N156" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O156">
         <v>18.44</v>
@@ -8456,10 +8444,10 @@
         <v>1.5</v>
       </c>
       <c r="F157" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G157" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H157">
         <v>215.19</v>
@@ -8468,19 +8456,19 @@
         <v>7.100000000000001</v>
       </c>
       <c r="J157" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K157">
         <v>8</v>
       </c>
       <c r="L157" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M157" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N157" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O157">
         <v>18.44</v>
@@ -8506,10 +8494,10 @@
         <v>0.5</v>
       </c>
       <c r="F158" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G158" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H158">
         <v>1016.45</v>
@@ -8518,19 +8506,19 @@
         <v>8.5</v>
       </c>
       <c r="J158" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K158">
         <v>14</v>
       </c>
       <c r="L158" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M158" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N158" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O158">
         <v>18.44</v>
@@ -8556,10 +8544,10 @@
         <v>0.5</v>
       </c>
       <c r="F159" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G159" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H159">
         <v>87.40000000000001</v>
@@ -8568,19 +8556,19 @@
         <v>8.5</v>
       </c>
       <c r="J159" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K159">
         <v>8</v>
       </c>
       <c r="L159" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M159" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N159" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O159">
         <v>18.44</v>
@@ -8606,10 +8594,10 @@
         <v>1.5</v>
       </c>
       <c r="F160" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G160" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H160">
         <v>1408.8</v>
@@ -8618,19 +8606,19 @@
         <v>9.100000000000001</v>
       </c>
       <c r="J160" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K160">
         <v>9</v>
       </c>
       <c r="L160" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M160" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N160" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O160">
         <v>18.44</v>
@@ -8656,10 +8644,10 @@
         <v>0.5</v>
       </c>
       <c r="F161" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G161" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H161">
         <v>125.82</v>
@@ -8668,19 +8656,19 @@
         <v>9.5</v>
       </c>
       <c r="J161" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K161">
         <v>3</v>
       </c>
       <c r="L161" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M161" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N161" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O161">
         <v>18.44</v>
@@ -8706,10 +8694,10 @@
         <v>0.5</v>
       </c>
       <c r="F162" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G162" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H162">
         <v>451.3</v>
@@ -8718,19 +8706,19 @@
         <v>12.2</v>
       </c>
       <c r="J162" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="K162">
         <v>3</v>
       </c>
       <c r="L162" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M162" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N162" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O162">
         <v>18.44</v>
@@ -8756,10 +8744,10 @@
         <v>0.5</v>
       </c>
       <c r="F163" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G163" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H163">
         <v>320.1</v>
@@ -8768,19 +8756,19 @@
         <v>13.6</v>
       </c>
       <c r="J163" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K163">
         <v>14</v>
       </c>
       <c r="L163" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M163" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N163" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O163">
         <v>18.44</v>
@@ -8806,10 +8794,10 @@
         <v>0.5</v>
       </c>
       <c r="F164" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G164" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H164">
         <v>9549.5</v>
@@ -8818,19 +8806,19 @@
         <v>13.9</v>
       </c>
       <c r="J164" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K164">
         <v>14</v>
       </c>
       <c r="L164" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M164" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N164" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="O164">
         <v>18.44</v>
@@ -8856,10 +8844,10 @@
         <v>0</v>
       </c>
       <c r="F165" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G165" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H165">
         <v>6727</v>
@@ -8871,13 +8859,13 @@
         <v>1</v>
       </c>
       <c r="L165" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="M165" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N165" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O165">
         <v>18.59</v>
@@ -8903,10 +8891,10 @@
         <v>0</v>
       </c>
       <c r="F166" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G166" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H166">
         <v>4135.1</v>
@@ -8918,13 +8906,13 @@
         <v>1</v>
       </c>
       <c r="L166" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="M166" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N166" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O166">
         <v>18.59</v>
@@ -8950,10 +8938,10 @@
         <v>0</v>
       </c>
       <c r="F167" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G167" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H167">
         <v>297</v>
@@ -8962,19 +8950,19 @@
         <v>0.7000000000000028</v>
       </c>
       <c r="J167" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K167">
         <v>1</v>
       </c>
       <c r="L167" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M167" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N167" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O167">
         <v>18.59</v>
@@ -9000,10 +8988,10 @@
         <v>0</v>
       </c>
       <c r="F168" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G168" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H168">
         <v>2335</v>
@@ -9012,19 +9000,19 @@
         <v>1.700000000000003</v>
       </c>
       <c r="J168" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K168">
         <v>1</v>
       </c>
       <c r="L168" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M168" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N168" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O168">
         <v>18.59</v>
@@ -9050,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="F169" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G169" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H169">
         <v>295.4</v>
@@ -9062,19 +9050,19 @@
         <v>3.599999999999994</v>
       </c>
       <c r="J169" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K169">
         <v>1</v>
       </c>
       <c r="L169" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M169" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N169" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O169">
         <v>18.59</v>
@@ -9100,10 +9088,10 @@
         <v>0</v>
       </c>
       <c r="F170" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G170" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H170">
         <v>1435.4</v>
@@ -9112,19 +9100,19 @@
         <v>3.700000000000003</v>
       </c>
       <c r="J170" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K170">
         <v>1</v>
       </c>
       <c r="L170" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M170" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N170" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O170">
         <v>18.59</v>
@@ -9150,10 +9138,10 @@
         <v>0</v>
       </c>
       <c r="F171" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G171" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H171">
         <v>1460.2</v>
@@ -9162,19 +9150,19 @@
         <v>4.599999999999994</v>
       </c>
       <c r="J171" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K171">
         <v>1</v>
       </c>
       <c r="L171" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M171" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N171" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O171">
         <v>18.59</v>
@@ -9200,10 +9188,10 @@
         <v>-0.5</v>
       </c>
       <c r="F172" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G172" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H172">
         <v>1369.6</v>
@@ -9212,19 +9200,19 @@
         <v>6</v>
       </c>
       <c r="J172" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K172">
         <v>15</v>
       </c>
       <c r="L172" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M172" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N172" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O172">
         <v>18.59</v>
@@ -9250,10 +9238,10 @@
         <v>-0.5</v>
       </c>
       <c r="F173" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G173" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H173">
         <v>4456.5</v>
@@ -9262,19 +9250,19 @@
         <v>6</v>
       </c>
       <c r="J173" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K173">
         <v>15</v>
       </c>
       <c r="L173" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M173" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N173" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O173">
         <v>18.59</v>
@@ -9300,10 +9288,10 @@
         <v>-2.9</v>
       </c>
       <c r="F174" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G174" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H174">
         <v>402.25</v>
@@ -9312,19 +9300,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J174" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K174">
         <v>5</v>
       </c>
       <c r="L174" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M174" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N174" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O174">
         <v>18.59</v>
@@ -9350,10 +9338,10 @@
         <v>0</v>
       </c>
       <c r="F175" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G175" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H175">
         <v>2022.9</v>
@@ -9362,19 +9350,19 @@
         <v>8.5</v>
       </c>
       <c r="J175" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K175">
         <v>1</v>
       </c>
       <c r="L175" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M175" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N175" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O175">
         <v>18.59</v>
@@ -9400,10 +9388,10 @@
         <v>0.5</v>
       </c>
       <c r="F176" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G176" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H176">
         <v>1410.5</v>
@@ -9412,19 +9400,19 @@
         <v>8.600000000000001</v>
       </c>
       <c r="J176" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K176">
         <v>10</v>
       </c>
       <c r="L176" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M176" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N176" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O176">
         <v>18.59</v>
@@ -9450,10 +9438,10 @@
         <v>0</v>
       </c>
       <c r="F177" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G177" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H177">
         <v>1056.25</v>
@@ -9462,19 +9450,19 @@
         <v>8.600000000000001</v>
       </c>
       <c r="J177" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K177">
         <v>1</v>
       </c>
       <c r="L177" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M177" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N177" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O177">
         <v>18.59</v>
@@ -9500,10 +9488,10 @@
         <v>0</v>
       </c>
       <c r="F178" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G178" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H178">
         <v>187.01</v>
@@ -9512,19 +9500,19 @@
         <v>9.100000000000001</v>
       </c>
       <c r="J178" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K178">
         <v>1</v>
       </c>
       <c r="L178" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M178" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N178" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O178">
         <v>18.59</v>
@@ -9550,10 +9538,10 @@
         <v>0</v>
       </c>
       <c r="F179" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G179" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H179">
         <v>180.18</v>
@@ -9562,19 +9550,19 @@
         <v>10.6</v>
       </c>
       <c r="J179" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K179">
         <v>1</v>
       </c>
       <c r="L179" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M179" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N179" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O179">
         <v>18.59</v>
@@ -9600,10 +9588,10 @@
         <v>0</v>
       </c>
       <c r="F180" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G180" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H180">
         <v>243.68</v>
@@ -9612,19 +9600,19 @@
         <v>10.6</v>
       </c>
       <c r="J180" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K180">
         <v>1</v>
       </c>
       <c r="L180" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M180" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N180" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O180">
         <v>18.59</v>
@@ -9650,10 +9638,10 @@
         <v>-0.5</v>
       </c>
       <c r="F181" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G181" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H181">
         <v>450.65</v>
@@ -9662,19 +9650,19 @@
         <v>12.7</v>
       </c>
       <c r="J181" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="K181">
         <v>4</v>
       </c>
       <c r="L181" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M181" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N181" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O181">
         <v>18.59</v>
@@ -9700,10 +9688,10 @@
         <v>0</v>
       </c>
       <c r="F182" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G182" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H182">
         <v>97.75</v>
@@ -9712,19 +9700,19 @@
         <v>13.1</v>
       </c>
       <c r="J182" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K182">
         <v>1</v>
       </c>
       <c r="L182" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M182" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N182" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O182">
         <v>18.59</v>
@@ -9750,10 +9738,10 @@
         <v>0.5</v>
       </c>
       <c r="F183" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G183" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H183">
         <v>9550.5</v>
@@ -9762,19 +9750,19 @@
         <v>13.4</v>
       </c>
       <c r="J183" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K183">
         <v>15</v>
       </c>
       <c r="L183" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M183" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N183" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O183">
         <v>18.59</v>
@@ -9800,10 +9788,10 @@
         <v>-0.5</v>
       </c>
       <c r="F184" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G184" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H184">
         <v>319.15</v>
@@ -9812,19 +9800,19 @@
         <v>14.1</v>
       </c>
       <c r="J184" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K184">
         <v>15</v>
       </c>
       <c r="L184" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M184" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N184" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O184">
         <v>18.59</v>
@@ -9850,10 +9838,10 @@
         <v>0</v>
       </c>
       <c r="F185" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G185" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="H185">
         <v>6727</v>
@@ -9865,13 +9853,13 @@
         <v>1</v>
       </c>
       <c r="L185" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="M185" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N185" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O185">
         <v>18.59</v>
@@ -9897,10 +9885,10 @@
         <v>0</v>
       </c>
       <c r="F186" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G186" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H186">
         <v>4135.1</v>
@@ -9912,13 +9900,13 @@
         <v>1</v>
       </c>
       <c r="L186" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="M186" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N186" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O186">
         <v>18.59</v>
@@ -9944,10 +9932,10 @@
         <v>0</v>
       </c>
       <c r="F187" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G187" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H187">
         <v>297</v>
@@ -9956,19 +9944,19 @@
         <v>0.7000000000000028</v>
       </c>
       <c r="J187" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K187">
         <v>2</v>
       </c>
       <c r="L187" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M187" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N187" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O187">
         <v>18.59</v>
@@ -9994,10 +9982,10 @@
         <v>0</v>
       </c>
       <c r="F188" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G188" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H188">
         <v>2335</v>
@@ -10006,19 +9994,19 @@
         <v>1.700000000000003</v>
       </c>
       <c r="J188" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K188">
         <v>2</v>
       </c>
       <c r="L188" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M188" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N188" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O188">
         <v>18.59</v>
@@ -10044,10 +10032,10 @@
         <v>0</v>
       </c>
       <c r="F189" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G189" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H189">
         <v>295.4</v>
@@ -10056,19 +10044,19 @@
         <v>3.599999999999994</v>
       </c>
       <c r="J189" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K189">
         <v>2</v>
       </c>
       <c r="L189" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M189" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N189" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O189">
         <v>18.59</v>
@@ -10094,10 +10082,10 @@
         <v>0</v>
       </c>
       <c r="F190" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G190" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H190">
         <v>1435.4</v>
@@ -10106,19 +10094,19 @@
         <v>3.700000000000003</v>
       </c>
       <c r="J190" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K190">
         <v>2</v>
       </c>
       <c r="L190" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M190" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N190" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O190">
         <v>18.59</v>
@@ -10144,10 +10132,10 @@
         <v>0</v>
       </c>
       <c r="F191" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G191" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H191">
         <v>1460.2</v>
@@ -10156,19 +10144,19 @@
         <v>4.599999999999994</v>
       </c>
       <c r="J191" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="K191">
         <v>2</v>
       </c>
       <c r="L191" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M191" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N191" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O191">
         <v>18.59</v>
@@ -10194,10 +10182,10 @@
         <v>0</v>
       </c>
       <c r="F192" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G192" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H192">
         <v>1369.6</v>
@@ -10206,19 +10194,19 @@
         <v>6</v>
       </c>
       <c r="J192" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K192">
         <v>16</v>
       </c>
       <c r="L192" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M192" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N192" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O192">
         <v>18.59</v>
@@ -10244,10 +10232,10 @@
         <v>0</v>
       </c>
       <c r="F193" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G193" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H193">
         <v>4456.5</v>
@@ -10256,19 +10244,19 @@
         <v>6</v>
       </c>
       <c r="J193" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K193">
         <v>16</v>
       </c>
       <c r="L193" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M193" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N193" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O193">
         <v>18.59</v>
@@ -10294,10 +10282,10 @@
         <v>0</v>
       </c>
       <c r="F194" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G194" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H194">
         <v>402.25</v>
@@ -10306,19 +10294,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J194" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K194">
         <v>6</v>
       </c>
       <c r="L194" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M194" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N194" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O194">
         <v>18.59</v>
@@ -10344,10 +10332,10 @@
         <v>0</v>
       </c>
       <c r="F195" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G195" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H195">
         <v>2022.9</v>
@@ -10356,19 +10344,19 @@
         <v>8.5</v>
       </c>
       <c r="J195" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K195">
         <v>2</v>
       </c>
       <c r="L195" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M195" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N195" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O195">
         <v>18.59</v>
@@ -10394,10 +10382,10 @@
         <v>0</v>
       </c>
       <c r="F196" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G196" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H196">
         <v>1410.5</v>
@@ -10406,19 +10394,19 @@
         <v>8.600000000000001</v>
       </c>
       <c r="J196" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K196">
         <v>11</v>
       </c>
       <c r="L196" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M196" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N196" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O196">
         <v>18.59</v>
@@ -10444,10 +10432,10 @@
         <v>0</v>
       </c>
       <c r="F197" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G197" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H197">
         <v>1056.25</v>
@@ -10456,19 +10444,19 @@
         <v>8.600000000000001</v>
       </c>
       <c r="J197" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K197">
         <v>2</v>
       </c>
       <c r="L197" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M197" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N197" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O197">
         <v>18.59</v>
@@ -10494,10 +10482,10 @@
         <v>0</v>
       </c>
       <c r="F198" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G198" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H198">
         <v>187.01</v>
@@ -10506,19 +10494,19 @@
         <v>9.100000000000001</v>
       </c>
       <c r="J198" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K198">
         <v>2</v>
       </c>
       <c r="L198" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M198" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N198" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O198">
         <v>18.59</v>
@@ -10544,10 +10532,10 @@
         <v>0</v>
       </c>
       <c r="F199" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G199" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H199">
         <v>180.18</v>
@@ -10556,19 +10544,19 @@
         <v>10.6</v>
       </c>
       <c r="J199" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K199">
         <v>2</v>
       </c>
       <c r="L199" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M199" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N199" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O199">
         <v>18.59</v>
@@ -10594,10 +10582,10 @@
         <v>0</v>
       </c>
       <c r="F200" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G200" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H200">
         <v>243.68</v>
@@ -10606,19 +10594,19 @@
         <v>10.6</v>
       </c>
       <c r="J200" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K200">
         <v>2</v>
       </c>
       <c r="L200" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M200" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N200" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O200">
         <v>18.59</v>
@@ -10644,10 +10632,10 @@
         <v>0</v>
       </c>
       <c r="F201" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G201" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H201">
         <v>450.65</v>
@@ -10656,19 +10644,19 @@
         <v>12.7</v>
       </c>
       <c r="J201" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="K201">
         <v>5</v>
       </c>
       <c r="L201" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M201" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N201" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O201">
         <v>18.59</v>
@@ -10694,10 +10682,10 @@
         <v>0</v>
       </c>
       <c r="F202" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G202" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H202">
         <v>97.75</v>
@@ -10706,19 +10694,19 @@
         <v>13.1</v>
       </c>
       <c r="J202" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K202">
         <v>2</v>
       </c>
       <c r="L202" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M202" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N202" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O202">
         <v>18.59</v>
@@ -10744,10 +10732,10 @@
         <v>0</v>
       </c>
       <c r="F203" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G203" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H203">
         <v>9550.5</v>
@@ -10756,19 +10744,19 @@
         <v>13.4</v>
       </c>
       <c r="J203" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K203">
         <v>16</v>
       </c>
       <c r="L203" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M203" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N203" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O203">
         <v>18.59</v>
@@ -10794,10 +10782,10 @@
         <v>0</v>
       </c>
       <c r="F204" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G204" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H204">
         <v>319.15</v>
@@ -10806,19 +10794,19 @@
         <v>14.1</v>
       </c>
       <c r="J204" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="K204">
         <v>16</v>
       </c>
       <c r="L204" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M204" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N204" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O204">
         <v>18.59</v>
@@ -10828,8 +10816,8 @@
       </c>
     </row>
     <row r="205" spans="1:16">
-      <c r="A205" t="s">
-        <v>16</v>
+      <c r="A205">
+        <v>20260424</v>
       </c>
       <c r="B205" t="s">
         <v>40</v>
@@ -10840,14 +10828,14 @@
       <c r="D205">
         <v>63.9</v>
       </c>
-      <c r="E205" t="s">
-        <v>72</v>
+      <c r="E205">
+        <v>0</v>
       </c>
       <c r="F205" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G205" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H205">
         <v>3774</v>
@@ -10856,19 +10844,19 @@
         <v>6.100000000000001</v>
       </c>
       <c r="J205" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K205">
         <v>1</v>
       </c>
       <c r="L205" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M205" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N205" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="O205">
         <v>19.3</v>
@@ -10878,8 +10866,8 @@
       </c>
     </row>
     <row r="206" spans="1:16">
-      <c r="A206" t="s">
-        <v>16</v>
+      <c r="A206">
+        <v>20260424</v>
       </c>
       <c r="B206" t="s">
         <v>39</v>
@@ -10890,14 +10878,14 @@
       <c r="D206">
         <v>61.5</v>
       </c>
-      <c r="E206" t="s">
-        <v>73</v>
+      <c r="E206">
+        <v>-2.4</v>
       </c>
       <c r="F206" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G206" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H206">
         <v>399.75</v>
@@ -10906,19 +10894,19 @@
         <v>8.5</v>
       </c>
       <c r="J206" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K206">
         <v>7</v>
       </c>
       <c r="L206" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="M206" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N206" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="O206">
         <v>19.3</v>
@@ -10928,8 +10916,8 @@
       </c>
     </row>
     <row r="207" spans="1:16">
-      <c r="A207" t="s">
-        <v>16</v>
+      <c r="A207">
+        <v>20260424</v>
       </c>
       <c r="B207" t="s">
         <v>49</v>
@@ -10940,14 +10928,14 @@
       <c r="D207">
         <v>61.5</v>
       </c>
-      <c r="E207" t="s">
-        <v>72</v>
+      <c r="E207">
+        <v>0</v>
       </c>
       <c r="F207" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G207" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H207">
         <v>123.77</v>
@@ -10956,19 +10944,19 @@
         <v>8.5</v>
       </c>
       <c r="J207" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K207">
         <v>1</v>
       </c>
       <c r="L207" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M207" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N207" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="O207">
         <v>19.3</v>
@@ -10978,8 +10966,8 @@
       </c>
     </row>
     <row r="208" spans="1:16">
-      <c r="A208" t="s">
-        <v>16</v>
+      <c r="A208">
+        <v>20260424</v>
       </c>
       <c r="B208" t="s">
         <v>41</v>
@@ -10990,14 +10978,14 @@
       <c r="D208">
         <v>61.4</v>
       </c>
-      <c r="E208" t="s">
-        <v>72</v>
+      <c r="E208">
+        <v>0</v>
       </c>
       <c r="F208" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G208" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H208">
         <v>210.85</v>
@@ -11006,19 +10994,19 @@
         <v>8.600000000000001</v>
       </c>
       <c r="J208" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K208">
         <v>1</v>
       </c>
       <c r="L208" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M208" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N208" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="O208">
         <v>19.3</v>
@@ -11028,8 +11016,8 @@
       </c>
     </row>
     <row r="209" spans="1:16">
-      <c r="A209" t="s">
-        <v>16</v>
+      <c r="A209">
+        <v>20260424</v>
       </c>
       <c r="B209" t="s">
         <v>22</v>
@@ -11040,14 +11028,14 @@
       <c r="D209">
         <v>61</v>
       </c>
-      <c r="E209" t="s">
-        <v>74</v>
+      <c r="E209">
+        <v>-3</v>
       </c>
       <c r="F209" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G209" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H209">
         <v>1353.9</v>
@@ -11056,19 +11044,19 @@
         <v>9</v>
       </c>
       <c r="J209" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K209">
         <v>17</v>
       </c>
       <c r="L209" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M209" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N209" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="O209">
         <v>19.3</v>
@@ -11078,8 +11066,8 @@
       </c>
     </row>
     <row r="210" spans="1:16">
-      <c r="A210" t="s">
-        <v>16</v>
+      <c r="A210">
+        <v>20260424</v>
       </c>
       <c r="B210" t="s">
         <v>23</v>
@@ -11090,14 +11078,14 @@
       <c r="D210">
         <v>61</v>
       </c>
-      <c r="E210" t="s">
-        <v>74</v>
+      <c r="E210">
+        <v>-3</v>
       </c>
       <c r="F210" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G210" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H210">
         <v>4397.1</v>
@@ -11106,19 +11094,19 @@
         <v>9</v>
       </c>
       <c r="J210" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K210">
         <v>17</v>
       </c>
       <c r="L210" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M210" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N210" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="O210">
         <v>19.3</v>
@@ -11128,8 +11116,8 @@
       </c>
     </row>
     <row r="211" spans="1:16">
-      <c r="A211" t="s">
-        <v>16</v>
+      <c r="A211">
+        <v>20260424</v>
       </c>
       <c r="B211" t="s">
         <v>33</v>
@@ -11140,14 +11128,14 @@
       <c r="D211">
         <v>61</v>
       </c>
-      <c r="E211" t="s">
-        <v>75</v>
+      <c r="E211">
+        <v>4.4</v>
       </c>
       <c r="F211" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G211" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H211">
         <v>9597.5</v>
@@ -11156,19 +11144,19 @@
         <v>9</v>
       </c>
       <c r="J211" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K211">
         <v>17</v>
       </c>
       <c r="L211" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M211" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N211" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="O211">
         <v>19.3</v>
@@ -11178,8 +11166,8 @@
       </c>
     </row>
     <row r="212" spans="1:16">
-      <c r="A212" t="s">
-        <v>16</v>
+      <c r="A212">
+        <v>20260424</v>
       </c>
       <c r="B212" t="s">
         <v>42</v>
@@ -11190,14 +11178,14 @@
       <c r="D212">
         <v>61</v>
       </c>
-      <c r="E212" t="s">
-        <v>72</v>
+      <c r="E212">
+        <v>0</v>
       </c>
       <c r="F212" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G212" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H212">
         <v>86.84999999999999</v>
@@ -11206,19 +11194,19 @@
         <v>9</v>
       </c>
       <c r="J212" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K212">
         <v>1</v>
       </c>
       <c r="L212" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M212" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N212" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="O212">
         <v>19.3</v>
@@ -11228,8 +11216,8 @@
       </c>
     </row>
     <row r="213" spans="1:16">
-      <c r="A213" t="s">
-        <v>16</v>
+      <c r="A213">
+        <v>20260424</v>
       </c>
       <c r="B213" t="s">
         <v>43</v>
@@ -11240,14 +11228,14 @@
       <c r="D213">
         <v>60.4</v>
       </c>
-      <c r="E213" t="s">
-        <v>72</v>
+      <c r="E213">
+        <v>0</v>
       </c>
       <c r="F213" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G213" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H213">
         <v>1246</v>
@@ -11256,19 +11244,19 @@
         <v>9.600000000000001</v>
       </c>
       <c r="J213" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K213">
         <v>1</v>
       </c>
       <c r="L213" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M213" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N213" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="O213">
         <v>19.3</v>
@@ -11278,8 +11266,8 @@
       </c>
     </row>
     <row r="214" spans="1:16">
-      <c r="A214" t="s">
-        <v>16</v>
+      <c r="A214">
+        <v>20260424</v>
       </c>
       <c r="B214" t="s">
         <v>44</v>
@@ -11290,14 +11278,14 @@
       <c r="D214">
         <v>60</v>
       </c>
-      <c r="E214" t="s">
-        <v>72</v>
+      <c r="E214">
+        <v>0</v>
       </c>
       <c r="F214" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G214" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H214">
         <v>124.57</v>
@@ -11306,19 +11294,19 @@
         <v>10</v>
       </c>
       <c r="J214" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="K214">
         <v>1</v>
       </c>
       <c r="L214" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M214" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N214" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="O214">
         <v>19.3</v>
@@ -11328,8 +11316,8 @@
       </c>
     </row>
     <row r="215" spans="1:16">
-      <c r="A215" t="s">
-        <v>16</v>
+      <c r="A215">
+        <v>20260424</v>
       </c>
       <c r="B215" t="s">
         <v>56</v>
@@ -11340,14 +11328,14 @@
       <c r="D215">
         <v>59.7</v>
       </c>
-      <c r="E215" t="s">
-        <v>76</v>
+      <c r="E215">
+        <v>2.4</v>
       </c>
       <c r="F215" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G215" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H215">
         <v>454.95</v>
@@ -11356,19 +11344,19 @@
         <v>10.3</v>
       </c>
       <c r="J215" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="K215">
         <v>6</v>
       </c>
       <c r="L215" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="M215" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N215" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="O215">
         <v>19.3</v>
@@ -11378,8 +11366,8 @@
       </c>
     </row>
     <row r="216" spans="1:16">
-      <c r="A216" t="s">
-        <v>16</v>
+      <c r="A216">
+        <v>20260424</v>
       </c>
       <c r="B216" t="s">
         <v>32</v>
@@ -11390,14 +11378,14 @@
       <c r="D216">
         <v>59.4</v>
       </c>
-      <c r="E216" t="s">
-        <v>77</v>
+      <c r="E216">
+        <v>-2</v>
       </c>
       <c r="F216" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G216" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H216">
         <v>1417.3</v>
@@ -11406,19 +11394,19 @@
         <v>10.6</v>
       </c>
       <c r="J216" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K216">
         <v>12</v>
       </c>
       <c r="L216" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="M216" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N216" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="O216">
         <v>19.3</v>
@@ -11428,8 +11416,8 @@
       </c>
     </row>
     <row r="217" spans="1:16">
-      <c r="A217" t="s">
-        <v>16</v>
+      <c r="A217">
+        <v>20260424</v>
       </c>
       <c r="B217" t="s">
         <v>45</v>
@@ -11440,14 +11428,14 @@
       <c r="D217">
         <v>59.4</v>
       </c>
-      <c r="E217" t="s">
-        <v>72</v>
+      <c r="E217">
+        <v>0</v>
       </c>
       <c r="F217" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G217" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H217">
         <v>1167.1</v>
@@ -11456,19 +11444,19 @@
         <v>10.6</v>
       </c>
       <c r="J217" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="K217">
         <v>1</v>
       </c>
       <c r="L217" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="M217" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N217" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="O217">
         <v>19.3</v>
@@ -11478,8 +11466,8 @@
       </c>
     </row>
     <row r="218" spans="1:16">
-      <c r="A218" t="s">
-        <v>16</v>
+      <c r="A218">
+        <v>20260424</v>
       </c>
       <c r="B218" t="s">
         <v>37</v>
@@ -11490,14 +11478,14 @@
       <c r="D218">
         <v>58.4</v>
       </c>
-      <c r="E218" t="s">
-        <v>78</v>
+      <c r="E218">
+        <v>2.5</v>
       </c>
       <c r="F218" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="G218" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="H218">
         <v>314.95</v>
@@ -11506,25 +11494,725 @@
         <v>11.6</v>
       </c>
       <c r="J218" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="K218">
         <v>17</v>
       </c>
       <c r="L218" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="M218" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="N218" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="O218">
         <v>19.3</v>
       </c>
       <c r="P218">
         <v>208</v>
+      </c>
+    </row>
+    <row r="219" spans="1:16">
+      <c r="A219" t="s">
+        <v>16</v>
+      </c>
+      <c r="B219" t="s">
+        <v>39</v>
+      </c>
+      <c r="C219" t="s">
+        <v>71</v>
+      </c>
+      <c r="D219">
+        <v>63.9</v>
+      </c>
+      <c r="E219" t="s">
+        <v>72</v>
+      </c>
+      <c r="F219" t="s">
+        <v>75</v>
+      </c>
+      <c r="G219" t="s">
+        <v>76</v>
+      </c>
+      <c r="H219">
+        <v>400.05</v>
+      </c>
+      <c r="I219">
+        <v>6.100000000000001</v>
+      </c>
+      <c r="J219" t="s">
+        <v>78</v>
+      </c>
+      <c r="K219">
+        <v>8</v>
+      </c>
+      <c r="L219" t="s">
+        <v>91</v>
+      </c>
+      <c r="M219" t="s">
+        <v>95</v>
+      </c>
+      <c r="N219" t="s">
+        <v>102</v>
+      </c>
+      <c r="O219">
+        <v>19.25</v>
+      </c>
+      <c r="P219">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="220" spans="1:16">
+      <c r="A220" t="s">
+        <v>16</v>
+      </c>
+      <c r="B220" t="s">
+        <v>40</v>
+      </c>
+      <c r="C220" t="s">
+        <v>71</v>
+      </c>
+      <c r="D220">
+        <v>63.9</v>
+      </c>
+      <c r="E220" t="s">
+        <v>73</v>
+      </c>
+      <c r="F220" t="s">
+        <v>75</v>
+      </c>
+      <c r="G220" t="s">
+        <v>76</v>
+      </c>
+      <c r="H220">
+        <v>3780.2</v>
+      </c>
+      <c r="I220">
+        <v>6.100000000000001</v>
+      </c>
+      <c r="J220" t="s">
+        <v>78</v>
+      </c>
+      <c r="K220">
+        <v>2</v>
+      </c>
+      <c r="L220" t="s">
+        <v>94</v>
+      </c>
+      <c r="M220" t="s">
+        <v>95</v>
+      </c>
+      <c r="N220" t="s">
+        <v>102</v>
+      </c>
+      <c r="O220">
+        <v>19.25</v>
+      </c>
+      <c r="P220">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="221" spans="1:16">
+      <c r="A221" t="s">
+        <v>16</v>
+      </c>
+      <c r="B221" t="s">
+        <v>49</v>
+      </c>
+      <c r="C221" t="s">
+        <v>71</v>
+      </c>
+      <c r="D221">
+        <v>61.5</v>
+      </c>
+      <c r="E221" t="s">
+        <v>73</v>
+      </c>
+      <c r="F221" t="s">
+        <v>75</v>
+      </c>
+      <c r="G221" t="s">
+        <v>76</v>
+      </c>
+      <c r="H221">
+        <v>123.85</v>
+      </c>
+      <c r="I221">
+        <v>8.5</v>
+      </c>
+      <c r="J221" t="s">
+        <v>79</v>
+      </c>
+      <c r="K221">
+        <v>2</v>
+      </c>
+      <c r="L221" t="s">
+        <v>94</v>
+      </c>
+      <c r="M221" t="s">
+        <v>95</v>
+      </c>
+      <c r="N221" t="s">
+        <v>102</v>
+      </c>
+      <c r="O221">
+        <v>19.25</v>
+      </c>
+      <c r="P221">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="222" spans="1:16">
+      <c r="A222" t="s">
+        <v>16</v>
+      </c>
+      <c r="B222" t="s">
+        <v>41</v>
+      </c>
+      <c r="C222" t="s">
+        <v>71</v>
+      </c>
+      <c r="D222">
+        <v>61.4</v>
+      </c>
+      <c r="E222" t="s">
+        <v>73</v>
+      </c>
+      <c r="F222" t="s">
+        <v>75</v>
+      </c>
+      <c r="G222" t="s">
+        <v>76</v>
+      </c>
+      <c r="H222">
+        <v>210.92</v>
+      </c>
+      <c r="I222">
+        <v>8.600000000000001</v>
+      </c>
+      <c r="J222" t="s">
+        <v>80</v>
+      </c>
+      <c r="K222">
+        <v>2</v>
+      </c>
+      <c r="L222" t="s">
+        <v>94</v>
+      </c>
+      <c r="M222" t="s">
+        <v>95</v>
+      </c>
+      <c r="N222" t="s">
+        <v>102</v>
+      </c>
+      <c r="O222">
+        <v>19.25</v>
+      </c>
+      <c r="P222">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="223" spans="1:16">
+      <c r="A223" t="s">
+        <v>16</v>
+      </c>
+      <c r="B223" t="s">
+        <v>22</v>
+      </c>
+      <c r="C223" t="s">
+        <v>71</v>
+      </c>
+      <c r="D223">
+        <v>61</v>
+      </c>
+      <c r="E223" t="s">
+        <v>73</v>
+      </c>
+      <c r="F223" t="s">
+        <v>75</v>
+      </c>
+      <c r="G223" t="s">
+        <v>76</v>
+      </c>
+      <c r="H223">
+        <v>1358.5</v>
+      </c>
+      <c r="I223">
+        <v>9</v>
+      </c>
+      <c r="J223" t="s">
+        <v>78</v>
+      </c>
+      <c r="K223">
+        <v>18</v>
+      </c>
+      <c r="L223" t="s">
+        <v>89</v>
+      </c>
+      <c r="M223" t="s">
+        <v>95</v>
+      </c>
+      <c r="N223" t="s">
+        <v>102</v>
+      </c>
+      <c r="O223">
+        <v>19.25</v>
+      </c>
+      <c r="P223">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="224" spans="1:16">
+      <c r="A224" t="s">
+        <v>16</v>
+      </c>
+      <c r="B224" t="s">
+        <v>23</v>
+      </c>
+      <c r="C224" t="s">
+        <v>71</v>
+      </c>
+      <c r="D224">
+        <v>61</v>
+      </c>
+      <c r="E224" t="s">
+        <v>73</v>
+      </c>
+      <c r="F224" t="s">
+        <v>75</v>
+      </c>
+      <c r="G224" t="s">
+        <v>76</v>
+      </c>
+      <c r="H224">
+        <v>4398.7</v>
+      </c>
+      <c r="I224">
+        <v>9</v>
+      </c>
+      <c r="J224" t="s">
+        <v>78</v>
+      </c>
+      <c r="K224">
+        <v>18</v>
+      </c>
+      <c r="L224" t="s">
+        <v>89</v>
+      </c>
+      <c r="M224" t="s">
+        <v>95</v>
+      </c>
+      <c r="N224" t="s">
+        <v>102</v>
+      </c>
+      <c r="O224">
+        <v>19.25</v>
+      </c>
+      <c r="P224">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="225" spans="1:16">
+      <c r="A225" t="s">
+        <v>16</v>
+      </c>
+      <c r="B225" t="s">
+        <v>33</v>
+      </c>
+      <c r="C225" t="s">
+        <v>71</v>
+      </c>
+      <c r="D225">
+        <v>61</v>
+      </c>
+      <c r="E225" t="s">
+        <v>73</v>
+      </c>
+      <c r="F225" t="s">
+        <v>75</v>
+      </c>
+      <c r="G225" t="s">
+        <v>76</v>
+      </c>
+      <c r="H225">
+        <v>9633</v>
+      </c>
+      <c r="I225">
+        <v>9</v>
+      </c>
+      <c r="J225" t="s">
+        <v>78</v>
+      </c>
+      <c r="K225">
+        <v>18</v>
+      </c>
+      <c r="L225" t="s">
+        <v>89</v>
+      </c>
+      <c r="M225" t="s">
+        <v>95</v>
+      </c>
+      <c r="N225" t="s">
+        <v>102</v>
+      </c>
+      <c r="O225">
+        <v>19.25</v>
+      </c>
+      <c r="P225">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="226" spans="1:16">
+      <c r="A226" t="s">
+        <v>16</v>
+      </c>
+      <c r="B226" t="s">
+        <v>42</v>
+      </c>
+      <c r="C226" t="s">
+        <v>71</v>
+      </c>
+      <c r="D226">
+        <v>61</v>
+      </c>
+      <c r="E226" t="s">
+        <v>73</v>
+      </c>
+      <c r="F226" t="s">
+        <v>75</v>
+      </c>
+      <c r="G226" t="s">
+        <v>76</v>
+      </c>
+      <c r="H226">
+        <v>87.38</v>
+      </c>
+      <c r="I226">
+        <v>9</v>
+      </c>
+      <c r="J226" t="s">
+        <v>78</v>
+      </c>
+      <c r="K226">
+        <v>2</v>
+      </c>
+      <c r="L226" t="s">
+        <v>94</v>
+      </c>
+      <c r="M226" t="s">
+        <v>95</v>
+      </c>
+      <c r="N226" t="s">
+        <v>102</v>
+      </c>
+      <c r="O226">
+        <v>19.25</v>
+      </c>
+      <c r="P226">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="227" spans="1:16">
+      <c r="A227" t="s">
+        <v>16</v>
+      </c>
+      <c r="B227" t="s">
+        <v>43</v>
+      </c>
+      <c r="C227" t="s">
+        <v>71</v>
+      </c>
+      <c r="D227">
+        <v>60.4</v>
+      </c>
+      <c r="E227" t="s">
+        <v>73</v>
+      </c>
+      <c r="F227" t="s">
+        <v>75</v>
+      </c>
+      <c r="G227" t="s">
+        <v>76</v>
+      </c>
+      <c r="H227">
+        <v>1251.6</v>
+      </c>
+      <c r="I227">
+        <v>9.600000000000001</v>
+      </c>
+      <c r="J227" t="s">
+        <v>78</v>
+      </c>
+      <c r="K227">
+        <v>2</v>
+      </c>
+      <c r="L227" t="s">
+        <v>94</v>
+      </c>
+      <c r="M227" t="s">
+        <v>95</v>
+      </c>
+      <c r="N227" t="s">
+        <v>102</v>
+      </c>
+      <c r="O227">
+        <v>19.25</v>
+      </c>
+      <c r="P227">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="228" spans="1:16">
+      <c r="A228" t="s">
+        <v>16</v>
+      </c>
+      <c r="B228" t="s">
+        <v>44</v>
+      </c>
+      <c r="C228" t="s">
+        <v>71</v>
+      </c>
+      <c r="D228">
+        <v>60</v>
+      </c>
+      <c r="E228" t="s">
+        <v>73</v>
+      </c>
+      <c r="F228" t="s">
+        <v>75</v>
+      </c>
+      <c r="G228" t="s">
+        <v>76</v>
+      </c>
+      <c r="H228">
+        <v>124.74</v>
+      </c>
+      <c r="I228">
+        <v>10</v>
+      </c>
+      <c r="J228" t="s">
+        <v>78</v>
+      </c>
+      <c r="K228">
+        <v>2</v>
+      </c>
+      <c r="L228" t="s">
+        <v>94</v>
+      </c>
+      <c r="M228" t="s">
+        <v>95</v>
+      </c>
+      <c r="N228" t="s">
+        <v>102</v>
+      </c>
+      <c r="O228">
+        <v>19.25</v>
+      </c>
+      <c r="P228">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="229" spans="1:16">
+      <c r="A229" t="s">
+        <v>16</v>
+      </c>
+      <c r="B229" t="s">
+        <v>56</v>
+      </c>
+      <c r="C229" t="s">
+        <v>71</v>
+      </c>
+      <c r="D229">
+        <v>59.7</v>
+      </c>
+      <c r="E229" t="s">
+        <v>73</v>
+      </c>
+      <c r="F229" t="s">
+        <v>75</v>
+      </c>
+      <c r="G229" t="s">
+        <v>76</v>
+      </c>
+      <c r="H229">
+        <v>456</v>
+      </c>
+      <c r="I229">
+        <v>10.3</v>
+      </c>
+      <c r="J229" t="s">
+        <v>86</v>
+      </c>
+      <c r="K229">
+        <v>7</v>
+      </c>
+      <c r="L229" t="s">
+        <v>92</v>
+      </c>
+      <c r="M229" t="s">
+        <v>95</v>
+      </c>
+      <c r="N229" t="s">
+        <v>102</v>
+      </c>
+      <c r="O229">
+        <v>19.25</v>
+      </c>
+      <c r="P229">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="230" spans="1:16">
+      <c r="A230" t="s">
+        <v>16</v>
+      </c>
+      <c r="B230" t="s">
+        <v>32</v>
+      </c>
+      <c r="C230" t="s">
+        <v>71</v>
+      </c>
+      <c r="D230">
+        <v>59.4</v>
+      </c>
+      <c r="E230" t="s">
+        <v>73</v>
+      </c>
+      <c r="F230" t="s">
+        <v>75</v>
+      </c>
+      <c r="G230" t="s">
+        <v>76</v>
+      </c>
+      <c r="H230">
+        <v>1415</v>
+      </c>
+      <c r="I230">
+        <v>10.6</v>
+      </c>
+      <c r="J230" t="s">
+        <v>80</v>
+      </c>
+      <c r="K230">
+        <v>13</v>
+      </c>
+      <c r="L230" t="s">
+        <v>88</v>
+      </c>
+      <c r="M230" t="s">
+        <v>95</v>
+      </c>
+      <c r="N230" t="s">
+        <v>102</v>
+      </c>
+      <c r="O230">
+        <v>19.25</v>
+      </c>
+      <c r="P230">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="231" spans="1:16">
+      <c r="A231" t="s">
+        <v>16</v>
+      </c>
+      <c r="B231" t="s">
+        <v>45</v>
+      </c>
+      <c r="C231" t="s">
+        <v>71</v>
+      </c>
+      <c r="D231">
+        <v>59.4</v>
+      </c>
+      <c r="E231" t="s">
+        <v>73</v>
+      </c>
+      <c r="F231" t="s">
+        <v>75</v>
+      </c>
+      <c r="G231" t="s">
+        <v>76</v>
+      </c>
+      <c r="H231">
+        <v>1171.55</v>
+      </c>
+      <c r="I231">
+        <v>10.6</v>
+      </c>
+      <c r="J231" t="s">
+        <v>80</v>
+      </c>
+      <c r="K231">
+        <v>2</v>
+      </c>
+      <c r="L231" t="s">
+        <v>94</v>
+      </c>
+      <c r="M231" t="s">
+        <v>95</v>
+      </c>
+      <c r="N231" t="s">
+        <v>102</v>
+      </c>
+      <c r="O231">
+        <v>19.25</v>
+      </c>
+      <c r="P231">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="232" spans="1:16">
+      <c r="A232" t="s">
+        <v>16</v>
+      </c>
+      <c r="B232" t="s">
+        <v>37</v>
+      </c>
+      <c r="C232" t="s">
+        <v>71</v>
+      </c>
+      <c r="D232">
+        <v>55.9</v>
+      </c>
+      <c r="E232" t="s">
+        <v>74</v>
+      </c>
+      <c r="F232" t="s">
+        <v>75</v>
+      </c>
+      <c r="G232" t="s">
+        <v>76</v>
+      </c>
+      <c r="H232">
+        <v>315.55</v>
+      </c>
+      <c r="I232">
+        <v>14.1</v>
+      </c>
+      <c r="J232" t="s">
+        <v>82</v>
+      </c>
+      <c r="K232">
+        <v>18</v>
+      </c>
+      <c r="L232" t="s">
+        <v>89</v>
+      </c>
+      <c r="M232" t="s">
+        <v>95</v>
+      </c>
+      <c r="N232" t="s">
+        <v>102</v>
+      </c>
+      <c r="O232">
+        <v>19.25</v>
+      </c>
+      <c r="P232">
+        <v>195</v>
       </c>
     </row>
   </sheetData>

--- a/reports/watchlist_history.xlsx
+++ b/reports/watchlist_history.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2000" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2179" uniqueCount="112">
   <si>
     <t>Date</t>
   </si>
@@ -229,31 +229,31 @@
     <t>VEDL</t>
   </si>
   <si>
+    <t>TIMKEN</t>
+  </si>
+  <si>
+    <t>ASTERDM</t>
+  </si>
+  <si>
+    <t>RADICO</t>
+  </si>
+  <si>
+    <t>WELCORP</t>
+  </si>
+  <si>
     <t>BUY</t>
   </si>
   <si>
     <t>WATCH</t>
   </si>
   <si>
+    <t>+0.0</t>
+  </si>
+  <si>
     <t>+3.0</t>
   </si>
   <si>
-    <t>+0.0</t>
-  </si>
-  <si>
-    <t>+2.5</t>
-  </si>
-  <si>
-    <t>+2.0</t>
-  </si>
-  <si>
     <t>+1.0</t>
-  </si>
-  <si>
-    <t>-1.8</t>
-  </si>
-  <si>
-    <t>-2.5</t>
   </si>
   <si>
     <t>Stage 2 — Uptrend ✓</t>
@@ -290,6 +290,9 @@
   </si>
   <si>
     <t>Score 60/100 — need macro improvement or volume surge</t>
+  </si>
+  <si>
+    <t>Score 61/100 — need macro improvement or volume surge</t>
   </si>
   <si>
     <t>20260421</t>
@@ -344,6 +347,9 @@
   </si>
   <si>
     <t>-5.1%</t>
+  </si>
+  <si>
+    <t>-4.9%</t>
   </si>
 </sst>
 </file>
@@ -675,7 +681,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P247"/>
+  <dimension ref="A1:P268"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:16">
@@ -736,7 +742,7 @@
         <v>17</v>
       </c>
       <c r="C2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D2">
         <v>77.09999999999999</v>
@@ -760,13 +766,13 @@
         <v>1</v>
       </c>
       <c r="L2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O2">
         <v>17.53</v>
@@ -783,7 +789,7 @@
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D3">
         <v>74</v>
@@ -807,13 +813,13 @@
         <v>1</v>
       </c>
       <c r="L3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O3">
         <v>17.53</v>
@@ -830,7 +836,7 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D4">
         <v>72</v>
@@ -854,13 +860,13 @@
         <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="M4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O4">
         <v>17.53</v>
@@ -877,7 +883,7 @@
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D5">
         <v>69.59999999999999</v>
@@ -904,13 +910,13 @@
         <v>1</v>
       </c>
       <c r="L5" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O5">
         <v>17.53</v>
@@ -927,7 +933,7 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D6">
         <v>69.09999999999999</v>
@@ -954,13 +960,13 @@
         <v>1</v>
       </c>
       <c r="L6" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M6" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O6">
         <v>17.53</v>
@@ -977,7 +983,7 @@
         <v>22</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D7">
         <v>67.2</v>
@@ -1004,13 +1010,13 @@
         <v>6</v>
       </c>
       <c r="L7" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M7" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N7" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O7">
         <v>17.53</v>
@@ -1027,7 +1033,7 @@
         <v>23</v>
       </c>
       <c r="C8" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D8">
         <v>67.2</v>
@@ -1054,13 +1060,13 @@
         <v>6</v>
       </c>
       <c r="L8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M8" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N8" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O8">
         <v>17.53</v>
@@ -1077,7 +1083,7 @@
         <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D9">
         <v>67.2</v>
@@ -1104,13 +1110,13 @@
         <v>6</v>
       </c>
       <c r="L9" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M9" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O9">
         <v>17.53</v>
@@ -1127,7 +1133,7 @@
         <v>25</v>
       </c>
       <c r="C10" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D10">
         <v>67.2</v>
@@ -1154,13 +1160,13 @@
         <v>1</v>
       </c>
       <c r="L10" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N10" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O10">
         <v>17.53</v>
@@ -1177,7 +1183,7 @@
         <v>24</v>
       </c>
       <c r="C11" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D11">
         <v>67.2</v>
@@ -1204,13 +1210,13 @@
         <v>6</v>
       </c>
       <c r="L11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M11" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N11" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O11">
         <v>17.53</v>
@@ -1227,7 +1233,7 @@
         <v>23</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D12">
         <v>67.2</v>
@@ -1254,13 +1260,13 @@
         <v>6</v>
       </c>
       <c r="L12" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M12" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N12" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O12">
         <v>17.53</v>
@@ -1277,7 +1283,7 @@
         <v>26</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D13">
         <v>67.09999999999999</v>
@@ -1304,13 +1310,13 @@
         <v>1</v>
       </c>
       <c r="L13" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M13" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N13" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O13">
         <v>17.53</v>
@@ -1327,7 +1333,7 @@
         <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D14">
         <v>67.09999999999999</v>
@@ -1354,13 +1360,13 @@
         <v>1</v>
       </c>
       <c r="L14" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M14" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N14" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O14">
         <v>17.53</v>
@@ -1377,7 +1383,7 @@
         <v>28</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D15">
         <v>65.59999999999999</v>
@@ -1404,13 +1410,13 @@
         <v>1</v>
       </c>
       <c r="L15" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M15" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N15" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O15">
         <v>17.53</v>
@@ -1427,7 +1433,7 @@
         <v>29</v>
       </c>
       <c r="C16" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D16">
         <v>65</v>
@@ -1454,13 +1460,13 @@
         <v>1</v>
       </c>
       <c r="L16" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M16" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N16" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O16">
         <v>17.53</v>
@@ -1477,7 +1483,7 @@
         <v>30</v>
       </c>
       <c r="C17" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D17">
         <v>64.7</v>
@@ -1504,13 +1510,13 @@
         <v>1</v>
       </c>
       <c r="L17" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M17" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N17" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O17">
         <v>17.53</v>
@@ -1527,7 +1533,7 @@
         <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D18">
         <v>64.7</v>
@@ -1554,13 +1560,13 @@
         <v>1</v>
       </c>
       <c r="L18" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M18" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N18" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O18">
         <v>17.53</v>
@@ -1577,7 +1583,7 @@
         <v>32</v>
       </c>
       <c r="C19" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D19">
         <v>64.59999999999999</v>
@@ -1604,13 +1610,13 @@
         <v>1</v>
       </c>
       <c r="L19" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M19" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N19" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O19">
         <v>17.53</v>
@@ -1627,7 +1633,7 @@
         <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D20">
         <v>64.2</v>
@@ -1654,13 +1660,13 @@
         <v>6</v>
       </c>
       <c r="L20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M20" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N20" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O20">
         <v>17.53</v>
@@ -1677,7 +1683,7 @@
         <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D21">
         <v>64.2</v>
@@ -1704,13 +1710,13 @@
         <v>1</v>
       </c>
       <c r="L21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M21" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N21" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O21">
         <v>17.53</v>
@@ -1727,7 +1733,7 @@
         <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D22">
         <v>63.6</v>
@@ -1754,13 +1760,13 @@
         <v>1</v>
       </c>
       <c r="L22" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M22" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N22" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O22">
         <v>17.53</v>
@@ -1777,7 +1783,7 @@
         <v>36</v>
       </c>
       <c r="C23" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D23">
         <v>61.6</v>
@@ -1804,13 +1810,13 @@
         <v>1</v>
       </c>
       <c r="L23" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M23" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N23" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O23">
         <v>17.53</v>
@@ -1827,7 +1833,7 @@
         <v>37</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D24">
         <v>61.5</v>
@@ -1854,13 +1860,13 @@
         <v>6</v>
       </c>
       <c r="L24" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M24" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N24" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O24">
         <v>17.53</v>
@@ -1877,7 +1883,7 @@
         <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D25">
         <v>70</v>
@@ -1901,13 +1907,13 @@
         <v>1</v>
       </c>
       <c r="L25" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M25" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N25" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O25">
         <v>18.27</v>
@@ -1924,7 +1930,7 @@
         <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D26">
         <v>69</v>
@@ -1951,13 +1957,13 @@
         <v>7</v>
       </c>
       <c r="L26" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M26" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O26">
         <v>18.27</v>
@@ -1974,7 +1980,7 @@
         <v>40</v>
       </c>
       <c r="C27" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D27">
         <v>69</v>
@@ -2001,13 +2007,13 @@
         <v>1</v>
       </c>
       <c r="L27" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M27" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N27" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O27">
         <v>18.27</v>
@@ -2024,7 +2030,7 @@
         <v>41</v>
       </c>
       <c r="C28" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D28">
         <v>67.5</v>
@@ -2051,13 +2057,13 @@
         <v>1</v>
       </c>
       <c r="L28" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M28" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N28" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O28">
         <v>18.27</v>
@@ -2074,7 +2080,7 @@
         <v>22</v>
       </c>
       <c r="C29" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D29">
         <v>66.7</v>
@@ -2101,13 +2107,13 @@
         <v>7</v>
       </c>
       <c r="L29" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M29" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O29">
         <v>18.27</v>
@@ -2124,7 +2130,7 @@
         <v>23</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D30">
         <v>66.7</v>
@@ -2151,13 +2157,13 @@
         <v>7</v>
       </c>
       <c r="L30" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M30" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N30" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O30">
         <v>18.27</v>
@@ -2174,7 +2180,7 @@
         <v>42</v>
       </c>
       <c r="C31" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D31">
         <v>66.7</v>
@@ -2201,13 +2207,13 @@
         <v>1</v>
       </c>
       <c r="L31" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M31" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N31" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O31">
         <v>18.27</v>
@@ -2224,7 +2230,7 @@
         <v>43</v>
       </c>
       <c r="C32" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D32">
         <v>66.59999999999999</v>
@@ -2251,13 +2257,13 @@
         <v>1</v>
       </c>
       <c r="L32" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M32" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N32" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O32">
         <v>18.27</v>
@@ -2274,7 +2280,7 @@
         <v>32</v>
       </c>
       <c r="C33" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D33">
         <v>64.09999999999999</v>
@@ -2301,13 +2307,13 @@
         <v>2</v>
       </c>
       <c r="L33" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M33" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N33" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O33">
         <v>18.27</v>
@@ -2324,7 +2330,7 @@
         <v>33</v>
       </c>
       <c r="C34" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D34">
         <v>63.7</v>
@@ -2351,13 +2357,13 @@
         <v>7</v>
       </c>
       <c r="L34" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M34" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N34" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O34">
         <v>18.27</v>
@@ -2374,7 +2380,7 @@
         <v>44</v>
       </c>
       <c r="C35" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D35">
         <v>62.7</v>
@@ -2401,13 +2407,13 @@
         <v>1</v>
       </c>
       <c r="L35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M35" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N35" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O35">
         <v>18.27</v>
@@ -2424,7 +2430,7 @@
         <v>45</v>
       </c>
       <c r="C36" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D36">
         <v>62.1</v>
@@ -2451,13 +2457,13 @@
         <v>1</v>
       </c>
       <c r="L36" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M36" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N36" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O36">
         <v>18.27</v>
@@ -2474,7 +2480,7 @@
         <v>24</v>
       </c>
       <c r="C37" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D37">
         <v>60.7</v>
@@ -2501,13 +2507,13 @@
         <v>7</v>
       </c>
       <c r="L37" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M37" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N37" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O37">
         <v>18.27</v>
@@ -2524,7 +2530,7 @@
         <v>37</v>
       </c>
       <c r="C38" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D38">
         <v>58.6</v>
@@ -2551,13 +2557,13 @@
         <v>7</v>
       </c>
       <c r="L38" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M38" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N38" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O38">
         <v>18.27</v>
@@ -2574,7 +2580,7 @@
         <v>46</v>
       </c>
       <c r="C39" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D39">
         <v>58.3</v>
@@ -2601,13 +2607,13 @@
         <v>1</v>
       </c>
       <c r="L39" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M39" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N39" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O39">
         <v>18.27</v>
@@ -2624,7 +2630,7 @@
         <v>47</v>
       </c>
       <c r="C40" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D40">
         <v>58.3</v>
@@ -2651,13 +2657,13 @@
         <v>1</v>
       </c>
       <c r="L40" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N40" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O40">
         <v>18.27</v>
@@ -2674,7 +2680,7 @@
         <v>48</v>
       </c>
       <c r="C41" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D41">
         <v>56.7</v>
@@ -2701,13 +2707,13 @@
         <v>3</v>
       </c>
       <c r="L41" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M41" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N41" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O41">
         <v>18.27</v>
@@ -2724,7 +2730,7 @@
         <v>49</v>
       </c>
       <c r="C42" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D42">
         <v>55.4</v>
@@ -2751,13 +2757,13 @@
         <v>1</v>
       </c>
       <c r="L42" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M42" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N42" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O42">
         <v>18.27</v>
@@ -2774,7 +2780,7 @@
         <v>22</v>
       </c>
       <c r="C43" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D43">
         <v>69.09999999999999</v>
@@ -2801,13 +2807,13 @@
         <v>8</v>
       </c>
       <c r="L43" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M43" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N43" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O43">
         <v>18.23</v>
@@ -2824,7 +2830,7 @@
         <v>39</v>
       </c>
       <c r="C44" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D44">
         <v>69</v>
@@ -2851,13 +2857,13 @@
         <v>8</v>
       </c>
       <c r="L44" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M44" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N44" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O44">
         <v>18.23</v>
@@ -2874,7 +2880,7 @@
         <v>40</v>
       </c>
       <c r="C45" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D45">
         <v>69</v>
@@ -2901,13 +2907,13 @@
         <v>2</v>
       </c>
       <c r="L45" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N45" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O45">
         <v>18.23</v>
@@ -2924,7 +2930,7 @@
         <v>41</v>
       </c>
       <c r="C46" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D46">
         <v>68.5</v>
@@ -2951,13 +2957,13 @@
         <v>2</v>
       </c>
       <c r="L46" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M46" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N46" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O46">
         <v>18.23</v>
@@ -2974,7 +2980,7 @@
         <v>23</v>
       </c>
       <c r="C47" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D47">
         <v>66.7</v>
@@ -3001,13 +3007,13 @@
         <v>8</v>
       </c>
       <c r="L47" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M47" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N47" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O47">
         <v>18.23</v>
@@ -3024,7 +3030,7 @@
         <v>42</v>
       </c>
       <c r="C48" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D48">
         <v>66.7</v>
@@ -3051,13 +3057,13 @@
         <v>2</v>
       </c>
       <c r="L48" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M48" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N48" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O48">
         <v>18.23</v>
@@ -3074,7 +3080,7 @@
         <v>43</v>
       </c>
       <c r="C49" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D49">
         <v>66.59999999999999</v>
@@ -3101,13 +3107,13 @@
         <v>2</v>
       </c>
       <c r="L49" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M49" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N49" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O49">
         <v>18.23</v>
@@ -3124,7 +3130,7 @@
         <v>32</v>
       </c>
       <c r="C50" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D50">
         <v>64.09999999999999</v>
@@ -3151,13 +3157,13 @@
         <v>3</v>
       </c>
       <c r="L50" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M50" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N50" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O50">
         <v>18.23</v>
@@ -3174,7 +3180,7 @@
         <v>33</v>
       </c>
       <c r="C51" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D51">
         <v>63.7</v>
@@ -3201,13 +3207,13 @@
         <v>8</v>
       </c>
       <c r="L51" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M51" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N51" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O51">
         <v>18.23</v>
@@ -3224,7 +3230,7 @@
         <v>44</v>
       </c>
       <c r="C52" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D52">
         <v>62.7</v>
@@ -3251,13 +3257,13 @@
         <v>2</v>
       </c>
       <c r="L52" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M52" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N52" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O52">
         <v>18.23</v>
@@ -3274,7 +3280,7 @@
         <v>45</v>
       </c>
       <c r="C53" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D53">
         <v>62.1</v>
@@ -3301,13 +3307,13 @@
         <v>2</v>
       </c>
       <c r="L53" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M53" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N53" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O53">
         <v>18.23</v>
@@ -3324,7 +3330,7 @@
         <v>24</v>
       </c>
       <c r="C54" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D54">
         <v>60.7</v>
@@ -3351,13 +3357,13 @@
         <v>8</v>
       </c>
       <c r="L54" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M54" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N54" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O54">
         <v>18.23</v>
@@ -3374,7 +3380,7 @@
         <v>37</v>
       </c>
       <c r="C55" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D55">
         <v>58.6</v>
@@ -3401,13 +3407,13 @@
         <v>8</v>
       </c>
       <c r="L55" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M55" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N55" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O55">
         <v>18.23</v>
@@ -3424,7 +3430,7 @@
         <v>46</v>
       </c>
       <c r="C56" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D56">
         <v>58.3</v>
@@ -3451,13 +3457,13 @@
         <v>2</v>
       </c>
       <c r="L56" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M56" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N56" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O56">
         <v>18.23</v>
@@ -3474,7 +3480,7 @@
         <v>47</v>
       </c>
       <c r="C57" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D57">
         <v>58.3</v>
@@ -3501,13 +3507,13 @@
         <v>2</v>
       </c>
       <c r="L57" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M57" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N57" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O57">
         <v>18.23</v>
@@ -3524,7 +3530,7 @@
         <v>48</v>
       </c>
       <c r="C58" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D58">
         <v>56.7</v>
@@ -3551,13 +3557,13 @@
         <v>4</v>
       </c>
       <c r="L58" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M58" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N58" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O58">
         <v>18.23</v>
@@ -3574,7 +3580,7 @@
         <v>49</v>
       </c>
       <c r="C59" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D59">
         <v>55.4</v>
@@ -3601,13 +3607,13 @@
         <v>2</v>
       </c>
       <c r="L59" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M59" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N59" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O59">
         <v>18.23</v>
@@ -3624,7 +3630,7 @@
         <v>40</v>
       </c>
       <c r="C60" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D60">
         <v>71.5</v>
@@ -3648,13 +3654,13 @@
         <v>1</v>
       </c>
       <c r="L60" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M60" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N60" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O60">
         <v>18.08</v>
@@ -3671,7 +3677,7 @@
         <v>22</v>
       </c>
       <c r="C61" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D61">
         <v>69.59999999999999</v>
@@ -3698,13 +3704,13 @@
         <v>9</v>
       </c>
       <c r="L61" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M61" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N61" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O61">
         <v>18.08</v>
@@ -3721,7 +3727,7 @@
         <v>39</v>
       </c>
       <c r="C62" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D62">
         <v>69.5</v>
@@ -3748,13 +3754,13 @@
         <v>9</v>
       </c>
       <c r="L62" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M62" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N62" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O62">
         <v>18.08</v>
@@ -3771,7 +3777,7 @@
         <v>41</v>
       </c>
       <c r="C63" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D63">
         <v>69</v>
@@ -3798,13 +3804,13 @@
         <v>3</v>
       </c>
       <c r="L63" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M63" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N63" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O63">
         <v>18.08</v>
@@ -3821,7 +3827,7 @@
         <v>23</v>
       </c>
       <c r="C64" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D64">
         <v>67.2</v>
@@ -3848,13 +3854,13 @@
         <v>9</v>
       </c>
       <c r="L64" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M64" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N64" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O64">
         <v>18.08</v>
@@ -3871,7 +3877,7 @@
         <v>24</v>
       </c>
       <c r="C65" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D65">
         <v>67.2</v>
@@ -3898,13 +3904,13 @@
         <v>9</v>
       </c>
       <c r="L65" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M65" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N65" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O65">
         <v>18.08</v>
@@ -3921,7 +3927,7 @@
         <v>42</v>
       </c>
       <c r="C66" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D66">
         <v>67.2</v>
@@ -3948,13 +3954,13 @@
         <v>3</v>
       </c>
       <c r="L66" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M66" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N66" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O66">
         <v>18.08</v>
@@ -3971,7 +3977,7 @@
         <v>43</v>
       </c>
       <c r="C67" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D67">
         <v>67.09999999999999</v>
@@ -3998,13 +4004,13 @@
         <v>3</v>
       </c>
       <c r="L67" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M67" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N67" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O67">
         <v>18.08</v>
@@ -4021,7 +4027,7 @@
         <v>32</v>
       </c>
       <c r="C68" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D68">
         <v>64.59999999999999</v>
@@ -4048,13 +4054,13 @@
         <v>4</v>
       </c>
       <c r="L68" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M68" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N68" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O68">
         <v>18.08</v>
@@ -4071,7 +4077,7 @@
         <v>44</v>
       </c>
       <c r="C69" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D69">
         <v>63.2</v>
@@ -4098,13 +4104,13 @@
         <v>3</v>
       </c>
       <c r="L69" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M69" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N69" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O69">
         <v>18.08</v>
@@ -4121,7 +4127,7 @@
         <v>45</v>
       </c>
       <c r="C70" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D70">
         <v>62.6</v>
@@ -4148,13 +4154,13 @@
         <v>3</v>
       </c>
       <c r="L70" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M70" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N70" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O70">
         <v>18.08</v>
@@ -4171,7 +4177,7 @@
         <v>33</v>
       </c>
       <c r="C71" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D71">
         <v>60.6</v>
@@ -4198,13 +4204,13 @@
         <v>9</v>
       </c>
       <c r="L71" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M71" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N71" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O71">
         <v>18.08</v>
@@ -4221,7 +4227,7 @@
         <v>37</v>
       </c>
       <c r="C72" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D72">
         <v>59.1</v>
@@ -4248,13 +4254,13 @@
         <v>9</v>
       </c>
       <c r="L72" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M72" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N72" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O72">
         <v>18.08</v>
@@ -4271,7 +4277,7 @@
         <v>46</v>
       </c>
       <c r="C73" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D73">
         <v>58.8</v>
@@ -4298,13 +4304,13 @@
         <v>3</v>
       </c>
       <c r="L73" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M73" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N73" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O73">
         <v>18.08</v>
@@ -4321,7 +4327,7 @@
         <v>47</v>
       </c>
       <c r="C74" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D74">
         <v>58.8</v>
@@ -4348,13 +4354,13 @@
         <v>3</v>
       </c>
       <c r="L74" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M74" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N74" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O74">
         <v>18.08</v>
@@ -4371,7 +4377,7 @@
         <v>48</v>
       </c>
       <c r="C75" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D75">
         <v>57.2</v>
@@ -4398,13 +4404,13 @@
         <v>5</v>
       </c>
       <c r="L75" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M75" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N75" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O75">
         <v>18.08</v>
@@ -4421,7 +4427,7 @@
         <v>50</v>
       </c>
       <c r="C76" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D76">
         <v>56.8</v>
@@ -4448,13 +4454,13 @@
         <v>1</v>
       </c>
       <c r="L76" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M76" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N76" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O76">
         <v>18.08</v>
@@ -4471,7 +4477,7 @@
         <v>49</v>
       </c>
       <c r="C77" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D77">
         <v>55.9</v>
@@ -4498,13 +4504,13 @@
         <v>3</v>
       </c>
       <c r="L77" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M77" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N77" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="O77">
         <v>18.08</v>
@@ -4521,7 +4527,7 @@
         <v>51</v>
       </c>
       <c r="C78" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D78">
         <v>73.7</v>
@@ -4545,13 +4551,13 @@
         <v>1</v>
       </c>
       <c r="L78" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M78" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N78" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O78">
         <v>18.3</v>
@@ -4568,7 +4574,7 @@
         <v>40</v>
       </c>
       <c r="C79" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D79">
         <v>71.5</v>
@@ -4592,13 +4598,13 @@
         <v>1</v>
       </c>
       <c r="L79" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M79" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N79" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O79">
         <v>18.3</v>
@@ -4615,7 +4621,7 @@
         <v>52</v>
       </c>
       <c r="C80" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D80">
         <v>71.09999999999999</v>
@@ -4639,13 +4645,13 @@
         <v>1</v>
       </c>
       <c r="L80" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M80" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N80" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O80">
         <v>18.3</v>
@@ -4662,7 +4668,7 @@
         <v>39</v>
       </c>
       <c r="C81" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D81">
         <v>70.5</v>
@@ -4686,13 +4692,13 @@
         <v>1</v>
       </c>
       <c r="L81" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M81" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N81" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O81">
         <v>18.3</v>
@@ -4709,7 +4715,7 @@
         <v>53</v>
       </c>
       <c r="C82" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D82">
         <v>69.59999999999999</v>
@@ -4736,13 +4742,13 @@
         <v>1</v>
       </c>
       <c r="L82" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M82" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N82" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O82">
         <v>18.3</v>
@@ -4759,7 +4765,7 @@
         <v>41</v>
       </c>
       <c r="C83" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D83">
         <v>69</v>
@@ -4786,13 +4792,13 @@
         <v>4</v>
       </c>
       <c r="L83" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M83" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N83" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O83">
         <v>18.3</v>
@@ -4809,7 +4815,7 @@
         <v>22</v>
       </c>
       <c r="C84" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D84">
         <v>67.2</v>
@@ -4836,13 +4842,13 @@
         <v>10</v>
       </c>
       <c r="L84" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M84" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N84" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O84">
         <v>18.3</v>
@@ -4859,7 +4865,7 @@
         <v>23</v>
       </c>
       <c r="C85" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D85">
         <v>67.2</v>
@@ -4886,13 +4892,13 @@
         <v>10</v>
       </c>
       <c r="L85" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M85" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N85" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O85">
         <v>18.3</v>
@@ -4909,7 +4915,7 @@
         <v>24</v>
       </c>
       <c r="C86" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D86">
         <v>67.2</v>
@@ -4936,13 +4942,13 @@
         <v>10</v>
       </c>
       <c r="L86" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M86" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N86" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O86">
         <v>18.3</v>
@@ -4959,7 +4965,7 @@
         <v>42</v>
       </c>
       <c r="C87" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D87">
         <v>67.2</v>
@@ -4986,13 +4992,13 @@
         <v>4</v>
       </c>
       <c r="L87" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M87" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N87" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O87">
         <v>18.3</v>
@@ -5009,7 +5015,7 @@
         <v>54</v>
       </c>
       <c r="C88" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D88">
         <v>65.2</v>
@@ -5036,13 +5042,13 @@
         <v>1</v>
       </c>
       <c r="L88" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M88" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N88" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O88">
         <v>18.3</v>
@@ -5059,7 +5065,7 @@
         <v>32</v>
       </c>
       <c r="C89" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D89">
         <v>64.59999999999999</v>
@@ -5086,13 +5092,13 @@
         <v>5</v>
       </c>
       <c r="L89" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M89" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N89" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O89">
         <v>18.3</v>
@@ -5109,7 +5115,7 @@
         <v>55</v>
       </c>
       <c r="C90" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D90">
         <v>64.59999999999999</v>
@@ -5136,13 +5142,13 @@
         <v>1</v>
       </c>
       <c r="L90" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M90" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N90" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O90">
         <v>18.3</v>
@@ -5159,7 +5165,7 @@
         <v>45</v>
       </c>
       <c r="C91" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D91">
         <v>63.6</v>
@@ -5186,13 +5192,13 @@
         <v>4</v>
       </c>
       <c r="L91" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M91" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N91" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O91">
         <v>18.3</v>
@@ -5209,7 +5215,7 @@
         <v>43</v>
       </c>
       <c r="C92" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D92">
         <v>61.1</v>
@@ -5236,13 +5242,13 @@
         <v>4</v>
       </c>
       <c r="L92" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M92" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N92" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O92">
         <v>18.3</v>
@@ -5259,7 +5265,7 @@
         <v>33</v>
       </c>
       <c r="C93" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D93">
         <v>60.6</v>
@@ -5286,13 +5292,13 @@
         <v>10</v>
       </c>
       <c r="L93" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M93" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N93" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O93">
         <v>18.3</v>
@@ -5309,7 +5315,7 @@
         <v>37</v>
       </c>
       <c r="C94" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D94">
         <v>59.1</v>
@@ -5336,13 +5342,13 @@
         <v>10</v>
       </c>
       <c r="L94" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M94" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N94" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O94">
         <v>18.3</v>
@@ -5359,7 +5365,7 @@
         <v>46</v>
       </c>
       <c r="C95" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D95">
         <v>58.8</v>
@@ -5386,13 +5392,13 @@
         <v>4</v>
       </c>
       <c r="L95" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M95" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N95" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O95">
         <v>18.3</v>
@@ -5409,7 +5415,7 @@
         <v>48</v>
       </c>
       <c r="C96" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D96">
         <v>57.2</v>
@@ -5436,13 +5442,13 @@
         <v>6</v>
       </c>
       <c r="L96" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M96" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N96" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O96">
         <v>18.3</v>
@@ -5459,7 +5465,7 @@
         <v>50</v>
       </c>
       <c r="C97" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D97">
         <v>56.8</v>
@@ -5486,13 +5492,13 @@
         <v>2</v>
       </c>
       <c r="L97" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M97" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N97" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O97">
         <v>18.3</v>
@@ -5509,7 +5515,7 @@
         <v>40</v>
       </c>
       <c r="C98" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D98">
         <v>70.3</v>
@@ -5533,13 +5539,13 @@
         <v>1</v>
       </c>
       <c r="L98" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M98" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N98" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O98">
         <v>18.3</v>
@@ -5556,7 +5562,7 @@
         <v>52</v>
       </c>
       <c r="C99" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D99">
         <v>69.90000000000001</v>
@@ -5583,13 +5589,13 @@
         <v>1</v>
       </c>
       <c r="L99" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M99" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N99" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O99">
         <v>18.3</v>
@@ -5606,7 +5612,7 @@
         <v>39</v>
       </c>
       <c r="C100" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D100">
         <v>69.3</v>
@@ -5633,13 +5639,13 @@
         <v>1</v>
       </c>
       <c r="L100" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M100" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N100" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O100">
         <v>18.3</v>
@@ -5656,7 +5662,7 @@
         <v>53</v>
       </c>
       <c r="C101" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D101">
         <v>68.40000000000001</v>
@@ -5683,13 +5689,13 @@
         <v>2</v>
       </c>
       <c r="L101" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M101" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N101" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O101">
         <v>18.3</v>
@@ -5706,7 +5712,7 @@
         <v>41</v>
       </c>
       <c r="C102" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D102">
         <v>67.8</v>
@@ -5733,13 +5739,13 @@
         <v>5</v>
       </c>
       <c r="L102" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M102" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N102" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O102">
         <v>18.3</v>
@@ -5756,7 +5762,7 @@
         <v>22</v>
       </c>
       <c r="C103" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D103">
         <v>66</v>
@@ -5783,13 +5789,13 @@
         <v>11</v>
       </c>
       <c r="L103" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M103" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N103" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O103">
         <v>18.3</v>
@@ -5806,7 +5812,7 @@
         <v>23</v>
       </c>
       <c r="C104" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D104">
         <v>66</v>
@@ -5833,13 +5839,13 @@
         <v>11</v>
       </c>
       <c r="L104" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M104" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N104" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O104">
         <v>18.3</v>
@@ -5856,7 +5862,7 @@
         <v>24</v>
       </c>
       <c r="C105" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D105">
         <v>66</v>
@@ -5883,13 +5889,13 @@
         <v>11</v>
       </c>
       <c r="L105" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M105" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N105" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O105">
         <v>18.3</v>
@@ -5906,7 +5912,7 @@
         <v>42</v>
       </c>
       <c r="C106" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D106">
         <v>66</v>
@@ -5933,13 +5939,13 @@
         <v>5</v>
       </c>
       <c r="L106" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M106" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N106" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O106">
         <v>18.3</v>
@@ -5956,7 +5962,7 @@
         <v>54</v>
       </c>
       <c r="C107" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D107">
         <v>64</v>
@@ -5983,13 +5989,13 @@
         <v>2</v>
       </c>
       <c r="L107" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M107" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N107" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O107">
         <v>18.3</v>
@@ -6006,7 +6012,7 @@
         <v>32</v>
       </c>
       <c r="C108" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D108">
         <v>63.4</v>
@@ -6033,13 +6039,13 @@
         <v>6</v>
       </c>
       <c r="L108" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M108" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N108" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O108">
         <v>18.3</v>
@@ -6056,7 +6062,7 @@
         <v>55</v>
       </c>
       <c r="C109" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D109">
         <v>63.4</v>
@@ -6083,13 +6089,13 @@
         <v>2</v>
       </c>
       <c r="L109" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M109" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N109" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O109">
         <v>18.3</v>
@@ -6106,7 +6112,7 @@
         <v>45</v>
       </c>
       <c r="C110" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D110">
         <v>62.4</v>
@@ -6133,13 +6139,13 @@
         <v>5</v>
       </c>
       <c r="L110" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M110" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N110" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O110">
         <v>18.3</v>
@@ -6156,7 +6162,7 @@
         <v>43</v>
       </c>
       <c r="C111" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D111">
         <v>59.9</v>
@@ -6183,13 +6189,13 @@
         <v>5</v>
       </c>
       <c r="L111" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M111" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N111" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O111">
         <v>18.3</v>
@@ -6206,7 +6212,7 @@
         <v>33</v>
       </c>
       <c r="C112" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D112">
         <v>59.4</v>
@@ -6233,13 +6239,13 @@
         <v>11</v>
       </c>
       <c r="L112" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M112" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N112" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O112">
         <v>18.3</v>
@@ -6256,7 +6262,7 @@
         <v>37</v>
       </c>
       <c r="C113" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D113">
         <v>57.9</v>
@@ -6283,13 +6289,13 @@
         <v>11</v>
       </c>
       <c r="L113" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M113" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N113" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O113">
         <v>18.3</v>
@@ -6306,7 +6312,7 @@
         <v>46</v>
       </c>
       <c r="C114" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D114">
         <v>57.6</v>
@@ -6333,13 +6339,13 @@
         <v>5</v>
       </c>
       <c r="L114" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M114" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N114" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O114">
         <v>18.3</v>
@@ -6356,7 +6362,7 @@
         <v>48</v>
       </c>
       <c r="C115" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D115">
         <v>56</v>
@@ -6383,13 +6389,13 @@
         <v>7</v>
       </c>
       <c r="L115" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M115" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N115" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O115">
         <v>18.3</v>
@@ -6406,7 +6412,7 @@
         <v>50</v>
       </c>
       <c r="C116" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D116">
         <v>55.6</v>
@@ -6433,13 +6439,13 @@
         <v>3</v>
       </c>
       <c r="L116" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M116" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N116" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="O116">
         <v>18.3</v>
@@ -6456,7 +6462,7 @@
         <v>43</v>
       </c>
       <c r="C117" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D117">
         <v>66.40000000000001</v>
@@ -6483,13 +6489,13 @@
         <v>6</v>
       </c>
       <c r="L117" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M117" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N117" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O117">
         <v>18.7</v>
@@ -6506,7 +6512,7 @@
         <v>49</v>
       </c>
       <c r="C118" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D118">
         <v>64.5</v>
@@ -6533,13 +6539,13 @@
         <v>1</v>
       </c>
       <c r="L118" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M118" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N118" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O118">
         <v>18.7</v>
@@ -6556,7 +6562,7 @@
         <v>22</v>
       </c>
       <c r="C119" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D119">
         <v>64</v>
@@ -6583,13 +6589,13 @@
         <v>12</v>
       </c>
       <c r="L119" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M119" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N119" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O119">
         <v>18.7</v>
@@ -6606,7 +6612,7 @@
         <v>23</v>
       </c>
       <c r="C120" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D120">
         <v>64</v>
@@ -6633,13 +6639,13 @@
         <v>12</v>
       </c>
       <c r="L120" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M120" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N120" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O120">
         <v>18.7</v>
@@ -6656,7 +6662,7 @@
         <v>46</v>
       </c>
       <c r="C121" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D121">
         <v>64</v>
@@ -6683,13 +6689,13 @@
         <v>6</v>
       </c>
       <c r="L121" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M121" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N121" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O121">
         <v>18.7</v>
@@ -6706,7 +6712,7 @@
         <v>39</v>
       </c>
       <c r="C122" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D122">
         <v>63.9</v>
@@ -6733,13 +6739,13 @@
         <v>2</v>
       </c>
       <c r="L122" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M122" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N122" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O122">
         <v>18.7</v>
@@ -6756,7 +6762,7 @@
         <v>40</v>
       </c>
       <c r="C123" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D123">
         <v>63.9</v>
@@ -6783,13 +6789,13 @@
         <v>1</v>
       </c>
       <c r="L123" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M123" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N123" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O123">
         <v>18.7</v>
@@ -6806,7 +6812,7 @@
         <v>37</v>
       </c>
       <c r="C124" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D124">
         <v>61.9</v>
@@ -6833,13 +6839,13 @@
         <v>12</v>
       </c>
       <c r="L124" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M124" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N124" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O124">
         <v>18.7</v>
@@ -6856,7 +6862,7 @@
         <v>41</v>
       </c>
       <c r="C125" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D125">
         <v>61.4</v>
@@ -6883,13 +6889,13 @@
         <v>6</v>
       </c>
       <c r="L125" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M125" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N125" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O125">
         <v>18.7</v>
@@ -6906,7 +6912,7 @@
         <v>24</v>
       </c>
       <c r="C126" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D126">
         <v>61</v>
@@ -6933,13 +6939,13 @@
         <v>12</v>
       </c>
       <c r="L126" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M126" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N126" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O126">
         <v>18.7</v>
@@ -6956,7 +6962,7 @@
         <v>42</v>
       </c>
       <c r="C127" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D127">
         <v>61</v>
@@ -6983,13 +6989,13 @@
         <v>6</v>
       </c>
       <c r="L127" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M127" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N127" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O127">
         <v>18.7</v>
@@ -7006,7 +7012,7 @@
         <v>44</v>
       </c>
       <c r="C128" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D128">
         <v>60</v>
@@ -7033,13 +7039,13 @@
         <v>1</v>
       </c>
       <c r="L128" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M128" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N128" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O128">
         <v>18.7</v>
@@ -7056,7 +7062,7 @@
         <v>32</v>
       </c>
       <c r="C129" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D129">
         <v>59.4</v>
@@ -7083,13 +7089,13 @@
         <v>7</v>
       </c>
       <c r="L129" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M129" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N129" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O129">
         <v>18.7</v>
@@ -7106,7 +7112,7 @@
         <v>45</v>
       </c>
       <c r="C130" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D130">
         <v>59.4</v>
@@ -7133,13 +7139,13 @@
         <v>6</v>
       </c>
       <c r="L130" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M130" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N130" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O130">
         <v>18.7</v>
@@ -7156,7 +7162,7 @@
         <v>56</v>
       </c>
       <c r="C131" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D131">
         <v>57.3</v>
@@ -7183,13 +7189,13 @@
         <v>1</v>
       </c>
       <c r="L131" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M131" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N131" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O131">
         <v>18.7</v>
@@ -7206,7 +7212,7 @@
         <v>33</v>
       </c>
       <c r="C132" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D132">
         <v>55.6</v>
@@ -7233,13 +7239,13 @@
         <v>12</v>
       </c>
       <c r="L132" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M132" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N132" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O132">
         <v>18.7</v>
@@ -7256,7 +7262,7 @@
         <v>43</v>
       </c>
       <c r="C133" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D133">
         <v>66.40000000000001</v>
@@ -7283,13 +7289,13 @@
         <v>7</v>
       </c>
       <c r="L133" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M133" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N133" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O133">
         <v>18.84</v>
@@ -7306,7 +7312,7 @@
         <v>49</v>
       </c>
       <c r="C134" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D134">
         <v>64.5</v>
@@ -7333,13 +7339,13 @@
         <v>2</v>
       </c>
       <c r="L134" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M134" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N134" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O134">
         <v>18.84</v>
@@ -7356,7 +7362,7 @@
         <v>22</v>
       </c>
       <c r="C135" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D135">
         <v>64</v>
@@ -7383,13 +7389,13 @@
         <v>13</v>
       </c>
       <c r="L135" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M135" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N135" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O135">
         <v>18.84</v>
@@ -7406,7 +7412,7 @@
         <v>23</v>
       </c>
       <c r="C136" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D136">
         <v>64</v>
@@ -7433,13 +7439,13 @@
         <v>13</v>
       </c>
       <c r="L136" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M136" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N136" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O136">
         <v>18.84</v>
@@ -7456,7 +7462,7 @@
         <v>46</v>
       </c>
       <c r="C137" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D137">
         <v>64</v>
@@ -7483,13 +7489,13 @@
         <v>7</v>
       </c>
       <c r="L137" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M137" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N137" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O137">
         <v>18.84</v>
@@ -7506,7 +7512,7 @@
         <v>39</v>
       </c>
       <c r="C138" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D138">
         <v>63.9</v>
@@ -7533,13 +7539,13 @@
         <v>3</v>
       </c>
       <c r="L138" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M138" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N138" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O138">
         <v>18.84</v>
@@ -7556,7 +7562,7 @@
         <v>40</v>
       </c>
       <c r="C139" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D139">
         <v>63.9</v>
@@ -7583,13 +7589,13 @@
         <v>2</v>
       </c>
       <c r="L139" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M139" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N139" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O139">
         <v>18.84</v>
@@ -7606,7 +7612,7 @@
         <v>41</v>
       </c>
       <c r="C140" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D140">
         <v>61.4</v>
@@ -7633,13 +7639,13 @@
         <v>7</v>
       </c>
       <c r="L140" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M140" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N140" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O140">
         <v>18.84</v>
@@ -7656,7 +7662,7 @@
         <v>24</v>
       </c>
       <c r="C141" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D141">
         <v>61</v>
@@ -7683,13 +7689,13 @@
         <v>13</v>
       </c>
       <c r="L141" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M141" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N141" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O141">
         <v>18.84</v>
@@ -7706,7 +7712,7 @@
         <v>42</v>
       </c>
       <c r="C142" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D142">
         <v>61</v>
@@ -7733,13 +7739,13 @@
         <v>7</v>
       </c>
       <c r="L142" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M142" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N142" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O142">
         <v>18.84</v>
@@ -7756,7 +7762,7 @@
         <v>44</v>
       </c>
       <c r="C143" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D143">
         <v>60</v>
@@ -7783,13 +7789,13 @@
         <v>2</v>
       </c>
       <c r="L143" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M143" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N143" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O143">
         <v>18.84</v>
@@ -7806,7 +7812,7 @@
         <v>32</v>
       </c>
       <c r="C144" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D144">
         <v>59.4</v>
@@ -7833,13 +7839,13 @@
         <v>8</v>
       </c>
       <c r="L144" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M144" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N144" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O144">
         <v>18.84</v>
@@ -7856,7 +7862,7 @@
         <v>45</v>
       </c>
       <c r="C145" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D145">
         <v>59.4</v>
@@ -7883,13 +7889,13 @@
         <v>7</v>
       </c>
       <c r="L145" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M145" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N145" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O145">
         <v>18.84</v>
@@ -7906,7 +7912,7 @@
         <v>56</v>
       </c>
       <c r="C146" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D146">
         <v>57.3</v>
@@ -7933,13 +7939,13 @@
         <v>2</v>
       </c>
       <c r="L146" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M146" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N146" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O146">
         <v>18.84</v>
@@ -7956,7 +7962,7 @@
         <v>37</v>
       </c>
       <c r="C147" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D147">
         <v>55.9</v>
@@ -7983,13 +7989,13 @@
         <v>13</v>
       </c>
       <c r="L147" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M147" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N147" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O147">
         <v>18.84</v>
@@ -8006,7 +8012,7 @@
         <v>33</v>
       </c>
       <c r="C148" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D148">
         <v>55.6</v>
@@ -8033,13 +8039,13 @@
         <v>13</v>
       </c>
       <c r="L148" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M148" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N148" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O148">
         <v>18.84</v>
@@ -8056,7 +8062,7 @@
         <v>43</v>
       </c>
       <c r="C149" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D149">
         <v>66.90000000000001</v>
@@ -8083,13 +8089,13 @@
         <v>8</v>
       </c>
       <c r="L149" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M149" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N149" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O149">
         <v>18.44</v>
@@ -8106,7 +8112,7 @@
         <v>39</v>
       </c>
       <c r="C150" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D150">
         <v>66.8</v>
@@ -8133,13 +8139,13 @@
         <v>4</v>
       </c>
       <c r="L150" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M150" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N150" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O150">
         <v>18.44</v>
@@ -8156,7 +8162,7 @@
         <v>49</v>
       </c>
       <c r="C151" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D151">
         <v>65</v>
@@ -8183,13 +8189,13 @@
         <v>3</v>
       </c>
       <c r="L151" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M151" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N151" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O151">
         <v>18.44</v>
@@ -8206,7 +8212,7 @@
         <v>22</v>
       </c>
       <c r="C152" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D152">
         <v>64.5</v>
@@ -8233,13 +8239,13 @@
         <v>14</v>
       </c>
       <c r="L152" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M152" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N152" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O152">
         <v>18.44</v>
@@ -8256,7 +8262,7 @@
         <v>23</v>
       </c>
       <c r="C153" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D153">
         <v>64.5</v>
@@ -8283,13 +8289,13 @@
         <v>14</v>
       </c>
       <c r="L153" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M153" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N153" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O153">
         <v>18.44</v>
@@ -8306,7 +8312,7 @@
         <v>46</v>
       </c>
       <c r="C154" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D154">
         <v>64.5</v>
@@ -8333,13 +8339,13 @@
         <v>8</v>
       </c>
       <c r="L154" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M154" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N154" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O154">
         <v>18.44</v>
@@ -8356,7 +8362,7 @@
         <v>40</v>
       </c>
       <c r="C155" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D155">
         <v>64.40000000000001</v>
@@ -8383,13 +8389,13 @@
         <v>3</v>
       </c>
       <c r="L155" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M155" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N155" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O155">
         <v>18.44</v>
@@ -8406,7 +8412,7 @@
         <v>45</v>
       </c>
       <c r="C156" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D156">
         <v>63.3</v>
@@ -8433,13 +8439,13 @@
         <v>8</v>
       </c>
       <c r="L156" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M156" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N156" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O156">
         <v>18.44</v>
@@ -8456,7 +8462,7 @@
         <v>41</v>
       </c>
       <c r="C157" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D157">
         <v>62.9</v>
@@ -8483,13 +8489,13 @@
         <v>8</v>
       </c>
       <c r="L157" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M157" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N157" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O157">
         <v>18.44</v>
@@ -8506,7 +8512,7 @@
         <v>24</v>
       </c>
       <c r="C158" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D158">
         <v>61.5</v>
@@ -8533,13 +8539,13 @@
         <v>14</v>
       </c>
       <c r="L158" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M158" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N158" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O158">
         <v>18.44</v>
@@ -8556,7 +8562,7 @@
         <v>42</v>
       </c>
       <c r="C159" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D159">
         <v>61.5</v>
@@ -8583,13 +8589,13 @@
         <v>8</v>
       </c>
       <c r="L159" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M159" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N159" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O159">
         <v>18.44</v>
@@ -8606,7 +8612,7 @@
         <v>32</v>
       </c>
       <c r="C160" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D160">
         <v>60.9</v>
@@ -8633,13 +8639,13 @@
         <v>9</v>
       </c>
       <c r="L160" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M160" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N160" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O160">
         <v>18.44</v>
@@ -8656,7 +8662,7 @@
         <v>44</v>
       </c>
       <c r="C161" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D161">
         <v>60.5</v>
@@ -8683,13 +8689,13 @@
         <v>3</v>
       </c>
       <c r="L161" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M161" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N161" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O161">
         <v>18.44</v>
@@ -8706,7 +8712,7 @@
         <v>56</v>
       </c>
       <c r="C162" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D162">
         <v>57.8</v>
@@ -8733,13 +8739,13 @@
         <v>3</v>
       </c>
       <c r="L162" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M162" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N162" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O162">
         <v>18.44</v>
@@ -8756,7 +8762,7 @@
         <v>37</v>
       </c>
       <c r="C163" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D163">
         <v>56.4</v>
@@ -8783,13 +8789,13 @@
         <v>14</v>
       </c>
       <c r="L163" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M163" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N163" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O163">
         <v>18.44</v>
@@ -8806,7 +8812,7 @@
         <v>33</v>
       </c>
       <c r="C164" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D164">
         <v>56.1</v>
@@ -8833,13 +8839,13 @@
         <v>14</v>
       </c>
       <c r="L164" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M164" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N164" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="O164">
         <v>18.44</v>
@@ -8856,7 +8862,7 @@
         <v>57</v>
       </c>
       <c r="C165" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D165">
         <v>78.8</v>
@@ -8880,13 +8886,13 @@
         <v>1</v>
       </c>
       <c r="L165" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M165" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N165" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O165">
         <v>18.59</v>
@@ -8903,7 +8909,7 @@
         <v>58</v>
       </c>
       <c r="C166" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D166">
         <v>75.8</v>
@@ -8927,13 +8933,13 @@
         <v>1</v>
       </c>
       <c r="L166" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M166" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N166" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O166">
         <v>18.59</v>
@@ -8950,7 +8956,7 @@
         <v>59</v>
       </c>
       <c r="C167" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D167">
         <v>69.3</v>
@@ -8977,13 +8983,13 @@
         <v>1</v>
       </c>
       <c r="L167" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M167" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N167" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O167">
         <v>18.59</v>
@@ -9000,7 +9006,7 @@
         <v>60</v>
       </c>
       <c r="C168" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D168">
         <v>68.3</v>
@@ -9027,13 +9033,13 @@
         <v>1</v>
       </c>
       <c r="L168" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M168" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N168" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O168">
         <v>18.59</v>
@@ -9050,7 +9056,7 @@
         <v>61</v>
       </c>
       <c r="C169" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D169">
         <v>66.40000000000001</v>
@@ -9077,13 +9083,13 @@
         <v>1</v>
       </c>
       <c r="L169" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M169" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N169" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O169">
         <v>18.59</v>
@@ -9100,7 +9106,7 @@
         <v>62</v>
       </c>
       <c r="C170" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D170">
         <v>66.3</v>
@@ -9127,13 +9133,13 @@
         <v>1</v>
       </c>
       <c r="L170" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M170" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N170" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O170">
         <v>18.59</v>
@@ -9150,7 +9156,7 @@
         <v>63</v>
       </c>
       <c r="C171" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D171">
         <v>65.40000000000001</v>
@@ -9177,13 +9183,13 @@
         <v>1</v>
       </c>
       <c r="L171" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M171" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N171" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O171">
         <v>18.59</v>
@@ -9200,7 +9206,7 @@
         <v>22</v>
       </c>
       <c r="C172" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D172">
         <v>64</v>
@@ -9227,13 +9233,13 @@
         <v>15</v>
       </c>
       <c r="L172" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M172" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N172" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O172">
         <v>18.59</v>
@@ -9250,7 +9256,7 @@
         <v>23</v>
       </c>
       <c r="C173" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D173">
         <v>64</v>
@@ -9277,13 +9283,13 @@
         <v>15</v>
       </c>
       <c r="L173" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M173" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N173" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O173">
         <v>18.59</v>
@@ -9300,7 +9306,7 @@
         <v>39</v>
       </c>
       <c r="C174" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D174">
         <v>63.9</v>
@@ -9327,13 +9333,13 @@
         <v>5</v>
       </c>
       <c r="L174" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M174" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N174" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O174">
         <v>18.59</v>
@@ -9350,7 +9356,7 @@
         <v>64</v>
       </c>
       <c r="C175" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D175">
         <v>61.5</v>
@@ -9377,13 +9383,13 @@
         <v>1</v>
       </c>
       <c r="L175" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M175" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N175" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O175">
         <v>18.59</v>
@@ -9400,7 +9406,7 @@
         <v>32</v>
       </c>
       <c r="C176" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D176">
         <v>61.4</v>
@@ -9427,13 +9433,13 @@
         <v>10</v>
       </c>
       <c r="L176" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M176" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N176" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O176">
         <v>18.59</v>
@@ -9450,7 +9456,7 @@
         <v>65</v>
       </c>
       <c r="C177" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D177">
         <v>61.4</v>
@@ -9477,13 +9483,13 @@
         <v>1</v>
       </c>
       <c r="L177" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M177" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N177" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O177">
         <v>18.59</v>
@@ -9500,7 +9506,7 @@
         <v>66</v>
       </c>
       <c r="C178" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D178">
         <v>60.9</v>
@@ -9527,13 +9533,13 @@
         <v>1</v>
       </c>
       <c r="L178" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M178" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N178" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O178">
         <v>18.59</v>
@@ -9550,7 +9556,7 @@
         <v>67</v>
       </c>
       <c r="C179" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D179">
         <v>59.4</v>
@@ -9577,13 +9583,13 @@
         <v>1</v>
       </c>
       <c r="L179" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M179" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N179" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O179">
         <v>18.59</v>
@@ -9600,7 +9606,7 @@
         <v>68</v>
       </c>
       <c r="C180" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D180">
         <v>59.4</v>
@@ -9627,13 +9633,13 @@
         <v>1</v>
       </c>
       <c r="L180" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M180" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N180" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O180">
         <v>18.59</v>
@@ -9650,7 +9656,7 @@
         <v>56</v>
       </c>
       <c r="C181" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D181">
         <v>57.3</v>
@@ -9677,13 +9683,13 @@
         <v>4</v>
       </c>
       <c r="L181" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M181" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N181" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O181">
         <v>18.59</v>
@@ -9700,7 +9706,7 @@
         <v>69</v>
       </c>
       <c r="C182" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D182">
         <v>56.9</v>
@@ -9727,13 +9733,13 @@
         <v>1</v>
       </c>
       <c r="L182" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M182" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N182" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O182">
         <v>18.59</v>
@@ -9750,7 +9756,7 @@
         <v>33</v>
       </c>
       <c r="C183" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D183">
         <v>56.6</v>
@@ -9777,13 +9783,13 @@
         <v>15</v>
       </c>
       <c r="L183" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M183" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N183" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O183">
         <v>18.59</v>
@@ -9800,7 +9806,7 @@
         <v>37</v>
       </c>
       <c r="C184" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D184">
         <v>55.9</v>
@@ -9827,13 +9833,13 @@
         <v>15</v>
       </c>
       <c r="L184" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M184" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N184" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O184">
         <v>18.59</v>
@@ -9850,7 +9856,7 @@
         <v>57</v>
       </c>
       <c r="C185" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D185">
         <v>78.8</v>
@@ -9874,13 +9880,13 @@
         <v>1</v>
       </c>
       <c r="L185" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M185" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N185" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O185">
         <v>18.59</v>
@@ -9897,7 +9903,7 @@
         <v>58</v>
       </c>
       <c r="C186" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="D186">
         <v>75.8</v>
@@ -9921,13 +9927,13 @@
         <v>1</v>
       </c>
       <c r="L186" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="M186" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N186" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O186">
         <v>18.59</v>
@@ -9944,7 +9950,7 @@
         <v>59</v>
       </c>
       <c r="C187" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D187">
         <v>69.3</v>
@@ -9971,13 +9977,13 @@
         <v>2</v>
       </c>
       <c r="L187" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M187" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N187" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O187">
         <v>18.59</v>
@@ -9994,7 +10000,7 @@
         <v>60</v>
       </c>
       <c r="C188" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D188">
         <v>68.3</v>
@@ -10021,13 +10027,13 @@
         <v>2</v>
       </c>
       <c r="L188" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M188" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N188" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O188">
         <v>18.59</v>
@@ -10044,7 +10050,7 @@
         <v>61</v>
       </c>
       <c r="C189" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D189">
         <v>66.40000000000001</v>
@@ -10071,13 +10077,13 @@
         <v>2</v>
       </c>
       <c r="L189" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M189" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N189" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O189">
         <v>18.59</v>
@@ -10094,7 +10100,7 @@
         <v>62</v>
       </c>
       <c r="C190" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D190">
         <v>66.3</v>
@@ -10121,13 +10127,13 @@
         <v>2</v>
       </c>
       <c r="L190" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M190" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N190" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O190">
         <v>18.59</v>
@@ -10144,7 +10150,7 @@
         <v>63</v>
       </c>
       <c r="C191" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D191">
         <v>65.40000000000001</v>
@@ -10171,13 +10177,13 @@
         <v>2</v>
       </c>
       <c r="L191" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M191" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N191" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O191">
         <v>18.59</v>
@@ -10194,7 +10200,7 @@
         <v>22</v>
       </c>
       <c r="C192" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D192">
         <v>64</v>
@@ -10221,13 +10227,13 @@
         <v>16</v>
       </c>
       <c r="L192" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M192" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N192" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O192">
         <v>18.59</v>
@@ -10244,7 +10250,7 @@
         <v>23</v>
       </c>
       <c r="C193" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D193">
         <v>64</v>
@@ -10271,13 +10277,13 @@
         <v>16</v>
       </c>
       <c r="L193" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M193" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N193" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O193">
         <v>18.59</v>
@@ -10294,7 +10300,7 @@
         <v>39</v>
       </c>
       <c r="C194" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D194">
         <v>63.9</v>
@@ -10321,13 +10327,13 @@
         <v>6</v>
       </c>
       <c r="L194" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M194" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N194" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O194">
         <v>18.59</v>
@@ -10344,7 +10350,7 @@
         <v>64</v>
       </c>
       <c r="C195" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D195">
         <v>61.5</v>
@@ -10371,13 +10377,13 @@
         <v>2</v>
       </c>
       <c r="L195" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M195" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N195" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O195">
         <v>18.59</v>
@@ -10394,7 +10400,7 @@
         <v>32</v>
       </c>
       <c r="C196" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D196">
         <v>61.4</v>
@@ -10421,13 +10427,13 @@
         <v>11</v>
       </c>
       <c r="L196" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M196" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N196" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O196">
         <v>18.59</v>
@@ -10444,7 +10450,7 @@
         <v>65</v>
       </c>
       <c r="C197" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D197">
         <v>61.4</v>
@@ -10471,13 +10477,13 @@
         <v>2</v>
       </c>
       <c r="L197" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M197" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N197" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O197">
         <v>18.59</v>
@@ -10494,7 +10500,7 @@
         <v>66</v>
       </c>
       <c r="C198" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D198">
         <v>60.9</v>
@@ -10521,13 +10527,13 @@
         <v>2</v>
       </c>
       <c r="L198" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M198" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N198" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O198">
         <v>18.59</v>
@@ -10544,7 +10550,7 @@
         <v>67</v>
       </c>
       <c r="C199" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D199">
         <v>59.4</v>
@@ -10571,13 +10577,13 @@
         <v>2</v>
       </c>
       <c r="L199" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M199" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N199" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O199">
         <v>18.59</v>
@@ -10594,7 +10600,7 @@
         <v>68</v>
       </c>
       <c r="C200" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D200">
         <v>59.4</v>
@@ -10621,13 +10627,13 @@
         <v>2</v>
       </c>
       <c r="L200" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M200" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N200" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O200">
         <v>18.59</v>
@@ -10644,7 +10650,7 @@
         <v>56</v>
       </c>
       <c r="C201" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D201">
         <v>57.3</v>
@@ -10671,13 +10677,13 @@
         <v>5</v>
       </c>
       <c r="L201" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M201" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N201" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O201">
         <v>18.59</v>
@@ -10694,7 +10700,7 @@
         <v>69</v>
       </c>
       <c r="C202" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D202">
         <v>56.9</v>
@@ -10721,13 +10727,13 @@
         <v>2</v>
       </c>
       <c r="L202" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M202" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N202" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O202">
         <v>18.59</v>
@@ -10744,7 +10750,7 @@
         <v>33</v>
       </c>
       <c r="C203" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D203">
         <v>56.6</v>
@@ -10771,13 +10777,13 @@
         <v>16</v>
       </c>
       <c r="L203" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M203" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N203" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O203">
         <v>18.59</v>
@@ -10794,7 +10800,7 @@
         <v>37</v>
       </c>
       <c r="C204" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D204">
         <v>55.9</v>
@@ -10821,13 +10827,13 @@
         <v>16</v>
       </c>
       <c r="L204" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M204" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N204" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="O204">
         <v>18.59</v>
@@ -10844,7 +10850,7 @@
         <v>40</v>
       </c>
       <c r="C205" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D205">
         <v>63.9</v>
@@ -10871,13 +10877,13 @@
         <v>1</v>
       </c>
       <c r="L205" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M205" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N205" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O205">
         <v>19.3</v>
@@ -10894,7 +10900,7 @@
         <v>39</v>
       </c>
       <c r="C206" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D206">
         <v>61.5</v>
@@ -10921,13 +10927,13 @@
         <v>7</v>
       </c>
       <c r="L206" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M206" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N206" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O206">
         <v>19.3</v>
@@ -10944,7 +10950,7 @@
         <v>49</v>
       </c>
       <c r="C207" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D207">
         <v>61.5</v>
@@ -10971,13 +10977,13 @@
         <v>1</v>
       </c>
       <c r="L207" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M207" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N207" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O207">
         <v>19.3</v>
@@ -10994,7 +11000,7 @@
         <v>41</v>
       </c>
       <c r="C208" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D208">
         <v>61.4</v>
@@ -11021,13 +11027,13 @@
         <v>1</v>
       </c>
       <c r="L208" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M208" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N208" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O208">
         <v>19.3</v>
@@ -11044,7 +11050,7 @@
         <v>22</v>
       </c>
       <c r="C209" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D209">
         <v>61</v>
@@ -11071,13 +11077,13 @@
         <v>17</v>
       </c>
       <c r="L209" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M209" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N209" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O209">
         <v>19.3</v>
@@ -11094,7 +11100,7 @@
         <v>23</v>
       </c>
       <c r="C210" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D210">
         <v>61</v>
@@ -11121,13 +11127,13 @@
         <v>17</v>
       </c>
       <c r="L210" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M210" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N210" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O210">
         <v>19.3</v>
@@ -11144,7 +11150,7 @@
         <v>33</v>
       </c>
       <c r="C211" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D211">
         <v>61</v>
@@ -11171,13 +11177,13 @@
         <v>17</v>
       </c>
       <c r="L211" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M211" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N211" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O211">
         <v>19.3</v>
@@ -11194,7 +11200,7 @@
         <v>42</v>
       </c>
       <c r="C212" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D212">
         <v>61</v>
@@ -11221,13 +11227,13 @@
         <v>1</v>
       </c>
       <c r="L212" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M212" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N212" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O212">
         <v>19.3</v>
@@ -11244,7 +11250,7 @@
         <v>43</v>
       </c>
       <c r="C213" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D213">
         <v>60.4</v>
@@ -11271,13 +11277,13 @@
         <v>1</v>
       </c>
       <c r="L213" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M213" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N213" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O213">
         <v>19.3</v>
@@ -11294,7 +11300,7 @@
         <v>44</v>
       </c>
       <c r="C214" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D214">
         <v>60</v>
@@ -11321,13 +11327,13 @@
         <v>1</v>
       </c>
       <c r="L214" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M214" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N214" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O214">
         <v>19.3</v>
@@ -11344,7 +11350,7 @@
         <v>56</v>
       </c>
       <c r="C215" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D215">
         <v>59.7</v>
@@ -11371,13 +11377,13 @@
         <v>6</v>
       </c>
       <c r="L215" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M215" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N215" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O215">
         <v>19.3</v>
@@ -11394,7 +11400,7 @@
         <v>32</v>
       </c>
       <c r="C216" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D216">
         <v>59.4</v>
@@ -11421,13 +11427,13 @@
         <v>12</v>
       </c>
       <c r="L216" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M216" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N216" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O216">
         <v>19.3</v>
@@ -11444,7 +11450,7 @@
         <v>45</v>
       </c>
       <c r="C217" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D217">
         <v>59.4</v>
@@ -11471,13 +11477,13 @@
         <v>1</v>
       </c>
       <c r="L217" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M217" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N217" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O217">
         <v>19.3</v>
@@ -11494,7 +11500,7 @@
         <v>37</v>
       </c>
       <c r="C218" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D218">
         <v>58.4</v>
@@ -11521,13 +11527,13 @@
         <v>17</v>
       </c>
       <c r="L218" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M218" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N218" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O218">
         <v>19.3</v>
@@ -11544,7 +11550,7 @@
         <v>39</v>
       </c>
       <c r="C219" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D219">
         <v>63.9</v>
@@ -11571,13 +11577,13 @@
         <v>8</v>
       </c>
       <c r="L219" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M219" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N219" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O219">
         <v>19.25</v>
@@ -11594,7 +11600,7 @@
         <v>40</v>
       </c>
       <c r="C220" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D220">
         <v>63.9</v>
@@ -11621,13 +11627,13 @@
         <v>2</v>
       </c>
       <c r="L220" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M220" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N220" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O220">
         <v>19.25</v>
@@ -11644,7 +11650,7 @@
         <v>49</v>
       </c>
       <c r="C221" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D221">
         <v>61.5</v>
@@ -11671,13 +11677,13 @@
         <v>2</v>
       </c>
       <c r="L221" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M221" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N221" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O221">
         <v>19.25</v>
@@ -11694,7 +11700,7 @@
         <v>41</v>
       </c>
       <c r="C222" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D222">
         <v>61.4</v>
@@ -11721,13 +11727,13 @@
         <v>2</v>
       </c>
       <c r="L222" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M222" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N222" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O222">
         <v>19.25</v>
@@ -11744,7 +11750,7 @@
         <v>22</v>
       </c>
       <c r="C223" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D223">
         <v>61</v>
@@ -11771,13 +11777,13 @@
         <v>18</v>
       </c>
       <c r="L223" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M223" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N223" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O223">
         <v>19.25</v>
@@ -11794,7 +11800,7 @@
         <v>23</v>
       </c>
       <c r="C224" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D224">
         <v>61</v>
@@ -11821,13 +11827,13 @@
         <v>18</v>
       </c>
       <c r="L224" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M224" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N224" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O224">
         <v>19.25</v>
@@ -11844,7 +11850,7 @@
         <v>33</v>
       </c>
       <c r="C225" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D225">
         <v>61</v>
@@ -11871,13 +11877,13 @@
         <v>18</v>
       </c>
       <c r="L225" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M225" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N225" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O225">
         <v>19.25</v>
@@ -11894,7 +11900,7 @@
         <v>42</v>
       </c>
       <c r="C226" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D226">
         <v>61</v>
@@ -11921,13 +11927,13 @@
         <v>2</v>
       </c>
       <c r="L226" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M226" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N226" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O226">
         <v>19.25</v>
@@ -11944,7 +11950,7 @@
         <v>43</v>
       </c>
       <c r="C227" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D227">
         <v>60.4</v>
@@ -11971,13 +11977,13 @@
         <v>2</v>
       </c>
       <c r="L227" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M227" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N227" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O227">
         <v>19.25</v>
@@ -11994,7 +12000,7 @@
         <v>44</v>
       </c>
       <c r="C228" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D228">
         <v>60</v>
@@ -12021,13 +12027,13 @@
         <v>2</v>
       </c>
       <c r="L228" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M228" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N228" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O228">
         <v>19.25</v>
@@ -12044,7 +12050,7 @@
         <v>56</v>
       </c>
       <c r="C229" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D229">
         <v>59.7</v>
@@ -12071,13 +12077,13 @@
         <v>7</v>
       </c>
       <c r="L229" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M229" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N229" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O229">
         <v>19.25</v>
@@ -12094,7 +12100,7 @@
         <v>32</v>
       </c>
       <c r="C230" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D230">
         <v>59.4</v>
@@ -12121,13 +12127,13 @@
         <v>13</v>
       </c>
       <c r="L230" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M230" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N230" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O230">
         <v>19.25</v>
@@ -12144,7 +12150,7 @@
         <v>45</v>
       </c>
       <c r="C231" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D231">
         <v>59.4</v>
@@ -12171,13 +12177,13 @@
         <v>2</v>
       </c>
       <c r="L231" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M231" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N231" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O231">
         <v>19.25</v>
@@ -12194,7 +12200,7 @@
         <v>37</v>
       </c>
       <c r="C232" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D232">
         <v>55.9</v>
@@ -12221,13 +12227,13 @@
         <v>18</v>
       </c>
       <c r="L232" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M232" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N232" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O232">
         <v>19.25</v>
@@ -12237,20 +12243,20 @@
       </c>
     </row>
     <row r="233" spans="1:16">
-      <c r="A233" t="s">
-        <v>16</v>
+      <c r="A233">
+        <v>20260424</v>
       </c>
       <c r="B233" t="s">
         <v>49</v>
       </c>
       <c r="C233" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D233">
         <v>64.5</v>
       </c>
-      <c r="E233" t="s">
-        <v>73</v>
+      <c r="E233">
+        <v>3</v>
       </c>
       <c r="F233" t="s">
         <v>80</v>
@@ -12271,13 +12277,13 @@
         <v>3</v>
       </c>
       <c r="L233" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M233" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N233" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O233">
         <v>19.74</v>
@@ -12287,20 +12293,20 @@
       </c>
     </row>
     <row r="234" spans="1:16">
-      <c r="A234" t="s">
-        <v>16</v>
+      <c r="A234">
+        <v>20260424</v>
       </c>
       <c r="B234" t="s">
         <v>42</v>
       </c>
       <c r="C234" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D234">
         <v>64</v>
       </c>
-      <c r="E234" t="s">
-        <v>73</v>
+      <c r="E234">
+        <v>3</v>
       </c>
       <c r="F234" t="s">
         <v>80</v>
@@ -12321,13 +12327,13 @@
         <v>3</v>
       </c>
       <c r="L234" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M234" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N234" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O234">
         <v>19.74</v>
@@ -12337,20 +12343,20 @@
       </c>
     </row>
     <row r="235" spans="1:16">
-      <c r="A235" t="s">
-        <v>16</v>
+      <c r="A235">
+        <v>20260424</v>
       </c>
       <c r="B235" t="s">
         <v>39</v>
       </c>
       <c r="C235" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D235">
         <v>63.9</v>
       </c>
-      <c r="E235" t="s">
-        <v>74</v>
+      <c r="E235">
+        <v>0</v>
       </c>
       <c r="F235" t="s">
         <v>80</v>
@@ -12371,13 +12377,13 @@
         <v>9</v>
       </c>
       <c r="L235" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="M235" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N235" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O235">
         <v>19.74</v>
@@ -12387,20 +12393,20 @@
       </c>
     </row>
     <row r="236" spans="1:16">
-      <c r="A236" t="s">
-        <v>16</v>
+      <c r="A236">
+        <v>20260424</v>
       </c>
       <c r="B236" t="s">
         <v>41</v>
       </c>
       <c r="C236" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D236">
         <v>63.9</v>
       </c>
-      <c r="E236" t="s">
-        <v>75</v>
+      <c r="E236">
+        <v>2.5</v>
       </c>
       <c r="F236" t="s">
         <v>80</v>
@@ -12421,13 +12427,13 @@
         <v>3</v>
       </c>
       <c r="L236" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M236" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N236" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O236">
         <v>19.74</v>
@@ -12437,20 +12443,20 @@
       </c>
     </row>
     <row r="237" spans="1:16">
-      <c r="A237" t="s">
-        <v>16</v>
+      <c r="A237">
+        <v>20260424</v>
       </c>
       <c r="B237" t="s">
         <v>40</v>
       </c>
       <c r="C237" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D237">
         <v>63.9</v>
       </c>
-      <c r="E237" t="s">
-        <v>74</v>
+      <c r="E237">
+        <v>0</v>
       </c>
       <c r="F237" t="s">
         <v>80</v>
@@ -12471,13 +12477,13 @@
         <v>3</v>
       </c>
       <c r="L237" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M237" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N237" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O237">
         <v>19.74</v>
@@ -12487,20 +12493,20 @@
       </c>
     </row>
     <row r="238" spans="1:16">
-      <c r="A238" t="s">
-        <v>16</v>
+      <c r="A238">
+        <v>20260424</v>
       </c>
       <c r="B238" t="s">
         <v>70</v>
       </c>
       <c r="C238" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D238">
         <v>61.6</v>
       </c>
-      <c r="E238" t="s">
-        <v>74</v>
+      <c r="E238">
+        <v>0</v>
       </c>
       <c r="F238" t="s">
         <v>80</v>
@@ -12521,13 +12527,13 @@
         <v>1</v>
       </c>
       <c r="L238" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M238" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N238" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O238">
         <v>19.74</v>
@@ -12537,20 +12543,20 @@
       </c>
     </row>
     <row r="239" spans="1:16">
-      <c r="A239" t="s">
-        <v>16</v>
+      <c r="A239">
+        <v>20260424</v>
       </c>
       <c r="B239" t="s">
         <v>32</v>
       </c>
       <c r="C239" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D239">
         <v>61.4</v>
       </c>
-      <c r="E239" t="s">
-        <v>76</v>
+      <c r="E239">
+        <v>2</v>
       </c>
       <c r="F239" t="s">
         <v>80</v>
@@ -12571,13 +12577,13 @@
         <v>14</v>
       </c>
       <c r="L239" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="M239" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N239" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O239">
         <v>19.74</v>
@@ -12587,20 +12593,20 @@
       </c>
     </row>
     <row r="240" spans="1:16">
-      <c r="A240" t="s">
-        <v>16</v>
+      <c r="A240">
+        <v>20260424</v>
       </c>
       <c r="B240" t="s">
         <v>22</v>
       </c>
       <c r="C240" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D240">
         <v>61</v>
       </c>
-      <c r="E240" t="s">
-        <v>74</v>
+      <c r="E240">
+        <v>0</v>
       </c>
       <c r="F240" t="s">
         <v>80</v>
@@ -12621,13 +12627,13 @@
         <v>19</v>
       </c>
       <c r="L240" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M240" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N240" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O240">
         <v>19.74</v>
@@ -12637,20 +12643,20 @@
       </c>
     </row>
     <row r="241" spans="1:16">
-      <c r="A241" t="s">
-        <v>16</v>
+      <c r="A241">
+        <v>20260424</v>
       </c>
       <c r="B241" t="s">
         <v>23</v>
       </c>
       <c r="C241" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D241">
         <v>61</v>
       </c>
-      <c r="E241" t="s">
-        <v>74</v>
+      <c r="E241">
+        <v>0</v>
       </c>
       <c r="F241" t="s">
         <v>80</v>
@@ -12671,13 +12677,13 @@
         <v>19</v>
       </c>
       <c r="L241" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M241" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N241" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O241">
         <v>19.74</v>
@@ -12687,20 +12693,20 @@
       </c>
     </row>
     <row r="242" spans="1:16">
-      <c r="A242" t="s">
-        <v>16</v>
+      <c r="A242">
+        <v>20260424</v>
       </c>
       <c r="B242" t="s">
         <v>45</v>
       </c>
       <c r="C242" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D242">
         <v>60.4</v>
       </c>
-      <c r="E242" t="s">
-        <v>77</v>
+      <c r="E242">
+        <v>1</v>
       </c>
       <c r="F242" t="s">
         <v>80</v>
@@ -12721,13 +12727,13 @@
         <v>3</v>
       </c>
       <c r="L242" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M242" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N242" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O242">
         <v>19.74</v>
@@ -12737,20 +12743,20 @@
       </c>
     </row>
     <row r="243" spans="1:16">
-      <c r="A243" t="s">
-        <v>16</v>
+      <c r="A243">
+        <v>20260424</v>
       </c>
       <c r="B243" t="s">
         <v>44</v>
       </c>
       <c r="C243" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D243">
         <v>60</v>
       </c>
-      <c r="E243" t="s">
-        <v>74</v>
+      <c r="E243">
+        <v>0</v>
       </c>
       <c r="F243" t="s">
         <v>80</v>
@@ -12771,13 +12777,13 @@
         <v>3</v>
       </c>
       <c r="L243" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M243" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N243" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O243">
         <v>19.74</v>
@@ -12787,20 +12793,20 @@
       </c>
     </row>
     <row r="244" spans="1:16">
-      <c r="A244" t="s">
-        <v>16</v>
+      <c r="A244">
+        <v>20260424</v>
       </c>
       <c r="B244" t="s">
         <v>56</v>
       </c>
       <c r="C244" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D244">
         <v>59.7</v>
       </c>
-      <c r="E244" t="s">
-        <v>74</v>
+      <c r="E244">
+        <v>0</v>
       </c>
       <c r="F244" t="s">
         <v>80</v>
@@ -12821,13 +12827,13 @@
         <v>8</v>
       </c>
       <c r="L244" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="M244" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N244" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O244">
         <v>19.74</v>
@@ -12837,20 +12843,20 @@
       </c>
     </row>
     <row r="245" spans="1:16">
-      <c r="A245" t="s">
-        <v>16</v>
+      <c r="A245">
+        <v>20260424</v>
       </c>
       <c r="B245" t="s">
         <v>33</v>
       </c>
       <c r="C245" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D245">
         <v>59.2</v>
       </c>
-      <c r="E245" t="s">
-        <v>78</v>
+      <c r="E245">
+        <v>-1.8</v>
       </c>
       <c r="F245" t="s">
         <v>80</v>
@@ -12871,13 +12877,13 @@
         <v>19</v>
       </c>
       <c r="L245" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M245" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N245" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O245">
         <v>19.74</v>
@@ -12887,20 +12893,20 @@
       </c>
     </row>
     <row r="246" spans="1:16">
-      <c r="A246" t="s">
-        <v>16</v>
+      <c r="A246">
+        <v>20260424</v>
       </c>
       <c r="B246" t="s">
         <v>37</v>
       </c>
       <c r="C246" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D246">
         <v>58.4</v>
       </c>
-      <c r="E246" t="s">
-        <v>75</v>
+      <c r="E246">
+        <v>2.5</v>
       </c>
       <c r="F246" t="s">
         <v>80</v>
@@ -12921,13 +12927,13 @@
         <v>19</v>
       </c>
       <c r="L246" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="M246" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N246" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O246">
         <v>19.74</v>
@@ -12937,20 +12943,20 @@
       </c>
     </row>
     <row r="247" spans="1:16">
-      <c r="A247" t="s">
-        <v>16</v>
+      <c r="A247">
+        <v>20260424</v>
       </c>
       <c r="B247" t="s">
         <v>43</v>
       </c>
       <c r="C247" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="D247">
         <v>57.9</v>
       </c>
-      <c r="E247" t="s">
-        <v>79</v>
+      <c r="E247">
+        <v>-2.5</v>
       </c>
       <c r="F247" t="s">
         <v>80</v>
@@ -12971,19 +12977,1066 @@
         <v>3</v>
       </c>
       <c r="L247" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M247" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N247" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O247">
         <v>19.74</v>
       </c>
       <c r="P247">
         <v>17</v>
+      </c>
+    </row>
+    <row r="248" spans="1:16">
+      <c r="A248" t="s">
+        <v>16</v>
+      </c>
+      <c r="B248" t="s">
+        <v>30</v>
+      </c>
+      <c r="C248" t="s">
+        <v>75</v>
+      </c>
+      <c r="D248">
+        <v>75.90000000000001</v>
+      </c>
+      <c r="E248" t="s">
+        <v>77</v>
+      </c>
+      <c r="F248" t="s">
+        <v>80</v>
+      </c>
+      <c r="G248" t="s">
+        <v>81</v>
+      </c>
+      <c r="H248">
+        <v>6452</v>
+      </c>
+      <c r="I248">
+        <v>0</v>
+      </c>
+      <c r="K248">
+        <v>1</v>
+      </c>
+      <c r="L248" t="s">
+        <v>16</v>
+      </c>
+      <c r="M248" t="s">
+        <v>101</v>
+      </c>
+      <c r="N248" t="s">
+        <v>111</v>
+      </c>
+      <c r="O248">
+        <v>19.71</v>
+      </c>
+      <c r="P248">
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="249" spans="1:16">
+      <c r="A249" t="s">
+        <v>16</v>
+      </c>
+      <c r="B249" t="s">
+        <v>21</v>
+      </c>
+      <c r="C249" t="s">
+        <v>76</v>
+      </c>
+      <c r="D249">
+        <v>69</v>
+      </c>
+      <c r="E249" t="s">
+        <v>77</v>
+      </c>
+      <c r="F249" t="s">
+        <v>80</v>
+      </c>
+      <c r="G249" t="s">
+        <v>82</v>
+      </c>
+      <c r="H249">
+        <v>1341</v>
+      </c>
+      <c r="I249">
+        <v>1</v>
+      </c>
+      <c r="J249" t="s">
+        <v>84</v>
+      </c>
+      <c r="K249">
+        <v>1</v>
+      </c>
+      <c r="L249" t="s">
+        <v>100</v>
+      </c>
+      <c r="M249" t="s">
+        <v>101</v>
+      </c>
+      <c r="N249" t="s">
+        <v>111</v>
+      </c>
+      <c r="O249">
+        <v>19.71</v>
+      </c>
+      <c r="P249">
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="250" spans="1:16">
+      <c r="A250" t="s">
+        <v>16</v>
+      </c>
+      <c r="B250" t="s">
+        <v>19</v>
+      </c>
+      <c r="C250" t="s">
+        <v>76</v>
+      </c>
+      <c r="D250">
+        <v>68.40000000000001</v>
+      </c>
+      <c r="E250" t="s">
+        <v>77</v>
+      </c>
+      <c r="F250" t="s">
+        <v>80</v>
+      </c>
+      <c r="G250" t="s">
+        <v>81</v>
+      </c>
+      <c r="H250">
+        <v>1699.5</v>
+      </c>
+      <c r="I250">
+        <v>1.599999999999994</v>
+      </c>
+      <c r="J250" t="s">
+        <v>83</v>
+      </c>
+      <c r="K250">
+        <v>1</v>
+      </c>
+      <c r="L250" t="s">
+        <v>100</v>
+      </c>
+      <c r="M250" t="s">
+        <v>101</v>
+      </c>
+      <c r="N250" t="s">
+        <v>111</v>
+      </c>
+      <c r="O250">
+        <v>19.71</v>
+      </c>
+      <c r="P250">
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="251" spans="1:16">
+      <c r="A251" t="s">
+        <v>16</v>
+      </c>
+      <c r="B251" t="s">
+        <v>35</v>
+      </c>
+      <c r="C251" t="s">
+        <v>76</v>
+      </c>
+      <c r="D251">
+        <v>68.3</v>
+      </c>
+      <c r="E251" t="s">
+        <v>77</v>
+      </c>
+      <c r="F251" t="s">
+        <v>80</v>
+      </c>
+      <c r="G251" t="s">
+        <v>81</v>
+      </c>
+      <c r="H251">
+        <v>1067.65</v>
+      </c>
+      <c r="I251">
+        <v>1.700000000000003</v>
+      </c>
+      <c r="J251" t="s">
+        <v>83</v>
+      </c>
+      <c r="K251">
+        <v>1</v>
+      </c>
+      <c r="L251" t="s">
+        <v>100</v>
+      </c>
+      <c r="M251" t="s">
+        <v>101</v>
+      </c>
+      <c r="N251" t="s">
+        <v>111</v>
+      </c>
+      <c r="O251">
+        <v>19.71</v>
+      </c>
+      <c r="P251">
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="252" spans="1:16">
+      <c r="A252" t="s">
+        <v>16</v>
+      </c>
+      <c r="B252" t="s">
+        <v>26</v>
+      </c>
+      <c r="C252" t="s">
+        <v>76</v>
+      </c>
+      <c r="D252">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="E252" t="s">
+        <v>77</v>
+      </c>
+      <c r="F252" t="s">
+        <v>80</v>
+      </c>
+      <c r="G252" t="s">
+        <v>81</v>
+      </c>
+      <c r="H252">
+        <v>564.85</v>
+      </c>
+      <c r="I252">
+        <v>3.599999999999994</v>
+      </c>
+      <c r="J252" t="s">
+        <v>83</v>
+      </c>
+      <c r="K252">
+        <v>1</v>
+      </c>
+      <c r="L252" t="s">
+        <v>100</v>
+      </c>
+      <c r="M252" t="s">
+        <v>101</v>
+      </c>
+      <c r="N252" t="s">
+        <v>111</v>
+      </c>
+      <c r="O252">
+        <v>19.71</v>
+      </c>
+      <c r="P252">
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="253" spans="1:16">
+      <c r="A253" t="s">
+        <v>16</v>
+      </c>
+      <c r="B253" t="s">
+        <v>71</v>
+      </c>
+      <c r="C253" t="s">
+        <v>76</v>
+      </c>
+      <c r="D253">
+        <v>66.40000000000001</v>
+      </c>
+      <c r="E253" t="s">
+        <v>77</v>
+      </c>
+      <c r="F253" t="s">
+        <v>80</v>
+      </c>
+      <c r="G253" t="s">
+        <v>81</v>
+      </c>
+      <c r="H253">
+        <v>3517.6</v>
+      </c>
+      <c r="I253">
+        <v>3.599999999999994</v>
+      </c>
+      <c r="J253" t="s">
+        <v>83</v>
+      </c>
+      <c r="K253">
+        <v>1</v>
+      </c>
+      <c r="L253" t="s">
+        <v>100</v>
+      </c>
+      <c r="M253" t="s">
+        <v>101</v>
+      </c>
+      <c r="N253" t="s">
+        <v>111</v>
+      </c>
+      <c r="O253">
+        <v>19.71</v>
+      </c>
+      <c r="P253">
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="254" spans="1:16">
+      <c r="A254" t="s">
+        <v>16</v>
+      </c>
+      <c r="B254" t="s">
+        <v>34</v>
+      </c>
+      <c r="C254" t="s">
+        <v>76</v>
+      </c>
+      <c r="D254">
+        <v>65</v>
+      </c>
+      <c r="E254" t="s">
+        <v>77</v>
+      </c>
+      <c r="F254" t="s">
+        <v>80</v>
+      </c>
+      <c r="G254" t="s">
+        <v>81</v>
+      </c>
+      <c r="H254">
+        <v>8033</v>
+      </c>
+      <c r="I254">
+        <v>5</v>
+      </c>
+      <c r="J254" t="s">
+        <v>83</v>
+      </c>
+      <c r="K254">
+        <v>1</v>
+      </c>
+      <c r="L254" t="s">
+        <v>100</v>
+      </c>
+      <c r="M254" t="s">
+        <v>101</v>
+      </c>
+      <c r="N254" t="s">
+        <v>111</v>
+      </c>
+      <c r="O254">
+        <v>19.71</v>
+      </c>
+      <c r="P254">
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="255" spans="1:16">
+      <c r="A255" t="s">
+        <v>16</v>
+      </c>
+      <c r="B255" t="s">
+        <v>22</v>
+      </c>
+      <c r="C255" t="s">
+        <v>76</v>
+      </c>
+      <c r="D255">
+        <v>64</v>
+      </c>
+      <c r="E255" t="s">
+        <v>78</v>
+      </c>
+      <c r="F255" t="s">
+        <v>80</v>
+      </c>
+      <c r="G255" t="s">
+        <v>81</v>
+      </c>
+      <c r="H255">
+        <v>1365.9</v>
+      </c>
+      <c r="I255">
+        <v>6</v>
+      </c>
+      <c r="J255" t="s">
+        <v>83</v>
+      </c>
+      <c r="K255">
+        <v>20</v>
+      </c>
+      <c r="L255" t="s">
+        <v>95</v>
+      </c>
+      <c r="M255" t="s">
+        <v>101</v>
+      </c>
+      <c r="N255" t="s">
+        <v>111</v>
+      </c>
+      <c r="O255">
+        <v>19.71</v>
+      </c>
+      <c r="P255">
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="256" spans="1:16">
+      <c r="A256" t="s">
+        <v>16</v>
+      </c>
+      <c r="B256" t="s">
+        <v>39</v>
+      </c>
+      <c r="C256" t="s">
+        <v>76</v>
+      </c>
+      <c r="D256">
+        <v>63.9</v>
+      </c>
+      <c r="E256" t="s">
+        <v>77</v>
+      </c>
+      <c r="F256" t="s">
+        <v>80</v>
+      </c>
+      <c r="G256" t="s">
+        <v>81</v>
+      </c>
+      <c r="H256">
+        <v>401.85</v>
+      </c>
+      <c r="I256">
+        <v>6.100000000000001</v>
+      </c>
+      <c r="J256" t="s">
+        <v>83</v>
+      </c>
+      <c r="K256">
+        <v>10</v>
+      </c>
+      <c r="L256" t="s">
+        <v>97</v>
+      </c>
+      <c r="M256" t="s">
+        <v>101</v>
+      </c>
+      <c r="N256" t="s">
+        <v>111</v>
+      </c>
+      <c r="O256">
+        <v>19.71</v>
+      </c>
+      <c r="P256">
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="257" spans="1:16">
+      <c r="A257" t="s">
+        <v>16</v>
+      </c>
+      <c r="B257" t="s">
+        <v>27</v>
+      </c>
+      <c r="C257" t="s">
+        <v>76</v>
+      </c>
+      <c r="D257">
+        <v>63.9</v>
+      </c>
+      <c r="E257" t="s">
+        <v>77</v>
+      </c>
+      <c r="F257" t="s">
+        <v>80</v>
+      </c>
+      <c r="G257" t="s">
+        <v>81</v>
+      </c>
+      <c r="H257">
+        <v>453.4</v>
+      </c>
+      <c r="I257">
+        <v>6.100000000000001</v>
+      </c>
+      <c r="J257" t="s">
+        <v>83</v>
+      </c>
+      <c r="K257">
+        <v>1</v>
+      </c>
+      <c r="L257" t="s">
+        <v>100</v>
+      </c>
+      <c r="M257" t="s">
+        <v>101</v>
+      </c>
+      <c r="N257" t="s">
+        <v>111</v>
+      </c>
+      <c r="O257">
+        <v>19.71</v>
+      </c>
+      <c r="P257">
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="258" spans="1:16">
+      <c r="A258" t="s">
+        <v>16</v>
+      </c>
+      <c r="B258" t="s">
+        <v>72</v>
+      </c>
+      <c r="C258" t="s">
+        <v>76</v>
+      </c>
+      <c r="D258">
+        <v>63.8</v>
+      </c>
+      <c r="E258" t="s">
+        <v>77</v>
+      </c>
+      <c r="F258" t="s">
+        <v>80</v>
+      </c>
+      <c r="G258" t="s">
+        <v>81</v>
+      </c>
+      <c r="H258">
+        <v>705.25</v>
+      </c>
+      <c r="I258">
+        <v>6.200000000000003</v>
+      </c>
+      <c r="J258" t="s">
+        <v>85</v>
+      </c>
+      <c r="K258">
+        <v>1</v>
+      </c>
+      <c r="L258" t="s">
+        <v>100</v>
+      </c>
+      <c r="M258" t="s">
+        <v>101</v>
+      </c>
+      <c r="N258" t="s">
+        <v>111</v>
+      </c>
+      <c r="O258">
+        <v>19.71</v>
+      </c>
+      <c r="P258">
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="259" spans="1:16">
+      <c r="A259" t="s">
+        <v>16</v>
+      </c>
+      <c r="B259" t="s">
+        <v>25</v>
+      </c>
+      <c r="C259" t="s">
+        <v>76</v>
+      </c>
+      <c r="D259">
+        <v>61.5</v>
+      </c>
+      <c r="E259" t="s">
+        <v>77</v>
+      </c>
+      <c r="F259" t="s">
+        <v>80</v>
+      </c>
+      <c r="G259" t="s">
+        <v>81</v>
+      </c>
+      <c r="H259">
+        <v>1093.2</v>
+      </c>
+      <c r="I259">
+        <v>8.5</v>
+      </c>
+      <c r="J259" t="s">
+        <v>85</v>
+      </c>
+      <c r="K259">
+        <v>1</v>
+      </c>
+      <c r="L259" t="s">
+        <v>100</v>
+      </c>
+      <c r="M259" t="s">
+        <v>101</v>
+      </c>
+      <c r="N259" t="s">
+        <v>111</v>
+      </c>
+      <c r="O259">
+        <v>19.71</v>
+      </c>
+      <c r="P259">
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="260" spans="1:16">
+      <c r="A260" t="s">
+        <v>16</v>
+      </c>
+      <c r="B260" t="s">
+        <v>32</v>
+      </c>
+      <c r="C260" t="s">
+        <v>76</v>
+      </c>
+      <c r="D260">
+        <v>61.4</v>
+      </c>
+      <c r="E260" t="s">
+        <v>77</v>
+      </c>
+      <c r="F260" t="s">
+        <v>80</v>
+      </c>
+      <c r="G260" t="s">
+        <v>81</v>
+      </c>
+      <c r="H260">
+        <v>1421.3</v>
+      </c>
+      <c r="I260">
+        <v>8.600000000000001</v>
+      </c>
+      <c r="J260" t="s">
+        <v>85</v>
+      </c>
+      <c r="K260">
+        <v>15</v>
+      </c>
+      <c r="L260" t="s">
+        <v>94</v>
+      </c>
+      <c r="M260" t="s">
+        <v>101</v>
+      </c>
+      <c r="N260" t="s">
+        <v>111</v>
+      </c>
+      <c r="O260">
+        <v>19.71</v>
+      </c>
+      <c r="P260">
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="261" spans="1:16">
+      <c r="A261" t="s">
+        <v>16</v>
+      </c>
+      <c r="B261" t="s">
+        <v>36</v>
+      </c>
+      <c r="C261" t="s">
+        <v>76</v>
+      </c>
+      <c r="D261">
+        <v>61.4</v>
+      </c>
+      <c r="E261" t="s">
+        <v>77</v>
+      </c>
+      <c r="F261" t="s">
+        <v>80</v>
+      </c>
+      <c r="G261" t="s">
+        <v>81</v>
+      </c>
+      <c r="H261">
+        <v>1033.65</v>
+      </c>
+      <c r="I261">
+        <v>8.600000000000001</v>
+      </c>
+      <c r="J261" t="s">
+        <v>85</v>
+      </c>
+      <c r="K261">
+        <v>1</v>
+      </c>
+      <c r="L261" t="s">
+        <v>100</v>
+      </c>
+      <c r="M261" t="s">
+        <v>101</v>
+      </c>
+      <c r="N261" t="s">
+        <v>111</v>
+      </c>
+      <c r="O261">
+        <v>19.71</v>
+      </c>
+      <c r="P261">
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="262" spans="1:16">
+      <c r="A262" t="s">
+        <v>16</v>
+      </c>
+      <c r="B262" t="s">
+        <v>23</v>
+      </c>
+      <c r="C262" t="s">
+        <v>76</v>
+      </c>
+      <c r="D262">
+        <v>61</v>
+      </c>
+      <c r="E262" t="s">
+        <v>77</v>
+      </c>
+      <c r="F262" t="s">
+        <v>80</v>
+      </c>
+      <c r="G262" t="s">
+        <v>81</v>
+      </c>
+      <c r="H262">
+        <v>4410</v>
+      </c>
+      <c r="I262">
+        <v>9</v>
+      </c>
+      <c r="J262" t="s">
+        <v>83</v>
+      </c>
+      <c r="K262">
+        <v>20</v>
+      </c>
+      <c r="L262" t="s">
+        <v>95</v>
+      </c>
+      <c r="M262" t="s">
+        <v>101</v>
+      </c>
+      <c r="N262" t="s">
+        <v>111</v>
+      </c>
+      <c r="O262">
+        <v>19.71</v>
+      </c>
+      <c r="P262">
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="263" spans="1:16">
+      <c r="A263" t="s">
+        <v>16</v>
+      </c>
+      <c r="B263" t="s">
+        <v>23</v>
+      </c>
+      <c r="C263" t="s">
+        <v>76</v>
+      </c>
+      <c r="D263">
+        <v>61</v>
+      </c>
+      <c r="E263" t="s">
+        <v>77</v>
+      </c>
+      <c r="F263" t="s">
+        <v>80</v>
+      </c>
+      <c r="G263" t="s">
+        <v>81</v>
+      </c>
+      <c r="H263">
+        <v>4410</v>
+      </c>
+      <c r="I263">
+        <v>9</v>
+      </c>
+      <c r="J263" t="s">
+        <v>83</v>
+      </c>
+      <c r="K263">
+        <v>20</v>
+      </c>
+      <c r="L263" t="s">
+        <v>95</v>
+      </c>
+      <c r="M263" t="s">
+        <v>101</v>
+      </c>
+      <c r="N263" t="s">
+        <v>111</v>
+      </c>
+      <c r="O263">
+        <v>19.71</v>
+      </c>
+      <c r="P263">
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="264" spans="1:16">
+      <c r="A264" t="s">
+        <v>16</v>
+      </c>
+      <c r="B264" t="s">
+        <v>28</v>
+      </c>
+      <c r="C264" t="s">
+        <v>76</v>
+      </c>
+      <c r="D264">
+        <v>61</v>
+      </c>
+      <c r="E264" t="s">
+        <v>77</v>
+      </c>
+      <c r="F264" t="s">
+        <v>80</v>
+      </c>
+      <c r="G264" t="s">
+        <v>81</v>
+      </c>
+      <c r="H264">
+        <v>193.37</v>
+      </c>
+      <c r="I264">
+        <v>9</v>
+      </c>
+      <c r="J264" t="s">
+        <v>83</v>
+      </c>
+      <c r="K264">
+        <v>1</v>
+      </c>
+      <c r="L264" t="s">
+        <v>100</v>
+      </c>
+      <c r="M264" t="s">
+        <v>101</v>
+      </c>
+      <c r="N264" t="s">
+        <v>111</v>
+      </c>
+      <c r="O264">
+        <v>19.71</v>
+      </c>
+      <c r="P264">
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="265" spans="1:16">
+      <c r="A265" t="s">
+        <v>16</v>
+      </c>
+      <c r="B265" t="s">
+        <v>56</v>
+      </c>
+      <c r="C265" t="s">
+        <v>76</v>
+      </c>
+      <c r="D265">
+        <v>60.7</v>
+      </c>
+      <c r="E265" t="s">
+        <v>79</v>
+      </c>
+      <c r="F265" t="s">
+        <v>80</v>
+      </c>
+      <c r="G265" t="s">
+        <v>81</v>
+      </c>
+      <c r="H265">
+        <v>456</v>
+      </c>
+      <c r="I265">
+        <v>9.299999999999997</v>
+      </c>
+      <c r="J265" t="s">
+        <v>92</v>
+      </c>
+      <c r="K265">
+        <v>9</v>
+      </c>
+      <c r="L265" t="s">
+        <v>98</v>
+      </c>
+      <c r="M265" t="s">
+        <v>101</v>
+      </c>
+      <c r="N265" t="s">
+        <v>111</v>
+      </c>
+      <c r="O265">
+        <v>19.71</v>
+      </c>
+      <c r="P265">
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="266" spans="1:16">
+      <c r="A266" t="s">
+        <v>16</v>
+      </c>
+      <c r="B266" t="s">
+        <v>33</v>
+      </c>
+      <c r="C266" t="s">
+        <v>76</v>
+      </c>
+      <c r="D266">
+        <v>59.2</v>
+      </c>
+      <c r="E266" t="s">
+        <v>77</v>
+      </c>
+      <c r="F266" t="s">
+        <v>80</v>
+      </c>
+      <c r="G266" t="s">
+        <v>81</v>
+      </c>
+      <c r="H266">
+        <v>9576</v>
+      </c>
+      <c r="I266">
+        <v>10.8</v>
+      </c>
+      <c r="J266" t="s">
+        <v>83</v>
+      </c>
+      <c r="K266">
+        <v>20</v>
+      </c>
+      <c r="L266" t="s">
+        <v>95</v>
+      </c>
+      <c r="M266" t="s">
+        <v>101</v>
+      </c>
+      <c r="N266" t="s">
+        <v>111</v>
+      </c>
+      <c r="O266">
+        <v>19.71</v>
+      </c>
+      <c r="P266">
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="267" spans="1:16">
+      <c r="A267" t="s">
+        <v>16</v>
+      </c>
+      <c r="B267" t="s">
+        <v>73</v>
+      </c>
+      <c r="C267" t="s">
+        <v>76</v>
+      </c>
+      <c r="D267">
+        <v>57</v>
+      </c>
+      <c r="E267" t="s">
+        <v>77</v>
+      </c>
+      <c r="F267" t="s">
+        <v>80</v>
+      </c>
+      <c r="G267" t="s">
+        <v>81</v>
+      </c>
+      <c r="H267">
+        <v>3187.2</v>
+      </c>
+      <c r="I267">
+        <v>13</v>
+      </c>
+      <c r="J267" t="s">
+        <v>85</v>
+      </c>
+      <c r="K267">
+        <v>1</v>
+      </c>
+      <c r="L267" t="s">
+        <v>100</v>
+      </c>
+      <c r="M267" t="s">
+        <v>101</v>
+      </c>
+      <c r="N267" t="s">
+        <v>111</v>
+      </c>
+      <c r="O267">
+        <v>19.71</v>
+      </c>
+      <c r="P267">
+        <v>-128</v>
+      </c>
+    </row>
+    <row r="268" spans="1:16">
+      <c r="A268" t="s">
+        <v>16</v>
+      </c>
+      <c r="B268" t="s">
+        <v>74</v>
+      </c>
+      <c r="C268" t="s">
+        <v>76</v>
+      </c>
+      <c r="D268">
+        <v>56.4</v>
+      </c>
+      <c r="E268" t="s">
+        <v>77</v>
+      </c>
+      <c r="F268" t="s">
+        <v>80</v>
+      </c>
+      <c r="G268" t="s">
+        <v>81</v>
+      </c>
+      <c r="H268">
+        <v>1207.45</v>
+      </c>
+      <c r="I268">
+        <v>13.6</v>
+      </c>
+      <c r="J268" t="s">
+        <v>85</v>
+      </c>
+      <c r="K268">
+        <v>1</v>
+      </c>
+      <c r="L268" t="s">
+        <v>100</v>
+      </c>
+      <c r="M268" t="s">
+        <v>101</v>
+      </c>
+      <c r="N268" t="s">
+        <v>111</v>
+      </c>
+      <c r="O268">
+        <v>19.71</v>
+      </c>
+      <c r="P268">
+        <v>-128</v>
       </c>
     </row>
   </sheetData>
